--- a/public/monthly_review.xlsx
+++ b/public/monthly_review.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="섹터x수급" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'신고가 근접'!$A$5:$L$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'섹터x수급'!$A$4:$N$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'신고가 근접'!$A$5:$L$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'섹터x수급'!$A$4:$O$28</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -27,7 +27,7 @@
     <numFmt numFmtId="165" formatCode="+0;-0;0"/>
     <numFmt numFmtId="166" formatCode="+#,##0;-#,##0;0"/>
     <numFmt numFmtId="167" formatCode="+#,##0.0;-#,##0.0;0.0"/>
-    <numFmt numFmtId="168" formatCode="+0.0;-0.0;0.0"/>
+    <numFmt numFmtId="168" formatCode="+0.00;-0.00;0"/>
     <numFmt numFmtId="169" formatCode="#,##0.0"/>
     <numFmt numFmtId="170" formatCode="+0.00;-0.00;0.00"/>
   </numFmts>
@@ -425,6 +425,9 @@
     <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -467,22 +470,19 @@
     <xf numFmtId="168" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="168" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -929,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K158"/>
+  <dimension ref="A1:K156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.9" customWidth="1" style="15" min="1" max="1"/>
@@ -970,7 +970,7 @@
       </c>
       <c r="I2" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14 16:24 KST</t>
+          <t>2026-09-14 23:33 KST</t>
         </is>
       </c>
     </row>
@@ -983,7 +983,7 @@
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>9월 증시는 AI 반도체 기대감에 따른 급등과 인플레이션 공포 및 외국인 대규모 매도세가 충돌하며 극심한 변동성을 보인 한 달이었습니다.</t>
+          <t>9월 증시는 AI 반도체 기대감에 따른 일시적 급등 이후, 인플레이션 우려와 외국인 대규모 매도세가 겹치며 변동성이 확대된 한 달이었습니다.</t>
         </is>
       </c>
     </row>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="G52" s="17" t="inlineStr">
         <is>
-          <t>물가 지표 부담과 외국인·기관의 대규모 매도로 지수가 급락했습니다.</t>
+          <t>외국인과 기관의 대규모 매도세로 코스피가 3.99% 급락했습니다.</t>
         </is>
       </c>
     </row>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="G53" s="17" t="inlineStr">
         <is>
-          <t>밸류업 기대감에 보험·건설 섹터가 상승하며 지수를 방어했습니다.</t>
+          <t>보험·건설 섹터 강세에도 전 주체 매도세로 지수 차별화가 나타났습니다.</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="G54" s="17" t="inlineStr">
         <is>
-          <t>외국인과 기관의 강력한 동반 매수세가 지수 상승을 견인했습니다.</t>
+          <t>외국인과 기관의 강력한 동반 매수세가 지수 급등을 견인했습니다.</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="G55" s="17" t="inlineStr">
         <is>
-          <t>AI 반도체 기대감과 원화 강세로 대형주 중심의 급등세가 나타났습니다.</t>
+          <t>반도체 및 원전 기대감으로 코스피가 4.61% 급등했습니다.</t>
         </is>
       </c>
     </row>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="G56" s="17" t="inlineStr">
         <is>
-          <t>원전 수주 모멘텀에도 불구하고 개인의 매도세가 지수 상단을 제한했습니다.</t>
+          <t>개인 매도세가 지수 하락 압박을 가하며 코스피가 0.58% 하락했습니다.</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G57" s="17" t="inlineStr">
         <is>
-          <t>기관의 매수세가 유입되며 코스피 7,000선 안착을 시도했습니다.</t>
+          <t>기관 매수세 유입으로 코스피가 7,000선에 안착했습니다.</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="G58" s="17" t="inlineStr">
         <is>
-          <t>유가 급등과 금리 상승 부담으로 지수 간 차별화가 나타났습니다.</t>
+          <t>외국인 매도세와 기관 매수세가 엇갈리며 지수 혼조세를 보였습니다.</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="G59" s="17" t="inlineStr">
         <is>
-          <t>미국 PPI 상승과 기술주 투매 여파로 시장 전반이 급락했습니다.</t>
+          <t>인플레이션 우려와 기술주 투매로 코스피가 1.76% 급락했습니다.</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
               <color rgb="00D64545"/>
               <sz val="10"/>
             </rPr>
-            <t>209▲ 상한2</t>
+            <t>295▲ 상한2</t>
           </r>
           <r>
             <t>/</t>
@@ -2696,7 +2696,7 @@
               <color rgb="003182F6"/>
               <sz val="10"/>
             </rPr>
-            <t>289▼</t>
+            <t>498▼</t>
           </r>
         </is>
       </c>
@@ -2711,7 +2711,7 @@
               <color rgb="00D64545"/>
               <sz val="10"/>
             </rPr>
-            <t>449▲ 상한6</t>
+            <t>627▲ 상한7</t>
           </r>
           <r>
             <t>/</t>
@@ -2722,7 +2722,7 @@
               <color rgb="003182F6"/>
               <sz val="10"/>
             </rPr>
-            <t>513▼</t>
+            <t>900▼</t>
           </r>
         </is>
       </c>
@@ -2733,7 +2733,7 @@
       </c>
       <c r="G60" s="17" t="inlineStr">
         <is>
-          <t>외국인의 3.3조 원 규모 매도세가 쏟아지며 지수가 크게 하락했습니다.</t>
+          <t>외국인 3.3조 매도세가 쏟아지며 코스피가 3.26% 급락했습니다.</t>
         </is>
       </c>
     </row>
@@ -2774,28 +2774,28 @@
     <row r="64" ht="15" customHeight="1" s="15">
       <c r="A64" s="17" t="inlineStr">
         <is>
-          <t>- 8월 미국 PPI(5.4%)와 CPI(3.4%) 등 물가 지표가 인플레이션 압력을 지속시키며 금리 인하 기대감을 약화시켰습니다.</t>
+          <t>- 미국 PPI 상승과 국내 GDP 성장률 둔화 등 매크로 불확실성이 지속되었습니다.</t>
         </is>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1" s="15">
       <c r="A65" s="17" t="inlineStr">
         <is>
-          <t>- 국내 2분기 GDP 성장률이 0.6%로 둔화되는 등 매크로 환경의 불확실성이 증대되었습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="31" customHeight="1" s="15">
+          <t>- 건설(+11.03%) 및 기계·장비(+7.87%) 섹터는 기관 순매수 집중으로 강세를 보였습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="15" customHeight="1" s="15">
       <c r="A66" s="17" t="inlineStr">
         <is>
-          <t>- 수급 측면에서는 전기·전자 섹터에 외국인 매물이 집중된 반면, 건설(+11.03%)과 기계·장비(+7.87%)는 기관 순매수로 강세를 보였습니다.</t>
+          <t>- 전기·전자 섹터는 AI 속도조절론으로 외국인 매물이 집중되며 수급 이탈이 발생했습니다.</t>
         </is>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" s="15">
       <c r="A67" s="17" t="inlineStr">
         <is>
-          <t>- 외국인의 대규모 매도세 진정 여부와 반도체 관련 수출입 확정치가 향후 시장 방향성의 핵심 변수가 될 전망입니다.</t>
+          <t>- 외국인 매도세 진정 여부와 수출입 확정치가 향후 증시 반등의 핵심 변수가 될 것입니다.</t>
         </is>
       </c>
     </row>
@@ -2902,25 +2902,25 @@
         </is>
       </c>
       <c r="E71" s="29" t="n">
-        <v>9513</v>
+        <v>9488</v>
       </c>
       <c r="F71" s="28" t="n">
-        <v>-480</v>
+        <v>-501</v>
       </c>
       <c r="G71" s="29" t="n">
-        <v>9992</v>
+        <v>9989</v>
       </c>
       <c r="H71" s="28" t="n">
-        <v>-38</v>
+        <v>-11</v>
       </c>
       <c r="I71" s="31" t="n">
         <v>270.3</v>
       </c>
       <c r="J71" s="31" t="n">
-        <v>1951.1</v>
+        <v>1949.9</v>
       </c>
       <c r="K71" s="31" t="n">
-        <v>-1680.6</v>
+        <v>-1681.8</v>
       </c>
     </row>
     <row r="72">
@@ -2943,25 +2943,25 @@
         </is>
       </c>
       <c r="E72" s="29" t="n">
-        <v>5448</v>
+        <v>5533</v>
       </c>
       <c r="F72" s="29" t="n">
-        <v>4900</v>
+        <v>4998</v>
       </c>
       <c r="G72" s="29" t="n">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="H72" s="28" t="n">
-        <v>-793</v>
+        <v>-878</v>
       </c>
       <c r="I72" s="31" t="n">
         <v>535</v>
       </c>
       <c r="J72" s="31" t="n">
-        <v>5043.5</v>
+        <v>5185.7</v>
       </c>
       <c r="K72" s="31" t="n">
-        <v>-110.5</v>
+        <v>31.7</v>
       </c>
     </row>
     <row r="73">
@@ -2984,25 +2984,25 @@
         </is>
       </c>
       <c r="E73" s="29" t="n">
-        <v>3710</v>
+        <v>3704</v>
       </c>
       <c r="F73" s="29" t="n">
-        <v>2050</v>
+        <v>2055</v>
       </c>
       <c r="G73" s="29" t="n">
-        <v>1660</v>
+        <v>1649</v>
       </c>
       <c r="H73" s="28" t="n">
-        <v>-3678</v>
+        <v>-3673</v>
       </c>
       <c r="I73" s="31" t="n">
         <v>752.6</v>
       </c>
       <c r="J73" s="31" t="n">
-        <v>3487.9</v>
+        <v>3195.3</v>
       </c>
       <c r="K73" s="31" t="n">
-        <v>90.59999999999999</v>
+        <v>-202</v>
       </c>
     </row>
     <row r="74">
@@ -3016,34 +3016,34 @@
       </c>
       <c r="C74" s="31" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="D74" s="34" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>운송·창고</t>
         </is>
       </c>
       <c r="E74" s="29" t="n">
-        <v>2611</v>
+        <v>2245</v>
       </c>
       <c r="F74" s="29" t="n">
-        <v>4675</v>
-      </c>
-      <c r="G74" s="28" t="n">
-        <v>-2064</v>
+        <v>2207</v>
+      </c>
+      <c r="G74" s="29" t="n">
+        <v>38</v>
       </c>
       <c r="H74" s="28" t="n">
-        <v>-2624</v>
+        <v>-2193</v>
       </c>
       <c r="I74" s="31" t="n">
-        <v>2626.2</v>
+        <v>203.8</v>
       </c>
       <c r="J74" s="31" t="n">
-        <v>29118.3</v>
+        <v>1755.7</v>
       </c>
       <c r="K74" s="31" t="n">
-        <v>-1774</v>
+        <v>87</v>
       </c>
     </row>
     <row r="75">
@@ -3057,34 +3057,34 @@
       </c>
       <c r="C75" s="31" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>SK스퀘어</t>
         </is>
       </c>
       <c r="D75" s="34" t="inlineStr">
         <is>
-          <t>운송·창고</t>
+          <t>금융</t>
         </is>
       </c>
       <c r="E75" s="29" t="n">
-        <v>2245</v>
+        <v>2139</v>
       </c>
       <c r="F75" s="29" t="n">
-        <v>2207</v>
-      </c>
-      <c r="G75" s="29" t="n">
-        <v>38</v>
+        <v>4333</v>
+      </c>
+      <c r="G75" s="28" t="n">
+        <v>-2194</v>
       </c>
       <c r="H75" s="28" t="n">
-        <v>-2194</v>
+        <v>-2153</v>
       </c>
       <c r="I75" s="31" t="n">
-        <v>203.8</v>
+        <v>2629.7</v>
       </c>
       <c r="J75" s="31" t="n">
-        <v>1713.8</v>
+        <v>27337.7</v>
       </c>
       <c r="K75" s="31" t="n">
-        <v>45.1</v>
+        <v>-3554.6</v>
       </c>
     </row>
     <row r="76">
@@ -3139,34 +3139,34 @@
       </c>
       <c r="C77" s="31" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="D77" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>기계·장비</t>
         </is>
       </c>
       <c r="E77" s="29" t="n">
-        <v>1829</v>
-      </c>
-      <c r="F77" s="28" t="n">
-        <v>-22691</v>
+        <v>1759</v>
+      </c>
+      <c r="F77" s="29" t="n">
+        <v>889</v>
       </c>
       <c r="G77" s="29" t="n">
-        <v>24520</v>
+        <v>870</v>
       </c>
       <c r="H77" s="28" t="n">
-        <v>-52593</v>
+        <v>-1779</v>
       </c>
       <c r="I77" s="31" t="n">
-        <v>26543.5</v>
+        <v>527.2</v>
       </c>
       <c r="J77" s="31" t="n">
-        <v>231378.1</v>
+        <v>5999.4</v>
       </c>
       <c r="K77" s="31" t="n">
-        <v>1788.1</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="78">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="C78" s="31" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="D78" s="34" t="inlineStr">
@@ -3189,25 +3189,25 @@
         </is>
       </c>
       <c r="E78" s="29" t="n">
-        <v>1775</v>
-      </c>
-      <c r="F78" s="29" t="n">
-        <v>903</v>
+        <v>1705</v>
+      </c>
+      <c r="F78" s="28" t="n">
+        <v>-55</v>
       </c>
       <c r="G78" s="29" t="n">
-        <v>872</v>
+        <v>1760</v>
       </c>
       <c r="H78" s="28" t="n">
-        <v>-1815</v>
+        <v>-1675</v>
       </c>
       <c r="I78" s="31" t="n">
-        <v>527.1</v>
+        <v>1942.6</v>
       </c>
       <c r="J78" s="31" t="n">
-        <v>6082.4</v>
+        <v>15175.1</v>
       </c>
       <c r="K78" s="31" t="n">
-        <v>1287</v>
+        <v>768</v>
       </c>
     </row>
     <row r="79">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="C79" s="31" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="D79" s="34" t="inlineStr">
@@ -3230,25 +3230,25 @@
         </is>
       </c>
       <c r="E79" s="29" t="n">
-        <v>1702</v>
+        <v>1238</v>
       </c>
       <c r="F79" s="28" t="n">
-        <v>-56</v>
+        <v>-231</v>
       </c>
       <c r="G79" s="29" t="n">
-        <v>1758</v>
+        <v>1469</v>
       </c>
       <c r="H79" s="28" t="n">
-        <v>-1678</v>
+        <v>-1196</v>
       </c>
       <c r="I79" s="31" t="n">
-        <v>1942.6</v>
+        <v>845</v>
       </c>
       <c r="J79" s="31" t="n">
-        <v>15397.8</v>
+        <v>6416.6</v>
       </c>
       <c r="K79" s="31" t="n">
-        <v>990.7</v>
+        <v>-42.6</v>
       </c>
     </row>
     <row r="80">
@@ -3262,34 +3262,34 @@
       </c>
       <c r="C80" s="31" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="D80" s="34" t="inlineStr">
         <is>
-          <t>기계·장비</t>
+          <t>일반서비스</t>
         </is>
       </c>
       <c r="E80" s="29" t="n">
-        <v>1237</v>
-      </c>
-      <c r="F80" s="28" t="n">
-        <v>-231</v>
+        <v>815</v>
+      </c>
+      <c r="F80" s="29" t="n">
+        <v>214</v>
       </c>
       <c r="G80" s="29" t="n">
-        <v>1467</v>
+        <v>600</v>
       </c>
       <c r="H80" s="28" t="n">
-        <v>-1196</v>
+        <v>-823</v>
       </c>
       <c r="I80" s="31" t="n">
-        <v>844.9</v>
+        <v>170.4</v>
       </c>
       <c r="J80" s="31" t="n">
-        <v>6860.5</v>
+        <v>3413.8</v>
       </c>
       <c r="K80" s="31" t="n">
-        <v>401.3</v>
+        <v>128.4</v>
       </c>
     </row>
     <row r="81">
@@ -3312,25 +3312,25 @@
         </is>
       </c>
       <c r="E81" s="28" t="n">
-        <v>-39295</v>
+        <v>-44239</v>
       </c>
       <c r="F81" s="28" t="n">
-        <v>-35363</v>
+        <v>-38738</v>
       </c>
       <c r="G81" s="28" t="n">
-        <v>-3933</v>
+        <v>-5501</v>
       </c>
       <c r="H81" s="28" t="n">
-        <v>-69246</v>
+        <v>-64200</v>
       </c>
       <c r="I81" s="31" t="n">
-        <v>43355.1</v>
+        <v>43370.2</v>
       </c>
       <c r="J81" s="31" t="n">
-        <v>220014.1</v>
+        <v>205396.7</v>
       </c>
       <c r="K81" s="31" t="n">
-        <v>23392.2</v>
+        <v>8774.799999999999</v>
       </c>
     </row>
     <row r="82">
@@ -3353,25 +3353,25 @@
         </is>
       </c>
       <c r="E82" s="28" t="n">
-        <v>-4897</v>
+        <v>-5273</v>
       </c>
       <c r="F82" s="28" t="n">
-        <v>-3082</v>
+        <v>-3268</v>
       </c>
       <c r="G82" s="28" t="n">
-        <v>-1815</v>
+        <v>-2006</v>
       </c>
       <c r="H82" s="29" t="n">
-        <v>4728</v>
+        <v>5093</v>
       </c>
       <c r="I82" s="31" t="n">
-        <v>3352</v>
+        <v>3352.1</v>
       </c>
       <c r="J82" s="31" t="n">
-        <v>33246</v>
+        <v>32675</v>
       </c>
       <c r="K82" s="31" t="n">
-        <v>-7548.7</v>
+        <v>-8119.7</v>
       </c>
     </row>
     <row r="83">
@@ -3394,25 +3394,25 @@
         </is>
       </c>
       <c r="E83" s="28" t="n">
-        <v>-3488</v>
+        <v>-3688</v>
       </c>
       <c r="F83" s="28" t="n">
-        <v>-423</v>
+        <v>-519</v>
       </c>
       <c r="G83" s="28" t="n">
-        <v>-3065</v>
+        <v>-3169</v>
       </c>
       <c r="H83" s="29" t="n">
-        <v>3592</v>
+        <v>3805</v>
       </c>
       <c r="I83" s="31" t="n">
         <v>3582</v>
       </c>
       <c r="J83" s="31" t="n">
-        <v>30926.8</v>
+        <v>29634.7</v>
       </c>
       <c r="K83" s="31" t="n">
-        <v>651.6</v>
+        <v>-640.5</v>
       </c>
     </row>
     <row r="84">
@@ -3435,25 +3435,25 @@
         </is>
       </c>
       <c r="E84" s="28" t="n">
-        <v>-3212</v>
+        <v>-3197</v>
       </c>
       <c r="F84" s="28" t="n">
-        <v>-334</v>
+        <v>-325</v>
       </c>
       <c r="G84" s="28" t="n">
-        <v>-2877</v>
+        <v>-2872</v>
       </c>
       <c r="H84" s="29" t="n">
-        <v>3579</v>
+        <v>3565</v>
       </c>
       <c r="I84" s="31" t="n">
         <v>2921.6</v>
       </c>
       <c r="J84" s="31" t="n">
-        <v>13097</v>
+        <v>12346.5</v>
       </c>
       <c r="K84" s="31" t="n">
-        <v>-1528.8</v>
+        <v>-2279.3</v>
       </c>
     </row>
     <row r="85">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="C85" s="31" t="inlineStr">
         <is>
-          <t>LG이노텍</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="D85" s="34" t="inlineStr">
@@ -3476,25 +3476,25 @@
         </is>
       </c>
       <c r="E85" s="28" t="n">
-        <v>-2678</v>
+        <v>-2946</v>
       </c>
       <c r="F85" s="28" t="n">
-        <v>-1205</v>
-      </c>
-      <c r="G85" s="28" t="n">
-        <v>-1473</v>
-      </c>
-      <c r="H85" s="29" t="n">
-        <v>2633</v>
+        <v>-24762</v>
+      </c>
+      <c r="G85" s="29" t="n">
+        <v>21816</v>
+      </c>
+      <c r="H85" s="28" t="n">
+        <v>-47570</v>
       </c>
       <c r="I85" s="31" t="n">
-        <v>1941.8</v>
+        <v>26563.6</v>
       </c>
       <c r="J85" s="31" t="n">
-        <v>8526.200000000001</v>
+        <v>223221.9</v>
       </c>
       <c r="K85" s="31" t="n">
-        <v>-4639.3</v>
+        <v>-6368.1</v>
       </c>
     </row>
     <row r="86">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="C86" s="31" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>LG이노텍</t>
         </is>
       </c>
       <c r="D86" s="34" t="inlineStr">
@@ -3517,25 +3517,25 @@
         </is>
       </c>
       <c r="E86" s="28" t="n">
-        <v>-2225</v>
+        <v>-2678</v>
       </c>
       <c r="F86" s="28" t="n">
-        <v>-1114</v>
+        <v>-1205</v>
       </c>
       <c r="G86" s="28" t="n">
-        <v>-1111</v>
+        <v>-1473</v>
       </c>
       <c r="H86" s="29" t="n">
-        <v>2108</v>
+        <v>2633</v>
       </c>
       <c r="I86" s="31" t="n">
-        <v>1488.4</v>
+        <v>1941.8</v>
       </c>
       <c r="J86" s="31" t="n">
-        <v>13358.1</v>
+        <v>8526.200000000001</v>
       </c>
       <c r="K86" s="31" t="n">
-        <v>-2801.7</v>
+        <v>-4639.3</v>
       </c>
     </row>
     <row r="87">
@@ -3549,34 +3549,34 @@
       </c>
       <c r="C87" s="31" t="inlineStr">
         <is>
-          <t>에이피알</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="D87" s="34" t="inlineStr">
         <is>
-          <t>화학</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="E87" s="28" t="n">
-        <v>-1610</v>
+        <v>-2306</v>
       </c>
       <c r="F87" s="28" t="n">
-        <v>-155</v>
+        <v>-1140</v>
       </c>
       <c r="G87" s="28" t="n">
-        <v>-1455</v>
+        <v>-1166</v>
       </c>
       <c r="H87" s="29" t="n">
-        <v>1591</v>
+        <v>2195</v>
       </c>
       <c r="I87" s="31" t="n">
-        <v>520.6</v>
+        <v>1489</v>
       </c>
       <c r="J87" s="31" t="n">
-        <v>14373.7</v>
+        <v>12935.4</v>
       </c>
       <c r="K87" s="31" t="n">
-        <v>-1848.1</v>
+        <v>-3224.4</v>
       </c>
     </row>
     <row r="88">
@@ -3599,25 +3599,25 @@
         </is>
       </c>
       <c r="E88" s="28" t="n">
-        <v>-1601</v>
+        <v>-1732</v>
       </c>
       <c r="F88" s="29" t="n">
-        <v>1320</v>
+        <v>1218</v>
       </c>
       <c r="G88" s="28" t="n">
-        <v>-2921</v>
+        <v>-2951</v>
       </c>
       <c r="H88" s="29" t="n">
-        <v>1550</v>
+        <v>1691</v>
       </c>
       <c r="I88" s="31" t="n">
-        <v>777.1</v>
+        <v>777.2</v>
       </c>
       <c r="J88" s="31" t="n">
-        <v>5228.9</v>
+        <v>4815.1</v>
       </c>
       <c r="K88" s="31" t="n">
-        <v>-1028.1</v>
+        <v>-1441.9</v>
       </c>
     </row>
     <row r="89">
@@ -3631,34 +3631,34 @@
       </c>
       <c r="C89" s="31" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>에이피알</t>
         </is>
       </c>
       <c r="D89" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>화학</t>
         </is>
       </c>
       <c r="E89" s="28" t="n">
-        <v>-1376</v>
+        <v>-1675</v>
       </c>
       <c r="F89" s="28" t="n">
-        <v>-395</v>
+        <v>-196</v>
       </c>
       <c r="G89" s="28" t="n">
-        <v>-981</v>
+        <v>-1479</v>
       </c>
       <c r="H89" s="29" t="n">
-        <v>1368</v>
+        <v>1650</v>
       </c>
       <c r="I89" s="31" t="n">
-        <v>920.1</v>
+        <v>520.6</v>
       </c>
       <c r="J89" s="31" t="n">
-        <v>6593.5</v>
+        <v>13931.3</v>
       </c>
       <c r="K89" s="31" t="n">
-        <v>-452.9</v>
+        <v>-2290.5</v>
       </c>
     </row>
     <row r="90">
@@ -3672,34 +3672,34 @@
       </c>
       <c r="C90" s="31" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="D90" s="34" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="E90" s="28" t="n">
-        <v>-1322</v>
+        <v>-1405</v>
       </c>
       <c r="F90" s="28" t="n">
-        <v>-152</v>
+        <v>-417</v>
       </c>
       <c r="G90" s="28" t="n">
-        <v>-1170</v>
+        <v>-988</v>
       </c>
       <c r="H90" s="29" t="n">
-        <v>661</v>
+        <v>1401</v>
       </c>
       <c r="I90" s="31" t="n">
-        <v>477.5</v>
+        <v>920.1</v>
       </c>
       <c r="J90" s="31" t="n">
-        <v>11912</v>
+        <v>6279.6</v>
       </c>
       <c r="K90" s="31" t="n">
-        <v>-1179.4</v>
+        <v>-766.8</v>
       </c>
     </row>
     <row r="91"/>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="5" t="inlineStr">
-        <is>
-          <t>우리금융지주</t>
+    <row r="94" ht="31" customHeight="1" s="15">
+      <c r="A94" s="36" t="inlineStr">
+        <is>
+          <t>HD한국조선해양</t>
         </is>
       </c>
       <c r="B94" s="34" t="inlineStr">
@@ -3751,7 +3751,7 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="C94" s="36" t="n">
+      <c r="C94" s="37" t="n">
         <v>3</v>
       </c>
       <c r="D94" s="31" t="inlineStr"/>
@@ -3766,7 +3766,7 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="I94" s="37" t="n">
+      <c r="I94" s="38" t="n">
         <v>3</v>
       </c>
       <c r="J94" s="31" t="inlineStr"/>
@@ -3775,12 +3775,12 @@
     <row r="95" ht="44.5" customHeight="1" s="15">
       <c r="A95" s="17" t="inlineStr">
         <is>
-          <t>외국인 +4,900억 순매수, 기관 +548억 순매수, 대차잔고 -110억 감소 — 금융(동반강세) 섹터 추세 지속형 상방 관찰</t>
+          <t>외국인 +224억 순매수, 기관 +78억 순매수, 대차잔고 -58억 감소 — 금융(동반강세) 섹터 추세 지속형 상방 관찰</t>
         </is>
       </c>
       <c r="G95" s="17" t="inlineStr">
         <is>
-          <t>외국인 +13억 순매수, 기관 +18억 순매수, 대차잔고 -80억 감소 — 증권(수급유입) 섹터 초기 유입형 상방 관찰</t>
+          <t>외국인 +13억 순매수, 기관 +18억 순매수, 대차잔고 -73억 감소 — 증권(수급유입) 섹터 초기 유입형 상방 관찰</t>
         </is>
       </c>
     </row>
@@ -3795,14 +3795,14 @@
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="C96" s="36" t="n">
+      <c r="C96" s="37" t="n">
         <v>3</v>
       </c>
       <c r="D96" s="31" t="inlineStr"/>
       <c r="E96" s="31" t="inlineStr"/>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="H96" s="34" t="inlineStr">
@@ -3810,8 +3810,8 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="I96" s="37" t="n">
-        <v>3</v>
+      <c r="I96" s="38" t="n">
+        <v>1</v>
       </c>
       <c r="J96" s="31" t="inlineStr"/>
       <c r="K96" s="31" t="inlineStr"/>
@@ -3819,12 +3819,12 @@
     <row r="97" ht="44.5" customHeight="1" s="15">
       <c r="A97" s="17" t="inlineStr">
         <is>
-          <t>외국인 +163억 순매수, 기관 +75억 순매수, 대차잔고 -125억 감소 — 운송·창고(동반강세) 섹터 추세 지속형 상방 관찰</t>
+          <t>외국인 +175억 순매수, 기관 +68억 순매수, 대차잔고 -163억 감소 — 운송·창고(동반강세) 섹터 추세 지속형 상방 관찰</t>
         </is>
       </c>
       <c r="G97" s="17" t="inlineStr">
         <is>
-          <t>외국인 +1억 순매수, 기관 +22억 순매수, 대차잔고 -14억 감소 — 증권(수급유입) 섹터 초기 유입형 상방 관찰</t>
+          <t>외국인 +304억 순매수, 대차잔고 -28억 감소 — 증권(수급유입) 섹터 초기 유입형 상방 관찰</t>
         </is>
       </c>
     </row>
@@ -3839,14 +3839,14 @@
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="C98" s="36" t="n">
+      <c r="C98" s="37" t="n">
         <v>3</v>
       </c>
       <c r="D98" s="31" t="inlineStr"/>
       <c r="E98" s="31" t="inlineStr"/>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>키움증권</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="H98" s="34" t="inlineStr">
@@ -3854,7 +3854,7 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="I98" s="37" t="n">
+      <c r="I98" s="38" t="n">
         <v>1</v>
       </c>
       <c r="J98" s="31" t="inlineStr"/>
@@ -3863,34 +3863,34 @@
     <row r="99" ht="44.5" customHeight="1" s="15">
       <c r="A99" s="17" t="inlineStr">
         <is>
-          <t>외국인 +31억 순매수, 기관 +44억 순매수, 대차잔고 -11억 감소 — 운송·창고(동반강세) 섹터 추세 지속형 상방 관찰</t>
+          <t>외국인 +32억 순매수, 기관 +44억 순매수, 대차잔고 -10억 감소 — 운송·창고(동반강세) 섹터 추세 지속형 상방 관찰</t>
         </is>
       </c>
       <c r="G99" s="17" t="inlineStr">
         <is>
-          <t>외국인 +321억 순매수, 대차잔고 -36억 감소 — 증권(수급유입) 섹터 초기 유입형 상방 관찰</t>
+          <t>외국인 +667억 순매수, 대차잔고 -1,250억 감소 — 증권(수급유입) 섹터 초기 유입형 상방 관찰</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="B100" s="34" t="inlineStr">
         <is>
-          <t>운송·창고</t>
-        </is>
-      </c>
-      <c r="C100" s="36" t="n">
+          <t>금융</t>
+        </is>
+      </c>
+      <c r="C100" s="37" t="n">
         <v>1</v>
       </c>
       <c r="D100" s="31" t="inlineStr"/>
       <c r="E100" s="31" t="inlineStr"/>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
+          <t>키움증권</t>
         </is>
       </c>
       <c r="H100" s="34" t="inlineStr">
@@ -3898,7 +3898,7 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="I100" s="37" t="n">
+      <c r="I100" s="38" t="n">
         <v>1</v>
       </c>
       <c r="J100" s="31" t="inlineStr"/>
@@ -3907,34 +3907,34 @@
     <row r="101" ht="31" customHeight="1" s="15">
       <c r="A101" s="17" t="inlineStr">
         <is>
-          <t>외국인 +2,207억 순매수, 기관 +38억 순매수 — 운송·창고(동반강세) 섹터 추세 지속형 상방 관찰</t>
+          <t>외국인 +4,998억 순매수, 기관 +536억 순매수 — 금융(동반강세) 섹터 추세 지속형 상방 관찰</t>
         </is>
       </c>
       <c r="G101" s="17" t="inlineStr">
         <is>
-          <t>외국인 +660억 순매수, 대차잔고 -1,033억 감소 — 증권(수급유입) 섹터 초기 유입형 상방 관찰</t>
+          <t>외국인 +315억 순매수, 대차잔고 -11억 감소 — 증권(수급유입) 섹터 초기 유입형 상방 관찰</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B102" s="34" t="inlineStr">
         <is>
-          <t>일반서비스</t>
-        </is>
-      </c>
-      <c r="C102" s="36" t="n">
+          <t>운송·창고</t>
+        </is>
+      </c>
+      <c r="C102" s="37" t="n">
         <v>1</v>
       </c>
       <c r="D102" s="31" t="inlineStr"/>
       <c r="E102" s="31" t="inlineStr"/>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>SK증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="H102" s="34" t="inlineStr">
@@ -3942,7 +3942,7 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="I102" s="37" t="n">
+      <c r="I102" s="38" t="n">
         <v>1</v>
       </c>
       <c r="J102" s="31" t="inlineStr"/>
@@ -3951,23 +3951,23 @@
     <row r="103" ht="31" customHeight="1" s="15">
       <c r="A103" s="17" t="inlineStr">
         <is>
-          <t>외국인 +288억 순매수, 기관 +533억 순매수 — 일반서비스(동반강세) 섹터 추세 지속형 상방 관찰</t>
+          <t>외국인 +2,207억 순매수, 기관 +38억 순매수 — 운송·창고(동반강세) 섹터 추세 지속형 상방 관찰</t>
         </is>
       </c>
       <c r="G103" s="17" t="inlineStr">
         <is>
-          <t>외국인 +98억 순매수, 대차잔고 -55억 감소 — 증권(수급유입) 섹터 초기 유입형 상방 관찰</t>
+          <t>기관 +22억 순매수, 대차잔고 -10억 감소 — 증권(수급유입) 섹터 초기 유입형 상방 관찰</t>
         </is>
       </c>
     </row>
     <row r="104"/>
     <row r="105">
-      <c r="A105" s="38" t="inlineStr">
+      <c r="A105" s="39" t="inlineStr">
         <is>
           <t>● 수급이탈 — 상승 후 약화 관찰</t>
         </is>
       </c>
-      <c r="G105" s="39" t="inlineStr">
+      <c r="G105" s="40" t="inlineStr">
         <is>
           <t>● 동반약세 — 약세 지속형 하방 관찰</t>
         </is>
@@ -3984,13 +3984,13 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="H106" s="40" t="inlineStr">
+      <c r="H106" s="41" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="I106" s="41" t="n">
-        <v>-4</v>
+      <c r="I106" s="42" t="n">
+        <v>-2</v>
       </c>
       <c r="J106" s="31" t="inlineStr"/>
       <c r="K106" s="31" t="inlineStr"/>
@@ -3998,23 +3998,23 @@
     <row r="107" ht="44.5" customHeight="1" s="15">
       <c r="G107" s="17" t="inlineStr">
         <is>
-          <t>외국인 -423억 순매도, 기관 -3,065억 순매도, 대차잔고 +652억 증가, 공매도 누적 상위 등재 — 운송장비·부품(동반약세) 섹터 약세 지속형 하방 관찰</t>
+          <t>외국인 -519억 순매도, 기관 -3,169억 순매도, 공매도 누적 상위 등재 — 운송장비·부품(동반약세) 섹터 약세 지속형 하방 관찰</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="G108" s="5" t="inlineStr">
         <is>
-          <t>CR홀딩스</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="H108" s="34" t="inlineStr">
         <is>
-          <t>비금속</t>
-        </is>
-      </c>
-      <c r="I108" s="41" t="n">
-        <v>-3</v>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="I108" s="42" t="n">
+        <v>-1</v>
       </c>
       <c r="J108" s="31" t="inlineStr"/>
       <c r="K108" s="31" t="inlineStr"/>
@@ -4022,14 +4022,14 @@
     <row r="109" ht="31" customHeight="1" s="15">
       <c r="G109" s="17" t="inlineStr">
         <is>
-          <t>외국인 -4억 순매도, 기관 0억 순매도, 대차잔고 +0억 증가 — 비금속(동반약세) 섹터 약세 지속형 하방 관찰</t>
+          <t>외국인 -5억 순매도, 기관 -1,589억 순매도 — 제약(동반약세) 섹터 약세 지속형 하방 관찰</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="H110" s="34" t="inlineStr">
@@ -4037,7 +4037,7 @@
           <t>제약</t>
         </is>
       </c>
-      <c r="I110" s="41" t="n">
+      <c r="I110" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="J110" s="31" t="inlineStr"/>
@@ -4046,22 +4046,22 @@
     <row r="111" ht="31" customHeight="1" s="15">
       <c r="G111" s="17" t="inlineStr">
         <is>
-          <t>외국인 -152억 순매도, 기관 -1,170억 순매도 — 제약(동반약세) 섹터 약세 지속형 하방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
+          <t>외국인 -861억 순매도, 기관 -80억 순매도 — 제약(동반약세) 섹터 약세 지속형 하방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="31" customHeight="1" s="15">
       <c r="G112" s="5" t="inlineStr">
         <is>
-          <t>HLB</t>
-        </is>
-      </c>
-      <c r="H112" s="34" t="inlineStr">
-        <is>
-          <t>제약</t>
-        </is>
-      </c>
-      <c r="I112" s="41" t="n">
+          <t>현대로템</t>
+        </is>
+      </c>
+      <c r="H112" s="41" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
+        </is>
+      </c>
+      <c r="I112" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="J112" s="31" t="inlineStr"/>
@@ -4070,22 +4070,22 @@
     <row r="113" ht="31" customHeight="1" s="15">
       <c r="G113" s="17" t="inlineStr">
         <is>
-          <t>외국인 -859억 순매도, 기관 -80억 순매도 — 제약(동반약세) 섹터 약세 지속형 하방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="31" customHeight="1" s="15">
+          <t>외국인 -58억 순매도, 기관 -617억 순매도 — 운송장비·부품(동반약세) 섹터 약세 지속형 하방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
       <c r="G114" s="5" t="inlineStr">
         <is>
-          <t>현대로템</t>
-        </is>
-      </c>
-      <c r="H114" s="40" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
-        </is>
-      </c>
-      <c r="I114" s="41" t="n">
+          <t>카카오</t>
+        </is>
+      </c>
+      <c r="H114" s="34" t="inlineStr">
+        <is>
+          <t>IT 서비스</t>
+        </is>
+      </c>
+      <c r="I114" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="J114" s="31" t="inlineStr"/>
@@ -4094,13 +4094,13 @@
     <row r="115" ht="31" customHeight="1" s="15">
       <c r="G115" s="17" t="inlineStr">
         <is>
-          <t>외국인 -68억 순매도, 기관 -608억 순매도 — 운송장비·부품(동반약세) 섹터 약세 지속형 하방 관찰</t>
+          <t>외국인 -244억 순매도, 기관 -174억 순매도 — IT 서비스(동반약세) 섹터 약세 지속형 하방 관찰</t>
         </is>
       </c>
     </row>
     <row r="116"/>
     <row r="117" ht="31" customHeight="1" s="15">
-      <c r="A117" s="42" t="inlineStr">
+      <c r="A117" s="43" t="inlineStr">
         <is>
           <t>현재 확보된 월간 리뷰 데이터 유니버스(순매수 상위 30 등재 · 공매도/대차 랭킹 · 월간 촉매 · 신호 섹터 시총 상위 10) 기준 — 전 시장 스크리닝 아님 · 관찰 우선순위이며 매매 권유 아님</t>
         </is>
@@ -4143,42 +4143,42 @@
     <row r="121" ht="15" customHeight="1" s="15">
       <c r="A121" s="17" t="inlineStr">
         <is>
-          <t>- 월 초 지정학적 리스크와 인플레이션 우려로 시장이 위축되며 출발했습니다.</t>
+          <t>- 월 초 지정학적 리스크와 인플레이션 우려로 시장 위축이 지속됨.</t>
         </is>
       </c>
     </row>
     <row r="122" ht="15" customHeight="1" s="15">
       <c r="A122" s="17" t="inlineStr">
         <is>
-          <t>- 중순 AI 반도체 및 HBM 수요 기대감으로 코스피가 7,000선에 근접하는 강한 랠리를 연출했습니다.</t>
+          <t>- 중순 AI 반도체 및 HBM 수요 기대감으로 코스피가 7,000선에 근접하며 강세를 보임.</t>
         </is>
       </c>
     </row>
     <row r="123" ht="15" customHeight="1" s="15">
       <c r="A123" s="17" t="inlineStr">
         <is>
-          <t>- 미국 고용지표 호조와 PPI 상승이 금리 인하 기대감을 후퇴시키며 투자 심리가 악화되었습니다.</t>
+          <t>- 미국 생산자물가지수(PPI) 상승 및 고용지표 호조로 금리 인하 기대감이 후퇴함.</t>
         </is>
       </c>
     </row>
     <row r="124" ht="15" customHeight="1" s="15">
       <c r="A124" s="17" t="inlineStr">
         <is>
-          <t>- 국제유가 급등과 인플레이션 공포가 시장 하방 압력으로 작용했습니다.</t>
+          <t>- 국제유가 급등 등 매크로 불확실성이 증대되며 시장 하방 압력으로 작용함.</t>
         </is>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1" s="15">
       <c r="A125" s="17" t="inlineStr">
         <is>
-          <t>- 월 후반 외국인의 대규모 매도세가 집중되며 지수 급락세가 시현되었습니다.</t>
+          <t>- 주 후반 미국발 'AI 속도조절론'이 부각되며 외국인 대규모 매도세가 출회됨.</t>
         </is>
       </c>
     </row>
     <row r="126" ht="15" customHeight="1" s="15">
       <c r="A126" s="17" t="inlineStr">
         <is>
-          <t>- 개인 투자자의 대규모 순매수에도 불구하고 외국인과 기관의 동반 매도세가 지수 하락을 주도했습니다.</t>
+          <t>- 전기·전자 섹터 중심의 급락으로 지수 변동성이 크게 확대됨.</t>
         </is>
       </c>
     </row>
@@ -4207,28 +4207,28 @@
     <row r="129" ht="15" customHeight="1" s="15">
       <c r="A129" s="17" t="inlineStr">
         <is>
-          <t>- 월 초 보험·금융 등 밸류업 관련주가 강세를 보였으나 이후 순환매가 발생했습니다.</t>
+          <t>- 초반 AI 반도체 및 HBM 관련주가 시장 상승을 주도함.</t>
         </is>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1" s="15">
       <c r="A130" s="17" t="inlineStr">
         <is>
-          <t>- 중순 AI 반도체 및 HBM 기대감으로 전기·전자 섹터가 시장 상승을 주도했습니다.</t>
+          <t>- 원전 및 전력 설비 관련주는 대형 수주 모멘텀으로 건설 및 기계·장비 섹터의 강세를 견인함.</t>
         </is>
       </c>
     </row>
     <row r="131" ht="15" customHeight="1" s="15">
       <c r="A131" s="17" t="inlineStr">
         <is>
-          <t>- 원전 및 전력 설비 모멘텀으로 건설 및 기계·장비 섹터가 지속적인 강세를 보였습니다.</t>
+          <t>- 인플레이션 우려 고조 시 보험 등 금리 상승 수혜주로 수급이 이동하는 순환매가 나타남.</t>
         </is>
       </c>
     </row>
     <row r="132" ht="15" customHeight="1" s="15">
       <c r="A132" s="17" t="inlineStr">
         <is>
-          <t>- 월 후반 인플레이션 우려 고조로 방어적 성격의 운송·창고 및 오락·문화 섹터로 수급이 분산되었습니다.</t>
+          <t>- 주 후반 AI 속도조절론으로 전기·전자 섹터에서 대규모 수급 이탈이 발생함.</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
         </is>
       </c>
       <c r="F136" s="29" t="n">
-        <v>55.03</v>
+        <v>53.62</v>
       </c>
       <c r="G136" s="17" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         </is>
       </c>
       <c r="F138" s="29" t="n">
-        <v>69.90000000000001</v>
+        <v>68.08</v>
       </c>
       <c r="G138" s="17" t="inlineStr">
         <is>
@@ -4403,12 +4403,12 @@
     <row r="139" ht="31" customHeight="1" s="15">
       <c r="A139" s="31" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B139" s="31" t="inlineStr">
         <is>
-          <t>우리로</t>
+          <t>카티스</t>
         </is>
       </c>
       <c r="C139" s="31" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="D139" s="34" t="inlineStr">
         <is>
-          <t>유통</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E139" s="14" t="inlineStr">
@@ -4427,11 +4427,11 @@
         </is>
       </c>
       <c r="F139" s="29" t="n">
-        <v>47.53</v>
+        <v>74.81</v>
       </c>
       <c r="G139" s="17" t="inlineStr">
         <is>
-          <t>미국 양자컴퓨터 투자 및 AI 광통신 관련주로 시장 관심 집중.</t>
+          <t>사상 최대 수주잔고 확보 및 AI 데이터센터 수주 확대에 따른 실적 턴어라운드 기대.</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="B140" s="31" t="inlineStr">
         <is>
-          <t>카티스</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="C140" s="31" t="inlineStr">
@@ -4462,11 +4462,11 @@
         </is>
       </c>
       <c r="F140" s="29" t="n">
-        <v>74.81</v>
+        <v>71.7</v>
       </c>
       <c r="G140" s="17" t="inlineStr">
         <is>
-          <t>사상 최대 수주잔고 확보 및 AI 데이터센터 수주 확대에 따른 실적 턴어라운드 기대.</t>
+          <t>엔비디아 CEO의 사이버 보안 핵심 시장 언급에 따른 보안주 수혜 기대감으로 상한가.</t>
         </is>
       </c>
     </row>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="B141" s="31" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="C141" s="31" t="inlineStr">
@@ -4497,11 +4497,11 @@
         </is>
       </c>
       <c r="F141" s="29" t="n">
-        <v>62.11</v>
+        <v>45.47</v>
       </c>
       <c r="G141" s="17" t="inlineStr">
         <is>
-          <t>엔비디아 CEO의 사이버 보안 핵심 시장 언급에 따른 보안주 수혜 기대감으로 상한가.</t>
+          <t>엔비디아 CEO의 사이버 보안 강조 발언에 따른 보안 솔루션 수요 증가 기대감으로 상한가.</t>
         </is>
       </c>
     </row>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="B142" s="31" t="inlineStr">
         <is>
-          <t>알파칩스</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="C142" s="31" t="inlineStr">
@@ -4532,11 +4532,11 @@
         </is>
       </c>
       <c r="F142" s="29" t="n">
-        <v>45.79</v>
+        <v>45.09</v>
       </c>
       <c r="G142" s="17" t="inlineStr">
         <is>
-          <t>관계사 포스텍의 차세대 CPO 광반도체 부품 양산 본격화 소식으로 상한가.</t>
+          <t>AI 데이터센터 및 ESS 시장 확대에 따른 MLCC 매출 증가 기대감으로 상한가 기록.</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="B143" s="31" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>알파칩스</t>
         </is>
       </c>
       <c r="C143" s="31" t="inlineStr">
@@ -4567,11 +4567,11 @@
         </is>
       </c>
       <c r="F143" s="29" t="n">
-        <v>44.26</v>
+        <v>44.93</v>
       </c>
       <c r="G143" s="17" t="inlineStr">
         <is>
-          <t>AI 데이터센터 및 ESS 시장 확대에 따른 MLCC 매출 증가 기대감으로 상한가 기록.</t>
+          <t>관계사 포스텍의 차세대 CPO 광반도체 부품 양산 본격화 소식으로 상한가.</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
         </is>
       </c>
       <c r="F147" s="29" t="n">
-        <v>5.01</v>
+        <v>5.49</v>
       </c>
       <c r="G147" s="17" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         </is>
       </c>
       <c r="F148" s="29" t="n">
-        <v>0.54</v>
+        <v>1.62</v>
       </c>
       <c r="G148" s="17" t="inlineStr">
         <is>
@@ -4775,68 +4775,53 @@
     <row r="151" ht="15" customHeight="1" s="15">
       <c r="A151" s="17" t="inlineStr">
         <is>
-          <t>- FOMC 금리 결정 이후 불확실성 해소 시 반등</t>
+          <t>- 외국인 매도세 진정 및 반도체 기술적 반등</t>
         </is>
       </c>
     </row>
     <row r="152" ht="15" customHeight="1" s="15">
       <c r="A152" s="17" t="inlineStr">
         <is>
-          <t>- 반도체 수출입 확정치 개선에 따른 기술주 회복</t>
+          <t>- FOMC 매파적 기조 확인 및 인플레이션 우려 지속</t>
         </is>
       </c>
     </row>
     <row r="153" ht="15" customHeight="1" s="15">
       <c r="A153" s="17" t="inlineStr">
         <is>
-          <t>- 미국 물가 지표 및 금리 결정에 따른 긴축 우려 지속</t>
+          <t>- 외국인 수급 전환 여부가 시장 방향성을 결정할 핵심 신호입니다.</t>
         </is>
       </c>
     </row>
     <row r="154" ht="15" customHeight="1" s="15">
       <c r="A154" s="17" t="inlineStr">
         <is>
-          <t>- 외국인 매도세 지속 시 지수 하방 압력 가중</t>
+          <t>- FOMC 기준금리 결정</t>
         </is>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1" s="15">
       <c r="A155" s="17" t="inlineStr">
         <is>
-          <t>- 외국인의 대규모 매도세 진정 여부와 반도체 섹터로의 수급 재유입이 지수 반등의 핵심 신호입니다.</t>
+          <t>- 무역수지 발표</t>
         </is>
       </c>
     </row>
     <row r="156" ht="15" customHeight="1" s="15">
       <c r="A156" s="17" t="inlineStr">
         <is>
-          <t>- 미국 중앙은행 기준금리 결정(9/17)</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="15" customHeight="1" s="15">
-      <c r="A157" s="17" t="inlineStr">
-        <is>
-          <t>- 미국 소매판매(9/16)</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="15" customHeight="1" s="15">
-      <c r="A158" s="17" t="inlineStr">
-        <is>
-          <t>- 국내 무역수지(9/15)</t>
+          <t>- 생산자물가지수 발표</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="75">
+  <mergeCells count="73">
     <mergeCell ref="G56:K56"/>
     <mergeCell ref="G52:K52"/>
     <mergeCell ref="G59:K59"/>
     <mergeCell ref="G105:K105"/>
     <mergeCell ref="A1:G2"/>
     <mergeCell ref="A130:K130"/>
-    <mergeCell ref="A157:K157"/>
     <mergeCell ref="A64:K64"/>
     <mergeCell ref="G115:K115"/>
     <mergeCell ref="A103:E103"/>
@@ -4862,7 +4847,6 @@
     <mergeCell ref="G93:K93"/>
     <mergeCell ref="G137:K137"/>
     <mergeCell ref="G146:K146"/>
-    <mergeCell ref="A158:K158"/>
     <mergeCell ref="A105:E105"/>
     <mergeCell ref="A95:E95"/>
     <mergeCell ref="A101:E101"/>
@@ -4916,7 +4900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.5" customWidth="1" style="15" min="1" max="1"/>
@@ -4995,62 +4979,62 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="43" t="inlineStr">
+      <c r="A5" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B5" s="43" t="inlineStr">
+      <c r="B5" s="44" t="inlineStr">
         <is>
           <t>시장</t>
         </is>
       </c>
-      <c r="C5" s="43" t="inlineStr">
+      <c r="C5" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D5" s="43" t="inlineStr">
+      <c r="D5" s="44" t="inlineStr">
         <is>
           <t>합산</t>
         </is>
       </c>
-      <c r="E5" s="43" t="inlineStr">
+      <c r="E5" s="44" t="inlineStr">
         <is>
           <t>외인</t>
         </is>
       </c>
-      <c r="F5" s="43" t="inlineStr">
+      <c r="F5" s="44" t="inlineStr">
         <is>
           <t>기관</t>
         </is>
       </c>
-      <c r="G5" s="43" t="inlineStr">
+      <c r="G5" s="44" t="inlineStr">
         <is>
           <t>개인</t>
         </is>
       </c>
-      <c r="H5" s="43" t="inlineStr">
+      <c r="H5" s="44" t="inlineStr">
         <is>
           <t>공매도</t>
         </is>
       </c>
-      <c r="I5" s="43" t="inlineStr">
+      <c r="I5" s="44" t="inlineStr">
         <is>
           <t>대차잔고</t>
         </is>
       </c>
-      <c r="J5" s="43" t="inlineStr">
+      <c r="J5" s="44" t="inlineStr">
         <is>
           <t>대차증감</t>
         </is>
       </c>
-      <c r="K5" s="43" t="inlineStr">
+      <c r="K5" s="44" t="inlineStr">
         <is>
           <t>월간등락(%)</t>
         </is>
       </c>
-      <c r="L5" s="43" t="inlineStr">
+      <c r="L5" s="44" t="inlineStr">
         <is>
           <t>신고가대비(%)</t>
         </is>
@@ -5072,32 +5056,32 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D6" s="44" t="n">
-        <v>716</v>
-      </c>
-      <c r="E6" s="45" t="n">
-        <v>-218</v>
-      </c>
-      <c r="F6" s="44" t="n">
-        <v>934</v>
-      </c>
-      <c r="G6" s="45" t="n">
-        <v>-673</v>
-      </c>
-      <c r="H6" s="46" t="n">
+      <c r="D6" s="45" t="n">
+        <v>705</v>
+      </c>
+      <c r="E6" s="46" t="n">
+        <v>-184</v>
+      </c>
+      <c r="F6" s="45" t="n">
+        <v>889</v>
+      </c>
+      <c r="G6" s="46" t="n">
+        <v>-663</v>
+      </c>
+      <c r="H6" s="47" t="n">
         <v>1778.1</v>
       </c>
-      <c r="I6" s="46" t="n">
-        <v>6747.5</v>
-      </c>
-      <c r="J6" s="47" t="n">
-        <v>-475.2</v>
-      </c>
-      <c r="K6" s="48" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="L6" s="49" t="n">
-        <v>-7.58</v>
+      <c r="I6" s="47" t="n">
+        <v>6793.5</v>
+      </c>
+      <c r="J6" s="48" t="n">
+        <v>-429.2</v>
+      </c>
+      <c r="K6" s="49" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="L6" s="50" t="n">
+        <v>-7.34</v>
       </c>
     </row>
     <row r="7">
@@ -5116,32 +5100,32 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D7" s="44" t="n">
-        <v>714</v>
-      </c>
-      <c r="E7" s="45" t="n">
-        <v>-1250</v>
-      </c>
-      <c r="F7" s="44" t="n">
-        <v>1965</v>
-      </c>
-      <c r="G7" s="45" t="n">
-        <v>-380</v>
-      </c>
-      <c r="H7" s="46" t="n">
-        <v>1714.8</v>
-      </c>
-      <c r="I7" s="46" t="n">
-        <v>7038.1</v>
-      </c>
-      <c r="J7" s="47" t="n">
-        <v>-78.59999999999999</v>
-      </c>
-      <c r="K7" s="48" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="L7" s="50" t="n">
-        <v>-1.92</v>
+      <c r="D7" s="45" t="n">
+        <v>719</v>
+      </c>
+      <c r="E7" s="46" t="n">
+        <v>-1200</v>
+      </c>
+      <c r="F7" s="45" t="n">
+        <v>1919</v>
+      </c>
+      <c r="G7" s="46" t="n">
+        <v>-386</v>
+      </c>
+      <c r="H7" s="47" t="n">
+        <v>1715.5</v>
+      </c>
+      <c r="I7" s="47" t="n">
+        <v>7357.9</v>
+      </c>
+      <c r="J7" s="51" t="n">
+        <v>241.2</v>
+      </c>
+      <c r="K7" s="49" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L7" s="52" t="n">
+        <v>-1.3</v>
       </c>
     </row>
     <row r="8">
@@ -5160,32 +5144,32 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D8" s="44" t="n">
-        <v>282</v>
-      </c>
-      <c r="E8" s="45" t="n">
-        <v>-187</v>
-      </c>
-      <c r="F8" s="44" t="n">
-        <v>469</v>
-      </c>
-      <c r="G8" s="45" t="n">
-        <v>-269</v>
-      </c>
-      <c r="H8" s="46" t="n">
-        <v>857.7</v>
-      </c>
-      <c r="I8" s="46" t="n">
-        <v>7004.4</v>
-      </c>
-      <c r="J8" s="47" t="n">
-        <v>-821</v>
-      </c>
-      <c r="K8" s="48" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L8" s="50" t="n">
-        <v>-1.93</v>
+      <c r="D8" s="45" t="n">
+        <v>306</v>
+      </c>
+      <c r="E8" s="46" t="n">
+        <v>-129</v>
+      </c>
+      <c r="F8" s="45" t="n">
+        <v>435</v>
+      </c>
+      <c r="G8" s="46" t="n">
+        <v>-290</v>
+      </c>
+      <c r="H8" s="47" t="n">
+        <v>857.8</v>
+      </c>
+      <c r="I8" s="47" t="n">
+        <v>7122.1</v>
+      </c>
+      <c r="J8" s="48" t="n">
+        <v>-703.3</v>
+      </c>
+      <c r="K8" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="L8" s="52" t="n">
+        <v>-1.5</v>
       </c>
     </row>
     <row r="9">
@@ -5204,120 +5188,120 @@
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="D9" s="44" t="n">
-        <v>2245</v>
-      </c>
-      <c r="E9" s="44" t="n">
+      <c r="D9" s="45" t="n">
+        <v>2244</v>
+      </c>
+      <c r="E9" s="45" t="n">
         <v>2207</v>
       </c>
-      <c r="F9" s="44" t="n">
-        <v>38</v>
-      </c>
-      <c r="G9" s="45" t="n">
+      <c r="F9" s="45" t="n">
+        <v>37</v>
+      </c>
+      <c r="G9" s="46" t="n">
         <v>-2193</v>
       </c>
-      <c r="H9" s="46" t="n">
+      <c r="H9" s="47" t="n">
         <v>203.9</v>
       </c>
-      <c r="I9" s="46" t="n">
-        <v>1713.8</v>
+      <c r="I9" s="47" t="n">
+        <v>1755.7</v>
       </c>
       <c r="J9" s="51" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="K9" s="48" t="n">
-        <v>6.23</v>
-      </c>
-      <c r="L9" s="52" t="n">
-        <v>-4.7</v>
+        <v>87</v>
+      </c>
+      <c r="K9" s="49" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="L9" s="50" t="n">
+        <v>-5.23</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="31" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>코웨이</t>
         </is>
       </c>
       <c r="B10" s="30" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="C10" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="D10" s="44" t="n">
-        <v>128</v>
-      </c>
-      <c r="E10" s="44" t="n">
-        <v>20</v>
-      </c>
-      <c r="F10" s="44" t="n">
-        <v>108</v>
-      </c>
-      <c r="G10" s="45" t="n">
-        <v>-113</v>
-      </c>
-      <c r="H10" s="46" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="I10" s="46" t="n">
-        <v>251.5</v>
-      </c>
-      <c r="J10" s="51" t="n">
-        <v>76.3</v>
-      </c>
-      <c r="K10" s="48" t="n">
-        <v>27.98</v>
-      </c>
-      <c r="L10" s="52" t="n">
-        <v>-4.55</v>
+          <t>일반서비스</t>
+        </is>
+      </c>
+      <c r="D10" s="46" t="n">
+        <v>-25</v>
+      </c>
+      <c r="E10" s="46" t="n">
+        <v>-101</v>
+      </c>
+      <c r="F10" s="45" t="n">
+        <v>75</v>
+      </c>
+      <c r="G10" s="46" t="n">
+        <v>-76</v>
+      </c>
+      <c r="H10" s="47" t="n">
+        <v>160.2</v>
+      </c>
+      <c r="I10" s="47" t="n">
+        <v>940.4</v>
+      </c>
+      <c r="J10" s="48" t="n">
+        <v>-77.09999999999999</v>
+      </c>
+      <c r="K10" s="49" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="L10" s="50" t="n">
+        <v>-9.130000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="31" t="inlineStr">
         <is>
-          <t>코웨이</t>
+          <t>샘씨엔에스</t>
         </is>
       </c>
       <c r="B11" s="30" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="C11" s="34" t="inlineStr">
         <is>
-          <t>일반서비스</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="D11" s="45" t="n">
-        <v>-29</v>
+        <v>128</v>
       </c>
       <c r="E11" s="45" t="n">
-        <v>-109</v>
-      </c>
-      <c r="F11" s="44" t="n">
-        <v>80</v>
-      </c>
-      <c r="G11" s="45" t="n">
-        <v>-72</v>
-      </c>
-      <c r="H11" s="46" t="n">
-        <v>160.2</v>
-      </c>
-      <c r="I11" s="46" t="n">
-        <v>889.9</v>
-      </c>
-      <c r="J11" s="47" t="n">
-        <v>-127.6</v>
-      </c>
-      <c r="K11" s="48" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L11" s="49" t="n">
-        <v>-8.800000000000001</v>
+        <v>20</v>
+      </c>
+      <c r="F11" s="45" t="n">
+        <v>108</v>
+      </c>
+      <c r="G11" s="46" t="n">
+        <v>-113</v>
+      </c>
+      <c r="H11" s="47" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="I11" s="47" t="n">
+        <v>257.7</v>
+      </c>
+      <c r="J11" s="51" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="K11" s="49" t="n">
+        <v>25.27</v>
+      </c>
+      <c r="L11" s="50" t="n">
+        <v>-6.75</v>
       </c>
     </row>
     <row r="12">
@@ -5336,38 +5320,38 @@
           <t>보험</t>
         </is>
       </c>
-      <c r="D12" s="44" t="n">
-        <v>112</v>
-      </c>
-      <c r="E12" s="45" t="n">
-        <v>-216</v>
-      </c>
-      <c r="F12" s="44" t="n">
-        <v>329</v>
-      </c>
-      <c r="G12" s="45" t="n">
-        <v>-98</v>
-      </c>
-      <c r="H12" s="46" t="n">
+      <c r="D12" s="45" t="n">
+        <v>106</v>
+      </c>
+      <c r="E12" s="46" t="n">
+        <v>-220</v>
+      </c>
+      <c r="F12" s="45" t="n">
+        <v>326</v>
+      </c>
+      <c r="G12" s="46" t="n">
+        <v>-91</v>
+      </c>
+      <c r="H12" s="47" t="n">
         <v>174.5</v>
       </c>
-      <c r="I12" s="46" t="n">
-        <v>1245</v>
-      </c>
-      <c r="J12" s="47" t="n">
-        <v>-98</v>
-      </c>
-      <c r="K12" s="48" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="L12" s="49" t="n">
-        <v>-7.47</v>
+      <c r="I12" s="47" t="n">
+        <v>1225.3</v>
+      </c>
+      <c r="J12" s="48" t="n">
+        <v>-117.7</v>
+      </c>
+      <c r="K12" s="49" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L12" s="50" t="n">
+        <v>-7.68</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="31" t="inlineStr">
         <is>
-          <t>자이에스앤디</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="B13" s="30" t="inlineStr">
@@ -5377,119 +5361,119 @@
       </c>
       <c r="C13" s="34" t="inlineStr">
         <is>
-          <t>부동산</t>
-        </is>
-      </c>
-      <c r="D13" s="44" t="n">
-        <v>120</v>
-      </c>
-      <c r="E13" s="44" t="n">
-        <v>66</v>
-      </c>
-      <c r="F13" s="44" t="n">
-        <v>53</v>
-      </c>
-      <c r="G13" s="45" t="n">
-        <v>-127</v>
-      </c>
-      <c r="H13" s="46" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="I13" s="46" t="n">
-        <v>118.2</v>
+          <t>운송·창고</t>
+        </is>
+      </c>
+      <c r="D13" s="45" t="n">
+        <v>87</v>
+      </c>
+      <c r="E13" s="46" t="n">
+        <v>-15</v>
+      </c>
+      <c r="F13" s="45" t="n">
+        <v>102</v>
+      </c>
+      <c r="G13" s="46" t="n">
+        <v>-84</v>
+      </c>
+      <c r="H13" s="47" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="I13" s="47" t="n">
+        <v>1228.9</v>
       </c>
       <c r="J13" s="51" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="K13" s="53" t="n">
-        <v>-4.24</v>
-      </c>
-      <c r="L13" s="49" t="n">
-        <v>-7.58</v>
+        <v>39.1</v>
+      </c>
+      <c r="K13" s="49" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="L13" s="50" t="n">
+        <v>-9.09</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="31" t="inlineStr">
-        <is>
-          <t>팬오션</t>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>리파인</t>
         </is>
       </c>
       <c r="B14" s="30" t="inlineStr">
         <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="C14" s="34" t="inlineStr"/>
+      <c r="D14" s="45" t="n">
+        <v>47</v>
+      </c>
+      <c r="E14" s="45" t="n">
+        <v>19</v>
+      </c>
+      <c r="F14" s="45" t="n">
+        <v>28</v>
+      </c>
+      <c r="G14" s="46" t="n">
+        <v>-106</v>
+      </c>
+      <c r="H14" s="47" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I14" s="47" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="J14" s="48" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="K14" s="49" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="L14" s="52" t="n">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="inlineStr">
+        <is>
+          <t>BGF리테일</t>
+        </is>
+      </c>
+      <c r="B15" s="30" t="inlineStr">
+        <is>
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C14" s="34" t="inlineStr">
-        <is>
-          <t>운송·창고</t>
-        </is>
-      </c>
-      <c r="D14" s="44" t="n">
-        <v>87</v>
-      </c>
-      <c r="E14" s="45" t="n">
-        <v>-15</v>
-      </c>
-      <c r="F14" s="44" t="n">
-        <v>102</v>
-      </c>
-      <c r="G14" s="45" t="n">
-        <v>-84</v>
-      </c>
-      <c r="H14" s="46" t="n">
-        <v>98.2</v>
-      </c>
-      <c r="I14" s="46" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J14" s="51" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="K14" s="48" t="n">
-        <v>6.53</v>
-      </c>
-      <c r="L14" s="49" t="n">
-        <v>-8.73</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>리파인</t>
-        </is>
-      </c>
-      <c r="B15" s="30" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="C15" s="34" t="inlineStr"/>
-      <c r="D15" s="44" t="n">
-        <v>46</v>
-      </c>
-      <c r="E15" s="44" t="n">
-        <v>19</v>
-      </c>
-      <c r="F15" s="44" t="n">
-        <v>27</v>
-      </c>
-      <c r="G15" s="45" t="n">
-        <v>-105</v>
-      </c>
-      <c r="H15" s="46" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I15" s="46" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="J15" s="47" t="n">
-        <v>-4</v>
-      </c>
-      <c r="K15" s="48" t="n">
-        <v>2.57</v>
+      <c r="C15" s="34" t="inlineStr">
+        <is>
+          <t>유통</t>
+        </is>
+      </c>
+      <c r="D15" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" s="45" t="n">
+        <v>41</v>
+      </c>
+      <c r="F15" s="46" t="n">
+        <v>-38</v>
+      </c>
+      <c r="G15" s="46" t="n">
+        <v>-14</v>
+      </c>
+      <c r="H15" s="47" t="n">
+        <v>196</v>
+      </c>
+      <c r="I15" s="47" t="n">
+        <v>1121.9</v>
+      </c>
+      <c r="J15" s="51" t="n">
+        <v>120.9</v>
+      </c>
+      <c r="K15" s="53" t="n">
+        <v>-3.56</v>
       </c>
       <c r="L15" s="50" t="n">
-        <v>-0.29</v>
+        <v>-9.050000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -5504,32 +5488,32 @@
         </is>
       </c>
       <c r="C16" s="34" t="inlineStr"/>
-      <c r="D16" s="44" t="n">
+      <c r="D16" s="45" t="n">
         <v>30</v>
       </c>
-      <c r="E16" s="44" t="n">
+      <c r="E16" s="45" t="n">
         <v>18</v>
       </c>
-      <c r="F16" s="44" t="n">
+      <c r="F16" s="45" t="n">
         <v>13</v>
       </c>
-      <c r="G16" s="45" t="n">
+      <c r="G16" s="46" t="n">
         <v>-23</v>
       </c>
-      <c r="H16" s="46" t="n">
+      <c r="H16" s="47" t="n">
         <v>5.4</v>
       </c>
-      <c r="I16" s="46" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="J16" s="47" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="K16" s="48" t="n">
-        <v>8.66</v>
-      </c>
-      <c r="L16" s="52" t="n">
-        <v>-4.76</v>
+      <c r="I16" s="47" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="J16" s="51" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" s="49" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="L16" s="50" t="n">
+        <v>-5.52</v>
       </c>
     </row>
     <row r="17">
@@ -5544,38 +5528,38 @@
         </is>
       </c>
       <c r="C17" s="34" t="inlineStr"/>
-      <c r="D17" s="44" t="n">
+      <c r="D17" s="45" t="n">
         <v>17</v>
       </c>
-      <c r="E17" s="45" t="n">
+      <c r="E17" s="46" t="n">
         <v>-4</v>
       </c>
-      <c r="F17" s="44" t="n">
+      <c r="F17" s="45" t="n">
         <v>21</v>
       </c>
-      <c r="G17" s="45" t="n">
+      <c r="G17" s="46" t="n">
         <v>-35</v>
       </c>
-      <c r="H17" s="46" t="n">
+      <c r="H17" s="47" t="n">
         <v>1.6</v>
       </c>
-      <c r="I17" s="46" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="J17" s="47" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="K17" s="48" t="n">
+      <c r="I17" s="47" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="J17" s="51" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" s="49" t="n">
         <v>14.01</v>
       </c>
-      <c r="L17" s="50" t="n">
+      <c r="L17" s="52" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="31" t="inlineStr">
         <is>
-          <t>BGF리테일</t>
+          <t>IPARK현대산업개발</t>
         </is>
       </c>
       <c r="B18" s="30" t="inlineStr">
@@ -5585,125 +5569,125 @@
       </c>
       <c r="C18" s="34" t="inlineStr">
         <is>
-          <t>유통</t>
-        </is>
-      </c>
-      <c r="D18" s="44" t="n">
-        <v>4</v>
-      </c>
-      <c r="E18" s="44" t="n">
-        <v>40</v>
+          <t>건설</t>
+        </is>
+      </c>
+      <c r="D18" s="45" t="n">
+        <v>79</v>
+      </c>
+      <c r="E18" s="45" t="n">
+        <v>12</v>
       </c>
       <c r="F18" s="45" t="n">
-        <v>-36</v>
-      </c>
-      <c r="G18" s="45" t="n">
-        <v>-14</v>
-      </c>
-      <c r="H18" s="46" t="n">
-        <v>196</v>
-      </c>
-      <c r="I18" s="46" t="n">
-        <v>1054.2</v>
+        <v>67</v>
+      </c>
+      <c r="G18" s="46" t="n">
+        <v>-134</v>
+      </c>
+      <c r="H18" s="47" t="n">
+        <v>31</v>
+      </c>
+      <c r="I18" s="47" t="n">
+        <v>470</v>
       </c>
       <c r="J18" s="51" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="K18" s="53" t="n">
-        <v>-3.56</v>
-      </c>
-      <c r="L18" s="49" t="n">
-        <v>-7.33</v>
+        <v>18.8</v>
+      </c>
+      <c r="K18" s="49" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="L18" s="54" t="n">
+        <v>-3.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="31" t="inlineStr">
         <is>
-          <t>IPARK현대산업개발</t>
+          <t>시선AI</t>
         </is>
       </c>
       <c r="B19" s="30" t="inlineStr">
         <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="C19" s="34" t="inlineStr">
-        <is>
-          <t>건설</t>
-        </is>
-      </c>
-      <c r="D19" s="44" t="n">
-        <v>79</v>
-      </c>
-      <c r="E19" s="44" t="n">
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="C19" s="34" t="inlineStr"/>
+      <c r="D19" s="45" t="n">
         <v>12</v>
       </c>
-      <c r="F19" s="44" t="n">
-        <v>67</v>
-      </c>
-      <c r="G19" s="45" t="n">
-        <v>-134</v>
-      </c>
-      <c r="H19" s="46" t="n">
-        <v>31</v>
-      </c>
-      <c r="I19" s="46" t="n">
-        <v>482.6</v>
+      <c r="E19" s="45" t="n">
+        <v>12</v>
+      </c>
+      <c r="F19" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="46" t="n">
+        <v>-8</v>
+      </c>
+      <c r="H19" s="47" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I19" s="47" t="n">
+        <v>16.1</v>
       </c>
       <c r="J19" s="51" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="K19" s="48" t="n">
-        <v>5.17</v>
-      </c>
-      <c r="L19" s="52" t="n">
-        <v>-3.3</v>
+        <v>2.4</v>
+      </c>
+      <c r="K19" s="49" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="L19" s="50" t="n">
+        <v>-6.07</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="31" t="inlineStr">
         <is>
-          <t>시선AI</t>
+          <t>빙그레</t>
         </is>
       </c>
       <c r="B20" s="30" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="C20" s="34" t="inlineStr"/>
-      <c r="D20" s="44" t="n">
-        <v>12</v>
-      </c>
-      <c r="E20" s="44" t="n">
-        <v>12</v>
-      </c>
-      <c r="F20" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="45" t="n">
-        <v>-8</v>
-      </c>
-      <c r="H20" s="46" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I20" s="46" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="J20" s="51" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="K20" s="48" t="n">
-        <v>18.98</v>
-      </c>
-      <c r="L20" s="49" t="n">
-        <v>-6.56</v>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="C20" s="34" t="inlineStr">
+        <is>
+          <t>음식료·담배</t>
+        </is>
+      </c>
+      <c r="D20" s="45" t="n">
+        <v>126</v>
+      </c>
+      <c r="E20" s="45" t="n">
+        <v>99</v>
+      </c>
+      <c r="F20" s="45" t="n">
+        <v>26</v>
+      </c>
+      <c r="G20" s="46" t="n">
+        <v>-129</v>
+      </c>
+      <c r="H20" s="47" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="I20" s="47" t="n">
+        <v>298.3</v>
+      </c>
+      <c r="J20" s="48" t="n">
+        <v>-22.6</v>
+      </c>
+      <c r="K20" s="53" t="n">
+        <v>-4.28</v>
+      </c>
+      <c r="L20" s="50" t="n">
+        <v>-9.59</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="31" t="inlineStr">
         <is>
-          <t>빙그레</t>
+          <t>롯데웰푸드</t>
         </is>
       </c>
       <c r="B21" s="30" t="inlineStr">
@@ -5716,38 +5700,38 @@
           <t>음식료·담배</t>
         </is>
       </c>
-      <c r="D21" s="44" t="n">
-        <v>145</v>
-      </c>
-      <c r="E21" s="44" t="n">
-        <v>119</v>
-      </c>
-      <c r="F21" s="44" t="n">
-        <v>26</v>
-      </c>
-      <c r="G21" s="45" t="n">
-        <v>-146</v>
-      </c>
-      <c r="H21" s="46" t="n">
-        <v>84.90000000000001</v>
-      </c>
-      <c r="I21" s="46" t="n">
-        <v>306.8</v>
-      </c>
-      <c r="J21" s="47" t="n">
-        <v>-14.1</v>
+      <c r="D21" s="45" t="n">
+        <v>55</v>
+      </c>
+      <c r="E21" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" s="45" t="n">
+        <v>45</v>
+      </c>
+      <c r="G21" s="46" t="n">
+        <v>-55</v>
+      </c>
+      <c r="H21" s="47" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="I21" s="47" t="n">
+        <v>352.7</v>
+      </c>
+      <c r="J21" s="51" t="n">
+        <v>23.7</v>
       </c>
       <c r="K21" s="53" t="n">
-        <v>-4.06</v>
-      </c>
-      <c r="L21" s="49" t="n">
-        <v>-9.710000000000001</v>
+        <v>-1.31</v>
+      </c>
+      <c r="L21" s="50" t="n">
+        <v>-9.85</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="31" t="inlineStr">
         <is>
-          <t>롯데웰푸드</t>
+          <t>코리안리</t>
         </is>
       </c>
       <c r="B22" s="30" t="inlineStr">
@@ -5757,41 +5741,41 @@
       </c>
       <c r="C22" s="34" t="inlineStr">
         <is>
-          <t>음식료·담배</t>
-        </is>
-      </c>
-      <c r="D22" s="44" t="n">
-        <v>55</v>
-      </c>
-      <c r="E22" s="44" t="n">
-        <v>10</v>
-      </c>
-      <c r="F22" s="44" t="n">
-        <v>45</v>
-      </c>
-      <c r="G22" s="45" t="n">
-        <v>-54</v>
-      </c>
-      <c r="H22" s="46" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="I22" s="46" t="n">
-        <v>360.8</v>
+          <t>보험</t>
+        </is>
+      </c>
+      <c r="D22" s="45" t="n">
+        <v>22</v>
+      </c>
+      <c r="E22" s="46" t="n">
+        <v>-24</v>
+      </c>
+      <c r="F22" s="45" t="n">
+        <v>46</v>
+      </c>
+      <c r="G22" s="46" t="n">
+        <v>-31</v>
+      </c>
+      <c r="H22" s="47" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="I22" s="47" t="n">
+        <v>870.4</v>
       </c>
       <c r="J22" s="51" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="K22" s="53" t="n">
-        <v>-2.21</v>
-      </c>
-      <c r="L22" s="49" t="n">
-        <v>-9.31</v>
+        <v>67.8</v>
+      </c>
+      <c r="K22" s="49" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="L22" s="54" t="n">
+        <v>-3.85</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="31" t="inlineStr">
         <is>
-          <t>코리안리</t>
+          <t>롯데렌탈</t>
         </is>
       </c>
       <c r="B23" s="30" t="inlineStr">
@@ -5801,41 +5785,41 @@
       </c>
       <c r="C23" s="34" t="inlineStr">
         <is>
-          <t>보험</t>
-        </is>
-      </c>
-      <c r="D23" s="44" t="n">
-        <v>20</v>
-      </c>
-      <c r="E23" s="45" t="n">
-        <v>-26</v>
-      </c>
-      <c r="F23" s="44" t="n">
-        <v>46</v>
-      </c>
-      <c r="G23" s="45" t="n">
-        <v>-30</v>
-      </c>
-      <c r="H23" s="46" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="I23" s="46" t="n">
-        <v>861.6</v>
+          <t>일반서비스</t>
+        </is>
+      </c>
+      <c r="D23" s="46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E23" s="46" t="n">
+        <v>-44</v>
+      </c>
+      <c r="F23" s="45" t="n">
+        <v>43</v>
+      </c>
+      <c r="G23" s="46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H23" s="47" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="I23" s="47" t="n">
+        <v>604.8</v>
       </c>
       <c r="J23" s="51" t="n">
-        <v>59</v>
-      </c>
-      <c r="K23" s="48" t="n">
-        <v>5.51</v>
-      </c>
-      <c r="L23" s="52" t="n">
-        <v>-3.16</v>
+        <v>40.4</v>
+      </c>
+      <c r="K23" s="49" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="L23" s="50" t="n">
+        <v>-7.71</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="31" t="inlineStr">
         <is>
-          <t>롯데렌탈</t>
+          <t>KB발해인프라</t>
         </is>
       </c>
       <c r="B24" s="30" t="inlineStr">
@@ -5843,178 +5827,48 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C24" s="34" t="inlineStr">
-        <is>
-          <t>일반서비스</t>
-        </is>
-      </c>
-      <c r="D24" s="45" t="n">
-        <v>-3</v>
+      <c r="C24" s="34" t="inlineStr"/>
+      <c r="D24" s="46" t="n">
+        <v>-2</v>
       </c>
       <c r="E24" s="45" t="n">
-        <v>-46</v>
-      </c>
-      <c r="F24" s="44" t="n">
-        <v>43</v>
-      </c>
-      <c r="G24" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="46" t="n">
-        <v>84.59999999999999</v>
-      </c>
-      <c r="I24" s="46" t="n">
-        <v>603.7</v>
-      </c>
-      <c r="J24" s="51" t="n">
-        <v>39.3</v>
-      </c>
-      <c r="K24" s="48" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="L24" s="49" t="n">
-        <v>-7.06</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="31" t="inlineStr">
-        <is>
-          <t>KB발해인프라</t>
-        </is>
-      </c>
-      <c r="B25" s="30" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="C25" s="34" t="inlineStr"/>
-      <c r="D25" s="45" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E25" s="44" t="n">
         <v>59</v>
       </c>
-      <c r="F25" s="45" t="n">
+      <c r="F24" s="46" t="n">
         <v>-61</v>
       </c>
-      <c r="G25" s="44" t="n">
+      <c r="G24" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="H25" s="46" t="n">
+      <c r="H24" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="I25" s="46" t="n">
-        <v>110.5</v>
-      </c>
-      <c r="J25" s="47" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="K25" s="53" t="n">
+      <c r="I24" s="47" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="J24" s="48" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="K24" s="53" t="n">
         <v>-0.09</v>
       </c>
-      <c r="L25" s="49" t="n">
+      <c r="L24" s="50" t="n">
         <v>-7.66</v>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
-      <c r="A26" s="31" t="inlineStr">
-        <is>
-          <t>S-Oil우</t>
-        </is>
-      </c>
-      <c r="B26" s="30" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="C26" s="34" t="inlineStr">
-        <is>
-          <t>화학</t>
-        </is>
-      </c>
-      <c r="D26" s="44" t="n">
-        <v>32</v>
-      </c>
-      <c r="E26" s="45" t="n">
-        <v>-15</v>
-      </c>
-      <c r="F26" s="44" t="n">
-        <v>47</v>
-      </c>
-      <c r="G26" s="45" t="n">
-        <v>-30</v>
-      </c>
-      <c r="H26" s="46" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="I26" s="46" t="n">
-        <v>173.5</v>
-      </c>
-      <c r="J26" s="51" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="K26" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="49" t="n">
-        <v>-7.82</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="31" t="inlineStr">
-        <is>
-          <t>방림</t>
-        </is>
-      </c>
-      <c r="B27" s="30" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="C27" s="34" t="inlineStr">
-        <is>
-          <t>섬유·의류</t>
-        </is>
-      </c>
-      <c r="D27" s="44" t="n">
-        <v>4</v>
-      </c>
-      <c r="E27" s="44" t="n">
-        <v>4</v>
-      </c>
-      <c r="F27" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="45" t="n">
-        <v>-4</v>
-      </c>
-      <c r="H27" s="46" t="inlineStr"/>
-      <c r="I27" s="46" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="J27" s="47" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="K27" s="48" t="n">
-        <v>6.92</v>
-      </c>
-      <c r="L27" s="52" t="n">
-        <v>-3.46</v>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="A26" s="18" t="inlineStr">
         <is>
           <t>최신 거래일 기준 · 52주 신고가 대비 -10% 이내 (KIS 랭킹) · ETF·ETN 제외 · 수급=월간 누적 확정(억원) · 동반 순매수(외인·기관 동일 방향)=합산 굵게</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:L27"/>
+  <autoFilter ref="A5:L24"/>
   <mergeCells count="6">
+    <mergeCell ref="A26:L26"/>
     <mergeCell ref="D4:J4"/>
-    <mergeCell ref="A29:L29"/>
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="K4:L4"/>
@@ -6030,7 +5884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q59"/>
+  <dimension ref="A1:Q73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4.5" customWidth="1" style="15" min="1" max="1"/>
@@ -6115,82 +5969,82 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="43" t="inlineStr">
+      <c r="A5" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B5" s="43" t="inlineStr">
+      <c r="B5" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C5" s="43" t="inlineStr">
+      <c r="C5" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D5" s="43" t="inlineStr">
+      <c r="D5" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E5" s="43" t="inlineStr">
+      <c r="E5" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F5" s="43" t="inlineStr">
+      <c r="F5" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G5" s="43" t="inlineStr">
+      <c r="G5" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H5" s="43" t="inlineStr">
+      <c r="H5" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="J5" s="43" t="inlineStr">
+      <c r="J5" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="K5" s="43" t="inlineStr">
+      <c r="K5" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="L5" s="43" t="inlineStr">
+      <c r="L5" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="M5" s="43" t="inlineStr">
+      <c r="M5" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="N5" s="43" t="inlineStr">
+      <c r="N5" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O5" s="43" t="inlineStr">
+      <c r="O5" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P5" s="43" t="inlineStr">
+      <c r="P5" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q5" s="43" t="inlineStr">
+      <c r="Q5" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -6210,8 +6064,8 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D6" s="45" t="n">
-        <v>4900</v>
+      <c r="D6" s="46" t="n">
+        <v>4998</v>
       </c>
       <c r="E6" s="30" t="n">
         <v>1</v>
@@ -6227,7 +6081,7 @@
         </is>
       </c>
       <c r="H6" s="59" t="n">
-        <v>-35363</v>
+        <v>-38738</v>
       </c>
       <c r="J6" s="30" t="n">
         <v>1</v>
@@ -6242,8 +6096,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M6" s="45" t="n">
-        <v>24520</v>
+      <c r="M6" s="46" t="n">
+        <v>21816</v>
       </c>
       <c r="N6" s="30" t="n">
         <v>1</v>
@@ -6259,7 +6113,7 @@
         </is>
       </c>
       <c r="Q6" s="59" t="n">
-        <v>-3933</v>
+        <v>-5501</v>
       </c>
     </row>
     <row r="7" ht="31" customHeight="1" s="15">
@@ -6276,8 +6130,8 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D7" s="45" t="n">
-        <v>4675</v>
+      <c r="D7" s="46" t="n">
+        <v>4333</v>
       </c>
       <c r="E7" s="30" t="n">
         <v>2</v>
@@ -6293,7 +6147,7 @@
         </is>
       </c>
       <c r="H7" s="59" t="n">
-        <v>-22691</v>
+        <v>-24762</v>
       </c>
       <c r="J7" s="30" t="n">
         <v>2</v>
@@ -6308,8 +6162,8 @@
           <t>유통</t>
         </is>
       </c>
-      <c r="M7" s="45" t="n">
-        <v>9992</v>
+      <c r="M7" s="46" t="n">
+        <v>9989</v>
       </c>
       <c r="N7" s="30" t="n">
         <v>2</v>
@@ -6319,13 +6173,13 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="P7" s="40" t="inlineStr">
+      <c r="P7" s="41" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
       <c r="Q7" s="59" t="n">
-        <v>-3065</v>
+        <v>-3169</v>
       </c>
     </row>
     <row r="8" ht="31" customHeight="1" s="15">
@@ -6342,7 +6196,7 @@
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="D8" s="45" t="n">
+      <c r="D8" s="46" t="n">
         <v>2207</v>
       </c>
       <c r="E8" s="30" t="n">
@@ -6359,7 +6213,7 @@
         </is>
       </c>
       <c r="H8" s="59" t="n">
-        <v>-3082</v>
+        <v>-3268</v>
       </c>
       <c r="J8" s="30" t="n">
         <v>3</v>
@@ -6374,7 +6228,7 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M8" s="45" t="n">
+      <c r="M8" s="46" t="n">
         <v>3496</v>
       </c>
       <c r="N8" s="30" t="n">
@@ -6385,13 +6239,13 @@
           <t>현대모비스</t>
         </is>
       </c>
-      <c r="P8" s="40" t="inlineStr">
+      <c r="P8" s="41" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
       <c r="Q8" s="59" t="n">
-        <v>-2921</v>
+        <v>-2951</v>
       </c>
     </row>
     <row r="9">
@@ -6408,8 +6262,8 @@
           <t>화학</t>
         </is>
       </c>
-      <c r="D9" s="45" t="n">
-        <v>2050</v>
+      <c r="D9" s="46" t="n">
+        <v>2055</v>
       </c>
       <c r="E9" s="30" t="n">
         <v>4</v>
@@ -6425,7 +6279,7 @@
         </is>
       </c>
       <c r="H9" s="59" t="n">
-        <v>-2758</v>
+        <v>-2816</v>
       </c>
       <c r="J9" s="30" t="n">
         <v>4</v>
@@ -6440,7 +6294,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M9" s="45" t="n">
+      <c r="M9" s="46" t="n">
         <v>2825</v>
       </c>
       <c r="N9" s="30" t="n">
@@ -6457,7 +6311,7 @@
         </is>
       </c>
       <c r="Q9" s="59" t="n">
-        <v>-2877</v>
+        <v>-2872</v>
       </c>
     </row>
     <row r="10">
@@ -6474,8 +6328,8 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D10" s="45" t="n">
-        <v>1443</v>
+      <c r="D10" s="46" t="n">
+        <v>1451</v>
       </c>
       <c r="E10" s="30" t="n">
         <v>5</v>
@@ -6491,7 +6345,7 @@
         </is>
       </c>
       <c r="H10" s="59" t="n">
-        <v>-2380</v>
+        <v>-2338</v>
       </c>
       <c r="J10" s="30" t="n">
         <v>5</v>
@@ -6506,8 +6360,8 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="M10" s="45" t="n">
-        <v>2036</v>
+      <c r="M10" s="46" t="n">
+        <v>1991</v>
       </c>
       <c r="N10" s="30" t="n">
         <v>5</v>
@@ -6523,7 +6377,7 @@
         </is>
       </c>
       <c r="Q10" s="59" t="n">
-        <v>-2064</v>
+        <v>-2194</v>
       </c>
     </row>
     <row r="11" ht="31" customHeight="1" s="15">
@@ -6535,29 +6389,29 @@
           <t>현대모비스</t>
         </is>
       </c>
-      <c r="C11" s="40" t="inlineStr">
+      <c r="C11" s="41" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="D11" s="45" t="n">
-        <v>1320</v>
+      <c r="D11" s="46" t="n">
+        <v>1218</v>
       </c>
       <c r="E11" s="30" t="n">
         <v>6</v>
       </c>
       <c r="F11" s="31" t="inlineStr">
         <is>
-          <t>HD현대중공업</t>
-        </is>
-      </c>
-      <c r="G11" s="40" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="G11" s="34" t="inlineStr">
+        <is>
+          <t>기계·장비</t>
         </is>
       </c>
       <c r="H11" s="59" t="n">
-        <v>-1667</v>
+        <v>-1796</v>
       </c>
       <c r="J11" s="30" t="n">
         <v>6</v>
@@ -6572,15 +6426,15 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M11" s="45" t="n">
-        <v>1758</v>
+      <c r="M11" s="46" t="n">
+        <v>1760</v>
       </c>
       <c r="N11" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="O11" s="31" t="inlineStr">
-        <is>
-          <t>대덕전자</t>
+      <c r="O11" s="1" t="inlineStr">
+        <is>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="P11" s="34" t="inlineStr">
@@ -6589,10 +6443,10 @@
         </is>
       </c>
       <c r="Q11" s="59" t="n">
-        <v>-1832</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>-2006</v>
+      </c>
+    </row>
+    <row r="12" ht="31" customHeight="1" s="15">
       <c r="A12" s="30" t="n">
         <v>7</v>
       </c>
@@ -6606,24 +6460,24 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D12" s="45" t="n">
-        <v>993</v>
+      <c r="D12" s="46" t="n">
+        <v>1009</v>
       </c>
       <c r="E12" s="30" t="n">
         <v>7</v>
       </c>
       <c r="F12" s="31" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
-        </is>
-      </c>
-      <c r="G12" s="34" t="inlineStr">
-        <is>
-          <t>기계·장비</t>
+          <t>HD현대중공업</t>
+        </is>
+      </c>
+      <c r="G12" s="41" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
         </is>
       </c>
       <c r="H12" s="59" t="n">
-        <v>-1610</v>
+        <v>-1741</v>
       </c>
       <c r="J12" s="30" t="n">
         <v>7</v>
@@ -6638,15 +6492,15 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M12" s="45" t="n">
-        <v>1721</v>
+      <c r="M12" s="46" t="n">
+        <v>1692</v>
       </c>
       <c r="N12" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="O12" s="1" t="inlineStr">
-        <is>
-          <t>삼성전기</t>
+      <c r="O12" s="31" t="inlineStr">
+        <is>
+          <t>대덕전자</t>
         </is>
       </c>
       <c r="P12" s="34" t="inlineStr">
@@ -6655,7 +6509,7 @@
         </is>
       </c>
       <c r="Q12" s="59" t="n">
-        <v>-1815</v>
+        <v>-1832</v>
       </c>
     </row>
     <row r="13">
@@ -6672,8 +6526,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D13" s="45" t="n">
-        <v>930</v>
+      <c r="D13" s="46" t="n">
+        <v>931</v>
       </c>
       <c r="E13" s="30" t="n">
         <v>8</v>
@@ -6704,8 +6558,8 @@
           <t>화학</t>
         </is>
       </c>
-      <c r="M13" s="45" t="n">
-        <v>1660</v>
+      <c r="M13" s="46" t="n">
+        <v>1649</v>
       </c>
       <c r="N13" s="30" t="n">
         <v>8</v>
@@ -6738,8 +6592,8 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D14" s="45" t="n">
-        <v>903</v>
+      <c r="D14" s="46" t="n">
+        <v>889</v>
       </c>
       <c r="E14" s="30" t="n">
         <v>9</v>
@@ -6755,7 +6609,7 @@
         </is>
       </c>
       <c r="H14" s="59" t="n">
-        <v>-1380</v>
+        <v>-1373</v>
       </c>
       <c r="J14" s="30" t="n">
         <v>9</v>
@@ -6770,24 +6624,24 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M14" s="45" t="n">
-        <v>1556</v>
+      <c r="M14" s="46" t="n">
+        <v>1554</v>
       </c>
       <c r="N14" s="30" t="n">
         <v>9</v>
       </c>
       <c r="O14" s="31" t="inlineStr">
         <is>
-          <t>LG이노텍</t>
+          <t>에이피알</t>
         </is>
       </c>
       <c r="P14" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>화학</t>
         </is>
       </c>
       <c r="Q14" s="59" t="n">
-        <v>-1473</v>
+        <v>-1479</v>
       </c>
     </row>
     <row r="15">
@@ -6804,7 +6658,7 @@
           <t>제약</t>
         </is>
       </c>
-      <c r="D15" s="45" t="n">
+      <c r="D15" s="46" t="n">
         <v>803</v>
       </c>
       <c r="E15" s="30" t="n">
@@ -6821,7 +6675,7 @@
         </is>
       </c>
       <c r="H15" s="59" t="n">
-        <v>-1278</v>
+        <v>-1228</v>
       </c>
       <c r="J15" s="30" t="n">
         <v>10</v>
@@ -6836,24 +6690,24 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M15" s="45" t="n">
-        <v>1550</v>
+      <c r="M15" s="46" t="n">
+        <v>1473</v>
       </c>
       <c r="N15" s="30" t="n">
         <v>10</v>
       </c>
       <c r="O15" s="31" t="inlineStr">
         <is>
-          <t>에이피알</t>
+          <t>LG이노텍</t>
         </is>
       </c>
       <c r="P15" s="34" t="inlineStr">
         <is>
-          <t>화학</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="Q15" s="59" t="n">
-        <v>-1455</v>
+        <v>-1473</v>
       </c>
     </row>
     <row r="16"/>
@@ -6902,82 +6756,82 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="43" t="inlineStr">
+      <c r="A19" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B19" s="43" t="inlineStr">
+      <c r="B19" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C19" s="43" t="inlineStr">
+      <c r="C19" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D19" s="43" t="inlineStr">
+      <c r="D19" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E19" s="43" t="inlineStr">
+      <c r="E19" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F19" s="43" t="inlineStr">
+      <c r="F19" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G19" s="43" t="inlineStr">
+      <c r="G19" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H19" s="43" t="inlineStr">
+      <c r="H19" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="J19" s="43" t="inlineStr">
+      <c r="J19" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="K19" s="43" t="inlineStr">
+      <c r="K19" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="L19" s="43" t="inlineStr">
+      <c r="L19" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="M19" s="43" t="inlineStr">
+      <c r="M19" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="N19" s="43" t="inlineStr">
+      <c r="N19" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O19" s="43" t="inlineStr">
+      <c r="O19" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P19" s="43" t="inlineStr">
+      <c r="P19" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q19" s="43" t="inlineStr">
+      <c r="Q19" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -6997,8 +6851,8 @@
           <t>유통</t>
         </is>
       </c>
-      <c r="D20" s="45" t="n">
-        <v>9513</v>
+      <c r="D20" s="46" t="n">
+        <v>9488</v>
       </c>
       <c r="E20" s="30" t="n">
         <v>1</v>
@@ -7014,7 +6868,7 @@
         </is>
       </c>
       <c r="H20" s="59" t="n">
-        <v>-39295</v>
+        <v>-44239</v>
       </c>
       <c r="J20" s="30" t="n">
         <v>1</v>
@@ -7029,8 +6883,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M20" s="45" t="n">
-        <v>4728</v>
+      <c r="M20" s="46" t="n">
+        <v>5093</v>
       </c>
       <c r="N20" s="30" t="n">
         <v>1</v>
@@ -7046,7 +6900,7 @@
         </is>
       </c>
       <c r="Q20" s="59" t="n">
-        <v>-69246</v>
+        <v>-64200</v>
       </c>
     </row>
     <row r="21" ht="31" customHeight="1" s="15">
@@ -7063,8 +6917,8 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D21" s="45" t="n">
-        <v>5448</v>
+      <c r="D21" s="46" t="n">
+        <v>5533</v>
       </c>
       <c r="E21" s="30" t="n">
         <v>2</v>
@@ -7080,7 +6934,7 @@
         </is>
       </c>
       <c r="H21" s="59" t="n">
-        <v>-4897</v>
+        <v>-5273</v>
       </c>
       <c r="J21" s="30" t="n">
         <v>2</v>
@@ -7090,13 +6944,13 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="L21" s="40" t="inlineStr">
+      <c r="L21" s="41" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="M21" s="45" t="n">
-        <v>3592</v>
+      <c r="M21" s="46" t="n">
+        <v>3805</v>
       </c>
       <c r="N21" s="30" t="n">
         <v>2</v>
@@ -7112,7 +6966,7 @@
         </is>
       </c>
       <c r="Q21" s="59" t="n">
-        <v>-52593</v>
+        <v>-47570</v>
       </c>
     </row>
     <row r="22" ht="31" customHeight="1" s="15">
@@ -7129,8 +6983,8 @@
           <t>화학</t>
         </is>
       </c>
-      <c r="D22" s="45" t="n">
-        <v>3710</v>
+      <c r="D22" s="46" t="n">
+        <v>3704</v>
       </c>
       <c r="E22" s="30" t="n">
         <v>3</v>
@@ -7140,13 +6994,13 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="G22" s="40" t="inlineStr">
+      <c r="G22" s="41" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
       <c r="H22" s="59" t="n">
-        <v>-3488</v>
+        <v>-3688</v>
       </c>
       <c r="J22" s="30" t="n">
         <v>3</v>
@@ -7161,8 +7015,8 @@
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="M22" s="45" t="n">
-        <v>3579</v>
+      <c r="M22" s="46" t="n">
+        <v>3565</v>
       </c>
       <c r="N22" s="30" t="n">
         <v>3</v>
@@ -7178,7 +7032,7 @@
         </is>
       </c>
       <c r="Q22" s="59" t="n">
-        <v>-3678</v>
+        <v>-3673</v>
       </c>
     </row>
     <row r="23">
@@ -7187,16 +7041,16 @@
       </c>
       <c r="B23" s="31" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C23" s="34" t="inlineStr">
         <is>
-          <t>금융</t>
-        </is>
-      </c>
-      <c r="D23" s="45" t="n">
-        <v>2611</v>
+          <t>운송·창고</t>
+        </is>
+      </c>
+      <c r="D23" s="46" t="n">
+        <v>2245</v>
       </c>
       <c r="E23" s="30" t="n">
         <v>4</v>
@@ -7212,7 +7066,7 @@
         </is>
       </c>
       <c r="H23" s="59" t="n">
-        <v>-3212</v>
+        <v>-3197</v>
       </c>
       <c r="J23" s="30" t="n">
         <v>4</v>
@@ -7227,7 +7081,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M23" s="45" t="n">
+      <c r="M23" s="46" t="n">
         <v>2633</v>
       </c>
       <c r="N23" s="30" t="n">
@@ -7235,16 +7089,16 @@
       </c>
       <c r="O23" s="31" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="P23" s="34" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>운송·창고</t>
         </is>
       </c>
       <c r="Q23" s="59" t="n">
-        <v>-2624</v>
+        <v>-2193</v>
       </c>
     </row>
     <row r="24">
@@ -7253,23 +7107,23 @@
       </c>
       <c r="B24" s="31" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>SK스퀘어</t>
         </is>
       </c>
       <c r="C24" s="34" t="inlineStr">
         <is>
-          <t>운송·창고</t>
-        </is>
-      </c>
-      <c r="D24" s="45" t="n">
-        <v>2245</v>
+          <t>금융</t>
+        </is>
+      </c>
+      <c r="D24" s="46" t="n">
+        <v>2139</v>
       </c>
       <c r="E24" s="30" t="n">
         <v>5</v>
       </c>
       <c r="F24" s="31" t="inlineStr">
         <is>
-          <t>LG이노텍</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="G24" s="34" t="inlineStr">
@@ -7278,7 +7132,7 @@
         </is>
       </c>
       <c r="H24" s="59" t="n">
-        <v>-2678</v>
+        <v>-2946</v>
       </c>
       <c r="J24" s="30" t="n">
         <v>5</v>
@@ -7293,27 +7147,27 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M24" s="45" t="n">
-        <v>2108</v>
+      <c r="M24" s="46" t="n">
+        <v>2195</v>
       </c>
       <c r="N24" s="30" t="n">
         <v>5</v>
       </c>
       <c r="O24" s="31" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>SK스퀘어</t>
         </is>
       </c>
       <c r="P24" s="34" t="inlineStr">
         <is>
-          <t>운송·창고</t>
+          <t>금융</t>
         </is>
       </c>
       <c r="Q24" s="59" t="n">
-        <v>-2194</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>-2153</v>
+      </c>
+    </row>
+    <row r="25" ht="31" customHeight="1" s="15">
       <c r="A25" s="30" t="n">
         <v>6</v>
       </c>
@@ -7327,7 +7181,7 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D25" s="45" t="n">
+      <c r="D25" s="46" t="n">
         <v>2081</v>
       </c>
       <c r="E25" s="30" t="n">
@@ -7335,7 +7189,7 @@
       </c>
       <c r="F25" s="31" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>LG이노텍</t>
         </is>
       </c>
       <c r="G25" s="34" t="inlineStr">
@@ -7344,23 +7198,23 @@
         </is>
       </c>
       <c r="H25" s="59" t="n">
-        <v>-2225</v>
+        <v>-2678</v>
       </c>
       <c r="J25" s="30" t="n">
         <v>6</v>
       </c>
       <c r="K25" s="31" t="inlineStr">
         <is>
-          <t>에이피알</t>
-        </is>
-      </c>
-      <c r="L25" s="34" t="inlineStr">
-        <is>
-          <t>화학</t>
-        </is>
-      </c>
-      <c r="M25" s="45" t="n">
-        <v>1591</v>
+          <t>현대모비스</t>
+        </is>
+      </c>
+      <c r="L25" s="41" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
+        </is>
+      </c>
+      <c r="M25" s="46" t="n">
+        <v>1691</v>
       </c>
       <c r="N25" s="30" t="n">
         <v>6</v>
@@ -7379,54 +7233,54 @@
         <v>-2055</v>
       </c>
     </row>
-    <row r="26" ht="31" customHeight="1" s="15">
+    <row r="26">
       <c r="A26" s="30" t="n">
         <v>7</v>
       </c>
       <c r="B26" s="31" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C26" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="D26" s="45" t="n">
-        <v>1829</v>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="D26" s="46" t="n">
+        <v>1759</v>
       </c>
       <c r="E26" s="30" t="n">
         <v>7</v>
       </c>
       <c r="F26" s="31" t="inlineStr">
         <is>
-          <t>에이피알</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="G26" s="34" t="inlineStr">
         <is>
-          <t>화학</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="H26" s="59" t="n">
-        <v>-1610</v>
+        <v>-2306</v>
       </c>
       <c r="J26" s="30" t="n">
         <v>7</v>
       </c>
       <c r="K26" s="31" t="inlineStr">
         <is>
-          <t>현대모비스</t>
-        </is>
-      </c>
-      <c r="L26" s="40" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
-        </is>
-      </c>
-      <c r="M26" s="45" t="n">
-        <v>1550</v>
+          <t>에이피알</t>
+        </is>
+      </c>
+      <c r="L26" s="34" t="inlineStr">
+        <is>
+          <t>화학</t>
+        </is>
+      </c>
+      <c r="M26" s="46" t="n">
+        <v>1650</v>
       </c>
       <c r="N26" s="30" t="n">
         <v>7</v>
@@ -7442,7 +7296,7 @@
         </is>
       </c>
       <c r="Q26" s="59" t="n">
-        <v>-1815</v>
+        <v>-1779</v>
       </c>
     </row>
     <row r="27" ht="31" customHeight="1" s="15">
@@ -7451,7 +7305,7 @@
       </c>
       <c r="B27" s="31" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C27" s="34" t="inlineStr">
@@ -7459,8 +7313,8 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D27" s="45" t="n">
-        <v>1775</v>
+      <c r="D27" s="46" t="n">
+        <v>1705</v>
       </c>
       <c r="E27" s="30" t="n">
         <v>8</v>
@@ -7470,13 +7324,13 @@
           <t>현대모비스</t>
         </is>
       </c>
-      <c r="G27" s="40" t="inlineStr">
+      <c r="G27" s="41" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
       <c r="H27" s="59" t="n">
-        <v>-1601</v>
+        <v>-1732</v>
       </c>
       <c r="J27" s="30" t="n">
         <v>8</v>
@@ -7491,8 +7345,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M27" s="45" t="n">
-        <v>1368</v>
+      <c r="M27" s="46" t="n">
+        <v>1401</v>
       </c>
       <c r="N27" s="30" t="n">
         <v>8</v>
@@ -7508,7 +7362,7 @@
         </is>
       </c>
       <c r="Q27" s="59" t="n">
-        <v>-1678</v>
+        <v>-1675</v>
       </c>
     </row>
     <row r="28">
@@ -7517,7 +7371,7 @@
       </c>
       <c r="B28" s="31" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="C28" s="34" t="inlineStr">
@@ -7525,24 +7379,24 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D28" s="45" t="n">
-        <v>1702</v>
+      <c r="D28" s="46" t="n">
+        <v>1238</v>
       </c>
       <c r="E28" s="30" t="n">
         <v>9</v>
       </c>
       <c r="F28" s="31" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>에이피알</t>
         </is>
       </c>
       <c r="G28" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>화학</t>
         </is>
       </c>
       <c r="H28" s="59" t="n">
-        <v>-1376</v>
+        <v>-1675</v>
       </c>
       <c r="J28" s="30" t="n">
         <v>9</v>
@@ -7557,8 +7411,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M28" s="45" t="n">
-        <v>1101</v>
+      <c r="M28" s="46" t="n">
+        <v>1138</v>
       </c>
       <c r="N28" s="30" t="n">
         <v>9</v>
@@ -7583,32 +7437,32 @@
       </c>
       <c r="B29" s="31" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>기계·장비</t>
-        </is>
-      </c>
-      <c r="D29" s="45" t="n">
-        <v>1237</v>
+          <t>일반서비스</t>
+        </is>
+      </c>
+      <c r="D29" s="46" t="n">
+        <v>815</v>
       </c>
       <c r="E29" s="30" t="n">
         <v>10</v>
       </c>
       <c r="F29" s="31" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="G29" s="34" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="H29" s="59" t="n">
-        <v>-1322</v>
+        <v>-1405</v>
       </c>
       <c r="J29" s="30" t="n">
         <v>10</v>
@@ -7623,7 +7477,7 @@
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="M29" s="45" t="n">
+      <c r="M29" s="46" t="n">
         <v>1032</v>
       </c>
       <c r="N29" s="30" t="n">
@@ -7631,16 +7485,16 @@
       </c>
       <c r="O29" s="31" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="P29" s="34" t="inlineStr">
         <is>
-          <t>일반서비스</t>
+          <t>금융</t>
         </is>
       </c>
       <c r="Q29" s="59" t="n">
-        <v>-824</v>
+        <v>-878</v>
       </c>
     </row>
     <row r="30"/>
@@ -7689,82 +7543,82 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="43" t="inlineStr">
+      <c r="A33" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B33" s="43" t="inlineStr">
+      <c r="B33" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C33" s="43" t="inlineStr">
+      <c r="C33" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D33" s="43" t="inlineStr">
+      <c r="D33" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E33" s="43" t="inlineStr">
+      <c r="E33" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F33" s="43" t="inlineStr">
+      <c r="F33" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G33" s="43" t="inlineStr">
+      <c r="G33" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H33" s="43" t="inlineStr">
+      <c r="H33" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="J33" s="43" t="inlineStr">
+      <c r="J33" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="K33" s="43" t="inlineStr">
+      <c r="K33" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="L33" s="43" t="inlineStr">
+      <c r="L33" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="M33" s="43" t="inlineStr">
+      <c r="M33" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="N33" s="43" t="inlineStr">
+      <c r="N33" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O33" s="43" t="inlineStr">
+      <c r="O33" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P33" s="43" t="inlineStr">
+      <c r="P33" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q33" s="43" t="inlineStr">
+      <c r="Q33" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -7784,8 +7638,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D34" s="45" t="n">
-        <v>27807</v>
+      <c r="D34" s="46" t="n">
+        <v>25911</v>
       </c>
       <c r="E34" s="30" t="n">
         <v>1</v>
@@ -7801,7 +7655,7 @@
         </is>
       </c>
       <c r="H34" s="59" t="n">
-        <v>-1921</v>
+        <v>-2046</v>
       </c>
       <c r="J34" s="30" t="n">
         <v>1</v>
@@ -7816,7 +7670,7 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M34" s="45" t="n">
+      <c r="M34" s="46" t="n">
         <v>3167</v>
       </c>
       <c r="N34" s="30" t="n">
@@ -7833,7 +7687,7 @@
         </is>
       </c>
       <c r="Q34" s="59" t="n">
-        <v>-11613</v>
+        <v>-12226</v>
       </c>
     </row>
     <row r="35">
@@ -7842,16 +7696,16 @@
       </c>
       <c r="B35" s="31" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>포스코인터내셔널</t>
         </is>
       </c>
       <c r="C35" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="D35" s="45" t="n">
-        <v>9575</v>
+          <t>유통</t>
+        </is>
+      </c>
+      <c r="D35" s="46" t="n">
+        <v>9392</v>
       </c>
       <c r="E35" s="30" t="n">
         <v>2</v>
@@ -7867,7 +7721,7 @@
         </is>
       </c>
       <c r="H35" s="59" t="n">
-        <v>-1256</v>
+        <v>-1254</v>
       </c>
       <c r="J35" s="30" t="n">
         <v>2</v>
@@ -7882,7 +7736,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M35" s="45" t="n">
+      <c r="M35" s="46" t="n">
         <v>2214</v>
       </c>
       <c r="N35" s="30" t="n">
@@ -7899,7 +7753,7 @@
         </is>
       </c>
       <c r="Q35" s="59" t="n">
-        <v>-1941</v>
+        <v>-2750</v>
       </c>
     </row>
     <row r="36">
@@ -7908,16 +7762,16 @@
       </c>
       <c r="B36" s="31" t="inlineStr">
         <is>
-          <t>포스코인터내셔널</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C36" s="34" t="inlineStr">
         <is>
-          <t>유통</t>
-        </is>
-      </c>
-      <c r="D36" s="45" t="n">
-        <v>9395</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D36" s="46" t="n">
+        <v>8618</v>
       </c>
       <c r="E36" s="30" t="n">
         <v>3</v>
@@ -7933,7 +7787,7 @@
         </is>
       </c>
       <c r="H36" s="59" t="n">
-        <v>-845</v>
+        <v>-952</v>
       </c>
       <c r="J36" s="30" t="n">
         <v>3</v>
@@ -7948,7 +7802,7 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M36" s="45" t="n">
+      <c r="M36" s="46" t="n">
         <v>2029</v>
       </c>
       <c r="N36" s="30" t="n">
@@ -7965,7 +7819,7 @@
         </is>
       </c>
       <c r="Q36" s="59" t="n">
-        <v>-1390</v>
+        <v>-1387</v>
       </c>
     </row>
     <row r="37" ht="31" customHeight="1" s="15">
@@ -7982,8 +7836,8 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D37" s="45" t="n">
-        <v>608</v>
+      <c r="D37" s="46" t="n">
+        <v>562</v>
       </c>
       <c r="E37" s="30" t="n">
         <v>4</v>
@@ -7999,7 +7853,7 @@
         </is>
       </c>
       <c r="H37" s="59" t="n">
-        <v>-711</v>
+        <v>-765</v>
       </c>
       <c r="J37" s="30" t="n">
         <v>4</v>
@@ -8014,7 +7868,7 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M37" s="45" t="n">
+      <c r="M37" s="46" t="n">
         <v>1539</v>
       </c>
       <c r="N37" s="30" t="n">
@@ -8025,7 +7879,7 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="P37" s="40" t="inlineStr">
+      <c r="P37" s="41" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
@@ -8043,13 +7897,13 @@
           <t>HD현대중공업</t>
         </is>
       </c>
-      <c r="C38" s="40" t="inlineStr">
+      <c r="C38" s="41" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="D38" s="45" t="n">
-        <v>337</v>
+      <c r="D38" s="46" t="n">
+        <v>315</v>
       </c>
       <c r="E38" s="30" t="n">
         <v>5</v>
@@ -8065,7 +7919,7 @@
         </is>
       </c>
       <c r="H38" s="59" t="n">
-        <v>-640</v>
+        <v>-652</v>
       </c>
       <c r="J38" s="30" t="n">
         <v>5</v>
@@ -8080,7 +7934,7 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M38" s="45" t="n">
+      <c r="M38" s="46" t="n">
         <v>1522</v>
       </c>
       <c r="N38" s="30" t="n">
@@ -8091,7 +7945,7 @@
           <t>현대모비스</t>
         </is>
       </c>
-      <c r="P38" s="40" t="inlineStr">
+      <c r="P38" s="41" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
@@ -8114,7 +7968,7 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="D39" s="45" t="n">
+      <c r="D39" s="46" t="n">
         <v>266</v>
       </c>
       <c r="E39" s="30" t="n">
@@ -8125,13 +7979,13 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="G39" s="40" t="inlineStr">
+      <c r="G39" s="41" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
       <c r="H39" s="59" t="n">
-        <v>-498</v>
+        <v>-531</v>
       </c>
       <c r="J39" s="30" t="n">
         <v>6</v>
@@ -8146,8 +8000,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M39" s="45" t="n">
-        <v>1493</v>
+      <c r="M39" s="46" t="n">
+        <v>1475</v>
       </c>
       <c r="N39" s="30" t="n">
         <v>6</v>
@@ -8163,7 +8017,7 @@
         </is>
       </c>
       <c r="Q39" s="59" t="n">
-        <v>-1178</v>
+        <v>-1177</v>
       </c>
     </row>
     <row r="40">
@@ -8180,8 +8034,8 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D40" s="45" t="n">
-        <v>265</v>
+      <c r="D40" s="46" t="n">
+        <v>252</v>
       </c>
       <c r="E40" s="30" t="n">
         <v>7</v>
@@ -8197,7 +8051,7 @@
         </is>
       </c>
       <c r="H40" s="59" t="n">
-        <v>-491</v>
+        <v>-492</v>
       </c>
       <c r="J40" s="30" t="n">
         <v>7</v>
@@ -8212,7 +8066,7 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M40" s="45" t="n">
+      <c r="M40" s="46" t="n">
         <v>1358</v>
       </c>
       <c r="N40" s="30" t="n">
@@ -8229,7 +8083,7 @@
         </is>
       </c>
       <c r="Q40" s="59" t="n">
-        <v>-1125</v>
+        <v>-1127</v>
       </c>
     </row>
     <row r="41">
@@ -8246,7 +8100,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D41" s="45" t="n">
+      <c r="D41" s="46" t="n">
         <v>231</v>
       </c>
       <c r="E41" s="30" t="n">
@@ -8263,14 +8117,14 @@
         </is>
       </c>
       <c r="H41" s="59" t="n">
-        <v>-408</v>
+        <v>-425</v>
       </c>
       <c r="J41" s="30" t="n">
         <v>8</v>
       </c>
       <c r="K41" s="31" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="L41" s="34" t="inlineStr">
@@ -8278,8 +8132,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M41" s="45" t="n">
-        <v>1131</v>
+      <c r="M41" s="46" t="n">
+        <v>1129</v>
       </c>
       <c r="N41" s="30" t="n">
         <v>8</v>
@@ -8312,8 +8166,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D42" s="45" t="n">
-        <v>230</v>
+      <c r="D42" s="46" t="n">
+        <v>219</v>
       </c>
       <c r="E42" s="30" t="n">
         <v>9</v>
@@ -8336,7 +8190,7 @@
       </c>
       <c r="K42" s="31" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="L42" s="34" t="inlineStr">
@@ -8344,8 +8198,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M42" s="45" t="n">
-        <v>1129</v>
+      <c r="M42" s="46" t="n">
+        <v>1066</v>
       </c>
       <c r="N42" s="30" t="n">
         <v>9</v>
@@ -8378,8 +8232,8 @@
           <t>보험</t>
         </is>
       </c>
-      <c r="D43" s="45" t="n">
-        <v>208</v>
+      <c r="D43" s="46" t="n">
+        <v>182</v>
       </c>
       <c r="E43" s="30" t="n">
         <v>10</v>
@@ -8410,7 +8264,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M43" s="45" t="n">
+      <c r="M43" s="46" t="n">
         <v>1056</v>
       </c>
       <c r="N43" s="30" t="n">
@@ -8444,7 +8298,7 @@
       </c>
       <c r="J45" s="25" t="inlineStr">
         <is>
-          <t>F8 보험</t>
+          <t>F8 기타법인</t>
         </is>
       </c>
       <c r="N45" s="56" t="inlineStr">
@@ -8476,82 +8330,82 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="43" t="inlineStr">
+      <c r="A47" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B47" s="43" t="inlineStr">
+      <c r="B47" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C47" s="43" t="inlineStr">
+      <c r="C47" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D47" s="43" t="inlineStr">
+      <c r="D47" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E47" s="43" t="inlineStr">
+      <c r="E47" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F47" s="43" t="inlineStr">
+      <c r="F47" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G47" s="43" t="inlineStr">
+      <c r="G47" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H47" s="43" t="inlineStr">
+      <c r="H47" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="J47" s="43" t="inlineStr">
+      <c r="J47" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="K47" s="43" t="inlineStr">
+      <c r="K47" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="L47" s="43" t="inlineStr">
+      <c r="L47" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="M47" s="43" t="inlineStr">
+      <c r="M47" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="N47" s="43" t="inlineStr">
+      <c r="N47" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O47" s="43" t="inlineStr">
+      <c r="O47" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P47" s="43" t="inlineStr">
+      <c r="P47" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q47" s="43" t="inlineStr">
+      <c r="Q47" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -8571,7 +8425,7 @@
           <t>화학</t>
         </is>
       </c>
-      <c r="D48" s="45" t="n">
+      <c r="D48" s="46" t="n">
         <v>1209</v>
       </c>
       <c r="E48" s="30" t="n">
@@ -8595,7 +8449,7 @@
       </c>
       <c r="K48" s="31" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="L48" s="34" t="inlineStr">
@@ -8603,27 +8457,27 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M48" s="45" t="n">
-        <v>509</v>
+      <c r="M48" s="46" t="n">
+        <v>108431</v>
       </c>
       <c r="N48" s="30" t="n">
         <v>1</v>
       </c>
       <c r="O48" s="31" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>포스코인터내셔널</t>
         </is>
       </c>
       <c r="P48" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>유통</t>
         </is>
       </c>
       <c r="Q48" s="59" t="n">
-        <v>-797</v>
-      </c>
-    </row>
-    <row r="49" ht="31" customHeight="1" s="15">
+        <v>-9471</v>
+      </c>
+    </row>
+    <row r="49">
       <c r="A49" s="30" t="n">
         <v>2</v>
       </c>
@@ -8637,7 +8491,7 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D49" s="45" t="n">
+      <c r="D49" s="46" t="n">
         <v>944</v>
       </c>
       <c r="E49" s="30" t="n">
@@ -8661,32 +8515,32 @@
       </c>
       <c r="K49" s="31" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="L49" s="34" t="inlineStr">
         <is>
-          <t>금융</t>
-        </is>
-      </c>
-      <c r="M49" s="45" t="n">
-        <v>344</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="M49" s="46" t="n">
+        <v>50221</v>
       </c>
       <c r="N49" s="30" t="n">
         <v>2</v>
       </c>
       <c r="O49" s="31" t="inlineStr">
         <is>
-          <t>현대모비스</t>
-        </is>
-      </c>
-      <c r="P49" s="40" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="P49" s="34" t="inlineStr">
+        <is>
+          <t>금융</t>
         </is>
       </c>
       <c r="Q49" s="59" t="n">
-        <v>-116</v>
+        <v>-4655</v>
       </c>
     </row>
     <row r="50" ht="31" customHeight="1" s="15">
@@ -8703,7 +8557,7 @@
           <t>보험</t>
         </is>
       </c>
-      <c r="D50" s="45" t="n">
+      <c r="D50" s="46" t="n">
         <v>640</v>
       </c>
       <c r="E50" s="30" t="n">
@@ -8714,45 +8568,45 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="G50" s="40" t="inlineStr">
+      <c r="G50" s="41" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
       <c r="H50" s="59" t="n">
-        <v>-1534</v>
+        <v>-1535</v>
       </c>
       <c r="J50" s="30" t="n">
         <v>3</v>
       </c>
       <c r="K50" s="31" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="L50" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="M50" s="45" t="n">
-        <v>264</v>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="M50" s="46" t="n">
+        <v>654</v>
       </c>
       <c r="N50" s="30" t="n">
         <v>3</v>
       </c>
       <c r="O50" s="31" t="inlineStr">
         <is>
-          <t>현대차</t>
-        </is>
-      </c>
-      <c r="P50" s="40" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="P50" s="34" t="inlineStr">
+        <is>
+          <t>일반서비스</t>
         </is>
       </c>
       <c r="Q50" s="59" t="n">
-        <v>-114</v>
+        <v>-386</v>
       </c>
     </row>
     <row r="51" ht="31" customHeight="1" s="15">
@@ -8769,7 +8623,7 @@
           <t>화학</t>
         </is>
       </c>
-      <c r="D51" s="45" t="n">
+      <c r="D51" s="46" t="n">
         <v>605</v>
       </c>
       <c r="E51" s="30" t="n">
@@ -8780,7 +8634,7 @@
           <t>현대모비스</t>
         </is>
       </c>
-      <c r="G51" s="40" t="inlineStr">
+      <c r="G51" s="41" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
@@ -8793,32 +8647,32 @@
       </c>
       <c r="K51" s="31" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="L51" s="34" t="inlineStr">
         <is>
-          <t>화학</t>
-        </is>
-      </c>
-      <c r="M51" s="45" t="n">
-        <v>168</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="M51" s="46" t="n">
+        <v>603</v>
       </c>
       <c r="N51" s="30" t="n">
         <v>4</v>
       </c>
       <c r="O51" s="31" t="inlineStr">
         <is>
-          <t>에이피알</t>
+          <t>LG에너지솔루션</t>
         </is>
       </c>
       <c r="P51" s="34" t="inlineStr">
         <is>
-          <t>화학</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="Q51" s="59" t="n">
-        <v>-105</v>
+        <v>-360</v>
       </c>
     </row>
     <row r="52">
@@ -8835,7 +8689,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D52" s="45" t="n">
+      <c r="D52" s="46" t="n">
         <v>596</v>
       </c>
       <c r="E52" s="30" t="n">
@@ -8859,35 +8713,35 @@
       </c>
       <c r="K52" s="31" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="L52" s="34" t="inlineStr">
         <is>
-          <t>기계·장비</t>
-        </is>
-      </c>
-      <c r="M52" s="45" t="n">
-        <v>122</v>
+          <t>금융</t>
+        </is>
+      </c>
+      <c r="M52" s="46" t="n">
+        <v>596</v>
       </c>
       <c r="N52" s="30" t="n">
         <v>5</v>
       </c>
       <c r="O52" s="31" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>신한지주</t>
         </is>
       </c>
       <c r="P52" s="34" t="inlineStr">
         <is>
-          <t>일반서비스</t>
+          <t>금융</t>
         </is>
       </c>
       <c r="Q52" s="59" t="n">
-        <v>-89</v>
-      </c>
-    </row>
-    <row r="53">
+        <v>-333</v>
+      </c>
+    </row>
+    <row r="53" ht="31" customHeight="1" s="15">
       <c r="A53" s="30" t="n">
         <v>6</v>
       </c>
@@ -8901,7 +8755,7 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D53" s="45" t="n">
+      <c r="D53" s="46" t="n">
         <v>587</v>
       </c>
       <c r="E53" s="30" t="n">
@@ -8925,32 +8779,32 @@
       </c>
       <c r="K53" s="31" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>현대백화점</t>
         </is>
       </c>
       <c r="L53" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="M53" s="45" t="n">
-        <v>90</v>
+          <t>유통</t>
+        </is>
+      </c>
+      <c r="M53" s="46" t="n">
+        <v>213</v>
       </c>
       <c r="N53" s="30" t="n">
         <v>6</v>
       </c>
       <c r="O53" s="31" t="inlineStr">
         <is>
-          <t>LG이노텍</t>
-        </is>
-      </c>
-      <c r="P53" s="34" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
+          <t>현대차</t>
+        </is>
+      </c>
+      <c r="P53" s="41" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
         </is>
       </c>
       <c r="Q53" s="59" t="n">
-        <v>-74</v>
+        <v>-173</v>
       </c>
     </row>
     <row r="54">
@@ -8967,7 +8821,7 @@
           <t>보험</t>
         </is>
       </c>
-      <c r="D54" s="45" t="n">
+      <c r="D54" s="46" t="n">
         <v>563</v>
       </c>
       <c r="E54" s="30" t="n">
@@ -8991,23 +8845,23 @@
       </c>
       <c r="K54" s="31" t="inlineStr">
         <is>
-          <t>메리츠금융지주</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="L54" s="34" t="inlineStr">
         <is>
-          <t>금융</t>
-        </is>
-      </c>
-      <c r="M54" s="45" t="n">
-        <v>86</v>
+          <t>건설</t>
+        </is>
+      </c>
+      <c r="M54" s="46" t="n">
+        <v>201</v>
       </c>
       <c r="N54" s="30" t="n">
         <v>7</v>
       </c>
       <c r="O54" s="31" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>HD현대</t>
         </is>
       </c>
       <c r="P54" s="34" t="inlineStr">
@@ -9016,10 +8870,10 @@
         </is>
       </c>
       <c r="Q54" s="59" t="n">
-        <v>-71</v>
-      </c>
-    </row>
-    <row r="55" ht="31" customHeight="1" s="15">
+        <v>-112</v>
+      </c>
+    </row>
+    <row r="55">
       <c r="A55" s="30" t="n">
         <v>8</v>
       </c>
@@ -9033,7 +8887,7 @@
           <t>건설</t>
         </is>
       </c>
-      <c r="D55" s="45" t="n">
+      <c r="D55" s="46" t="n">
         <v>430</v>
       </c>
       <c r="E55" s="30" t="n">
@@ -9057,23 +8911,23 @@
       </c>
       <c r="K55" s="31" t="inlineStr">
         <is>
-          <t>HD현대중공업</t>
-        </is>
-      </c>
-      <c r="L55" s="40" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
-        </is>
-      </c>
-      <c r="M55" s="45" t="n">
-        <v>81</v>
+          <t>삼성SDI</t>
+        </is>
+      </c>
+      <c r="L55" s="34" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="M55" s="46" t="n">
+        <v>148</v>
       </c>
       <c r="N55" s="30" t="n">
         <v>8</v>
       </c>
       <c r="O55" s="31" t="inlineStr">
         <is>
-          <t>한국금융지주</t>
+          <t>OCI홀딩스</t>
         </is>
       </c>
       <c r="P55" s="34" t="inlineStr">
@@ -9082,7 +8936,7 @@
         </is>
       </c>
       <c r="Q55" s="59" t="n">
-        <v>-71</v>
+        <v>-84</v>
       </c>
     </row>
     <row r="56">
@@ -9099,7 +8953,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D56" s="45" t="n">
+      <c r="D56" s="46" t="n">
         <v>427</v>
       </c>
       <c r="E56" s="30" t="n">
@@ -9123,7 +8977,7 @@
       </c>
       <c r="K56" s="31" t="inlineStr">
         <is>
-          <t>두산</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="L56" s="34" t="inlineStr">
@@ -9131,24 +8985,24 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M56" s="45" t="n">
-        <v>76</v>
+      <c r="M56" s="46" t="n">
+        <v>134</v>
       </c>
       <c r="N56" s="30" t="n">
         <v>9</v>
       </c>
       <c r="O56" s="31" t="inlineStr">
         <is>
-          <t>NAVER</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="P56" s="34" t="inlineStr">
         <is>
-          <t>IT 서비스</t>
+          <t>화학</t>
         </is>
       </c>
       <c r="Q56" s="59" t="n">
-        <v>-63</v>
+        <v>-64</v>
       </c>
     </row>
     <row r="57">
@@ -9165,7 +9019,7 @@
           <t>유통</t>
         </is>
       </c>
-      <c r="D57" s="45" t="n">
+      <c r="D57" s="46" t="n">
         <v>377</v>
       </c>
       <c r="E57" s="30" t="n">
@@ -9189,44 +9043,451 @@
       </c>
       <c r="K57" s="31" t="inlineStr">
         <is>
-          <t>현대건설</t>
+          <t>두산</t>
         </is>
       </c>
       <c r="L57" s="34" t="inlineStr">
         <is>
-          <t>건설</t>
-        </is>
-      </c>
-      <c r="M57" s="45" t="n">
-        <v>68</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="M57" s="46" t="n">
+        <v>123</v>
       </c>
       <c r="N57" s="30" t="n">
         <v>10</v>
       </c>
       <c r="O57" s="31" t="inlineStr">
         <is>
+          <t>대한항공</t>
+        </is>
+      </c>
+      <c r="P57" s="34" t="inlineStr">
+        <is>
+          <t>운송·창고</t>
+        </is>
+      </c>
+      <c r="Q57" s="59" t="n">
+        <v>-52</v>
+      </c>
+    </row>
+    <row r="58"/>
+    <row r="59" ht="18" customHeight="1" s="15">
+      <c r="A59" s="25" t="inlineStr">
+        <is>
+          <t>F9 보험</t>
+        </is>
+      </c>
+      <c r="E59" s="56" t="inlineStr">
+        <is>
+          <t>월간 누적 · 억원</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="57" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="E60" s="58" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="44" t="inlineStr">
+        <is>
+          <t>순위</t>
+        </is>
+      </c>
+      <c r="B61" s="44" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="C61" s="44" t="inlineStr">
+        <is>
+          <t>섹터명</t>
+        </is>
+      </c>
+      <c r="D61" s="44" t="inlineStr">
+        <is>
+          <t>금액</t>
+        </is>
+      </c>
+      <c r="E61" s="44" t="inlineStr">
+        <is>
+          <t>순위</t>
+        </is>
+      </c>
+      <c r="F61" s="44" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="G61" s="44" t="inlineStr">
+        <is>
+          <t>섹터명</t>
+        </is>
+      </c>
+      <c r="H61" s="44" t="inlineStr">
+        <is>
+          <t>금액</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="B62" s="31" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="C62" s="34" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D62" s="46" t="n">
+        <v>509</v>
+      </c>
+      <c r="E62" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" s="31" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="G62" s="34" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="H62" s="59" t="n">
+        <v>-797</v>
+      </c>
+    </row>
+    <row r="63" ht="31" customHeight="1" s="15">
+      <c r="A63" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="B63" s="31" t="inlineStr">
+        <is>
+          <t>SK스퀘어</t>
+        </is>
+      </c>
+      <c r="C63" s="34" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+      <c r="D63" s="46" t="n">
+        <v>343</v>
+      </c>
+      <c r="E63" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F63" s="31" t="inlineStr">
+        <is>
+          <t>현대모비스</t>
+        </is>
+      </c>
+      <c r="G63" s="41" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
+        </is>
+      </c>
+      <c r="H63" s="59" t="n">
+        <v>-116</v>
+      </c>
+    </row>
+    <row r="64" ht="31" customHeight="1" s="15">
+      <c r="A64" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="B64" s="31" t="inlineStr">
+        <is>
+          <t>삼성전자우</t>
+        </is>
+      </c>
+      <c r="C64" s="34" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D64" s="46" t="n">
+        <v>264</v>
+      </c>
+      <c r="E64" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="F64" s="31" t="inlineStr">
+        <is>
+          <t>현대차</t>
+        </is>
+      </c>
+      <c r="G64" s="41" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
+        </is>
+      </c>
+      <c r="H64" s="59" t="n">
+        <v>-114</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="B65" s="31" t="inlineStr">
+        <is>
+          <t>SK이노베이션</t>
+        </is>
+      </c>
+      <c r="C65" s="34" t="inlineStr">
+        <is>
+          <t>화학</t>
+        </is>
+      </c>
+      <c r="D65" s="46" t="n">
+        <v>168</v>
+      </c>
+      <c r="E65" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="F65" s="31" t="inlineStr">
+        <is>
+          <t>에이피알</t>
+        </is>
+      </c>
+      <c r="G65" s="34" t="inlineStr">
+        <is>
+          <t>화학</t>
+        </is>
+      </c>
+      <c r="H65" s="59" t="n">
+        <v>-105</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="B66" s="31" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="C66" s="34" t="inlineStr">
+        <is>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="D66" s="46" t="n">
+        <v>122</v>
+      </c>
+      <c r="E66" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="F66" s="31" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="G66" s="34" t="inlineStr">
+        <is>
+          <t>일반서비스</t>
+        </is>
+      </c>
+      <c r="H66" s="59" t="n">
+        <v>-89</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="B67" s="31" t="inlineStr">
+        <is>
+          <t>삼성SDI</t>
+        </is>
+      </c>
+      <c r="C67" s="34" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D67" s="46" t="n">
+        <v>90</v>
+      </c>
+      <c r="E67" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="F67" s="31" t="inlineStr">
+        <is>
+          <t>LG이노텍</t>
+        </is>
+      </c>
+      <c r="G67" s="34" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="H67" s="59" t="n">
+        <v>-74</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="B68" s="31" t="inlineStr">
+        <is>
+          <t>메리츠금융지주</t>
+        </is>
+      </c>
+      <c r="C68" s="34" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+      <c r="D68" s="46" t="n">
+        <v>86</v>
+      </c>
+      <c r="E68" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="F68" s="31" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="G68" s="34" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+      <c r="H68" s="59" t="n">
+        <v>-71</v>
+      </c>
+    </row>
+    <row r="69" ht="31" customHeight="1" s="15">
+      <c r="A69" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="B69" s="31" t="inlineStr">
+        <is>
+          <t>HD현대중공업</t>
+        </is>
+      </c>
+      <c r="C69" s="41" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
+        </is>
+      </c>
+      <c r="D69" s="46" t="n">
+        <v>81</v>
+      </c>
+      <c r="E69" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="F69" s="31" t="inlineStr">
+        <is>
+          <t>한국금융지주</t>
+        </is>
+      </c>
+      <c r="G69" s="34" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+      <c r="H69" s="59" t="n">
+        <v>-71</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="B70" s="31" t="inlineStr">
+        <is>
+          <t>두산</t>
+        </is>
+      </c>
+      <c r="C70" s="34" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D70" s="46" t="n">
+        <v>76</v>
+      </c>
+      <c r="E70" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="F70" s="31" t="inlineStr">
+        <is>
+          <t>NAVER</t>
+        </is>
+      </c>
+      <c r="G70" s="34" t="inlineStr">
+        <is>
+          <t>IT 서비스</t>
+        </is>
+      </c>
+      <c r="H70" s="59" t="n">
+        <v>-63</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="B71" s="31" t="inlineStr">
+        <is>
+          <t>현대건설</t>
+        </is>
+      </c>
+      <c r="C71" s="34" t="inlineStr">
+        <is>
+          <t>건설</t>
+        </is>
+      </c>
+      <c r="D71" s="46" t="n">
+        <v>68</v>
+      </c>
+      <c r="E71" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="F71" s="31" t="inlineStr">
+        <is>
           <t>HD현대일렉트릭</t>
         </is>
       </c>
-      <c r="P57" s="34" t="inlineStr">
+      <c r="G71" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q57" s="59" t="n">
+      <c r="H71" s="59" t="n">
         <v>-59</v>
       </c>
     </row>
-    <row r="58"/>
-    <row r="59" ht="31" customHeight="1" s="15">
-      <c r="A59" s="60" t="inlineStr">
-        <is>
-          <t>외인·기관 동시 등재 종목=종목명 굵게(동반 매수/매도) · netbuy_rank 일별 아카이브 합산 — 상위 30 리스트 등재일만 반영되는 근사치 · 금융투자=증권, 투신(사모)=투자신탁+사모펀드 (확정 병합분) · 외인+기관=합산 카드와 동일</t>
+    <row r="72"/>
+    <row r="73" ht="31" customHeight="1" s="15">
+      <c r="A73" s="60" t="inlineStr">
+        <is>
+          <t>외인·기관 동시 등재 종목=종목명 굵게(동반 매수/매도) · netbuy_rank 일별 아카이브 합산 — 상위 30 리스트 등재일만 반영되는 근사치 · 금융투자=증권, 투신(사모)=투자신탁+사모펀드, 기타법인=일반법인(자사주 매입 등) (확정 병합분) · 외인+기관=합산 카드와 동일</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="35">
+  <mergeCells count="39">
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="E45:H45"/>
     <mergeCell ref="O1:Q1"/>
@@ -9234,7 +9495,7 @@
     <mergeCell ref="J31:M31"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="J3:M3"/>
-    <mergeCell ref="A59:Q59"/>
+    <mergeCell ref="A73:Q73"/>
     <mergeCell ref="J46:M46"/>
     <mergeCell ref="E32:H32"/>
     <mergeCell ref="J18:M18"/>
@@ -9244,7 +9505,9 @@
     <mergeCell ref="E3:H3"/>
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="N4:Q4"/>
+    <mergeCell ref="A59:D59"/>
     <mergeCell ref="N32:Q32"/>
+    <mergeCell ref="A60:D60"/>
     <mergeCell ref="A45:D45"/>
     <mergeCell ref="E17:H17"/>
     <mergeCell ref="A1:M1"/>
@@ -9255,11 +9518,13 @@
     <mergeCell ref="N18:Q18"/>
     <mergeCell ref="J45:M45"/>
     <mergeCell ref="A18:D18"/>
+    <mergeCell ref="E60:H60"/>
     <mergeCell ref="E31:H31"/>
     <mergeCell ref="N17:Q17"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="J4:M4"/>
     <mergeCell ref="E46:H46"/>
+    <mergeCell ref="E59:H59"/>
     <mergeCell ref="J32:M32"/>
     <mergeCell ref="A32:D32"/>
   </mergeCells>
@@ -9330,72 +9595,72 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B4" s="43" t="inlineStr">
+      <c r="B4" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C4" s="43" t="inlineStr">
+      <c r="C4" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D4" s="43" t="inlineStr">
+      <c r="D4" s="44" t="inlineStr">
         <is>
           <t>공매도 누적</t>
         </is>
       </c>
-      <c r="F4" s="43" t="inlineStr">
+      <c r="F4" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="G4" s="43" t="inlineStr">
+      <c r="G4" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H4" s="43" t="inlineStr">
+      <c r="H4" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="I4" s="43" t="inlineStr">
+      <c r="I4" s="44" t="inlineStr">
         <is>
           <t>증감</t>
         </is>
       </c>
-      <c r="J4" s="43" t="inlineStr">
+      <c r="J4" s="44" t="inlineStr">
         <is>
           <t>잔고</t>
         </is>
       </c>
-      <c r="L4" s="43" t="inlineStr">
+      <c r="L4" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="M4" s="43" t="inlineStr">
+      <c r="M4" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="N4" s="43" t="inlineStr">
+      <c r="N4" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="O4" s="43" t="inlineStr">
+      <c r="O4" s="44" t="inlineStr">
         <is>
           <t>증감</t>
         </is>
       </c>
-      <c r="P4" s="43" t="inlineStr">
+      <c r="P4" s="44" t="inlineStr">
         <is>
           <t>잔고</t>
         </is>
@@ -9416,7 +9681,7 @@
         </is>
       </c>
       <c r="D5" s="61" t="n">
-        <v>43380</v>
+        <v>43395</v>
       </c>
       <c r="F5" s="30" t="n">
         <v>1</v>
@@ -9431,11 +9696,11 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="I5" s="47" t="n">
-        <v>23392.2</v>
+      <c r="I5" s="48" t="n">
+        <v>8774.799999999999</v>
       </c>
       <c r="J5" s="62" t="n">
-        <v>220014.1</v>
+        <v>205396.7</v>
       </c>
       <c r="L5" s="30" t="n">
         <v>1</v>
@@ -9451,10 +9716,10 @@
         </is>
       </c>
       <c r="O5" s="63" t="n">
-        <v>-7548.7</v>
+        <v>-8119.7</v>
       </c>
       <c r="P5" s="62" t="n">
-        <v>33246</v>
+        <v>32675</v>
       </c>
     </row>
     <row r="6">
@@ -9472,7 +9737,7 @@
         </is>
       </c>
       <c r="D6" s="61" t="n">
-        <v>26561</v>
+        <v>26582</v>
       </c>
       <c r="F6" s="30" t="n">
         <v>2</v>
@@ -9483,18 +9748,18 @@
         </is>
       </c>
       <c r="H6" s="34" t="inlineStr"/>
-      <c r="I6" s="47" t="n">
-        <v>6442.8</v>
+      <c r="I6" s="48" t="n">
+        <v>5006.9</v>
       </c>
       <c r="J6" s="62" t="n">
-        <v>27949.9</v>
+        <v>26514</v>
       </c>
       <c r="L6" s="30" t="n">
         <v>2</v>
       </c>
       <c r="M6" s="31" t="inlineStr">
         <is>
-          <t>LG이노텍</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="N6" s="34" t="inlineStr">
@@ -9503,10 +9768,10 @@
         </is>
       </c>
       <c r="O6" s="63" t="n">
-        <v>-4957.4</v>
+        <v>-6368.1</v>
       </c>
       <c r="P6" s="62" t="n">
-        <v>8208.1</v>
+        <v>223221.9</v>
       </c>
     </row>
     <row r="7">
@@ -9539,30 +9804,30 @@
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="I7" s="47" t="n">
-        <v>3061.8</v>
+      <c r="I7" s="48" t="n">
+        <v>2397.6</v>
       </c>
       <c r="J7" s="62" t="n">
-        <v>5907</v>
+        <v>5242.8</v>
       </c>
       <c r="L7" s="30" t="n">
         <v>3</v>
       </c>
       <c r="M7" s="31" t="inlineStr">
         <is>
-          <t>삼성바이오로직스</t>
+          <t>LG이노텍</t>
         </is>
       </c>
       <c r="N7" s="34" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="O7" s="63" t="n">
-        <v>-3740.9</v>
+        <v>-5532.1</v>
       </c>
       <c r="P7" s="62" t="n">
-        <v>9972.200000000001</v>
+        <v>7633.4</v>
       </c>
     </row>
     <row r="8">
@@ -9580,14 +9845,14 @@
         </is>
       </c>
       <c r="D8" s="61" t="n">
-        <v>4145</v>
+        <v>4146</v>
       </c>
       <c r="F8" s="30" t="n">
         <v>4</v>
       </c>
       <c r="G8" s="31" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="H8" s="34" t="inlineStr">
@@ -9595,11 +9860,11 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="I8" s="47" t="n">
-        <v>2545.1</v>
+      <c r="I8" s="48" t="n">
+        <v>2177.4</v>
       </c>
       <c r="J8" s="62" t="n">
-        <v>19863</v>
+        <v>42744</v>
       </c>
       <c r="L8" s="30" t="n">
         <v>4</v>
@@ -9615,13 +9880,13 @@
         </is>
       </c>
       <c r="O8" s="63" t="n">
-        <v>-3622.7</v>
+        <v>-4065.1</v>
       </c>
       <c r="P8" s="62" t="n">
-        <v>14373.7</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>13931.3</v>
+      </c>
+    </row>
+    <row r="9" ht="31" customHeight="1" s="15">
       <c r="A9" s="30" t="n">
         <v>5</v>
       </c>
@@ -9639,41 +9904,41 @@
       </c>
       <c r="G9" s="31" t="inlineStr">
         <is>
-          <t>한미반도체</t>
-        </is>
-      </c>
-      <c r="H9" s="34" t="inlineStr">
-        <is>
-          <t>기계·장비</t>
-        </is>
-      </c>
-      <c r="I9" s="47" t="n">
-        <v>2501.9</v>
+          <t>HD현대중공업</t>
+        </is>
+      </c>
+      <c r="H9" s="41" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
+        </is>
+      </c>
+      <c r="I9" s="48" t="n">
+        <v>1925.1</v>
       </c>
       <c r="J9" s="62" t="n">
-        <v>43068.5</v>
+        <v>31046.5</v>
       </c>
       <c r="L9" s="30" t="n">
         <v>5</v>
       </c>
       <c r="M9" s="31" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼성바이오로직스</t>
         </is>
       </c>
       <c r="N9" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="O9" s="63" t="n">
-        <v>-3019.7</v>
+        <v>-3830.4</v>
       </c>
       <c r="P9" s="62" t="n">
-        <v>2534.6</v>
-      </c>
-    </row>
-    <row r="10" ht="31" customHeight="1" s="15">
+        <v>9882.700000000001</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" s="30" t="n">
         <v>6</v>
       </c>
@@ -9695,38 +9960,38 @@
       </c>
       <c r="G10" s="31" t="inlineStr">
         <is>
-          <t>HD현대중공업</t>
-        </is>
-      </c>
-      <c r="H10" s="40" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
-        </is>
-      </c>
-      <c r="I10" s="47" t="n">
-        <v>2446.8</v>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="H10" s="34" t="inlineStr">
+        <is>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="I10" s="48" t="n">
+        <v>1684.8</v>
       </c>
       <c r="J10" s="62" t="n">
-        <v>31568.2</v>
+        <v>19002.7</v>
       </c>
       <c r="L10" s="30" t="n">
         <v>6</v>
       </c>
       <c r="M10" s="31" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>SK스퀘어</t>
         </is>
       </c>
       <c r="N10" s="34" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>금융</t>
         </is>
       </c>
       <c r="O10" s="63" t="n">
-        <v>-2989.4</v>
+        <v>-3554.6</v>
       </c>
       <c r="P10" s="62" t="n">
-        <v>4653.3</v>
+        <v>27337.7</v>
       </c>
     </row>
     <row r="11">
@@ -9759,30 +10024,30 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="I11" s="47" t="n">
-        <v>1884.9</v>
+      <c r="I11" s="48" t="n">
+        <v>1666.3</v>
       </c>
       <c r="J11" s="62" t="n">
-        <v>7296.3</v>
+        <v>7077.7</v>
       </c>
       <c r="L11" s="30" t="n">
         <v>7</v>
       </c>
       <c r="M11" s="31" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="N11" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="O11" s="63" t="n">
-        <v>-2801.7</v>
+        <v>-3367.2</v>
       </c>
       <c r="P11" s="62" t="n">
-        <v>13358.1</v>
+        <v>4275.5</v>
       </c>
     </row>
     <row r="12">
@@ -9800,45 +10065,45 @@
         </is>
       </c>
       <c r="D12" s="61" t="n">
-        <v>2627</v>
+        <v>2631</v>
       </c>
       <c r="F12" s="30" t="n">
         <v>8</v>
       </c>
       <c r="G12" s="31" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H12" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="I12" s="47" t="n">
-        <v>1788.1</v>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="I12" s="48" t="n">
+        <v>1204</v>
       </c>
       <c r="J12" s="62" t="n">
-        <v>231378.1</v>
+        <v>5999.4</v>
       </c>
       <c r="L12" s="30" t="n">
         <v>8</v>
       </c>
       <c r="M12" s="31" t="inlineStr">
         <is>
-          <t>삼양식품</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="N12" s="34" t="inlineStr">
         <is>
-          <t>음식료·담배</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="O12" s="63" t="n">
-        <v>-2499</v>
+        <v>-3224.4</v>
       </c>
       <c r="P12" s="62" t="n">
-        <v>7599.4</v>
+        <v>12935.4</v>
       </c>
     </row>
     <row r="13">
@@ -9863,38 +10128,38 @@
       </c>
       <c r="G13" s="31" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>DB하이텍</t>
         </is>
       </c>
       <c r="H13" s="34" t="inlineStr">
         <is>
-          <t>기계·장비</t>
-        </is>
-      </c>
-      <c r="I13" s="47" t="n">
-        <v>1307</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="I13" s="48" t="n">
+        <v>1173.5</v>
       </c>
       <c r="J13" s="62" t="n">
-        <v>6102.4</v>
+        <v>5628.1</v>
       </c>
       <c r="L13" s="30" t="n">
         <v>9</v>
       </c>
       <c r="M13" s="31" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="N13" s="34" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="O13" s="63" t="n">
-        <v>-1774</v>
+        <v>-3059.1</v>
       </c>
       <c r="P13" s="62" t="n">
-        <v>29118.3</v>
+        <v>2495.2</v>
       </c>
     </row>
     <row r="14">
@@ -9927,30 +10192,30 @@
           <t>유통</t>
         </is>
       </c>
-      <c r="I14" s="47" t="n">
-        <v>1249.9</v>
+      <c r="I14" s="48" t="n">
+        <v>976.3</v>
       </c>
       <c r="J14" s="62" t="n">
-        <v>4194.7</v>
+        <v>3921.1</v>
       </c>
       <c r="L14" s="30" t="n">
         <v>10</v>
       </c>
       <c r="M14" s="31" t="inlineStr">
         <is>
-          <t>LG에너지솔루션</t>
+          <t>삼양식품</t>
         </is>
       </c>
       <c r="N14" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>음식료·담배</t>
         </is>
       </c>
       <c r="O14" s="63" t="n">
-        <v>-1719.6</v>
+        <v>-2292.6</v>
       </c>
       <c r="P14" s="62" t="n">
-        <v>31851.3</v>
+        <v>7805.8</v>
       </c>
     </row>
     <row r="15"/>
@@ -9980,7 +10245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20.5" customWidth="1" style="15" min="1" max="1"/>
@@ -9996,7 +10261,8 @@
     <col width="9.5" customWidth="1" style="15" min="11" max="11"/>
     <col width="9.5" customWidth="1" style="15" min="12" max="12"/>
     <col width="9.5" customWidth="1" style="15" min="13" max="13"/>
-    <col width="11.5" customWidth="1" style="15" min="14" max="14"/>
+    <col width="9.5" customWidth="1" style="15" min="14" max="14"/>
+    <col width="11.5" customWidth="1" style="15" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="20.25" customHeight="1" s="15">
@@ -10044,74 +10310,80 @@
       </c>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="44" t="inlineStr">
         <is>
           <t>업종</t>
         </is>
       </c>
-      <c r="B4" s="43" t="inlineStr">
+      <c r="B4" s="44" t="inlineStr">
         <is>
           <t>YTD</t>
         </is>
       </c>
-      <c r="C4" s="43" t="inlineStr">
+      <c r="C4" s="44" t="inlineStr">
         <is>
           <t>6M</t>
         </is>
       </c>
-      <c r="D4" s="43" t="inlineStr">
+      <c r="D4" s="44" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="E4" s="43" t="inlineStr">
+      <c r="E4" s="44" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="F4" s="43" t="inlineStr">
+      <c r="F4" s="44" t="inlineStr">
         <is>
           <t>외인</t>
         </is>
       </c>
-      <c r="G4" s="43" t="inlineStr">
+      <c r="G4" s="44" t="inlineStr">
         <is>
           <t>기관(합)</t>
         </is>
       </c>
-      <c r="H4" s="43" t="inlineStr">
+      <c r="H4" s="44" t="inlineStr">
         <is>
           <t>외인+기관</t>
         </is>
       </c>
-      <c r="I4" s="43" t="inlineStr">
+      <c r="I4" s="44" t="inlineStr">
         <is>
           <t>금융투자</t>
         </is>
       </c>
-      <c r="J4" s="43" t="inlineStr">
+      <c r="J4" s="44" t="inlineStr">
         <is>
           <t>투신(사모)</t>
         </is>
       </c>
-      <c r="K4" s="43" t="inlineStr">
+      <c r="K4" s="44" t="inlineStr">
         <is>
           <t>연기금</t>
         </is>
       </c>
-      <c r="L4" s="43" t="inlineStr">
+      <c r="L4" s="44" t="inlineStr">
+        <is>
+          <t>기타법인</t>
+        </is>
+      </c>
+      <c r="M4" s="44" t="inlineStr">
         <is>
           <t>보험</t>
         </is>
       </c>
-      <c r="M4" s="43" t="inlineStr">
+      <c r="N4" s="44" t="inlineStr">
         <is>
           <t>개인</t>
         </is>
       </c>
-      <c r="N4" s="43" t="inlineStr">
+      <c r="O4" s="44" t="inlineStr">
         <is>
           <t>신호</t>
         </is>
@@ -10136,16 +10408,16 @@
         <v>4.79</v>
       </c>
       <c r="F5" s="66" t="n">
-        <v>-1187</v>
+        <v>-1185</v>
       </c>
       <c r="G5" s="67" t="n">
-        <v>3190</v>
+        <v>3188</v>
       </c>
       <c r="H5" s="67" t="n">
         <v>2003</v>
       </c>
       <c r="I5" s="67" t="n">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="J5" s="67" t="n">
         <v>534</v>
@@ -10153,13 +10425,16 @@
       <c r="K5" s="67" t="n">
         <v>740</v>
       </c>
-      <c r="L5" s="67" t="n">
+      <c r="L5" s="66" t="n">
+        <v>-1752</v>
+      </c>
+      <c r="M5" s="67" t="n">
         <v>20</v>
       </c>
-      <c r="M5" s="66" t="n">
+      <c r="N5" s="66" t="n">
         <v>-251</v>
       </c>
-      <c r="N5" s="57" t="inlineStr">
+      <c r="O5" s="57" t="inlineStr">
         <is>
           <t>동반강세</t>
         </is>
@@ -10184,16 +10459,16 @@
         <v>3.57</v>
       </c>
       <c r="F6" s="66" t="n">
-        <v>-3692</v>
+        <v>-3685</v>
       </c>
       <c r="G6" s="67" t="n">
-        <v>5425</v>
+        <v>5421</v>
       </c>
       <c r="H6" s="67" t="n">
-        <v>1733</v>
+        <v>1736</v>
       </c>
       <c r="I6" s="66" t="n">
-        <v>-598</v>
+        <v>-602</v>
       </c>
       <c r="J6" s="67" t="n">
         <v>4551</v>
@@ -10202,12 +10477,15 @@
         <v>1263</v>
       </c>
       <c r="L6" s="67" t="n">
+        <v>27</v>
+      </c>
+      <c r="M6" s="67" t="n">
         <v>201</v>
       </c>
-      <c r="M6" s="66" t="n">
-        <v>-1760</v>
-      </c>
-      <c r="N6" s="30" t="inlineStr"/>
+      <c r="N6" s="66" t="n">
+        <v>-1763</v>
+      </c>
+      <c r="O6" s="30" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="31" t="inlineStr">
@@ -10228,16 +10506,16 @@
         <v>2.91</v>
       </c>
       <c r="F7" s="66" t="n">
-        <v>-848</v>
+        <v>-841</v>
       </c>
       <c r="G7" s="67" t="n">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H7" s="67" t="n">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="I7" s="67" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J7" s="67" t="n">
         <v>968</v>
@@ -10246,12 +10524,15 @@
         <v>205</v>
       </c>
       <c r="L7" s="67" t="n">
+        <v>1053</v>
+      </c>
+      <c r="M7" s="67" t="n">
         <v>83</v>
       </c>
-      <c r="M7" s="66" t="n">
-        <v>-1767</v>
-      </c>
-      <c r="N7" s="30" t="inlineStr"/>
+      <c r="N7" s="66" t="n">
+        <v>-1773</v>
+      </c>
+      <c r="O7" s="30" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="31" t="inlineStr">
@@ -10290,12 +10571,15 @@
         <v>151</v>
       </c>
       <c r="L8" s="67" t="n">
+        <v>13</v>
+      </c>
+      <c r="M8" s="67" t="n">
         <v>8</v>
       </c>
-      <c r="M8" s="66" t="n">
+      <c r="N8" s="66" t="n">
         <v>-133</v>
       </c>
-      <c r="N8" s="30" t="inlineStr"/>
+      <c r="O8" s="30" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="31" t="inlineStr">
@@ -10316,16 +10600,16 @@
         <v>1.22</v>
       </c>
       <c r="F9" s="67" t="n">
-        <v>2365</v>
+        <v>2366</v>
       </c>
       <c r="G9" s="67" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H9" s="67" t="n">
-        <v>2603</v>
+        <v>2602</v>
       </c>
       <c r="I9" s="66" t="n">
-        <v>-623</v>
+        <v>-624</v>
       </c>
       <c r="J9" s="67" t="n">
         <v>348</v>
@@ -10333,13 +10617,16 @@
       <c r="K9" s="67" t="n">
         <v>475</v>
       </c>
-      <c r="L9" s="67" t="n">
+      <c r="L9" s="66" t="n">
+        <v>-51</v>
+      </c>
+      <c r="M9" s="67" t="n">
         <v>32</v>
       </c>
-      <c r="M9" s="66" t="n">
-        <v>-2551</v>
-      </c>
-      <c r="N9" s="57" t="inlineStr">
+      <c r="N9" s="66" t="n">
+        <v>-2550</v>
+      </c>
+      <c r="O9" s="57" t="inlineStr">
         <is>
           <t>동반강세</t>
         </is>
@@ -10367,27 +10654,30 @@
         <v>8139</v>
       </c>
       <c r="G10" s="67" t="n">
-        <v>3455</v>
+        <v>3433</v>
       </c>
       <c r="H10" s="67" t="n">
-        <v>11595</v>
+        <v>11572</v>
       </c>
       <c r="I10" s="66" t="n">
-        <v>-1865</v>
+        <v>-1888</v>
       </c>
       <c r="J10" s="67" t="n">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="K10" s="67" t="n">
         <v>2195</v>
       </c>
-      <c r="L10" s="67" t="n">
-        <v>297</v>
-      </c>
-      <c r="M10" s="66" t="n">
-        <v>-7421</v>
-      </c>
-      <c r="N10" s="57" t="inlineStr">
+      <c r="L10" s="66" t="n">
+        <v>-4177</v>
+      </c>
+      <c r="M10" s="67" t="n">
+        <v>298</v>
+      </c>
+      <c r="N10" s="66" t="n">
+        <v>-7394</v>
+      </c>
+      <c r="O10" s="57" t="inlineStr">
         <is>
           <t>동반강세</t>
         </is>
@@ -10415,7 +10705,7 @@
         <v>13</v>
       </c>
       <c r="G11" s="67" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H11" s="67" t="n">
         <v>230</v>
@@ -10429,13 +10719,16 @@
       <c r="K11" s="67" t="n">
         <v>185</v>
       </c>
-      <c r="L11" s="67" t="n">
+      <c r="L11" s="66" t="n">
+        <v>-16</v>
+      </c>
+      <c r="M11" s="67" t="n">
         <v>20</v>
       </c>
-      <c r="M11" s="66" t="n">
+      <c r="N11" s="66" t="n">
         <v>-214</v>
       </c>
-      <c r="N11" s="30" t="inlineStr"/>
+      <c r="O11" s="30" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="31" t="inlineStr">
@@ -10474,12 +10767,15 @@
         <v>113</v>
       </c>
       <c r="L12" s="66" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M12" s="66" t="n">
         <v>-20</v>
       </c>
-      <c r="M12" s="66" t="n">
+      <c r="N12" s="66" t="n">
         <v>-119</v>
       </c>
-      <c r="N12" s="68" t="inlineStr">
+      <c r="O12" s="68" t="inlineStr">
         <is>
           <t>수급유입</t>
         </is>
@@ -10504,16 +10800,16 @@
         <v>-0.17</v>
       </c>
       <c r="F13" s="66" t="n">
-        <v>-1738</v>
+        <v>-1739</v>
       </c>
       <c r="G13" s="67" t="n">
-        <v>2433</v>
+        <v>2430</v>
       </c>
       <c r="H13" s="67" t="n">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="I13" s="66" t="n">
-        <v>-184</v>
+        <v>-187</v>
       </c>
       <c r="J13" s="67" t="n">
         <v>696</v>
@@ -10522,12 +10818,15 @@
         <v>1883</v>
       </c>
       <c r="L13" s="67" t="n">
+        <v>32</v>
+      </c>
+      <c r="M13" s="67" t="n">
         <v>41</v>
       </c>
-      <c r="M13" s="66" t="n">
-        <v>-728</v>
-      </c>
-      <c r="N13" s="30" t="inlineStr"/>
+      <c r="N13" s="66" t="n">
+        <v>-723</v>
+      </c>
+      <c r="O13" s="30" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="31" t="inlineStr">
@@ -10565,13 +10864,16 @@
       <c r="K14" s="67" t="n">
         <v>71</v>
       </c>
-      <c r="L14" s="66" t="n">
+      <c r="L14" s="67" t="n">
+        <v>7</v>
+      </c>
+      <c r="M14" s="66" t="n">
         <v>-4</v>
       </c>
-      <c r="M14" s="67" t="n">
+      <c r="N14" s="67" t="n">
         <v>13</v>
       </c>
-      <c r="N14" s="30" t="inlineStr"/>
+      <c r="O14" s="30" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="31" t="inlineStr">
@@ -10595,10 +10897,10 @@
         <v>116</v>
       </c>
       <c r="G15" s="66" t="n">
-        <v>-149</v>
+        <v>-150</v>
       </c>
       <c r="H15" s="66" t="n">
-        <v>-33</v>
+        <v>-34</v>
       </c>
       <c r="I15" s="66" t="n">
         <v>-117</v>
@@ -10610,12 +10912,15 @@
         <v>8</v>
       </c>
       <c r="L15" s="66" t="n">
+        <v>-25</v>
+      </c>
+      <c r="M15" s="66" t="n">
         <v>-17</v>
       </c>
-      <c r="M15" s="67" t="n">
-        <v>58</v>
-      </c>
-      <c r="N15" s="30" t="inlineStr"/>
+      <c r="N15" s="67" t="n">
+        <v>59</v>
+      </c>
+      <c r="O15" s="30" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="31" t="inlineStr">
@@ -10653,13 +10958,16 @@
       <c r="K16" s="67" t="n">
         <v>1</v>
       </c>
-      <c r="L16" s="69" t="n">
+      <c r="L16" s="67" t="n">
+        <v>3</v>
+      </c>
+      <c r="M16" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="M16" s="66" t="n">
+      <c r="N16" s="66" t="n">
         <v>-10</v>
       </c>
-      <c r="N16" s="30" t="inlineStr"/>
+      <c r="O16" s="30" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="31" t="inlineStr">
@@ -10680,16 +10988,16 @@
         <v>-2.14</v>
       </c>
       <c r="F17" s="66" t="n">
-        <v>-2237</v>
+        <v>-2238</v>
       </c>
       <c r="G17" s="67" t="n">
-        <v>10599</v>
+        <v>10596</v>
       </c>
       <c r="H17" s="67" t="n">
-        <v>8361</v>
+        <v>8358</v>
       </c>
       <c r="I17" s="67" t="n">
-        <v>8883</v>
+        <v>8880</v>
       </c>
       <c r="J17" s="67" t="n">
         <v>1291</v>
@@ -10697,13 +11005,16 @@
       <c r="K17" s="67" t="n">
         <v>338</v>
       </c>
-      <c r="L17" s="67" t="n">
+      <c r="L17" s="66" t="n">
+        <v>-8160</v>
+      </c>
+      <c r="M17" s="67" t="n">
         <v>84</v>
       </c>
-      <c r="M17" s="66" t="n">
-        <v>-202</v>
-      </c>
-      <c r="N17" s="30" t="inlineStr"/>
+      <c r="N17" s="66" t="n">
+        <v>-198</v>
+      </c>
+      <c r="O17" s="30" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="31" t="inlineStr">
@@ -10724,7 +11035,7 @@
         <v>-2.19</v>
       </c>
       <c r="F18" s="67" t="n">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="G18" s="66" t="n">
         <v>-987</v>
@@ -10733,7 +11044,7 @@
         <v>347</v>
       </c>
       <c r="I18" s="67" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J18" s="66" t="n">
         <v>-46</v>
@@ -10742,12 +11053,15 @@
         <v>-841</v>
       </c>
       <c r="L18" s="66" t="n">
-        <v>-135</v>
+        <v>-18</v>
       </c>
       <c r="M18" s="66" t="n">
+        <v>-134</v>
+      </c>
+      <c r="N18" s="66" t="n">
         <v>-329</v>
       </c>
-      <c r="N18" s="68" t="inlineStr">
+      <c r="O18" s="68" t="inlineStr">
         <is>
           <t>수급유입</t>
         </is>
@@ -10775,13 +11089,13 @@
         <v>173</v>
       </c>
       <c r="G19" s="66" t="n">
-        <v>-390</v>
+        <v>-392</v>
       </c>
       <c r="H19" s="66" t="n">
-        <v>-217</v>
+        <v>-219</v>
       </c>
       <c r="I19" s="67" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="J19" s="66" t="n">
         <v>-657</v>
@@ -10790,12 +11104,15 @@
         <v>148</v>
       </c>
       <c r="L19" s="66" t="n">
+        <v>-28</v>
+      </c>
+      <c r="M19" s="66" t="n">
         <v>-44</v>
       </c>
-      <c r="M19" s="67" t="n">
-        <v>245</v>
-      </c>
-      <c r="N19" s="30" t="inlineStr"/>
+      <c r="N19" s="67" t="n">
+        <v>247</v>
+      </c>
+      <c r="O19" s="30" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="31" t="inlineStr">
@@ -10816,30 +11133,33 @@
         <v>-2.47</v>
       </c>
       <c r="F20" s="66" t="n">
-        <v>-79925</v>
+        <v>-80432</v>
       </c>
       <c r="G20" s="67" t="n">
-        <v>13666</v>
+        <v>13527</v>
       </c>
       <c r="H20" s="66" t="n">
-        <v>-66259</v>
+        <v>-66904</v>
       </c>
       <c r="I20" s="67" t="n">
-        <v>31866</v>
+        <v>31739</v>
       </c>
       <c r="J20" s="66" t="n">
-        <v>-13190</v>
+        <v>-13202</v>
       </c>
       <c r="K20" s="66" t="n">
         <v>-5017</v>
       </c>
       <c r="L20" s="67" t="n">
+        <v>160255</v>
+      </c>
+      <c r="M20" s="67" t="n">
         <v>46</v>
       </c>
-      <c r="M20" s="66" t="n">
-        <v>-93965</v>
-      </c>
-      <c r="N20" s="30" t="inlineStr"/>
+      <c r="N20" s="66" t="n">
+        <v>-93351</v>
+      </c>
+      <c r="O20" s="30" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="31" t="inlineStr">
@@ -10860,30 +11180,33 @@
         <v>-2.57</v>
       </c>
       <c r="F21" s="66" t="n">
-        <v>-81419</v>
+        <v>-81921</v>
       </c>
       <c r="G21" s="67" t="n">
-        <v>8482</v>
+        <v>8316</v>
       </c>
       <c r="H21" s="66" t="n">
-        <v>-72936</v>
+        <v>-73605</v>
       </c>
       <c r="I21" s="67" t="n">
-        <v>26405</v>
+        <v>26251</v>
       </c>
       <c r="J21" s="66" t="n">
-        <v>-12106</v>
+        <v>-12118</v>
       </c>
       <c r="K21" s="66" t="n">
         <v>-5875</v>
       </c>
       <c r="L21" s="67" t="n">
+        <v>161756</v>
+      </c>
+      <c r="M21" s="67" t="n">
         <v>199</v>
       </c>
-      <c r="M21" s="66" t="n">
-        <v>-88797</v>
-      </c>
-      <c r="N21" s="30" t="inlineStr"/>
+      <c r="N21" s="66" t="n">
+        <v>-88152</v>
+      </c>
+      <c r="O21" s="30" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="31" t="inlineStr">
@@ -10921,13 +11244,16 @@
       <c r="K22" s="66" t="n">
         <v>-24</v>
       </c>
-      <c r="L22" s="69" t="n">
+      <c r="L22" s="67" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="M22" s="67" t="n">
+      <c r="N22" s="67" t="n">
         <v>88</v>
       </c>
-      <c r="N22" s="58" t="inlineStr">
+      <c r="O22" s="58" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -10952,16 +11278,16 @@
         <v>-2.77</v>
       </c>
       <c r="F23" s="67" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G23" s="66" t="n">
-        <v>-6443</v>
+        <v>-6456</v>
       </c>
       <c r="H23" s="66" t="n">
-        <v>-6160</v>
+        <v>-6172</v>
       </c>
       <c r="I23" s="66" t="n">
-        <v>-1031</v>
+        <v>-1043</v>
       </c>
       <c r="J23" s="66" t="n">
         <v>-1176</v>
@@ -10969,13 +11295,16 @@
       <c r="K23" s="66" t="n">
         <v>-3975</v>
       </c>
-      <c r="L23" s="66" t="n">
+      <c r="L23" s="67" t="n">
+        <v>112</v>
+      </c>
+      <c r="M23" s="66" t="n">
         <v>-208</v>
       </c>
-      <c r="M23" s="67" t="n">
-        <v>6044</v>
-      </c>
-      <c r="N23" s="58" t="inlineStr">
+      <c r="N23" s="67" t="n">
+        <v>6059</v>
+      </c>
+      <c r="O23" s="58" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -11003,13 +11332,13 @@
         <v>-768</v>
       </c>
       <c r="G24" s="67" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H24" s="66" t="n">
-        <v>-706</v>
+        <v>-708</v>
       </c>
       <c r="I24" s="66" t="n">
-        <v>-814</v>
+        <v>-817</v>
       </c>
       <c r="J24" s="67" t="n">
         <v>436</v>
@@ -11018,12 +11347,15 @@
         <v>411</v>
       </c>
       <c r="L24" s="67" t="n">
+        <v>296</v>
+      </c>
+      <c r="M24" s="67" t="n">
         <v>17</v>
       </c>
-      <c r="M24" s="67" t="n">
-        <v>410</v>
-      </c>
-      <c r="N24" s="30" t="inlineStr"/>
+      <c r="N24" s="67" t="n">
+        <v>412</v>
+      </c>
+      <c r="O24" s="30" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="31" t="inlineStr">
@@ -11044,16 +11376,16 @@
         <v>-4.02</v>
       </c>
       <c r="F25" s="67" t="n">
-        <v>1272</v>
+        <v>1275</v>
       </c>
       <c r="G25" s="67" t="n">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="H25" s="67" t="n">
-        <v>1785</v>
+        <v>1783</v>
       </c>
       <c r="I25" s="66" t="n">
-        <v>-2164</v>
+        <v>-2169</v>
       </c>
       <c r="J25" s="67" t="n">
         <v>442</v>
@@ -11061,13 +11393,16 @@
       <c r="K25" s="67" t="n">
         <v>1991</v>
       </c>
-      <c r="L25" s="67" t="n">
+      <c r="L25" s="66" t="n">
+        <v>-35</v>
+      </c>
+      <c r="M25" s="67" t="n">
         <v>272</v>
       </c>
-      <c r="M25" s="66" t="n">
-        <v>-1751</v>
-      </c>
-      <c r="N25" s="30" t="inlineStr"/>
+      <c r="N25" s="66" t="n">
+        <v>-1748</v>
+      </c>
+      <c r="O25" s="30" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="31" t="inlineStr">
@@ -11091,13 +11426,13 @@
         <v>851</v>
       </c>
       <c r="G26" s="66" t="n">
-        <v>-3242</v>
+        <v>-3245</v>
       </c>
       <c r="H26" s="66" t="n">
-        <v>-2390</v>
+        <v>-2394</v>
       </c>
       <c r="I26" s="66" t="n">
-        <v>-829</v>
+        <v>-833</v>
       </c>
       <c r="J26" s="66" t="n">
         <v>-1547</v>
@@ -11105,13 +11440,16 @@
       <c r="K26" s="66" t="n">
         <v>-773</v>
       </c>
-      <c r="L26" s="66" t="n">
+      <c r="L26" s="67" t="n">
+        <v>1061</v>
+      </c>
+      <c r="M26" s="66" t="n">
         <v>-98</v>
       </c>
-      <c r="M26" s="67" t="n">
-        <v>1329</v>
-      </c>
-      <c r="N26" s="58" t="inlineStr">
+      <c r="N26" s="67" t="n">
+        <v>1333</v>
+      </c>
+      <c r="O26" s="58" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -11136,16 +11474,16 @@
         <v>-6.11</v>
       </c>
       <c r="F27" s="67" t="n">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="G27" s="66" t="n">
-        <v>-1597</v>
+        <v>-1599</v>
       </c>
       <c r="H27" s="66" t="n">
-        <v>-963</v>
+        <v>-966</v>
       </c>
       <c r="I27" s="66" t="n">
-        <v>-96</v>
+        <v>-98</v>
       </c>
       <c r="J27" s="66" t="n">
         <v>-1454</v>
@@ -11153,13 +11491,16 @@
       <c r="K27" s="67" t="n">
         <v>27</v>
       </c>
-      <c r="L27" s="66" t="n">
+      <c r="L27" s="67" t="n">
+        <v>7</v>
+      </c>
+      <c r="M27" s="66" t="n">
         <v>-36</v>
       </c>
-      <c r="M27" s="67" t="n">
-        <v>953</v>
-      </c>
-      <c r="N27" s="30" t="inlineStr"/>
+      <c r="N27" s="67" t="n">
+        <v>959</v>
+      </c>
+      <c r="O27" s="30" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="31" t="inlineStr">
@@ -11183,13 +11524,13 @@
         <v>1318</v>
       </c>
       <c r="G28" s="66" t="n">
-        <v>-3885</v>
+        <v>-3888</v>
       </c>
       <c r="H28" s="66" t="n">
-        <v>-2567</v>
+        <v>-2570</v>
       </c>
       <c r="I28" s="66" t="n">
-        <v>-493</v>
+        <v>-496</v>
       </c>
       <c r="J28" s="66" t="n">
         <v>-1522</v>
@@ -11197,13 +11538,16 @@
       <c r="K28" s="66" t="n">
         <v>-1686</v>
       </c>
-      <c r="L28" s="66" t="n">
+      <c r="L28" s="67" t="n">
+        <v>110</v>
+      </c>
+      <c r="M28" s="66" t="n">
         <v>-175</v>
       </c>
-      <c r="M28" s="67" t="n">
+      <c r="N28" s="67" t="n">
         <v>2460</v>
       </c>
-      <c r="N28" s="58" t="inlineStr">
+      <c r="O28" s="58" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -11225,12 +11569,12 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:N28"/>
+  <autoFilter ref="A4:O28"/>
   <mergeCells count="4">
-    <mergeCell ref="L1:N1"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A31:N31"/>
-    <mergeCell ref="A30:N30"/>
+    <mergeCell ref="L1:O1"/>
+    <mergeCell ref="A31:O31"/>
+    <mergeCell ref="A30:O30"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B28">
     <cfRule type="dataBar" priority="1">
@@ -11241,7 +11585,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1F269059-8226-46AC-9566-DA9D87241A9F}</x14:id>
+          <x14:id>{52119893-F2E8-4375-A669-099B318F34F5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11255,7 +11599,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{63C0BD58-7207-4A6B-A50E-CFCD9DBB87B7}</x14:id>
+          <x14:id>{F04CAFF2-0BE9-495C-AC96-D6B1C1E28D73}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11269,7 +11613,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{B140D0C0-326B-41BF-96A1-E846091EC5CD}</x14:id>
+          <x14:id>{61F2EA4C-6B5C-4898-BEE1-36F098A8C332}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11283,7 +11627,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{747687B9-E2C6-4036-98AC-8896E92DA536}</x14:id>
+          <x14:id>{1DA41913-2B0F-4E82-8FC2-19385FEB771E}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11293,7 +11637,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1F269059-8226-46AC-9566-DA9D87241A9F}">
+          <x14:cfRule type="dataBar" id="{52119893-F2E8-4375-A669-099B318F34F5}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11306,7 +11650,7 @@
           <xm:sqref>B5:B28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{63C0BD58-7207-4A6B-A50E-CFCD9DBB87B7}">
+          <x14:cfRule type="dataBar" id="{F04CAFF2-0BE9-495C-AC96-D6B1C1E28D73}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11319,7 +11663,7 @@
           <xm:sqref>C5:C28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{B140D0C0-326B-41BF-96A1-E846091EC5CD}">
+          <x14:cfRule type="dataBar" id="{61F2EA4C-6B5C-4898-BEE1-36F098A8C332}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11332,7 +11676,7 @@
           <xm:sqref>D5:D28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{747687B9-E2C6-4036-98AC-8896E92DA536}">
+          <x14:cfRule type="dataBar" id="{1DA41913-2B0F-4E82-8FC2-19385FEB771E}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/public/monthly_review.xlsx
+++ b/public/monthly_review.xlsx
@@ -22,15 +22,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="+0.0&quot;%&quot;;-0.0&quot;%&quot;;0.0&quot;%&quot;"/>
     <numFmt numFmtId="165" formatCode="+0;-0;0"/>
     <numFmt numFmtId="166" formatCode="+#,##0;-#,##0;0"/>
     <numFmt numFmtId="167" formatCode="+#,##0.0;-#,##0.0;0.0"/>
     <numFmt numFmtId="168" formatCode="+0.00;-0.00;0"/>
-    <numFmt numFmtId="169" formatCode="0.000"/>
-    <numFmt numFmtId="170" formatCode="#,##0.0"/>
-    <numFmt numFmtId="171" formatCode="+0.00;-0.00;0.00"/>
+    <numFmt numFmtId="169" formatCode="+0.00;-0.00;0.00"/>
   </numFmts>
   <fonts count="31">
     <font>
@@ -336,7 +334,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -523,22 +521,16 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -553,7 +545,7 @@
     <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -10973,15 +10965,15 @@
     <col width="16" customWidth="1" style="15" min="8" max="8"/>
     <col width="12.5" customWidth="1" style="15" min="9" max="9"/>
     <col width="10.5" customWidth="1" style="15" min="10" max="10"/>
-    <col width="10" customWidth="1" style="15" min="11" max="11"/>
-    <col width="9" customWidth="1" style="15" min="12" max="12"/>
+    <col width="12.5" customWidth="1" style="15" min="11" max="11"/>
+    <col width="10.5" customWidth="1" style="15" min="12" max="12"/>
     <col width="2" customWidth="1" style="15" min="13" max="13"/>
     <col width="4.5" customWidth="1" style="15" min="14" max="14"/>
     <col width="16" customWidth="1" style="15" min="15" max="15"/>
     <col width="12.5" customWidth="1" style="15" min="16" max="16"/>
     <col width="10.5" customWidth="1" style="15" min="17" max="17"/>
-    <col width="10" customWidth="1" style="15" min="18" max="18"/>
-    <col width="9" customWidth="1" style="15" min="19" max="19"/>
+    <col width="12.5" customWidth="1" style="15" min="18" max="18"/>
+    <col width="10.5" customWidth="1" style="15" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="20.25" customHeight="1" s="15">
@@ -11067,7 +11059,7 @@
       </c>
       <c r="K4" s="45" t="inlineStr">
         <is>
-          <t>잔고(억)</t>
+          <t>대차잔고(억)</t>
         </is>
       </c>
       <c r="L4" s="45" t="inlineStr">
@@ -11097,7 +11089,7 @@
       </c>
       <c r="R4" s="45" t="inlineStr">
         <is>
-          <t>잔고(억)</t>
+          <t>대차잔고(억)</t>
         </is>
       </c>
       <c r="S4" s="45" t="inlineStr">
@@ -11124,7 +11116,7 @@
         <v>59426</v>
       </c>
       <c r="E5" s="64" t="n">
-        <v>0.435</v>
+        <v>0.43</v>
       </c>
       <c r="G5" s="30" t="n">
         <v>1</v>
@@ -11139,13 +11131,13 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J5" s="53" t="n">
+      <c r="J5" s="47" t="n">
         <v>12378</v>
       </c>
       <c r="K5" s="65" t="n">
         <v>208999.9</v>
       </c>
-      <c r="L5" s="66" t="n">
+      <c r="L5" s="64" t="n">
         <v>1.53</v>
       </c>
       <c r="N5" s="30" t="n">
@@ -11161,13 +11153,13 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q5" s="67" t="n">
+      <c r="Q5" s="60" t="n">
         <v>-6226.1</v>
       </c>
       <c r="R5" s="65" t="n">
         <v>6939.4</v>
       </c>
-      <c r="S5" s="66" t="n">
+      <c r="S5" s="64" t="n">
         <v>5.65</v>
       </c>
     </row>
@@ -11189,7 +11181,7 @@
         <v>35381</v>
       </c>
       <c r="E6" s="64" t="n">
-        <v>0.221</v>
+        <v>0.22</v>
       </c>
       <c r="G6" s="30" t="n">
         <v>2</v>
@@ -11204,13 +11196,13 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J6" s="53" t="n">
+      <c r="J6" s="47" t="n">
         <v>11215.1</v>
       </c>
       <c r="K6" s="65" t="n">
         <v>240805.1</v>
       </c>
-      <c r="L6" s="66" t="n">
+      <c r="L6" s="64" t="n">
         <v>1.5</v>
       </c>
       <c r="N6" s="30" t="n">
@@ -11226,13 +11218,13 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q6" s="67" t="n">
+      <c r="Q6" s="60" t="n">
         <v>-5616</v>
       </c>
       <c r="R6" s="65" t="n">
         <v>35178.7</v>
       </c>
-      <c r="S6" s="66" t="n">
+      <c r="S6" s="64" t="n">
         <v>3.3</v>
       </c>
     </row>
@@ -11254,7 +11246,7 @@
         <v>6953</v>
       </c>
       <c r="E7" s="64" t="n">
-        <v>3.085</v>
+        <v>3.08</v>
       </c>
       <c r="G7" s="30" t="n">
         <v>3</v>
@@ -11265,13 +11257,13 @@
         </is>
       </c>
       <c r="I7" s="35" t="inlineStr"/>
-      <c r="J7" s="53" t="n">
+      <c r="J7" s="47" t="n">
         <v>8488.6</v>
       </c>
       <c r="K7" s="65" t="n">
         <v>29995.7</v>
       </c>
-      <c r="L7" s="66" t="n">
+      <c r="L7" s="64" t="n">
         <v>1.77</v>
       </c>
       <c r="N7" s="30" t="n">
@@ -11287,13 +11279,13 @@
           <t>화학</t>
         </is>
       </c>
-      <c r="Q7" s="67" t="n">
+      <c r="Q7" s="60" t="n">
         <v>-4150.1</v>
       </c>
       <c r="R7" s="65" t="n">
         <v>13846.3</v>
       </c>
-      <c r="S7" s="66" t="n">
+      <c r="S7" s="64" t="n">
         <v>10.11</v>
       </c>
     </row>
@@ -11315,7 +11307,7 @@
         <v>6312</v>
       </c>
       <c r="E8" s="64" t="n">
-        <v>1.155</v>
+        <v>1.16</v>
       </c>
       <c r="G8" s="30" t="n">
         <v>4</v>
@@ -11330,13 +11322,13 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="J8" s="53" t="n">
+      <c r="J8" s="47" t="n">
         <v>7411.2</v>
       </c>
       <c r="K8" s="65" t="n">
         <v>47977.8</v>
       </c>
-      <c r="L8" s="66" t="n">
+      <c r="L8" s="64" t="n">
         <v>21.28</v>
       </c>
       <c r="N8" s="30" t="n">
@@ -11352,13 +11344,13 @@
           <t>제약</t>
         </is>
       </c>
-      <c r="Q8" s="67" t="n">
+      <c r="Q8" s="60" t="n">
         <v>-3828.9</v>
       </c>
       <c r="R8" s="65" t="n">
         <v>9884.200000000001</v>
       </c>
-      <c r="S8" s="66" t="n">
+      <c r="S8" s="64" t="n">
         <v>1.52</v>
       </c>
     </row>
@@ -11376,7 +11368,7 @@
         <v>5212</v>
       </c>
       <c r="E9" s="64" t="n">
-        <v>0.714</v>
+        <v>0.71</v>
       </c>
       <c r="G9" s="30" t="n">
         <v>5</v>
@@ -11391,13 +11383,13 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J9" s="53" t="n">
+      <c r="J9" s="47" t="n">
         <v>2760.5</v>
       </c>
       <c r="K9" s="65" t="n">
         <v>7215.1</v>
       </c>
-      <c r="L9" s="66" t="n">
+      <c r="L9" s="64" t="n">
         <v>12.57</v>
       </c>
       <c r="N9" s="30" t="n">
@@ -11413,13 +11405,13 @@
           <t>제약</t>
         </is>
       </c>
-      <c r="Q9" s="67" t="n">
+      <c r="Q9" s="60" t="n">
         <v>-3500</v>
       </c>
       <c r="R9" s="65" t="n">
         <v>4142.7</v>
       </c>
-      <c r="S9" s="66" t="n">
+      <c r="S9" s="64" t="n">
         <v>9.73</v>
       </c>
     </row>
@@ -11441,7 +11433,7 @@
         <v>4502</v>
       </c>
       <c r="E10" s="64" t="n">
-        <v>0.422</v>
+        <v>0.42</v>
       </c>
       <c r="G10" s="30" t="n">
         <v>6</v>
@@ -11456,13 +11448,13 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="J10" s="53" t="n">
+      <c r="J10" s="47" t="n">
         <v>2662.8</v>
       </c>
       <c r="K10" s="65" t="n">
         <v>8074.2</v>
       </c>
-      <c r="L10" s="66" t="n">
+      <c r="L10" s="64" t="n">
         <v>13.54</v>
       </c>
       <c r="N10" s="30" t="n">
@@ -11478,13 +11470,13 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q10" s="67" t="n">
+      <c r="Q10" s="60" t="n">
         <v>-3193.1</v>
       </c>
       <c r="R10" s="65" t="n">
         <v>2361.2</v>
       </c>
-      <c r="S10" s="66" t="n">
+      <c r="S10" s="64" t="n">
         <v>5.54</v>
       </c>
     </row>
@@ -11506,7 +11498,7 @@
         <v>3808</v>
       </c>
       <c r="E11" s="64" t="n">
-        <v>0.256</v>
+        <v>0.26</v>
       </c>
       <c r="G11" s="30" t="n">
         <v>7</v>
@@ -11521,13 +11513,13 @@
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="J11" s="53" t="n">
+      <c r="J11" s="47" t="n">
         <v>2589</v>
       </c>
       <c r="K11" s="65" t="n">
         <v>5434.2</v>
       </c>
-      <c r="L11" s="66" t="n">
+      <c r="L11" s="64" t="n">
         <v>10.97</v>
       </c>
       <c r="N11" s="30" t="n">
@@ -11543,13 +11535,13 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q11" s="67" t="n">
+      <c r="Q11" s="60" t="n">
         <v>-3157.3</v>
       </c>
       <c r="R11" s="65" t="n">
         <v>13002.5</v>
       </c>
-      <c r="S11" s="66" t="n">
+      <c r="S11" s="64" t="n">
         <v>3.03</v>
       </c>
     </row>
@@ -11571,7 +11563,7 @@
         <v>3667</v>
       </c>
       <c r="E12" s="64" t="n">
-        <v>3.839</v>
+        <v>3.84</v>
       </c>
       <c r="G12" s="30" t="n">
         <v>8</v>
@@ -11586,13 +11578,13 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="J12" s="53" t="n">
+      <c r="J12" s="47" t="n">
         <v>2259.1</v>
       </c>
       <c r="K12" s="65" t="n">
         <v>19577</v>
       </c>
-      <c r="L12" s="66" t="n">
+      <c r="L12" s="64" t="n">
         <v>3.58</v>
       </c>
       <c r="N12" s="30" t="n">
@@ -11608,13 +11600,13 @@
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="Q12" s="67" t="n">
+      <c r="Q12" s="60" t="n">
         <v>-2785.3</v>
       </c>
       <c r="R12" s="65" t="n">
         <v>11840.5</v>
       </c>
-      <c r="S12" s="66" t="n">
+      <c r="S12" s="64" t="n">
         <v>6.67</v>
       </c>
     </row>
@@ -11636,7 +11628,7 @@
         <v>3334</v>
       </c>
       <c r="E13" s="64" t="n">
-        <v>1.877</v>
+        <v>1.88</v>
       </c>
       <c r="G13" s="30" t="n">
         <v>9</v>
@@ -11651,13 +11643,13 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J13" s="53" t="n">
+      <c r="J13" s="47" t="n">
         <v>1812</v>
       </c>
       <c r="K13" s="65" t="n">
         <v>4132.8</v>
       </c>
-      <c r="L13" s="66" t="n">
+      <c r="L13" s="64" t="n">
         <v>4.36</v>
       </c>
       <c r="N13" s="30" t="n">
@@ -11673,13 +11665,13 @@
           <t>음식료·담배</t>
         </is>
       </c>
-      <c r="Q13" s="67" t="n">
+      <c r="Q13" s="60" t="n">
         <v>-2687.3</v>
       </c>
       <c r="R13" s="65" t="n">
         <v>7411.1</v>
       </c>
-      <c r="S13" s="66" t="n">
+      <c r="S13" s="64" t="n">
         <v>7.71</v>
       </c>
     </row>
@@ -11701,7 +11693,7 @@
         <v>3219</v>
       </c>
       <c r="E14" s="64" t="n">
-        <v>0.391</v>
+        <v>0.39</v>
       </c>
       <c r="G14" s="30" t="n">
         <v>10</v>
@@ -11716,13 +11708,13 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="J14" s="53" t="n">
+      <c r="J14" s="47" t="n">
         <v>1595.9</v>
       </c>
       <c r="K14" s="65" t="n">
         <v>16003</v>
       </c>
-      <c r="L14" s="66" t="n">
+      <c r="L14" s="64" t="n">
         <v>16.75</v>
       </c>
       <c r="N14" s="30" t="n">
@@ -11738,13 +11730,13 @@
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q14" s="67" t="n">
+      <c r="Q14" s="60" t="n">
         <v>-2081.4</v>
       </c>
       <c r="R14" s="65" t="n">
         <v>7449.2</v>
       </c>
-      <c r="S14" s="66" t="n">
+      <c r="S14" s="64" t="n">
         <v>4.11</v>
       </c>
     </row>
@@ -11925,43 +11917,43 @@
           <t>의료·정밀기기</t>
         </is>
       </c>
-      <c r="B5" s="68" t="n">
+      <c r="B5" s="66" t="n">
         <v>21.13</v>
       </c>
-      <c r="C5" s="68" t="n">
+      <c r="C5" s="66" t="n">
         <v>0.48</v>
       </c>
-      <c r="D5" s="69" t="n">
+      <c r="D5" s="67" t="n">
         <v>-3.99</v>
       </c>
-      <c r="E5" s="68" t="n">
+      <c r="E5" s="66" t="n">
         <v>14.6</v>
       </c>
-      <c r="F5" s="70" t="n">
+      <c r="F5" s="68" t="n">
         <v>90</v>
       </c>
-      <c r="G5" s="70" t="n">
+      <c r="G5" s="68" t="n">
         <v>395</v>
       </c>
-      <c r="H5" s="70" t="n">
+      <c r="H5" s="68" t="n">
         <v>485</v>
       </c>
-      <c r="I5" s="70" t="n">
+      <c r="I5" s="68" t="n">
         <v>38</v>
       </c>
-      <c r="J5" s="70" t="n">
+      <c r="J5" s="68" t="n">
         <v>80</v>
       </c>
-      <c r="K5" s="70" t="n">
+      <c r="K5" s="68" t="n">
         <v>239</v>
       </c>
-      <c r="L5" s="70" t="n">
+      <c r="L5" s="68" t="n">
         <v>36</v>
       </c>
-      <c r="M5" s="71" t="n">
+      <c r="M5" s="69" t="n">
         <v>-485</v>
       </c>
-      <c r="N5" s="72" t="n">
+      <c r="N5" s="70" t="n">
         <v>0</v>
       </c>
       <c r="O5" s="58" t="inlineStr">
@@ -11976,43 +11968,43 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="B6" s="68" t="n">
+      <c r="B6" s="66" t="n">
         <v>122.14</v>
       </c>
-      <c r="C6" s="68" t="n">
+      <c r="C6" s="66" t="n">
         <v>49.6</v>
       </c>
-      <c r="D6" s="69" t="n">
+      <c r="D6" s="67" t="n">
         <v>-28.1</v>
       </c>
-      <c r="E6" s="68" t="n">
+      <c r="E6" s="66" t="n">
         <v>6.51</v>
       </c>
-      <c r="F6" s="71" t="n">
+      <c r="F6" s="69" t="n">
         <v>-110686</v>
       </c>
-      <c r="G6" s="70" t="n">
+      <c r="G6" s="68" t="n">
         <v>43765</v>
       </c>
-      <c r="H6" s="71" t="n">
+      <c r="H6" s="69" t="n">
         <v>-66921</v>
       </c>
-      <c r="I6" s="70" t="n">
+      <c r="I6" s="68" t="n">
         <v>55017</v>
       </c>
-      <c r="J6" s="71" t="n">
+      <c r="J6" s="69" t="n">
         <v>-8409</v>
       </c>
-      <c r="K6" s="71" t="n">
+      <c r="K6" s="69" t="n">
         <v>-3252</v>
       </c>
-      <c r="L6" s="70" t="n">
+      <c r="L6" s="68" t="n">
         <v>249</v>
       </c>
-      <c r="M6" s="71" t="n">
+      <c r="M6" s="69" t="n">
         <v>-191343</v>
       </c>
-      <c r="N6" s="70" t="n">
+      <c r="N6" s="68" t="n">
         <v>258264</v>
       </c>
       <c r="O6" s="30" t="inlineStr"/>
@@ -12023,43 +12015,43 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="B7" s="68" t="n">
+      <c r="B7" s="66" t="n">
         <v>16.02</v>
       </c>
-      <c r="C7" s="69" t="n">
+      <c r="C7" s="67" t="n">
         <v>-19.7</v>
       </c>
-      <c r="D7" s="69" t="n">
+      <c r="D7" s="67" t="n">
         <v>-12.44</v>
       </c>
-      <c r="E7" s="68" t="n">
+      <c r="E7" s="66" t="n">
         <v>3.94</v>
       </c>
-      <c r="F7" s="71" t="n">
+      <c r="F7" s="69" t="n">
         <v>-6663</v>
       </c>
-      <c r="G7" s="70" t="n">
+      <c r="G7" s="68" t="n">
         <v>4926</v>
       </c>
-      <c r="H7" s="71" t="n">
+      <c r="H7" s="69" t="n">
         <v>-1738</v>
       </c>
-      <c r="I7" s="71" t="n">
+      <c r="I7" s="69" t="n">
         <v>-684</v>
       </c>
-      <c r="J7" s="70" t="n">
+      <c r="J7" s="68" t="n">
         <v>4183</v>
       </c>
-      <c r="K7" s="70" t="n">
+      <c r="K7" s="68" t="n">
         <v>1234</v>
       </c>
-      <c r="L7" s="70" t="n">
+      <c r="L7" s="68" t="n">
         <v>177</v>
       </c>
-      <c r="M7" s="70" t="n">
+      <c r="M7" s="68" t="n">
         <v>1711</v>
       </c>
-      <c r="N7" s="70" t="n">
+      <c r="N7" s="68" t="n">
         <v>27</v>
       </c>
       <c r="O7" s="30" t="inlineStr"/>
@@ -12070,46 +12062,46 @@
           <t>제조</t>
         </is>
       </c>
-      <c r="B8" s="68" t="n">
+      <c r="B8" s="66" t="n">
         <v>77.28</v>
       </c>
-      <c r="C8" s="68" t="n">
+      <c r="C8" s="66" t="n">
         <v>27.88</v>
       </c>
-      <c r="D8" s="69" t="n">
+      <c r="D8" s="67" t="n">
         <v>-25.39</v>
       </c>
-      <c r="E8" s="68" t="n">
+      <c r="E8" s="66" t="n">
         <v>3.8</v>
       </c>
-      <c r="F8" s="71" t="n">
+      <c r="F8" s="69" t="n">
         <v>-123600</v>
       </c>
-      <c r="G8" s="70" t="n">
+      <c r="G8" s="68" t="n">
         <v>39490</v>
       </c>
-      <c r="H8" s="71" t="n">
+      <c r="H8" s="69" t="n">
         <v>-84110</v>
       </c>
-      <c r="I8" s="70" t="n">
+      <c r="I8" s="68" t="n">
         <v>52110</v>
       </c>
-      <c r="J8" s="71" t="n">
+      <c r="J8" s="69" t="n">
         <v>-8432</v>
       </c>
-      <c r="K8" s="71" t="n">
+      <c r="K8" s="69" t="n">
         <v>-4436</v>
       </c>
-      <c r="L8" s="70" t="n">
+      <c r="L8" s="68" t="n">
         <v>188</v>
       </c>
-      <c r="M8" s="71" t="n">
+      <c r="M8" s="69" t="n">
         <v>-176325</v>
       </c>
-      <c r="N8" s="70" t="n">
+      <c r="N8" s="68" t="n">
         <v>260434</v>
       </c>
-      <c r="O8" s="73" t="inlineStr">
+      <c r="O8" s="71" t="inlineStr">
         <is>
           <t>수급이탈</t>
         </is>
@@ -12121,40 +12113,40 @@
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="B9" s="74" t="inlineStr"/>
-      <c r="C9" s="74" t="inlineStr"/>
-      <c r="D9" s="74" t="inlineStr"/>
-      <c r="E9" s="68" t="n">
+      <c r="B9" s="72" t="inlineStr"/>
+      <c r="C9" s="72" t="inlineStr"/>
+      <c r="D9" s="72" t="inlineStr"/>
+      <c r="E9" s="66" t="n">
         <v>3.77</v>
       </c>
-      <c r="F9" s="71" t="n">
+      <c r="F9" s="69" t="n">
         <v>-2413</v>
       </c>
-      <c r="G9" s="70" t="n">
+      <c r="G9" s="68" t="n">
         <v>3760</v>
       </c>
-      <c r="H9" s="70" t="n">
+      <c r="H9" s="68" t="n">
         <v>1347</v>
       </c>
-      <c r="I9" s="70" t="n">
+      <c r="I9" s="68" t="n">
         <v>2126</v>
       </c>
-      <c r="J9" s="70" t="n">
+      <c r="J9" s="68" t="n">
         <v>643</v>
       </c>
-      <c r="K9" s="70" t="n">
+      <c r="K9" s="68" t="n">
         <v>946</v>
       </c>
-      <c r="L9" s="70" t="n">
+      <c r="L9" s="68" t="n">
         <v>53</v>
       </c>
-      <c r="M9" s="70" t="n">
+      <c r="M9" s="68" t="n">
         <v>412</v>
       </c>
-      <c r="N9" s="71" t="n">
+      <c r="N9" s="69" t="n">
         <v>-1759</v>
       </c>
-      <c r="O9" s="75" t="inlineStr">
+      <c r="O9" s="73" t="inlineStr">
         <is>
           <t>데이터부족</t>
         </is>
@@ -12166,43 +12158,43 @@
           <t>건설</t>
         </is>
       </c>
-      <c r="B10" s="68" t="n">
+      <c r="B10" s="66" t="n">
         <v>80.48</v>
       </c>
-      <c r="C10" s="69" t="n">
+      <c r="C10" s="67" t="n">
         <v>-12.44</v>
       </c>
-      <c r="D10" s="68" t="n">
+      <c r="D10" s="66" t="n">
         <v>2.43</v>
       </c>
-      <c r="E10" s="68" t="n">
+      <c r="E10" s="66" t="n">
         <v>3.63</v>
       </c>
-      <c r="F10" s="71" t="n">
+      <c r="F10" s="69" t="n">
         <v>-1713</v>
       </c>
-      <c r="G10" s="70" t="n">
+      <c r="G10" s="68" t="n">
         <v>2178</v>
       </c>
-      <c r="H10" s="70" t="n">
+      <c r="H10" s="68" t="n">
         <v>465</v>
       </c>
-      <c r="I10" s="70" t="n">
+      <c r="I10" s="68" t="n">
         <v>648</v>
       </c>
-      <c r="J10" s="70" t="n">
+      <c r="J10" s="68" t="n">
         <v>1079</v>
       </c>
-      <c r="K10" s="70" t="n">
+      <c r="K10" s="68" t="n">
         <v>344</v>
       </c>
-      <c r="L10" s="70" t="n">
+      <c r="L10" s="68" t="n">
         <v>102</v>
       </c>
-      <c r="M10" s="71" t="n">
+      <c r="M10" s="69" t="n">
         <v>-1744</v>
       </c>
-      <c r="N10" s="70" t="n">
+      <c r="N10" s="68" t="n">
         <v>1279</v>
       </c>
       <c r="O10" s="30" t="inlineStr"/>
@@ -12213,43 +12205,43 @@
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="B11" s="68" t="n">
+      <c r="B11" s="66" t="n">
         <v>10.99</v>
       </c>
-      <c r="C11" s="69" t="n">
+      <c r="C11" s="67" t="n">
         <v>-3.32</v>
       </c>
-      <c r="D11" s="68" t="n">
+      <c r="D11" s="66" t="n">
         <v>6.6</v>
       </c>
-      <c r="E11" s="68" t="n">
+      <c r="E11" s="66" t="n">
         <v>1.36</v>
       </c>
-      <c r="F11" s="70" t="n">
+      <c r="F11" s="68" t="n">
         <v>2903</v>
       </c>
-      <c r="G11" s="70" t="n">
+      <c r="G11" s="68" t="n">
         <v>825</v>
       </c>
-      <c r="H11" s="70" t="n">
+      <c r="H11" s="68" t="n">
         <v>3728</v>
       </c>
-      <c r="I11" s="71" t="n">
+      <c r="I11" s="69" t="n">
         <v>-332</v>
       </c>
-      <c r="J11" s="70" t="n">
+      <c r="J11" s="68" t="n">
         <v>363</v>
       </c>
-      <c r="K11" s="70" t="n">
+      <c r="K11" s="68" t="n">
         <v>755</v>
       </c>
-      <c r="L11" s="70" t="n">
+      <c r="L11" s="68" t="n">
         <v>36</v>
       </c>
-      <c r="M11" s="71" t="n">
+      <c r="M11" s="69" t="n">
         <v>-3672</v>
       </c>
-      <c r="N11" s="71" t="n">
+      <c r="N11" s="69" t="n">
         <v>-57</v>
       </c>
       <c r="O11" s="58" t="inlineStr">
@@ -12264,43 +12256,43 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="B12" s="68" t="n">
+      <c r="B12" s="66" t="n">
         <v>44.44</v>
       </c>
-      <c r="C12" s="68" t="n">
+      <c r="C12" s="66" t="n">
         <v>10.56</v>
       </c>
-      <c r="D12" s="69" t="n">
+      <c r="D12" s="67" t="n">
         <v>-15.68</v>
       </c>
-      <c r="E12" s="68" t="n">
+      <c r="E12" s="66" t="n">
         <v>1.01</v>
       </c>
-      <c r="F12" s="70" t="n">
+      <c r="F12" s="68" t="n">
         <v>4880</v>
       </c>
-      <c r="G12" s="70" t="n">
+      <c r="G12" s="68" t="n">
         <v>6475</v>
       </c>
-      <c r="H12" s="70" t="n">
+      <c r="H12" s="68" t="n">
         <v>11355</v>
       </c>
-      <c r="I12" s="70" t="n">
+      <c r="I12" s="68" t="n">
         <v>2616</v>
       </c>
-      <c r="J12" s="71" t="n">
+      <c r="J12" s="69" t="n">
         <v>-345</v>
       </c>
-      <c r="K12" s="70" t="n">
+      <c r="K12" s="68" t="n">
         <v>642</v>
       </c>
-      <c r="L12" s="70" t="n">
+      <c r="L12" s="68" t="n">
         <v>222</v>
       </c>
-      <c r="M12" s="71" t="n">
+      <c r="M12" s="69" t="n">
         <v>-7282</v>
       </c>
-      <c r="N12" s="71" t="n">
+      <c r="N12" s="69" t="n">
         <v>-4073</v>
       </c>
       <c r="O12" s="58" t="inlineStr">
@@ -12315,43 +12307,43 @@
           <t>섬유·의류</t>
         </is>
       </c>
-      <c r="B13" s="69" t="n">
+      <c r="B13" s="67" t="n">
         <v>-5.45</v>
       </c>
-      <c r="C13" s="69" t="n">
+      <c r="C13" s="67" t="n">
         <v>-8.359999999999999</v>
       </c>
-      <c r="D13" s="69" t="n">
+      <c r="D13" s="67" t="n">
         <v>-1.57</v>
       </c>
-      <c r="E13" s="68" t="n">
+      <c r="E13" s="66" t="n">
         <v>0.17</v>
       </c>
-      <c r="F13" s="71" t="n">
+      <c r="F13" s="69" t="n">
         <v>-215</v>
       </c>
-      <c r="G13" s="70" t="n">
+      <c r="G13" s="68" t="n">
         <v>213</v>
       </c>
-      <c r="H13" s="71" t="n">
+      <c r="H13" s="69" t="n">
         <v>-2</v>
       </c>
-      <c r="I13" s="70" t="n">
+      <c r="I13" s="68" t="n">
         <v>50</v>
       </c>
-      <c r="J13" s="70" t="n">
+      <c r="J13" s="68" t="n">
         <v>40</v>
       </c>
-      <c r="K13" s="70" t="n">
+      <c r="K13" s="68" t="n">
         <v>123</v>
       </c>
-      <c r="L13" s="70" t="n">
+      <c r="L13" s="68" t="n">
         <v>12</v>
       </c>
-      <c r="M13" s="71" t="n">
+      <c r="M13" s="69" t="n">
         <v>-30</v>
       </c>
-      <c r="N13" s="70" t="n">
+      <c r="N13" s="68" t="n">
         <v>33</v>
       </c>
       <c r="O13" s="30" t="inlineStr"/>
@@ -12362,46 +12354,46 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="B14" s="69" t="n">
+      <c r="B14" s="67" t="n">
         <v>-9.84</v>
       </c>
-      <c r="C14" s="69" t="n">
+      <c r="C14" s="67" t="n">
         <v>-13.08</v>
       </c>
-      <c r="D14" s="68" t="n">
+      <c r="D14" s="66" t="n">
         <v>3.05</v>
       </c>
-      <c r="E14" s="69" t="n">
+      <c r="E14" s="67" t="n">
         <v>-0.66</v>
       </c>
-      <c r="F14" s="70" t="n">
+      <c r="F14" s="68" t="n">
         <v>14</v>
       </c>
-      <c r="G14" s="70" t="n">
+      <c r="G14" s="68" t="n">
         <v>178</v>
       </c>
-      <c r="H14" s="70" t="n">
+      <c r="H14" s="68" t="n">
         <v>193</v>
       </c>
-      <c r="I14" s="70" t="n">
+      <c r="I14" s="68" t="n">
         <v>160</v>
       </c>
-      <c r="J14" s="71" t="n">
+      <c r="J14" s="69" t="n">
         <v>-104</v>
       </c>
-      <c r="K14" s="70" t="n">
+      <c r="K14" s="68" t="n">
         <v>155</v>
       </c>
-      <c r="L14" s="71" t="n">
+      <c r="L14" s="69" t="n">
         <v>-30</v>
       </c>
-      <c r="M14" s="71" t="n">
+      <c r="M14" s="69" t="n">
         <v>-178</v>
       </c>
-      <c r="N14" s="71" t="n">
+      <c r="N14" s="69" t="n">
         <v>-15</v>
       </c>
-      <c r="O14" s="76" t="inlineStr">
+      <c r="O14" s="74" t="inlineStr">
         <is>
           <t>수급유입</t>
         </is>
@@ -12413,43 +12405,43 @@
           <t>유통</t>
         </is>
       </c>
-      <c r="B15" s="68" t="n">
+      <c r="B15" s="66" t="n">
         <v>28.65</v>
       </c>
-      <c r="C15" s="68" t="n">
+      <c r="C15" s="66" t="n">
         <v>4.46</v>
       </c>
-      <c r="D15" s="69" t="n">
+      <c r="D15" s="67" t="n">
         <v>-22.79</v>
       </c>
-      <c r="E15" s="69" t="n">
+      <c r="E15" s="67" t="n">
         <v>-2.07</v>
       </c>
-      <c r="F15" s="71" t="n">
+      <c r="F15" s="69" t="n">
         <v>-3801</v>
       </c>
-      <c r="G15" s="70" t="n">
+      <c r="G15" s="68" t="n">
         <v>10939</v>
       </c>
-      <c r="H15" s="70" t="n">
+      <c r="H15" s="68" t="n">
         <v>7139</v>
       </c>
-      <c r="I15" s="70" t="n">
+      <c r="I15" s="68" t="n">
         <v>9090</v>
       </c>
-      <c r="J15" s="70" t="n">
+      <c r="J15" s="68" t="n">
         <v>1299</v>
       </c>
-      <c r="K15" s="70" t="n">
+      <c r="K15" s="68" t="n">
         <v>506</v>
       </c>
-      <c r="L15" s="70" t="n">
+      <c r="L15" s="68" t="n">
         <v>40</v>
       </c>
-      <c r="M15" s="70" t="n">
+      <c r="M15" s="68" t="n">
         <v>322</v>
       </c>
-      <c r="N15" s="71" t="n">
+      <c r="N15" s="69" t="n">
         <v>-7461</v>
       </c>
       <c r="O15" s="30" t="inlineStr"/>
@@ -12460,43 +12452,43 @@
           <t>보험</t>
         </is>
       </c>
-      <c r="B16" s="68" t="n">
+      <c r="B16" s="66" t="n">
         <v>56.78</v>
       </c>
-      <c r="C16" s="68" t="n">
+      <c r="C16" s="66" t="n">
         <v>21.31</v>
       </c>
-      <c r="D16" s="69" t="n">
+      <c r="D16" s="67" t="n">
         <v>-19.36</v>
       </c>
-      <c r="E16" s="69" t="n">
+      <c r="E16" s="67" t="n">
         <v>-3.19</v>
       </c>
-      <c r="F16" s="71" t="n">
+      <c r="F16" s="69" t="n">
         <v>-2295</v>
       </c>
-      <c r="G16" s="70" t="n">
+      <c r="G16" s="68" t="n">
         <v>2350</v>
       </c>
-      <c r="H16" s="70" t="n">
+      <c r="H16" s="68" t="n">
         <v>55</v>
       </c>
-      <c r="I16" s="70" t="n">
+      <c r="I16" s="68" t="n">
         <v>276</v>
       </c>
-      <c r="J16" s="70" t="n">
+      <c r="J16" s="68" t="n">
         <v>605</v>
       </c>
-      <c r="K16" s="70" t="n">
+      <c r="K16" s="68" t="n">
         <v>1450</v>
       </c>
-      <c r="L16" s="70" t="n">
+      <c r="L16" s="68" t="n">
         <v>25</v>
       </c>
-      <c r="M16" s="71" t="n">
+      <c r="M16" s="69" t="n">
         <v>-208</v>
       </c>
-      <c r="N16" s="70" t="n">
+      <c r="N16" s="68" t="n">
         <v>153</v>
       </c>
       <c r="O16" s="30" t="inlineStr"/>
@@ -12507,43 +12499,43 @@
           <t>전기·가스</t>
         </is>
       </c>
-      <c r="B17" s="69" t="n">
+      <c r="B17" s="67" t="n">
         <v>-27.82</v>
       </c>
-      <c r="C17" s="69" t="n">
+      <c r="C17" s="67" t="n">
         <v>-32.47</v>
       </c>
-      <c r="D17" s="69" t="n">
+      <c r="D17" s="67" t="n">
         <v>-13.54</v>
       </c>
-      <c r="E17" s="69" t="n">
+      <c r="E17" s="67" t="n">
         <v>-3.22</v>
       </c>
-      <c r="F17" s="71" t="n">
+      <c r="F17" s="69" t="n">
         <v>-572</v>
       </c>
-      <c r="G17" s="70" t="n">
+      <c r="G17" s="68" t="n">
         <v>32</v>
       </c>
-      <c r="H17" s="71" t="n">
+      <c r="H17" s="69" t="n">
         <v>-540</v>
       </c>
-      <c r="I17" s="70" t="n">
+      <c r="I17" s="68" t="n">
         <v>106</v>
       </c>
-      <c r="J17" s="71" t="n">
+      <c r="J17" s="69" t="n">
         <v>-132</v>
       </c>
-      <c r="K17" s="70" t="n">
+      <c r="K17" s="68" t="n">
         <v>46</v>
       </c>
-      <c r="L17" s="70" t="n">
+      <c r="L17" s="68" t="n">
         <v>12</v>
       </c>
-      <c r="M17" s="70" t="n">
+      <c r="M17" s="68" t="n">
         <v>556</v>
       </c>
-      <c r="N17" s="71" t="n">
+      <c r="N17" s="69" t="n">
         <v>-16</v>
       </c>
       <c r="O17" s="59" t="inlineStr">
@@ -12558,43 +12550,43 @@
           <t>종이·목재</t>
         </is>
       </c>
-      <c r="B18" s="69" t="n">
+      <c r="B18" s="67" t="n">
         <v>-20.68</v>
       </c>
-      <c r="C18" s="69" t="n">
+      <c r="C18" s="67" t="n">
         <v>-20.63</v>
       </c>
-      <c r="D18" s="68" t="n">
+      <c r="D18" s="66" t="n">
         <v>0.96</v>
       </c>
-      <c r="E18" s="69" t="n">
+      <c r="E18" s="67" t="n">
         <v>-3.49</v>
       </c>
-      <c r="F18" s="71" t="n">
+      <c r="F18" s="69" t="n">
         <v>-21</v>
       </c>
-      <c r="G18" s="70" t="n">
+      <c r="G18" s="68" t="n">
         <v>25</v>
       </c>
-      <c r="H18" s="70" t="n">
+      <c r="H18" s="68" t="n">
         <v>4</v>
       </c>
-      <c r="I18" s="70" t="n">
+      <c r="I18" s="68" t="n">
         <v>22</v>
       </c>
-      <c r="J18" s="70" t="n">
+      <c r="J18" s="68" t="n">
         <v>3</v>
       </c>
-      <c r="K18" s="71" t="n">
+      <c r="K18" s="69" t="n">
         <v>-1</v>
       </c>
-      <c r="L18" s="72" t="n">
+      <c r="L18" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="M18" s="71" t="n">
+      <c r="M18" s="69" t="n">
         <v>-5</v>
       </c>
-      <c r="N18" s="70" t="n">
+      <c r="N18" s="68" t="n">
         <v>1</v>
       </c>
       <c r="O18" s="30" t="inlineStr"/>
@@ -12605,43 +12597,43 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="B19" s="68" t="n">
+      <c r="B19" s="66" t="n">
         <v>16.22</v>
       </c>
-      <c r="C19" s="69" t="n">
+      <c r="C19" s="67" t="n">
         <v>-39.23</v>
       </c>
-      <c r="D19" s="69" t="n">
+      <c r="D19" s="67" t="n">
         <v>-21.35</v>
       </c>
-      <c r="E19" s="69" t="n">
+      <c r="E19" s="67" t="n">
         <v>-3.51</v>
       </c>
-      <c r="F19" s="70" t="n">
+      <c r="F19" s="68" t="n">
         <v>1149</v>
       </c>
-      <c r="G19" s="71" t="n">
+      <c r="G19" s="69" t="n">
         <v>-963</v>
       </c>
-      <c r="H19" s="70" t="n">
+      <c r="H19" s="68" t="n">
         <v>186</v>
       </c>
-      <c r="I19" s="70" t="n">
+      <c r="I19" s="68" t="n">
         <v>288</v>
       </c>
-      <c r="J19" s="71" t="n">
+      <c r="J19" s="69" t="n">
         <v>-78</v>
       </c>
-      <c r="K19" s="71" t="n">
+      <c r="K19" s="69" t="n">
         <v>-1032</v>
       </c>
-      <c r="L19" s="71" t="n">
+      <c r="L19" s="69" t="n">
         <v>-171</v>
       </c>
-      <c r="M19" s="71" t="n">
+      <c r="M19" s="69" t="n">
         <v>-187</v>
       </c>
-      <c r="N19" s="70" t="n">
+      <c r="N19" s="68" t="n">
         <v>1</v>
       </c>
       <c r="O19" s="30" t="inlineStr"/>
@@ -12652,43 +12644,43 @@
           <t>통신</t>
         </is>
       </c>
-      <c r="B20" s="68" t="n">
+      <c r="B20" s="66" t="n">
         <v>25.11</v>
       </c>
-      <c r="C20" s="69" t="n">
+      <c r="C20" s="67" t="n">
         <v>-1.65</v>
       </c>
-      <c r="D20" s="69" t="n">
+      <c r="D20" s="67" t="n">
         <v>-3.08</v>
       </c>
-      <c r="E20" s="69" t="n">
+      <c r="E20" s="67" t="n">
         <v>-4.31</v>
       </c>
-      <c r="F20" s="70" t="n">
+      <c r="F20" s="68" t="n">
         <v>29</v>
       </c>
-      <c r="G20" s="71" t="n">
+      <c r="G20" s="69" t="n">
         <v>-509</v>
       </c>
-      <c r="H20" s="71" t="n">
+      <c r="H20" s="69" t="n">
         <v>-479</v>
       </c>
-      <c r="I20" s="70" t="n">
+      <c r="I20" s="68" t="n">
         <v>643</v>
       </c>
-      <c r="J20" s="71" t="n">
+      <c r="J20" s="69" t="n">
         <v>-860</v>
       </c>
-      <c r="K20" s="71" t="n">
+      <c r="K20" s="69" t="n">
         <v>-231</v>
       </c>
-      <c r="L20" s="71" t="n">
+      <c r="L20" s="69" t="n">
         <v>-60</v>
       </c>
-      <c r="M20" s="70" t="n">
+      <c r="M20" s="68" t="n">
         <v>515</v>
       </c>
-      <c r="N20" s="71" t="n">
+      <c r="N20" s="69" t="n">
         <v>-36</v>
       </c>
       <c r="O20" s="30" t="inlineStr"/>
@@ -12699,43 +12691,43 @@
           <t>비금속</t>
         </is>
       </c>
-      <c r="B21" s="69" t="n">
+      <c r="B21" s="67" t="n">
         <v>-13.78</v>
       </c>
-      <c r="C21" s="69" t="n">
+      <c r="C21" s="67" t="n">
         <v>-20.76</v>
       </c>
-      <c r="D21" s="69" t="n">
+      <c r="D21" s="67" t="n">
         <v>-0.86</v>
       </c>
-      <c r="E21" s="69" t="n">
+      <c r="E21" s="67" t="n">
         <v>-4.53</v>
       </c>
-      <c r="F21" s="71" t="n">
+      <c r="F21" s="69" t="n">
         <v>-77</v>
       </c>
-      <c r="G21" s="71" t="n">
+      <c r="G21" s="69" t="n">
         <v>-26</v>
       </c>
-      <c r="H21" s="71" t="n">
+      <c r="H21" s="69" t="n">
         <v>-103</v>
       </c>
-      <c r="I21" s="70" t="n">
+      <c r="I21" s="68" t="n">
         <v>56</v>
       </c>
-      <c r="J21" s="71" t="n">
+      <c r="J21" s="69" t="n">
         <v>-52</v>
       </c>
-      <c r="K21" s="71" t="n">
+      <c r="K21" s="69" t="n">
         <v>-30</v>
       </c>
-      <c r="L21" s="72" t="n">
+      <c r="L21" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="M21" s="70" t="n">
+      <c r="M21" s="68" t="n">
         <v>101</v>
       </c>
-      <c r="N21" s="70" t="n">
+      <c r="N21" s="68" t="n">
         <v>2</v>
       </c>
       <c r="O21" s="59" t="inlineStr">
@@ -12750,43 +12742,43 @@
           <t>금속</t>
         </is>
       </c>
-      <c r="B22" s="68" t="n">
+      <c r="B22" s="66" t="n">
         <v>3.29</v>
       </c>
-      <c r="C22" s="69" t="n">
+      <c r="C22" s="67" t="n">
         <v>-16.33</v>
       </c>
-      <c r="D22" s="69" t="n">
+      <c r="D22" s="67" t="n">
         <v>-6.01</v>
       </c>
-      <c r="E22" s="69" t="n">
+      <c r="E22" s="67" t="n">
         <v>-5.13</v>
       </c>
-      <c r="F22" s="71" t="n">
+      <c r="F22" s="69" t="n">
         <v>-2049</v>
       </c>
-      <c r="G22" s="70" t="n">
+      <c r="G22" s="68" t="n">
         <v>700</v>
       </c>
-      <c r="H22" s="71" t="n">
+      <c r="H22" s="69" t="n">
         <v>-1350</v>
       </c>
-      <c r="I22" s="71" t="n">
+      <c r="I22" s="69" t="n">
         <v>-585</v>
       </c>
-      <c r="J22" s="70" t="n">
+      <c r="J22" s="68" t="n">
         <v>637</v>
       </c>
-      <c r="K22" s="70" t="n">
+      <c r="K22" s="68" t="n">
         <v>640</v>
       </c>
-      <c r="L22" s="70" t="n">
+      <c r="L22" s="68" t="n">
         <v>1</v>
       </c>
-      <c r="M22" s="70" t="n">
+      <c r="M22" s="68" t="n">
         <v>526</v>
       </c>
-      <c r="N22" s="70" t="n">
+      <c r="N22" s="68" t="n">
         <v>823</v>
       </c>
       <c r="O22" s="59" t="inlineStr">
@@ -12801,43 +12793,43 @@
           <t>화학</t>
         </is>
       </c>
-      <c r="B23" s="68" t="n">
+      <c r="B23" s="66" t="n">
         <v>14.97</v>
       </c>
-      <c r="C23" s="69" t="n">
+      <c r="C23" s="67" t="n">
         <v>-3.34</v>
       </c>
-      <c r="D23" s="68" t="n">
+      <c r="D23" s="66" t="n">
         <v>2.95</v>
       </c>
-      <c r="E23" s="69" t="n">
+      <c r="E23" s="67" t="n">
         <v>-5.27</v>
       </c>
-      <c r="F23" s="71" t="n">
+      <c r="F23" s="69" t="n">
         <v>-70</v>
       </c>
-      <c r="G23" s="70" t="n">
+      <c r="G23" s="68" t="n">
         <v>1433</v>
       </c>
-      <c r="H23" s="70" t="n">
+      <c r="H23" s="68" t="n">
         <v>1363</v>
       </c>
-      <c r="I23" s="71" t="n">
+      <c r="I23" s="69" t="n">
         <v>-1760</v>
       </c>
-      <c r="J23" s="70" t="n">
+      <c r="J23" s="68" t="n">
         <v>24</v>
       </c>
-      <c r="K23" s="70" t="n">
+      <c r="K23" s="68" t="n">
         <v>2853</v>
       </c>
-      <c r="L23" s="70" t="n">
+      <c r="L23" s="68" t="n">
         <v>336</v>
       </c>
-      <c r="M23" s="71" t="n">
+      <c r="M23" s="69" t="n">
         <v>-1375</v>
       </c>
-      <c r="N23" s="70" t="n">
+      <c r="N23" s="68" t="n">
         <v>12</v>
       </c>
       <c r="O23" s="30" t="inlineStr"/>
@@ -12848,43 +12840,43 @@
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="B24" s="69" t="n">
+      <c r="B24" s="67" t="n">
         <v>-11.8</v>
       </c>
-      <c r="C24" s="69" t="n">
+      <c r="C24" s="67" t="n">
         <v>-7.59</v>
       </c>
-      <c r="D24" s="69" t="n">
+      <c r="D24" s="67" t="n">
         <v>-10.13</v>
       </c>
-      <c r="E24" s="69" t="n">
+      <c r="E24" s="67" t="n">
         <v>-7.1</v>
       </c>
-      <c r="F24" s="71" t="n">
+      <c r="F24" s="69" t="n">
         <v>-2632</v>
       </c>
-      <c r="G24" s="71" t="n">
+      <c r="G24" s="69" t="n">
         <v>-5170</v>
       </c>
-      <c r="H24" s="71" t="n">
+      <c r="H24" s="69" t="n">
         <v>-7802</v>
       </c>
-      <c r="I24" s="71" t="n">
+      <c r="I24" s="69" t="n">
         <v>-240</v>
       </c>
-      <c r="J24" s="71" t="n">
+      <c r="J24" s="69" t="n">
         <v>-2040</v>
       </c>
-      <c r="K24" s="71" t="n">
+      <c r="K24" s="69" t="n">
         <v>-2601</v>
       </c>
-      <c r="L24" s="71" t="n">
+      <c r="L24" s="69" t="n">
         <v>-280</v>
       </c>
-      <c r="M24" s="70" t="n">
+      <c r="M24" s="68" t="n">
         <v>7658</v>
       </c>
-      <c r="N24" s="70" t="n">
+      <c r="N24" s="68" t="n">
         <v>144</v>
       </c>
       <c r="O24" s="59" t="inlineStr">
@@ -12899,43 +12891,43 @@
           <t>제약</t>
         </is>
       </c>
-      <c r="B25" s="69" t="n">
+      <c r="B25" s="67" t="n">
         <v>-15.02</v>
       </c>
-      <c r="C25" s="69" t="n">
+      <c r="C25" s="67" t="n">
         <v>-13.6</v>
       </c>
-      <c r="D25" s="68" t="n">
+      <c r="D25" s="66" t="n">
         <v>5.87</v>
       </c>
-      <c r="E25" s="69" t="n">
+      <c r="E25" s="67" t="n">
         <v>-7.2</v>
       </c>
-      <c r="F25" s="71" t="n">
+      <c r="F25" s="69" t="n">
         <v>-422</v>
       </c>
-      <c r="G25" s="71" t="n">
+      <c r="G25" s="69" t="n">
         <v>-2126</v>
       </c>
-      <c r="H25" s="71" t="n">
+      <c r="H25" s="69" t="n">
         <v>-2549</v>
       </c>
-      <c r="I25" s="71" t="n">
+      <c r="I25" s="69" t="n">
         <v>-403</v>
       </c>
-      <c r="J25" s="71" t="n">
+      <c r="J25" s="69" t="n">
         <v>-982</v>
       </c>
-      <c r="K25" s="71" t="n">
+      <c r="K25" s="69" t="n">
         <v>-615</v>
       </c>
-      <c r="L25" s="71" t="n">
+      <c r="L25" s="69" t="n">
         <v>-127</v>
       </c>
-      <c r="M25" s="70" t="n">
+      <c r="M25" s="68" t="n">
         <v>1475</v>
       </c>
-      <c r="N25" s="70" t="n">
+      <c r="N25" s="68" t="n">
         <v>1073</v>
       </c>
       <c r="O25" s="59" t="inlineStr">
@@ -12950,43 +12942,43 @@
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="B26" s="69" t="n">
+      <c r="B26" s="67" t="n">
         <v>-3.37</v>
       </c>
-      <c r="C26" s="69" t="n">
+      <c r="C26" s="67" t="n">
         <v>-25.86</v>
       </c>
-      <c r="D26" s="69" t="n">
+      <c r="D26" s="67" t="n">
         <v>-27.34</v>
       </c>
-      <c r="E26" s="69" t="n">
+      <c r="E26" s="67" t="n">
         <v>-7.56</v>
       </c>
-      <c r="F26" s="71" t="n">
+      <c r="F26" s="69" t="n">
         <v>-4012</v>
       </c>
-      <c r="G26" s="71" t="n">
+      <c r="G26" s="69" t="n">
         <v>-7871</v>
       </c>
-      <c r="H26" s="71" t="n">
+      <c r="H26" s="69" t="n">
         <v>-11882</v>
       </c>
-      <c r="I26" s="70" t="n">
+      <c r="I26" s="68" t="n">
         <v>323</v>
       </c>
-      <c r="J26" s="71" t="n">
+      <c r="J26" s="69" t="n">
         <v>-2294</v>
       </c>
-      <c r="K26" s="71" t="n">
+      <c r="K26" s="69" t="n">
         <v>-5482</v>
       </c>
-      <c r="L26" s="71" t="n">
+      <c r="L26" s="69" t="n">
         <v>-366</v>
       </c>
-      <c r="M26" s="70" t="n">
+      <c r="M26" s="68" t="n">
         <v>11713</v>
       </c>
-      <c r="N26" s="70" t="n">
+      <c r="N26" s="68" t="n">
         <v>169</v>
       </c>
       <c r="O26" s="59" t="inlineStr">
@@ -13001,46 +12993,46 @@
           <t>음식료·담배</t>
         </is>
       </c>
-      <c r="B27" s="68" t="n">
+      <c r="B27" s="66" t="n">
         <v>4.41</v>
       </c>
-      <c r="C27" s="68" t="n">
+      <c r="C27" s="66" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="D27" s="68" t="n">
+      <c r="D27" s="66" t="n">
         <v>3.49</v>
       </c>
-      <c r="E27" s="69" t="n">
+      <c r="E27" s="67" t="n">
         <v>-7.98</v>
       </c>
-      <c r="F27" s="70" t="n">
+      <c r="F27" s="68" t="n">
         <v>529</v>
       </c>
-      <c r="G27" s="71" t="n">
+      <c r="G27" s="69" t="n">
         <v>-1944</v>
       </c>
-      <c r="H27" s="71" t="n">
+      <c r="H27" s="69" t="n">
         <v>-1415</v>
       </c>
-      <c r="I27" s="70" t="n">
+      <c r="I27" s="68" t="n">
         <v>35</v>
       </c>
-      <c r="J27" s="71" t="n">
+      <c r="J27" s="69" t="n">
         <v>-1665</v>
       </c>
-      <c r="K27" s="71" t="n">
+      <c r="K27" s="69" t="n">
         <v>-146</v>
       </c>
-      <c r="L27" s="71" t="n">
+      <c r="L27" s="69" t="n">
         <v>-132</v>
       </c>
-      <c r="M27" s="70" t="n">
+      <c r="M27" s="68" t="n">
         <v>1391</v>
       </c>
-      <c r="N27" s="70" t="n">
+      <c r="N27" s="68" t="n">
         <v>24</v>
       </c>
-      <c r="O27" s="73" t="inlineStr">
+      <c r="O27" s="71" t="inlineStr">
         <is>
           <t>수급이탈</t>
         </is>
@@ -13052,43 +13044,43 @@
           <t>오락·문화</t>
         </is>
       </c>
-      <c r="B28" s="69" t="n">
+      <c r="B28" s="67" t="n">
         <v>-45.3</v>
       </c>
-      <c r="C28" s="69" t="n">
+      <c r="C28" s="67" t="n">
         <v>-44.38</v>
       </c>
-      <c r="D28" s="69" t="n">
+      <c r="D28" s="67" t="n">
         <v>-19.57</v>
       </c>
-      <c r="E28" s="69" t="n">
+      <c r="E28" s="67" t="n">
         <v>-8.68</v>
       </c>
-      <c r="F28" s="71" t="n">
+      <c r="F28" s="69" t="n">
         <v>-522</v>
       </c>
-      <c r="G28" s="71" t="n">
+      <c r="G28" s="69" t="n">
         <v>-391</v>
       </c>
-      <c r="H28" s="71" t="n">
+      <c r="H28" s="69" t="n">
         <v>-913</v>
       </c>
-      <c r="I28" s="71" t="n">
+      <c r="I28" s="69" t="n">
         <v>-63</v>
       </c>
-      <c r="J28" s="71" t="n">
+      <c r="J28" s="69" t="n">
         <v>-139</v>
       </c>
-      <c r="K28" s="71" t="n">
+      <c r="K28" s="69" t="n">
         <v>-164</v>
       </c>
-      <c r="L28" s="71" t="n">
+      <c r="L28" s="69" t="n">
         <v>-26</v>
       </c>
-      <c r="M28" s="70" t="n">
+      <c r="M28" s="68" t="n">
         <v>928</v>
       </c>
-      <c r="N28" s="71" t="n">
+      <c r="N28" s="69" t="n">
         <v>-15</v>
       </c>
       <c r="O28" s="59" t="inlineStr">
@@ -13129,7 +13121,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{A86CA837-001B-4D58-925E-B028B4B491BC}</x14:id>
+          <x14:id>{4BE69835-DAF8-4219-B681-0A8C13BEFB6D}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13143,7 +13135,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1ED5A19B-DC6C-48CA-BABA-76F320E0C0D0}</x14:id>
+          <x14:id>{6AE1BE58-5A60-4594-B619-5FD33618FBC1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13157,7 +13149,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{DD921719-EC41-4E46-BC8A-D2C534732E6E}</x14:id>
+          <x14:id>{124DF2BC-1266-42BD-87CC-1C0FB8DDC17C}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13171,7 +13163,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{B2409AA5-AAD8-4BB9-9EF4-548FA8726B38}</x14:id>
+          <x14:id>{DE0C0095-F9FE-4262-A83C-D994DF3E1439}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13181,7 +13173,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{A86CA837-001B-4D58-925E-B028B4B491BC}">
+          <x14:cfRule type="dataBar" id="{4BE69835-DAF8-4219-B681-0A8C13BEFB6D}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13194,7 +13186,7 @@
           <xm:sqref>B5:B28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1ED5A19B-DC6C-48CA-BABA-76F320E0C0D0}">
+          <x14:cfRule type="dataBar" id="{6AE1BE58-5A60-4594-B619-5FD33618FBC1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13207,7 +13199,7 @@
           <xm:sqref>C5:C28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{DD921719-EC41-4E46-BC8A-D2C534732E6E}">
+          <x14:cfRule type="dataBar" id="{124DF2BC-1266-42BD-87CC-1C0FB8DDC17C}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13220,7 +13212,7 @@
           <xm:sqref>D5:D28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{B2409AA5-AAD8-4BB9-9EF4-548FA8726B38}">
+          <x14:cfRule type="dataBar" id="{DE0C0095-F9FE-4262-A83C-D994DF3E1439}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/public/monthly_review.xlsx
+++ b/public/monthly_review.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="섹터x수급" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'신고가 근접'!$A$5:$L$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'신고가 근접'!$A$5:$L$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'섹터x수급'!$A$4:$O$28</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -456,14 +456,26 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -471,16 +483,7 @@
     <xf numFmtId="168" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -490,9 +493,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -942,7 +942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K187"/>
+  <dimension ref="A1:K193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.9" customWidth="1" style="15" min="1" max="1"/>
@@ -971,7 +971,7 @@
       </c>
       <c r="I1" s="25" t="inlineStr">
         <is>
-          <t>2026-09-01 ~ 2026-09-23</t>
+          <t>2026-09-01 ~ 2026-09-24</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       </c>
       <c r="I2" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23 16:26 KST</t>
+          <t>2026-09-24 16:27 KST</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4" ht="31" customHeight="1" s="15">
+    <row r="4" ht="17.25" customHeight="1" s="15">
       <c r="A4" s="26" t="inlineStr">
         <is>
           <t>MARKET SIGNAL</t>
@@ -996,7 +996,7 @@
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>9월 한국 증시는 AI 반도체 모멘텀과 인플레이션 우려 사이의 변동성 속에서 코스피 7000선을 회복하며 마감했습니다.</t>
+          <t>9월 국내 증시는 AI 반도체 랠리와 매크로 불확실성 속에서 기관 주도 장세가 펼쳐졌습니다.</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>미국 종가 기준 08/31 → 09/21, %</t>
+          <t>미국 종가 기준 08/31 → 09/23, %</t>
         </is>
       </c>
       <c r="I6" s="18" t="inlineStr"/>
@@ -1092,28 +1092,28 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>-194036</v>
+        <v>-208685</v>
       </c>
       <c r="C8" s="28" t="n">
-        <v>-133712</v>
+        <v>-138654</v>
       </c>
       <c r="D8" s="29" t="n">
-        <v>47046</v>
+        <v>50235</v>
       </c>
       <c r="E8" s="29" t="n">
-        <v>1.02</v>
+        <v>0.26</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>-2.14</v>
+        <v>-3.15</v>
       </c>
       <c r="G8" s="29" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="H8" s="28" t="n">
-        <v>-0.34</v>
+        <v>2.14</v>
+      </c>
+      <c r="H8" s="29" t="n">
+        <v>1.74</v>
       </c>
       <c r="I8" s="29" t="n">
-        <v>7.79</v>
+        <v>8.66</v>
       </c>
     </row>
     <row r="9">
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="B9" s="29" t="n">
-        <v>11546</v>
+        <v>11821</v>
       </c>
       <c r="C9" s="28" t="n">
-        <v>-14891</v>
+        <v>-15353</v>
       </c>
       <c r="D9" s="29" t="n">
-        <v>2821</v>
+        <v>2897</v>
       </c>
     </row>
     <row r="10"/>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="D12" s="32" t="n">
-        <v>7.08</v>
+        <v>8.039999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="D13" s="32" t="n">
-        <v>4.6</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="14">
@@ -1230,11 +1230,11 @@
       </c>
       <c r="C15" s="31" t="inlineStr">
         <is>
-          <t>소재</t>
+          <t>금융</t>
         </is>
       </c>
       <c r="D15" s="34" t="n">
-        <v>-5.22</v>
+        <v>-5.16</v>
       </c>
     </row>
     <row r="16">
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="D16" s="34" t="n">
-        <v>-3.53</v>
+        <v>-4.89</v>
       </c>
     </row>
     <row r="17">
@@ -1270,11 +1270,11 @@
       </c>
       <c r="C17" s="31" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="D17" s="34" t="n">
-        <v>-2.79</v>
+        <v>-4.49</v>
       </c>
     </row>
     <row r="18">
@@ -2716,7 +2716,7 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="31" customHeight="1" s="15">
+    <row r="65" ht="15" customHeight="1" s="15">
       <c r="A65" s="31" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="G65" s="17" t="inlineStr">
         <is>
-          <t>지정학적 리스크와 유가 급등으로 투자 심리가 위축되었습니다.</t>
+          <t>지정학적 리스크와 인플레이션 우려로 투자 심리 위축.</t>
         </is>
       </c>
     </row>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="G66" s="17" t="inlineStr">
         <is>
-          <t>물가 상승 부담과 외국인·기관의 대규모 매도로 지수가 급락했습니다.</t>
+          <t>외국인·기관 대규모 매도와 CPI 상승으로 지수 급락.</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="G67" s="17" t="inlineStr">
         <is>
-          <t>보험과 건설 섹터의 강세로 지수 차별화가 나타났습니다.</t>
+          <t>환율 하락에도 금리 부담 지속, 보험·건설 섹터 강세.</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="G68" s="17" t="inlineStr">
         <is>
-          <t>외국인과 기관의 동반 매수세가 지수 상승을 견인했습니다.</t>
+          <t>외국인·기관 매수세와 원화 강세로 지수 상승.</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="G69" s="17" t="inlineStr">
         <is>
-          <t>반도체와 원전 관련주 급등으로 코스피가 4.61% 급등했습니다.</t>
+          <t>외국인·기관 매수세와 원화 강세로 KOSPI 급등.</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G70" s="17" t="inlineStr">
         <is>
-          <t>개인의 매도세가 지수 하락을 압박하며 약세 마감했습니다.</t>
+          <t>개인 매도세와 금리 상승으로 지수 하락 압박.</t>
         </is>
       </c>
     </row>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="G71" s="17" t="inlineStr">
         <is>
-          <t>기관의 강한 매수세에 힘입어 코스피가 7000선에 안착했습니다.</t>
+          <t>기관·외국인 매수세와 원화 강세로 지수 상승.</t>
         </is>
       </c>
     </row>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="G72" s="17" t="inlineStr">
         <is>
-          <t>외국인의 매도세가 지속되며 지수 간 차별화가 나타났습니다.</t>
+          <t>외국인 매도세와 유가 급등으로 인플레이션 우려.</t>
         </is>
       </c>
     </row>
@@ -3153,7 +3153,7 @@
       </c>
       <c r="G73" s="17" t="inlineStr">
         <is>
-          <t>인플레이션 우려와 미국 기술주 투매로 지수가 급락했습니다.</t>
+          <t>미국 PPI 상승, 유가 100달러 돌파 등 삼중 악재로 급락.</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="G74" s="17" t="inlineStr">
         <is>
-          <t>외국인의 대규모 매도세가 쏟아지며 코스피가 급락했습니다.</t>
+          <t>외국인 대규모 매도세와 AI 속도조절론으로 지수 급락.</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="G75" s="17" t="inlineStr">
         <is>
-          <t>대외 악재로 인한 밸류에이션 부담으로 지수가 하락했습니다.</t>
+          <t>외국인·기관 매도세와 환율 상승으로 투자 심리 위축.</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="G76" s="17" t="inlineStr">
         <is>
-          <t>기관의 대규모 순매수가 지수 방어를 주도했습니다.</t>
+          <t>기관 매수세에도 대외 불확실성으로 외국인 매도 지속.</t>
         </is>
       </c>
     </row>
@@ -3393,7 +3393,7 @@
       </c>
       <c r="G77" s="17" t="inlineStr">
         <is>
-          <t>외국인의 대규모 매도세로 코스피가 하락 마감했습니다.</t>
+          <t>외국인 매도세와 고유가 우려로 투자 심리 위축.</t>
         </is>
       </c>
     </row>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="G78" s="17" t="inlineStr">
         <is>
-          <t>미국 기술주 강세 훈풍으로 코스피가 2.66% 급등했습니다.</t>
+          <t>미국 기술주 강세와 기관·외국인 매수세로 지수 급등.</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="G79" s="17" t="inlineStr">
         <is>
-          <t>반도체 수출 호조와 기관 매수로 코스피가 7000선을 회복했습니다.</t>
+          <t>기관 매수세와 반도체 수출 호조로 KOSPI 7000선 회복.</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="G80" s="17" t="inlineStr">
         <is>
-          <t>개인의 매도세에도 외국인 매수세가 지수를 방어했습니다.</t>
+          <t>개인 매도에도 외국인 매수세와 환율 하락으로 KOSPI 상승.</t>
         </is>
       </c>
     </row>
@@ -3669,228 +3669,222 @@
       </c>
       <c r="G81" s="17" t="inlineStr">
         <is>
-          <t>반도체 모멘텀이 지속되었으나 외국인 매도세로 상단이 제한되었습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82"/>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+          <t>개인·외국인 매도세에도 소비자심리지수 개선으로 지수 방어.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="31" customHeight="1" s="15">
+      <c r="A82" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B82" s="29" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C82" s="31" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00D64545"/>
+              <sz val="10"/>
+            </rPr>
+            <t>311▲</t>
+          </r>
+          <r>
+            <t>/</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="003182F6"/>
+              <sz val="10"/>
+            </rPr>
+            <t>548▼</t>
+          </r>
+        </is>
+      </c>
+      <c r="D82" s="29" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="E82" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00D64545"/>
+              <sz val="10"/>
+            </rPr>
+            <t>856▲ 상한4</t>
+          </r>
+          <r>
+            <t>/</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="003182F6"/>
+              <sz val="10"/>
+            </rPr>
+            <t>786▼</t>
+          </r>
+        </is>
+      </c>
+      <c r="F82" s="17" t="inlineStr">
+        <is>
+          <t>의료·정밀기기, 전기·전자</t>
+        </is>
+      </c>
+      <c r="G82" s="17" t="inlineStr">
+        <is>
+          <t>외국인 매도세에도 기관 매수세와 금리 하락으로 지수 방어.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83"/>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>05</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
+      <c r="B84" s="3" t="inlineStr">
         <is>
           <t>월간 종합 코멘트 — 매크로·수급</t>
         </is>
       </c>
-      <c r="C83" s="3" t="inlineStr"/>
-      <c r="D83" s="3" t="inlineStr"/>
-      <c r="E83" s="3" t="inlineStr"/>
-      <c r="F83" s="3" t="inlineStr"/>
-      <c r="G83" s="3" t="inlineStr"/>
-      <c r="H83" s="3" t="inlineStr"/>
-      <c r="I83" s="3" t="inlineStr"/>
-      <c r="J83" s="3" t="inlineStr"/>
-      <c r="K83" s="3" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="4" t="inlineStr">
+      <c r="C84" s="3" t="inlineStr"/>
+      <c r="D84" s="3" t="inlineStr"/>
+      <c r="E84" s="3" t="inlineStr"/>
+      <c r="F84" s="3" t="inlineStr"/>
+      <c r="G84" s="3" t="inlineStr"/>
+      <c r="H84" s="3" t="inlineStr"/>
+      <c r="I84" s="3" t="inlineStr"/>
+      <c r="J84" s="3" t="inlineStr"/>
+      <c r="K84" s="3" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B84" s="4" t="inlineStr">
+      <c r="B85" s="4" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="15" customHeight="1" s="15">
-      <c r="A85" s="17" t="inlineStr">
-        <is>
-          <t>- 9월 매크로 환경은 미국 CPI와 PPI 등 물가 지표가 인플레이션 압력을 지속적으로 시사하며 시장 변동성을 키웠습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="31" customHeight="1" s="15">
+    <row r="86" ht="58" customHeight="1" s="15">
       <c r="A86" s="17" t="inlineStr">
         <is>
-          <t>- 수급 구도는 월중 외국인의 대규모 매도세가 출회되었으나, 기관이 전기·전자 등 주도 섹터를 중심으로 지수 하단을 방어하는 양상이었습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="15" customHeight="1" s="15">
+          <t>- 월간 매크로 환경은 미국 ISM 제조업 PMI(54.6)가 예상치를 하회하고 국내 소비자물가지수(CPI)가 3.1%로 이전치를 상회하는 등 인플레이션 압력이 지속되었습니다. 미국 중앙은행 기준금리가 4.0%로 인상되고 10년물 국채금리가 5%를 돌파하며 긴축 공포가 시장 변동성을 키웠습니다. 다만, 국내 수출 전년대비 68.7% 급증과 소비자심리지수 106.6으로 개선은 경기 하방 경직성을 확보하는 요인으로 작용했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="58" customHeight="1" s="15">
       <c r="A87" s="17" t="inlineStr">
         <is>
-          <t>- 국내 수출 데이터가 견조한 흐름을 보이며 AI 인프라 수요 기대감과 함께 증시의 하방 경직성을 확보하는 데 기여했습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88"/>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+          <t>- 월간 수급 구도는 외국인이 전기·전자(-110,600억)와 제조(-126,162억) 섹터에서 대규모 순매도를 보이며 지수 하방 압력을 가했습니다. 반면 기관은 전기·전자(50,024억)와 제조(43,530억) 섹터에서 순매수를 기록하며 지수 방어에 기여했습니다. 개인은 전기·전자(-213,910억)와 제조(-194,163억) 섹터에서 대규모 순매도를 보이며 차익 실현에 집중했습니다. 의료·정밀기기 섹터는 외국인(73억)과 기관(498억)의 동반 매수세로 월간 18.45% 상승하며 강세를 보였습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="44.5" customHeight="1" s="15">
+      <c r="A88" s="17" t="inlineStr">
+        <is>
+          <t>- 월간 시장은 AI 반도체 랠리와 견조한 수출 데이터가 지수 하단을 지지했으나, 미국발 인플레이션 우려와 고금리 장기화 부담, 그리고 외국인 수급의 변동성이 시장의 상승 탄력을 둔화시키는 양상이었습니다. 특히 건설 섹터는 월간 -2.24% 하락하며 외국인(-2,770억)과 기관(-790억)의 동반 이탈이 두드러졌습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="31" customHeight="1" s="15">
+      <c r="A89" s="17" t="inlineStr">
+        <is>
+          <t>- 종합적으로 매크로 불확실성 속에서도 AI 인프라 수요 기대감과 실적 모멘텀이 확실한 반도체 및 일부 기술주 중심의 차별화 장세가 지속될 것으로 예상됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90"/>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>06</t>
         </is>
       </c>
-      <c r="B89" s="3" t="inlineStr">
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t>투자자 합산 순매수 상위/하위</t>
         </is>
       </c>
-      <c r="C89" s="3" t="inlineStr"/>
-      <c r="D89" s="3" t="inlineStr"/>
-      <c r="E89" s="3" t="inlineStr"/>
-      <c r="F89" s="3" t="inlineStr"/>
-      <c r="G89" s="3" t="inlineStr"/>
-      <c r="H89" s="3" t="inlineStr"/>
-      <c r="I89" s="3" t="inlineStr"/>
-      <c r="J89" s="18" t="inlineStr">
+      <c r="C91" s="3" t="inlineStr"/>
+      <c r="D91" s="3" t="inlineStr"/>
+      <c r="E91" s="3" t="inlineStr"/>
+      <c r="F91" s="3" t="inlineStr"/>
+      <c r="G91" s="3" t="inlineStr"/>
+      <c r="H91" s="3" t="inlineStr"/>
+      <c r="I91" s="3" t="inlineStr"/>
+      <c r="J91" s="18" t="inlineStr">
         <is>
           <t>외인+기관계, 억원</t>
         </is>
       </c>
-      <c r="K89" s="3" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="4" t="inlineStr">
+      <c r="K91" s="3" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B90" s="4" t="inlineStr">
+      <c r="B92" s="4" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="C90" s="4" t="inlineStr">
+      <c r="C92" s="4" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="D90" s="4" t="inlineStr">
+      <c r="D92" s="4" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr">
+      <c r="E92" s="4" t="inlineStr">
         <is>
           <t>합산</t>
         </is>
       </c>
-      <c r="F90" s="4" t="inlineStr">
+      <c r="F92" s="4" t="inlineStr">
         <is>
           <t>외인</t>
         </is>
       </c>
-      <c r="G90" s="4" t="inlineStr">
+      <c r="G92" s="4" t="inlineStr">
         <is>
           <t>기관</t>
         </is>
       </c>
-      <c r="H90" s="4" t="inlineStr">
+      <c r="H92" s="4" t="inlineStr">
         <is>
           <t>개인</t>
         </is>
       </c>
-      <c r="I90" s="4" t="inlineStr">
+      <c r="I92" s="4" t="inlineStr">
         <is>
           <t>공매도</t>
         </is>
       </c>
-      <c r="J90" s="4" t="inlineStr">
+      <c r="J92" s="4" t="inlineStr">
         <is>
           <t>대차잔고</t>
         </is>
       </c>
-      <c r="K90" s="4" t="inlineStr">
+      <c r="K92" s="4" t="inlineStr">
         <is>
           <t>대차증감</t>
         </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="8" t="inlineStr">
-        <is>
-          <t>순매수 상위</t>
-        </is>
-      </c>
-      <c r="B91" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C91" s="31" t="inlineStr">
-        <is>
-          <t>삼성전자</t>
-        </is>
-      </c>
-      <c r="D91" s="35" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="E91" s="29" t="n">
-        <v>26933</v>
-      </c>
-      <c r="F91" s="28" t="n">
-        <v>-12432</v>
-      </c>
-      <c r="G91" s="29" t="n">
-        <v>39366</v>
-      </c>
-      <c r="H91" s="28" t="n">
-        <v>-107841</v>
-      </c>
-      <c r="I91" s="31" t="n">
-        <v>34854.2</v>
-      </c>
-      <c r="J91" s="31" t="n">
-        <v>242446.3</v>
-      </c>
-      <c r="K91" s="31" t="n">
-        <v>12856.3</v>
-      </c>
-    </row>
-    <row r="92" ht="31" customHeight="1" s="15">
-      <c r="A92" s="8" t="inlineStr">
-        <is>
-          <t>순매수 상위</t>
-        </is>
-      </c>
-      <c r="B92" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="C92" s="17" t="inlineStr">
-        <is>
-          <t>포스코인터내셔널</t>
-        </is>
-      </c>
-      <c r="D92" s="35" t="inlineStr">
-        <is>
-          <t>유통</t>
-        </is>
-      </c>
-      <c r="E92" s="29" t="n">
-        <v>9402</v>
-      </c>
-      <c r="F92" s="28" t="n">
-        <v>-937</v>
-      </c>
-      <c r="G92" s="29" t="n">
-        <v>10339</v>
-      </c>
-      <c r="H92" s="29" t="n">
-        <v>75</v>
-      </c>
-      <c r="I92" s="31" t="n">
-        <v>495.2</v>
-      </c>
-      <c r="J92" s="31" t="n">
-        <v>1859.5</v>
-      </c>
-      <c r="K92" s="31" t="n">
-        <v>-1772.2</v>
       </c>
     </row>
     <row r="93">
@@ -3900,79 +3894,79 @@
         </is>
       </c>
       <c r="B93" s="31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C93" s="31" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="D93" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="E93" s="29" t="n">
-        <v>6576</v>
-      </c>
-      <c r="F93" s="29" t="n">
-        <v>8390</v>
-      </c>
-      <c r="G93" s="28" t="n">
-        <v>-1814</v>
+        <v>34714</v>
+      </c>
+      <c r="F93" s="28" t="n">
+        <v>-6914</v>
+      </c>
+      <c r="G93" s="29" t="n">
+        <v>41629</v>
       </c>
       <c r="H93" s="28" t="n">
-        <v>-6528</v>
+        <v>-107841</v>
       </c>
       <c r="I93" s="31" t="n">
-        <v>3883.7</v>
+        <v>34854.2</v>
       </c>
       <c r="J93" s="31" t="n">
-        <v>30302.8</v>
+        <v>246411.2</v>
       </c>
       <c r="K93" s="31" t="n">
-        <v>-589.5</v>
-      </c>
-    </row>
-    <row r="94">
+        <v>16821.2</v>
+      </c>
+    </row>
+    <row r="94" ht="31" customHeight="1" s="15">
       <c r="A94" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
       <c r="B94" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="C94" s="31" t="inlineStr">
-        <is>
-          <t>우리금융지주</t>
+        <v>2</v>
+      </c>
+      <c r="C94" s="17" t="inlineStr">
+        <is>
+          <t>포스코인터내셔널</t>
         </is>
       </c>
       <c r="D94" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>유통</t>
         </is>
       </c>
       <c r="E94" s="29" t="n">
-        <v>5388</v>
-      </c>
-      <c r="F94" s="29" t="n">
-        <v>4771</v>
+        <v>9370</v>
+      </c>
+      <c r="F94" s="28" t="n">
+        <v>-933</v>
       </c>
       <c r="G94" s="29" t="n">
-        <v>617</v>
-      </c>
-      <c r="H94" s="28" t="n">
-        <v>-778</v>
+        <v>10303</v>
+      </c>
+      <c r="H94" s="29" t="n">
+        <v>75</v>
       </c>
       <c r="I94" s="31" t="n">
-        <v>686.4</v>
+        <v>495.2</v>
       </c>
       <c r="J94" s="31" t="n">
-        <v>4852.5</v>
+        <v>1675.7</v>
       </c>
       <c r="K94" s="31" t="n">
-        <v>-301.5</v>
+        <v>-1956</v>
       </c>
     </row>
     <row r="95">
@@ -3982,38 +3976,38 @@
         </is>
       </c>
       <c r="B95" s="31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C95" s="31" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>SK스퀘어</t>
         </is>
       </c>
       <c r="D95" s="35" t="inlineStr">
         <is>
-          <t>화학</t>
+          <t>기타금융</t>
         </is>
       </c>
       <c r="E95" s="29" t="n">
-        <v>4583</v>
+        <v>6493</v>
       </c>
       <c r="F95" s="29" t="n">
-        <v>2752</v>
-      </c>
-      <c r="G95" s="29" t="n">
-        <v>1831</v>
+        <v>8118</v>
+      </c>
+      <c r="G95" s="28" t="n">
+        <v>-1625</v>
       </c>
       <c r="H95" s="28" t="n">
-        <v>-4557</v>
+        <v>-6528</v>
       </c>
       <c r="I95" s="31" t="n">
-        <v>1069.9</v>
+        <v>3883.7</v>
       </c>
       <c r="J95" s="31" t="n">
-        <v>3375.6</v>
+        <v>32724.5</v>
       </c>
       <c r="K95" s="31" t="n">
-        <v>-21.7</v>
+        <v>1832.2</v>
       </c>
     </row>
     <row r="96">
@@ -4023,38 +4017,38 @@
         </is>
       </c>
       <c r="B96" s="31" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C96" s="31" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="D96" s="35" t="inlineStr">
         <is>
-          <t>운송·창고</t>
+          <t>기타금융</t>
         </is>
       </c>
       <c r="E96" s="29" t="n">
-        <v>3592</v>
+        <v>5388</v>
       </c>
       <c r="F96" s="29" t="n">
-        <v>2924</v>
+        <v>4771</v>
       </c>
       <c r="G96" s="29" t="n">
-        <v>668</v>
+        <v>617</v>
       </c>
       <c r="H96" s="28" t="n">
-        <v>-3521</v>
+        <v>-778</v>
       </c>
       <c r="I96" s="31" t="n">
-        <v>274.6</v>
+        <v>686.4</v>
       </c>
       <c r="J96" s="31" t="n">
-        <v>1909.4</v>
+        <v>4852.5</v>
       </c>
       <c r="K96" s="31" t="n">
-        <v>240.7</v>
+        <v>-301.5</v>
       </c>
     </row>
     <row r="97">
@@ -4064,38 +4058,38 @@
         </is>
       </c>
       <c r="B97" s="31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C97" s="31" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="D97" s="35" t="inlineStr">
         <is>
-          <t>기계·장비</t>
+          <t>화학</t>
         </is>
       </c>
       <c r="E97" s="29" t="n">
-        <v>2225</v>
-      </c>
-      <c r="F97" s="28" t="n">
-        <v>-1248</v>
+        <v>4905</v>
+      </c>
+      <c r="F97" s="29" t="n">
+        <v>2991</v>
       </c>
       <c r="G97" s="29" t="n">
-        <v>3473</v>
+        <v>1914</v>
       </c>
       <c r="H97" s="28" t="n">
-        <v>-2199</v>
+        <v>-4557</v>
       </c>
       <c r="I97" s="31" t="n">
-        <v>5498.7</v>
+        <v>1069.9</v>
       </c>
       <c r="J97" s="31" t="n">
-        <v>47711.7</v>
+        <v>3634.4</v>
       </c>
       <c r="K97" s="31" t="n">
-        <v>7145.1</v>
+        <v>237.1</v>
       </c>
     </row>
     <row r="98">
@@ -4105,38 +4099,38 @@
         </is>
       </c>
       <c r="B98" s="31" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C98" s="31" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="D98" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>운송·창고</t>
         </is>
       </c>
       <c r="E98" s="29" t="n">
-        <v>1631</v>
+        <v>3636</v>
       </c>
       <c r="F98" s="29" t="n">
-        <v>1115</v>
+        <v>2898</v>
       </c>
       <c r="G98" s="29" t="n">
-        <v>517</v>
+        <v>737</v>
       </c>
       <c r="H98" s="28" t="n">
-        <v>-1635</v>
+        <v>-3521</v>
       </c>
       <c r="I98" s="31" t="n">
-        <v>644.9</v>
+        <v>274.6</v>
       </c>
       <c r="J98" s="31" t="n">
-        <v>4095.7</v>
+        <v>1997.5</v>
       </c>
       <c r="K98" s="31" t="n">
-        <v>1774.9</v>
+        <v>328.8</v>
       </c>
     </row>
     <row r="99">
@@ -4146,38 +4140,38 @@
         </is>
       </c>
       <c r="B99" s="31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C99" s="31" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="D99" s="35" t="inlineStr">
         <is>
-          <t>기계·장비</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="E99" s="29" t="n">
-        <v>1597</v>
-      </c>
-      <c r="F99" s="29" t="n">
-        <v>911</v>
+        <v>2365</v>
+      </c>
+      <c r="F99" s="28" t="n">
+        <v>-1308</v>
       </c>
       <c r="G99" s="29" t="n">
-        <v>686</v>
+        <v>3673</v>
       </c>
       <c r="H99" s="28" t="n">
-        <v>-1607</v>
+        <v>-1378</v>
       </c>
       <c r="I99" s="31" t="n">
-        <v>624.6</v>
+        <v>942.4</v>
       </c>
       <c r="J99" s="31" t="n">
-        <v>6070.1</v>
+        <v>28532.1</v>
       </c>
       <c r="K99" s="31" t="n">
-        <v>1274.7</v>
+        <v>7025</v>
       </c>
     </row>
     <row r="100">
@@ -4187,120 +4181,120 @@
         </is>
       </c>
       <c r="B100" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="C100" s="31" t="inlineStr">
+        <is>
+          <t>한미반도체</t>
+        </is>
+      </c>
+      <c r="D100" s="35" t="inlineStr">
+        <is>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="E100" s="29" t="n">
+        <v>2225</v>
+      </c>
+      <c r="F100" s="28" t="n">
+        <v>-1248</v>
+      </c>
+      <c r="G100" s="29" t="n">
+        <v>3473</v>
+      </c>
+      <c r="H100" s="28" t="n">
+        <v>-2199</v>
+      </c>
+      <c r="I100" s="31" t="n">
+        <v>5498.7</v>
+      </c>
+      <c r="J100" s="31" t="n">
+        <v>47711.7</v>
+      </c>
+      <c r="K100" s="31" t="n">
+        <v>7145.1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B101" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="C101" s="31" t="inlineStr">
+        <is>
+          <t>로보티즈</t>
+        </is>
+      </c>
+      <c r="D101" s="35" t="inlineStr">
+        <is>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="E101" s="29" t="n">
+        <v>1597</v>
+      </c>
+      <c r="F101" s="29" t="n">
+        <v>911</v>
+      </c>
+      <c r="G101" s="29" t="n">
+        <v>686</v>
+      </c>
+      <c r="H101" s="28" t="n">
+        <v>-1607</v>
+      </c>
+      <c r="I101" s="31" t="n">
+        <v>624.6</v>
+      </c>
+      <c r="J101" s="31" t="n">
+        <v>6070.1</v>
+      </c>
+      <c r="K101" s="31" t="n">
+        <v>1274.7</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B102" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="C100" s="31" t="inlineStr">
-        <is>
-          <t>HPSP</t>
-        </is>
-      </c>
-      <c r="D100" s="35" t="inlineStr">
-        <is>
-          <t>기계·장비</t>
-        </is>
-      </c>
-      <c r="E100" s="29" t="n">
-        <v>1272</v>
-      </c>
-      <c r="F100" s="28" t="n">
-        <v>-240</v>
-      </c>
-      <c r="G100" s="29" t="n">
-        <v>1512</v>
-      </c>
-      <c r="H100" s="28" t="n">
-        <v>-1231</v>
-      </c>
-      <c r="I100" s="31" t="n">
-        <v>965</v>
-      </c>
-      <c r="J100" s="31" t="n">
-        <v>6912.3</v>
-      </c>
-      <c r="K100" s="31" t="n">
-        <v>453.1</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="10" t="inlineStr">
-        <is>
-          <t>순매도 상위</t>
-        </is>
-      </c>
-      <c r="B101" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C101" s="31" t="inlineStr">
-        <is>
-          <t>SK하이닉스</t>
-        </is>
-      </c>
-      <c r="D101" s="35" t="inlineStr">
+      <c r="C102" s="31" t="inlineStr">
+        <is>
+          <t>가온전선</t>
+        </is>
+      </c>
+      <c r="D102" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="E101" s="28" t="n">
-        <v>-76483</v>
-      </c>
-      <c r="F101" s="28" t="n">
-        <v>-72174</v>
-      </c>
-      <c r="G101" s="28" t="n">
-        <v>-4308</v>
-      </c>
-      <c r="H101" s="28" t="n">
-        <v>-99877</v>
-      </c>
-      <c r="I101" s="31" t="n">
-        <v>58216.8</v>
-      </c>
-      <c r="J101" s="31" t="n">
-        <v>202612</v>
-      </c>
-      <c r="K101" s="31" t="n">
-        <v>5990.1</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="10" t="inlineStr">
-        <is>
-          <t>순매도 상위</t>
-        </is>
-      </c>
-      <c r="B102" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="C102" s="31" t="inlineStr">
-        <is>
-          <t>현대차</t>
-        </is>
-      </c>
-      <c r="D102" s="35" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
-        </is>
-      </c>
-      <c r="E102" s="28" t="n">
-        <v>-5536</v>
-      </c>
-      <c r="F102" s="28" t="n">
-        <v>-1676</v>
-      </c>
-      <c r="G102" s="28" t="n">
-        <v>-3860</v>
-      </c>
-      <c r="H102" s="29" t="n">
-        <v>5622</v>
+      <c r="E102" s="29" t="n">
+        <v>1510</v>
+      </c>
+      <c r="F102" s="29" t="n">
+        <v>1016</v>
+      </c>
+      <c r="G102" s="29" t="n">
+        <v>494</v>
+      </c>
+      <c r="H102" s="28" t="n">
+        <v>-1635</v>
       </c>
       <c r="I102" s="31" t="n">
-        <v>5364.4</v>
+        <v>644.9</v>
       </c>
       <c r="J102" s="31" t="n">
-        <v>29351.3</v>
+        <v>4091.2</v>
       </c>
       <c r="K102" s="31" t="n">
-        <v>-923.9</v>
+        <v>1770.4</v>
       </c>
     </row>
     <row r="103">
@@ -4310,38 +4304,38 @@
         </is>
       </c>
       <c r="B103" s="31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C103" s="31" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="D103" s="35" t="inlineStr">
         <is>
-          <t>기계·장비</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="E103" s="28" t="n">
-        <v>-4810</v>
+        <v>-84773</v>
       </c>
       <c r="F103" s="28" t="n">
-        <v>-4879</v>
-      </c>
-      <c r="G103" s="29" t="n">
-        <v>69</v>
-      </c>
-      <c r="H103" s="29" t="n">
-        <v>4820</v>
+        <v>-82160</v>
+      </c>
+      <c r="G103" s="28" t="n">
+        <v>-2613</v>
+      </c>
+      <c r="H103" s="28" t="n">
+        <v>-99877</v>
       </c>
       <c r="I103" s="31" t="n">
-        <v>6855.1</v>
+        <v>58216.8</v>
       </c>
       <c r="J103" s="31" t="n">
-        <v>19849.4</v>
+        <v>204586.6</v>
       </c>
       <c r="K103" s="31" t="n">
-        <v>2531.5</v>
+        <v>7964.7</v>
       </c>
     </row>
     <row r="104">
@@ -4351,38 +4345,38 @@
         </is>
       </c>
       <c r="B104" s="31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C104" s="31" t="inlineStr">
         <is>
-          <t>NAVER</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="D104" s="35" t="inlineStr">
         <is>
-          <t>IT 서비스</t>
+          <t>운송장비·부품</t>
         </is>
       </c>
       <c r="E104" s="28" t="n">
-        <v>-3793</v>
+        <v>-6347</v>
       </c>
       <c r="F104" s="28" t="n">
-        <v>-222</v>
+        <v>-2315</v>
       </c>
       <c r="G104" s="28" t="n">
-        <v>-3571</v>
+        <v>-4032</v>
       </c>
       <c r="H104" s="29" t="n">
-        <v>3803</v>
+        <v>5622</v>
       </c>
       <c r="I104" s="31" t="n">
-        <v>2680.2</v>
+        <v>5364.4</v>
       </c>
       <c r="J104" s="31" t="n">
-        <v>11345.6</v>
+        <v>30043</v>
       </c>
       <c r="K104" s="31" t="n">
-        <v>-760.1</v>
+        <v>-232.2</v>
       </c>
     </row>
     <row r="105">
@@ -4392,38 +4386,38 @@
         </is>
       </c>
       <c r="B105" s="31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C105" s="31" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="D105" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>기계·장비</t>
         </is>
       </c>
       <c r="E105" s="28" t="n">
-        <v>-3596</v>
+        <v>-5969</v>
       </c>
       <c r="F105" s="28" t="n">
-        <v>-1544</v>
+        <v>-5851</v>
       </c>
       <c r="G105" s="28" t="n">
-        <v>-2051</v>
+        <v>-118</v>
       </c>
       <c r="H105" s="29" t="n">
-        <v>3491</v>
+        <v>4820</v>
       </c>
       <c r="I105" s="31" t="n">
-        <v>2269</v>
+        <v>6855.1</v>
       </c>
       <c r="J105" s="31" t="n">
-        <v>13135.6</v>
+        <v>19557</v>
       </c>
       <c r="K105" s="31" t="n">
-        <v>-3024.2</v>
+        <v>2239.1</v>
       </c>
     </row>
     <row r="106">
@@ -4433,38 +4427,38 @@
         </is>
       </c>
       <c r="B106" s="31" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C106" s="31" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>NAVER</t>
         </is>
       </c>
       <c r="D106" s="35" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>IT 서비스</t>
         </is>
       </c>
       <c r="E106" s="28" t="n">
-        <v>-3385</v>
+        <v>-4632</v>
       </c>
       <c r="F106" s="28" t="n">
-        <v>-317</v>
+        <v>-828</v>
       </c>
       <c r="G106" s="28" t="n">
-        <v>-3068</v>
+        <v>-3804</v>
       </c>
       <c r="H106" s="29" t="n">
-        <v>3760</v>
+        <v>3803</v>
       </c>
       <c r="I106" s="31" t="n">
-        <v>3164.5</v>
+        <v>2680.2</v>
       </c>
       <c r="J106" s="31" t="n">
-        <v>11598.7</v>
+        <v>11204.5</v>
       </c>
       <c r="K106" s="31" t="n">
-        <v>-3027.1</v>
+        <v>-901.2</v>
       </c>
     </row>
     <row r="107">
@@ -4474,11 +4468,11 @@
         </is>
       </c>
       <c r="B107" s="31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C107" s="31" t="inlineStr">
         <is>
-          <t>LG이노텍</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="D107" s="35" t="inlineStr">
@@ -4487,25 +4481,25 @@
         </is>
       </c>
       <c r="E107" s="28" t="n">
-        <v>-2546</v>
+        <v>-3841</v>
       </c>
       <c r="F107" s="28" t="n">
-        <v>-1126</v>
+        <v>-1591</v>
       </c>
       <c r="G107" s="28" t="n">
-        <v>-1420</v>
+        <v>-2249</v>
       </c>
       <c r="H107" s="29" t="n">
-        <v>2488</v>
+        <v>3491</v>
       </c>
       <c r="I107" s="31" t="n">
-        <v>2506.5</v>
+        <v>2269</v>
       </c>
       <c r="J107" s="31" t="n">
-        <v>7385.1</v>
+        <v>13102.5</v>
       </c>
       <c r="K107" s="31" t="n">
-        <v>-5780.4</v>
+        <v>-3057.3</v>
       </c>
     </row>
     <row r="108">
@@ -4515,38 +4509,38 @@
         </is>
       </c>
       <c r="B108" s="31" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C108" s="31" t="inlineStr">
         <is>
-          <t>현대모비스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="D108" s="35" t="inlineStr">
         <is>
-          <t>운송장비·부품</t>
+          <t>일반서비스</t>
         </is>
       </c>
       <c r="E108" s="28" t="n">
-        <v>-2248</v>
-      </c>
-      <c r="F108" s="29" t="n">
-        <v>998</v>
+        <v>-3385</v>
+      </c>
+      <c r="F108" s="28" t="n">
+        <v>-317</v>
       </c>
       <c r="G108" s="28" t="n">
-        <v>-3246</v>
+        <v>-3068</v>
       </c>
       <c r="H108" s="29" t="n">
-        <v>2207</v>
+        <v>3760</v>
       </c>
       <c r="I108" s="31" t="n">
-        <v>985</v>
+        <v>3164.5</v>
       </c>
       <c r="J108" s="31" t="n">
-        <v>4696</v>
+        <v>11598.7</v>
       </c>
       <c r="K108" s="31" t="n">
-        <v>-1561</v>
+        <v>-3027.1</v>
       </c>
     </row>
     <row r="109">
@@ -4556,11 +4550,11 @@
         </is>
       </c>
       <c r="B109" s="31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C109" s="31" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>LG이노텍</t>
         </is>
       </c>
       <c r="D109" s="35" t="inlineStr">
@@ -4569,25 +4563,25 @@
         </is>
       </c>
       <c r="E109" s="28" t="n">
-        <v>-1782</v>
+        <v>-2627</v>
       </c>
       <c r="F109" s="28" t="n">
-        <v>-430</v>
+        <v>-1228</v>
       </c>
       <c r="G109" s="28" t="n">
-        <v>-1353</v>
+        <v>-1399</v>
       </c>
       <c r="H109" s="29" t="n">
-        <v>1788</v>
+        <v>2488</v>
       </c>
       <c r="I109" s="31" t="n">
-        <v>1373.7</v>
+        <v>2506.5</v>
       </c>
       <c r="J109" s="31" t="n">
-        <v>6111</v>
+        <v>7439.6</v>
       </c>
       <c r="K109" s="31" t="n">
-        <v>-935.4</v>
+        <v>-5725.9</v>
       </c>
     </row>
     <row r="110">
@@ -4597,116 +4591,169 @@
         </is>
       </c>
       <c r="B110" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="C110" s="31" t="inlineStr">
+        <is>
+          <t>현대모비스</t>
+        </is>
+      </c>
+      <c r="D110" s="35" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
+        </is>
+      </c>
+      <c r="E110" s="28" t="n">
+        <v>-2384</v>
+      </c>
+      <c r="F110" s="29" t="n">
+        <v>895</v>
+      </c>
+      <c r="G110" s="28" t="n">
+        <v>-3279</v>
+      </c>
+      <c r="H110" s="29" t="n">
+        <v>2207</v>
+      </c>
+      <c r="I110" s="31" t="n">
+        <v>985</v>
+      </c>
+      <c r="J110" s="31" t="n">
+        <v>4643.7</v>
+      </c>
+      <c r="K110" s="31" t="n">
+        <v>-1613.3</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B111" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="C111" s="31" t="inlineStr">
+        <is>
+          <t>엘앤에프</t>
+        </is>
+      </c>
+      <c r="D111" s="35" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="E111" s="28" t="n">
+        <v>-1782</v>
+      </c>
+      <c r="F111" s="28" t="n">
+        <v>-430</v>
+      </c>
+      <c r="G111" s="28" t="n">
+        <v>-1353</v>
+      </c>
+      <c r="H111" s="29" t="n">
+        <v>1788</v>
+      </c>
+      <c r="I111" s="31" t="n">
+        <v>1373.7</v>
+      </c>
+      <c r="J111" s="31" t="n">
+        <v>6111</v>
+      </c>
+      <c r="K111" s="31" t="n">
+        <v>-935.4</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B112" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="C110" s="31" t="inlineStr">
-        <is>
-          <t>에이피알</t>
-        </is>
-      </c>
-      <c r="D110" s="35" t="inlineStr">
-        <is>
-          <t>화학</t>
-        </is>
-      </c>
-      <c r="E110" s="28" t="n">
-        <v>-1702</v>
-      </c>
-      <c r="F110" s="29" t="n">
-        <v>184</v>
-      </c>
-      <c r="G110" s="28" t="n">
-        <v>-1886</v>
-      </c>
-      <c r="H110" s="29" t="n">
-        <v>1669</v>
-      </c>
-      <c r="I110" s="31" t="n">
-        <v>947</v>
-      </c>
-      <c r="J110" s="31" t="n">
-        <v>13632.5</v>
-      </c>
-      <c r="K110" s="31" t="n">
-        <v>-2589.3</v>
-      </c>
-    </row>
-    <row r="111"/>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+      <c r="C112" s="31" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="D112" s="35" t="inlineStr">
+        <is>
+          <t>건설</t>
+        </is>
+      </c>
+      <c r="E112" s="28" t="n">
+        <v>-1765</v>
+      </c>
+      <c r="F112" s="28" t="n">
+        <v>-1439</v>
+      </c>
+      <c r="G112" s="28" t="n">
+        <v>-327</v>
+      </c>
+      <c r="H112" s="29" t="n">
+        <v>1270</v>
+      </c>
+      <c r="I112" s="31" t="n">
+        <v>1258.6</v>
+      </c>
+      <c r="J112" s="31" t="n">
+        <v>5249.2</v>
+      </c>
+      <c r="K112" s="31" t="n">
+        <v>-382.3</v>
+      </c>
+    </row>
+    <row r="113"/>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>07</t>
         </is>
       </c>
-      <c r="B112" s="3" t="inlineStr">
+      <c r="B114" s="3" t="inlineStr">
         <is>
           <t>섹터 시그널 종목 관찰</t>
         </is>
       </c>
-      <c r="C112" s="3" t="inlineStr"/>
-      <c r="D112" s="3" t="inlineStr"/>
-      <c r="E112" s="3" t="inlineStr"/>
-      <c r="F112" s="3" t="inlineStr"/>
-      <c r="G112" s="18" t="inlineStr">
+      <c r="C114" s="3" t="inlineStr"/>
+      <c r="D114" s="3" t="inlineStr"/>
+      <c r="E114" s="3" t="inlineStr"/>
+      <c r="F114" s="3" t="inlineStr"/>
+      <c r="G114" s="18" t="inlineStr">
         <is>
           <t>섹터 상태 x 수급 x 공매도·대차 x 촉매</t>
         </is>
       </c>
-      <c r="H112" s="3" t="inlineStr"/>
-      <c r="I112" s="3" t="inlineStr"/>
-      <c r="J112" s="3" t="inlineStr"/>
-      <c r="K112" s="3" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="36" t="inlineStr">
+      <c r="H114" s="3" t="inlineStr"/>
+      <c r="I114" s="3" t="inlineStr"/>
+      <c r="J114" s="3" t="inlineStr"/>
+      <c r="K114" s="3" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="36" t="inlineStr">
         <is>
           <t>● 동반강세 — 추세 지속형 상방 관찰</t>
         </is>
       </c>
-      <c r="G113" s="3" t="inlineStr">
+      <c r="G115" s="3" t="inlineStr">
         <is>
           <t>● 수급유입 — 초기 유입형 상방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="5" t="inlineStr">
-        <is>
-          <t>우리금융지주</t>
-        </is>
-      </c>
-      <c r="B114" s="35" t="inlineStr">
-        <is>
-          <t>금융</t>
-        </is>
-      </c>
-      <c r="C114" s="37" t="n">
-        <v>3</v>
-      </c>
-      <c r="D114" s="31" t="inlineStr"/>
-      <c r="E114" s="31" t="inlineStr"/>
-      <c r="G114" s="31" t="inlineStr">
-        <is>
-          <t>해당 섹터·조건 충족 종목 없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="44.5" customHeight="1" s="15">
-      <c r="A115" s="17" t="inlineStr">
-        <is>
-          <t>외국인 +4,771억 순매수, 기관 +617억 순매수, 대차잔고 -302억 감소 — 금융(동반강세) 섹터 추세 지속형 상방 관찰</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>아시아나항공</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="B116" s="35" t="inlineStr">
         <is>
-          <t>운송·창고</t>
+          <t>금융</t>
         </is>
       </c>
       <c r="C116" s="37" t="n">
@@ -4714,18 +4761,23 @@
       </c>
       <c r="D116" s="31" t="inlineStr"/>
       <c r="E116" s="31" t="inlineStr"/>
+      <c r="G116" s="31" t="inlineStr">
+        <is>
+          <t>해당 섹터·조건 충족 종목 없음</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="44.5" customHeight="1" s="15">
       <c r="A117" s="17" t="inlineStr">
         <is>
-          <t>외국인 +46억 순매수, 기관 +95억 순매수, 대차잔고 -7억 감소 — 운송·창고(동반강세) 섹터 추세 지속형 상방 관찰</t>
+          <t>외국인 +4,771억 순매수, 기관 +617억 순매수, 대차잔고 -302억 감소 — 금융(동반강세) 섹터 추세 지속형 상방 관찰</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>HMM</t>
+          <t>아시아나항공</t>
         </is>
       </c>
       <c r="B118" s="35" t="inlineStr">
@@ -4742,7 +4794,7 @@
     <row r="119" ht="44.5" customHeight="1" s="15">
       <c r="A119" s="17" t="inlineStr">
         <is>
-          <t>외국인 +27억 순매수, 기관 +63억 순매수, 대차잔고 -27억 감소 — 운송·창고(동반강세) 섹터 추세 지속형 상방 관찰</t>
+          <t>외국인 +46억 순매수, 기관 +95억 순매수, 대차잔고 -7억 감소 — 운송·창고(동반강세) 섹터 추세 지속형 상방 관찰</t>
         </is>
       </c>
     </row>
@@ -4766,14 +4818,14 @@
     <row r="121" ht="44.5" customHeight="1" s="15">
       <c r="A121" s="17" t="inlineStr">
         <is>
-          <t>외국인 +22억 순매수, 기관 +59억 순매수, 대차잔고 -19억 감소 — 의료·정밀기기(동반강세) 섹터 추세 지속형 상방 관찰</t>
+          <t>외국인 +23억 순매수, 기관 +59억 순매수, 대차잔고 -21억 감소 — 의료·정밀기기(동반강세) 섹터 추세 지속형 상방 관찰</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>HMM</t>
         </is>
       </c>
       <c r="B122" s="35" t="inlineStr">
@@ -4782,94 +4834,74 @@
         </is>
       </c>
       <c r="C122" s="37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D122" s="31" t="inlineStr"/>
       <c r="E122" s="31" t="inlineStr"/>
     </row>
-    <row r="123" ht="31" customHeight="1" s="15">
+    <row r="123" ht="44.5" customHeight="1" s="15">
       <c r="A123" s="17" t="inlineStr">
         <is>
-          <t>외국인 +2,924억 순매수, 기관 +668억 순매수 — 운송·창고(동반강세) 섹터 추세 지속형 상방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="124"/>
-    <row r="125">
-      <c r="A125" s="38" t="inlineStr">
+          <t>외국인 +17억 순매수, 기관 +65억 순매수, 대차잔고 -196억 감소 — 운송·창고(동반강세) 섹터 추세 지속형 상방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>대한항공</t>
+        </is>
+      </c>
+      <c r="B124" s="35" t="inlineStr">
+        <is>
+          <t>운송·창고</t>
+        </is>
+      </c>
+      <c r="C124" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D124" s="31" t="inlineStr"/>
+      <c r="E124" s="31" t="inlineStr"/>
+    </row>
+    <row r="125" ht="31" customHeight="1" s="15">
+      <c r="A125" s="17" t="inlineStr">
+        <is>
+          <t>외국인 +2,898억 순매수, 기관 +737억 순매수 — 운송·창고(동반강세) 섹터 추세 지속형 상방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="126"/>
+    <row r="127">
+      <c r="A127" s="38" t="inlineStr">
         <is>
           <t>● 수급이탈 — 상승 후 약화 관찰</t>
         </is>
       </c>
-      <c r="G125" s="39" t="inlineStr">
+      <c r="G127" s="39" t="inlineStr">
         <is>
           <t>● 동반약세 — 약세 지속형 하방 관찰</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="5" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
         <is>
           <t>CJ제일제당</t>
         </is>
       </c>
-      <c r="B126" s="35" t="inlineStr">
+      <c r="B128" s="35" t="inlineStr">
         <is>
           <t>음식료·담배</t>
         </is>
       </c>
-      <c r="C126" s="40" t="n">
+      <c r="C128" s="40" t="n">
         <v>-3</v>
-      </c>
-      <c r="D126" s="31" t="inlineStr"/>
-      <c r="E126" s="31" t="inlineStr"/>
-      <c r="G126" s="5" t="inlineStr">
-        <is>
-          <t>에스엠</t>
-        </is>
-      </c>
-      <c r="H126" s="35" t="inlineStr">
-        <is>
-          <t>오락·문화</t>
-        </is>
-      </c>
-      <c r="I126" s="41" t="n">
-        <v>-3</v>
-      </c>
-      <c r="J126" s="31" t="inlineStr"/>
-      <c r="K126" s="31" t="inlineStr"/>
-    </row>
-    <row r="127" ht="44.5" customHeight="1" s="15">
-      <c r="A127" s="17" t="inlineStr">
-        <is>
-          <t>외국인 -322억 순매도, 기관 -86억 순매도, 대차잔고 +51억 증가 — 음식료·담배(수급이탈) 섹터 상승 후 약화 관찰</t>
-        </is>
-      </c>
-      <c r="G127" s="17" t="inlineStr">
-        <is>
-          <t>외국인 -263억 순매도, 기관 -74억 순매도, 대차잔고 +184억 증가 — 오락·문화(동반약세) 섹터 약세 지속형 하방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="31" customHeight="1" s="15">
-      <c r="A128" s="5" t="inlineStr">
-        <is>
-          <t>오리온</t>
-        </is>
-      </c>
-      <c r="B128" s="35" t="inlineStr">
-        <is>
-          <t>음식료·담배</t>
-        </is>
-      </c>
-      <c r="C128" s="40" t="n">
-        <v>-1</v>
       </c>
       <c r="D128" s="31" t="inlineStr"/>
       <c r="E128" s="31" t="inlineStr"/>
-      <c r="G128" s="42" t="inlineStr">
-        <is>
-          <t>와이지엔터테인먼트</t>
+      <c r="G128" s="5" t="inlineStr">
+        <is>
+          <t>에스엠</t>
         </is>
       </c>
       <c r="H128" s="35" t="inlineStr">
@@ -4886,19 +4918,19 @@
     <row r="129" ht="44.5" customHeight="1" s="15">
       <c r="A129" s="17" t="inlineStr">
         <is>
-          <t>외국인 -1억 순매도, 기관 -217억 순매도 — 음식료·담배(수급이탈) 섹터 상승 후 약화 관찰</t>
+          <t>외국인 -316억 순매도, 기관 -86억 순매도, 대차잔고 +124억 증가 — 음식료·담배(수급이탈) 섹터 상승 후 약화 관찰</t>
         </is>
       </c>
       <c r="G129" s="17" t="inlineStr">
         <is>
-          <t>외국인 -131억 순매도, 기관 -93억 순매도, 대차잔고 +15억 증가 — 오락·문화(동반약세) 섹터 약세 지속형 하방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
+          <t>외국인 -264억 순매도, 기관 -74억 순매도, 대차잔고 +214억 증가 — 오락·문화(동반약세) 섹터 약세 지속형 하방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="31" customHeight="1" s="15">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>롯데칠성</t>
+          <t>오리온</t>
         </is>
       </c>
       <c r="B130" s="35" t="inlineStr">
@@ -4907,18 +4939,18 @@
         </is>
       </c>
       <c r="C130" s="40" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="D130" s="31" t="inlineStr"/>
       <c r="E130" s="31" t="inlineStr"/>
-      <c r="G130" s="5" t="inlineStr">
-        <is>
-          <t>풍산</t>
+      <c r="G130" s="42" t="inlineStr">
+        <is>
+          <t>와이지엔터테인먼트</t>
         </is>
       </c>
       <c r="H130" s="35" t="inlineStr">
         <is>
-          <t>금속</t>
+          <t>오락·문화</t>
         </is>
       </c>
       <c r="I130" s="41" t="n">
@@ -4930,19 +4962,19 @@
     <row r="131" ht="44.5" customHeight="1" s="15">
       <c r="A131" s="17" t="inlineStr">
         <is>
-          <t>외국인 -49억 순매도, 기관 -24억 순매도 — 음식료·담배(수급이탈) 섹터 상승 후 약화 관찰</t>
+          <t>외국인 -2억 순매도, 기관 -217억 순매도, 대차잔고 +14억 증가 — 음식료·담배(수급이탈) 섹터 상승 후 약화 관찰</t>
         </is>
       </c>
       <c r="G131" s="17" t="inlineStr">
         <is>
-          <t>외국인 -101억 순매도, 기관 -12억 순매도, 대차잔고 +27억 증가 — 금속(동반약세) 섹터 약세 지속형 하방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="31" customHeight="1" s="15">
+          <t>외국인 -131억 순매도, 기관 -93억 순매도, 대차잔고 +26억 증가 — 오락·문화(동반약세) 섹터 약세 지속형 하방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>하이트진로</t>
+          <t>롯데칠성</t>
         </is>
       </c>
       <c r="B132" s="35" t="inlineStr">
@@ -4955,9 +4987,9 @@
       </c>
       <c r="D132" s="31" t="inlineStr"/>
       <c r="E132" s="31" t="inlineStr"/>
-      <c r="G132" s="42" t="inlineStr">
-        <is>
-          <t>LIG디펜스앤에어로스페이스</t>
+      <c r="G132" s="5" t="inlineStr">
+        <is>
+          <t>풍산</t>
         </is>
       </c>
       <c r="H132" s="35" t="inlineStr">
@@ -4974,16 +5006,31 @@
     <row r="133" ht="44.5" customHeight="1" s="15">
       <c r="A133" s="17" t="inlineStr">
         <is>
-          <t>외국인 -11억 순매도, 기관 -4억 순매도 — 음식료·담배(수급이탈) 섹터 상승 후 약화 관찰</t>
+          <t>외국인 -49억 순매도, 기관 -24억 순매도 — 음식료·담배(수급이탈) 섹터 상승 후 약화 관찰</t>
         </is>
       </c>
       <c r="G133" s="17" t="inlineStr">
         <is>
-          <t>외국인 -71억 순매도, 기관 -16억 순매도, 대차잔고 +447억 증가 — 금속(동반약세) 섹터 약세 지속형 하방 관찰</t>
+          <t>외국인 -103억 순매도, 기관 -12억 순매도, 대차잔고 +5억 증가 — 금속(동반약세) 섹터 약세 지속형 하방 관찰</t>
         </is>
       </c>
     </row>
     <row r="134">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>하이트진로</t>
+        </is>
+      </c>
+      <c r="B134" s="35" t="inlineStr">
+        <is>
+          <t>음식료·담배</t>
+        </is>
+      </c>
+      <c r="C134" s="40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D134" s="31" t="inlineStr"/>
+      <c r="E134" s="31" t="inlineStr"/>
       <c r="G134" s="5" t="inlineStr">
         <is>
           <t>CJ ENM</t>
@@ -5001,449 +5048,296 @@
       <c r="K134" s="31" t="inlineStr"/>
     </row>
     <row r="135" ht="44.5" customHeight="1" s="15">
+      <c r="A135" s="17" t="inlineStr">
+        <is>
+          <t>외국인 -11억 순매도, 기관 -4억 순매도 — 음식료·담배(수급이탈) 섹터 상승 후 약화 관찰</t>
+        </is>
+      </c>
       <c r="G135" s="17" t="inlineStr">
         <is>
-          <t>외국인 -46억 순매도, 기관 -26억 순매도, 대차잔고 +22억 증가 — 오락·문화(동반약세) 섹터 약세 지속형 하방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="136"/>
-    <row r="137" ht="31" customHeight="1" s="15">
-      <c r="A137" s="43" t="inlineStr">
+          <t>외국인 -46억 순매도, 기관 -26억 순매도, 대차잔고 +29억 증가 — 오락·문화(동반약세) 섹터 약세 지속형 하방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="31" customHeight="1" s="15">
+      <c r="G136" s="42" t="inlineStr">
+        <is>
+          <t>LIG디펜스앤에어로스페이스</t>
+        </is>
+      </c>
+      <c r="H136" s="35" t="inlineStr">
+        <is>
+          <t>금속</t>
+        </is>
+      </c>
+      <c r="I136" s="41" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J136" s="31" t="inlineStr"/>
+      <c r="K136" s="31" t="inlineStr"/>
+    </row>
+    <row r="137" ht="44.5" customHeight="1" s="15">
+      <c r="G137" s="17" t="inlineStr">
+        <is>
+          <t>외국인 -52억 순매도, 기관 -14억 순매도, 대차잔고 +356억 증가 — 금속(동반약세) 섹터 약세 지속형 하방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="138"/>
+    <row r="139" ht="31" customHeight="1" s="15">
+      <c r="A139" s="43" t="inlineStr">
         <is>
           <t>현재 확보된 월간 리뷰 데이터 유니버스(순매수 상위 30 등재 · 공매도/대차 랭킹 · 월간 촉매 · 신호 섹터 시총 상위 10) 기준 — 전 시장 스크리닝 아님 · 관찰 우선순위이며 매매 권유 아님</t>
         </is>
       </c>
     </row>
-    <row r="138"/>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="140"/>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>08</t>
         </is>
       </c>
-      <c r="B139" s="3" t="inlineStr">
+      <c r="B141" s="3" t="inlineStr">
         <is>
           <t>월간 시장 흐름</t>
         </is>
       </c>
-      <c r="C139" s="3" t="inlineStr"/>
-      <c r="D139" s="3" t="inlineStr"/>
-      <c r="E139" s="3" t="inlineStr"/>
-      <c r="F139" s="3" t="inlineStr"/>
-      <c r="G139" s="3" t="inlineStr"/>
-      <c r="H139" s="3" t="inlineStr"/>
-      <c r="I139" s="3" t="inlineStr"/>
-      <c r="J139" s="3" t="inlineStr"/>
-      <c r="K139" s="3" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="4" t="inlineStr">
+      <c r="C141" s="3" t="inlineStr"/>
+      <c r="D141" s="3" t="inlineStr"/>
+      <c r="E141" s="3" t="inlineStr"/>
+      <c r="F141" s="3" t="inlineStr"/>
+      <c r="G141" s="3" t="inlineStr"/>
+      <c r="H141" s="3" t="inlineStr"/>
+      <c r="I141" s="3" t="inlineStr"/>
+      <c r="J141" s="3" t="inlineStr"/>
+      <c r="K141" s="3" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B140" s="4" t="inlineStr">
+      <c r="B142" s="4" t="inlineStr">
         <is>
           <t>Market Flow</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="15" customHeight="1" s="15">
-      <c r="A141" s="17" t="inlineStr">
-        <is>
-          <t>- 월 초 AI 반도체 기대감으로 코스피가 7000선에 근접했으나, 인플레이션 우려와 미국 기술주 투매로 변동성이 확대되었습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="15" customHeight="1" s="15">
-      <c r="A142" s="17" t="inlineStr">
-        <is>
-          <t>- 미국 고용지표 호조와 생산자물가지수(PPI) 상승이 금리 인하 기대감을 후퇴시키며 위험회피 심리가 강화되었습니다.</t>
         </is>
       </c>
     </row>
     <row r="143" ht="15" customHeight="1" s="15">
       <c r="A143" s="17" t="inlineStr">
         <is>
-          <t>- 중순에는 미국 10년물 국채금리 5% 돌파 등 긴축 공포가 시장을 짓눌렀으나, 기관의 저가 매수세가 지수 하단을 방어했습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="15" customHeight="1" s="15">
+          <t>- 월 초 KOSPI는 외국인과 기관의 대규모 매도세로 급락하며 시작했으나, 개인의 매수세가 지수 하단을 방어했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="31" customHeight="1" s="15">
       <c r="A144" s="17" t="inlineStr">
         <is>
-          <t>- 월 후반 미국 기술주 반등과 견조한 수출 데이터가 투자 심리를 회복시키며 코스피 7000선 안착을 이끌었습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="15" customHeight="1" s="15">
+          <t>- 월 중순 AI 반도체 및 HBM 수요 기대감으로 KOSPI가 7,000선에 근접하는 강한 반등을 보였으나, 미국 고용지표 호조와 생산자물가지수(PPI) 상승으로 인플레이션 우려가 재부각되며 변동성이 확대되었습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="31" customHeight="1" s="15">
       <c r="A145" s="17" t="inlineStr">
         <is>
-          <t>- 수급 측면에서는 외국인의 대규모 매도세가 출회되는 구간마다 기관이 지수 방어의 핵심 주체로 나섰습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="146"/>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="B147" s="3" t="inlineStr">
-        <is>
-          <t>섹터·테마 흐름</t>
-        </is>
-      </c>
-      <c r="C147" s="3" t="inlineStr"/>
-      <c r="D147" s="3" t="inlineStr"/>
-      <c r="E147" s="3" t="inlineStr"/>
-      <c r="F147" s="3" t="inlineStr"/>
-      <c r="G147" s="3" t="inlineStr"/>
-      <c r="H147" s="3" t="inlineStr"/>
-      <c r="I147" s="3" t="inlineStr"/>
-      <c r="J147" s="3" t="inlineStr"/>
-      <c r="K147" s="3" t="inlineStr"/>
+          <t>- 국제유가 100달러 돌파와 미국 국채금리 급등 등 대외 악재가 겹치며 시장의 위험회피 심리가 고조되었고, 외국인 자금 이탈이 가속화되었습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="31" customHeight="1" s="15">
+      <c r="A146" s="17" t="inlineStr">
+        <is>
+          <t>- 월 후반 미국 기술주 강세 훈풍과 견조한 국내 수출 지표에 힘입어 반도체 중심의 기술주 모멘텀이 시장을 견인하며 KOSPI 7,000선을 회복했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="15" customHeight="1" s="15">
+      <c r="A147" s="17" t="inlineStr">
+        <is>
+          <t>- 기관 투자자는 월간 전반에 걸쳐 주요 매수 주체로 활동하며 지수 하락 방어 및 상승 전환에 기여했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="15" customHeight="1" s="15">
       <c r="A148" s="17" t="inlineStr">
         <is>
-          <t>- 전기·전자 및 의료·정밀기기 섹터는 AI 반도체 및 HBM 수요 기대감으로 월중 주도주 지위를 유지했습니다.</t>
+          <t>- 외국인 투자자는 월 초 대규모 매도세를 보였으나, 월 중순 이후 반도체 섹터 중심으로 매수세가 유입되며 수급 개선을 이끌었습니다.</t>
         </is>
       </c>
     </row>
     <row r="149" ht="15" customHeight="1" s="15">
       <c r="A149" s="17" t="inlineStr">
         <is>
-          <t>- 건설 및 기계·장비 섹터는 원전 수주 모멘텀으로 강세를 보였으나, 월 후반 프로젝트 불확실성으로 조정받았습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="15" customHeight="1" s="15">
-      <c r="A150" s="17" t="inlineStr">
-        <is>
-          <t>- 인플레이션 우려가 고조될 때마다 보험 등 금리 상승 수혜주로 수급이 순환되는 흐름이 나타났습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="151"/>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+          <t>- 개인 투자자는 지수 하락 시 매수, 상승 시 차익 실현에 집중하며 시장 변동성에 대응하는 모습을 보였습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150"/>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>섹터·테마 흐름</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr"/>
+      <c r="D151" s="3" t="inlineStr"/>
+      <c r="E151" s="3" t="inlineStr"/>
+      <c r="F151" s="3" t="inlineStr"/>
+      <c r="G151" s="3" t="inlineStr"/>
+      <c r="H151" s="3" t="inlineStr"/>
+      <c r="I151" s="3" t="inlineStr"/>
+      <c r="J151" s="3" t="inlineStr"/>
+      <c r="K151" s="3" t="inlineStr"/>
+    </row>
+    <row r="152" ht="15" customHeight="1" s="15">
+      <c r="A152" s="17" t="inlineStr">
+        <is>
+          <t>- 월 초 유통, 보험, 금융 등 내수 및 방어적 성격의 섹터가 강세를 보였으나, 건설, 기계·장비, 운송장비·부품 등은 하락했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="15" customHeight="1" s="15">
+      <c r="A153" s="17" t="inlineStr">
+        <is>
+          <t>- 월 중순 AI 반도체 및 HBM 수요 기대감으로 전기·전자, 의료·정밀기기, 기계·장비 섹터가 시장 상승을 주도했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="31" customHeight="1" s="15">
+      <c r="A154" s="17" t="inlineStr">
+        <is>
+          <t>- 인플레이션 우려가 고조되면서 금리 상승 수혜가 예상되는 보험 섹터와 방어적 성격의 건설 섹터로 수급이 순환매되는 양상이 나타났습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="31" customHeight="1" s="15">
+      <c r="A155" s="17" t="inlineStr">
+        <is>
+          <t>- 월 후반 반도체/AI 관련주가 지속적인 강세를 보이며 삼성전자와 디아이 등이 상승을 주도했으나, 건설 섹터는 프로젝트 관련 불확실성으로 급락하며 섹터 간 양극화가 심화되었습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="31" customHeight="1" s="15">
+      <c r="A156" s="17" t="inlineStr">
+        <is>
+          <t>- 월간 전체적으로 의료·정밀기기(+18.45%), 전기·전자(+8.59%), 제조(+5.11%) 섹터가 상승을 주도했으며, IT 서비스(-9.34%), 운송장비·부품(-9.73%), 음식료·담배(-9.23%) 섹터는 하락했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157"/>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B152" s="3" t="inlineStr">
+      <c r="B158" s="3" t="inlineStr">
         <is>
           <t>월간 촉매 타임라인</t>
         </is>
       </c>
-      <c r="C152" s="3" t="inlineStr"/>
-      <c r="D152" s="3" t="inlineStr"/>
-      <c r="E152" s="3" t="inlineStr"/>
-      <c r="F152" s="3" t="inlineStr"/>
-      <c r="G152" s="3" t="inlineStr"/>
-      <c r="H152" s="3" t="inlineStr"/>
-      <c r="I152" s="3" t="inlineStr"/>
-      <c r="J152" s="18" t="inlineStr">
+      <c r="C158" s="3" t="inlineStr"/>
+      <c r="D158" s="3" t="inlineStr"/>
+      <c r="E158" s="3" t="inlineStr"/>
+      <c r="F158" s="3" t="inlineStr"/>
+      <c r="G158" s="3" t="inlineStr"/>
+      <c r="H158" s="3" t="inlineStr"/>
+      <c r="I158" s="3" t="inlineStr"/>
+      <c r="J158" s="18" t="inlineStr">
         <is>
           <t>등락률 = 월간 누적 · ★5 주차 상위</t>
         </is>
       </c>
-      <c r="K152" s="3" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="4" t="inlineStr">
+      <c r="K158" s="3" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="4" t="inlineStr">
         <is>
           <t>날짜</t>
         </is>
       </c>
-      <c r="B153" s="4" t="inlineStr">
+      <c r="B159" s="4" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C153" s="4" t="inlineStr">
+      <c r="C159" s="4" t="inlineStr">
         <is>
           <t>시장</t>
         </is>
       </c>
-      <c r="D153" s="4" t="inlineStr">
+      <c r="D159" s="4" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="E153" s="4" t="inlineStr">
+      <c r="E159" s="4" t="inlineStr">
         <is>
           <t>별점</t>
         </is>
       </c>
-      <c r="F153" s="4" t="inlineStr">
+      <c r="F159" s="4" t="inlineStr">
         <is>
           <t>등락률(%)</t>
         </is>
       </c>
-      <c r="G153" s="4" t="inlineStr">
+      <c r="G159" s="4" t="inlineStr">
         <is>
           <t>핵심 촉매</t>
         </is>
       </c>
     </row>
-    <row r="154" ht="15" customHeight="1" s="15">
-      <c r="A154" s="31" t="inlineStr">
+    <row r="160" ht="15" customHeight="1" s="15">
+      <c r="A160" s="31" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B154" s="31" t="inlineStr">
+      <c r="B160" s="31" t="inlineStr">
         <is>
           <t>빛과전자</t>
         </is>
       </c>
-      <c r="C154" s="31" t="inlineStr">
+      <c r="C160" s="31" t="inlineStr">
         <is>
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D154" s="35" t="inlineStr">
+      <c r="D160" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="E154" s="14" t="inlineStr">
+      <c r="E160" s="14" t="inlineStr">
         <is>
           <t>★★★★★</t>
         </is>
       </c>
-      <c r="F154" s="29" t="n">
+      <c r="F160" s="29" t="n">
         <v>41.8</v>
       </c>
-      <c r="G154" s="17" t="inlineStr">
+      <c r="G160" s="17" t="inlineStr">
         <is>
           <t>차세대 광통신 부품 국산화 국책 사업 수행기관 선정.</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="31" customHeight="1" s="15">
-      <c r="A155" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B155" s="31" t="inlineStr">
-        <is>
-          <t>에스엠벡셀</t>
-        </is>
-      </c>
-      <c r="C155" s="31" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D155" s="35" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
-        </is>
-      </c>
-      <c r="E155" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="F155" s="29" t="n">
-        <v>67.88</v>
-      </c>
-      <c r="G155" s="17" t="inlineStr">
-        <is>
-          <t>미국 글로벌 자동차 기업과 차세대 LMR 배터리 기술 협력.</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="15" customHeight="1" s="15">
-      <c r="A156" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B156" s="31" t="inlineStr">
-        <is>
-          <t>머큐리</t>
-        </is>
-      </c>
-      <c r="C156" s="31" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D156" s="35" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="E156" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="F156" s="29" t="n">
-        <v>39.55</v>
-      </c>
-      <c r="G156" s="17" t="inlineStr">
-        <is>
-          <t>미국 버라이즌-코닝 광섬유 공급 계약에 따른 인프라 수혜.</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="31" customHeight="1" s="15">
-      <c r="A157" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B157" s="31" t="inlineStr">
-        <is>
-          <t>범한퓨얼셀</t>
-        </is>
-      </c>
-      <c r="C157" s="31" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D157" s="35" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="E157" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="F157" s="29" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="G157" s="17" t="inlineStr">
-        <is>
-          <t>AI 데이터센터 전력원으로서 연료전지 수요 급증에 따른 수혜.</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="31" customHeight="1" s="15">
-      <c r="A158" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="B158" s="31" t="inlineStr">
-        <is>
-          <t>아모텍</t>
-        </is>
-      </c>
-      <c r="C158" s="31" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D158" s="35" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="E158" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="F158" s="29" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="G158" s="17" t="inlineStr">
-        <is>
-          <t>AI 데이터센터 및 ESS 시장 확대에 따른 MLCC 매출 증가 기대감으로 상한가 기록.</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="31" customHeight="1" s="15">
-      <c r="A159" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="B159" s="31" t="inlineStr">
-        <is>
-          <t>엑스게이트</t>
-        </is>
-      </c>
-      <c r="C159" s="31" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D159" s="35" t="inlineStr">
-        <is>
-          <t>IT 서비스</t>
-        </is>
-      </c>
-      <c r="E159" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="F159" s="29" t="n">
-        <v>53.85</v>
-      </c>
-      <c r="G159" s="17" t="inlineStr">
-        <is>
-          <t>엔비디아 CEO의 사이버 보안 강조 발언에 따른 보안 솔루션 수요 증가 기대감으로 상한가.</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="31" customHeight="1" s="15">
-      <c r="A160" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="B160" s="31" t="inlineStr">
-        <is>
-          <t>샌즈랩</t>
-        </is>
-      </c>
-      <c r="C160" s="31" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D160" s="35" t="inlineStr">
-        <is>
-          <t>IT 서비스</t>
-        </is>
-      </c>
-      <c r="E160" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="F160" s="29" t="n">
-        <v>52.28</v>
-      </c>
-      <c r="G160" s="17" t="inlineStr">
-        <is>
-          <t>엔비디아 CEO의 사이버 보안 핵심 시장 언급에 따른 보안주 수혜 기대감으로 상한가.</t>
         </is>
       </c>
     </row>
     <row r="161" ht="31" customHeight="1" s="15">
       <c r="A161" s="31" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B161" s="31" t="inlineStr">
         <is>
-          <t>카티스</t>
+          <t>에스엠벡셀</t>
         </is>
       </c>
       <c r="C161" s="31" t="inlineStr">
@@ -5453,67 +5347,67 @@
       </c>
       <c r="D161" s="35" t="inlineStr">
         <is>
+          <t>운송장비·부품</t>
+        </is>
+      </c>
+      <c r="E161" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="F161" s="29" t="n">
+        <v>64.54000000000001</v>
+      </c>
+      <c r="G161" s="17" t="inlineStr">
+        <is>
+          <t>미국 글로벌 자동차 기업과 차세대 LMR 배터리 기술 협력.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="15" customHeight="1" s="15">
+      <c r="A162" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B162" s="31" t="inlineStr">
+        <is>
+          <t>머큐리</t>
+        </is>
+      </c>
+      <c r="C162" s="31" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D162" s="35" t="inlineStr">
+        <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="E161" s="14" t="inlineStr">
+      <c r="E162" s="14" t="inlineStr">
         <is>
           <t>★★★★★</t>
         </is>
       </c>
-      <c r="F161" s="29" t="n">
-        <v>47.47</v>
-      </c>
-      <c r="G161" s="17" t="inlineStr">
-        <is>
-          <t>사상 최대 수주잔고 확보 및 AI 데이터센터 수주 확대에 따른 실적 턴어라운드 기대.</t>
-        </is>
-      </c>
-    </row>
-    <row r="162" ht="31" customHeight="1" s="15">
-      <c r="A162" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B162" s="31" t="inlineStr">
-        <is>
-          <t>삼익제약</t>
-        </is>
-      </c>
-      <c r="C162" s="31" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D162" s="35" t="inlineStr">
-        <is>
-          <t>제약</t>
-        </is>
-      </c>
-      <c r="E162" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
       <c r="F162" s="29" t="n">
-        <v>67.72</v>
+        <v>39.14</v>
       </c>
       <c r="G162" s="17" t="inlineStr">
         <is>
-          <t>탈모 치료제 관련 특허 보유 사실이 시장에서 부각되었습니다.</t>
+          <t>미국 버라이즌-코닝 광섬유 공급 계약에 따른 인프라 수혜.</t>
         </is>
       </c>
     </row>
     <row r="163" ht="31" customHeight="1" s="15">
       <c r="A163" s="31" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B163" s="31" t="inlineStr">
         <is>
-          <t>삼현</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C163" s="31" t="inlineStr">
@@ -5523,7 +5417,7 @@
       </c>
       <c r="D163" s="35" t="inlineStr">
         <is>
-          <t>운송장비·부품</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="E163" s="14" t="inlineStr">
@@ -5532,23 +5426,23 @@
         </is>
       </c>
       <c r="F163" s="29" t="n">
-        <v>60.93</v>
+        <v>38.89</v>
       </c>
       <c r="G163" s="17" t="inlineStr">
         <is>
-          <t>정부의 제조업 AI 전환 정책 및 스마트 액추에이터 기술력 부각입니다.</t>
+          <t>AI 데이터센터 전력원으로서 연료전지 수요 급증에 따른 수혜.</t>
         </is>
       </c>
     </row>
     <row r="164" ht="31" customHeight="1" s="15">
       <c r="A164" s="31" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B164" s="31" t="inlineStr">
         <is>
-          <t>하이젠알앤엠</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="C164" s="31" t="inlineStr">
@@ -5567,421 +5461,421 @@
         </is>
       </c>
       <c r="F164" s="29" t="n">
-        <v>57.87</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="G164" s="17" t="inlineStr">
         <is>
-          <t>정부의 제조업 AI 전환 정책 및 로봇 핵심 부품 기술력이 부각되었습니다.</t>
+          <t>AI 데이터센터 및 ESS 시장 확대에 따른 MLCC 매출 증가 기대감으로 상한가 기록.</t>
         </is>
       </c>
     </row>
     <row r="165" ht="31" customHeight="1" s="15">
       <c r="A165" s="31" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B165" s="31" t="inlineStr">
+        <is>
+          <t>엑스게이트</t>
+        </is>
+      </c>
+      <c r="C165" s="31" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D165" s="35" t="inlineStr">
+        <is>
+          <t>IT 서비스</t>
+        </is>
+      </c>
+      <c r="E165" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="F165" s="29" t="n">
+        <v>55.12</v>
+      </c>
+      <c r="G165" s="17" t="inlineStr">
+        <is>
+          <t>엔비디아 CEO의 사이버 보안 강조 발언에 따른 보안 솔루션 수요 증가 기대감으로 상한가.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="31" customHeight="1" s="15">
+      <c r="A166" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B166" s="31" t="inlineStr">
+        <is>
+          <t>샌즈랩</t>
+        </is>
+      </c>
+      <c r="C166" s="31" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D166" s="35" t="inlineStr">
+        <is>
+          <t>IT 서비스</t>
+        </is>
+      </c>
+      <c r="E166" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="F166" s="29" t="n">
+        <v>52.28</v>
+      </c>
+      <c r="G166" s="17" t="inlineStr">
+        <is>
+          <t>엔비디아 CEO의 사이버 보안 핵심 시장 언급에 따른 보안주 수혜 기대감으로 상한가.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="31" customHeight="1" s="15">
+      <c r="A167" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B167" s="31" t="inlineStr">
+        <is>
+          <t>카티스</t>
+        </is>
+      </c>
+      <c r="C167" s="31" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D167" s="35" t="inlineStr">
+        <is>
+          <t>IT 서비스</t>
+        </is>
+      </c>
+      <c r="E167" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="F167" s="29" t="n">
+        <v>47.47</v>
+      </c>
+      <c r="G167" s="17" t="inlineStr">
+        <is>
+          <t>사상 최대 수주잔고 확보 및 AI 데이터센터 수주 확대에 따른 실적 턴어라운드 기대.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="31" customHeight="1" s="15">
+      <c r="A168" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B168" s="31" t="inlineStr">
+        <is>
+          <t>삼익제약</t>
+        </is>
+      </c>
+      <c r="C168" s="31" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D168" s="35" t="inlineStr">
+        <is>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="E168" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="F168" s="29" t="n">
+        <v>69.56999999999999</v>
+      </c>
+      <c r="G168" s="17" t="inlineStr">
+        <is>
+          <t>탈모 치료제 관련 특허 보유 사실이 시장에서 부각되었습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="31" customHeight="1" s="15">
+      <c r="A169" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B169" s="31" t="inlineStr">
+        <is>
+          <t>삼현</t>
+        </is>
+      </c>
+      <c r="C169" s="31" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D169" s="35" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
+        </is>
+      </c>
+      <c r="E169" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="F169" s="29" t="n">
+        <v>60.31</v>
+      </c>
+      <c r="G169" s="17" t="inlineStr">
+        <is>
+          <t>정부의 제조업 AI 전환 정책 및 스마트 액추에이터 기술력 부각입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="31" customHeight="1" s="15">
+      <c r="A170" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B170" s="31" t="inlineStr">
+        <is>
+          <t>하이젠알앤엠</t>
+        </is>
+      </c>
+      <c r="C170" s="31" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D170" s="35" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="E170" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="F170" s="29" t="n">
+        <v>58.67</v>
+      </c>
+      <c r="G170" s="17" t="inlineStr">
+        <is>
+          <t>정부의 제조업 AI 전환 정책 및 로봇 핵심 부품 기술력이 부각되었습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="31" customHeight="1" s="15">
+      <c r="A171" s="31" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="B165" s="31" t="inlineStr">
+      <c r="B171" s="31" t="inlineStr">
         <is>
           <t>빛샘전자</t>
         </is>
       </c>
-      <c r="C165" s="31" t="inlineStr">
+      <c r="C171" s="31" t="inlineStr">
         <is>
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D165" s="35" t="inlineStr">
+      <c r="D171" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="E165" s="14" t="inlineStr">
+      <c r="E171" s="14" t="inlineStr">
         <is>
           <t>★★★★★</t>
         </is>
       </c>
-      <c r="F165" s="29" t="n">
-        <v>62.18</v>
-      </c>
-      <c r="G165" s="17" t="inlineStr">
+      <c r="F171" s="29" t="n">
+        <v>61.26</v>
+      </c>
+      <c r="G171" s="17" t="inlineStr">
         <is>
           <t>AI 데이터센터 인프라 확장에 따른 광통신 부품 수요 기대감.</t>
         </is>
       </c>
     </row>
-    <row r="166" ht="44.5" customHeight="1" s="15">
-      <c r="A166" s="31" t="inlineStr">
+    <row r="172" ht="44.5" customHeight="1" s="15">
+      <c r="A172" s="31" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="B166" s="31" t="inlineStr">
+      <c r="B172" s="31" t="inlineStr">
         <is>
           <t>우리로 (2회)</t>
         </is>
       </c>
-      <c r="C166" s="31" t="inlineStr">
+      <c r="C172" s="31" t="inlineStr">
         <is>
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D166" s="35" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="E166" s="14" t="inlineStr">
+      <c r="D172" s="35" t="inlineStr">
+        <is>
+          <t>유통</t>
+        </is>
+      </c>
+      <c r="E172" s="14" t="inlineStr">
         <is>
           <t>★★★★★</t>
         </is>
       </c>
-      <c r="F166" s="29" t="n">
-        <v>58.83</v>
-      </c>
-      <c r="G166" s="17" t="inlineStr">
+      <c r="F172" s="29" t="n">
+        <v>59.23</v>
+      </c>
+      <c r="G172" s="17" t="inlineStr">
         <is>
           <t>AI 데이터센터 확대에 따른 광통신 수혜 기대.
 (09-09) 미국 양자컴퓨터 투자 및 AI 광통신 관련주로 시장 관심 집중.</t>
         </is>
       </c>
     </row>
-    <row r="167" ht="44.5" customHeight="1" s="15">
-      <c r="A167" s="31" t="inlineStr">
+    <row r="173" ht="44.5" customHeight="1" s="15">
+      <c r="A173" s="31" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="B167" s="31" t="inlineStr">
+      <c r="B173" s="31" t="inlineStr">
         <is>
           <t>앤씨앤 (2회)</t>
         </is>
       </c>
-      <c r="C167" s="31" t="inlineStr">
+      <c r="C173" s="31" t="inlineStr">
         <is>
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D167" s="35" t="inlineStr">
+      <c r="D173" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="E167" s="14" t="inlineStr">
+      <c r="E173" s="14" t="inlineStr">
         <is>
           <t>★★★★★</t>
         </is>
       </c>
-      <c r="F167" s="29" t="n">
+      <c r="F173" s="29" t="n">
         <v>57.91</v>
       </c>
-      <c r="G167" s="17" t="inlineStr">
+      <c r="G173" s="17" t="inlineStr">
         <is>
           <t>비투엔의 경영권 인수 추진 소식에 따른 급등.
 (09-17) 경영권 인수 및 유상증자 결정이라는 기업 지배구조 변화 재료로 상한가 기록.</t>
         </is>
       </c>
     </row>
-    <row r="168" ht="15" customHeight="1" s="15">
-      <c r="A168" s="31" t="inlineStr">
+    <row r="174" ht="15" customHeight="1" s="15">
+      <c r="A174" s="31" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="B168" s="31" t="inlineStr">
+      <c r="B174" s="31" t="inlineStr">
         <is>
           <t>성호전자</t>
         </is>
       </c>
-      <c r="C168" s="31" t="inlineStr">
+      <c r="C174" s="31" t="inlineStr">
         <is>
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D168" s="35" t="inlineStr">
+      <c r="D174" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="E168" s="14" t="inlineStr">
+      <c r="E174" s="14" t="inlineStr">
         <is>
           <t>★★★★★</t>
         </is>
       </c>
-      <c r="F168" s="29" t="n">
-        <v>53.42</v>
-      </c>
-      <c r="G168" s="17" t="inlineStr">
+      <c r="F174" s="29" t="n">
+        <v>57.54</v>
+      </c>
+      <c r="G174" s="17" t="inlineStr">
         <is>
           <t>AI 데이터센터 투자 확대에 따른 전송 수요 증가.</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="44.5" customHeight="1" s="15">
-      <c r="A169" s="31" t="inlineStr">
+    <row r="175" ht="44.5" customHeight="1" s="15">
+      <c r="A175" s="31" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="B169" s="31" t="inlineStr">
+      <c r="B175" s="31" t="inlineStr">
         <is>
           <t>가온전선 (2회)</t>
         </is>
       </c>
-      <c r="C169" s="31" t="inlineStr">
+      <c r="C175" s="31" t="inlineStr">
         <is>
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D169" s="35" t="inlineStr">
+      <c r="D175" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="E169" s="14" t="inlineStr">
+      <c r="E175" s="14" t="inlineStr">
         <is>
           <t>★★★★★</t>
         </is>
       </c>
-      <c r="F169" s="29" t="n">
-        <v>50.83</v>
-      </c>
-      <c r="G169" s="17" t="inlineStr">
+      <c r="F175" s="29" t="n">
+        <v>51.31</v>
+      </c>
+      <c r="G175" s="17" t="inlineStr">
         <is>
           <t>아마존 데이터센터용 전력장비 공급 계약 체결.
 (09-09) 캐나다 공공 전력망 시장 첫 진출 및 북미 사업 확대 가시화.</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="31" customHeight="1" s="15">
-      <c r="A170" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B170" s="31" t="inlineStr">
-        <is>
-          <t>토마토시스템</t>
-        </is>
-      </c>
-      <c r="C170" s="31" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D170" s="35" t="inlineStr">
-        <is>
-          <t>IT 서비스</t>
-        </is>
-      </c>
-      <c r="E170" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="F170" s="29" t="n">
-        <v>66.95</v>
-      </c>
-      <c r="G170" s="17" t="inlineStr">
-        <is>
-          <t>투자한 미국 보험사의 사업 최종 승인이라는 확실한 대형 호재로 상한가를 기록함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="31" customHeight="1" s="15">
-      <c r="A171" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B171" s="31" t="inlineStr">
-        <is>
-          <t>시그네틱스</t>
-        </is>
-      </c>
-      <c r="C171" s="31" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D171" s="35" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="E171" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="F171" s="29" t="n">
-        <v>34.95</v>
-      </c>
-      <c r="G171" s="17" t="inlineStr">
-        <is>
-          <t>AI 시장 확대에 따른 첨단 패키징 수요 급증이라는 산업적 호재로 상한가를 기록함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="172" ht="31" customHeight="1" s="15">
-      <c r="A172" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B172" s="31" t="inlineStr">
-        <is>
-          <t>인벤테라</t>
-        </is>
-      </c>
-      <c r="C172" s="31" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D172" s="35" t="inlineStr">
-        <is>
-          <t>제약</t>
-        </is>
-      </c>
-      <c r="E172" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="F172" s="29" t="n">
-        <v>19.61</v>
-      </c>
-      <c r="G172" s="17" t="inlineStr">
-        <is>
-          <t>조영제 임상 3상 결과 발표라는 제약·바이오 분야의 핵심적 성과가 주가 급등을 견인함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="173" ht="31" customHeight="1" s="15">
-      <c r="A173" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B173" s="31" t="inlineStr">
-        <is>
-          <t>비트플래닛</t>
-        </is>
-      </c>
-      <c r="C173" s="31" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D173" s="35" t="inlineStr">
-        <is>
-          <t>IT 서비스</t>
-        </is>
-      </c>
-      <c r="E173" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="F173" s="29" t="n">
-        <v>12.31</v>
-      </c>
-      <c r="G173" s="17" t="inlineStr">
-        <is>
-          <t>비트코인 가격 반등 및 규제 정비 기대감이라는 시장 모멘텀으로 상한가를 기록함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="174" ht="31" customHeight="1" s="15">
-      <c r="A174" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B174" s="31" t="inlineStr">
-        <is>
-          <t>우리넷</t>
-        </is>
-      </c>
-      <c r="C174" s="31" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D174" s="35" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="E174" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="F174" s="29" t="n">
-        <v>62.47</v>
-      </c>
-      <c r="G174" s="17" t="inlineStr">
-        <is>
-          <t>양자암호 전송장비 수요 확대 및 실적 턴어라운드 기대감으로 상한가 기록.</t>
-        </is>
-      </c>
-    </row>
-    <row r="175" ht="31" customHeight="1" s="15">
-      <c r="A175" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B175" s="31" t="inlineStr">
-        <is>
-          <t>파두</t>
-        </is>
-      </c>
-      <c r="C175" s="31" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D175" s="35" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="E175" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="F175" s="29" t="n">
-        <v>23.29</v>
-      </c>
-      <c r="G175" s="17" t="inlineStr">
-        <is>
-          <t>메타의 AI 에이전트 '뮤즈' 흥행에 따른 eSSD 컨트롤러 공급 수혜 기대감.</t>
-        </is>
-      </c>
-    </row>
     <row r="176" ht="31" customHeight="1" s="15">
       <c r="A176" s="31" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B176" s="31" t="inlineStr">
         <is>
-          <t>KSS해운</t>
+          <t>토마토시스템</t>
         </is>
       </c>
       <c r="C176" s="31" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="D176" s="35" t="inlineStr">
         <is>
-          <t>운송·창고</t>
+          <t>IT 서비스</t>
         </is>
       </c>
       <c r="E176" s="14" t="inlineStr">
@@ -5990,193 +5884,408 @@
         </is>
       </c>
       <c r="F176" s="29" t="n">
-        <v>19.22</v>
+        <v>57.42</v>
       </c>
       <c r="G176" s="17" t="inlineStr">
         <is>
-          <t>약 200억 원 규모의 대규모 자사주 매입 결정에 따른 주주가치 제고 기대감.</t>
+          <t>투자한 미국 보험사의 사업 최종 승인이라는 확실한 대형 호재로 상한가를 기록함.</t>
         </is>
       </c>
     </row>
     <row r="177" ht="31" customHeight="1" s="15">
       <c r="A177" s="31" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B177" s="31" t="inlineStr">
+        <is>
+          <t>시그네틱스</t>
+        </is>
+      </c>
+      <c r="C177" s="31" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D177" s="35" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="E177" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="F177" s="29" t="n">
+        <v>35.92</v>
+      </c>
+      <c r="G177" s="17" t="inlineStr">
+        <is>
+          <t>AI 시장 확대에 따른 첨단 패키징 수요 급증이라는 산업적 호재로 상한가를 기록함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="31" customHeight="1" s="15">
+      <c r="A178" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B178" s="31" t="inlineStr">
+        <is>
+          <t>인벤테라</t>
+        </is>
+      </c>
+      <c r="C178" s="31" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D178" s="35" t="inlineStr">
+        <is>
+          <t>일반서비스</t>
+        </is>
+      </c>
+      <c r="E178" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="F178" s="29" t="n">
+        <v>19.61</v>
+      </c>
+      <c r="G178" s="17" t="inlineStr">
+        <is>
+          <t>조영제 임상 3상 결과 발표라는 제약·바이오 분야의 핵심적 성과가 주가 급등을 견인함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="31" customHeight="1" s="15">
+      <c r="A179" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B179" s="31" t="inlineStr">
+        <is>
+          <t>비트플래닛</t>
+        </is>
+      </c>
+      <c r="C179" s="31" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D179" s="35" t="inlineStr">
+        <is>
+          <t>IT 서비스</t>
+        </is>
+      </c>
+      <c r="E179" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="F179" s="29" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="G179" s="17" t="inlineStr">
+        <is>
+          <t>비트코인 가격 반등 및 규제 정비 기대감이라는 시장 모멘텀으로 상한가를 기록함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="15" customHeight="1" s="15">
+      <c r="A180" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B180" s="31" t="inlineStr">
+        <is>
+          <t>노타</t>
+        </is>
+      </c>
+      <c r="C180" s="31" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D180" s="35" t="inlineStr">
+        <is>
+          <t>IT 서비스</t>
+        </is>
+      </c>
+      <c r="E180" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="F180" s="29" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="G180" s="17" t="inlineStr">
+        <is>
+          <t>퀄컴 칩 기반 휴머노이드 AI 가속 기술 부각.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="31" customHeight="1" s="15">
+      <c r="A181" s="31" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B177" s="31" t="inlineStr">
-        <is>
-          <t>쓰리빌리언</t>
-        </is>
-      </c>
-      <c r="C177" s="31" t="inlineStr">
+      <c r="B181" s="31" t="inlineStr">
+        <is>
+          <t>우리넷</t>
+        </is>
+      </c>
+      <c r="C181" s="31" t="inlineStr">
         <is>
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D177" s="35" t="inlineStr">
-        <is>
-          <t>일반서비스</t>
-        </is>
-      </c>
-      <c r="E177" s="14" t="inlineStr">
+      <c r="D181" s="35" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="E181" s="14" t="inlineStr">
         <is>
           <t>★★★★★</t>
         </is>
       </c>
-      <c r="F177" s="29" t="n">
-        <v>11</v>
-      </c>
-      <c r="G177" s="17" t="inlineStr">
-        <is>
-          <t>한국형 ARPA-H 희귀질환 치료제 개발 국책과제 공동연구기관 선정.</t>
-        </is>
-      </c>
-    </row>
-    <row r="178"/>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+      <c r="F181" s="29" t="n">
+        <v>62.47</v>
+      </c>
+      <c r="G181" s="17" t="inlineStr">
+        <is>
+          <t>양자암호 전송장비 수요 확대 및 실적 턴어라운드 기대감으로 상한가 기록.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="31" customHeight="1" s="15">
+      <c r="A182" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B182" s="31" t="inlineStr">
+        <is>
+          <t>파두</t>
+        </is>
+      </c>
+      <c r="C182" s="31" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D182" s="35" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="E182" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="F182" s="29" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="G182" s="17" t="inlineStr">
+        <is>
+          <t>메타의 AI 에이전트 '뮤즈' 흥행에 따른 eSSD 컨트롤러 공급 수혜 기대감.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="31" customHeight="1" s="15">
+      <c r="A183" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B183" s="31" t="inlineStr">
+        <is>
+          <t>KSS해운</t>
+        </is>
+      </c>
+      <c r="C183" s="31" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="D183" s="35" t="inlineStr">
+        <is>
+          <t>운송·창고</t>
+        </is>
+      </c>
+      <c r="E183" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="F183" s="29" t="n">
+        <v>18.01</v>
+      </c>
+      <c r="G183" s="17" t="inlineStr">
+        <is>
+          <t>약 200억 원 규모의 대규모 자사주 매입 결정에 따른 주주가치 제고 기대감.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184"/>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B179" s="3" t="inlineStr">
+      <c r="B185" s="3" t="inlineStr">
         <is>
           <t>다음 달 프리뷰</t>
         </is>
       </c>
-      <c r="C179" s="3" t="inlineStr"/>
-      <c r="D179" s="3" t="inlineStr"/>
-      <c r="E179" s="3" t="inlineStr"/>
-      <c r="F179" s="3" t="inlineStr"/>
-      <c r="G179" s="3" t="inlineStr"/>
-      <c r="H179" s="3" t="inlineStr"/>
-      <c r="I179" s="3" t="inlineStr"/>
-      <c r="J179" s="3" t="inlineStr"/>
-      <c r="K179" s="3" t="inlineStr"/>
-    </row>
-    <row r="180" ht="15" customHeight="1" s="15">
-      <c r="A180" s="17" t="inlineStr">
-        <is>
-          <t>- 반도체 수출 호조 지속</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="15" customHeight="1" s="15">
-      <c r="A181" s="17" t="inlineStr">
-        <is>
-          <t>- AI 인프라 투자 확대</t>
-        </is>
-      </c>
-    </row>
-    <row r="182" ht="15" customHeight="1" s="15">
-      <c r="A182" s="17" t="inlineStr">
-        <is>
-          <t>- 미국 국채금리 추가 상승</t>
-        </is>
-      </c>
-    </row>
-    <row r="183" ht="15" customHeight="1" s="15">
-      <c r="A183" s="17" t="inlineStr">
-        <is>
-          <t>- 인플레이션 압력 지속</t>
-        </is>
-      </c>
-    </row>
-    <row r="184" ht="15" customHeight="1" s="15">
-      <c r="A184" s="17" t="inlineStr">
-        <is>
-          <t>- 외국인 수급의 순매수 전환 여부가 지수 방향성을 결정할 핵심 신호입니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="185" ht="15" customHeight="1" s="15">
-      <c r="A185" s="17" t="inlineStr">
-        <is>
-          <t>- 9/24 신규 실업수당청구건수</t>
-        </is>
-      </c>
+      <c r="C185" s="3" t="inlineStr"/>
+      <c r="D185" s="3" t="inlineStr"/>
+      <c r="E185" s="3" t="inlineStr"/>
+      <c r="F185" s="3" t="inlineStr"/>
+      <c r="G185" s="3" t="inlineStr"/>
+      <c r="H185" s="3" t="inlineStr"/>
+      <c r="I185" s="3" t="inlineStr"/>
+      <c r="J185" s="3" t="inlineStr"/>
+      <c r="K185" s="3" t="inlineStr"/>
     </row>
     <row r="186" ht="15" customHeight="1" s="15">
       <c r="A186" s="17" t="inlineStr">
         <is>
-          <t>- 9/30 국내 광공업생산</t>
+          <t>- 미국 고용지표 및 물가지수가 예상치를 하회하며 연준의 긴축 완화 기대감이 커질 경우, 위험자산 선호 심리가 회복될 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="187" ht="15" customHeight="1" s="15">
       <c r="A187" s="17" t="inlineStr">
         <is>
-          <t>- 9/30 미국 근원 개인소비지출물가</t>
+          <t>- 국내 수출 지표가 견조한 흐름을 이어가고 AI 반도체 수요가 지속될 경우, 기술주 중심의 상승 랠리가 재개될 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="31" customHeight="1" s="15">
+      <c r="A188" s="17" t="inlineStr">
+        <is>
+          <t>- 미국 고용지표 및 물가지수가 예상치를 상회하며 인플레이션 우려가 재부각될 경우, 금리 인상 압력이 커져 시장 전반의 투자 심리가 위축될 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="15" customHeight="1" s="15">
+      <c r="A189" s="17" t="inlineStr">
+        <is>
+          <t>- 국제유가 급등 및 원/달러 환율 상승이 지속될 경우, 기업 실적 악화 우려와 외국인 자금 이탈이 가속화될 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="15" customHeight="1" s="15">
+      <c r="A190" s="17" t="inlineStr">
+        <is>
+          <t>- 미국 고용지표 및 물가지수 발표 결과와 국제유가 및 원/달러 환율 추이가 시장 방향성을 결정하는 핵심 신호가 될 것입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="15" customHeight="1" s="15">
+      <c r="A191" s="17" t="inlineStr">
+        <is>
+          <t>- 2026-10-01 09:00 KST: 한국 수출 전년대비 (중요도 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="15" customHeight="1" s="15">
+      <c r="A192" s="17" t="inlineStr">
+        <is>
+          <t>- 2026-10-01 09:00 KST: 한국 수입 전년대비 (중요도 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="15" customHeight="1" s="15">
+      <c r="A193" s="17" t="inlineStr">
+        <is>
+          <t>- 2026-10-01 23:00 KST: 미국 ISM 제조업 구매관리자지수(PMI) (중요도 4)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="89">
-    <mergeCell ref="G158:K158"/>
-    <mergeCell ref="B84:K84"/>
+  <mergeCells count="95">
     <mergeCell ref="G77:K77"/>
     <mergeCell ref="A186:K186"/>
     <mergeCell ref="G169:K169"/>
+    <mergeCell ref="G178:K178"/>
     <mergeCell ref="G67:K67"/>
+    <mergeCell ref="B142:K142"/>
     <mergeCell ref="G70:K70"/>
-    <mergeCell ref="G125:K125"/>
+    <mergeCell ref="G116:K116"/>
     <mergeCell ref="G127:K127"/>
     <mergeCell ref="G167:K167"/>
     <mergeCell ref="A149:K149"/>
-    <mergeCell ref="A113:E113"/>
     <mergeCell ref="A129:E129"/>
-    <mergeCell ref="A85:K85"/>
     <mergeCell ref="G65:K65"/>
     <mergeCell ref="G79:K79"/>
+    <mergeCell ref="A188:K188"/>
     <mergeCell ref="G73:K73"/>
-    <mergeCell ref="A141:K141"/>
     <mergeCell ref="A131:E131"/>
-    <mergeCell ref="G153:K153"/>
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="G129:K129"/>
+    <mergeCell ref="A190:K190"/>
     <mergeCell ref="A115:E115"/>
     <mergeCell ref="G173:K173"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="G131:K131"/>
-    <mergeCell ref="G155:K155"/>
-    <mergeCell ref="A142:K142"/>
-    <mergeCell ref="A182:K182"/>
+    <mergeCell ref="G115:K115"/>
+    <mergeCell ref="A191:K191"/>
     <mergeCell ref="A119:E119"/>
     <mergeCell ref="G170:K170"/>
-    <mergeCell ref="G157:K157"/>
+    <mergeCell ref="G179:K179"/>
+    <mergeCell ref="A88:K88"/>
+    <mergeCell ref="B85:K85"/>
     <mergeCell ref="G166:K166"/>
+    <mergeCell ref="A153:K153"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="G172:K172"/>
-    <mergeCell ref="A137:K137"/>
     <mergeCell ref="A133:E133"/>
     <mergeCell ref="G69:K69"/>
     <mergeCell ref="G78:K78"/>
+    <mergeCell ref="A192:K192"/>
     <mergeCell ref="A145:K145"/>
+    <mergeCell ref="A139:K139"/>
+    <mergeCell ref="A154:K154"/>
     <mergeCell ref="G133:K133"/>
     <mergeCell ref="G80:K80"/>
-    <mergeCell ref="A181:K181"/>
     <mergeCell ref="G64:K64"/>
     <mergeCell ref="G135:K135"/>
-    <mergeCell ref="A184:K184"/>
-    <mergeCell ref="A180:K180"/>
     <mergeCell ref="G159:K159"/>
+    <mergeCell ref="A155:K155"/>
     <mergeCell ref="G164:K164"/>
     <mergeCell ref="A143:K143"/>
     <mergeCell ref="G161:K161"/>
     <mergeCell ref="A1:G2"/>
     <mergeCell ref="A123:E123"/>
+    <mergeCell ref="G82:K82"/>
     <mergeCell ref="G174:K174"/>
-    <mergeCell ref="G156:K156"/>
     <mergeCell ref="A87:K87"/>
     <mergeCell ref="G66:K66"/>
+    <mergeCell ref="A193:K193"/>
+    <mergeCell ref="A89:K89"/>
     <mergeCell ref="G74:K74"/>
-    <mergeCell ref="B140:K140"/>
     <mergeCell ref="G68:K68"/>
-    <mergeCell ref="A185:K185"/>
+    <mergeCell ref="G180:K180"/>
+    <mergeCell ref="A135:E135"/>
     <mergeCell ref="G168:K168"/>
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="G182:K182"/>
     <mergeCell ref="A125:E125"/>
+    <mergeCell ref="A147:K147"/>
+    <mergeCell ref="A156:K156"/>
     <mergeCell ref="A121:E121"/>
     <mergeCell ref="A127:E127"/>
     <mergeCell ref="G72:K72"/>
@@ -6184,21 +6293,22 @@
     <mergeCell ref="A148:K148"/>
     <mergeCell ref="G71:K71"/>
     <mergeCell ref="G176:K176"/>
+    <mergeCell ref="A146:K146"/>
+    <mergeCell ref="G181:K181"/>
     <mergeCell ref="G160:K160"/>
     <mergeCell ref="A187:K187"/>
     <mergeCell ref="G175:K175"/>
-    <mergeCell ref="A183:K183"/>
     <mergeCell ref="G162:K162"/>
+    <mergeCell ref="G137:K137"/>
     <mergeCell ref="G171:K171"/>
+    <mergeCell ref="A189:K189"/>
     <mergeCell ref="G177:K177"/>
     <mergeCell ref="A86:K86"/>
-    <mergeCell ref="G114:K114"/>
-    <mergeCell ref="G154:K154"/>
-    <mergeCell ref="A150:K150"/>
     <mergeCell ref="G163:K163"/>
     <mergeCell ref="A144:K144"/>
-    <mergeCell ref="G113:K113"/>
     <mergeCell ref="G76:K76"/>
+    <mergeCell ref="A152:K152"/>
+    <mergeCell ref="G183:K183"/>
     <mergeCell ref="G165:K165"/>
     <mergeCell ref="A117:E117"/>
     <mergeCell ref="G75:K75"/>
@@ -6213,7 +6323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.5" customWidth="1" style="15" min="1" max="1"/>
@@ -6243,7 +6353,7 @@
       </c>
       <c r="K1" s="25" t="inlineStr">
         <is>
-          <t>2026-09-01 ~ 2026-09-23</t>
+          <t>2026-09-01 ~ 2026-09-24</t>
         </is>
       </c>
     </row>
@@ -6356,171 +6466,171 @@
     <row r="6">
       <c r="A6" s="31" t="inlineStr">
         <is>
-          <t>와이즈플래닛컴퍼니</t>
-        </is>
-      </c>
-      <c r="B6" s="30" t="inlineStr"/>
+          <t>삼성전자우</t>
+        </is>
+      </c>
+      <c r="B6" s="30" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
       <c r="C6" s="35" t="inlineStr">
         <is>
-          <t>유통</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="D6" s="45" t="n">
-        <v>-91</v>
-      </c>
-      <c r="E6" s="45" t="n">
-        <v>-5</v>
+        <v>673</v>
+      </c>
+      <c r="E6" s="46" t="n">
+        <v>-3380</v>
       </c>
       <c r="F6" s="45" t="n">
-        <v>-86</v>
+        <v>4052</v>
       </c>
       <c r="G6" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="47" t="inlineStr"/>
-      <c r="I6" s="47" t="inlineStr"/>
-      <c r="J6" s="48" t="inlineStr"/>
-      <c r="K6" s="49" t="inlineStr"/>
+        <v>-1319</v>
+      </c>
+      <c r="H6" s="47" t="n">
+        <v>1151.7</v>
+      </c>
+      <c r="I6" s="47" t="n">
+        <v>28532.1</v>
+      </c>
+      <c r="J6" s="48" t="n">
+        <v>7025</v>
+      </c>
+      <c r="K6" s="49" t="n">
+        <v>19.03</v>
+      </c>
       <c r="L6" s="50" t="n">
-        <v>-5.26</v>
+        <v>-9.68</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="31" t="inlineStr">
         <is>
-          <t>신한지주</t>
-        </is>
-      </c>
-      <c r="B7" s="30" t="inlineStr">
+          <t>와이즈플래닛컴퍼니</t>
+        </is>
+      </c>
+      <c r="B7" s="30" t="inlineStr"/>
+      <c r="C7" s="35" t="inlineStr">
+        <is>
+          <t>화학</t>
+        </is>
+      </c>
+      <c r="D7" s="46" t="n">
+        <v>-183</v>
+      </c>
+      <c r="E7" s="46" t="n">
+        <v>-11</v>
+      </c>
+      <c r="F7" s="46" t="n">
+        <v>-172</v>
+      </c>
+      <c r="G7" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="47" t="inlineStr"/>
+      <c r="I7" s="47" t="inlineStr"/>
+      <c r="J7" s="52" t="inlineStr"/>
+      <c r="K7" s="53" t="inlineStr"/>
+      <c r="L7" s="50" t="n">
+        <v>-5.03</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>대한항공</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C7" s="35" t="inlineStr">
-        <is>
-          <t>금융</t>
-        </is>
-      </c>
-      <c r="D7" s="51" t="n">
-        <v>636</v>
-      </c>
-      <c r="E7" s="45" t="n">
-        <v>-2012</v>
-      </c>
-      <c r="F7" s="51" t="n">
-        <v>2648</v>
-      </c>
-      <c r="G7" s="45" t="n">
-        <v>-294</v>
-      </c>
-      <c r="H7" s="47" t="n">
-        <v>2390</v>
-      </c>
-      <c r="I7" s="47" t="n">
-        <v>7642.4</v>
-      </c>
-      <c r="J7" s="52" t="n">
-        <v>525.7</v>
-      </c>
-      <c r="K7" s="53" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="L7" s="50" t="n">
-        <v>-6.3</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="31" t="inlineStr">
-        <is>
-          <t>하나금융지주</t>
-        </is>
-      </c>
-      <c r="B8" s="30" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
       <c r="C8" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>운송·창고</t>
         </is>
       </c>
       <c r="D8" s="45" t="n">
-        <v>-17</v>
+        <v>3607</v>
       </c>
       <c r="E8" s="45" t="n">
-        <v>-983</v>
-      </c>
-      <c r="F8" s="51" t="n">
-        <v>966</v>
-      </c>
-      <c r="G8" s="51" t="n">
-        <v>31</v>
+        <v>2887</v>
+      </c>
+      <c r="F8" s="45" t="n">
+        <v>720</v>
+      </c>
+      <c r="G8" s="46" t="n">
+        <v>-3530</v>
       </c>
       <c r="H8" s="47" t="n">
-        <v>1113.8</v>
+        <v>304.9</v>
       </c>
       <c r="I8" s="47" t="n">
-        <v>7178.9</v>
-      </c>
-      <c r="J8" s="54" t="n">
-        <v>-646.5</v>
-      </c>
-      <c r="K8" s="55" t="n">
-        <v>-1.19</v>
-      </c>
-      <c r="L8" s="50" t="n">
-        <v>-6.82</v>
+        <v>1997.5</v>
+      </c>
+      <c r="J8" s="48" t="n">
+        <v>328.8</v>
+      </c>
+      <c r="K8" s="49" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="L8" s="54" t="n">
+        <v>-1.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="31" t="inlineStr">
         <is>
-          <t>메가터치</t>
+          <t>신한지주</t>
         </is>
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="C9" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="D9" s="51" t="n">
-        <v>44</v>
-      </c>
-      <c r="E9" s="51" t="n">
-        <v>23</v>
-      </c>
-      <c r="F9" s="51" t="n">
-        <v>21</v>
-      </c>
-      <c r="G9" s="45" t="n">
-        <v>-42</v>
+          <t>기타금융</t>
+        </is>
+      </c>
+      <c r="D9" s="45" t="n">
+        <v>579</v>
+      </c>
+      <c r="E9" s="46" t="n">
+        <v>-2077</v>
+      </c>
+      <c r="F9" s="45" t="n">
+        <v>2656</v>
+      </c>
+      <c r="G9" s="46" t="n">
+        <v>-238</v>
       </c>
       <c r="H9" s="47" t="n">
-        <v>14.3</v>
+        <v>2390</v>
       </c>
       <c r="I9" s="47" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="J9" s="52" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="K9" s="53" t="n">
-        <v>53.37</v>
+        <v>7455.8</v>
+      </c>
+      <c r="J9" s="48" t="n">
+        <v>339.1</v>
+      </c>
+      <c r="K9" s="49" t="n">
+        <v>1.01</v>
       </c>
       <c r="L9" s="50" t="n">
-        <v>-6.29</v>
+        <v>-5.81</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="31" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B10" s="30" t="inlineStr">
@@ -6530,85 +6640,85 @@
       </c>
       <c r="C10" s="35" t="inlineStr">
         <is>
-          <t>기계·장비</t>
-        </is>
-      </c>
-      <c r="D10" s="51" t="n">
-        <v>33</v>
-      </c>
-      <c r="E10" s="51" t="n">
-        <v>3</v>
-      </c>
-      <c r="F10" s="51" t="n">
-        <v>29</v>
-      </c>
-      <c r="G10" s="45" t="n">
-        <v>-33</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D10" s="45" t="n">
+        <v>568</v>
+      </c>
+      <c r="E10" s="45" t="n">
+        <v>155</v>
+      </c>
+      <c r="F10" s="45" t="n">
+        <v>413</v>
+      </c>
+      <c r="G10" s="46" t="n">
+        <v>-536</v>
       </c>
       <c r="H10" s="47" t="n">
-        <v>14</v>
+        <v>1715.5</v>
       </c>
       <c r="I10" s="47" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="J10" s="52" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="K10" s="53" t="n">
-        <v>38.14</v>
-      </c>
-      <c r="L10" s="56" t="n">
-        <v>-3.51</v>
+        <v>9939.5</v>
+      </c>
+      <c r="J10" s="48" t="n">
+        <v>982.4</v>
+      </c>
+      <c r="K10" s="49" t="n">
+        <v>16.63</v>
+      </c>
+      <c r="L10" s="50" t="n">
+        <v>-9.91</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="31" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>하나금융지주</t>
         </is>
       </c>
       <c r="B11" s="30" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="C11" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="D11" s="51" t="n">
-        <v>215</v>
-      </c>
-      <c r="E11" s="51" t="n">
-        <v>126</v>
-      </c>
-      <c r="F11" s="51" t="n">
-        <v>90</v>
+          <t>기타금융</t>
+        </is>
+      </c>
+      <c r="D11" s="46" t="n">
+        <v>-36</v>
+      </c>
+      <c r="E11" s="46" t="n">
+        <v>-1008</v>
+      </c>
+      <c r="F11" s="45" t="n">
+        <v>972</v>
       </c>
       <c r="G11" s="45" t="n">
-        <v>-220</v>
+        <v>49</v>
       </c>
       <c r="H11" s="47" t="n">
-        <v>163.9</v>
+        <v>1113.8</v>
       </c>
       <c r="I11" s="47" t="n">
-        <v>695.7</v>
-      </c>
-      <c r="J11" s="52" t="n">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="K11" s="53" t="n">
-        <v>19.57</v>
-      </c>
-      <c r="L11" s="56" t="n">
-        <v>-3.39</v>
+        <v>7059.1</v>
+      </c>
+      <c r="J11" s="55" t="n">
+        <v>-766.3</v>
+      </c>
+      <c r="K11" s="56" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="L11" s="50" t="n">
+        <v>-6.58</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="31" t="inlineStr">
         <is>
-          <t>뉴파워프라즈마</t>
+          <t>메가터치</t>
         </is>
       </c>
       <c r="B12" s="30" t="inlineStr">
@@ -6618,41 +6728,41 @@
       </c>
       <c r="C12" s="35" t="inlineStr">
         <is>
-          <t>기계·장비</t>
-        </is>
-      </c>
-      <c r="D12" s="51" t="n">
-        <v>70</v>
-      </c>
-      <c r="E12" s="51" t="n">
-        <v>93</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D12" s="45" t="n">
+        <v>44</v>
+      </c>
+      <c r="E12" s="45" t="n">
+        <v>23</v>
       </c>
       <c r="F12" s="45" t="n">
-        <v>-22</v>
-      </c>
-      <c r="G12" s="45" t="n">
-        <v>-49</v>
+        <v>21</v>
+      </c>
+      <c r="G12" s="46" t="n">
+        <v>-42</v>
       </c>
       <c r="H12" s="47" t="n">
-        <v>60.7</v>
+        <v>14.3</v>
       </c>
       <c r="I12" s="47" t="n">
-        <v>170.1</v>
-      </c>
-      <c r="J12" s="52" t="n">
-        <v>71.2</v>
-      </c>
-      <c r="K12" s="53" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="L12" s="56" t="n">
-        <v>-4.08</v>
+        <v>52.9</v>
+      </c>
+      <c r="J12" s="48" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="K12" s="49" t="n">
+        <v>52.95</v>
+      </c>
+      <c r="L12" s="50" t="n">
+        <v>-7.07</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="31" t="inlineStr">
         <is>
-          <t>마이크로컨텍솔</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="B13" s="30" t="inlineStr">
@@ -6662,41 +6772,41 @@
       </c>
       <c r="C13" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="D13" s="51" t="n">
-        <v>137</v>
-      </c>
-      <c r="E13" s="51" t="n">
-        <v>124</v>
-      </c>
-      <c r="F13" s="51" t="n">
-        <v>13</v>
-      </c>
-      <c r="G13" s="45" t="n">
-        <v>-199</v>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="D13" s="45" t="n">
+        <v>33</v>
+      </c>
+      <c r="E13" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" s="45" t="n">
+        <v>29</v>
+      </c>
+      <c r="G13" s="46" t="n">
+        <v>-34</v>
       </c>
       <c r="H13" s="47" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I13" s="47" t="n">
-        <v>194.4</v>
-      </c>
-      <c r="J13" s="52" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="K13" s="53" t="n">
-        <v>39.57</v>
+        <v>103.7</v>
+      </c>
+      <c r="J13" s="48" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="K13" s="49" t="n">
+        <v>36.74</v>
       </c>
       <c r="L13" s="50" t="n">
-        <v>-6.54</v>
+        <v>-5.27</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="31" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>오킨스전자</t>
         </is>
       </c>
       <c r="B14" s="30" t="inlineStr">
@@ -6706,129 +6816,129 @@
       </c>
       <c r="C14" s="35" t="inlineStr">
         <is>
-          <t>기계·장비</t>
-        </is>
-      </c>
-      <c r="D14" s="51" t="n">
-        <v>340</v>
-      </c>
-      <c r="E14" s="51" t="n">
-        <v>241</v>
-      </c>
-      <c r="F14" s="51" t="n">
-        <v>98</v>
-      </c>
-      <c r="G14" s="45" t="n">
-        <v>-272</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D14" s="45" t="n">
+        <v>106</v>
+      </c>
+      <c r="E14" s="46" t="n">
+        <v>-7</v>
+      </c>
+      <c r="F14" s="45" t="n">
+        <v>113</v>
+      </c>
+      <c r="G14" s="46" t="n">
+        <v>-80</v>
       </c>
       <c r="H14" s="47" t="n">
-        <v>113.5</v>
+        <v>43.3</v>
       </c>
       <c r="I14" s="47" t="n">
-        <v>887.6</v>
-      </c>
-      <c r="J14" s="52" t="n">
-        <v>322.8</v>
-      </c>
-      <c r="K14" s="53" t="n">
-        <v>64.02</v>
+        <v>258.2</v>
+      </c>
+      <c r="J14" s="48" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="K14" s="49" t="n">
+        <v>19.29</v>
       </c>
       <c r="L14" s="50" t="n">
-        <v>-5.44</v>
+        <v>-9.779999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="31" t="inlineStr">
         <is>
-          <t>코웨이</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="B15" s="30" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="C15" s="35" t="inlineStr">
         <is>
-          <t>일반서비스</t>
-        </is>
-      </c>
-      <c r="D15" s="51" t="n">
-        <v>13</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D15" s="45" t="n">
+        <v>194</v>
       </c>
       <c r="E15" s="45" t="n">
-        <v>-258</v>
-      </c>
-      <c r="F15" s="51" t="n">
-        <v>271</v>
-      </c>
-      <c r="G15" s="45" t="n">
-        <v>-109</v>
+        <v>104</v>
+      </c>
+      <c r="F15" s="45" t="n">
+        <v>90</v>
+      </c>
+      <c r="G15" s="46" t="n">
+        <v>-201</v>
       </c>
       <c r="H15" s="47" t="n">
-        <v>346.9</v>
+        <v>163.9</v>
       </c>
       <c r="I15" s="47" t="n">
-        <v>896.5</v>
-      </c>
-      <c r="J15" s="54" t="n">
-        <v>-121</v>
-      </c>
-      <c r="K15" s="53" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="L15" s="50" t="n">
-        <v>-9.42</v>
+        <v>723.6</v>
+      </c>
+      <c r="J15" s="48" t="n">
+        <v>118.3</v>
+      </c>
+      <c r="K15" s="49" t="n">
+        <v>20</v>
+      </c>
+      <c r="L15" s="57" t="n">
+        <v>-3.39</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="31" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>코웨이</t>
         </is>
       </c>
       <c r="B16" s="30" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="C16" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="D16" s="51" t="n">
-        <v>213</v>
-      </c>
-      <c r="E16" s="51" t="n">
-        <v>93</v>
-      </c>
-      <c r="F16" s="51" t="n">
-        <v>119</v>
-      </c>
-      <c r="G16" s="45" t="n">
-        <v>-191</v>
+          <t>일반서비스</t>
+        </is>
+      </c>
+      <c r="D16" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="E16" s="46" t="n">
+        <v>-261</v>
+      </c>
+      <c r="F16" s="45" t="n">
+        <v>272</v>
+      </c>
+      <c r="G16" s="46" t="n">
+        <v>-108</v>
       </c>
       <c r="H16" s="47" t="n">
-        <v>49.4</v>
+        <v>346.9</v>
       </c>
       <c r="I16" s="47" t="n">
-        <v>272.1</v>
-      </c>
-      <c r="J16" s="52" t="n">
-        <v>96.90000000000001</v>
-      </c>
-      <c r="K16" s="53" t="n">
-        <v>40.39</v>
-      </c>
-      <c r="L16" s="56" t="n">
-        <v>-2.21</v>
+        <v>882</v>
+      </c>
+      <c r="J16" s="55" t="n">
+        <v>-135.5</v>
+      </c>
+      <c r="K16" s="49" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="L16" s="50" t="n">
+        <v>-9.529999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="31" t="inlineStr">
         <is>
-          <t>안랩</t>
+          <t>뉴파워프라즈마</t>
         </is>
       </c>
       <c r="B17" s="30" t="inlineStr">
@@ -6838,173 +6948,173 @@
       </c>
       <c r="C17" s="35" t="inlineStr">
         <is>
-          <t>IT 서비스</t>
-        </is>
-      </c>
-      <c r="D17" s="51" t="n">
-        <v>228</v>
-      </c>
-      <c r="E17" s="51" t="n">
-        <v>126</v>
-      </c>
-      <c r="F17" s="51" t="n">
-        <v>102</v>
-      </c>
-      <c r="G17" s="45" t="n">
-        <v>-232</v>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="D17" s="45" t="n">
+        <v>70</v>
+      </c>
+      <c r="E17" s="45" t="n">
+        <v>93</v>
+      </c>
+      <c r="F17" s="46" t="n">
+        <v>-22</v>
+      </c>
+      <c r="G17" s="46" t="n">
+        <v>-49</v>
       </c>
       <c r="H17" s="47" t="n">
-        <v>42.9</v>
+        <v>60.7</v>
       </c>
       <c r="I17" s="47" t="n">
-        <v>367.5</v>
-      </c>
-      <c r="J17" s="52" t="n">
-        <v>53.4</v>
-      </c>
-      <c r="K17" s="53" t="n">
-        <v>24.87</v>
-      </c>
-      <c r="L17" s="56" t="n">
-        <v>-2.58</v>
+        <v>176.7</v>
+      </c>
+      <c r="J17" s="48" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="K17" s="49" t="n">
+        <v>36.68</v>
+      </c>
+      <c r="L17" s="57" t="n">
+        <v>-3.91</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="31" t="inlineStr">
         <is>
-          <t>유니퀘스트</t>
+          <t>마이크로컨텍솔</t>
         </is>
       </c>
       <c r="B18" s="30" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="C18" s="35" t="inlineStr">
         <is>
-          <t>유통</t>
-        </is>
-      </c>
-      <c r="D18" s="51" t="n">
-        <v>62</v>
-      </c>
-      <c r="E18" s="51" t="n">
-        <v>51</v>
-      </c>
-      <c r="F18" s="51" t="n">
-        <v>11</v>
-      </c>
-      <c r="G18" s="45" t="n">
-        <v>-63</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D18" s="45" t="n">
+        <v>137</v>
+      </c>
+      <c r="E18" s="45" t="n">
+        <v>124</v>
+      </c>
+      <c r="F18" s="45" t="n">
+        <v>13</v>
+      </c>
+      <c r="G18" s="46" t="n">
+        <v>-199</v>
       </c>
       <c r="H18" s="47" t="n">
-        <v>4.3</v>
+        <v>20</v>
       </c>
       <c r="I18" s="47" t="n">
-        <v>56.3</v>
-      </c>
-      <c r="J18" s="54" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="K18" s="53" t="n">
-        <v>14.97</v>
-      </c>
-      <c r="L18" s="56" t="n">
-        <v>-4.04</v>
+        <v>199.1</v>
+      </c>
+      <c r="J18" s="48" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="K18" s="49" t="n">
+        <v>40.77</v>
+      </c>
+      <c r="L18" s="50" t="n">
+        <v>-5.45</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="31" t="inlineStr">
         <is>
-          <t>드림텍</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B19" s="30" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="C19" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="D19" s="51" t="n">
-        <v>202</v>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="D19" s="45" t="n">
+        <v>339</v>
       </c>
       <c r="E19" s="45" t="n">
-        <v>-86</v>
-      </c>
-      <c r="F19" s="51" t="n">
-        <v>287</v>
-      </c>
-      <c r="G19" s="45" t="n">
-        <v>-200</v>
+        <v>241</v>
+      </c>
+      <c r="F19" s="45" t="n">
+        <v>98</v>
+      </c>
+      <c r="G19" s="46" t="n">
+        <v>-271</v>
       </c>
       <c r="H19" s="47" t="n">
-        <v>66.59999999999999</v>
+        <v>113.5</v>
       </c>
       <c r="I19" s="47" t="n">
-        <v>184.6</v>
-      </c>
-      <c r="J19" s="52" t="n">
-        <v>85.3</v>
-      </c>
-      <c r="K19" s="53" t="n">
-        <v>47.31</v>
+        <v>878.1</v>
+      </c>
+      <c r="J19" s="48" t="n">
+        <v>313.3</v>
+      </c>
+      <c r="K19" s="49" t="n">
+        <v>64.92</v>
       </c>
       <c r="L19" s="50" t="n">
-        <v>-7.93</v>
+        <v>-5.64</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>S-Oil우</t>
+          <t>샘씨엔에스</t>
         </is>
       </c>
       <c r="B20" s="30" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="C20" s="35" t="inlineStr">
         <is>
-          <t>화학</t>
-        </is>
-      </c>
-      <c r="D20" s="51" t="n">
-        <v>78</v>
-      </c>
-      <c r="E20" s="51" t="n">
-        <v>7</v>
-      </c>
-      <c r="F20" s="51" t="n">
-        <v>70</v>
-      </c>
-      <c r="G20" s="45" t="n">
-        <v>-75</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D20" s="45" t="n">
+        <v>213</v>
+      </c>
+      <c r="E20" s="45" t="n">
+        <v>93</v>
+      </c>
+      <c r="F20" s="45" t="n">
+        <v>119</v>
+      </c>
+      <c r="G20" s="46" t="n">
+        <v>-191</v>
       </c>
       <c r="H20" s="47" t="n">
-        <v>4.2</v>
+        <v>49.4</v>
       </c>
       <c r="I20" s="47" t="n">
-        <v>200.9</v>
-      </c>
-      <c r="J20" s="52" t="n">
-        <v>36.1</v>
-      </c>
-      <c r="K20" s="53" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="L20" s="57" t="n">
-        <v>-0.6</v>
+        <v>283.3</v>
+      </c>
+      <c r="J20" s="48" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="K20" s="49" t="n">
+        <v>40.39</v>
+      </c>
+      <c r="L20" s="54" t="n">
+        <v>-1.93</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="31" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>안랩</t>
         </is>
       </c>
       <c r="B21" s="30" t="inlineStr">
@@ -7014,261 +7124,261 @@
       </c>
       <c r="C21" s="35" t="inlineStr">
         <is>
-          <t>제약</t>
-        </is>
-      </c>
-      <c r="D21" s="51" t="n">
-        <v>105</v>
-      </c>
-      <c r="E21" s="51" t="n">
-        <v>144</v>
+          <t>IT 서비스</t>
+        </is>
+      </c>
+      <c r="D21" s="45" t="n">
+        <v>239</v>
+      </c>
+      <c r="E21" s="45" t="n">
+        <v>136</v>
       </c>
       <c r="F21" s="45" t="n">
-        <v>-39</v>
-      </c>
-      <c r="G21" s="45" t="n">
-        <v>-105</v>
+        <v>102</v>
+      </c>
+      <c r="G21" s="46" t="n">
+        <v>-243</v>
       </c>
       <c r="H21" s="47" t="n">
-        <v>230.9</v>
+        <v>42.9</v>
       </c>
       <c r="I21" s="47" t="n">
-        <v>770.8</v>
-      </c>
-      <c r="J21" s="54" t="n">
-        <v>-37.7</v>
-      </c>
-      <c r="K21" s="53" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="L21" s="50" t="n">
-        <v>-5.3</v>
+        <v>388.8</v>
+      </c>
+      <c r="J21" s="48" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="K21" s="49" t="n">
+        <v>24.53</v>
+      </c>
+      <c r="L21" s="57" t="n">
+        <v>-2.58</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="31" t="inlineStr">
         <is>
-          <t>코미팜</t>
+          <t>유니퀘스트</t>
         </is>
       </c>
       <c r="B22" s="30" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="C22" s="35" t="inlineStr">
         <is>
-          <t>제약</t>
-        </is>
-      </c>
-      <c r="D22" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="51" t="n">
-        <v>1</v>
+          <t>유통</t>
+        </is>
+      </c>
+      <c r="D22" s="45" t="n">
+        <v>62</v>
+      </c>
+      <c r="E22" s="45" t="n">
+        <v>50</v>
+      </c>
+      <c r="F22" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="G22" s="46" t="n">
+        <v>-63</v>
       </c>
       <c r="H22" s="47" t="n">
-        <v>31.8</v>
+        <v>4.3</v>
       </c>
       <c r="I22" s="47" t="n">
-        <v>240.2</v>
-      </c>
-      <c r="J22" s="54" t="n">
-        <v>-159</v>
-      </c>
-      <c r="K22" s="53" t="n">
-        <v>6.02</v>
-      </c>
-      <c r="L22" s="50" t="n">
-        <v>-9.1</v>
+        <v>60.3</v>
+      </c>
+      <c r="J22" s="48" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K22" s="49" t="n">
+        <v>15.09</v>
+      </c>
+      <c r="L22" s="57" t="n">
+        <v>-4.04</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="31" t="inlineStr">
         <is>
-          <t>한국알콜</t>
+          <t>드림텍</t>
         </is>
       </c>
       <c r="B23" s="30" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="C23" s="35" t="inlineStr">
         <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D23" s="45" t="n">
+        <v>202</v>
+      </c>
+      <c r="E23" s="46" t="n">
+        <v>-86</v>
+      </c>
+      <c r="F23" s="45" t="n">
+        <v>287</v>
+      </c>
+      <c r="G23" s="46" t="n">
+        <v>-200</v>
+      </c>
+      <c r="H23" s="47" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="I23" s="47" t="n">
+        <v>182.1</v>
+      </c>
+      <c r="J23" s="48" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="K23" s="49" t="n">
+        <v>47.31</v>
+      </c>
+      <c r="L23" s="50" t="n">
+        <v>-7.29</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>S-Oil우</t>
+        </is>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="C24" s="35" t="inlineStr">
+        <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D23" s="51" t="n">
-        <v>30</v>
-      </c>
-      <c r="E23" s="51" t="n">
-        <v>31</v>
-      </c>
-      <c r="F23" s="45" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G23" s="45" t="n">
-        <v>-30</v>
-      </c>
-      <c r="H23" s="47" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="I23" s="47" t="n">
-        <v>77</v>
-      </c>
-      <c r="J23" s="54" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="K23" s="53" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="L23" s="50" t="n">
-        <v>-5.69</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="31" t="inlineStr">
-        <is>
-          <t>디지털대성</t>
-        </is>
-      </c>
-      <c r="B24" s="30" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="C24" s="35" t="inlineStr">
-        <is>
-          <t>일반서비스</t>
-        </is>
-      </c>
-      <c r="D24" s="51" t="n">
-        <v>14</v>
+      <c r="D24" s="45" t="n">
+        <v>78</v>
       </c>
       <c r="E24" s="45" t="n">
-        <v>-8</v>
-      </c>
-      <c r="F24" s="51" t="n">
-        <v>22</v>
-      </c>
-      <c r="G24" s="45" t="n">
-        <v>-22</v>
+        <v>7</v>
+      </c>
+      <c r="F24" s="45" t="n">
+        <v>70</v>
+      </c>
+      <c r="G24" s="46" t="n">
+        <v>-75</v>
       </c>
       <c r="H24" s="47" t="n">
-        <v>0.2</v>
+        <v>4.2</v>
       </c>
       <c r="I24" s="47" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="J24" s="52" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="K24" s="53" t="n">
-        <v>11.78</v>
-      </c>
-      <c r="L24" s="56" t="n">
-        <v>-2.68</v>
+        <v>211.9</v>
+      </c>
+      <c r="J24" s="48" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="K24" s="49" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="L24" s="54" t="n">
+        <v>-1.08</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="31" t="inlineStr">
         <is>
-          <t>코리안리</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="B25" s="30" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="C25" s="35" t="inlineStr">
         <is>
-          <t>보험</t>
-        </is>
-      </c>
-      <c r="D25" s="51" t="n">
-        <v>3</v>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="D25" s="45" t="n">
+        <v>104</v>
       </c>
       <c r="E25" s="45" t="n">
-        <v>-42</v>
-      </c>
-      <c r="F25" s="51" t="n">
-        <v>45</v>
-      </c>
-      <c r="G25" s="45" t="n">
-        <v>-33</v>
+        <v>143</v>
+      </c>
+      <c r="F25" s="46" t="n">
+        <v>-39</v>
+      </c>
+      <c r="G25" s="46" t="n">
+        <v>-105</v>
       </c>
       <c r="H25" s="47" t="n">
-        <v>40.6</v>
+        <v>230.9</v>
       </c>
       <c r="I25" s="47" t="n">
-        <v>812.4</v>
-      </c>
-      <c r="J25" s="52" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="K25" s="53" t="n">
-        <v>2.23</v>
+        <v>758.6</v>
+      </c>
+      <c r="J25" s="55" t="n">
+        <v>-49.9</v>
+      </c>
+      <c r="K25" s="49" t="n">
+        <v>1.5</v>
       </c>
       <c r="L25" s="50" t="n">
-        <v>-6.82</v>
+        <v>-5.61</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="31" t="inlineStr">
         <is>
-          <t>IPARK현대산업개발</t>
+          <t>코미팜</t>
         </is>
       </c>
       <c r="B26" s="30" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="C26" s="35" t="inlineStr">
         <is>
-          <t>건설</t>
-        </is>
-      </c>
-      <c r="D26" s="51" t="n">
-        <v>81</v>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="D26" s="45" t="n">
+        <v>1</v>
       </c>
       <c r="E26" s="51" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F26" s="51" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="G26" s="45" t="n">
-        <v>-172</v>
+        <v>1</v>
       </c>
       <c r="H26" s="47" t="n">
-        <v>50.8</v>
+        <v>31.8</v>
       </c>
       <c r="I26" s="47" t="n">
-        <v>427.8</v>
-      </c>
-      <c r="J26" s="54" t="n">
-        <v>-23.4</v>
-      </c>
-      <c r="K26" s="53" t="n">
-        <v>0.22</v>
+        <v>242</v>
+      </c>
+      <c r="J26" s="55" t="n">
+        <v>-157.2</v>
+      </c>
+      <c r="K26" s="49" t="n">
+        <v>6.66</v>
       </c>
       <c r="L26" s="50" t="n">
-        <v>-8.210000000000001</v>
+        <v>-8.66</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="31" t="inlineStr">
         <is>
-          <t>지어소프트</t>
+          <t>한국알콜</t>
         </is>
       </c>
       <c r="B27" s="30" t="inlineStr">
@@ -7276,83 +7386,87 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C27" s="35" t="inlineStr"/>
-      <c r="D27" s="51" t="n">
-        <v>59</v>
-      </c>
-      <c r="E27" s="51" t="n">
-        <v>56</v>
-      </c>
-      <c r="F27" s="51" t="n">
-        <v>3</v>
-      </c>
-      <c r="G27" s="45" t="n">
-        <v>-45</v>
+      <c r="C27" s="35" t="inlineStr">
+        <is>
+          <t>화학</t>
+        </is>
+      </c>
+      <c r="D27" s="45" t="n">
+        <v>30</v>
+      </c>
+      <c r="E27" s="45" t="n">
+        <v>31</v>
+      </c>
+      <c r="F27" s="46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G27" s="46" t="n">
+        <v>-30</v>
       </c>
       <c r="H27" s="47" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="I27" s="47" t="n">
-        <v>39</v>
-      </c>
-      <c r="J27" s="52" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="K27" s="53" t="n">
-        <v>29.26</v>
+        <v>82.5</v>
+      </c>
+      <c r="J27" s="48" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K27" s="49" t="n">
+        <v>5.47</v>
       </c>
       <c r="L27" s="50" t="n">
-        <v>-6.7</v>
+        <v>-5.48</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="31" t="inlineStr">
         <is>
-          <t>동아지질</t>
+          <t>디지털대성</t>
         </is>
       </c>
       <c r="B28" s="30" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="C28" s="35" t="inlineStr">
         <is>
-          <t>건설</t>
-        </is>
-      </c>
-      <c r="D28" s="51" t="n">
-        <v>40</v>
-      </c>
-      <c r="E28" s="45" t="n">
-        <v>-1</v>
-      </c>
-      <c r="F28" s="51" t="n">
-        <v>41</v>
-      </c>
-      <c r="G28" s="45" t="n">
-        <v>-38</v>
+          <t>일반서비스</t>
+        </is>
+      </c>
+      <c r="D28" s="45" t="n">
+        <v>14</v>
+      </c>
+      <c r="E28" s="46" t="n">
+        <v>-8</v>
+      </c>
+      <c r="F28" s="45" t="n">
+        <v>22</v>
+      </c>
+      <c r="G28" s="46" t="n">
+        <v>-22</v>
       </c>
       <c r="H28" s="47" t="n">
-        <v>3.1</v>
+        <v>0.2</v>
       </c>
       <c r="I28" s="47" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="J28" s="52" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="K28" s="53" t="n">
-        <v>11.24</v>
-      </c>
-      <c r="L28" s="50" t="n">
-        <v>-5.17</v>
+        <v>28.3</v>
+      </c>
+      <c r="J28" s="48" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K28" s="49" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="L28" s="57" t="n">
+        <v>-3.11</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="31" t="inlineStr">
         <is>
-          <t>케이씨</t>
+          <t>코리안리</t>
         </is>
       </c>
       <c r="B29" s="30" t="inlineStr">
@@ -7362,96 +7476,272 @@
       </c>
       <c r="C29" s="35" t="inlineStr">
         <is>
-          <t>의료·정밀기기</t>
-        </is>
-      </c>
-      <c r="D29" s="51" t="n">
-        <v>38</v>
-      </c>
-      <c r="E29" s="51" t="n">
-        <v>32</v>
-      </c>
-      <c r="F29" s="51" t="n">
-        <v>6</v>
-      </c>
-      <c r="G29" s="45" t="n">
-        <v>-36</v>
+          <t>보험</t>
+        </is>
+      </c>
+      <c r="D29" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" s="46" t="n">
+        <v>-42</v>
+      </c>
+      <c r="F29" s="45" t="n">
+        <v>45</v>
+      </c>
+      <c r="G29" s="46" t="n">
+        <v>-33</v>
       </c>
       <c r="H29" s="47" t="n">
-        <v>7.4</v>
+        <v>40.6</v>
       </c>
       <c r="I29" s="47" t="n">
-        <v>96.90000000000001</v>
-      </c>
-      <c r="J29" s="54" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="K29" s="53" t="n">
-        <v>6.36</v>
-      </c>
-      <c r="L29" s="56" t="n">
-        <v>-2.74</v>
+        <v>809.5</v>
+      </c>
+      <c r="J29" s="48" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K29" s="49" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L29" s="50" t="n">
+        <v>-7.04</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="31" t="inlineStr">
         <is>
+          <t>IPARK현대산업개발</t>
+        </is>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="C30" s="35" t="inlineStr">
+        <is>
+          <t>건설</t>
+        </is>
+      </c>
+      <c r="D30" s="45" t="n">
+        <v>83</v>
+      </c>
+      <c r="E30" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="F30" s="45" t="n">
+        <v>73</v>
+      </c>
+      <c r="G30" s="46" t="n">
+        <v>-174</v>
+      </c>
+      <c r="H30" s="47" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="I30" s="47" t="n">
+        <v>423.5</v>
+      </c>
+      <c r="J30" s="55" t="n">
+        <v>-27.7</v>
+      </c>
+      <c r="K30" s="49" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="L30" s="50" t="n">
+        <v>-6.6</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="31" t="inlineStr">
+        <is>
+          <t>지어소프트</t>
+        </is>
+      </c>
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="C31" s="35" t="inlineStr">
+        <is>
+          <t>IT 서비스</t>
+        </is>
+      </c>
+      <c r="D31" s="45" t="n">
+        <v>59</v>
+      </c>
+      <c r="E31" s="45" t="n">
+        <v>56</v>
+      </c>
+      <c r="F31" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="G31" s="46" t="n">
+        <v>-45</v>
+      </c>
+      <c r="H31" s="47" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="I31" s="47" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="J31" s="48" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K31" s="49" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="L31" s="50" t="n">
+        <v>-9.039999999999999</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="31" t="inlineStr">
+        <is>
+          <t>동아지질</t>
+        </is>
+      </c>
+      <c r="B32" s="30" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="C32" s="35" t="inlineStr">
+        <is>
+          <t>건설</t>
+        </is>
+      </c>
+      <c r="D32" s="45" t="n">
+        <v>40</v>
+      </c>
+      <c r="E32" s="46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F32" s="45" t="n">
+        <v>41</v>
+      </c>
+      <c r="G32" s="46" t="n">
+        <v>-38</v>
+      </c>
+      <c r="H32" s="47" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I32" s="47" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="J32" s="48" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K32" s="49" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="L32" s="50" t="n">
+        <v>-6.14</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>케이씨</t>
+        </is>
+      </c>
+      <c r="B33" s="30" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="C33" s="35" t="inlineStr">
+        <is>
+          <t>의료·정밀기기</t>
+        </is>
+      </c>
+      <c r="D33" s="45" t="n">
+        <v>37</v>
+      </c>
+      <c r="E33" s="45" t="n">
+        <v>31</v>
+      </c>
+      <c r="F33" s="45" t="n">
+        <v>6</v>
+      </c>
+      <c r="G33" s="46" t="n">
+        <v>-36</v>
+      </c>
+      <c r="H33" s="47" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="I33" s="47" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="J33" s="55" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="K33" s="49" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="L33" s="57" t="n">
+        <v>-3.45</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="31" t="inlineStr">
+        <is>
           <t>롯데렌탈</t>
         </is>
       </c>
-      <c r="B30" s="30" t="inlineStr">
+      <c r="B34" s="30" t="inlineStr">
         <is>
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C30" s="35" t="inlineStr">
+      <c r="C34" s="35" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="D30" s="45" t="n">
-        <v>-12</v>
-      </c>
-      <c r="E30" s="45" t="n">
-        <v>-63</v>
-      </c>
-      <c r="F30" s="51" t="n">
+      <c r="D34" s="46" t="n">
+        <v>-13</v>
+      </c>
+      <c r="E34" s="46" t="n">
+        <v>-65</v>
+      </c>
+      <c r="F34" s="45" t="n">
         <v>52</v>
       </c>
-      <c r="G30" s="51" t="n">
-        <v>11</v>
-      </c>
-      <c r="H30" s="47" t="n">
+      <c r="G34" s="45" t="n">
+        <v>12</v>
+      </c>
+      <c r="H34" s="47" t="n">
         <v>121.5</v>
       </c>
-      <c r="I30" s="47" t="n">
-        <v>625.9</v>
-      </c>
-      <c r="J30" s="52" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="K30" s="53" t="n">
+      <c r="I34" s="47" t="n">
+        <v>625.2</v>
+      </c>
+      <c r="J34" s="48" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="K34" s="49" t="n">
         <v>4.97</v>
       </c>
-      <c r="L30" s="50" t="n">
-        <v>-6.95</v>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" s="18" t="inlineStr">
+      <c r="L34" s="50" t="n">
+        <v>-7.06</v>
+      </c>
+    </row>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
         <is>
           <t>최신 거래일 기준 · 52주 신고가 대비 -10% 이내 (KIS 랭킹) · ETF·ETN 제외 · 수급=월간 누적 확정(억원) · 동반 순매수(외인·기관 동일 방향)=합산 굵게</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:L30"/>
+  <autoFilter ref="A5:L34"/>
   <mergeCells count="6">
     <mergeCell ref="D4:J4"/>
     <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A32:L32"/>
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A36:L36"/>
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="A4:C4"/>
   </mergeCells>
@@ -7500,7 +7790,7 @@
       </c>
       <c r="O1" s="25" t="inlineStr">
         <is>
-          <t>2026-09-01 ~ 2026-09-23</t>
+          <t>2026-09-01 ~ 2026-09-24</t>
         </is>
       </c>
     </row>
@@ -7631,7 +7921,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="31" customHeight="1" s="15">
       <c r="A6" s="30" t="n">
         <v>1</v>
       </c>
@@ -7642,11 +7932,11 @@
       </c>
       <c r="C6" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
-        </is>
-      </c>
-      <c r="D6" s="45" t="n">
-        <v>8390</v>
+          <t>기타금융</t>
+        </is>
+      </c>
+      <c r="D6" s="46" t="n">
+        <v>8118</v>
       </c>
       <c r="E6" s="30" t="n">
         <v>1</v>
@@ -7662,7 +7952,7 @@
         </is>
       </c>
       <c r="H6" s="61" t="n">
-        <v>-72174</v>
+        <v>-82160</v>
       </c>
       <c r="J6" s="30" t="n">
         <v>1</v>
@@ -7677,27 +7967,27 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M6" s="45" t="n">
-        <v>39366</v>
+      <c r="M6" s="46" t="n">
+        <v>41629</v>
       </c>
       <c r="N6" s="30" t="n">
         <v>1</v>
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
-        </is>
-      </c>
-      <c r="P6" s="35" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
+          <t>현대차</t>
+        </is>
+      </c>
+      <c r="P6" s="62" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
         </is>
       </c>
       <c r="Q6" s="61" t="n">
-        <v>-4308</v>
-      </c>
-    </row>
-    <row r="7" ht="31" customHeight="1" s="15">
+        <v>-4032</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="30" t="n">
         <v>2</v>
       </c>
@@ -7708,10 +7998,10 @@
       </c>
       <c r="C7" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
-        </is>
-      </c>
-      <c r="D7" s="45" t="n">
+          <t>기타금융</t>
+        </is>
+      </c>
+      <c r="D7" s="46" t="n">
         <v>4771</v>
       </c>
       <c r="E7" s="30" t="n">
@@ -7728,7 +8018,7 @@
         </is>
       </c>
       <c r="H7" s="61" t="n">
-        <v>-12432</v>
+        <v>-6914</v>
       </c>
       <c r="J7" s="30" t="n">
         <v>2</v>
@@ -7743,42 +8033,42 @@
           <t>유통</t>
         </is>
       </c>
-      <c r="M7" s="45" t="n">
-        <v>10339</v>
+      <c r="M7" s="46" t="n">
+        <v>10303</v>
       </c>
       <c r="N7" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="O7" s="1" t="inlineStr">
-        <is>
-          <t>현대차</t>
-        </is>
-      </c>
-      <c r="P7" s="62" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
+      <c r="O7" s="31" t="inlineStr">
+        <is>
+          <t>NAVER</t>
+        </is>
+      </c>
+      <c r="P7" s="35" t="inlineStr">
+        <is>
+          <t>IT 서비스</t>
         </is>
       </c>
       <c r="Q7" s="61" t="n">
-        <v>-3860</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>-3804</v>
+      </c>
+    </row>
+    <row r="8" ht="31" customHeight="1" s="15">
       <c r="A8" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="31" t="inlineStr">
-        <is>
-          <t>대한항공</t>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C8" s="35" t="inlineStr">
         <is>
-          <t>운송·창고</t>
-        </is>
-      </c>
-      <c r="D8" s="45" t="n">
-        <v>2924</v>
+          <t>화학</t>
+        </is>
+      </c>
+      <c r="D8" s="46" t="n">
+        <v>2991</v>
       </c>
       <c r="E8" s="30" t="n">
         <v>3</v>
@@ -7794,7 +8084,7 @@
         </is>
       </c>
       <c r="H8" s="61" t="n">
-        <v>-4879</v>
+        <v>-5851</v>
       </c>
       <c r="J8" s="30" t="n">
         <v>3</v>
@@ -7809,49 +8099,49 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M8" s="45" t="n">
-        <v>3788</v>
+      <c r="M8" s="46" t="n">
+        <v>3673</v>
       </c>
       <c r="N8" s="30" t="n">
         <v>3</v>
       </c>
       <c r="O8" s="31" t="inlineStr">
         <is>
-          <t>NAVER</t>
-        </is>
-      </c>
-      <c r="P8" s="35" t="inlineStr">
-        <is>
-          <t>IT 서비스</t>
+          <t>현대모비스</t>
+        </is>
+      </c>
+      <c r="P8" s="62" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
         </is>
       </c>
       <c r="Q8" s="61" t="n">
-        <v>-3571</v>
-      </c>
-    </row>
-    <row r="9" ht="31" customHeight="1" s="15">
+        <v>-3279</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>SK이노베이션</t>
+      <c r="B9" s="31" t="inlineStr">
+        <is>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C9" s="35" t="inlineStr">
         <is>
-          <t>화학</t>
-        </is>
-      </c>
-      <c r="D9" s="45" t="n">
-        <v>2752</v>
+          <t>운송·창고</t>
+        </is>
+      </c>
+      <c r="D9" s="46" t="n">
+        <v>2898</v>
       </c>
       <c r="E9" s="30" t="n">
         <v>4</v>
       </c>
       <c r="F9" s="31" t="inlineStr">
         <is>
-          <t>두산</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="G9" s="35" t="inlineStr">
@@ -7860,7 +8150,7 @@
         </is>
       </c>
       <c r="H9" s="61" t="n">
-        <v>-3014</v>
+        <v>-3572</v>
       </c>
       <c r="J9" s="30" t="n">
         <v>4</v>
@@ -7875,7 +8165,7 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M9" s="45" t="n">
+      <c r="M9" s="46" t="n">
         <v>3473</v>
       </c>
       <c r="N9" s="30" t="n">
@@ -7883,16 +8173,16 @@
       </c>
       <c r="O9" s="31" t="inlineStr">
         <is>
-          <t>현대모비스</t>
-        </is>
-      </c>
-      <c r="P9" s="62" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="P9" s="35" t="inlineStr">
+        <is>
+          <t>일반서비스</t>
         </is>
       </c>
       <c r="Q9" s="61" t="n">
-        <v>-3246</v>
+        <v>-3068</v>
       </c>
     </row>
     <row r="10">
@@ -7906,18 +8196,18 @@
       </c>
       <c r="C10" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
-        </is>
-      </c>
-      <c r="D10" s="45" t="n">
-        <v>2017</v>
+          <t>기타금융</t>
+        </is>
+      </c>
+      <c r="D10" s="46" t="n">
+        <v>2109</v>
       </c>
       <c r="E10" s="30" t="n">
         <v>5</v>
       </c>
       <c r="F10" s="31" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>두산</t>
         </is>
       </c>
       <c r="G10" s="35" t="inlineStr">
@@ -7926,7 +8216,7 @@
         </is>
       </c>
       <c r="H10" s="61" t="n">
-        <v>-2896</v>
+        <v>-3014</v>
       </c>
       <c r="J10" s="30" t="n">
         <v>5</v>
@@ -7938,27 +8228,27 @@
       </c>
       <c r="L10" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
-        </is>
-      </c>
-      <c r="M10" s="45" t="n">
-        <v>2600</v>
+          <t>기타금융</t>
+        </is>
+      </c>
+      <c r="M10" s="46" t="n">
+        <v>2678</v>
       </c>
       <c r="N10" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="O10" s="31" t="inlineStr">
-        <is>
-          <t>알테오젠</t>
+      <c r="O10" s="1" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="P10" s="35" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="Q10" s="61" t="n">
-        <v>-3068</v>
+        <v>-2613</v>
       </c>
     </row>
     <row r="11">
@@ -7975,8 +8265,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D11" s="45" t="n">
-        <v>1115</v>
+      <c r="D11" s="46" t="n">
+        <v>1016</v>
       </c>
       <c r="E11" s="30" t="n">
         <v>6</v>
@@ -8004,11 +8294,11 @@
       </c>
       <c r="L11" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
-        </is>
-      </c>
-      <c r="M11" s="45" t="n">
-        <v>2254</v>
+          <t>기타금융</t>
+        </is>
+      </c>
+      <c r="M11" s="46" t="n">
+        <v>2252</v>
       </c>
       <c r="N11" s="30" t="n">
         <v>6</v>
@@ -8024,10 +8314,10 @@
         </is>
       </c>
       <c r="Q11" s="61" t="n">
-        <v>-2051</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>-2249</v>
+      </c>
+    </row>
+    <row r="12" ht="31" customHeight="1" s="15">
       <c r="A12" s="30" t="n">
         <v>7</v>
       </c>
@@ -8041,31 +8331,31 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D12" s="45" t="n">
-        <v>1060</v>
+      <c r="D12" s="46" t="n">
+        <v>999</v>
       </c>
       <c r="E12" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="F12" s="31" t="inlineStr">
-        <is>
-          <t>삼성전기</t>
-        </is>
-      </c>
-      <c r="G12" s="35" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>현대차</t>
+        </is>
+      </c>
+      <c r="G12" s="62" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
         </is>
       </c>
       <c r="H12" s="61" t="n">
-        <v>-2146</v>
+        <v>-2315</v>
       </c>
       <c r="J12" s="30" t="n">
         <v>7</v>
       </c>
       <c r="K12" s="31" t="inlineStr">
         <is>
-          <t>DB하이텍</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="L12" s="35" t="inlineStr">
@@ -8073,8 +8363,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M12" s="45" t="n">
-        <v>1854</v>
+      <c r="M12" s="46" t="n">
+        <v>1967</v>
       </c>
       <c r="N12" s="30" t="n">
         <v>7</v>
@@ -8090,25 +8380,25 @@
         </is>
       </c>
       <c r="Q12" s="61" t="n">
-        <v>-1886</v>
-      </c>
-    </row>
-    <row r="13" ht="31" customHeight="1" s="15">
+        <v>-1919</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" s="30" t="n">
         <v>8</v>
       </c>
       <c r="B13" s="31" t="inlineStr">
         <is>
-          <t>현대모비스</t>
-        </is>
-      </c>
-      <c r="C13" s="62" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
-        </is>
-      </c>
-      <c r="D13" s="45" t="n">
-        <v>998</v>
+          <t>로보티즈</t>
+        </is>
+      </c>
+      <c r="C13" s="35" t="inlineStr">
+        <is>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="D13" s="46" t="n">
+        <v>911</v>
       </c>
       <c r="E13" s="30" t="n">
         <v>8</v>
@@ -8120,11 +8410,11 @@
       </c>
       <c r="G13" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>기타금융</t>
         </is>
       </c>
       <c r="H13" s="61" t="n">
-        <v>-1982</v>
+        <v>-2209</v>
       </c>
       <c r="J13" s="30" t="n">
         <v>8</v>
@@ -8139,24 +8429,24 @@
           <t>화학</t>
         </is>
       </c>
-      <c r="M13" s="45" t="n">
-        <v>1831</v>
+      <c r="M13" s="46" t="n">
+        <v>1914</v>
       </c>
       <c r="N13" s="30" t="n">
         <v>8</v>
       </c>
       <c r="O13" s="31" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>삼양식품</t>
         </is>
       </c>
       <c r="P13" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>음식료·담배</t>
         </is>
       </c>
       <c r="Q13" s="61" t="n">
-        <v>-1814</v>
+        <v>-1657</v>
       </c>
     </row>
     <row r="14" ht="31" customHeight="1" s="15">
@@ -8165,39 +8455,39 @@
       </c>
       <c r="B14" s="31" t="inlineStr">
         <is>
-          <t>로보티즈</t>
-        </is>
-      </c>
-      <c r="C14" s="35" t="inlineStr">
-        <is>
-          <t>기계·장비</t>
-        </is>
-      </c>
-      <c r="D14" s="45" t="n">
-        <v>911</v>
+          <t>현대모비스</t>
+        </is>
+      </c>
+      <c r="C14" s="62" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
+        </is>
+      </c>
+      <c r="D14" s="46" t="n">
+        <v>895</v>
       </c>
       <c r="E14" s="30" t="n">
         <v>9</v>
       </c>
       <c r="F14" s="31" t="inlineStr">
         <is>
-          <t>HD현대중공업</t>
-        </is>
-      </c>
-      <c r="G14" s="62" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
+          <t>리노공업</t>
+        </is>
+      </c>
+      <c r="G14" s="35" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="H14" s="61" t="n">
-        <v>-1742</v>
+        <v>-2055</v>
       </c>
       <c r="J14" s="30" t="n">
         <v>9</v>
       </c>
       <c r="K14" s="31" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>DB하이텍</t>
         </is>
       </c>
       <c r="L14" s="35" t="inlineStr">
@@ -8205,27 +8495,27 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M14" s="45" t="n">
-        <v>1652</v>
+      <c r="M14" s="46" t="n">
+        <v>1854</v>
       </c>
       <c r="N14" s="30" t="n">
         <v>9</v>
       </c>
       <c r="O14" s="31" t="inlineStr">
         <is>
-          <t>삼양식품</t>
+          <t>SK스퀘어</t>
         </is>
       </c>
       <c r="P14" s="35" t="inlineStr">
         <is>
-          <t>음식료·담배</t>
+          <t>기타금융</t>
         </is>
       </c>
       <c r="Q14" s="61" t="n">
-        <v>-1596</v>
-      </c>
-    </row>
-    <row r="15" ht="31" customHeight="1" s="15">
+        <v>-1625</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" s="30" t="n">
         <v>10</v>
       </c>
@@ -8239,24 +8529,24 @@
           <t>제약</t>
         </is>
       </c>
-      <c r="D15" s="45" t="n">
+      <c r="D15" s="46" t="n">
         <v>879</v>
       </c>
       <c r="E15" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="F15" s="1" t="inlineStr">
-        <is>
-          <t>현대차</t>
-        </is>
-      </c>
-      <c r="G15" s="62" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
+      <c r="F15" s="31" t="inlineStr">
+        <is>
+          <t>KB금융</t>
+        </is>
+      </c>
+      <c r="G15" s="35" t="inlineStr">
+        <is>
+          <t>기타금융</t>
         </is>
       </c>
       <c r="H15" s="61" t="n">
-        <v>-1676</v>
+        <v>-1766</v>
       </c>
       <c r="J15" s="30" t="n">
         <v>10</v>
@@ -8271,8 +8561,8 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M15" s="45" t="n">
-        <v>1644</v>
+      <c r="M15" s="46" t="n">
+        <v>1657</v>
       </c>
       <c r="N15" s="30" t="n">
         <v>10</v>
@@ -8288,7 +8578,7 @@
         </is>
       </c>
       <c r="Q15" s="61" t="n">
-        <v>-1535</v>
+        <v>-1502</v>
       </c>
     </row>
     <row r="16"/>
@@ -8432,8 +8722,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D20" s="45" t="n">
-        <v>26933</v>
+      <c r="D20" s="46" t="n">
+        <v>34714</v>
       </c>
       <c r="E20" s="30" t="n">
         <v>1</v>
@@ -8449,7 +8739,7 @@
         </is>
       </c>
       <c r="H20" s="61" t="n">
-        <v>-76483</v>
+        <v>-84773</v>
       </c>
       <c r="J20" s="30" t="n">
         <v>1</v>
@@ -8464,7 +8754,7 @@
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="M20" s="45" t="n">
+      <c r="M20" s="46" t="n">
         <v>5622</v>
       </c>
       <c r="N20" s="30" t="n">
@@ -8498,8 +8788,8 @@
           <t>유통</t>
         </is>
       </c>
-      <c r="D21" s="45" t="n">
-        <v>9402</v>
+      <c r="D21" s="46" t="n">
+        <v>9370</v>
       </c>
       <c r="E21" s="30" t="n">
         <v>2</v>
@@ -8515,7 +8805,7 @@
         </is>
       </c>
       <c r="H21" s="61" t="n">
-        <v>-5536</v>
+        <v>-6347</v>
       </c>
       <c r="J21" s="30" t="n">
         <v>2</v>
@@ -8530,7 +8820,7 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M21" s="45" t="n">
+      <c r="M21" s="46" t="n">
         <v>4820</v>
       </c>
       <c r="N21" s="30" t="n">
@@ -8561,11 +8851,11 @@
       </c>
       <c r="C22" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
-        </is>
-      </c>
-      <c r="D22" s="45" t="n">
-        <v>6576</v>
+          <t>기타금융</t>
+        </is>
+      </c>
+      <c r="D22" s="46" t="n">
+        <v>6493</v>
       </c>
       <c r="E22" s="30" t="n">
         <v>3</v>
@@ -8581,7 +8871,7 @@
         </is>
       </c>
       <c r="H22" s="61" t="n">
-        <v>-4810</v>
+        <v>-5969</v>
       </c>
       <c r="J22" s="30" t="n">
         <v>3</v>
@@ -8596,7 +8886,7 @@
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="M22" s="45" t="n">
+      <c r="M22" s="46" t="n">
         <v>3803</v>
       </c>
       <c r="N22" s="30" t="n">
@@ -8609,7 +8899,7 @@
       </c>
       <c r="P22" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>기타금융</t>
         </is>
       </c>
       <c r="Q22" s="61" t="n">
@@ -8627,10 +8917,10 @@
       </c>
       <c r="C23" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
-        </is>
-      </c>
-      <c r="D23" s="45" t="n">
+          <t>기타금융</t>
+        </is>
+      </c>
+      <c r="D23" s="46" t="n">
         <v>5388</v>
       </c>
       <c r="E23" s="30" t="n">
@@ -8647,7 +8937,7 @@
         </is>
       </c>
       <c r="H23" s="61" t="n">
-        <v>-3793</v>
+        <v>-4632</v>
       </c>
       <c r="J23" s="30" t="n">
         <v>4</v>
@@ -8659,10 +8949,10 @@
       </c>
       <c r="L23" s="35" t="inlineStr">
         <is>
-          <t>제약</t>
-        </is>
-      </c>
-      <c r="M23" s="45" t="n">
+          <t>일반서비스</t>
+        </is>
+      </c>
+      <c r="M23" s="46" t="n">
         <v>3760</v>
       </c>
       <c r="N23" s="30" t="n">
@@ -8696,8 +8986,8 @@
           <t>화학</t>
         </is>
       </c>
-      <c r="D24" s="45" t="n">
-        <v>4583</v>
+      <c r="D24" s="46" t="n">
+        <v>4905</v>
       </c>
       <c r="E24" s="30" t="n">
         <v>5</v>
@@ -8713,7 +9003,7 @@
         </is>
       </c>
       <c r="H24" s="61" t="n">
-        <v>-3596</v>
+        <v>-3841</v>
       </c>
       <c r="J24" s="30" t="n">
         <v>5</v>
@@ -8728,7 +9018,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M24" s="45" t="n">
+      <c r="M24" s="46" t="n">
         <v>3491</v>
       </c>
       <c r="N24" s="30" t="n">
@@ -8762,8 +9052,8 @@
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="D25" s="45" t="n">
-        <v>3592</v>
+      <c r="D25" s="46" t="n">
+        <v>3636</v>
       </c>
       <c r="E25" s="30" t="n">
         <v>6</v>
@@ -8775,7 +9065,7 @@
       </c>
       <c r="G25" s="35" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>일반서비스</t>
         </is>
       </c>
       <c r="H25" s="61" t="n">
@@ -8794,7 +9084,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M25" s="45" t="n">
+      <c r="M25" s="46" t="n">
         <v>2488</v>
       </c>
       <c r="N25" s="30" t="n">
@@ -8820,16 +9110,16 @@
       </c>
       <c r="B26" s="31" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="C26" s="35" t="inlineStr">
         <is>
-          <t>기계·장비</t>
-        </is>
-      </c>
-      <c r="D26" s="45" t="n">
-        <v>2225</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D26" s="46" t="n">
+        <v>2365</v>
       </c>
       <c r="E26" s="30" t="n">
         <v>7</v>
@@ -8845,7 +9135,7 @@
         </is>
       </c>
       <c r="H26" s="61" t="n">
-        <v>-2546</v>
+        <v>-2627</v>
       </c>
       <c r="J26" s="30" t="n">
         <v>7</v>
@@ -8860,7 +9150,7 @@
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="M26" s="45" t="n">
+      <c r="M26" s="46" t="n">
         <v>2207</v>
       </c>
       <c r="N26" s="30" t="n">
@@ -8886,16 +9176,16 @@
       </c>
       <c r="B27" s="31" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="C27" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="D27" s="45" t="n">
-        <v>1631</v>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="D27" s="46" t="n">
+        <v>2225</v>
       </c>
       <c r="E27" s="30" t="n">
         <v>8</v>
@@ -8911,7 +9201,7 @@
         </is>
       </c>
       <c r="H27" s="61" t="n">
-        <v>-2248</v>
+        <v>-2384</v>
       </c>
       <c r="J27" s="30" t="n">
         <v>8</v>
@@ -8926,7 +9216,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M27" s="45" t="n">
+      <c r="M27" s="46" t="n">
         <v>1788</v>
       </c>
       <c r="N27" s="30" t="n">
@@ -8960,7 +9250,7 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D28" s="45" t="n">
+      <c r="D28" s="46" t="n">
         <v>1597</v>
       </c>
       <c r="E28" s="30" t="n">
@@ -8992,7 +9282,7 @@
           <t>화학</t>
         </is>
       </c>
-      <c r="M28" s="45" t="n">
+      <c r="M28" s="46" t="n">
         <v>1669</v>
       </c>
       <c r="N28" s="30" t="n">
@@ -9018,32 +9308,32 @@
       </c>
       <c r="B29" s="31" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="C29" s="35" t="inlineStr">
         <is>
-          <t>기계·장비</t>
-        </is>
-      </c>
-      <c r="D29" s="45" t="n">
-        <v>1272</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D29" s="46" t="n">
+        <v>1510</v>
       </c>
       <c r="E29" s="30" t="n">
         <v>10</v>
       </c>
       <c r="F29" s="31" t="inlineStr">
         <is>
-          <t>에이피알</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="G29" s="35" t="inlineStr">
         <is>
-          <t>화학</t>
+          <t>건설</t>
         </is>
       </c>
       <c r="H29" s="61" t="n">
-        <v>-1702</v>
+        <v>-1765</v>
       </c>
       <c r="J29" s="30" t="n">
         <v>10</v>
@@ -9055,10 +9345,10 @@
       </c>
       <c r="L29" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
-        </is>
-      </c>
-      <c r="M29" s="45" t="n">
+          <t>기타금융</t>
+        </is>
+      </c>
+      <c r="M29" s="46" t="n">
         <v>1446</v>
       </c>
       <c r="N29" s="30" t="n">
@@ -9219,7 +9509,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D34" s="45" t="n">
+      <c r="D34" s="46" t="n">
         <v>40740</v>
       </c>
       <c r="E34" s="30" t="n">
@@ -9232,7 +9522,7 @@
       </c>
       <c r="G34" s="35" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>일반서비스</t>
         </is>
       </c>
       <c r="H34" s="61" t="n">
@@ -9251,7 +9541,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M34" s="45" t="n">
+      <c r="M34" s="46" t="n">
         <v>3202</v>
       </c>
       <c r="N34" s="30" t="n">
@@ -9285,7 +9575,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D35" s="45" t="n">
+      <c r="D35" s="46" t="n">
         <v>10869</v>
       </c>
       <c r="E35" s="30" t="n">
@@ -9298,7 +9588,7 @@
       </c>
       <c r="G35" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>기타금융</t>
         </is>
       </c>
       <c r="H35" s="61" t="n">
@@ -9317,7 +9607,7 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M35" s="45" t="n">
+      <c r="M35" s="46" t="n">
         <v>3178</v>
       </c>
       <c r="N35" s="30" t="n">
@@ -9351,7 +9641,7 @@
           <t>유통</t>
         </is>
       </c>
-      <c r="D36" s="45" t="n">
+      <c r="D36" s="46" t="n">
         <v>9362</v>
       </c>
       <c r="E36" s="30" t="n">
@@ -9383,7 +9673,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M36" s="45" t="n">
+      <c r="M36" s="46" t="n">
         <v>3032</v>
       </c>
       <c r="N36" s="30" t="n">
@@ -9414,10 +9704,10 @@
       </c>
       <c r="C37" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
-        </is>
-      </c>
-      <c r="D37" s="45" t="n">
+          <t>기타금융</t>
+        </is>
+      </c>
+      <c r="D37" s="46" t="n">
         <v>2038</v>
       </c>
       <c r="E37" s="30" t="n">
@@ -9449,7 +9739,7 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M37" s="45" t="n">
+      <c r="M37" s="46" t="n">
         <v>2016</v>
       </c>
       <c r="N37" s="30" t="n">
@@ -9483,7 +9773,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D38" s="45" t="n">
+      <c r="D38" s="46" t="n">
         <v>844</v>
       </c>
       <c r="E38" s="30" t="n">
@@ -9515,7 +9805,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M38" s="45" t="n">
+      <c r="M38" s="46" t="n">
         <v>1543</v>
       </c>
       <c r="N38" s="30" t="n">
@@ -9549,7 +9839,7 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="D39" s="45" t="n">
+      <c r="D39" s="46" t="n">
         <v>295</v>
       </c>
       <c r="E39" s="30" t="n">
@@ -9581,7 +9871,7 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M39" s="45" t="n">
+      <c r="M39" s="46" t="n">
         <v>1527</v>
       </c>
       <c r="N39" s="30" t="n">
@@ -9615,7 +9905,7 @@
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="D40" s="45" t="n">
+      <c r="D40" s="46" t="n">
         <v>276</v>
       </c>
       <c r="E40" s="30" t="n">
@@ -9647,7 +9937,7 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M40" s="45" t="n">
+      <c r="M40" s="46" t="n">
         <v>1524</v>
       </c>
       <c r="N40" s="30" t="n">
@@ -9660,7 +9950,7 @@
       </c>
       <c r="P40" s="35" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>일반서비스</t>
         </is>
       </c>
       <c r="Q40" s="61" t="n">
@@ -9678,10 +9968,10 @@
       </c>
       <c r="C41" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
-        </is>
-      </c>
-      <c r="D41" s="45" t="n">
+          <t>기타금융</t>
+        </is>
+      </c>
+      <c r="D41" s="46" t="n">
         <v>257</v>
       </c>
       <c r="E41" s="30" t="n">
@@ -9713,7 +10003,7 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M41" s="45" t="n">
+      <c r="M41" s="46" t="n">
         <v>1366</v>
       </c>
       <c r="N41" s="30" t="n">
@@ -9744,10 +10034,10 @@
       </c>
       <c r="C42" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
-        </is>
-      </c>
-      <c r="D42" s="45" t="n">
+          <t>기타금융</t>
+        </is>
+      </c>
+      <c r="D42" s="46" t="n">
         <v>235</v>
       </c>
       <c r="E42" s="30" t="n">
@@ -9779,7 +10069,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M42" s="45" t="n">
+      <c r="M42" s="46" t="n">
         <v>1222</v>
       </c>
       <c r="N42" s="30" t="n">
@@ -9810,10 +10100,10 @@
       </c>
       <c r="C43" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
-        </is>
-      </c>
-      <c r="D43" s="45" t="n">
+          <t>기타금융</t>
+        </is>
+      </c>
+      <c r="D43" s="46" t="n">
         <v>212</v>
       </c>
       <c r="E43" s="30" t="n">
@@ -9845,7 +10135,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M43" s="45" t="n">
+      <c r="M43" s="46" t="n">
         <v>1208</v>
       </c>
       <c r="N43" s="30" t="n">
@@ -9998,16 +10288,16 @@
       </c>
       <c r="B48" s="31" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C48" s="35" t="inlineStr">
         <is>
-          <t>화학</t>
-        </is>
-      </c>
-      <c r="D48" s="45" t="n">
-        <v>1272</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D48" s="46" t="n">
+        <v>1307</v>
       </c>
       <c r="E48" s="30" t="n">
         <v>1</v>
@@ -10023,7 +10313,7 @@
         </is>
       </c>
       <c r="H48" s="61" t="n">
-        <v>-2171</v>
+        <v>-2253</v>
       </c>
       <c r="J48" s="30" t="n">
         <v>1</v>
@@ -10035,10 +10325,10 @@
       </c>
       <c r="L48" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
-        </is>
-      </c>
-      <c r="M48" s="45" t="n">
+          <t>기타금융</t>
+        </is>
+      </c>
+      <c r="M48" s="46" t="n">
         <v>497</v>
       </c>
       <c r="N48" s="30" t="n">
@@ -10064,16 +10354,16 @@
       </c>
       <c r="B49" s="31" t="inlineStr">
         <is>
-          <t>두산</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C49" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="D49" s="45" t="n">
-        <v>1020</v>
+          <t>화학</t>
+        </is>
+      </c>
+      <c r="D49" s="46" t="n">
+        <v>1302</v>
       </c>
       <c r="E49" s="30" t="n">
         <v>2</v>
@@ -10085,11 +10375,11 @@
       </c>
       <c r="G49" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>기타금융</t>
         </is>
       </c>
       <c r="H49" s="61" t="n">
-        <v>-2064</v>
+        <v>-1993</v>
       </c>
       <c r="J49" s="30" t="n">
         <v>2</v>
@@ -10104,7 +10394,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M49" s="45" t="n">
+      <c r="M49" s="46" t="n">
         <v>440</v>
       </c>
       <c r="N49" s="30" t="n">
@@ -10130,16 +10420,16 @@
       </c>
       <c r="B50" s="31" t="inlineStr">
         <is>
-          <t>LG화학</t>
+          <t>두산</t>
         </is>
       </c>
       <c r="C50" s="35" t="inlineStr">
         <is>
-          <t>화학</t>
-        </is>
-      </c>
-      <c r="D50" s="45" t="n">
-        <v>773</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D50" s="46" t="n">
+        <v>1020</v>
       </c>
       <c r="E50" s="30" t="n">
         <v>3</v>
@@ -10155,7 +10445,7 @@
         </is>
       </c>
       <c r="H50" s="61" t="n">
-        <v>-1542</v>
+        <v>-1564</v>
       </c>
       <c r="J50" s="30" t="n">
         <v>3</v>
@@ -10170,7 +10460,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M50" s="45" t="n">
+      <c r="M50" s="46" t="n">
         <v>360</v>
       </c>
       <c r="N50" s="30" t="n">
@@ -10196,32 +10486,32 @@
       </c>
       <c r="B51" s="31" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>LG화학</t>
         </is>
       </c>
       <c r="C51" s="35" t="inlineStr">
         <is>
-          <t>기계·장비</t>
-        </is>
-      </c>
-      <c r="D51" s="45" t="n">
-        <v>612</v>
+          <t>화학</t>
+        </is>
+      </c>
+      <c r="D51" s="46" t="n">
+        <v>773</v>
       </c>
       <c r="E51" s="30" t="n">
         <v>4</v>
       </c>
       <c r="F51" s="31" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>NAVER</t>
         </is>
       </c>
       <c r="G51" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>IT 서비스</t>
         </is>
       </c>
       <c r="H51" s="61" t="n">
-        <v>-1443</v>
+        <v>-1452</v>
       </c>
       <c r="J51" s="30" t="n">
         <v>4</v>
@@ -10236,7 +10526,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M51" s="45" t="n">
+      <c r="M51" s="46" t="n">
         <v>235</v>
       </c>
       <c r="N51" s="30" t="n">
@@ -10262,32 +10552,32 @@
       </c>
       <c r="B52" s="31" t="inlineStr">
         <is>
-          <t>메리츠금융지주</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C52" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
-        </is>
-      </c>
-      <c r="D52" s="45" t="n">
-        <v>610</v>
+          <t>운송·창고</t>
+        </is>
+      </c>
+      <c r="D52" s="46" t="n">
+        <v>614</v>
       </c>
       <c r="E52" s="30" t="n">
         <v>5</v>
       </c>
       <c r="F52" s="31" t="inlineStr">
         <is>
-          <t>NAVER</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="G52" s="35" t="inlineStr">
         <is>
-          <t>IT 서비스</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="H52" s="61" t="n">
-        <v>-1320</v>
+        <v>-1343</v>
       </c>
       <c r="J52" s="30" t="n">
         <v>5</v>
@@ -10302,7 +10592,7 @@
           <t>화학</t>
         </is>
       </c>
-      <c r="M52" s="45" t="n">
+      <c r="M52" s="46" t="n">
         <v>195</v>
       </c>
       <c r="N52" s="30" t="n">
@@ -10315,7 +10605,7 @@
       </c>
       <c r="P52" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>기타금융</t>
         </is>
       </c>
       <c r="Q52" s="61" t="n">
@@ -10328,23 +10618,23 @@
       </c>
       <c r="B53" s="31" t="inlineStr">
         <is>
-          <t>포스코인터내셔널</t>
+          <t>메리츠금융지주</t>
         </is>
       </c>
       <c r="C53" s="35" t="inlineStr">
         <is>
-          <t>유통</t>
-        </is>
-      </c>
-      <c r="D53" s="45" t="n">
-        <v>605</v>
+          <t>기타금융</t>
+        </is>
+      </c>
+      <c r="D53" s="46" t="n">
+        <v>610</v>
       </c>
       <c r="E53" s="30" t="n">
         <v>6</v>
       </c>
       <c r="F53" s="31" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="G53" s="35" t="inlineStr">
@@ -10353,7 +10643,7 @@
         </is>
       </c>
       <c r="H53" s="61" t="n">
-        <v>-1043</v>
+        <v>-1239</v>
       </c>
       <c r="J53" s="30" t="n">
         <v>6</v>
@@ -10368,7 +10658,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M53" s="45" t="n">
+      <c r="M53" s="46" t="n">
         <v>127</v>
       </c>
       <c r="N53" s="30" t="n">
@@ -10388,7 +10678,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" ht="31" customHeight="1" s="15">
       <c r="A54" s="30" t="n">
         <v>7</v>
       </c>
@@ -10402,7 +10692,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D54" s="45" t="n">
+      <c r="D54" s="46" t="n">
         <v>588</v>
       </c>
       <c r="E54" s="30" t="n">
@@ -10410,16 +10700,16 @@
       </c>
       <c r="F54" s="31" t="inlineStr">
         <is>
-          <t>삼성전기</t>
-        </is>
-      </c>
-      <c r="G54" s="35" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
+          <t>기아</t>
+        </is>
+      </c>
+      <c r="G54" s="62" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
         </is>
       </c>
       <c r="H54" s="61" t="n">
-        <v>-914</v>
+        <v>-910</v>
       </c>
       <c r="J54" s="30" t="n">
         <v>7</v>
@@ -10431,10 +10721,10 @@
       </c>
       <c r="L54" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
-        </is>
-      </c>
-      <c r="M54" s="45" t="n">
+          <t>기타금융</t>
+        </is>
+      </c>
+      <c r="M54" s="46" t="n">
         <v>92</v>
       </c>
       <c r="N54" s="30" t="n">
@@ -10447,45 +10737,45 @@
       </c>
       <c r="P54" s="35" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>일반서비스</t>
         </is>
       </c>
       <c r="Q54" s="61" t="n">
         <v>-96</v>
       </c>
     </row>
-    <row r="55" ht="31" customHeight="1" s="15">
+    <row r="55">
       <c r="A55" s="30" t="n">
         <v>8</v>
       </c>
       <c r="B55" s="31" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="C55" s="35" t="inlineStr">
         <is>
-          <t>운송·창고</t>
-        </is>
-      </c>
-      <c r="D55" s="45" t="n">
-        <v>584</v>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="D55" s="46" t="n">
+        <v>575</v>
       </c>
       <c r="E55" s="30" t="n">
         <v>8</v>
       </c>
       <c r="F55" s="31" t="inlineStr">
         <is>
-          <t>기아</t>
-        </is>
-      </c>
-      <c r="G55" s="62" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
+          <t>삼성전기</t>
+        </is>
+      </c>
+      <c r="G55" s="35" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="H55" s="61" t="n">
-        <v>-898</v>
+        <v>-839</v>
       </c>
       <c r="J55" s="30" t="n">
         <v>8</v>
@@ -10500,7 +10790,7 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M55" s="45" t="n">
+      <c r="M55" s="46" t="n">
         <v>86</v>
       </c>
       <c r="N55" s="30" t="n">
@@ -10526,16 +10816,16 @@
       </c>
       <c r="B56" s="31" t="inlineStr">
         <is>
-          <t>삼성화재</t>
+          <t>포스코인터내셔널</t>
         </is>
       </c>
       <c r="C56" s="35" t="inlineStr">
         <is>
-          <t>보험</t>
-        </is>
-      </c>
-      <c r="D56" s="45" t="n">
-        <v>563</v>
+          <t>유통</t>
+        </is>
+      </c>
+      <c r="D56" s="46" t="n">
+        <v>569</v>
       </c>
       <c r="E56" s="30" t="n">
         <v>9</v>
@@ -10551,7 +10841,7 @@
         </is>
       </c>
       <c r="H56" s="61" t="n">
-        <v>-727</v>
+        <v>-699</v>
       </c>
       <c r="J56" s="30" t="n">
         <v>9</v>
@@ -10566,7 +10856,7 @@
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="M56" s="45" t="n">
+      <c r="M56" s="46" t="n">
         <v>68</v>
       </c>
       <c r="N56" s="30" t="n">
@@ -10579,7 +10869,7 @@
       </c>
       <c r="P56" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>기타금융</t>
         </is>
       </c>
       <c r="Q56" s="61" t="n">
@@ -10592,16 +10882,16 @@
       </c>
       <c r="B57" s="31" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>삼성화재</t>
         </is>
       </c>
       <c r="C57" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="D57" s="45" t="n">
-        <v>554</v>
+          <t>보험</t>
+        </is>
+      </c>
+      <c r="D57" s="46" t="n">
+        <v>563</v>
       </c>
       <c r="E57" s="30" t="n">
         <v>10</v>
@@ -10632,7 +10922,7 @@
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="M57" s="45" t="n">
+      <c r="M57" s="46" t="n">
         <v>64</v>
       </c>
       <c r="N57" s="30" t="n">
@@ -10733,7 +11023,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D62" s="45" t="n">
+      <c r="D62" s="46" t="n">
         <v>176352</v>
       </c>
       <c r="E62" s="30" t="n">
@@ -10767,7 +11057,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D63" s="45" t="n">
+      <c r="D63" s="46" t="n">
         <v>80613</v>
       </c>
       <c r="E63" s="30" t="n">
@@ -10780,7 +11070,7 @@
       </c>
       <c r="G63" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>기타금융</t>
         </is>
       </c>
       <c r="H63" s="61" t="n">
@@ -10801,7 +11091,7 @@
           <t>제약</t>
         </is>
       </c>
-      <c r="D64" s="45" t="n">
+      <c r="D64" s="46" t="n">
         <v>654</v>
       </c>
       <c r="E64" s="30" t="n">
@@ -10835,7 +11125,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D65" s="45" t="n">
+      <c r="D65" s="46" t="n">
         <v>640</v>
       </c>
       <c r="E65" s="30" t="n">
@@ -10848,7 +11138,7 @@
       </c>
       <c r="G65" s="35" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>일반서비스</t>
         </is>
       </c>
       <c r="H65" s="61" t="n">
@@ -10866,10 +11156,10 @@
       </c>
       <c r="C66" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
-        </is>
-      </c>
-      <c r="D66" s="45" t="n">
+          <t>기타금융</t>
+        </is>
+      </c>
+      <c r="D66" s="46" t="n">
         <v>596</v>
       </c>
       <c r="E66" s="30" t="n">
@@ -10882,7 +11172,7 @@
       </c>
       <c r="G66" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>기타금융</t>
         </is>
       </c>
       <c r="H66" s="61" t="n">
@@ -10903,7 +11193,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D67" s="45" t="n">
+      <c r="D67" s="46" t="n">
         <v>485</v>
       </c>
       <c r="E67" s="30" t="n">
@@ -10937,7 +11227,7 @@
           <t>금속</t>
         </is>
       </c>
-      <c r="D68" s="45" t="n">
+      <c r="D68" s="46" t="n">
         <v>285</v>
       </c>
       <c r="E68" s="30" t="n">
@@ -10950,7 +11240,7 @@
       </c>
       <c r="G68" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>기타금융</t>
         </is>
       </c>
       <c r="H68" s="61" t="n">
@@ -10971,7 +11261,7 @@
           <t>유통</t>
         </is>
       </c>
-      <c r="D69" s="45" t="n">
+      <c r="D69" s="46" t="n">
         <v>213</v>
       </c>
       <c r="E69" s="30" t="n">
@@ -10984,7 +11274,7 @@
       </c>
       <c r="G69" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>기타금융</t>
         </is>
       </c>
       <c r="H69" s="61" t="n">
@@ -11005,7 +11295,7 @@
           <t>건설</t>
         </is>
       </c>
-      <c r="D70" s="45" t="n">
+      <c r="D70" s="46" t="n">
         <v>211</v>
       </c>
       <c r="E70" s="30" t="n">
@@ -11039,7 +11329,7 @@
           <t>유통</t>
         </is>
       </c>
-      <c r="D71" s="45" t="n">
+      <c r="D71" s="46" t="n">
         <v>182</v>
       </c>
       <c r="E71" s="30" t="n">
@@ -11156,7 +11446,7 @@
       </c>
       <c r="Q1" s="25" t="inlineStr">
         <is>
-          <t>2026-09-01 ~ 2026-09-23</t>
+          <t>2026-09-01 ~ 2026-09-24</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11570,7 @@
         </is>
       </c>
       <c r="D5" s="64" t="n">
-        <v>62971</v>
+        <v>62972</v>
       </c>
       <c r="E5" s="65" t="n">
         <v>0.47</v>
@@ -11298,14 +11588,14 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J5" s="45" t="n">
-        <v>12856.3</v>
+      <c r="J5" s="46" t="n">
+        <v>16821.2</v>
       </c>
       <c r="K5" s="66" t="n">
-        <v>242446.3</v>
+        <v>246411.2</v>
       </c>
       <c r="L5" s="65" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="N5" s="30" t="n">
         <v>1</v>
@@ -11321,13 +11611,13 @@
         </is>
       </c>
       <c r="Q5" s="61" t="n">
-        <v>-5780.4</v>
+        <v>-5725.9</v>
       </c>
       <c r="R5" s="66" t="n">
-        <v>7385.1</v>
+        <v>7439.6</v>
       </c>
       <c r="S5" s="65" t="n">
-        <v>5.76</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="6">
@@ -11355,40 +11645,44 @@
       </c>
       <c r="H6" s="31" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
-        </is>
-      </c>
-      <c r="I6" s="35" t="inlineStr"/>
-      <c r="J6" s="45" t="n">
-        <v>9173.700000000001</v>
+          <t>한미반도체</t>
+        </is>
+      </c>
+      <c r="I6" s="35" t="inlineStr">
+        <is>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="J6" s="46" t="n">
+        <v>9063.1</v>
       </c>
       <c r="K6" s="66" t="n">
-        <v>30680.8</v>
+        <v>49629.7</v>
       </c>
       <c r="L6" s="65" t="n">
-        <v>1.81</v>
+        <v>21.7</v>
       </c>
       <c r="N6" s="30" t="n">
         <v>2</v>
       </c>
       <c r="O6" s="31" t="inlineStr">
         <is>
-          <t>에이피알</t>
+          <t>삼성바이오로직스</t>
         </is>
       </c>
       <c r="P6" s="35" t="inlineStr">
         <is>
-          <t>화학</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="Q6" s="61" t="n">
-        <v>-4363.9</v>
+        <v>-4207</v>
       </c>
       <c r="R6" s="66" t="n">
-        <v>13632.5</v>
+        <v>9506.1</v>
       </c>
       <c r="S6" s="65" t="n">
-        <v>10.07</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="7">
@@ -11416,44 +11710,44 @@
       </c>
       <c r="H7" s="31" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="I7" s="35" t="inlineStr">
         <is>
-          <t>기계·장비</t>
-        </is>
-      </c>
-      <c r="J7" s="45" t="n">
-        <v>8673.6</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="J7" s="46" t="n">
+        <v>7964.7</v>
       </c>
       <c r="K7" s="66" t="n">
-        <v>49240.2</v>
+        <v>204586.6</v>
       </c>
       <c r="L7" s="65" t="n">
-        <v>21.53</v>
+        <v>1.52</v>
       </c>
       <c r="N7" s="30" t="n">
         <v>3</v>
       </c>
       <c r="O7" s="31" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>에이피알</t>
         </is>
       </c>
       <c r="P7" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>화학</t>
         </is>
       </c>
       <c r="Q7" s="61" t="n">
-        <v>-4262.3</v>
+        <v>-4119.7</v>
       </c>
       <c r="R7" s="66" t="n">
-        <v>36532.4</v>
+        <v>13876.7</v>
       </c>
       <c r="S7" s="65" t="n">
-        <v>3.29</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="8">
@@ -11481,44 +11775,40 @@
       </c>
       <c r="H8" s="31" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
-        </is>
-      </c>
-      <c r="I8" s="35" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="J8" s="45" t="n">
-        <v>5990.1</v>
+          <t>삼성전자우</t>
+        </is>
+      </c>
+      <c r="I8" s="35" t="inlineStr"/>
+      <c r="J8" s="46" t="n">
+        <v>7025</v>
       </c>
       <c r="K8" s="66" t="n">
-        <v>202612</v>
+        <v>28532.1</v>
       </c>
       <c r="L8" s="65" t="n">
-        <v>1.51</v>
+        <v>1.68</v>
       </c>
       <c r="N8" s="30" t="n">
         <v>4</v>
       </c>
       <c r="O8" s="31" t="inlineStr">
         <is>
-          <t>삼성바이오로직스</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="P8" s="35" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="Q8" s="61" t="n">
-        <v>-4029.6</v>
+        <v>-3756.8</v>
       </c>
       <c r="R8" s="66" t="n">
-        <v>9683.5</v>
+        <v>37037.9</v>
       </c>
       <c r="S8" s="65" t="n">
-        <v>1.5</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="9">
@@ -11532,7 +11822,7 @@
       </c>
       <c r="C9" s="35" t="inlineStr"/>
       <c r="D9" s="64" t="n">
-        <v>5699</v>
+        <v>5703</v>
       </c>
       <c r="E9" s="65" t="n">
         <v>0.78</v>
@@ -11542,22 +11832,22 @@
       </c>
       <c r="H9" s="31" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>DB하이텍</t>
         </is>
       </c>
       <c r="I9" s="35" t="inlineStr">
         <is>
-          <t>일반서비스</t>
-        </is>
-      </c>
-      <c r="J9" s="45" t="n">
-        <v>2828.2</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="J9" s="46" t="n">
+        <v>2631.2</v>
       </c>
       <c r="K9" s="66" t="n">
-        <v>5673.4</v>
+        <v>7085.8</v>
       </c>
       <c r="L9" s="65" t="n">
-        <v>10.75</v>
+        <v>12.46</v>
       </c>
       <c r="N9" s="30" t="n">
         <v>5</v>
@@ -11573,13 +11863,13 @@
         </is>
       </c>
       <c r="Q9" s="61" t="n">
-        <v>-3542.3</v>
+        <v>-3676.4</v>
       </c>
       <c r="R9" s="66" t="n">
-        <v>4100.4</v>
+        <v>3966.3</v>
       </c>
       <c r="S9" s="65" t="n">
-        <v>9.91</v>
+        <v>9.59</v>
       </c>
     </row>
     <row r="10">
@@ -11597,54 +11887,54 @@
         </is>
       </c>
       <c r="D10" s="64" t="n">
-        <v>4212</v>
+        <v>4612</v>
       </c>
       <c r="E10" s="65" t="n">
-        <v>0.38</v>
+        <v>0.42</v>
       </c>
       <c r="G10" s="30" t="n">
         <v>6</v>
       </c>
       <c r="H10" s="31" t="inlineStr">
         <is>
-          <t>DB하이텍</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="I10" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="J10" s="45" t="n">
-        <v>2648.2</v>
+          <t>일반서비스</t>
+        </is>
+      </c>
+      <c r="J10" s="46" t="n">
+        <v>2534.2</v>
       </c>
       <c r="K10" s="66" t="n">
-        <v>7102.8</v>
+        <v>5379.4</v>
       </c>
       <c r="L10" s="65" t="n">
-        <v>12.49</v>
+        <v>10.19</v>
       </c>
       <c r="N10" s="30" t="n">
         <v>6</v>
       </c>
       <c r="O10" s="31" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="P10" s="35" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="Q10" s="61" t="n">
-        <v>-3027.1</v>
+        <v>-3057.3</v>
       </c>
       <c r="R10" s="66" t="n">
-        <v>11598.7</v>
+        <v>13102.5</v>
       </c>
       <c r="S10" s="65" t="n">
-        <v>6.67</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="11">
@@ -11658,7 +11948,7 @@
       </c>
       <c r="C11" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>기타금융</t>
         </is>
       </c>
       <c r="D11" s="64" t="n">
@@ -11672,7 +11962,7 @@
       </c>
       <c r="H11" s="31" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="I11" s="35" t="inlineStr">
@@ -11680,36 +11970,36 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="J11" s="45" t="n">
-        <v>2531.5</v>
+      <c r="J11" s="46" t="n">
+        <v>2406.1</v>
       </c>
       <c r="K11" s="66" t="n">
-        <v>19849.4</v>
+        <v>7817.5</v>
       </c>
       <c r="L11" s="65" t="n">
-        <v>3.58</v>
+        <v>13.4</v>
       </c>
       <c r="N11" s="30" t="n">
         <v>7</v>
       </c>
       <c r="O11" s="31" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="P11" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>일반서비스</t>
         </is>
       </c>
       <c r="Q11" s="61" t="n">
-        <v>-3024.2</v>
+        <v>-3039.8</v>
       </c>
       <c r="R11" s="66" t="n">
-        <v>13135.6</v>
+        <v>11586</v>
       </c>
       <c r="S11" s="65" t="n">
-        <v>3.08</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="12">
@@ -11737,7 +12027,7 @@
       </c>
       <c r="H12" s="31" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="I12" s="35" t="inlineStr">
@@ -11745,36 +12035,36 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="J12" s="45" t="n">
-        <v>2440.9</v>
+      <c r="J12" s="46" t="n">
+        <v>2239.1</v>
       </c>
       <c r="K12" s="66" t="n">
-        <v>7852.3</v>
+        <v>19557</v>
       </c>
       <c r="L12" s="65" t="n">
-        <v>13.46</v>
+        <v>3.53</v>
       </c>
       <c r="N12" s="30" t="n">
         <v>8</v>
       </c>
       <c r="O12" s="31" t="inlineStr">
         <is>
-          <t>삼양식품</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="P12" s="35" t="inlineStr">
         <is>
-          <t>음식료·담배</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="Q12" s="61" t="n">
-        <v>-2946</v>
+        <v>-3016.3</v>
       </c>
       <c r="R12" s="66" t="n">
-        <v>7152.4</v>
+        <v>2538</v>
       </c>
       <c r="S12" s="65" t="n">
-        <v>7.58</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="13">
@@ -11788,7 +12078,7 @@
       </c>
       <c r="C13" s="35" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>일반서비스</t>
         </is>
       </c>
       <c r="D13" s="64" t="n">
@@ -11810,39 +12100,39 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J13" s="45" t="n">
-        <v>1812.9</v>
+      <c r="J13" s="46" t="n">
+        <v>2140.1</v>
       </c>
       <c r="K13" s="66" t="n">
-        <v>9101.200000000001</v>
+        <v>9428.4</v>
       </c>
       <c r="L13" s="65" t="n">
-        <v>3.82</v>
+        <v>3.95</v>
       </c>
       <c r="N13" s="30" t="n">
         <v>9</v>
       </c>
       <c r="O13" s="31" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼양식품</t>
         </is>
       </c>
       <c r="P13" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>음식료·담배</t>
         </is>
       </c>
       <c r="Q13" s="61" t="n">
-        <v>-2934.3</v>
+        <v>-2784.2</v>
       </c>
       <c r="R13" s="66" t="n">
-        <v>2620</v>
+        <v>7314.2</v>
       </c>
       <c r="S13" s="65" t="n">
-        <v>6.19</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>7.76</v>
+      </c>
+    </row>
+    <row r="14" ht="31" customHeight="1" s="15">
       <c r="A14" s="30" t="n">
         <v>10</v>
       </c>
@@ -11867,7 +12157,7 @@
       </c>
       <c r="H14" s="31" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>에코프로비엠</t>
         </is>
       </c>
       <c r="I14" s="35" t="inlineStr">
@@ -11875,36 +12165,36 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J14" s="45" t="n">
-        <v>1774.9</v>
+      <c r="J14" s="46" t="n">
+        <v>1923.3</v>
       </c>
       <c r="K14" s="66" t="n">
-        <v>4095.7</v>
+        <v>13434.9</v>
       </c>
       <c r="L14" s="65" t="n">
-        <v>4.28</v>
+        <v>13.17</v>
       </c>
       <c r="N14" s="30" t="n">
         <v>10</v>
       </c>
       <c r="O14" s="31" t="inlineStr">
         <is>
-          <t>OCI홀딩스</t>
-        </is>
-      </c>
-      <c r="P14" s="35" t="inlineStr">
-        <is>
-          <t>금융</t>
+          <t>한국항공우주</t>
+        </is>
+      </c>
+      <c r="P14" s="62" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
         </is>
       </c>
       <c r="Q14" s="61" t="n">
-        <v>-2056.2</v>
+        <v>-2426.5</v>
       </c>
       <c r="R14" s="66" t="n">
-        <v>2443.5</v>
+        <v>14618.6</v>
       </c>
       <c r="S14" s="65" t="n">
-        <v>6.96</v>
+        <v>11.51</v>
       </c>
     </row>
     <row r="15"/>
@@ -11967,7 +12257,7 @@
       </c>
       <c r="L1" s="25" t="inlineStr">
         <is>
-          <t>2026-09-01 ~ 2026-09-23</t>
+          <t>2026-09-01 ~ 2026-09-24</t>
         </is>
       </c>
     </row>
@@ -12097,13 +12387,13 @@
         <v>18.45</v>
       </c>
       <c r="F5" s="68" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G5" s="68" t="n">
         <v>498</v>
       </c>
       <c r="H5" s="68" t="n">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="I5" s="68" t="n">
         <v>36</v>
@@ -12118,10 +12408,10 @@
         <v>57</v>
       </c>
       <c r="M5" s="69" t="n">
-        <v>-577</v>
+        <v>-574</v>
       </c>
       <c r="N5" s="68" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O5" s="59" t="inlineStr">
         <is>
@@ -12148,31 +12438,31 @@
         <v>8.59</v>
       </c>
       <c r="F6" s="69" t="n">
-        <v>-110773</v>
+        <v>-110600</v>
       </c>
       <c r="G6" s="68" t="n">
-        <v>50032</v>
+        <v>50024</v>
       </c>
       <c r="H6" s="69" t="n">
-        <v>-60741</v>
+        <v>-60576</v>
       </c>
       <c r="I6" s="68" t="n">
-        <v>58309</v>
+        <v>58306</v>
       </c>
       <c r="J6" s="69" t="n">
         <v>-7700</v>
       </c>
       <c r="K6" s="69" t="n">
-        <v>-1108</v>
+        <v>-1114</v>
       </c>
       <c r="L6" s="68" t="n">
         <v>396</v>
       </c>
       <c r="M6" s="69" t="n">
-        <v>-213672</v>
+        <v>-213910</v>
       </c>
       <c r="N6" s="68" t="n">
-        <v>274413</v>
+        <v>274486</v>
       </c>
       <c r="O6" s="30" t="inlineStr"/>
     </row>
@@ -12195,16 +12485,16 @@
         <v>5.11</v>
       </c>
       <c r="F7" s="69" t="n">
-        <v>-126300</v>
+        <v>-126162</v>
       </c>
       <c r="G7" s="68" t="n">
-        <v>43526</v>
+        <v>43530</v>
       </c>
       <c r="H7" s="69" t="n">
-        <v>-82774</v>
+        <v>-82631</v>
       </c>
       <c r="I7" s="68" t="n">
-        <v>55280</v>
+        <v>55285</v>
       </c>
       <c r="J7" s="69" t="n">
         <v>-8633</v>
@@ -12216,10 +12506,10 @@
         <v>285</v>
       </c>
       <c r="M7" s="69" t="n">
-        <v>-193940</v>
+        <v>-194163</v>
       </c>
       <c r="N7" s="68" t="n">
-        <v>276713</v>
+        <v>276795</v>
       </c>
       <c r="O7" s="30" t="inlineStr"/>
     </row>
@@ -12242,13 +12532,13 @@
         <v>1.97</v>
       </c>
       <c r="F8" s="69" t="n">
-        <v>-2847</v>
+        <v>-2839</v>
       </c>
       <c r="G8" s="68" t="n">
         <v>3717</v>
       </c>
       <c r="H8" s="68" t="n">
-        <v>870</v>
+        <v>878</v>
       </c>
       <c r="I8" s="68" t="n">
         <v>2141</v>
@@ -12263,7 +12553,7 @@
         <v>55</v>
       </c>
       <c r="M8" s="68" t="n">
-        <v>890</v>
+        <v>882</v>
       </c>
       <c r="N8" s="69" t="n">
         <v>-1760</v>
@@ -12293,13 +12583,13 @@
         <v>1.47</v>
       </c>
       <c r="F9" s="68" t="n">
-        <v>4607</v>
+        <v>4625</v>
       </c>
       <c r="G9" s="68" t="n">
         <v>7914</v>
       </c>
       <c r="H9" s="68" t="n">
-        <v>12521</v>
+        <v>12539</v>
       </c>
       <c r="I9" s="68" t="n">
         <v>3672</v>
@@ -12314,10 +12604,10 @@
         <v>242</v>
       </c>
       <c r="M9" s="69" t="n">
-        <v>-8441</v>
+        <v>-8458</v>
       </c>
       <c r="N9" s="69" t="n">
-        <v>-4081</v>
+        <v>-4080</v>
       </c>
       <c r="O9" s="59" t="inlineStr">
         <is>
@@ -12344,13 +12634,13 @@
         <v>0.6</v>
       </c>
       <c r="F10" s="69" t="n">
-        <v>-8224</v>
+        <v>-8245</v>
       </c>
       <c r="G10" s="68" t="n">
         <v>4015</v>
       </c>
       <c r="H10" s="69" t="n">
-        <v>-4209</v>
+        <v>-4231</v>
       </c>
       <c r="I10" s="69" t="n">
         <v>-986</v>
@@ -12365,10 +12655,10 @@
         <v>144</v>
       </c>
       <c r="M10" s="68" t="n">
-        <v>4139</v>
+        <v>4157</v>
       </c>
       <c r="N10" s="68" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="O10" s="30" t="inlineStr"/>
     </row>
@@ -12412,7 +12702,7 @@
         <v>-33</v>
       </c>
       <c r="M11" s="69" t="n">
-        <v>-187</v>
+        <v>-186</v>
       </c>
       <c r="N11" s="69" t="n">
         <v>-20</v>
@@ -12438,13 +12728,13 @@
         <v>-0.28</v>
       </c>
       <c r="F12" s="68" t="n">
-        <v>2913</v>
+        <v>2910</v>
       </c>
       <c r="G12" s="68" t="n">
         <v>853</v>
       </c>
       <c r="H12" s="68" t="n">
-        <v>3766</v>
+        <v>3763</v>
       </c>
       <c r="I12" s="69" t="n">
         <v>-298</v>
@@ -12459,7 +12749,7 @@
         <v>39</v>
       </c>
       <c r="M12" s="69" t="n">
-        <v>-3711</v>
+        <v>-3709</v>
       </c>
       <c r="N12" s="69" t="n">
         <v>-54</v>
@@ -12536,13 +12826,13 @@
         <v>-2.24</v>
       </c>
       <c r="F14" s="69" t="n">
-        <v>-2773</v>
+        <v>-2770</v>
       </c>
       <c r="G14" s="68" t="n">
         <v>1219</v>
       </c>
       <c r="H14" s="69" t="n">
-        <v>-1554</v>
+        <v>-1552</v>
       </c>
       <c r="I14" s="68" t="n">
         <v>401</v>
@@ -12557,10 +12847,10 @@
         <v>74</v>
       </c>
       <c r="M14" s="68" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="N14" s="68" t="n">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="O14" s="30" t="inlineStr"/>
     </row>
@@ -12583,13 +12873,13 @@
         <v>-2.9</v>
       </c>
       <c r="F15" s="69" t="n">
-        <v>-3815</v>
+        <v>-3820</v>
       </c>
       <c r="G15" s="68" t="n">
         <v>10794</v>
       </c>
       <c r="H15" s="68" t="n">
-        <v>6979</v>
+        <v>6974</v>
       </c>
       <c r="I15" s="68" t="n">
         <v>9082</v>
@@ -12604,10 +12894,10 @@
         <v>51</v>
       </c>
       <c r="M15" s="68" t="n">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="N15" s="69" t="n">
-        <v>-7430</v>
+        <v>-7431</v>
       </c>
       <c r="O15" s="30" t="inlineStr"/>
     </row>
@@ -12630,13 +12920,13 @@
         <v>-3.05</v>
       </c>
       <c r="F16" s="69" t="n">
-        <v>-2314</v>
+        <v>-2317</v>
       </c>
       <c r="G16" s="68" t="n">
         <v>2310</v>
       </c>
       <c r="H16" s="69" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="I16" s="68" t="n">
         <v>425</v>
@@ -12651,7 +12941,7 @@
         <v>-2</v>
       </c>
       <c r="M16" s="69" t="n">
-        <v>-159</v>
+        <v>-156</v>
       </c>
       <c r="N16" s="68" t="n">
         <v>163</v>
@@ -12724,16 +13014,16 @@
         <v>-4.06</v>
       </c>
       <c r="F18" s="68" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="G18" s="68" t="n">
         <v>1790</v>
       </c>
       <c r="H18" s="68" t="n">
-        <v>2463</v>
+        <v>2464</v>
       </c>
       <c r="I18" s="69" t="n">
-        <v>-1781</v>
+        <v>-1782</v>
       </c>
       <c r="J18" s="68" t="n">
         <v>275</v>
@@ -12777,7 +13067,7 @@
         <v>-850</v>
       </c>
       <c r="H19" s="68" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I19" s="68" t="n">
         <v>289</v>
@@ -12818,13 +13108,13 @@
         <v>-4.59</v>
       </c>
       <c r="F20" s="68" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G20" s="69" t="n">
         <v>-609</v>
       </c>
       <c r="H20" s="69" t="n">
-        <v>-496</v>
+        <v>-495</v>
       </c>
       <c r="I20" s="68" t="n">
         <v>574</v>
@@ -12839,7 +13129,7 @@
         <v>-54</v>
       </c>
       <c r="M20" s="68" t="n">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="N20" s="69" t="n">
         <v>-34</v>
@@ -12865,16 +13155,16 @@
         <v>-4.89</v>
       </c>
       <c r="F21" s="69" t="n">
-        <v>-684</v>
+        <v>-721</v>
       </c>
       <c r="G21" s="69" t="n">
-        <v>-185</v>
+        <v>-147</v>
       </c>
       <c r="H21" s="69" t="n">
         <v>-869</v>
       </c>
       <c r="I21" s="68" t="n">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="J21" s="69" t="n">
         <v>-152</v>
@@ -12886,7 +13176,7 @@
         <v>2</v>
       </c>
       <c r="M21" s="68" t="n">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="N21" s="69" t="n">
         <v>-18</v>
@@ -12916,13 +13206,13 @@
         <v>-5.17</v>
       </c>
       <c r="F22" s="69" t="n">
-        <v>-86</v>
+        <v>-87</v>
       </c>
       <c r="G22" s="69" t="n">
         <v>-26</v>
       </c>
       <c r="H22" s="69" t="n">
-        <v>-112</v>
+        <v>-113</v>
       </c>
       <c r="I22" s="68" t="n">
         <v>60</v>
@@ -12967,13 +13257,13 @@
         <v>-6.73</v>
       </c>
       <c r="F23" s="69" t="n">
-        <v>-2323</v>
+        <v>-2316</v>
       </c>
       <c r="G23" s="68" t="n">
         <v>362</v>
       </c>
       <c r="H23" s="69" t="n">
-        <v>-1961</v>
+        <v>-1954</v>
       </c>
       <c r="I23" s="69" t="n">
         <v>-540</v>
@@ -12988,10 +13278,10 @@
         <v>-11</v>
       </c>
       <c r="M23" s="68" t="n">
-        <v>1122</v>
+        <v>1116</v>
       </c>
       <c r="N23" s="68" t="n">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="O23" s="60" t="inlineStr">
         <is>
@@ -13018,16 +13308,16 @@
         <v>-8.06</v>
       </c>
       <c r="F24" s="69" t="n">
-        <v>-502</v>
+        <v>-510</v>
       </c>
       <c r="G24" s="69" t="n">
-        <v>-2144</v>
+        <v>-2137</v>
       </c>
       <c r="H24" s="69" t="n">
-        <v>-2646</v>
+        <v>-2647</v>
       </c>
       <c r="I24" s="69" t="n">
-        <v>-310</v>
+        <v>-303</v>
       </c>
       <c r="J24" s="69" t="n">
         <v>-990</v>
@@ -13039,7 +13329,7 @@
         <v>-139</v>
       </c>
       <c r="M24" s="68" t="n">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="N24" s="68" t="n">
         <v>1086</v>
@@ -13171,13 +13461,13 @@
         <v>-9.34</v>
       </c>
       <c r="F27" s="69" t="n">
-        <v>-3542</v>
+        <v>-3540</v>
       </c>
       <c r="G27" s="69" t="n">
         <v>-6044</v>
       </c>
       <c r="H27" s="69" t="n">
-        <v>-9586</v>
+        <v>-9584</v>
       </c>
       <c r="I27" s="69" t="n">
         <v>-432</v>
@@ -13192,10 +13482,10 @@
         <v>-302</v>
       </c>
       <c r="M27" s="68" t="n">
-        <v>9479</v>
+        <v>9582</v>
       </c>
       <c r="N27" s="68" t="n">
-        <v>107</v>
+        <v>2</v>
       </c>
       <c r="O27" s="60" t="inlineStr">
         <is>
@@ -13222,13 +13512,13 @@
         <v>-9.73</v>
       </c>
       <c r="F28" s="69" t="n">
-        <v>-5644</v>
+        <v>-5659</v>
       </c>
       <c r="G28" s="69" t="n">
         <v>-8952</v>
       </c>
       <c r="H28" s="69" t="n">
-        <v>-14596</v>
+        <v>-14611</v>
       </c>
       <c r="I28" s="68" t="n">
         <v>381</v>
@@ -13243,10 +13533,10 @@
         <v>-407</v>
       </c>
       <c r="M28" s="68" t="n">
-        <v>14411</v>
+        <v>14421</v>
       </c>
       <c r="N28" s="68" t="n">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="O28" s="60" t="inlineStr">
         <is>
@@ -13286,7 +13576,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7EC0C6BB-2730-42DF-8E8B-F1C5985B11AA}</x14:id>
+          <x14:id>{9E000867-A916-4865-8887-6C923CDB5826}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13300,7 +13590,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{D135F358-E427-4494-B9B1-EDAC701AA7ED}</x14:id>
+          <x14:id>{77DCFCE3-A0D5-471A-9234-988517A198BD}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13314,7 +13604,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{56274B12-1581-4CBB-BE38-318C7B777066}</x14:id>
+          <x14:id>{7B77ED0A-F457-42C8-BAB6-48B37902D852}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13328,7 +13618,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{989BE010-128B-4C89-ACB2-C57FD752383D}</x14:id>
+          <x14:id>{0DAB3FDC-D89B-43EA-9FA6-9F86D998E6CE}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13338,7 +13628,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7EC0C6BB-2730-42DF-8E8B-F1C5985B11AA}">
+          <x14:cfRule type="dataBar" id="{9E000867-A916-4865-8887-6C923CDB5826}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13351,7 +13641,7 @@
           <xm:sqref>B5:B28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{D135F358-E427-4494-B9B1-EDAC701AA7ED}">
+          <x14:cfRule type="dataBar" id="{77DCFCE3-A0D5-471A-9234-988517A198BD}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13364,7 +13654,7 @@
           <xm:sqref>C5:C28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{56274B12-1581-4CBB-BE38-318C7B777066}">
+          <x14:cfRule type="dataBar" id="{7B77ED0A-F457-42C8-BAB6-48B37902D852}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13377,7 +13667,7 @@
           <xm:sqref>D5:D28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{989BE010-128B-4C89-ACB2-C57FD752383D}">
+          <x14:cfRule type="dataBar" id="{0DAB3FDC-D89B-43EA-9FA6-9F86D998E6CE}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/public/monthly_review.xlsx
+++ b/public/monthly_review.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="섹터x수급" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'신고가 근접'!$A$5:$L$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'신고가 근접'!$A$5:$L$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'섹터x수급'!$A$4:$O$28</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -456,26 +456,14 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -483,7 +471,16 @@
     <xf numFmtId="168" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -493,6 +490,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -942,7 +942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K193"/>
+  <dimension ref="A1:K186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.9" customWidth="1" style="15" min="1" max="1"/>
@@ -971,7 +971,7 @@
       </c>
       <c r="I1" s="25" t="inlineStr">
         <is>
-          <t>2026-09-01 ~ 2026-09-24</t>
+          <t>2026-09-01 ~ 2026-09-23</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       </c>
       <c r="I2" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24 16:27 KST</t>
+          <t>2026-09-24 17:09 KST</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4" ht="17.25" customHeight="1" s="15">
+    <row r="4" ht="31" customHeight="1" s="15">
       <c r="A4" s="26" t="inlineStr">
         <is>
           <t>MARKET SIGNAL</t>
@@ -996,7 +996,7 @@
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>9월 국내 증시는 AI 반도체 랠리와 매크로 불확실성 속에서 기관 주도 장세가 펼쳐졌습니다.</t>
+          <t>9월 한국 증시는 AI 반도체 랠리와 인플레이션 공포, 고금리 장기화 우려가 교차하며 극심한 변동성을 보인 한 달이었습니다.</t>
         </is>
       </c>
     </row>
@@ -1092,13 +1092,13 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>-208685</v>
+        <v>-194036</v>
       </c>
       <c r="C8" s="28" t="n">
-        <v>-138654</v>
+        <v>-133712</v>
       </c>
       <c r="D8" s="29" t="n">
-        <v>50235</v>
+        <v>47046</v>
       </c>
       <c r="E8" s="29" t="n">
         <v>0.26</v>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="B9" s="29" t="n">
-        <v>11821</v>
+        <v>11546</v>
       </c>
       <c r="C9" s="28" t="n">
-        <v>-15353</v>
+        <v>-14891</v>
       </c>
       <c r="D9" s="29" t="n">
-        <v>2897</v>
+        <v>2821</v>
       </c>
     </row>
     <row r="10"/>
@@ -1270,11 +1270,11 @@
       </c>
       <c r="C17" s="31" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>산업재</t>
         </is>
       </c>
       <c r="D17" s="34" t="n">
-        <v>-4.49</v>
+        <v>-2.61</v>
       </c>
     </row>
     <row r="18">
@@ -2716,7 +2716,7 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="15" customHeight="1" s="15">
+    <row r="65" ht="31" customHeight="1" s="15">
       <c r="A65" s="31" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="G65" s="17" t="inlineStr">
         <is>
-          <t>지정학적 리스크와 인플레이션 우려로 투자 심리 위축.</t>
+          <t>전 주체 매도세와 지정학적 리스크로 시장 온도 차가 뚜렷했습니다.</t>
         </is>
       </c>
     </row>
@@ -2778,11 +2778,11 @@
       </c>
       <c r="G66" s="17" t="inlineStr">
         <is>
-          <t>외국인·기관 대규모 매도와 CPI 상승으로 지수 급락.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="15" customHeight="1" s="15">
+          <t>물가 상승 우려와 외국인·기관의 대규모 매도로 지수가 급락했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="31" customHeight="1" s="15">
       <c r="A67" s="31" t="inlineStr">
         <is>
           <t>2026-09-03</t>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="G67" s="17" t="inlineStr">
         <is>
-          <t>환율 하락에도 금리 부담 지속, 보험·건설 섹터 강세.</t>
+          <t>보험·건설 섹터 강세에도 전 주체 매도세로 지수 차별화가 나타났습니다.</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="G68" s="17" t="inlineStr">
         <is>
-          <t>외국인·기관 매수세와 원화 강세로 지수 상승.</t>
+          <t>외국인과 기관의 강력한 동반 매수세가 지수 급등을 견인했습니다.</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="G69" s="17" t="inlineStr">
         <is>
-          <t>외국인·기관 매수세와 원화 강세로 KOSPI 급등.</t>
+          <t>외국인과 기관의 대규모 매수세에 힘입어 KOSPI가 4.61% 급등했습니다.</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G70" s="17" t="inlineStr">
         <is>
-          <t>개인 매도세와 금리 상승으로 지수 하락 압박.</t>
+          <t>개인의 대규모 매도세가 지수 하락을 압박하며 지수가 하락했습니다.</t>
         </is>
       </c>
     </row>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="G71" s="17" t="inlineStr">
         <is>
-          <t>기관·외국인 매수세와 원화 강세로 지수 상승.</t>
+          <t>기관의 강한 매수세가 유입되며 KOSPI 7,000선 안착을 시도했습니다.</t>
         </is>
       </c>
     </row>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="G72" s="17" t="inlineStr">
         <is>
-          <t>외국인 매도세와 유가 급등으로 인플레이션 우려.</t>
+          <t>외국인 매도와 기관 매수가 엇갈리며 지수 간 차별화가 나타났습니다.</t>
         </is>
       </c>
     </row>
@@ -3153,7 +3153,7 @@
       </c>
       <c r="G73" s="17" t="inlineStr">
         <is>
-          <t>미국 PPI 상승, 유가 100달러 돌파 등 삼중 악재로 급락.</t>
+          <t>인플레이션 우려와 미국 기술주 투매로 지수가 급락 마감했습니다.</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="G74" s="17" t="inlineStr">
         <is>
-          <t>외국인 대규모 매도세와 AI 속도조절론으로 지수 급락.</t>
+          <t>외국인의 3.3조 원 규모 대규모 매도세가 지수 하락을 주도했습니다.</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="G75" s="17" t="inlineStr">
         <is>
-          <t>외국인·기관 매도세와 환율 상승으로 투자 심리 위축.</t>
+          <t>외국인과 기관의 동반 매도세가 쏟아지며 지수 하방 압력이 커졌습니다.</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="G76" s="17" t="inlineStr">
         <is>
-          <t>기관 매수세에도 대외 불확실성으로 외국인 매도 지속.</t>
+          <t>기관의 대규모 순매수가 지수 방어를 주도하며 상승 마감했습니다.</t>
         </is>
       </c>
     </row>
@@ -3393,7 +3393,7 @@
       </c>
       <c r="G77" s="17" t="inlineStr">
         <is>
-          <t>외국인 매도세와 고유가 우려로 투자 심리 위축.</t>
+          <t>외국인의 2.3조 원 규모 매도세에 눌려 지수 상단이 제한되었습니다.</t>
         </is>
       </c>
     </row>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="G78" s="17" t="inlineStr">
         <is>
-          <t>미국 기술주 강세와 기관·외국인 매수세로 지수 급등.</t>
+          <t>미국 기술주 강세 훈풍과 기관 매수세로 지수가 급등했습니다.</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="G79" s="17" t="inlineStr">
         <is>
-          <t>기관 매수세와 반도체 수출 호조로 KOSPI 7000선 회복.</t>
+          <t>기관의 강한 매수세에 힘입어 KOSPI가 7,000선을 회복했습니다.</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="G80" s="17" t="inlineStr">
         <is>
-          <t>개인 매도에도 외국인 매수세와 환율 하락으로 KOSPI 상승.</t>
+          <t>개인의 대규모 매도세에도 외국인 매수세가 지수를 방어했습니다.</t>
         </is>
       </c>
     </row>
@@ -3669,222 +3669,228 @@
       </c>
       <c r="G81" s="17" t="inlineStr">
         <is>
-          <t>개인·외국인 매도세에도 소비자심리지수 개선으로 지수 방어.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="31" customHeight="1" s="15">
-      <c r="A82" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B82" s="29" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C82" s="31" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00D64545"/>
-              <sz val="10"/>
-            </rPr>
-            <t>311▲</t>
-          </r>
-          <r>
-            <t>/</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="003182F6"/>
-              <sz val="10"/>
-            </rPr>
-            <t>548▼</t>
-          </r>
-        </is>
-      </c>
-      <c r="D82" s="29" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="E82" s="17" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00D64545"/>
-              <sz val="10"/>
-            </rPr>
-            <t>856▲ 상한4</t>
-          </r>
-          <r>
-            <t>/</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="003182F6"/>
-              <sz val="10"/>
-            </rPr>
-            <t>786▼</t>
-          </r>
-        </is>
-      </c>
-      <c r="F82" s="17" t="inlineStr">
-        <is>
-          <t>의료·정밀기기, 전기·전자</t>
-        </is>
-      </c>
-      <c r="G82" s="17" t="inlineStr">
-        <is>
-          <t>외국인 매도세에도 기관 매수세와 금리 하락으로 지수 방어.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83"/>
+          <t>개인과 외국인의 동반 매도세로 지수 상단이 제한되었습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82"/>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>월간 종합 코멘트 — 매크로·수급</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr"/>
+      <c r="D83" s="3" t="inlineStr"/>
+      <c r="E83" s="3" t="inlineStr"/>
+      <c r="F83" s="3" t="inlineStr"/>
+      <c r="G83" s="3" t="inlineStr"/>
+      <c r="H83" s="3" t="inlineStr"/>
+      <c r="I83" s="3" t="inlineStr"/>
+      <c r="J83" s="3" t="inlineStr"/>
+      <c r="K83" s="3" t="inlineStr"/>
+    </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="B84" s="3" t="inlineStr">
-        <is>
-          <t>월간 종합 코멘트 — 매크로·수급</t>
-        </is>
-      </c>
-      <c r="C84" s="3" t="inlineStr"/>
-      <c r="D84" s="3" t="inlineStr"/>
-      <c r="E84" s="3" t="inlineStr"/>
-      <c r="F84" s="3" t="inlineStr"/>
-      <c r="G84" s="3" t="inlineStr"/>
-      <c r="H84" s="3" t="inlineStr"/>
-      <c r="I84" s="3" t="inlineStr"/>
-      <c r="J84" s="3" t="inlineStr"/>
-      <c r="K84" s="3" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="4" t="inlineStr">
+      <c r="A84" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B85" s="4" t="inlineStr">
+      <c r="B84" s="4" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="58" customHeight="1" s="15">
+    <row r="85" ht="31" customHeight="1" s="15">
+      <c r="A85" s="17" t="inlineStr">
+        <is>
+          <t>- 미국 CPI와 PPI가 예상치를 상회하거나 부합하며 인플레이션 압력이 지속되었고, 국내 GDP 성장률 둔화와 고금리 기조가 매크로 부담으로 작용했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="31" customHeight="1" s="15">
       <c r="A86" s="17" t="inlineStr">
         <is>
-          <t>- 월간 매크로 환경은 미국 ISM 제조업 PMI(54.6)가 예상치를 하회하고 국내 소비자물가지수(CPI)가 3.1%로 이전치를 상회하는 등 인플레이션 압력이 지속되었습니다. 미국 중앙은행 기준금리가 4.0%로 인상되고 10년물 국채금리가 5%를 돌파하며 긴축 공포가 시장 변동성을 키웠습니다. 다만, 국내 수출 전년대비 68.7% 급증과 소비자심리지수 106.6으로 개선은 경기 하방 경직성을 확보하는 요인으로 작용했습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="58" customHeight="1" s="15">
+          <t>- 수급 측면에서는 전기·전자 섹터에 기관의 매수세가 집중되었으나, 건설 및 오락·문화 섹터는 외국인과 기관의 동반 이탈로 약세를 보였습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="31" customHeight="1" s="15">
       <c r="A87" s="17" t="inlineStr">
         <is>
-          <t>- 월간 수급 구도는 외국인이 전기·전자(-110,600억)와 제조(-126,162억) 섹터에서 대규모 순매도를 보이며 지수 하방 압력을 가했습니다. 반면 기관은 전기·전자(50,024억)와 제조(43,530억) 섹터에서 순매수를 기록하며 지수 방어에 기여했습니다. 개인은 전기·전자(-213,910억)와 제조(-194,163억) 섹터에서 대규모 순매도를 보이며 차익 실현에 집중했습니다. 의료·정밀기기 섹터는 외국인(73억)과 기관(498억)의 동반 매수세로 월간 18.45% 상승하며 강세를 보였습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="44.5" customHeight="1" s="15">
-      <c r="A88" s="17" t="inlineStr">
-        <is>
-          <t>- 월간 시장은 AI 반도체 랠리와 견조한 수출 데이터가 지수 하단을 지지했으나, 미국발 인플레이션 우려와 고금리 장기화 부담, 그리고 외국인 수급의 변동성이 시장의 상승 탄력을 둔화시키는 양상이었습니다. 특히 건설 섹터는 월간 -2.24% 하락하며 외국인(-2,770억)과 기관(-790억)의 동반 이탈이 두드러졌습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="31" customHeight="1" s="15">
-      <c r="A89" s="17" t="inlineStr">
-        <is>
-          <t>- 종합적으로 매크로 불확실성 속에서도 AI 인프라 수요 기대감과 실적 모멘텀이 확실한 반도체 및 일부 기술주 중심의 차별화 장세가 지속될 것으로 예상됩니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90"/>
+          <t>- AI 반도체와 HBM 관련 실적 모멘텀이 시장 하단을 지지하고 있으나, 외국인 수급 변동성과 매크로 불확실성이 상단을 제한하는 양상입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88"/>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>투자자 합산 순매수 상위/하위</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr"/>
+      <c r="D89" s="3" t="inlineStr"/>
+      <c r="E89" s="3" t="inlineStr"/>
+      <c r="F89" s="3" t="inlineStr"/>
+      <c r="G89" s="3" t="inlineStr"/>
+      <c r="H89" s="3" t="inlineStr"/>
+      <c r="I89" s="3" t="inlineStr"/>
+      <c r="J89" s="18" t="inlineStr">
+        <is>
+          <t>외인+기관계, 억원</t>
+        </is>
+      </c>
+      <c r="K89" s="3" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>순위</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>섹터명</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>합산</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>외인</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>기관</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>개인</t>
+        </is>
+      </c>
+      <c r="I90" s="4" t="inlineStr">
+        <is>
+          <t>공매도</t>
+        </is>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>대차잔고</t>
+        </is>
+      </c>
+      <c r="K90" s="4" t="inlineStr">
+        <is>
+          <t>대차증감</t>
+        </is>
+      </c>
+    </row>
     <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
-      </c>
-      <c r="B91" s="3" t="inlineStr">
-        <is>
-          <t>투자자 합산 순매수 상위/하위</t>
-        </is>
-      </c>
-      <c r="C91" s="3" t="inlineStr"/>
-      <c r="D91" s="3" t="inlineStr"/>
-      <c r="E91" s="3" t="inlineStr"/>
-      <c r="F91" s="3" t="inlineStr"/>
-      <c r="G91" s="3" t="inlineStr"/>
-      <c r="H91" s="3" t="inlineStr"/>
-      <c r="I91" s="3" t="inlineStr"/>
-      <c r="J91" s="18" t="inlineStr">
-        <is>
-          <t>외인+기관계, 억원</t>
-        </is>
-      </c>
-      <c r="K91" s="3" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="4" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="inlineStr">
-        <is>
-          <t>순위</t>
-        </is>
-      </c>
-      <c r="C92" s="4" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="D92" s="4" t="inlineStr">
-        <is>
-          <t>섹터명</t>
-        </is>
-      </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>합산</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>외인</t>
-        </is>
-      </c>
-      <c r="G92" s="4" t="inlineStr">
-        <is>
-          <t>기관</t>
-        </is>
-      </c>
-      <c r="H92" s="4" t="inlineStr">
-        <is>
-          <t>개인</t>
-        </is>
-      </c>
-      <c r="I92" s="4" t="inlineStr">
-        <is>
-          <t>공매도</t>
-        </is>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>대차잔고</t>
-        </is>
-      </c>
-      <c r="K92" s="4" t="inlineStr">
-        <is>
-          <t>대차증감</t>
-        </is>
+      <c r="A91" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B91" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C91" s="31" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="D91" s="35" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="E91" s="29" t="n">
+        <v>26933</v>
+      </c>
+      <c r="F91" s="28" t="n">
+        <v>-12432</v>
+      </c>
+      <c r="G91" s="29" t="n">
+        <v>39366</v>
+      </c>
+      <c r="H91" s="28" t="n">
+        <v>-107841</v>
+      </c>
+      <c r="I91" s="31" t="n">
+        <v>34854.2</v>
+      </c>
+      <c r="J91" s="31" t="n">
+        <v>246411.2</v>
+      </c>
+      <c r="K91" s="31" t="n">
+        <v>16821.2</v>
+      </c>
+    </row>
+    <row r="92" ht="31" customHeight="1" s="15">
+      <c r="A92" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B92" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C92" s="17" t="inlineStr">
+        <is>
+          <t>포스코인터내셔널</t>
+        </is>
+      </c>
+      <c r="D92" s="35" t="inlineStr">
+        <is>
+          <t>유통</t>
+        </is>
+      </c>
+      <c r="E92" s="29" t="n">
+        <v>9402</v>
+      </c>
+      <c r="F92" s="28" t="n">
+        <v>-937</v>
+      </c>
+      <c r="G92" s="29" t="n">
+        <v>10339</v>
+      </c>
+      <c r="H92" s="29" t="n">
+        <v>75</v>
+      </c>
+      <c r="I92" s="31" t="n">
+        <v>495.2</v>
+      </c>
+      <c r="J92" s="31" t="n">
+        <v>1675.7</v>
+      </c>
+      <c r="K92" s="31" t="n">
+        <v>-1956</v>
       </c>
     </row>
     <row r="93">
@@ -3894,79 +3900,79 @@
         </is>
       </c>
       <c r="B93" s="31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C93" s="31" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK스퀘어</t>
         </is>
       </c>
       <c r="D93" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>기타금융</t>
         </is>
       </c>
       <c r="E93" s="29" t="n">
-        <v>34714</v>
-      </c>
-      <c r="F93" s="28" t="n">
-        <v>-6914</v>
-      </c>
-      <c r="G93" s="29" t="n">
-        <v>41629</v>
+        <v>6576</v>
+      </c>
+      <c r="F93" s="29" t="n">
+        <v>8390</v>
+      </c>
+      <c r="G93" s="28" t="n">
+        <v>-1814</v>
       </c>
       <c r="H93" s="28" t="n">
-        <v>-107841</v>
+        <v>-6528</v>
       </c>
       <c r="I93" s="31" t="n">
-        <v>34854.2</v>
+        <v>3883.7</v>
       </c>
       <c r="J93" s="31" t="n">
-        <v>246411.2</v>
+        <v>32724.5</v>
       </c>
       <c r="K93" s="31" t="n">
-        <v>16821.2</v>
-      </c>
-    </row>
-    <row r="94" ht="31" customHeight="1" s="15">
+        <v>1832.2</v>
+      </c>
+    </row>
+    <row r="94">
       <c r="A94" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
       <c r="B94" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="C94" s="17" t="inlineStr">
-        <is>
-          <t>포스코인터내셔널</t>
+        <v>4</v>
+      </c>
+      <c r="C94" s="31" t="inlineStr">
+        <is>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="D94" s="35" t="inlineStr">
         <is>
-          <t>유통</t>
+          <t>기타금융</t>
         </is>
       </c>
       <c r="E94" s="29" t="n">
-        <v>9370</v>
-      </c>
-      <c r="F94" s="28" t="n">
-        <v>-933</v>
+        <v>5388</v>
+      </c>
+      <c r="F94" s="29" t="n">
+        <v>4771</v>
       </c>
       <c r="G94" s="29" t="n">
-        <v>10303</v>
-      </c>
-      <c r="H94" s="29" t="n">
-        <v>75</v>
+        <v>617</v>
+      </c>
+      <c r="H94" s="28" t="n">
+        <v>-778</v>
       </c>
       <c r="I94" s="31" t="n">
-        <v>495.2</v>
+        <v>686.4</v>
       </c>
       <c r="J94" s="31" t="n">
-        <v>1675.7</v>
+        <v>4852.5</v>
       </c>
       <c r="K94" s="31" t="n">
-        <v>-1956</v>
+        <v>-301.5</v>
       </c>
     </row>
     <row r="95">
@@ -3976,38 +3982,38 @@
         </is>
       </c>
       <c r="B95" s="31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C95" s="31" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="D95" s="35" t="inlineStr">
         <is>
-          <t>기타금융</t>
+          <t>화학</t>
         </is>
       </c>
       <c r="E95" s="29" t="n">
-        <v>6493</v>
+        <v>4583</v>
       </c>
       <c r="F95" s="29" t="n">
-        <v>8118</v>
-      </c>
-      <c r="G95" s="28" t="n">
-        <v>-1625</v>
+        <v>2752</v>
+      </c>
+      <c r="G95" s="29" t="n">
+        <v>1831</v>
       </c>
       <c r="H95" s="28" t="n">
-        <v>-6528</v>
+        <v>-4557</v>
       </c>
       <c r="I95" s="31" t="n">
-        <v>3883.7</v>
+        <v>1069.9</v>
       </c>
       <c r="J95" s="31" t="n">
-        <v>32724.5</v>
+        <v>3634.4</v>
       </c>
       <c r="K95" s="31" t="n">
-        <v>1832.2</v>
+        <v>237.1</v>
       </c>
     </row>
     <row r="96">
@@ -4017,38 +4023,38 @@
         </is>
       </c>
       <c r="B96" s="31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C96" s="31" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="D96" s="35" t="inlineStr">
         <is>
-          <t>기타금융</t>
+          <t>운송·창고</t>
         </is>
       </c>
       <c r="E96" s="29" t="n">
-        <v>5388</v>
+        <v>3592</v>
       </c>
       <c r="F96" s="29" t="n">
-        <v>4771</v>
+        <v>2924</v>
       </c>
       <c r="G96" s="29" t="n">
-        <v>617</v>
+        <v>668</v>
       </c>
       <c r="H96" s="28" t="n">
-        <v>-778</v>
+        <v>-3521</v>
       </c>
       <c r="I96" s="31" t="n">
-        <v>686.4</v>
+        <v>274.6</v>
       </c>
       <c r="J96" s="31" t="n">
-        <v>4852.5</v>
+        <v>1997.5</v>
       </c>
       <c r="K96" s="31" t="n">
-        <v>-301.5</v>
+        <v>328.8</v>
       </c>
     </row>
     <row r="97">
@@ -4058,38 +4064,38 @@
         </is>
       </c>
       <c r="B97" s="31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C97" s="31" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="D97" s="35" t="inlineStr">
         <is>
-          <t>화학</t>
+          <t>기계·장비</t>
         </is>
       </c>
       <c r="E97" s="29" t="n">
-        <v>4905</v>
-      </c>
-      <c r="F97" s="29" t="n">
-        <v>2991</v>
+        <v>2225</v>
+      </c>
+      <c r="F97" s="28" t="n">
+        <v>-1248</v>
       </c>
       <c r="G97" s="29" t="n">
-        <v>1914</v>
+        <v>3473</v>
       </c>
       <c r="H97" s="28" t="n">
-        <v>-4557</v>
+        <v>-2199</v>
       </c>
       <c r="I97" s="31" t="n">
-        <v>1069.9</v>
+        <v>5498.7</v>
       </c>
       <c r="J97" s="31" t="n">
-        <v>3634.4</v>
+        <v>47711.7</v>
       </c>
       <c r="K97" s="31" t="n">
-        <v>237.1</v>
+        <v>7145.1</v>
       </c>
     </row>
     <row r="98">
@@ -4099,38 +4105,38 @@
         </is>
       </c>
       <c r="B98" s="31" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C98" s="31" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="D98" s="35" t="inlineStr">
         <is>
-          <t>운송·창고</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="E98" s="29" t="n">
-        <v>3636</v>
+        <v>1631</v>
       </c>
       <c r="F98" s="29" t="n">
-        <v>2898</v>
+        <v>1115</v>
       </c>
       <c r="G98" s="29" t="n">
-        <v>737</v>
+        <v>517</v>
       </c>
       <c r="H98" s="28" t="n">
-        <v>-3521</v>
+        <v>-1635</v>
       </c>
       <c r="I98" s="31" t="n">
-        <v>274.6</v>
+        <v>644.9</v>
       </c>
       <c r="J98" s="31" t="n">
-        <v>1997.5</v>
+        <v>4091.2</v>
       </c>
       <c r="K98" s="31" t="n">
-        <v>328.8</v>
+        <v>1770.4</v>
       </c>
     </row>
     <row r="99">
@@ -4140,38 +4146,38 @@
         </is>
       </c>
       <c r="B99" s="31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C99" s="31" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="D99" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>기계·장비</t>
         </is>
       </c>
       <c r="E99" s="29" t="n">
-        <v>2365</v>
-      </c>
-      <c r="F99" s="28" t="n">
-        <v>-1308</v>
+        <v>1597</v>
+      </c>
+      <c r="F99" s="29" t="n">
+        <v>911</v>
       </c>
       <c r="G99" s="29" t="n">
-        <v>3673</v>
+        <v>686</v>
       </c>
       <c r="H99" s="28" t="n">
-        <v>-1378</v>
+        <v>-1607</v>
       </c>
       <c r="I99" s="31" t="n">
-        <v>942.4</v>
+        <v>624.6</v>
       </c>
       <c r="J99" s="31" t="n">
-        <v>28532.1</v>
+        <v>6070.1</v>
       </c>
       <c r="K99" s="31" t="n">
-        <v>7025</v>
+        <v>1274.7</v>
       </c>
     </row>
     <row r="100">
@@ -4181,11 +4187,11 @@
         </is>
       </c>
       <c r="B100" s="31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C100" s="31" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="D100" s="35" t="inlineStr">
@@ -4194,107 +4200,107 @@
         </is>
       </c>
       <c r="E100" s="29" t="n">
-        <v>2225</v>
+        <v>1272</v>
       </c>
       <c r="F100" s="28" t="n">
-        <v>-1248</v>
+        <v>-240</v>
       </c>
       <c r="G100" s="29" t="n">
-        <v>3473</v>
+        <v>1512</v>
       </c>
       <c r="H100" s="28" t="n">
-        <v>-2199</v>
+        <v>-1231</v>
       </c>
       <c r="I100" s="31" t="n">
-        <v>5498.7</v>
+        <v>965</v>
       </c>
       <c r="J100" s="31" t="n">
-        <v>47711.7</v>
+        <v>6912.3</v>
       </c>
       <c r="K100" s="31" t="n">
-        <v>7145.1</v>
+        <v>453.1</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="8" t="inlineStr">
-        <is>
-          <t>순매수 상위</t>
+      <c r="A101" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
         </is>
       </c>
       <c r="B101" s="31" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C101" s="31" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="D101" s="35" t="inlineStr">
         <is>
-          <t>기계·장비</t>
-        </is>
-      </c>
-      <c r="E101" s="29" t="n">
-        <v>1597</v>
-      </c>
-      <c r="F101" s="29" t="n">
-        <v>911</v>
-      </c>
-      <c r="G101" s="29" t="n">
-        <v>686</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="E101" s="28" t="n">
+        <v>-76483</v>
+      </c>
+      <c r="F101" s="28" t="n">
+        <v>-72174</v>
+      </c>
+      <c r="G101" s="28" t="n">
+        <v>-4308</v>
       </c>
       <c r="H101" s="28" t="n">
-        <v>-1607</v>
+        <v>-99877</v>
       </c>
       <c r="I101" s="31" t="n">
-        <v>624.6</v>
+        <v>58216.8</v>
       </c>
       <c r="J101" s="31" t="n">
-        <v>6070.1</v>
+        <v>204586.6</v>
       </c>
       <c r="K101" s="31" t="n">
-        <v>1274.7</v>
+        <v>7964.7</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="8" t="inlineStr">
-        <is>
-          <t>순매수 상위</t>
+      <c r="A102" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
         </is>
       </c>
       <c r="B102" s="31" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C102" s="31" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="D102" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="E102" s="29" t="n">
-        <v>1510</v>
-      </c>
-      <c r="F102" s="29" t="n">
-        <v>1016</v>
-      </c>
-      <c r="G102" s="29" t="n">
-        <v>494</v>
-      </c>
-      <c r="H102" s="28" t="n">
-        <v>-1635</v>
+          <t>운송장비·부품</t>
+        </is>
+      </c>
+      <c r="E102" s="28" t="n">
+        <v>-5536</v>
+      </c>
+      <c r="F102" s="28" t="n">
+        <v>-1676</v>
+      </c>
+      <c r="G102" s="28" t="n">
+        <v>-3860</v>
+      </c>
+      <c r="H102" s="29" t="n">
+        <v>5622</v>
       </c>
       <c r="I102" s="31" t="n">
-        <v>644.9</v>
+        <v>5364.4</v>
       </c>
       <c r="J102" s="31" t="n">
-        <v>4091.2</v>
+        <v>30043</v>
       </c>
       <c r="K102" s="31" t="n">
-        <v>1770.4</v>
+        <v>-232.2</v>
       </c>
     </row>
     <row r="103">
@@ -4304,38 +4310,38 @@
         </is>
       </c>
       <c r="B103" s="31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C103" s="31" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="D103" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>기계·장비</t>
         </is>
       </c>
       <c r="E103" s="28" t="n">
-        <v>-84773</v>
+        <v>-4810</v>
       </c>
       <c r="F103" s="28" t="n">
-        <v>-82160</v>
-      </c>
-      <c r="G103" s="28" t="n">
-        <v>-2613</v>
-      </c>
-      <c r="H103" s="28" t="n">
-        <v>-99877</v>
+        <v>-4879</v>
+      </c>
+      <c r="G103" s="29" t="n">
+        <v>69</v>
+      </c>
+      <c r="H103" s="29" t="n">
+        <v>4820</v>
       </c>
       <c r="I103" s="31" t="n">
-        <v>58216.8</v>
+        <v>6855.1</v>
       </c>
       <c r="J103" s="31" t="n">
-        <v>204586.6</v>
+        <v>19557</v>
       </c>
       <c r="K103" s="31" t="n">
-        <v>7964.7</v>
+        <v>2239.1</v>
       </c>
     </row>
     <row r="104">
@@ -4345,38 +4351,38 @@
         </is>
       </c>
       <c r="B104" s="31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C104" s="31" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>NAVER</t>
         </is>
       </c>
       <c r="D104" s="35" t="inlineStr">
         <is>
-          <t>운송장비·부품</t>
+          <t>IT 서비스</t>
         </is>
       </c>
       <c r="E104" s="28" t="n">
-        <v>-6347</v>
+        <v>-3793</v>
       </c>
       <c r="F104" s="28" t="n">
-        <v>-2315</v>
+        <v>-222</v>
       </c>
       <c r="G104" s="28" t="n">
-        <v>-4032</v>
+        <v>-3571</v>
       </c>
       <c r="H104" s="29" t="n">
-        <v>5622</v>
+        <v>3803</v>
       </c>
       <c r="I104" s="31" t="n">
-        <v>5364.4</v>
+        <v>2680.2</v>
       </c>
       <c r="J104" s="31" t="n">
-        <v>30043</v>
+        <v>11204.5</v>
       </c>
       <c r="K104" s="31" t="n">
-        <v>-232.2</v>
+        <v>-901.2</v>
       </c>
     </row>
     <row r="105">
@@ -4386,38 +4392,38 @@
         </is>
       </c>
       <c r="B105" s="31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C105" s="31" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="D105" s="35" t="inlineStr">
         <is>
-          <t>기계·장비</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="E105" s="28" t="n">
-        <v>-5969</v>
+        <v>-3596</v>
       </c>
       <c r="F105" s="28" t="n">
-        <v>-5851</v>
+        <v>-1544</v>
       </c>
       <c r="G105" s="28" t="n">
-        <v>-118</v>
+        <v>-2051</v>
       </c>
       <c r="H105" s="29" t="n">
-        <v>4820</v>
+        <v>3491</v>
       </c>
       <c r="I105" s="31" t="n">
-        <v>6855.1</v>
+        <v>2269</v>
       </c>
       <c r="J105" s="31" t="n">
-        <v>19557</v>
+        <v>13102.5</v>
       </c>
       <c r="K105" s="31" t="n">
-        <v>2239.1</v>
+        <v>-3057.3</v>
       </c>
     </row>
     <row r="106">
@@ -4427,38 +4433,38 @@
         </is>
       </c>
       <c r="B106" s="31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C106" s="31" t="inlineStr">
         <is>
-          <t>NAVER</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="D106" s="35" t="inlineStr">
         <is>
-          <t>IT 서비스</t>
+          <t>일반서비스</t>
         </is>
       </c>
       <c r="E106" s="28" t="n">
-        <v>-4632</v>
+        <v>-3385</v>
       </c>
       <c r="F106" s="28" t="n">
-        <v>-828</v>
+        <v>-317</v>
       </c>
       <c r="G106" s="28" t="n">
-        <v>-3804</v>
+        <v>-3068</v>
       </c>
       <c r="H106" s="29" t="n">
-        <v>3803</v>
+        <v>3760</v>
       </c>
       <c r="I106" s="31" t="n">
-        <v>2680.2</v>
+        <v>3164.5</v>
       </c>
       <c r="J106" s="31" t="n">
-        <v>11204.5</v>
+        <v>11598.7</v>
       </c>
       <c r="K106" s="31" t="n">
-        <v>-901.2</v>
+        <v>-3027.1</v>
       </c>
     </row>
     <row r="107">
@@ -4468,11 +4474,11 @@
         </is>
       </c>
       <c r="B107" s="31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C107" s="31" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>LG이노텍</t>
         </is>
       </c>
       <c r="D107" s="35" t="inlineStr">
@@ -4481,25 +4487,25 @@
         </is>
       </c>
       <c r="E107" s="28" t="n">
-        <v>-3841</v>
+        <v>-2546</v>
       </c>
       <c r="F107" s="28" t="n">
-        <v>-1591</v>
+        <v>-1126</v>
       </c>
       <c r="G107" s="28" t="n">
-        <v>-2249</v>
+        <v>-1420</v>
       </c>
       <c r="H107" s="29" t="n">
-        <v>3491</v>
+        <v>2488</v>
       </c>
       <c r="I107" s="31" t="n">
-        <v>2269</v>
+        <v>2506.5</v>
       </c>
       <c r="J107" s="31" t="n">
-        <v>13102.5</v>
+        <v>7439.6</v>
       </c>
       <c r="K107" s="31" t="n">
-        <v>-3057.3</v>
+        <v>-5725.9</v>
       </c>
     </row>
     <row r="108">
@@ -4509,38 +4515,38 @@
         </is>
       </c>
       <c r="B108" s="31" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C108" s="31" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>현대모비스</t>
         </is>
       </c>
       <c r="D108" s="35" t="inlineStr">
         <is>
-          <t>일반서비스</t>
+          <t>운송장비·부품</t>
         </is>
       </c>
       <c r="E108" s="28" t="n">
-        <v>-3385</v>
-      </c>
-      <c r="F108" s="28" t="n">
-        <v>-317</v>
+        <v>-2248</v>
+      </c>
+      <c r="F108" s="29" t="n">
+        <v>998</v>
       </c>
       <c r="G108" s="28" t="n">
-        <v>-3068</v>
+        <v>-3246</v>
       </c>
       <c r="H108" s="29" t="n">
-        <v>3760</v>
+        <v>2207</v>
       </c>
       <c r="I108" s="31" t="n">
-        <v>3164.5</v>
+        <v>985</v>
       </c>
       <c r="J108" s="31" t="n">
-        <v>11598.7</v>
+        <v>4643.7</v>
       </c>
       <c r="K108" s="31" t="n">
-        <v>-3027.1</v>
+        <v>-1613.3</v>
       </c>
     </row>
     <row r="109">
@@ -4550,11 +4556,11 @@
         </is>
       </c>
       <c r="B109" s="31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C109" s="31" t="inlineStr">
         <is>
-          <t>LG이노텍</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="D109" s="35" t="inlineStr">
@@ -4563,25 +4569,25 @@
         </is>
       </c>
       <c r="E109" s="28" t="n">
-        <v>-2627</v>
+        <v>-1782</v>
       </c>
       <c r="F109" s="28" t="n">
-        <v>-1228</v>
+        <v>-430</v>
       </c>
       <c r="G109" s="28" t="n">
-        <v>-1399</v>
+        <v>-1353</v>
       </c>
       <c r="H109" s="29" t="n">
-        <v>2488</v>
+        <v>1788</v>
       </c>
       <c r="I109" s="31" t="n">
-        <v>2506.5</v>
+        <v>1373.7</v>
       </c>
       <c r="J109" s="31" t="n">
-        <v>7439.6</v>
+        <v>6111</v>
       </c>
       <c r="K109" s="31" t="n">
-        <v>-5725.9</v>
+        <v>-935.4</v>
       </c>
     </row>
     <row r="110">
@@ -4591,169 +4597,116 @@
         </is>
       </c>
       <c r="B110" s="31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C110" s="31" t="inlineStr">
         <is>
-          <t>현대모비스</t>
+          <t>에이피알</t>
         </is>
       </c>
       <c r="D110" s="35" t="inlineStr">
         <is>
-          <t>운송장비·부품</t>
+          <t>화학</t>
         </is>
       </c>
       <c r="E110" s="28" t="n">
-        <v>-2384</v>
+        <v>-1702</v>
       </c>
       <c r="F110" s="29" t="n">
-        <v>895</v>
+        <v>184</v>
       </c>
       <c r="G110" s="28" t="n">
-        <v>-3279</v>
+        <v>-1886</v>
       </c>
       <c r="H110" s="29" t="n">
-        <v>2207</v>
+        <v>1669</v>
       </c>
       <c r="I110" s="31" t="n">
-        <v>985</v>
+        <v>947</v>
       </c>
       <c r="J110" s="31" t="n">
-        <v>4643.7</v>
+        <v>13876.7</v>
       </c>
       <c r="K110" s="31" t="n">
-        <v>-1613.3</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="10" t="inlineStr">
-        <is>
-          <t>순매도 상위</t>
-        </is>
-      </c>
-      <c r="B111" s="31" t="n">
-        <v>9</v>
-      </c>
-      <c r="C111" s="31" t="inlineStr">
-        <is>
-          <t>엘앤에프</t>
-        </is>
-      </c>
-      <c r="D111" s="35" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="E111" s="28" t="n">
-        <v>-1782</v>
-      </c>
-      <c r="F111" s="28" t="n">
-        <v>-430</v>
-      </c>
-      <c r="G111" s="28" t="n">
-        <v>-1353</v>
-      </c>
-      <c r="H111" s="29" t="n">
-        <v>1788</v>
-      </c>
-      <c r="I111" s="31" t="n">
-        <v>1373.7</v>
-      </c>
-      <c r="J111" s="31" t="n">
-        <v>6111</v>
-      </c>
-      <c r="K111" s="31" t="n">
-        <v>-935.4</v>
-      </c>
-    </row>
+        <v>-2345.1</v>
+      </c>
+    </row>
+    <row r="111"/>
     <row r="112">
-      <c r="A112" s="10" t="inlineStr">
-        <is>
-          <t>순매도 상위</t>
-        </is>
-      </c>
-      <c r="B112" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="C112" s="31" t="inlineStr">
-        <is>
-          <t>대우건설</t>
-        </is>
-      </c>
-      <c r="D112" s="35" t="inlineStr">
-        <is>
-          <t>건설</t>
-        </is>
-      </c>
-      <c r="E112" s="28" t="n">
-        <v>-1765</v>
-      </c>
-      <c r="F112" s="28" t="n">
-        <v>-1439</v>
-      </c>
-      <c r="G112" s="28" t="n">
-        <v>-327</v>
-      </c>
-      <c r="H112" s="29" t="n">
-        <v>1270</v>
-      </c>
-      <c r="I112" s="31" t="n">
-        <v>1258.6</v>
-      </c>
-      <c r="J112" s="31" t="n">
-        <v>5249.2</v>
-      </c>
-      <c r="K112" s="31" t="n">
-        <v>-382.3</v>
-      </c>
-    </row>
-    <row r="113"/>
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>섹터 시그널 종목 관찰</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr"/>
+      <c r="D112" s="3" t="inlineStr"/>
+      <c r="E112" s="3" t="inlineStr"/>
+      <c r="F112" s="3" t="inlineStr"/>
+      <c r="G112" s="18" t="inlineStr">
+        <is>
+          <t>섹터 상태 x 수급 x 공매도·대차 x 촉매</t>
+        </is>
+      </c>
+      <c r="H112" s="3" t="inlineStr"/>
+      <c r="I112" s="3" t="inlineStr"/>
+      <c r="J112" s="3" t="inlineStr"/>
+      <c r="K112" s="3" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="36" t="inlineStr">
+        <is>
+          <t>● 동반강세 — 추세 지속형 상방 관찰</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>● 수급유입 — 초기 유입형 상방 관찰</t>
+        </is>
+      </c>
+    </row>
     <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
-      </c>
-      <c r="B114" s="3" t="inlineStr">
-        <is>
-          <t>섹터 시그널 종목 관찰</t>
-        </is>
-      </c>
-      <c r="C114" s="3" t="inlineStr"/>
-      <c r="D114" s="3" t="inlineStr"/>
-      <c r="E114" s="3" t="inlineStr"/>
-      <c r="F114" s="3" t="inlineStr"/>
-      <c r="G114" s="18" t="inlineStr">
-        <is>
-          <t>섹터 상태 x 수급 x 공매도·대차 x 촉매</t>
-        </is>
-      </c>
-      <c r="H114" s="3" t="inlineStr"/>
-      <c r="I114" s="3" t="inlineStr"/>
-      <c r="J114" s="3" t="inlineStr"/>
-      <c r="K114" s="3" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="36" t="inlineStr">
-        <is>
-          <t>● 동반강세 — 추세 지속형 상방 관찰</t>
-        </is>
-      </c>
-      <c r="G115" s="3" t="inlineStr">
-        <is>
-          <t>● 수급유입 — 초기 유입형 상방 관찰</t>
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="B114" s="35" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+      <c r="C114" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="D114" s="31" t="inlineStr"/>
+      <c r="E114" s="31" t="inlineStr"/>
+      <c r="G114" s="31" t="inlineStr">
+        <is>
+          <t>해당 섹터·조건 충족 종목 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="44.5" customHeight="1" s="15">
+      <c r="A115" s="17" t="inlineStr">
+        <is>
+          <t>외국인 +4,771억 순매수, 기관 +617억 순매수, 대차잔고 -302억 감소 — 금융(동반강세) 섹터 추세 지속형 상방 관찰</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>아시아나항공</t>
         </is>
       </c>
       <c r="B116" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>운송·창고</t>
         </is>
       </c>
       <c r="C116" s="37" t="n">
@@ -4761,28 +4714,23 @@
       </c>
       <c r="D116" s="31" t="inlineStr"/>
       <c r="E116" s="31" t="inlineStr"/>
-      <c r="G116" s="31" t="inlineStr">
-        <is>
-          <t>해당 섹터·조건 충족 종목 없음</t>
-        </is>
-      </c>
     </row>
     <row r="117" ht="44.5" customHeight="1" s="15">
       <c r="A117" s="17" t="inlineStr">
         <is>
-          <t>외국인 +4,771억 순매수, 기관 +617억 순매수, 대차잔고 -302억 감소 — 금융(동반강세) 섹터 추세 지속형 상방 관찰</t>
+          <t>외국인 +46억 순매수, 기관 +95억 순매수, 대차잔고 -7억 감소 — 운송·창고(동반강세) 섹터 추세 지속형 상방 관찰</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>아시아나항공</t>
+          <t>인바디</t>
         </is>
       </c>
       <c r="B118" s="35" t="inlineStr">
         <is>
-          <t>운송·창고</t>
+          <t>의료·정밀기기</t>
         </is>
       </c>
       <c r="C118" s="37" t="n">
@@ -4794,19 +4742,19 @@
     <row r="119" ht="44.5" customHeight="1" s="15">
       <c r="A119" s="17" t="inlineStr">
         <is>
-          <t>외국인 +46억 순매수, 기관 +95억 순매수, 대차잔고 -7억 감소 — 운송·창고(동반강세) 섹터 추세 지속형 상방 관찰</t>
+          <t>외국인 +23억 순매수, 기관 +59억 순매수, 대차잔고 -21억 감소 — 의료·정밀기기(동반강세) 섹터 추세 지속형 상방 관찰</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>인바디</t>
+          <t>HMM</t>
         </is>
       </c>
       <c r="B120" s="35" t="inlineStr">
         <is>
-          <t>의료·정밀기기</t>
+          <t>운송·창고</t>
         </is>
       </c>
       <c r="C120" s="37" t="n">
@@ -4818,14 +4766,14 @@
     <row r="121" ht="44.5" customHeight="1" s="15">
       <c r="A121" s="17" t="inlineStr">
         <is>
-          <t>외국인 +23억 순매수, 기관 +59억 순매수, 대차잔고 -21억 감소 — 의료·정밀기기(동반강세) 섹터 추세 지속형 상방 관찰</t>
+          <t>외국인 +17억 순매수, 기관 +65억 순매수, 대차잔고 -196억 감소 — 운송·창고(동반강세) 섹터 추세 지속형 상방 관찰</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>HMM</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B122" s="35" t="inlineStr">
@@ -4834,59 +4782,79 @@
         </is>
       </c>
       <c r="C122" s="37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D122" s="31" t="inlineStr"/>
       <c r="E122" s="31" t="inlineStr"/>
     </row>
-    <row r="123" ht="44.5" customHeight="1" s="15">
+    <row r="123" ht="31" customHeight="1" s="15">
       <c r="A123" s="17" t="inlineStr">
         <is>
-          <t>외국인 +17억 순매수, 기관 +65억 순매수, 대차잔고 -196억 감소 — 운송·창고(동반강세) 섹터 추세 지속형 상방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="5" t="inlineStr">
-        <is>
-          <t>대한항공</t>
-        </is>
-      </c>
-      <c r="B124" s="35" t="inlineStr">
-        <is>
-          <t>운송·창고</t>
-        </is>
-      </c>
-      <c r="C124" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="D124" s="31" t="inlineStr"/>
-      <c r="E124" s="31" t="inlineStr"/>
-    </row>
-    <row r="125" ht="31" customHeight="1" s="15">
-      <c r="A125" s="17" t="inlineStr">
-        <is>
-          <t>외국인 +2,898억 순매수, 기관 +737억 순매수 — 운송·창고(동반강세) 섹터 추세 지속형 상방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="126"/>
-    <row r="127">
-      <c r="A127" s="38" t="inlineStr">
+          <t>외국인 +2,924억 순매수, 기관 +668억 순매수 — 운송·창고(동반강세) 섹터 추세 지속형 상방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="124"/>
+    <row r="125">
+      <c r="A125" s="38" t="inlineStr">
         <is>
           <t>● 수급이탈 — 상승 후 약화 관찰</t>
         </is>
       </c>
-      <c r="G127" s="39" t="inlineStr">
+      <c r="G125" s="39" t="inlineStr">
         <is>
           <t>● 동반약세 — 약세 지속형 하방 관찰</t>
         </is>
       </c>
     </row>
-    <row r="128">
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>CJ제일제당</t>
+        </is>
+      </c>
+      <c r="B126" s="35" t="inlineStr">
+        <is>
+          <t>음식료·담배</t>
+        </is>
+      </c>
+      <c r="C126" s="40" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D126" s="31" t="inlineStr"/>
+      <c r="E126" s="31" t="inlineStr"/>
+      <c r="G126" s="5" t="inlineStr">
+        <is>
+          <t>에스엠</t>
+        </is>
+      </c>
+      <c r="H126" s="35" t="inlineStr">
+        <is>
+          <t>오락·문화</t>
+        </is>
+      </c>
+      <c r="I126" s="41" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J126" s="31" t="inlineStr"/>
+      <c r="K126" s="31" t="inlineStr"/>
+    </row>
+    <row r="127" ht="44.5" customHeight="1" s="15">
+      <c r="A127" s="17" t="inlineStr">
+        <is>
+          <t>외국인 -316억 순매도, 기관 -86억 순매도, 대차잔고 +124억 증가 — 음식료·담배(수급이탈) 섹터 상승 후 약화 관찰</t>
+        </is>
+      </c>
+      <c r="G127" s="17" t="inlineStr">
+        <is>
+          <t>외국인 -264억 순매도, 기관 -74억 순매도, 대차잔고 +214억 증가 — 오락·문화(동반약세) 섹터 약세 지속형 하방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="31" customHeight="1" s="15">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>CJ제일제당</t>
+          <t>오리온</t>
         </is>
       </c>
       <c r="B128" s="35" t="inlineStr">
@@ -4899,9 +4867,9 @@
       </c>
       <c r="D128" s="31" t="inlineStr"/>
       <c r="E128" s="31" t="inlineStr"/>
-      <c r="G128" s="5" t="inlineStr">
-        <is>
-          <t>에스엠</t>
+      <c r="G128" s="42" t="inlineStr">
+        <is>
+          <t>와이지엔터테인먼트</t>
         </is>
       </c>
       <c r="H128" s="35" t="inlineStr">
@@ -4918,19 +4886,19 @@
     <row r="129" ht="44.5" customHeight="1" s="15">
       <c r="A129" s="17" t="inlineStr">
         <is>
-          <t>외국인 -316억 순매도, 기관 -86억 순매도, 대차잔고 +124억 증가 — 음식료·담배(수급이탈) 섹터 상승 후 약화 관찰</t>
+          <t>외국인 -2억 순매도, 기관 -217억 순매도, 대차잔고 +14억 증가 — 음식료·담배(수급이탈) 섹터 상승 후 약화 관찰</t>
         </is>
       </c>
       <c r="G129" s="17" t="inlineStr">
         <is>
-          <t>외국인 -264억 순매도, 기관 -74억 순매도, 대차잔고 +214억 증가 — 오락·문화(동반약세) 섹터 약세 지속형 하방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="31" customHeight="1" s="15">
+          <t>외국인 -131억 순매도, 기관 -93억 순매도, 대차잔고 +26억 증가 — 오락·문화(동반약세) 섹터 약세 지속형 하방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>오리온</t>
+          <t>롯데칠성</t>
         </is>
       </c>
       <c r="B130" s="35" t="inlineStr">
@@ -4939,18 +4907,18 @@
         </is>
       </c>
       <c r="C130" s="40" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D130" s="31" t="inlineStr"/>
       <c r="E130" s="31" t="inlineStr"/>
-      <c r="G130" s="42" t="inlineStr">
-        <is>
-          <t>와이지엔터테인먼트</t>
+      <c r="G130" s="5" t="inlineStr">
+        <is>
+          <t>풍산</t>
         </is>
       </c>
       <c r="H130" s="35" t="inlineStr">
         <is>
-          <t>오락·문화</t>
+          <t>금속</t>
         </is>
       </c>
       <c r="I130" s="41" t="n">
@@ -4962,19 +4930,19 @@
     <row r="131" ht="44.5" customHeight="1" s="15">
       <c r="A131" s="17" t="inlineStr">
         <is>
-          <t>외국인 -2억 순매도, 기관 -217억 순매도, 대차잔고 +14억 증가 — 음식료·담배(수급이탈) 섹터 상승 후 약화 관찰</t>
+          <t>외국인 -49억 순매도, 기관 -24억 순매도 — 음식료·담배(수급이탈) 섹터 상승 후 약화 관찰</t>
         </is>
       </c>
       <c r="G131" s="17" t="inlineStr">
         <is>
-          <t>외국인 -131억 순매도, 기관 -93억 순매도, 대차잔고 +26억 증가 — 오락·문화(동반약세) 섹터 약세 지속형 하방 관찰</t>
+          <t>외국인 -103억 순매도, 기관 -12억 순매도, 대차잔고 +5억 증가 — 금속(동반약세) 섹터 약세 지속형 하방 관찰</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>롯데칠성</t>
+          <t>하이트진로</t>
         </is>
       </c>
       <c r="B132" s="35" t="inlineStr">
@@ -4989,12 +4957,12 @@
       <c r="E132" s="31" t="inlineStr"/>
       <c r="G132" s="5" t="inlineStr">
         <is>
-          <t>풍산</t>
+          <t>CJ ENM</t>
         </is>
       </c>
       <c r="H132" s="35" t="inlineStr">
         <is>
-          <t>금속</t>
+          <t>오락·문화</t>
         </is>
       </c>
       <c r="I132" s="41" t="n">
@@ -5006,39 +4974,24 @@
     <row r="133" ht="44.5" customHeight="1" s="15">
       <c r="A133" s="17" t="inlineStr">
         <is>
-          <t>외국인 -49억 순매도, 기관 -24억 순매도 — 음식료·담배(수급이탈) 섹터 상승 후 약화 관찰</t>
+          <t>외국인 -11억 순매도, 기관 -4억 순매도 — 음식료·담배(수급이탈) 섹터 상승 후 약화 관찰</t>
         </is>
       </c>
       <c r="G133" s="17" t="inlineStr">
         <is>
-          <t>외국인 -103억 순매도, 기관 -12억 순매도, 대차잔고 +5억 증가 — 금속(동반약세) 섹터 약세 지속형 하방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="5" t="inlineStr">
-        <is>
-          <t>하이트진로</t>
-        </is>
-      </c>
-      <c r="B134" s="35" t="inlineStr">
-        <is>
-          <t>음식료·담배</t>
-        </is>
-      </c>
-      <c r="C134" s="40" t="n">
-        <v>-1</v>
-      </c>
-      <c r="D134" s="31" t="inlineStr"/>
-      <c r="E134" s="31" t="inlineStr"/>
-      <c r="G134" s="5" t="inlineStr">
-        <is>
-          <t>CJ ENM</t>
+          <t>외국인 -46억 순매도, 기관 -26억 순매도, 대차잔고 +29억 증가 — 오락·문화(동반약세) 섹터 약세 지속형 하방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="31" customHeight="1" s="15">
+      <c r="G134" s="42" t="inlineStr">
+        <is>
+          <t>LIG디펜스앤에어로스페이스</t>
         </is>
       </c>
       <c r="H134" s="35" t="inlineStr">
         <is>
-          <t>오락·문화</t>
+          <t>금속</t>
         </is>
       </c>
       <c r="I134" s="41" t="n">
@@ -5048,261 +5001,414 @@
       <c r="K134" s="31" t="inlineStr"/>
     </row>
     <row r="135" ht="44.5" customHeight="1" s="15">
-      <c r="A135" s="17" t="inlineStr">
-        <is>
-          <t>외국인 -11억 순매도, 기관 -4억 순매도 — 음식료·담배(수급이탈) 섹터 상승 후 약화 관찰</t>
-        </is>
-      </c>
       <c r="G135" s="17" t="inlineStr">
         <is>
-          <t>외국인 -46억 순매도, 기관 -26억 순매도, 대차잔고 +29억 증가 — 오락·문화(동반약세) 섹터 약세 지속형 하방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="31" customHeight="1" s="15">
-      <c r="G136" s="42" t="inlineStr">
-        <is>
-          <t>LIG디펜스앤에어로스페이스</t>
-        </is>
-      </c>
-      <c r="H136" s="35" t="inlineStr">
-        <is>
-          <t>금속</t>
-        </is>
-      </c>
-      <c r="I136" s="41" t="n">
-        <v>-3</v>
-      </c>
-      <c r="J136" s="31" t="inlineStr"/>
-      <c r="K136" s="31" t="inlineStr"/>
-    </row>
-    <row r="137" ht="44.5" customHeight="1" s="15">
-      <c r="G137" s="17" t="inlineStr">
-        <is>
           <t>외국인 -52억 순매도, 기관 -14억 순매도, 대차잔고 +356억 증가 — 금속(동반약세) 섹터 약세 지속형 하방 관찰</t>
         </is>
       </c>
     </row>
+    <row r="136"/>
+    <row r="137" ht="31" customHeight="1" s="15">
+      <c r="A137" s="43" t="inlineStr">
+        <is>
+          <t>현재 확보된 월간 리뷰 데이터 유니버스(순매수 상위 30 등재 · 공매도/대차 랭킹 · 월간 촉매 · 신호 섹터 시총 상위 10) 기준 — 전 시장 스크리닝 아님 · 관찰 우선순위이며 매매 권유 아님</t>
+        </is>
+      </c>
+    </row>
     <row r="138"/>
-    <row r="139" ht="31" customHeight="1" s="15">
-      <c r="A139" s="43" t="inlineStr">
-        <is>
-          <t>현재 확보된 월간 리뷰 데이터 유니버스(순매수 상위 30 등재 · 공매도/대차 랭킹 · 월간 촉매 · 신호 섹터 시총 상위 10) 기준 — 전 시장 스크리닝 아님 · 관찰 우선순위이며 매매 권유 아님</t>
-        </is>
-      </c>
-    </row>
-    <row r="140"/>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>08</t>
         </is>
       </c>
-      <c r="B141" s="3" t="inlineStr">
+      <c r="B139" s="3" t="inlineStr">
         <is>
           <t>월간 시장 흐름</t>
         </is>
       </c>
-      <c r="C141" s="3" t="inlineStr"/>
-      <c r="D141" s="3" t="inlineStr"/>
-      <c r="E141" s="3" t="inlineStr"/>
-      <c r="F141" s="3" t="inlineStr"/>
-      <c r="G141" s="3" t="inlineStr"/>
-      <c r="H141" s="3" t="inlineStr"/>
-      <c r="I141" s="3" t="inlineStr"/>
-      <c r="J141" s="3" t="inlineStr"/>
-      <c r="K141" s="3" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="4" t="inlineStr">
+      <c r="C139" s="3" t="inlineStr"/>
+      <c r="D139" s="3" t="inlineStr"/>
+      <c r="E139" s="3" t="inlineStr"/>
+      <c r="F139" s="3" t="inlineStr"/>
+      <c r="G139" s="3" t="inlineStr"/>
+      <c r="H139" s="3" t="inlineStr"/>
+      <c r="I139" s="3" t="inlineStr"/>
+      <c r="J139" s="3" t="inlineStr"/>
+      <c r="K139" s="3" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B142" s="4" t="inlineStr">
+      <c r="B140" s="4" t="inlineStr">
         <is>
           <t>Market Flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="31" customHeight="1" s="15">
+      <c r="A141" s="17" t="inlineStr">
+        <is>
+          <t>- 월 초 AI 반도체 및 HBM 수요 기대감으로 KOSPI가 7,000선에 근접했으나, 인플레이션 우려와 미국 기술주 투매로 상승분을 반납했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="15" customHeight="1" s="15">
+      <c r="A142" s="17" t="inlineStr">
+        <is>
+          <t>- 미국 10년물 국채금리 급등과 고유가 등 매크로 불확실성이 커지며 외국인의 대규모 매도세가 지수 하방 압력을 가중했습니다.</t>
         </is>
       </c>
     </row>
     <row r="143" ht="15" customHeight="1" s="15">
       <c r="A143" s="17" t="inlineStr">
         <is>
-          <t>- 월 초 KOSPI는 외국인과 기관의 대규모 매도세로 급락하며 시작했으나, 개인의 매수세가 지수 하단을 방어했습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="31" customHeight="1" s="15">
+          <t>- 주 중반 이후 기관의 저가 매수세가 유입되며 지수 하단을 방어했고, 반도체 중심의 수급 개선이 나타났습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="15" customHeight="1" s="15">
       <c r="A144" s="17" t="inlineStr">
         <is>
-          <t>- 월 중순 AI 반도체 및 HBM 수요 기대감으로 KOSPI가 7,000선에 근접하는 강한 반등을 보였으나, 미국 고용지표 호조와 생산자물가지수(PPI) 상승으로 인플레이션 우려가 재부각되며 변동성이 확대되었습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="31" customHeight="1" s="15">
+          <t>- 건설 섹터는 프로젝트 관련 악재와 수급 이탈로 급락하며 섹터 간 양극화가 심화되었습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="15" customHeight="1" s="15">
       <c r="A145" s="17" t="inlineStr">
         <is>
-          <t>- 국제유가 100달러 돌파와 미국 국채금리 급등 등 대외 악재가 겹치며 시장의 위험회피 심리가 고조되었고, 외국인 자금 이탈이 가속화되었습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="31" customHeight="1" s="15">
-      <c r="A146" s="17" t="inlineStr">
-        <is>
-          <t>- 월 후반 미국 기술주 강세 훈풍과 견조한 국내 수출 지표에 힘입어 반도체 중심의 기술주 모멘텀이 시장을 견인하며 KOSPI 7,000선을 회복했습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="15" customHeight="1" s="15">
-      <c r="A147" s="17" t="inlineStr">
-        <is>
-          <t>- 기관 투자자는 월간 전반에 걸쳐 주요 매수 주체로 활동하며 지수 하락 방어 및 상승 전환에 기여했습니다.</t>
-        </is>
-      </c>
+          <t>- 월말까지 외국인과 기관의 수급 공방이 지속되며 지수 변동성이 높은 흐름을 보였습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146"/>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>섹터·테마 흐름</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr"/>
+      <c r="D147" s="3" t="inlineStr"/>
+      <c r="E147" s="3" t="inlineStr"/>
+      <c r="F147" s="3" t="inlineStr"/>
+      <c r="G147" s="3" t="inlineStr"/>
+      <c r="H147" s="3" t="inlineStr"/>
+      <c r="I147" s="3" t="inlineStr"/>
+      <c r="J147" s="3" t="inlineStr"/>
+      <c r="K147" s="3" t="inlineStr"/>
     </row>
     <row r="148" ht="15" customHeight="1" s="15">
       <c r="A148" s="17" t="inlineStr">
         <is>
-          <t>- 외국인 투자자는 월 초 대규모 매도세를 보였으나, 월 중순 이후 반도체 섹터 중심으로 매수세가 유입되며 수급 개선을 이끌었습니다.</t>
+          <t>- 전기·전자 및 의료·정밀기기 섹터는 AI 반도체 훈풍과 HBM 수요 기대감으로 시장 상승을 주도했습니다.</t>
         </is>
       </c>
     </row>
     <row r="149" ht="15" customHeight="1" s="15">
       <c r="A149" s="17" t="inlineStr">
         <is>
-          <t>- 개인 투자자는 지수 하락 시 매수, 상승 시 차익 실현에 집중하며 시장 변동성에 대응하는 모습을 보였습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="150"/>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="B151" s="3" t="inlineStr">
-        <is>
-          <t>섹터·테마 흐름</t>
-        </is>
-      </c>
-      <c r="C151" s="3" t="inlineStr"/>
-      <c r="D151" s="3" t="inlineStr"/>
-      <c r="E151" s="3" t="inlineStr"/>
-      <c r="F151" s="3" t="inlineStr"/>
-      <c r="G151" s="3" t="inlineStr"/>
-      <c r="H151" s="3" t="inlineStr"/>
-      <c r="I151" s="3" t="inlineStr"/>
-      <c r="J151" s="3" t="inlineStr"/>
-      <c r="K151" s="3" t="inlineStr"/>
-    </row>
-    <row r="152" ht="15" customHeight="1" s="15">
-      <c r="A152" s="17" t="inlineStr">
-        <is>
-          <t>- 월 초 유통, 보험, 금융 등 내수 및 방어적 성격의 섹터가 강세를 보였으나, 건설, 기계·장비, 운송장비·부품 등은 하락했습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="15" customHeight="1" s="15">
-      <c r="A153" s="17" t="inlineStr">
-        <is>
-          <t>- 월 중순 AI 반도체 및 HBM 수요 기대감으로 전기·전자, 의료·정밀기기, 기계·장비 섹터가 시장 상승을 주도했습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="31" customHeight="1" s="15">
-      <c r="A154" s="17" t="inlineStr">
-        <is>
-          <t>- 인플레이션 우려가 고조되면서 금리 상승 수혜가 예상되는 보험 섹터와 방어적 성격의 건설 섹터로 수급이 순환매되는 양상이 나타났습니다.</t>
+          <t>- 건설 및 기계·장비 섹터는 원전 수주 모멘텀으로 강세를 보였으나, 월 후반 악재 부각으로 수급이 이탈했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="15" customHeight="1" s="15">
+      <c r="A150" s="17" t="inlineStr">
+        <is>
+          <t>- 보험 및 금융 섹터는 금리 상승기 방어주로서의 성격이 부각되며 순환매 흐름을 보였습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151"/>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>월간 촉매 타임라인</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr"/>
+      <c r="D152" s="3" t="inlineStr"/>
+      <c r="E152" s="3" t="inlineStr"/>
+      <c r="F152" s="3" t="inlineStr"/>
+      <c r="G152" s="3" t="inlineStr"/>
+      <c r="H152" s="3" t="inlineStr"/>
+      <c r="I152" s="3" t="inlineStr"/>
+      <c r="J152" s="18" t="inlineStr">
+        <is>
+          <t>등락률 = 월간 누적 · ★5 주차 상위</t>
+        </is>
+      </c>
+      <c r="K152" s="3" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>날짜</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>시장</t>
+        </is>
+      </c>
+      <c r="D153" s="4" t="inlineStr">
+        <is>
+          <t>섹터명</t>
+        </is>
+      </c>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>별점</t>
+        </is>
+      </c>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>등락률(%)</t>
+        </is>
+      </c>
+      <c r="G153" s="4" t="inlineStr">
+        <is>
+          <t>핵심 촉매</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="15" customHeight="1" s="15">
+      <c r="A154" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B154" s="31" t="inlineStr">
+        <is>
+          <t>빛과전자</t>
+        </is>
+      </c>
+      <c r="C154" s="31" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D154" s="35" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="E154" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="F154" s="29" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="G154" s="17" t="inlineStr">
+        <is>
+          <t>차세대 광통신 부품 국산화 국책 사업 수행기관 선정.</t>
         </is>
       </c>
     </row>
     <row r="155" ht="31" customHeight="1" s="15">
-      <c r="A155" s="17" t="inlineStr">
-        <is>
-          <t>- 월 후반 반도체/AI 관련주가 지속적인 강세를 보이며 삼성전자와 디아이 등이 상승을 주도했으나, 건설 섹터는 프로젝트 관련 불확실성으로 급락하며 섹터 간 양극화가 심화되었습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="31" customHeight="1" s="15">
-      <c r="A156" s="17" t="inlineStr">
-        <is>
-          <t>- 월간 전체적으로 의료·정밀기기(+18.45%), 전기·전자(+8.59%), 제조(+5.11%) 섹터가 상승을 주도했으며, IT 서비스(-9.34%), 운송장비·부품(-9.73%), 음식료·담배(-9.23%) 섹터는 하락했습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="157"/>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B158" s="3" t="inlineStr">
-        <is>
-          <t>월간 촉매 타임라인</t>
-        </is>
-      </c>
-      <c r="C158" s="3" t="inlineStr"/>
-      <c r="D158" s="3" t="inlineStr"/>
-      <c r="E158" s="3" t="inlineStr"/>
-      <c r="F158" s="3" t="inlineStr"/>
-      <c r="G158" s="3" t="inlineStr"/>
-      <c r="H158" s="3" t="inlineStr"/>
-      <c r="I158" s="3" t="inlineStr"/>
-      <c r="J158" s="18" t="inlineStr">
-        <is>
-          <t>등락률 = 월간 누적 · ★5 주차 상위</t>
-        </is>
-      </c>
-      <c r="K158" s="3" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="4" t="inlineStr">
-        <is>
-          <t>날짜</t>
-        </is>
-      </c>
-      <c r="B159" s="4" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="C159" s="4" t="inlineStr">
-        <is>
-          <t>시장</t>
-        </is>
-      </c>
-      <c r="D159" s="4" t="inlineStr">
-        <is>
-          <t>섹터명</t>
-        </is>
-      </c>
-      <c r="E159" s="4" t="inlineStr">
-        <is>
-          <t>별점</t>
-        </is>
-      </c>
-      <c r="F159" s="4" t="inlineStr">
-        <is>
-          <t>등락률(%)</t>
-        </is>
-      </c>
-      <c r="G159" s="4" t="inlineStr">
-        <is>
-          <t>핵심 촉매</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="15" customHeight="1" s="15">
+      <c r="A155" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B155" s="31" t="inlineStr">
+        <is>
+          <t>에스엠벡셀</t>
+        </is>
+      </c>
+      <c r="C155" s="31" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D155" s="35" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
+        </is>
+      </c>
+      <c r="E155" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="F155" s="29" t="n">
+        <v>64.54000000000001</v>
+      </c>
+      <c r="G155" s="17" t="inlineStr">
+        <is>
+          <t>미국 글로벌 자동차 기업과 차세대 LMR 배터리 기술 협력.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="15" customHeight="1" s="15">
+      <c r="A156" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B156" s="31" t="inlineStr">
+        <is>
+          <t>머큐리</t>
+        </is>
+      </c>
+      <c r="C156" s="31" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D156" s="35" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="E156" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="F156" s="29" t="n">
+        <v>39.14</v>
+      </c>
+      <c r="G156" s="17" t="inlineStr">
+        <is>
+          <t>미국 버라이즌-코닝 광섬유 공급 계약에 따른 인프라 수혜.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="31" customHeight="1" s="15">
+      <c r="A157" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B157" s="31" t="inlineStr">
+        <is>
+          <t>범한퓨얼셀</t>
+        </is>
+      </c>
+      <c r="C157" s="31" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D157" s="35" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="E157" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="F157" s="29" t="n">
+        <v>38.89</v>
+      </c>
+      <c r="G157" s="17" t="inlineStr">
+        <is>
+          <t>AI 데이터센터 전력원으로서 연료전지 수요 급증에 따른 수혜.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="31" customHeight="1" s="15">
+      <c r="A158" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B158" s="31" t="inlineStr">
+        <is>
+          <t>아모텍</t>
+        </is>
+      </c>
+      <c r="C158" s="31" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D158" s="35" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="E158" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="F158" s="29" t="n">
+        <v>77.31999999999999</v>
+      </c>
+      <c r="G158" s="17" t="inlineStr">
+        <is>
+          <t>AI 데이터센터 및 ESS 시장 확대에 따른 MLCC 매출 증가 기대감으로 상한가 기록.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="31" customHeight="1" s="15">
+      <c r="A159" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B159" s="31" t="inlineStr">
+        <is>
+          <t>엑스게이트</t>
+        </is>
+      </c>
+      <c r="C159" s="31" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D159" s="35" t="inlineStr">
+        <is>
+          <t>IT 서비스</t>
+        </is>
+      </c>
+      <c r="E159" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="F159" s="29" t="n">
+        <v>55.12</v>
+      </c>
+      <c r="G159" s="17" t="inlineStr">
+        <is>
+          <t>엔비디아 CEO의 사이버 보안 강조 발언에 따른 보안 솔루션 수요 증가 기대감으로 상한가.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="31" customHeight="1" s="15">
       <c r="A160" s="31" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B160" s="31" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="C160" s="31" t="inlineStr">
@@ -5312,7 +5418,7 @@
       </c>
       <c r="D160" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>IT 서비스</t>
         </is>
       </c>
       <c r="E160" s="14" t="inlineStr">
@@ -5321,23 +5427,23 @@
         </is>
       </c>
       <c r="F160" s="29" t="n">
-        <v>41.8</v>
+        <v>52.28</v>
       </c>
       <c r="G160" s="17" t="inlineStr">
         <is>
-          <t>차세대 광통신 부품 국산화 국책 사업 수행기관 선정.</t>
+          <t>엔비디아 CEO의 사이버 보안 핵심 시장 언급에 따른 보안주 수혜 기대감으로 상한가.</t>
         </is>
       </c>
     </row>
     <row r="161" ht="31" customHeight="1" s="15">
       <c r="A161" s="31" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B161" s="31" t="inlineStr">
         <is>
-          <t>에스엠벡셀</t>
+          <t>카티스</t>
         </is>
       </c>
       <c r="C161" s="31" t="inlineStr">
@@ -5347,7 +5453,7 @@
       </c>
       <c r="D161" s="35" t="inlineStr">
         <is>
-          <t>운송장비·부품</t>
+          <t>IT 서비스</t>
         </is>
       </c>
       <c r="E161" s="14" t="inlineStr">
@@ -5356,23 +5462,23 @@
         </is>
       </c>
       <c r="F161" s="29" t="n">
-        <v>64.54000000000001</v>
+        <v>47.47</v>
       </c>
       <c r="G161" s="17" t="inlineStr">
         <is>
-          <t>미국 글로벌 자동차 기업과 차세대 LMR 배터리 기술 협력.</t>
-        </is>
-      </c>
-    </row>
-    <row r="162" ht="15" customHeight="1" s="15">
+          <t>사상 최대 수주잔고 확보 및 AI 데이터센터 수주 확대에 따른 실적 턴어라운드 기대.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="31" customHeight="1" s="15">
       <c r="A162" s="31" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B162" s="31" t="inlineStr">
         <is>
-          <t>머큐리</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="C162" s="31" t="inlineStr">
@@ -5382,7 +5488,7 @@
       </c>
       <c r="D162" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="E162" s="14" t="inlineStr">
@@ -5391,23 +5497,23 @@
         </is>
       </c>
       <c r="F162" s="29" t="n">
-        <v>39.14</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="G162" s="17" t="inlineStr">
         <is>
-          <t>미국 버라이즌-코닝 광섬유 공급 계약에 따른 인프라 수혜.</t>
+          <t>탈모 치료제 관련 특허 보유 사실이 시장에서 부각되었습니다.</t>
         </is>
       </c>
     </row>
     <row r="163" ht="31" customHeight="1" s="15">
       <c r="A163" s="31" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B163" s="31" t="inlineStr">
         <is>
-          <t>범한퓨얼셀</t>
+          <t>삼현</t>
         </is>
       </c>
       <c r="C163" s="31" t="inlineStr">
@@ -5417,7 +5523,7 @@
       </c>
       <c r="D163" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>운송장비·부품</t>
         </is>
       </c>
       <c r="E163" s="14" t="inlineStr">
@@ -5426,23 +5532,23 @@
         </is>
       </c>
       <c r="F163" s="29" t="n">
-        <v>38.89</v>
+        <v>60.31</v>
       </c>
       <c r="G163" s="17" t="inlineStr">
         <is>
-          <t>AI 데이터센터 전력원으로서 연료전지 수요 급증에 따른 수혜.</t>
+          <t>정부의 제조업 AI 전환 정책 및 스마트 액추에이터 기술력 부각입니다.</t>
         </is>
       </c>
     </row>
     <row r="164" ht="31" customHeight="1" s="15">
       <c r="A164" s="31" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B164" s="31" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>하이젠알앤엠</t>
         </is>
       </c>
       <c r="C164" s="31" t="inlineStr">
@@ -5461,23 +5567,23 @@
         </is>
       </c>
       <c r="F164" s="29" t="n">
-        <v>77.31999999999999</v>
+        <v>58.67</v>
       </c>
       <c r="G164" s="17" t="inlineStr">
         <is>
-          <t>AI 데이터센터 및 ESS 시장 확대에 따른 MLCC 매출 증가 기대감으로 상한가 기록.</t>
+          <t>정부의 제조업 AI 전환 정책 및 로봇 핵심 부품 기술력이 부각되었습니다.</t>
         </is>
       </c>
     </row>
     <row r="165" ht="31" customHeight="1" s="15">
       <c r="A165" s="31" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B165" s="31" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>빛샘전자</t>
         </is>
       </c>
       <c r="C165" s="31" t="inlineStr">
@@ -5487,7 +5593,7 @@
       </c>
       <c r="D165" s="35" t="inlineStr">
         <is>
-          <t>IT 서비스</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="E165" s="14" t="inlineStr">
@@ -5496,23 +5602,23 @@
         </is>
       </c>
       <c r="F165" s="29" t="n">
-        <v>55.12</v>
+        <v>61.26</v>
       </c>
       <c r="G165" s="17" t="inlineStr">
         <is>
-          <t>엔비디아 CEO의 사이버 보안 강조 발언에 따른 보안 솔루션 수요 증가 기대감으로 상한가.</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="31" customHeight="1" s="15">
+          <t>AI 데이터센터 인프라 확장에 따른 광통신 부품 수요 기대감.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="44.5" customHeight="1" s="15">
       <c r="A166" s="31" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B166" s="31" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>우리로 (2회)</t>
         </is>
       </c>
       <c r="C166" s="31" t="inlineStr">
@@ -5522,7 +5628,7 @@
       </c>
       <c r="D166" s="35" t="inlineStr">
         <is>
-          <t>IT 서비스</t>
+          <t>유통</t>
         </is>
       </c>
       <c r="E166" s="14" t="inlineStr">
@@ -5531,23 +5637,24 @@
         </is>
       </c>
       <c r="F166" s="29" t="n">
-        <v>52.28</v>
+        <v>59.23</v>
       </c>
       <c r="G166" s="17" t="inlineStr">
         <is>
-          <t>엔비디아 CEO의 사이버 보안 핵심 시장 언급에 따른 보안주 수혜 기대감으로 상한가.</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="31" customHeight="1" s="15">
+          <t>AI 데이터센터 확대에 따른 광통신 수혜 기대.
+(09-09) 미국 양자컴퓨터 투자 및 AI 광통신 관련주로 시장 관심 집중.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="44.5" customHeight="1" s="15">
       <c r="A167" s="31" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B167" s="31" t="inlineStr">
         <is>
-          <t>카티스</t>
+          <t>앤씨앤 (2회)</t>
         </is>
       </c>
       <c r="C167" s="31" t="inlineStr">
@@ -5557,7 +5664,7 @@
       </c>
       <c r="D167" s="35" t="inlineStr">
         <is>
-          <t>IT 서비스</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="E167" s="14" t="inlineStr">
@@ -5566,23 +5673,24 @@
         </is>
       </c>
       <c r="F167" s="29" t="n">
-        <v>47.47</v>
+        <v>57.91</v>
       </c>
       <c r="G167" s="17" t="inlineStr">
         <is>
-          <t>사상 최대 수주잔고 확보 및 AI 데이터센터 수주 확대에 따른 실적 턴어라운드 기대.</t>
-        </is>
-      </c>
-    </row>
-    <row r="168" ht="31" customHeight="1" s="15">
+          <t>비투엔의 경영권 인수 추진 소식에 따른 급등.
+(09-17) 경영권 인수 및 유상증자 결정이라는 기업 지배구조 변화 재료로 상한가 기록.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="15" customHeight="1" s="15">
       <c r="A168" s="31" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B168" s="31" t="inlineStr">
         <is>
-          <t>삼익제약</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="C168" s="31" t="inlineStr">
@@ -5592,7 +5700,7 @@
       </c>
       <c r="D168" s="35" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="E168" s="14" t="inlineStr">
@@ -5601,33 +5709,33 @@
         </is>
       </c>
       <c r="F168" s="29" t="n">
-        <v>69.56999999999999</v>
+        <v>57.54</v>
       </c>
       <c r="G168" s="17" t="inlineStr">
         <is>
-          <t>탈모 치료제 관련 특허 보유 사실이 시장에서 부각되었습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="169" ht="31" customHeight="1" s="15">
+          <t>AI 데이터센터 투자 확대에 따른 전송 수요 증가.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="44.5" customHeight="1" s="15">
       <c r="A169" s="31" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B169" s="31" t="inlineStr">
         <is>
-          <t>삼현</t>
+          <t>가온전선 (2회)</t>
         </is>
       </c>
       <c r="C169" s="31" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="D169" s="35" t="inlineStr">
         <is>
-          <t>운송장비·부품</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="E169" s="14" t="inlineStr">
@@ -5636,23 +5744,24 @@
         </is>
       </c>
       <c r="F169" s="29" t="n">
-        <v>60.31</v>
+        <v>51.31</v>
       </c>
       <c r="G169" s="17" t="inlineStr">
         <is>
-          <t>정부의 제조업 AI 전환 정책 및 스마트 액추에이터 기술력 부각입니다.</t>
+          <t>아마존 데이터센터용 전력장비 공급 계약 체결.
+(09-09) 캐나다 공공 전력망 시장 첫 진출 및 북미 사업 확대 가시화.</t>
         </is>
       </c>
     </row>
     <row r="170" ht="31" customHeight="1" s="15">
       <c r="A170" s="31" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B170" s="31" t="inlineStr">
         <is>
-          <t>하이젠알앤엠</t>
+          <t>토마토시스템</t>
         </is>
       </c>
       <c r="C170" s="31" t="inlineStr">
@@ -5662,7 +5771,7 @@
       </c>
       <c r="D170" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>IT 서비스</t>
         </is>
       </c>
       <c r="E170" s="14" t="inlineStr">
@@ -5671,23 +5780,23 @@
         </is>
       </c>
       <c r="F170" s="29" t="n">
-        <v>58.67</v>
+        <v>57.42</v>
       </c>
       <c r="G170" s="17" t="inlineStr">
         <is>
-          <t>정부의 제조업 AI 전환 정책 및 로봇 핵심 부품 기술력이 부각되었습니다.</t>
+          <t>투자한 미국 보험사의 사업 최종 승인이라는 확실한 대형 호재로 상한가를 기록함.</t>
         </is>
       </c>
     </row>
     <row r="171" ht="31" customHeight="1" s="15">
       <c r="A171" s="31" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B171" s="31" t="inlineStr">
         <is>
-          <t>빛샘전자</t>
+          <t>시그네틱스</t>
         </is>
       </c>
       <c r="C171" s="31" t="inlineStr">
@@ -5706,23 +5815,23 @@
         </is>
       </c>
       <c r="F171" s="29" t="n">
-        <v>61.26</v>
+        <v>35.92</v>
       </c>
       <c r="G171" s="17" t="inlineStr">
         <is>
-          <t>AI 데이터센터 인프라 확장에 따른 광통신 부품 수요 기대감.</t>
-        </is>
-      </c>
-    </row>
-    <row r="172" ht="44.5" customHeight="1" s="15">
+          <t>AI 시장 확대에 따른 첨단 패키징 수요 급증이라는 산업적 호재로 상한가를 기록함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="31" customHeight="1" s="15">
       <c r="A172" s="31" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B172" s="31" t="inlineStr">
         <is>
-          <t>우리로 (2회)</t>
+          <t>인벤테라</t>
         </is>
       </c>
       <c r="C172" s="31" t="inlineStr">
@@ -5732,7 +5841,7 @@
       </c>
       <c r="D172" s="35" t="inlineStr">
         <is>
-          <t>유통</t>
+          <t>일반서비스</t>
         </is>
       </c>
       <c r="E172" s="14" t="inlineStr">
@@ -5741,24 +5850,23 @@
         </is>
       </c>
       <c r="F172" s="29" t="n">
-        <v>59.23</v>
+        <v>19.61</v>
       </c>
       <c r="G172" s="17" t="inlineStr">
         <is>
-          <t>AI 데이터센터 확대에 따른 광통신 수혜 기대.
-(09-09) 미국 양자컴퓨터 투자 및 AI 광통신 관련주로 시장 관심 집중.</t>
-        </is>
-      </c>
-    </row>
-    <row r="173" ht="44.5" customHeight="1" s="15">
+          <t>조영제 임상 3상 결과 발표라는 제약·바이오 분야의 핵심적 성과가 주가 급등을 견인함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="31" customHeight="1" s="15">
       <c r="A173" s="31" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B173" s="31" t="inlineStr">
         <is>
-          <t>앤씨앤 (2회)</t>
+          <t>비트플래닛</t>
         </is>
       </c>
       <c r="C173" s="31" t="inlineStr">
@@ -5768,7 +5876,7 @@
       </c>
       <c r="D173" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>IT 서비스</t>
         </is>
       </c>
       <c r="E173" s="14" t="inlineStr">
@@ -5777,24 +5885,23 @@
         </is>
       </c>
       <c r="F173" s="29" t="n">
-        <v>57.91</v>
+        <v>12.31</v>
       </c>
       <c r="G173" s="17" t="inlineStr">
         <is>
-          <t>비투엔의 경영권 인수 추진 소식에 따른 급등.
-(09-17) 경영권 인수 및 유상증자 결정이라는 기업 지배구조 변화 재료로 상한가 기록.</t>
+          <t>비트코인 가격 반등 및 규제 정비 기대감이라는 시장 모멘텀으로 상한가를 기록함.</t>
         </is>
       </c>
     </row>
     <row r="174" ht="15" customHeight="1" s="15">
       <c r="A174" s="31" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B174" s="31" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>노타</t>
         </is>
       </c>
       <c r="C174" s="31" t="inlineStr">
@@ -5804,68 +5911,67 @@
       </c>
       <c r="D174" s="35" t="inlineStr">
         <is>
+          <t>IT 서비스</t>
+        </is>
+      </c>
+      <c r="E174" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="F174" s="29" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="G174" s="17" t="inlineStr">
+        <is>
+          <t>퀄컴 칩 기반 휴머노이드 AI 가속 기술 부각.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="31" customHeight="1" s="15">
+      <c r="A175" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B175" s="31" t="inlineStr">
+        <is>
+          <t>우리넷</t>
+        </is>
+      </c>
+      <c r="C175" s="31" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D175" s="35" t="inlineStr">
+        <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="E174" s="14" t="inlineStr">
+      <c r="E175" s="14" t="inlineStr">
         <is>
           <t>★★★★★</t>
         </is>
       </c>
-      <c r="F174" s="29" t="n">
-        <v>57.54</v>
-      </c>
-      <c r="G174" s="17" t="inlineStr">
-        <is>
-          <t>AI 데이터센터 투자 확대에 따른 전송 수요 증가.</t>
-        </is>
-      </c>
-    </row>
-    <row r="175" ht="44.5" customHeight="1" s="15">
-      <c r="A175" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B175" s="31" t="inlineStr">
-        <is>
-          <t>가온전선 (2회)</t>
-        </is>
-      </c>
-      <c r="C175" s="31" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D175" s="35" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="E175" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
       <c r="F175" s="29" t="n">
-        <v>51.31</v>
+        <v>62.47</v>
       </c>
       <c r="G175" s="17" t="inlineStr">
         <is>
-          <t>아마존 데이터센터용 전력장비 공급 계약 체결.
-(09-09) 캐나다 공공 전력망 시장 첫 진출 및 북미 사업 확대 가시화.</t>
+          <t>양자암호 전송장비 수요 확대 및 실적 턴어라운드 기대감으로 상한가 기록.</t>
         </is>
       </c>
     </row>
     <row r="176" ht="31" customHeight="1" s="15">
       <c r="A176" s="31" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B176" s="31" t="inlineStr">
         <is>
-          <t>토마토시스템</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="C176" s="31" t="inlineStr">
@@ -5875,7 +5981,7 @@
       </c>
       <c r="D176" s="35" t="inlineStr">
         <is>
-          <t>IT 서비스</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="E176" s="14" t="inlineStr">
@@ -5884,33 +5990,33 @@
         </is>
       </c>
       <c r="F176" s="29" t="n">
-        <v>57.42</v>
+        <v>23.9</v>
       </c>
       <c r="G176" s="17" t="inlineStr">
         <is>
-          <t>투자한 미국 보험사의 사업 최종 승인이라는 확실한 대형 호재로 상한가를 기록함.</t>
+          <t>메타의 AI 에이전트 '뮤즈' 흥행에 따른 eSSD 컨트롤러 공급 수혜 기대감.</t>
         </is>
       </c>
     </row>
     <row r="177" ht="31" customHeight="1" s="15">
       <c r="A177" s="31" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B177" s="31" t="inlineStr">
         <is>
-          <t>시그네틱스</t>
+          <t>KSS해운</t>
         </is>
       </c>
       <c r="C177" s="31" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="D177" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>운송·창고</t>
         </is>
       </c>
       <c r="E177" s="14" t="inlineStr">
@@ -5919,373 +6025,151 @@
         </is>
       </c>
       <c r="F177" s="29" t="n">
-        <v>35.92</v>
+        <v>18.01</v>
       </c>
       <c r="G177" s="17" t="inlineStr">
         <is>
-          <t>AI 시장 확대에 따른 첨단 패키징 수요 급증이라는 산업적 호재로 상한가를 기록함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="31" customHeight="1" s="15">
-      <c r="A178" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B178" s="31" t="inlineStr">
-        <is>
-          <t>인벤테라</t>
-        </is>
-      </c>
-      <c r="C178" s="31" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D178" s="35" t="inlineStr">
-        <is>
-          <t>일반서비스</t>
-        </is>
-      </c>
-      <c r="E178" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="F178" s="29" t="n">
-        <v>19.61</v>
-      </c>
-      <c r="G178" s="17" t="inlineStr">
-        <is>
-          <t>조영제 임상 3상 결과 발표라는 제약·바이오 분야의 핵심적 성과가 주가 급등을 견인함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="179" ht="31" customHeight="1" s="15">
-      <c r="A179" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B179" s="31" t="inlineStr">
-        <is>
-          <t>비트플래닛</t>
-        </is>
-      </c>
-      <c r="C179" s="31" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D179" s="35" t="inlineStr">
-        <is>
-          <t>IT 서비스</t>
-        </is>
-      </c>
-      <c r="E179" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="F179" s="29" t="n">
-        <v>12.31</v>
-      </c>
-      <c r="G179" s="17" t="inlineStr">
-        <is>
-          <t>비트코인 가격 반등 및 규제 정비 기대감이라는 시장 모멘텀으로 상한가를 기록함.</t>
-        </is>
-      </c>
+          <t>약 200억 원 규모의 대규모 자사주 매입 결정에 따른 주주가치 제고 기대감.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178"/>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>다음 달 프리뷰</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="inlineStr"/>
+      <c r="D179" s="3" t="inlineStr"/>
+      <c r="E179" s="3" t="inlineStr"/>
+      <c r="F179" s="3" t="inlineStr"/>
+      <c r="G179" s="3" t="inlineStr"/>
+      <c r="H179" s="3" t="inlineStr"/>
+      <c r="I179" s="3" t="inlineStr"/>
+      <c r="J179" s="3" t="inlineStr"/>
+      <c r="K179" s="3" t="inlineStr"/>
     </row>
     <row r="180" ht="15" customHeight="1" s="15">
-      <c r="A180" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B180" s="31" t="inlineStr">
-        <is>
-          <t>노타</t>
-        </is>
-      </c>
-      <c r="C180" s="31" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D180" s="35" t="inlineStr">
-        <is>
-          <t>IT 서비스</t>
-        </is>
-      </c>
-      <c r="E180" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="F180" s="29" t="n">
-        <v>9.15</v>
-      </c>
-      <c r="G180" s="17" t="inlineStr">
-        <is>
-          <t>퀄컴 칩 기반 휴머노이드 AI 가속 기술 부각.</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="31" customHeight="1" s="15">
-      <c r="A181" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B181" s="31" t="inlineStr">
-        <is>
-          <t>우리넷</t>
-        </is>
-      </c>
-      <c r="C181" s="31" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D181" s="35" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="E181" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="F181" s="29" t="n">
-        <v>62.47</v>
-      </c>
-      <c r="G181" s="17" t="inlineStr">
-        <is>
-          <t>양자암호 전송장비 수요 확대 및 실적 턴어라운드 기대감으로 상한가 기록.</t>
-        </is>
-      </c>
-    </row>
-    <row r="182" ht="31" customHeight="1" s="15">
-      <c r="A182" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B182" s="31" t="inlineStr">
-        <is>
-          <t>파두</t>
-        </is>
-      </c>
-      <c r="C182" s="31" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D182" s="35" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="E182" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="F182" s="29" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="G182" s="17" t="inlineStr">
-        <is>
-          <t>메타의 AI 에이전트 '뮤즈' 흥행에 따른 eSSD 컨트롤러 공급 수혜 기대감.</t>
-        </is>
-      </c>
-    </row>
-    <row r="183" ht="31" customHeight="1" s="15">
-      <c r="A183" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B183" s="31" t="inlineStr">
-        <is>
-          <t>KSS해운</t>
-        </is>
-      </c>
-      <c r="C183" s="31" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D183" s="35" t="inlineStr">
-        <is>
-          <t>운송·창고</t>
-        </is>
-      </c>
-      <c r="E183" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="F183" s="29" t="n">
-        <v>18.01</v>
-      </c>
-      <c r="G183" s="17" t="inlineStr">
-        <is>
-          <t>약 200억 원 규모의 대규모 자사주 매입 결정에 따른 주주가치 제고 기대감.</t>
-        </is>
-      </c>
-    </row>
-    <row r="184"/>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B185" s="3" t="inlineStr">
-        <is>
-          <t>다음 달 프리뷰</t>
-        </is>
-      </c>
-      <c r="C185" s="3" t="inlineStr"/>
-      <c r="D185" s="3" t="inlineStr"/>
-      <c r="E185" s="3" t="inlineStr"/>
-      <c r="F185" s="3" t="inlineStr"/>
-      <c r="G185" s="3" t="inlineStr"/>
-      <c r="H185" s="3" t="inlineStr"/>
-      <c r="I185" s="3" t="inlineStr"/>
-      <c r="J185" s="3" t="inlineStr"/>
-      <c r="K185" s="3" t="inlineStr"/>
+      <c r="A180" s="17" t="inlineStr">
+        <is>
+          <t>- 반도체 및 AI 밸류체인 중심의 기술주 반등</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="15" customHeight="1" s="15">
+      <c r="A181" s="17" t="inlineStr">
+        <is>
+          <t>- 수출 데이터 개선에 따른 투자 심리 회복</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="15" customHeight="1" s="15">
+      <c r="A182" s="17" t="inlineStr">
+        <is>
+          <t>- 미국 국채금리 급등에 따른 밸류에이션 부담</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="15" customHeight="1" s="15">
+      <c r="A183" s="17" t="inlineStr">
+        <is>
+          <t>- 외국인 수급 이탈 지속</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="15" customHeight="1" s="15">
+      <c r="A184" s="17" t="inlineStr">
+        <is>
+          <t>- 외국인의 순매수 전환 여부가 지수 7,000선 안착의 핵심 신호입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="15" customHeight="1" s="15">
+      <c r="A185" s="17" t="inlineStr">
+        <is>
+          <t>- 10월 1일 한국 수출입 데이터 발표</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="15" customHeight="1" s="15">
       <c r="A186" s="17" t="inlineStr">
         <is>
-          <t>- 미국 고용지표 및 물가지수가 예상치를 하회하며 연준의 긴축 완화 기대감이 커질 경우, 위험자산 선호 심리가 회복될 수 있습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="187" ht="15" customHeight="1" s="15">
-      <c r="A187" s="17" t="inlineStr">
-        <is>
-          <t>- 국내 수출 지표가 견조한 흐름을 이어가고 AI 반도체 수요가 지속될 경우, 기술주 중심의 상승 랠리가 재개될 수 있습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="188" ht="31" customHeight="1" s="15">
-      <c r="A188" s="17" t="inlineStr">
-        <is>
-          <t>- 미국 고용지표 및 물가지수가 예상치를 상회하며 인플레이션 우려가 재부각될 경우, 금리 인상 압력이 커져 시장 전반의 투자 심리가 위축될 수 있습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="189" ht="15" customHeight="1" s="15">
-      <c r="A189" s="17" t="inlineStr">
-        <is>
-          <t>- 국제유가 급등 및 원/달러 환율 상승이 지속될 경우, 기업 실적 악화 우려와 외국인 자금 이탈이 가속화될 수 있습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="190" ht="15" customHeight="1" s="15">
-      <c r="A190" s="17" t="inlineStr">
-        <is>
-          <t>- 미국 고용지표 및 물가지수 발표 결과와 국제유가 및 원/달러 환율 추이가 시장 방향성을 결정하는 핵심 신호가 될 것입니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="191" ht="15" customHeight="1" s="15">
-      <c r="A191" s="17" t="inlineStr">
-        <is>
-          <t>- 2026-10-01 09:00 KST: 한국 수출 전년대비 (중요도 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="192" ht="15" customHeight="1" s="15">
-      <c r="A192" s="17" t="inlineStr">
-        <is>
-          <t>- 2026-10-01 09:00 KST: 한국 수입 전년대비 (중요도 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="193" ht="15" customHeight="1" s="15">
-      <c r="A193" s="17" t="inlineStr">
-        <is>
-          <t>- 2026-10-01 23:00 KST: 미국 ISM 제조업 구매관리자지수(PMI) (중요도 4)</t>
+          <t>- 10월 1일 미국 ISM 제조업 PMI 발표</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="95">
+  <mergeCells count="88">
+    <mergeCell ref="G158:K158"/>
+    <mergeCell ref="B84:K84"/>
     <mergeCell ref="G77:K77"/>
     <mergeCell ref="A186:K186"/>
     <mergeCell ref="G169:K169"/>
-    <mergeCell ref="G178:K178"/>
     <mergeCell ref="G67:K67"/>
-    <mergeCell ref="B142:K142"/>
     <mergeCell ref="G70:K70"/>
-    <mergeCell ref="G116:K116"/>
+    <mergeCell ref="G125:K125"/>
     <mergeCell ref="G127:K127"/>
     <mergeCell ref="G167:K167"/>
     <mergeCell ref="A149:K149"/>
+    <mergeCell ref="A113:E113"/>
     <mergeCell ref="A129:E129"/>
+    <mergeCell ref="A85:K85"/>
     <mergeCell ref="G65:K65"/>
     <mergeCell ref="G79:K79"/>
-    <mergeCell ref="A188:K188"/>
     <mergeCell ref="G73:K73"/>
+    <mergeCell ref="A141:K141"/>
     <mergeCell ref="A131:E131"/>
+    <mergeCell ref="G153:K153"/>
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="G129:K129"/>
-    <mergeCell ref="A190:K190"/>
     <mergeCell ref="A115:E115"/>
     <mergeCell ref="G173:K173"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="G131:K131"/>
-    <mergeCell ref="G115:K115"/>
-    <mergeCell ref="A191:K191"/>
+    <mergeCell ref="G155:K155"/>
+    <mergeCell ref="A142:K142"/>
+    <mergeCell ref="A182:K182"/>
     <mergeCell ref="A119:E119"/>
     <mergeCell ref="G170:K170"/>
-    <mergeCell ref="G179:K179"/>
-    <mergeCell ref="A88:K88"/>
-    <mergeCell ref="B85:K85"/>
+    <mergeCell ref="G157:K157"/>
     <mergeCell ref="G166:K166"/>
-    <mergeCell ref="A153:K153"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="G172:K172"/>
+    <mergeCell ref="A137:K137"/>
     <mergeCell ref="A133:E133"/>
     <mergeCell ref="G69:K69"/>
     <mergeCell ref="G78:K78"/>
-    <mergeCell ref="A192:K192"/>
     <mergeCell ref="A145:K145"/>
-    <mergeCell ref="A139:K139"/>
-    <mergeCell ref="A154:K154"/>
     <mergeCell ref="G133:K133"/>
     <mergeCell ref="G80:K80"/>
+    <mergeCell ref="A181:K181"/>
     <mergeCell ref="G64:K64"/>
     <mergeCell ref="G135:K135"/>
+    <mergeCell ref="A184:K184"/>
+    <mergeCell ref="A180:K180"/>
     <mergeCell ref="G159:K159"/>
-    <mergeCell ref="A155:K155"/>
     <mergeCell ref="G164:K164"/>
     <mergeCell ref="A143:K143"/>
     <mergeCell ref="G161:K161"/>
     <mergeCell ref="A1:G2"/>
     <mergeCell ref="A123:E123"/>
-    <mergeCell ref="G82:K82"/>
     <mergeCell ref="G174:K174"/>
+    <mergeCell ref="G156:K156"/>
     <mergeCell ref="A87:K87"/>
     <mergeCell ref="G66:K66"/>
-    <mergeCell ref="A193:K193"/>
-    <mergeCell ref="A89:K89"/>
     <mergeCell ref="G74:K74"/>
+    <mergeCell ref="B140:K140"/>
     <mergeCell ref="G68:K68"/>
-    <mergeCell ref="G180:K180"/>
-    <mergeCell ref="A135:E135"/>
+    <mergeCell ref="A185:K185"/>
     <mergeCell ref="G168:K168"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="G182:K182"/>
     <mergeCell ref="A125:E125"/>
-    <mergeCell ref="A147:K147"/>
-    <mergeCell ref="A156:K156"/>
     <mergeCell ref="A121:E121"/>
     <mergeCell ref="A127:E127"/>
     <mergeCell ref="G72:K72"/>
@@ -6293,22 +6177,20 @@
     <mergeCell ref="A148:K148"/>
     <mergeCell ref="G71:K71"/>
     <mergeCell ref="G176:K176"/>
-    <mergeCell ref="A146:K146"/>
-    <mergeCell ref="G181:K181"/>
     <mergeCell ref="G160:K160"/>
-    <mergeCell ref="A187:K187"/>
     <mergeCell ref="G175:K175"/>
+    <mergeCell ref="A183:K183"/>
     <mergeCell ref="G162:K162"/>
-    <mergeCell ref="G137:K137"/>
     <mergeCell ref="G171:K171"/>
-    <mergeCell ref="A189:K189"/>
     <mergeCell ref="G177:K177"/>
     <mergeCell ref="A86:K86"/>
+    <mergeCell ref="G114:K114"/>
+    <mergeCell ref="G154:K154"/>
+    <mergeCell ref="A150:K150"/>
     <mergeCell ref="G163:K163"/>
     <mergeCell ref="A144:K144"/>
+    <mergeCell ref="G113:K113"/>
     <mergeCell ref="G76:K76"/>
-    <mergeCell ref="A152:K152"/>
-    <mergeCell ref="G183:K183"/>
     <mergeCell ref="G165:K165"/>
     <mergeCell ref="A117:E117"/>
     <mergeCell ref="G75:K75"/>
@@ -6323,7 +6205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.5" customWidth="1" style="15" min="1" max="1"/>
@@ -6353,7 +6235,7 @@
       </c>
       <c r="K1" s="25" t="inlineStr">
         <is>
-          <t>2026-09-01 ~ 2026-09-24</t>
+          <t>2026-09-01 ~ 2026-09-23</t>
         </is>
       </c>
     </row>
@@ -6466,83 +6348,83 @@
     <row r="6">
       <c r="A6" s="31" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
-        </is>
-      </c>
-      <c r="B6" s="30" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
+          <t>와이즈플래닛컴퍼니</t>
+        </is>
+      </c>
+      <c r="B6" s="30" t="inlineStr"/>
       <c r="C6" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>화학</t>
         </is>
       </c>
       <c r="D6" s="45" t="n">
-        <v>673</v>
-      </c>
-      <c r="E6" s="46" t="n">
-        <v>-3380</v>
+        <v>-91</v>
+      </c>
+      <c r="E6" s="45" t="n">
+        <v>-5</v>
       </c>
       <c r="F6" s="45" t="n">
-        <v>4052</v>
+        <v>-86</v>
       </c>
       <c r="G6" s="46" t="n">
-        <v>-1319</v>
-      </c>
-      <c r="H6" s="47" t="n">
-        <v>1151.7</v>
-      </c>
-      <c r="I6" s="47" t="n">
-        <v>28532.1</v>
-      </c>
-      <c r="J6" s="48" t="n">
-        <v>7025</v>
-      </c>
-      <c r="K6" s="49" t="n">
-        <v>19.03</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H6" s="47" t="inlineStr"/>
+      <c r="I6" s="47" t="inlineStr"/>
+      <c r="J6" s="48" t="inlineStr"/>
+      <c r="K6" s="49" t="inlineStr"/>
       <c r="L6" s="50" t="n">
-        <v>-9.68</v>
+        <v>-5.26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="31" t="inlineStr">
         <is>
-          <t>와이즈플래닛컴퍼니</t>
-        </is>
-      </c>
-      <c r="B7" s="30" t="inlineStr"/>
+          <t>신한지주</t>
+        </is>
+      </c>
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
       <c r="C7" s="35" t="inlineStr">
         <is>
-          <t>화학</t>
-        </is>
-      </c>
-      <c r="D7" s="46" t="n">
-        <v>-183</v>
-      </c>
-      <c r="E7" s="46" t="n">
-        <v>-11</v>
-      </c>
-      <c r="F7" s="46" t="n">
-        <v>-172</v>
-      </c>
-      <c r="G7" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="47" t="inlineStr"/>
-      <c r="I7" s="47" t="inlineStr"/>
-      <c r="J7" s="52" t="inlineStr"/>
-      <c r="K7" s="53" t="inlineStr"/>
+          <t>기타금융</t>
+        </is>
+      </c>
+      <c r="D7" s="51" t="n">
+        <v>579</v>
+      </c>
+      <c r="E7" s="45" t="n">
+        <v>-2077</v>
+      </c>
+      <c r="F7" s="51" t="n">
+        <v>2656</v>
+      </c>
+      <c r="G7" s="45" t="n">
+        <v>-238</v>
+      </c>
+      <c r="H7" s="47" t="n">
+        <v>2390</v>
+      </c>
+      <c r="I7" s="47" t="n">
+        <v>7455.8</v>
+      </c>
+      <c r="J7" s="52" t="n">
+        <v>339.1</v>
+      </c>
+      <c r="K7" s="53" t="n">
+        <v>1.01</v>
+      </c>
       <c r="L7" s="50" t="n">
-        <v>-5.03</v>
+        <v>-6.3</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>대한항공</t>
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>하나금융지주</t>
         </is>
       </c>
       <c r="B8" s="30" t="inlineStr">
@@ -6552,85 +6434,85 @@
       </c>
       <c r="C8" s="35" t="inlineStr">
         <is>
-          <t>운송·창고</t>
+          <t>기타금융</t>
         </is>
       </c>
       <c r="D8" s="45" t="n">
-        <v>3607</v>
+        <v>-36</v>
       </c>
       <c r="E8" s="45" t="n">
-        <v>2887</v>
-      </c>
-      <c r="F8" s="45" t="n">
-        <v>720</v>
-      </c>
-      <c r="G8" s="46" t="n">
-        <v>-3530</v>
+        <v>-1008</v>
+      </c>
+      <c r="F8" s="51" t="n">
+        <v>972</v>
+      </c>
+      <c r="G8" s="51" t="n">
+        <v>49</v>
       </c>
       <c r="H8" s="47" t="n">
-        <v>304.9</v>
+        <v>1113.8</v>
       </c>
       <c r="I8" s="47" t="n">
-        <v>1997.5</v>
-      </c>
-      <c r="J8" s="48" t="n">
-        <v>328.8</v>
-      </c>
-      <c r="K8" s="49" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="L8" s="54" t="n">
-        <v>-1.9</v>
+        <v>7059.1</v>
+      </c>
+      <c r="J8" s="54" t="n">
+        <v>-766.3</v>
+      </c>
+      <c r="K8" s="55" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="L8" s="50" t="n">
+        <v>-6.82</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="31" t="inlineStr">
         <is>
-          <t>신한지주</t>
+          <t>메가터치</t>
         </is>
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="C9" s="35" t="inlineStr">
         <is>
-          <t>기타금융</t>
-        </is>
-      </c>
-      <c r="D9" s="45" t="n">
-        <v>579</v>
-      </c>
-      <c r="E9" s="46" t="n">
-        <v>-2077</v>
-      </c>
-      <c r="F9" s="45" t="n">
-        <v>2656</v>
-      </c>
-      <c r="G9" s="46" t="n">
-        <v>-238</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D9" s="51" t="n">
+        <v>44</v>
+      </c>
+      <c r="E9" s="51" t="n">
+        <v>23</v>
+      </c>
+      <c r="F9" s="51" t="n">
+        <v>21</v>
+      </c>
+      <c r="G9" s="45" t="n">
+        <v>-42</v>
       </c>
       <c r="H9" s="47" t="n">
-        <v>2390</v>
+        <v>14.3</v>
       </c>
       <c r="I9" s="47" t="n">
-        <v>7455.8</v>
-      </c>
-      <c r="J9" s="48" t="n">
-        <v>339.1</v>
-      </c>
-      <c r="K9" s="49" t="n">
-        <v>1.01</v>
+        <v>52.9</v>
+      </c>
+      <c r="J9" s="52" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="K9" s="53" t="n">
+        <v>52.95</v>
       </c>
       <c r="L9" s="50" t="n">
-        <v>-5.81</v>
+        <v>-6.29</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="31" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="B10" s="30" t="inlineStr">
@@ -6640,85 +6522,85 @@
       </c>
       <c r="C10" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="D10" s="45" t="n">
-        <v>568</v>
-      </c>
-      <c r="E10" s="45" t="n">
-        <v>155</v>
-      </c>
-      <c r="F10" s="45" t="n">
-        <v>413</v>
-      </c>
-      <c r="G10" s="46" t="n">
-        <v>-536</v>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="D10" s="51" t="n">
+        <v>33</v>
+      </c>
+      <c r="E10" s="51" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="51" t="n">
+        <v>29</v>
+      </c>
+      <c r="G10" s="45" t="n">
+        <v>-34</v>
       </c>
       <c r="H10" s="47" t="n">
-        <v>1715.5</v>
+        <v>14</v>
       </c>
       <c r="I10" s="47" t="n">
-        <v>9939.5</v>
-      </c>
-      <c r="J10" s="48" t="n">
-        <v>982.4</v>
-      </c>
-      <c r="K10" s="49" t="n">
-        <v>16.63</v>
-      </c>
-      <c r="L10" s="50" t="n">
-        <v>-9.91</v>
+        <v>103.7</v>
+      </c>
+      <c r="J10" s="52" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="K10" s="53" t="n">
+        <v>36.74</v>
+      </c>
+      <c r="L10" s="56" t="n">
+        <v>-3.51</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="31" t="inlineStr">
         <is>
-          <t>하나금융지주</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="B11" s="30" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="C11" s="35" t="inlineStr">
         <is>
-          <t>기타금융</t>
-        </is>
-      </c>
-      <c r="D11" s="46" t="n">
-        <v>-36</v>
-      </c>
-      <c r="E11" s="46" t="n">
-        <v>-1008</v>
-      </c>
-      <c r="F11" s="45" t="n">
-        <v>972</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D11" s="51" t="n">
+        <v>194</v>
+      </c>
+      <c r="E11" s="51" t="n">
+        <v>104</v>
+      </c>
+      <c r="F11" s="51" t="n">
+        <v>90</v>
       </c>
       <c r="G11" s="45" t="n">
-        <v>49</v>
+        <v>-201</v>
       </c>
       <c r="H11" s="47" t="n">
-        <v>1113.8</v>
+        <v>163.9</v>
       </c>
       <c r="I11" s="47" t="n">
-        <v>7059.1</v>
-      </c>
-      <c r="J11" s="55" t="n">
-        <v>-766.3</v>
-      </c>
-      <c r="K11" s="56" t="n">
-        <v>-0.96</v>
-      </c>
-      <c r="L11" s="50" t="n">
-        <v>-6.58</v>
+        <v>723.6</v>
+      </c>
+      <c r="J11" s="52" t="n">
+        <v>118.3</v>
+      </c>
+      <c r="K11" s="53" t="n">
+        <v>20</v>
+      </c>
+      <c r="L11" s="56" t="n">
+        <v>-3.39</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="31" t="inlineStr">
         <is>
-          <t>메가터치</t>
+          <t>뉴파워프라즈마</t>
         </is>
       </c>
       <c r="B12" s="30" t="inlineStr">
@@ -6728,41 +6610,41 @@
       </c>
       <c r="C12" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="D12" s="45" t="n">
-        <v>44</v>
-      </c>
-      <c r="E12" s="45" t="n">
-        <v>23</v>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="D12" s="51" t="n">
+        <v>70</v>
+      </c>
+      <c r="E12" s="51" t="n">
+        <v>93</v>
       </c>
       <c r="F12" s="45" t="n">
-        <v>21</v>
-      </c>
-      <c r="G12" s="46" t="n">
-        <v>-42</v>
+        <v>-22</v>
+      </c>
+      <c r="G12" s="45" t="n">
+        <v>-49</v>
       </c>
       <c r="H12" s="47" t="n">
-        <v>14.3</v>
+        <v>60.7</v>
       </c>
       <c r="I12" s="47" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="J12" s="48" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="K12" s="49" t="n">
-        <v>52.95</v>
-      </c>
-      <c r="L12" s="50" t="n">
-        <v>-7.07</v>
+        <v>176.7</v>
+      </c>
+      <c r="J12" s="52" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="K12" s="53" t="n">
+        <v>36.68</v>
+      </c>
+      <c r="L12" s="56" t="n">
+        <v>-4.08</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="31" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>마이크로컨텍솔</t>
         </is>
       </c>
       <c r="B13" s="30" t="inlineStr">
@@ -6772,41 +6654,41 @@
       </c>
       <c r="C13" s="35" t="inlineStr">
         <is>
-          <t>기계·장비</t>
-        </is>
-      </c>
-      <c r="D13" s="45" t="n">
-        <v>33</v>
-      </c>
-      <c r="E13" s="45" t="n">
-        <v>3</v>
-      </c>
-      <c r="F13" s="45" t="n">
-        <v>29</v>
-      </c>
-      <c r="G13" s="46" t="n">
-        <v>-34</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D13" s="51" t="n">
+        <v>137</v>
+      </c>
+      <c r="E13" s="51" t="n">
+        <v>124</v>
+      </c>
+      <c r="F13" s="51" t="n">
+        <v>13</v>
+      </c>
+      <c r="G13" s="45" t="n">
+        <v>-199</v>
       </c>
       <c r="H13" s="47" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I13" s="47" t="n">
-        <v>103.7</v>
-      </c>
-      <c r="J13" s="48" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="K13" s="49" t="n">
-        <v>36.74</v>
+        <v>199.1</v>
+      </c>
+      <c r="J13" s="52" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="K13" s="53" t="n">
+        <v>40.77</v>
       </c>
       <c r="L13" s="50" t="n">
-        <v>-5.27</v>
+        <v>-6.54</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="31" t="inlineStr">
         <is>
-          <t>오킨스전자</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B14" s="30" t="inlineStr">
@@ -6816,129 +6698,129 @@
       </c>
       <c r="C14" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="D14" s="45" t="n">
-        <v>106</v>
-      </c>
-      <c r="E14" s="46" t="n">
-        <v>-7</v>
-      </c>
-      <c r="F14" s="45" t="n">
-        <v>113</v>
-      </c>
-      <c r="G14" s="46" t="n">
-        <v>-80</v>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="D14" s="51" t="n">
+        <v>339</v>
+      </c>
+      <c r="E14" s="51" t="n">
+        <v>241</v>
+      </c>
+      <c r="F14" s="51" t="n">
+        <v>98</v>
+      </c>
+      <c r="G14" s="45" t="n">
+        <v>-271</v>
       </c>
       <c r="H14" s="47" t="n">
-        <v>43.3</v>
+        <v>113.5</v>
       </c>
       <c r="I14" s="47" t="n">
-        <v>258.2</v>
-      </c>
-      <c r="J14" s="48" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="K14" s="49" t="n">
-        <v>19.29</v>
+        <v>878.1</v>
+      </c>
+      <c r="J14" s="52" t="n">
+        <v>313.3</v>
+      </c>
+      <c r="K14" s="53" t="n">
+        <v>64.92</v>
       </c>
       <c r="L14" s="50" t="n">
-        <v>-9.779999999999999</v>
+        <v>-5.44</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="31" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>코웨이</t>
         </is>
       </c>
       <c r="B15" s="30" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="C15" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="D15" s="45" t="n">
-        <v>194</v>
+          <t>일반서비스</t>
+        </is>
+      </c>
+      <c r="D15" s="51" t="n">
+        <v>11</v>
       </c>
       <c r="E15" s="45" t="n">
-        <v>104</v>
-      </c>
-      <c r="F15" s="45" t="n">
-        <v>90</v>
-      </c>
-      <c r="G15" s="46" t="n">
-        <v>-201</v>
+        <v>-261</v>
+      </c>
+      <c r="F15" s="51" t="n">
+        <v>272</v>
+      </c>
+      <c r="G15" s="45" t="n">
+        <v>-108</v>
       </c>
       <c r="H15" s="47" t="n">
-        <v>163.9</v>
+        <v>346.9</v>
       </c>
       <c r="I15" s="47" t="n">
-        <v>723.6</v>
-      </c>
-      <c r="J15" s="48" t="n">
-        <v>118.3</v>
-      </c>
-      <c r="K15" s="49" t="n">
-        <v>20</v>
-      </c>
-      <c r="L15" s="57" t="n">
-        <v>-3.39</v>
+        <v>882</v>
+      </c>
+      <c r="J15" s="54" t="n">
+        <v>-135.5</v>
+      </c>
+      <c r="K15" s="53" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="L15" s="50" t="n">
+        <v>-9.42</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="31" t="inlineStr">
         <is>
-          <t>코웨이</t>
+          <t>샘씨엔에스</t>
         </is>
       </c>
       <c r="B16" s="30" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="C16" s="35" t="inlineStr">
         <is>
-          <t>일반서비스</t>
-        </is>
-      </c>
-      <c r="D16" s="45" t="n">
-        <v>11</v>
-      </c>
-      <c r="E16" s="46" t="n">
-        <v>-261</v>
-      </c>
-      <c r="F16" s="45" t="n">
-        <v>272</v>
-      </c>
-      <c r="G16" s="46" t="n">
-        <v>-108</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D16" s="51" t="n">
+        <v>213</v>
+      </c>
+      <c r="E16" s="51" t="n">
+        <v>93</v>
+      </c>
+      <c r="F16" s="51" t="n">
+        <v>119</v>
+      </c>
+      <c r="G16" s="45" t="n">
+        <v>-191</v>
       </c>
       <c r="H16" s="47" t="n">
-        <v>346.9</v>
+        <v>49.4</v>
       </c>
       <c r="I16" s="47" t="n">
-        <v>882</v>
-      </c>
-      <c r="J16" s="55" t="n">
-        <v>-135.5</v>
-      </c>
-      <c r="K16" s="49" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="L16" s="50" t="n">
-        <v>-9.529999999999999</v>
+        <v>283.3</v>
+      </c>
+      <c r="J16" s="52" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="K16" s="53" t="n">
+        <v>40.39</v>
+      </c>
+      <c r="L16" s="56" t="n">
+        <v>-2.21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="31" t="inlineStr">
         <is>
-          <t>뉴파워프라즈마</t>
+          <t>안랩</t>
         </is>
       </c>
       <c r="B17" s="30" t="inlineStr">
@@ -6948,173 +6830,173 @@
       </c>
       <c r="C17" s="35" t="inlineStr">
         <is>
-          <t>기계·장비</t>
-        </is>
-      </c>
-      <c r="D17" s="45" t="n">
-        <v>70</v>
-      </c>
-      <c r="E17" s="45" t="n">
-        <v>93</v>
-      </c>
-      <c r="F17" s="46" t="n">
-        <v>-22</v>
-      </c>
-      <c r="G17" s="46" t="n">
-        <v>-49</v>
+          <t>IT 서비스</t>
+        </is>
+      </c>
+      <c r="D17" s="51" t="n">
+        <v>239</v>
+      </c>
+      <c r="E17" s="51" t="n">
+        <v>136</v>
+      </c>
+      <c r="F17" s="51" t="n">
+        <v>102</v>
+      </c>
+      <c r="G17" s="45" t="n">
+        <v>-243</v>
       </c>
       <c r="H17" s="47" t="n">
-        <v>60.7</v>
+        <v>42.9</v>
       </c>
       <c r="I17" s="47" t="n">
-        <v>176.7</v>
-      </c>
-      <c r="J17" s="48" t="n">
-        <v>77.8</v>
-      </c>
-      <c r="K17" s="49" t="n">
-        <v>36.68</v>
-      </c>
-      <c r="L17" s="57" t="n">
-        <v>-3.91</v>
+        <v>388.8</v>
+      </c>
+      <c r="J17" s="52" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="K17" s="53" t="n">
+        <v>24.53</v>
+      </c>
+      <c r="L17" s="56" t="n">
+        <v>-2.58</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="31" t="inlineStr">
         <is>
-          <t>마이크로컨텍솔</t>
+          <t>유니퀘스트</t>
         </is>
       </c>
       <c r="B18" s="30" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="C18" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="D18" s="45" t="n">
-        <v>137</v>
-      </c>
-      <c r="E18" s="45" t="n">
-        <v>124</v>
-      </c>
-      <c r="F18" s="45" t="n">
-        <v>13</v>
-      </c>
-      <c r="G18" s="46" t="n">
-        <v>-199</v>
+          <t>유통</t>
+        </is>
+      </c>
+      <c r="D18" s="51" t="n">
+        <v>62</v>
+      </c>
+      <c r="E18" s="51" t="n">
+        <v>50</v>
+      </c>
+      <c r="F18" s="51" t="n">
+        <v>11</v>
+      </c>
+      <c r="G18" s="45" t="n">
+        <v>-63</v>
       </c>
       <c r="H18" s="47" t="n">
-        <v>20</v>
+        <v>4.3</v>
       </c>
       <c r="I18" s="47" t="n">
-        <v>199.1</v>
-      </c>
-      <c r="J18" s="48" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="K18" s="49" t="n">
-        <v>40.77</v>
-      </c>
-      <c r="L18" s="50" t="n">
-        <v>-5.45</v>
+        <v>60.3</v>
+      </c>
+      <c r="J18" s="52" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K18" s="53" t="n">
+        <v>15.09</v>
+      </c>
+      <c r="L18" s="56" t="n">
+        <v>-4.04</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="31" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>드림텍</t>
         </is>
       </c>
       <c r="B19" s="30" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="C19" s="35" t="inlineStr">
         <is>
-          <t>기계·장비</t>
-        </is>
-      </c>
-      <c r="D19" s="45" t="n">
-        <v>339</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D19" s="51" t="n">
+        <v>202</v>
       </c>
       <c r="E19" s="45" t="n">
-        <v>241</v>
-      </c>
-      <c r="F19" s="45" t="n">
-        <v>98</v>
-      </c>
-      <c r="G19" s="46" t="n">
-        <v>-271</v>
+        <v>-86</v>
+      </c>
+      <c r="F19" s="51" t="n">
+        <v>287</v>
+      </c>
+      <c r="G19" s="45" t="n">
+        <v>-200</v>
       </c>
       <c r="H19" s="47" t="n">
-        <v>113.5</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="I19" s="47" t="n">
-        <v>878.1</v>
-      </c>
-      <c r="J19" s="48" t="n">
-        <v>313.3</v>
-      </c>
-      <c r="K19" s="49" t="n">
-        <v>64.92</v>
+        <v>182.1</v>
+      </c>
+      <c r="J19" s="52" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="K19" s="53" t="n">
+        <v>47.31</v>
       </c>
       <c r="L19" s="50" t="n">
-        <v>-5.64</v>
+        <v>-7.93</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>S-Oil우</t>
         </is>
       </c>
       <c r="B20" s="30" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="C20" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="D20" s="45" t="n">
-        <v>213</v>
-      </c>
-      <c r="E20" s="45" t="n">
-        <v>93</v>
-      </c>
-      <c r="F20" s="45" t="n">
-        <v>119</v>
-      </c>
-      <c r="G20" s="46" t="n">
-        <v>-191</v>
+          <t>화학</t>
+        </is>
+      </c>
+      <c r="D20" s="51" t="n">
+        <v>78</v>
+      </c>
+      <c r="E20" s="51" t="n">
+        <v>7</v>
+      </c>
+      <c r="F20" s="51" t="n">
+        <v>70</v>
+      </c>
+      <c r="G20" s="45" t="n">
+        <v>-75</v>
       </c>
       <c r="H20" s="47" t="n">
-        <v>49.4</v>
+        <v>4.2</v>
       </c>
       <c r="I20" s="47" t="n">
-        <v>283.3</v>
-      </c>
-      <c r="J20" s="48" t="n">
-        <v>108.1</v>
-      </c>
-      <c r="K20" s="49" t="n">
-        <v>40.39</v>
-      </c>
-      <c r="L20" s="54" t="n">
-        <v>-1.93</v>
+        <v>211.9</v>
+      </c>
+      <c r="J20" s="52" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="K20" s="53" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="L20" s="57" t="n">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="31" t="inlineStr">
         <is>
-          <t>안랩</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="B21" s="30" t="inlineStr">
@@ -7124,261 +7006,261 @@
       </c>
       <c r="C21" s="35" t="inlineStr">
         <is>
-          <t>IT 서비스</t>
-        </is>
-      </c>
-      <c r="D21" s="45" t="n">
-        <v>239</v>
-      </c>
-      <c r="E21" s="45" t="n">
-        <v>136</v>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="D21" s="51" t="n">
+        <v>104</v>
+      </c>
+      <c r="E21" s="51" t="n">
+        <v>143</v>
       </c>
       <c r="F21" s="45" t="n">
-        <v>102</v>
-      </c>
-      <c r="G21" s="46" t="n">
-        <v>-243</v>
+        <v>-39</v>
+      </c>
+      <c r="G21" s="45" t="n">
+        <v>-105</v>
       </c>
       <c r="H21" s="47" t="n">
-        <v>42.9</v>
+        <v>230.9</v>
       </c>
       <c r="I21" s="47" t="n">
-        <v>388.8</v>
-      </c>
-      <c r="J21" s="48" t="n">
-        <v>74.7</v>
-      </c>
-      <c r="K21" s="49" t="n">
-        <v>24.53</v>
-      </c>
-      <c r="L21" s="57" t="n">
-        <v>-2.58</v>
+        <v>758.6</v>
+      </c>
+      <c r="J21" s="54" t="n">
+        <v>-49.9</v>
+      </c>
+      <c r="K21" s="53" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L21" s="50" t="n">
+        <v>-5.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="31" t="inlineStr">
         <is>
-          <t>유니퀘스트</t>
+          <t>코미팜</t>
         </is>
       </c>
       <c r="B22" s="30" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="C22" s="35" t="inlineStr">
         <is>
-          <t>유통</t>
-        </is>
-      </c>
-      <c r="D22" s="45" t="n">
-        <v>62</v>
-      </c>
-      <c r="E22" s="45" t="n">
-        <v>50</v>
-      </c>
-      <c r="F22" s="45" t="n">
-        <v>11</v>
-      </c>
-      <c r="G22" s="46" t="n">
-        <v>-63</v>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="D22" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="H22" s="47" t="n">
-        <v>4.3</v>
+        <v>31.8</v>
       </c>
       <c r="I22" s="47" t="n">
-        <v>60.3</v>
-      </c>
-      <c r="J22" s="48" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K22" s="49" t="n">
-        <v>15.09</v>
-      </c>
-      <c r="L22" s="57" t="n">
-        <v>-4.04</v>
+        <v>242</v>
+      </c>
+      <c r="J22" s="54" t="n">
+        <v>-157.2</v>
+      </c>
+      <c r="K22" s="53" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="L22" s="50" t="n">
+        <v>-9.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="31" t="inlineStr">
         <is>
-          <t>드림텍</t>
+          <t>한국알콜</t>
         </is>
       </c>
       <c r="B23" s="30" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="C23" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="D23" s="45" t="n">
-        <v>202</v>
-      </c>
-      <c r="E23" s="46" t="n">
-        <v>-86</v>
+          <t>화학</t>
+        </is>
+      </c>
+      <c r="D23" s="51" t="n">
+        <v>30</v>
+      </c>
+      <c r="E23" s="51" t="n">
+        <v>31</v>
       </c>
       <c r="F23" s="45" t="n">
-        <v>287</v>
-      </c>
-      <c r="G23" s="46" t="n">
-        <v>-200</v>
+        <v>-1</v>
+      </c>
+      <c r="G23" s="45" t="n">
+        <v>-30</v>
       </c>
       <c r="H23" s="47" t="n">
-        <v>66.59999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="I23" s="47" t="n">
-        <v>182.1</v>
-      </c>
-      <c r="J23" s="48" t="n">
-        <v>82.8</v>
-      </c>
-      <c r="K23" s="49" t="n">
-        <v>47.31</v>
+        <v>82.5</v>
+      </c>
+      <c r="J23" s="52" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K23" s="53" t="n">
+        <v>5.47</v>
       </c>
       <c r="L23" s="50" t="n">
-        <v>-7.29</v>
+        <v>-5.69</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>S-Oil우</t>
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>디지털대성</t>
         </is>
       </c>
       <c r="B24" s="30" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="C24" s="35" t="inlineStr">
         <is>
-          <t>화학</t>
-        </is>
-      </c>
-      <c r="D24" s="45" t="n">
-        <v>78</v>
+          <t>일반서비스</t>
+        </is>
+      </c>
+      <c r="D24" s="51" t="n">
+        <v>14</v>
       </c>
       <c r="E24" s="45" t="n">
-        <v>7</v>
-      </c>
-      <c r="F24" s="45" t="n">
-        <v>70</v>
-      </c>
-      <c r="G24" s="46" t="n">
-        <v>-75</v>
+        <v>-8</v>
+      </c>
+      <c r="F24" s="51" t="n">
+        <v>22</v>
+      </c>
+      <c r="G24" s="45" t="n">
+        <v>-22</v>
       </c>
       <c r="H24" s="47" t="n">
-        <v>4.2</v>
+        <v>0.2</v>
       </c>
       <c r="I24" s="47" t="n">
-        <v>211.9</v>
-      </c>
-      <c r="J24" s="48" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="K24" s="49" t="n">
-        <v>19.77</v>
-      </c>
-      <c r="L24" s="54" t="n">
-        <v>-1.08</v>
+        <v>28.3</v>
+      </c>
+      <c r="J24" s="52" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K24" s="53" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="L24" s="56" t="n">
+        <v>-2.68</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="31" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>코리안리</t>
         </is>
       </c>
       <c r="B25" s="30" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="C25" s="35" t="inlineStr">
         <is>
-          <t>제약</t>
-        </is>
-      </c>
-      <c r="D25" s="45" t="n">
-        <v>104</v>
+          <t>보험</t>
+        </is>
+      </c>
+      <c r="D25" s="51" t="n">
+        <v>2</v>
       </c>
       <c r="E25" s="45" t="n">
-        <v>143</v>
-      </c>
-      <c r="F25" s="46" t="n">
-        <v>-39</v>
-      </c>
-      <c r="G25" s="46" t="n">
-        <v>-105</v>
+        <v>-42</v>
+      </c>
+      <c r="F25" s="51" t="n">
+        <v>45</v>
+      </c>
+      <c r="G25" s="45" t="n">
+        <v>-33</v>
       </c>
       <c r="H25" s="47" t="n">
-        <v>230.9</v>
+        <v>40.6</v>
       </c>
       <c r="I25" s="47" t="n">
-        <v>758.6</v>
-      </c>
-      <c r="J25" s="55" t="n">
-        <v>-49.9</v>
-      </c>
-      <c r="K25" s="49" t="n">
-        <v>1.5</v>
+        <v>809.5</v>
+      </c>
+      <c r="J25" s="52" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K25" s="53" t="n">
+        <v>2.3</v>
       </c>
       <c r="L25" s="50" t="n">
-        <v>-5.61</v>
+        <v>-6.82</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="31" t="inlineStr">
         <is>
-          <t>코미팜</t>
+          <t>IPARK현대산업개발</t>
         </is>
       </c>
       <c r="B26" s="30" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="C26" s="35" t="inlineStr">
         <is>
-          <t>제약</t>
-        </is>
-      </c>
-      <c r="D26" s="45" t="n">
-        <v>1</v>
+          <t>건설</t>
+        </is>
+      </c>
+      <c r="D26" s="51" t="n">
+        <v>83</v>
       </c>
       <c r="E26" s="51" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F26" s="51" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="G26" s="45" t="n">
-        <v>1</v>
+        <v>-174</v>
       </c>
       <c r="H26" s="47" t="n">
-        <v>31.8</v>
+        <v>50.8</v>
       </c>
       <c r="I26" s="47" t="n">
-        <v>242</v>
-      </c>
-      <c r="J26" s="55" t="n">
-        <v>-157.2</v>
-      </c>
-      <c r="K26" s="49" t="n">
-        <v>6.66</v>
+        <v>423.5</v>
+      </c>
+      <c r="J26" s="54" t="n">
+        <v>-27.7</v>
+      </c>
+      <c r="K26" s="53" t="n">
+        <v>1.08</v>
       </c>
       <c r="L26" s="50" t="n">
-        <v>-8.66</v>
+        <v>-8.210000000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="31" t="inlineStr">
         <is>
-          <t>한국알콜</t>
+          <t>지어소프트</t>
         </is>
       </c>
       <c r="B27" s="30" t="inlineStr">
@@ -7388,85 +7270,85 @@
       </c>
       <c r="C27" s="35" t="inlineStr">
         <is>
-          <t>화학</t>
-        </is>
-      </c>
-      <c r="D27" s="45" t="n">
-        <v>30</v>
-      </c>
-      <c r="E27" s="45" t="n">
-        <v>31</v>
-      </c>
-      <c r="F27" s="46" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G27" s="46" t="n">
-        <v>-30</v>
+          <t>IT 서비스</t>
+        </is>
+      </c>
+      <c r="D27" s="51" t="n">
+        <v>59</v>
+      </c>
+      <c r="E27" s="51" t="n">
+        <v>56</v>
+      </c>
+      <c r="F27" s="51" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" s="45" t="n">
+        <v>-45</v>
       </c>
       <c r="H27" s="47" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="I27" s="47" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="J27" s="48" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K27" s="49" t="n">
-        <v>5.47</v>
+        <v>39.9</v>
+      </c>
+      <c r="J27" s="52" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K27" s="53" t="n">
+        <v>26.8</v>
       </c>
       <c r="L27" s="50" t="n">
-        <v>-5.48</v>
+        <v>-6.7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="31" t="inlineStr">
         <is>
-          <t>디지털대성</t>
+          <t>동아지질</t>
         </is>
       </c>
       <c r="B28" s="30" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="C28" s="35" t="inlineStr">
         <is>
-          <t>일반서비스</t>
-        </is>
-      </c>
-      <c r="D28" s="45" t="n">
-        <v>14</v>
-      </c>
-      <c r="E28" s="46" t="n">
-        <v>-8</v>
-      </c>
-      <c r="F28" s="45" t="n">
-        <v>22</v>
-      </c>
-      <c r="G28" s="46" t="n">
-        <v>-22</v>
+          <t>건설</t>
+        </is>
+      </c>
+      <c r="D28" s="51" t="n">
+        <v>40</v>
+      </c>
+      <c r="E28" s="45" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F28" s="51" t="n">
+        <v>41</v>
+      </c>
+      <c r="G28" s="45" t="n">
+        <v>-38</v>
       </c>
       <c r="H28" s="47" t="n">
-        <v>0.2</v>
+        <v>3.1</v>
       </c>
       <c r="I28" s="47" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="J28" s="48" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K28" s="49" t="n">
-        <v>11.43</v>
-      </c>
-      <c r="L28" s="57" t="n">
-        <v>-3.11</v>
+        <v>63.1</v>
+      </c>
+      <c r="J28" s="52" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K28" s="53" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="L28" s="50" t="n">
+        <v>-5.17</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="31" t="inlineStr">
         <is>
-          <t>코리안리</t>
+          <t>케이씨</t>
         </is>
       </c>
       <c r="B29" s="30" t="inlineStr">
@@ -7476,41 +7358,41 @@
       </c>
       <c r="C29" s="35" t="inlineStr">
         <is>
-          <t>보험</t>
-        </is>
-      </c>
-      <c r="D29" s="45" t="n">
-        <v>2</v>
-      </c>
-      <c r="E29" s="46" t="n">
-        <v>-42</v>
-      </c>
-      <c r="F29" s="45" t="n">
-        <v>45</v>
-      </c>
-      <c r="G29" s="46" t="n">
-        <v>-33</v>
+          <t>의료·정밀기기</t>
+        </is>
+      </c>
+      <c r="D29" s="51" t="n">
+        <v>37</v>
+      </c>
+      <c r="E29" s="51" t="n">
+        <v>31</v>
+      </c>
+      <c r="F29" s="51" t="n">
+        <v>6</v>
+      </c>
+      <c r="G29" s="45" t="n">
+        <v>-36</v>
       </c>
       <c r="H29" s="47" t="n">
-        <v>40.6</v>
+        <v>7.4</v>
       </c>
       <c r="I29" s="47" t="n">
-        <v>809.5</v>
-      </c>
-      <c r="J29" s="48" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="K29" s="49" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="L29" s="50" t="n">
-        <v>-7.04</v>
+        <v>96.90000000000001</v>
+      </c>
+      <c r="J29" s="54" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="K29" s="53" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="L29" s="56" t="n">
+        <v>-2.74</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="31" t="inlineStr">
         <is>
-          <t>IPARK현대산업개발</t>
+          <t>롯데렌탈</t>
         </is>
       </c>
       <c r="B30" s="30" t="inlineStr">
@@ -7520,228 +7402,52 @@
       </c>
       <c r="C30" s="35" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>일반서비스</t>
         </is>
       </c>
       <c r="D30" s="45" t="n">
-        <v>83</v>
+        <v>-13</v>
       </c>
       <c r="E30" s="45" t="n">
-        <v>11</v>
-      </c>
-      <c r="F30" s="45" t="n">
-        <v>73</v>
-      </c>
-      <c r="G30" s="46" t="n">
-        <v>-174</v>
+        <v>-65</v>
+      </c>
+      <c r="F30" s="51" t="n">
+        <v>52</v>
+      </c>
+      <c r="G30" s="51" t="n">
+        <v>12</v>
       </c>
       <c r="H30" s="47" t="n">
-        <v>50.8</v>
+        <v>121.5</v>
       </c>
       <c r="I30" s="47" t="n">
-        <v>423.5</v>
-      </c>
-      <c r="J30" s="55" t="n">
-        <v>-27.7</v>
-      </c>
-      <c r="K30" s="49" t="n">
-        <v>1.08</v>
+        <v>625.2</v>
+      </c>
+      <c r="J30" s="52" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="K30" s="53" t="n">
+        <v>4.97</v>
       </c>
       <c r="L30" s="50" t="n">
-        <v>-6.6</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="31" t="inlineStr">
-        <is>
-          <t>지어소프트</t>
-        </is>
-      </c>
-      <c r="B31" s="30" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="C31" s="35" t="inlineStr">
-        <is>
-          <t>IT 서비스</t>
-        </is>
-      </c>
-      <c r="D31" s="45" t="n">
-        <v>59</v>
-      </c>
-      <c r="E31" s="45" t="n">
-        <v>56</v>
-      </c>
-      <c r="F31" s="45" t="n">
-        <v>3</v>
-      </c>
-      <c r="G31" s="46" t="n">
-        <v>-45</v>
-      </c>
-      <c r="H31" s="47" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="I31" s="47" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="J31" s="48" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K31" s="49" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="L31" s="50" t="n">
-        <v>-9.039999999999999</v>
-      </c>
-    </row>
+        <v>-6.95</v>
+      </c>
+    </row>
+    <row r="31"/>
     <row r="32">
-      <c r="A32" s="31" t="inlineStr">
-        <is>
-          <t>동아지질</t>
-        </is>
-      </c>
-      <c r="B32" s="30" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="C32" s="35" t="inlineStr">
-        <is>
-          <t>건설</t>
-        </is>
-      </c>
-      <c r="D32" s="45" t="n">
-        <v>40</v>
-      </c>
-      <c r="E32" s="46" t="n">
-        <v>-1</v>
-      </c>
-      <c r="F32" s="45" t="n">
-        <v>41</v>
-      </c>
-      <c r="G32" s="46" t="n">
-        <v>-38</v>
-      </c>
-      <c r="H32" s="47" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="I32" s="47" t="n">
-        <v>63.1</v>
-      </c>
-      <c r="J32" s="48" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K32" s="49" t="n">
-        <v>10.95</v>
-      </c>
-      <c r="L32" s="50" t="n">
-        <v>-6.14</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="31" t="inlineStr">
-        <is>
-          <t>케이씨</t>
-        </is>
-      </c>
-      <c r="B33" s="30" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="C33" s="35" t="inlineStr">
-        <is>
-          <t>의료·정밀기기</t>
-        </is>
-      </c>
-      <c r="D33" s="45" t="n">
-        <v>37</v>
-      </c>
-      <c r="E33" s="45" t="n">
-        <v>31</v>
-      </c>
-      <c r="F33" s="45" t="n">
-        <v>6</v>
-      </c>
-      <c r="G33" s="46" t="n">
-        <v>-36</v>
-      </c>
-      <c r="H33" s="47" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="I33" s="47" t="n">
-        <v>96.90000000000001</v>
-      </c>
-      <c r="J33" s="55" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="K33" s="49" t="n">
-        <v>6.36</v>
-      </c>
-      <c r="L33" s="57" t="n">
-        <v>-3.45</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="31" t="inlineStr">
-        <is>
-          <t>롯데렌탈</t>
-        </is>
-      </c>
-      <c r="B34" s="30" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="C34" s="35" t="inlineStr">
-        <is>
-          <t>일반서비스</t>
-        </is>
-      </c>
-      <c r="D34" s="46" t="n">
-        <v>-13</v>
-      </c>
-      <c r="E34" s="46" t="n">
-        <v>-65</v>
-      </c>
-      <c r="F34" s="45" t="n">
-        <v>52</v>
-      </c>
-      <c r="G34" s="45" t="n">
-        <v>12</v>
-      </c>
-      <c r="H34" s="47" t="n">
-        <v>121.5</v>
-      </c>
-      <c r="I34" s="47" t="n">
-        <v>625.2</v>
-      </c>
-      <c r="J34" s="48" t="n">
-        <v>60.8</v>
-      </c>
-      <c r="K34" s="49" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="L34" s="50" t="n">
-        <v>-7.06</v>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="18" t="inlineStr">
+      <c r="A32" s="18" t="inlineStr">
         <is>
           <t>최신 거래일 기준 · 52주 신고가 대비 -10% 이내 (KIS 랭킹) · ETF·ETN 제외 · 수급=월간 누적 확정(억원) · 동반 순매수(외인·기관 동일 방향)=합산 굵게</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:L34"/>
+  <autoFilter ref="A5:L30"/>
   <mergeCells count="6">
     <mergeCell ref="D4:J4"/>
     <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A32:L32"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A36:L36"/>
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="A4:C4"/>
   </mergeCells>
@@ -7790,7 +7496,7 @@
       </c>
       <c r="O1" s="25" t="inlineStr">
         <is>
-          <t>2026-09-01 ~ 2026-09-24</t>
+          <t>2026-09-01 ~ 2026-09-23</t>
         </is>
       </c>
     </row>
@@ -7921,7 +7627,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="31" customHeight="1" s="15">
+    <row r="6">
       <c r="A6" s="30" t="n">
         <v>1</v>
       </c>
@@ -7935,8 +7641,8 @@
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D6" s="46" t="n">
-        <v>8118</v>
+      <c r="D6" s="45" t="n">
+        <v>8390</v>
       </c>
       <c r="E6" s="30" t="n">
         <v>1</v>
@@ -7952,7 +7658,7 @@
         </is>
       </c>
       <c r="H6" s="61" t="n">
-        <v>-82160</v>
+        <v>-72174</v>
       </c>
       <c r="J6" s="30" t="n">
         <v>1</v>
@@ -7967,27 +7673,27 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M6" s="46" t="n">
-        <v>41629</v>
+      <c r="M6" s="45" t="n">
+        <v>39366</v>
       </c>
       <c r="N6" s="30" t="n">
         <v>1</v>
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>현대차</t>
-        </is>
-      </c>
-      <c r="P6" s="62" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="P6" s="35" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="Q6" s="61" t="n">
-        <v>-4032</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>-4308</v>
+      </c>
+    </row>
+    <row r="7" ht="31" customHeight="1" s="15">
       <c r="A7" s="30" t="n">
         <v>2</v>
       </c>
@@ -8001,7 +7707,7 @@
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D7" s="46" t="n">
+      <c r="D7" s="45" t="n">
         <v>4771</v>
       </c>
       <c r="E7" s="30" t="n">
@@ -8018,7 +7724,7 @@
         </is>
       </c>
       <c r="H7" s="61" t="n">
-        <v>-6914</v>
+        <v>-12432</v>
       </c>
       <c r="J7" s="30" t="n">
         <v>2</v>
@@ -8033,42 +7739,42 @@
           <t>유통</t>
         </is>
       </c>
-      <c r="M7" s="46" t="n">
-        <v>10303</v>
+      <c r="M7" s="45" t="n">
+        <v>10339</v>
       </c>
       <c r="N7" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="O7" s="31" t="inlineStr">
-        <is>
-          <t>NAVER</t>
-        </is>
-      </c>
-      <c r="P7" s="35" t="inlineStr">
-        <is>
-          <t>IT 서비스</t>
+      <c r="O7" s="1" t="inlineStr">
+        <is>
+          <t>현대차</t>
+        </is>
+      </c>
+      <c r="P7" s="62" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
         </is>
       </c>
       <c r="Q7" s="61" t="n">
-        <v>-3804</v>
-      </c>
-    </row>
-    <row r="8" ht="31" customHeight="1" s="15">
+        <v>-3860</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>SK이노베이션</t>
+      <c r="B8" s="31" t="inlineStr">
+        <is>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C8" s="35" t="inlineStr">
         <is>
-          <t>화학</t>
-        </is>
-      </c>
-      <c r="D8" s="46" t="n">
-        <v>2991</v>
+          <t>운송·창고</t>
+        </is>
+      </c>
+      <c r="D8" s="45" t="n">
+        <v>2924</v>
       </c>
       <c r="E8" s="30" t="n">
         <v>3</v>
@@ -8084,7 +7790,7 @@
         </is>
       </c>
       <c r="H8" s="61" t="n">
-        <v>-5851</v>
+        <v>-4879</v>
       </c>
       <c r="J8" s="30" t="n">
         <v>3</v>
@@ -8099,49 +7805,49 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M8" s="46" t="n">
-        <v>3673</v>
+      <c r="M8" s="45" t="n">
+        <v>3788</v>
       </c>
       <c r="N8" s="30" t="n">
         <v>3</v>
       </c>
       <c r="O8" s="31" t="inlineStr">
         <is>
-          <t>현대모비스</t>
-        </is>
-      </c>
-      <c r="P8" s="62" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
+          <t>NAVER</t>
+        </is>
+      </c>
+      <c r="P8" s="35" t="inlineStr">
+        <is>
+          <t>IT 서비스</t>
         </is>
       </c>
       <c r="Q8" s="61" t="n">
-        <v>-3279</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>-3571</v>
+      </c>
+    </row>
+    <row r="9" ht="31" customHeight="1" s="15">
       <c r="A9" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="31" t="inlineStr">
-        <is>
-          <t>대한항공</t>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C9" s="35" t="inlineStr">
         <is>
-          <t>운송·창고</t>
-        </is>
-      </c>
-      <c r="D9" s="46" t="n">
-        <v>2898</v>
+          <t>화학</t>
+        </is>
+      </c>
+      <c r="D9" s="45" t="n">
+        <v>2752</v>
       </c>
       <c r="E9" s="30" t="n">
         <v>4</v>
       </c>
       <c r="F9" s="31" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>두산</t>
         </is>
       </c>
       <c r="G9" s="35" t="inlineStr">
@@ -8150,7 +7856,7 @@
         </is>
       </c>
       <c r="H9" s="61" t="n">
-        <v>-3572</v>
+        <v>-3014</v>
       </c>
       <c r="J9" s="30" t="n">
         <v>4</v>
@@ -8165,7 +7871,7 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M9" s="46" t="n">
+      <c r="M9" s="45" t="n">
         <v>3473</v>
       </c>
       <c r="N9" s="30" t="n">
@@ -8173,16 +7879,16 @@
       </c>
       <c r="O9" s="31" t="inlineStr">
         <is>
-          <t>알테오젠</t>
-        </is>
-      </c>
-      <c r="P9" s="35" t="inlineStr">
-        <is>
-          <t>일반서비스</t>
+          <t>현대모비스</t>
+        </is>
+      </c>
+      <c r="P9" s="62" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
         </is>
       </c>
       <c r="Q9" s="61" t="n">
-        <v>-3068</v>
+        <v>-3246</v>
       </c>
     </row>
     <row r="10">
@@ -8199,15 +7905,15 @@
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D10" s="46" t="n">
-        <v>2109</v>
+      <c r="D10" s="45" t="n">
+        <v>2017</v>
       </c>
       <c r="E10" s="30" t="n">
         <v>5</v>
       </c>
       <c r="F10" s="31" t="inlineStr">
         <is>
-          <t>두산</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="G10" s="35" t="inlineStr">
@@ -8216,7 +7922,7 @@
         </is>
       </c>
       <c r="H10" s="61" t="n">
-        <v>-3014</v>
+        <v>-2896</v>
       </c>
       <c r="J10" s="30" t="n">
         <v>5</v>
@@ -8231,24 +7937,24 @@
           <t>기타금융</t>
         </is>
       </c>
-      <c r="M10" s="46" t="n">
-        <v>2678</v>
+      <c r="M10" s="45" t="n">
+        <v>2600</v>
       </c>
       <c r="N10" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="O10" s="1" t="inlineStr">
-        <is>
-          <t>SK하이닉스</t>
+      <c r="O10" s="31" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="P10" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>일반서비스</t>
         </is>
       </c>
       <c r="Q10" s="61" t="n">
-        <v>-2613</v>
+        <v>-3068</v>
       </c>
     </row>
     <row r="11">
@@ -8265,8 +7971,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D11" s="46" t="n">
-        <v>1016</v>
+      <c r="D11" s="45" t="n">
+        <v>1115</v>
       </c>
       <c r="E11" s="30" t="n">
         <v>6</v>
@@ -8297,8 +8003,8 @@
           <t>기타금융</t>
         </is>
       </c>
-      <c r="M11" s="46" t="n">
-        <v>2252</v>
+      <c r="M11" s="45" t="n">
+        <v>2254</v>
       </c>
       <c r="N11" s="30" t="n">
         <v>6</v>
@@ -8314,10 +8020,10 @@
         </is>
       </c>
       <c r="Q11" s="61" t="n">
-        <v>-2249</v>
-      </c>
-    </row>
-    <row r="12" ht="31" customHeight="1" s="15">
+        <v>-2051</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" s="30" t="n">
         <v>7</v>
       </c>
@@ -8331,31 +8037,31 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D12" s="46" t="n">
-        <v>999</v>
+      <c r="D12" s="45" t="n">
+        <v>1060</v>
       </c>
       <c r="E12" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>현대차</t>
-        </is>
-      </c>
-      <c r="G12" s="62" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
+      <c r="F12" s="31" t="inlineStr">
+        <is>
+          <t>삼성전기</t>
+        </is>
+      </c>
+      <c r="G12" s="35" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="H12" s="61" t="n">
-        <v>-2315</v>
+        <v>-2146</v>
       </c>
       <c r="J12" s="30" t="n">
         <v>7</v>
       </c>
       <c r="K12" s="31" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>DB하이텍</t>
         </is>
       </c>
       <c r="L12" s="35" t="inlineStr">
@@ -8363,8 +8069,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M12" s="46" t="n">
-        <v>1967</v>
+      <c r="M12" s="45" t="n">
+        <v>1854</v>
       </c>
       <c r="N12" s="30" t="n">
         <v>7</v>
@@ -8380,25 +8086,25 @@
         </is>
       </c>
       <c r="Q12" s="61" t="n">
-        <v>-1919</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>-1886</v>
+      </c>
+    </row>
+    <row r="13" ht="31" customHeight="1" s="15">
       <c r="A13" s="30" t="n">
         <v>8</v>
       </c>
       <c r="B13" s="31" t="inlineStr">
         <is>
-          <t>로보티즈</t>
-        </is>
-      </c>
-      <c r="C13" s="35" t="inlineStr">
-        <is>
-          <t>기계·장비</t>
-        </is>
-      </c>
-      <c r="D13" s="46" t="n">
-        <v>911</v>
+          <t>현대모비스</t>
+        </is>
+      </c>
+      <c r="C13" s="62" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
+        </is>
+      </c>
+      <c r="D13" s="45" t="n">
+        <v>998</v>
       </c>
       <c r="E13" s="30" t="n">
         <v>8</v>
@@ -8414,7 +8120,7 @@
         </is>
       </c>
       <c r="H13" s="61" t="n">
-        <v>-2209</v>
+        <v>-1982</v>
       </c>
       <c r="J13" s="30" t="n">
         <v>8</v>
@@ -8429,24 +8135,24 @@
           <t>화학</t>
         </is>
       </c>
-      <c r="M13" s="46" t="n">
-        <v>1914</v>
+      <c r="M13" s="45" t="n">
+        <v>1831</v>
       </c>
       <c r="N13" s="30" t="n">
         <v>8</v>
       </c>
       <c r="O13" s="31" t="inlineStr">
         <is>
-          <t>삼양식품</t>
+          <t>SK스퀘어</t>
         </is>
       </c>
       <c r="P13" s="35" t="inlineStr">
         <is>
-          <t>음식료·담배</t>
+          <t>기타금융</t>
         </is>
       </c>
       <c r="Q13" s="61" t="n">
-        <v>-1657</v>
+        <v>-1814</v>
       </c>
     </row>
     <row r="14" ht="31" customHeight="1" s="15">
@@ -8455,39 +8161,39 @@
       </c>
       <c r="B14" s="31" t="inlineStr">
         <is>
-          <t>현대모비스</t>
-        </is>
-      </c>
-      <c r="C14" s="62" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
-        </is>
-      </c>
-      <c r="D14" s="46" t="n">
-        <v>895</v>
+          <t>로보티즈</t>
+        </is>
+      </c>
+      <c r="C14" s="35" t="inlineStr">
+        <is>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="D14" s="45" t="n">
+        <v>911</v>
       </c>
       <c r="E14" s="30" t="n">
         <v>9</v>
       </c>
       <c r="F14" s="31" t="inlineStr">
         <is>
-          <t>리노공업</t>
-        </is>
-      </c>
-      <c r="G14" s="35" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
+          <t>HD현대중공업</t>
+        </is>
+      </c>
+      <c r="G14" s="62" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
         </is>
       </c>
       <c r="H14" s="61" t="n">
-        <v>-2055</v>
+        <v>-1742</v>
       </c>
       <c r="J14" s="30" t="n">
         <v>9</v>
       </c>
       <c r="K14" s="31" t="inlineStr">
         <is>
-          <t>DB하이텍</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="L14" s="35" t="inlineStr">
@@ -8495,27 +8201,27 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M14" s="46" t="n">
-        <v>1854</v>
+      <c r="M14" s="45" t="n">
+        <v>1652</v>
       </c>
       <c r="N14" s="30" t="n">
         <v>9</v>
       </c>
       <c r="O14" s="31" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>삼양식품</t>
         </is>
       </c>
       <c r="P14" s="35" t="inlineStr">
         <is>
-          <t>기타금융</t>
+          <t>음식료·담배</t>
         </is>
       </c>
       <c r="Q14" s="61" t="n">
-        <v>-1625</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>-1596</v>
+      </c>
+    </row>
+    <row r="15" ht="31" customHeight="1" s="15">
       <c r="A15" s="30" t="n">
         <v>10</v>
       </c>
@@ -8529,24 +8235,24 @@
           <t>제약</t>
         </is>
       </c>
-      <c r="D15" s="46" t="n">
+      <c r="D15" s="45" t="n">
         <v>879</v>
       </c>
       <c r="E15" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="F15" s="31" t="inlineStr">
-        <is>
-          <t>KB금융</t>
-        </is>
-      </c>
-      <c r="G15" s="35" t="inlineStr">
-        <is>
-          <t>기타금융</t>
+      <c r="F15" s="1" t="inlineStr">
+        <is>
+          <t>현대차</t>
+        </is>
+      </c>
+      <c r="G15" s="62" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
         </is>
       </c>
       <c r="H15" s="61" t="n">
-        <v>-1766</v>
+        <v>-1676</v>
       </c>
       <c r="J15" s="30" t="n">
         <v>10</v>
@@ -8561,8 +8267,8 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M15" s="46" t="n">
-        <v>1657</v>
+      <c r="M15" s="45" t="n">
+        <v>1644</v>
       </c>
       <c r="N15" s="30" t="n">
         <v>10</v>
@@ -8578,7 +8284,7 @@
         </is>
       </c>
       <c r="Q15" s="61" t="n">
-        <v>-1502</v>
+        <v>-1535</v>
       </c>
     </row>
     <row r="16"/>
@@ -8722,8 +8428,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D20" s="46" t="n">
-        <v>34714</v>
+      <c r="D20" s="45" t="n">
+        <v>26933</v>
       </c>
       <c r="E20" s="30" t="n">
         <v>1</v>
@@ -8739,7 +8445,7 @@
         </is>
       </c>
       <c r="H20" s="61" t="n">
-        <v>-84773</v>
+        <v>-76483</v>
       </c>
       <c r="J20" s="30" t="n">
         <v>1</v>
@@ -8754,7 +8460,7 @@
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="M20" s="46" t="n">
+      <c r="M20" s="45" t="n">
         <v>5622</v>
       </c>
       <c r="N20" s="30" t="n">
@@ -8788,8 +8494,8 @@
           <t>유통</t>
         </is>
       </c>
-      <c r="D21" s="46" t="n">
-        <v>9370</v>
+      <c r="D21" s="45" t="n">
+        <v>9402</v>
       </c>
       <c r="E21" s="30" t="n">
         <v>2</v>
@@ -8805,7 +8511,7 @@
         </is>
       </c>
       <c r="H21" s="61" t="n">
-        <v>-6347</v>
+        <v>-5536</v>
       </c>
       <c r="J21" s="30" t="n">
         <v>2</v>
@@ -8820,7 +8526,7 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M21" s="46" t="n">
+      <c r="M21" s="45" t="n">
         <v>4820</v>
       </c>
       <c r="N21" s="30" t="n">
@@ -8854,8 +8560,8 @@
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D22" s="46" t="n">
-        <v>6493</v>
+      <c r="D22" s="45" t="n">
+        <v>6576</v>
       </c>
       <c r="E22" s="30" t="n">
         <v>3</v>
@@ -8871,7 +8577,7 @@
         </is>
       </c>
       <c r="H22" s="61" t="n">
-        <v>-5969</v>
+        <v>-4810</v>
       </c>
       <c r="J22" s="30" t="n">
         <v>3</v>
@@ -8886,7 +8592,7 @@
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="M22" s="46" t="n">
+      <c r="M22" s="45" t="n">
         <v>3803</v>
       </c>
       <c r="N22" s="30" t="n">
@@ -8920,7 +8626,7 @@
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D23" s="46" t="n">
+      <c r="D23" s="45" t="n">
         <v>5388</v>
       </c>
       <c r="E23" s="30" t="n">
@@ -8937,7 +8643,7 @@
         </is>
       </c>
       <c r="H23" s="61" t="n">
-        <v>-4632</v>
+        <v>-3793</v>
       </c>
       <c r="J23" s="30" t="n">
         <v>4</v>
@@ -8952,7 +8658,7 @@
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="M23" s="46" t="n">
+      <c r="M23" s="45" t="n">
         <v>3760</v>
       </c>
       <c r="N23" s="30" t="n">
@@ -8986,8 +8692,8 @@
           <t>화학</t>
         </is>
       </c>
-      <c r="D24" s="46" t="n">
-        <v>4905</v>
+      <c r="D24" s="45" t="n">
+        <v>4583</v>
       </c>
       <c r="E24" s="30" t="n">
         <v>5</v>
@@ -9003,7 +8709,7 @@
         </is>
       </c>
       <c r="H24" s="61" t="n">
-        <v>-3841</v>
+        <v>-3596</v>
       </c>
       <c r="J24" s="30" t="n">
         <v>5</v>
@@ -9018,7 +8724,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M24" s="46" t="n">
+      <c r="M24" s="45" t="n">
         <v>3491</v>
       </c>
       <c r="N24" s="30" t="n">
@@ -9052,8 +8758,8 @@
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="D25" s="46" t="n">
-        <v>3636</v>
+      <c r="D25" s="45" t="n">
+        <v>3592</v>
       </c>
       <c r="E25" s="30" t="n">
         <v>6</v>
@@ -9084,7 +8790,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M25" s="46" t="n">
+      <c r="M25" s="45" t="n">
         <v>2488</v>
       </c>
       <c r="N25" s="30" t="n">
@@ -9110,16 +8816,16 @@
       </c>
       <c r="B26" s="31" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="C26" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="D26" s="46" t="n">
-        <v>2365</v>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="D26" s="45" t="n">
+        <v>2225</v>
       </c>
       <c r="E26" s="30" t="n">
         <v>7</v>
@@ -9135,7 +8841,7 @@
         </is>
       </c>
       <c r="H26" s="61" t="n">
-        <v>-2627</v>
+        <v>-2546</v>
       </c>
       <c r="J26" s="30" t="n">
         <v>7</v>
@@ -9150,7 +8856,7 @@
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="M26" s="46" t="n">
+      <c r="M26" s="45" t="n">
         <v>2207</v>
       </c>
       <c r="N26" s="30" t="n">
@@ -9176,16 +8882,16 @@
       </c>
       <c r="B27" s="31" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="C27" s="35" t="inlineStr">
         <is>
-          <t>기계·장비</t>
-        </is>
-      </c>
-      <c r="D27" s="46" t="n">
-        <v>2225</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D27" s="45" t="n">
+        <v>1631</v>
       </c>
       <c r="E27" s="30" t="n">
         <v>8</v>
@@ -9201,7 +8907,7 @@
         </is>
       </c>
       <c r="H27" s="61" t="n">
-        <v>-2384</v>
+        <v>-2248</v>
       </c>
       <c r="J27" s="30" t="n">
         <v>8</v>
@@ -9216,7 +8922,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M27" s="46" t="n">
+      <c r="M27" s="45" t="n">
         <v>1788</v>
       </c>
       <c r="N27" s="30" t="n">
@@ -9250,7 +8956,7 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D28" s="46" t="n">
+      <c r="D28" s="45" t="n">
         <v>1597</v>
       </c>
       <c r="E28" s="30" t="n">
@@ -9282,7 +8988,7 @@
           <t>화학</t>
         </is>
       </c>
-      <c r="M28" s="46" t="n">
+      <c r="M28" s="45" t="n">
         <v>1669</v>
       </c>
       <c r="N28" s="30" t="n">
@@ -9308,32 +9014,32 @@
       </c>
       <c r="B29" s="31" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="C29" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="D29" s="46" t="n">
-        <v>1510</v>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="D29" s="45" t="n">
+        <v>1272</v>
       </c>
       <c r="E29" s="30" t="n">
         <v>10</v>
       </c>
       <c r="F29" s="31" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>에이피알</t>
         </is>
       </c>
       <c r="G29" s="35" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>화학</t>
         </is>
       </c>
       <c r="H29" s="61" t="n">
-        <v>-1765</v>
+        <v>-1702</v>
       </c>
       <c r="J29" s="30" t="n">
         <v>10</v>
@@ -9348,7 +9054,7 @@
           <t>기타금융</t>
         </is>
       </c>
-      <c r="M29" s="46" t="n">
+      <c r="M29" s="45" t="n">
         <v>1446</v>
       </c>
       <c r="N29" s="30" t="n">
@@ -9509,7 +9215,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D34" s="46" t="n">
+      <c r="D34" s="45" t="n">
         <v>40740</v>
       </c>
       <c r="E34" s="30" t="n">
@@ -9541,7 +9247,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M34" s="46" t="n">
+      <c r="M34" s="45" t="n">
         <v>3202</v>
       </c>
       <c r="N34" s="30" t="n">
@@ -9575,7 +9281,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D35" s="46" t="n">
+      <c r="D35" s="45" t="n">
         <v>10869</v>
       </c>
       <c r="E35" s="30" t="n">
@@ -9607,7 +9313,7 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M35" s="46" t="n">
+      <c r="M35" s="45" t="n">
         <v>3178</v>
       </c>
       <c r="N35" s="30" t="n">
@@ -9641,7 +9347,7 @@
           <t>유통</t>
         </is>
       </c>
-      <c r="D36" s="46" t="n">
+      <c r="D36" s="45" t="n">
         <v>9362</v>
       </c>
       <c r="E36" s="30" t="n">
@@ -9673,7 +9379,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M36" s="46" t="n">
+      <c r="M36" s="45" t="n">
         <v>3032</v>
       </c>
       <c r="N36" s="30" t="n">
@@ -9707,7 +9413,7 @@
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D37" s="46" t="n">
+      <c r="D37" s="45" t="n">
         <v>2038</v>
       </c>
       <c r="E37" s="30" t="n">
@@ -9739,7 +9445,7 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M37" s="46" t="n">
+      <c r="M37" s="45" t="n">
         <v>2016</v>
       </c>
       <c r="N37" s="30" t="n">
@@ -9773,7 +9479,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D38" s="46" t="n">
+      <c r="D38" s="45" t="n">
         <v>844</v>
       </c>
       <c r="E38" s="30" t="n">
@@ -9805,7 +9511,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M38" s="46" t="n">
+      <c r="M38" s="45" t="n">
         <v>1543</v>
       </c>
       <c r="N38" s="30" t="n">
@@ -9839,7 +9545,7 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="D39" s="46" t="n">
+      <c r="D39" s="45" t="n">
         <v>295</v>
       </c>
       <c r="E39" s="30" t="n">
@@ -9871,7 +9577,7 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M39" s="46" t="n">
+      <c r="M39" s="45" t="n">
         <v>1527</v>
       </c>
       <c r="N39" s="30" t="n">
@@ -9905,7 +9611,7 @@
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="D40" s="46" t="n">
+      <c r="D40" s="45" t="n">
         <v>276</v>
       </c>
       <c r="E40" s="30" t="n">
@@ -9937,7 +9643,7 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M40" s="46" t="n">
+      <c r="M40" s="45" t="n">
         <v>1524</v>
       </c>
       <c r="N40" s="30" t="n">
@@ -9971,7 +9677,7 @@
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D41" s="46" t="n">
+      <c r="D41" s="45" t="n">
         <v>257</v>
       </c>
       <c r="E41" s="30" t="n">
@@ -10003,7 +9709,7 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M41" s="46" t="n">
+      <c r="M41" s="45" t="n">
         <v>1366</v>
       </c>
       <c r="N41" s="30" t="n">
@@ -10037,7 +9743,7 @@
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D42" s="46" t="n">
+      <c r="D42" s="45" t="n">
         <v>235</v>
       </c>
       <c r="E42" s="30" t="n">
@@ -10069,7 +9775,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M42" s="46" t="n">
+      <c r="M42" s="45" t="n">
         <v>1222</v>
       </c>
       <c r="N42" s="30" t="n">
@@ -10103,7 +9809,7 @@
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D43" s="46" t="n">
+      <c r="D43" s="45" t="n">
         <v>212</v>
       </c>
       <c r="E43" s="30" t="n">
@@ -10135,7 +9841,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M43" s="46" t="n">
+      <c r="M43" s="45" t="n">
         <v>1208</v>
       </c>
       <c r="N43" s="30" t="n">
@@ -10288,16 +9994,16 @@
       </c>
       <c r="B48" s="31" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C48" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="D48" s="46" t="n">
-        <v>1307</v>
+          <t>화학</t>
+        </is>
+      </c>
+      <c r="D48" s="45" t="n">
+        <v>1272</v>
       </c>
       <c r="E48" s="30" t="n">
         <v>1</v>
@@ -10313,7 +10019,7 @@
         </is>
       </c>
       <c r="H48" s="61" t="n">
-        <v>-2253</v>
+        <v>-2171</v>
       </c>
       <c r="J48" s="30" t="n">
         <v>1</v>
@@ -10328,7 +10034,7 @@
           <t>기타금융</t>
         </is>
       </c>
-      <c r="M48" s="46" t="n">
+      <c r="M48" s="45" t="n">
         <v>497</v>
       </c>
       <c r="N48" s="30" t="n">
@@ -10354,16 +10060,16 @@
       </c>
       <c r="B49" s="31" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>두산</t>
         </is>
       </c>
       <c r="C49" s="35" t="inlineStr">
         <is>
-          <t>화학</t>
-        </is>
-      </c>
-      <c r="D49" s="46" t="n">
-        <v>1302</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D49" s="45" t="n">
+        <v>1020</v>
       </c>
       <c r="E49" s="30" t="n">
         <v>2</v>
@@ -10379,7 +10085,7 @@
         </is>
       </c>
       <c r="H49" s="61" t="n">
-        <v>-1993</v>
+        <v>-2064</v>
       </c>
       <c r="J49" s="30" t="n">
         <v>2</v>
@@ -10394,7 +10100,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M49" s="46" t="n">
+      <c r="M49" s="45" t="n">
         <v>440</v>
       </c>
       <c r="N49" s="30" t="n">
@@ -10420,16 +10126,16 @@
       </c>
       <c r="B50" s="31" t="inlineStr">
         <is>
-          <t>두산</t>
+          <t>LG화학</t>
         </is>
       </c>
       <c r="C50" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="D50" s="46" t="n">
-        <v>1020</v>
+          <t>화학</t>
+        </is>
+      </c>
+      <c r="D50" s="45" t="n">
+        <v>773</v>
       </c>
       <c r="E50" s="30" t="n">
         <v>3</v>
@@ -10445,7 +10151,7 @@
         </is>
       </c>
       <c r="H50" s="61" t="n">
-        <v>-1564</v>
+        <v>-1542</v>
       </c>
       <c r="J50" s="30" t="n">
         <v>3</v>
@@ -10460,7 +10166,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M50" s="46" t="n">
+      <c r="M50" s="45" t="n">
         <v>360</v>
       </c>
       <c r="N50" s="30" t="n">
@@ -10486,32 +10192,32 @@
       </c>
       <c r="B51" s="31" t="inlineStr">
         <is>
-          <t>LG화학</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="C51" s="35" t="inlineStr">
         <is>
-          <t>화학</t>
-        </is>
-      </c>
-      <c r="D51" s="46" t="n">
-        <v>773</v>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="D51" s="45" t="n">
+        <v>612</v>
       </c>
       <c r="E51" s="30" t="n">
         <v>4</v>
       </c>
       <c r="F51" s="31" t="inlineStr">
         <is>
-          <t>NAVER</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="G51" s="35" t="inlineStr">
         <is>
-          <t>IT 서비스</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="H51" s="61" t="n">
-        <v>-1452</v>
+        <v>-1443</v>
       </c>
       <c r="J51" s="30" t="n">
         <v>4</v>
@@ -10526,7 +10232,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M51" s="46" t="n">
+      <c r="M51" s="45" t="n">
         <v>235</v>
       </c>
       <c r="N51" s="30" t="n">
@@ -10552,32 +10258,32 @@
       </c>
       <c r="B52" s="31" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>메리츠금융지주</t>
         </is>
       </c>
       <c r="C52" s="35" t="inlineStr">
         <is>
-          <t>운송·창고</t>
-        </is>
-      </c>
-      <c r="D52" s="46" t="n">
-        <v>614</v>
+          <t>기타금융</t>
+        </is>
+      </c>
+      <c r="D52" s="45" t="n">
+        <v>610</v>
       </c>
       <c r="E52" s="30" t="n">
         <v>5</v>
       </c>
       <c r="F52" s="31" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>NAVER</t>
         </is>
       </c>
       <c r="G52" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>IT 서비스</t>
         </is>
       </c>
       <c r="H52" s="61" t="n">
-        <v>-1343</v>
+        <v>-1320</v>
       </c>
       <c r="J52" s="30" t="n">
         <v>5</v>
@@ -10592,7 +10298,7 @@
           <t>화학</t>
         </is>
       </c>
-      <c r="M52" s="46" t="n">
+      <c r="M52" s="45" t="n">
         <v>195</v>
       </c>
       <c r="N52" s="30" t="n">
@@ -10618,23 +10324,23 @@
       </c>
       <c r="B53" s="31" t="inlineStr">
         <is>
-          <t>메리츠금융지주</t>
+          <t>포스코인터내셔널</t>
         </is>
       </c>
       <c r="C53" s="35" t="inlineStr">
         <is>
-          <t>기타금융</t>
-        </is>
-      </c>
-      <c r="D53" s="46" t="n">
-        <v>610</v>
+          <t>유통</t>
+        </is>
+      </c>
+      <c r="D53" s="45" t="n">
+        <v>605</v>
       </c>
       <c r="E53" s="30" t="n">
         <v>6</v>
       </c>
       <c r="F53" s="31" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="G53" s="35" t="inlineStr">
@@ -10643,7 +10349,7 @@
         </is>
       </c>
       <c r="H53" s="61" t="n">
-        <v>-1239</v>
+        <v>-1043</v>
       </c>
       <c r="J53" s="30" t="n">
         <v>6</v>
@@ -10658,7 +10364,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M53" s="46" t="n">
+      <c r="M53" s="45" t="n">
         <v>127</v>
       </c>
       <c r="N53" s="30" t="n">
@@ -10678,7 +10384,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="54" ht="31" customHeight="1" s="15">
+    <row r="54">
       <c r="A54" s="30" t="n">
         <v>7</v>
       </c>
@@ -10692,7 +10398,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D54" s="46" t="n">
+      <c r="D54" s="45" t="n">
         <v>588</v>
       </c>
       <c r="E54" s="30" t="n">
@@ -10700,16 +10406,16 @@
       </c>
       <c r="F54" s="31" t="inlineStr">
         <is>
-          <t>기아</t>
-        </is>
-      </c>
-      <c r="G54" s="62" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
+          <t>삼성전기</t>
+        </is>
+      </c>
+      <c r="G54" s="35" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="H54" s="61" t="n">
-        <v>-910</v>
+        <v>-914</v>
       </c>
       <c r="J54" s="30" t="n">
         <v>7</v>
@@ -10724,7 +10430,7 @@
           <t>기타금융</t>
         </is>
       </c>
-      <c r="M54" s="46" t="n">
+      <c r="M54" s="45" t="n">
         <v>92</v>
       </c>
       <c r="N54" s="30" t="n">
@@ -10744,38 +10450,38 @@
         <v>-96</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" ht="31" customHeight="1" s="15">
       <c r="A55" s="30" t="n">
         <v>8</v>
       </c>
       <c r="B55" s="31" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C55" s="35" t="inlineStr">
         <is>
-          <t>기계·장비</t>
-        </is>
-      </c>
-      <c r="D55" s="46" t="n">
-        <v>575</v>
+          <t>운송·창고</t>
+        </is>
+      </c>
+      <c r="D55" s="45" t="n">
+        <v>584</v>
       </c>
       <c r="E55" s="30" t="n">
         <v>8</v>
       </c>
       <c r="F55" s="31" t="inlineStr">
         <is>
-          <t>삼성전기</t>
-        </is>
-      </c>
-      <c r="G55" s="35" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
+          <t>기아</t>
+        </is>
+      </c>
+      <c r="G55" s="62" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
         </is>
       </c>
       <c r="H55" s="61" t="n">
-        <v>-839</v>
+        <v>-898</v>
       </c>
       <c r="J55" s="30" t="n">
         <v>8</v>
@@ -10790,7 +10496,7 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M55" s="46" t="n">
+      <c r="M55" s="45" t="n">
         <v>86</v>
       </c>
       <c r="N55" s="30" t="n">
@@ -10816,16 +10522,16 @@
       </c>
       <c r="B56" s="31" t="inlineStr">
         <is>
-          <t>포스코인터내셔널</t>
+          <t>삼성화재</t>
         </is>
       </c>
       <c r="C56" s="35" t="inlineStr">
         <is>
-          <t>유통</t>
-        </is>
-      </c>
-      <c r="D56" s="46" t="n">
-        <v>569</v>
+          <t>보험</t>
+        </is>
+      </c>
+      <c r="D56" s="45" t="n">
+        <v>563</v>
       </c>
       <c r="E56" s="30" t="n">
         <v>9</v>
@@ -10841,7 +10547,7 @@
         </is>
       </c>
       <c r="H56" s="61" t="n">
-        <v>-699</v>
+        <v>-727</v>
       </c>
       <c r="J56" s="30" t="n">
         <v>9</v>
@@ -10856,7 +10562,7 @@
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="M56" s="46" t="n">
+      <c r="M56" s="45" t="n">
         <v>68</v>
       </c>
       <c r="N56" s="30" t="n">
@@ -10882,16 +10588,16 @@
       </c>
       <c r="B57" s="31" t="inlineStr">
         <is>
-          <t>삼성화재</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C57" s="35" t="inlineStr">
         <is>
-          <t>보험</t>
-        </is>
-      </c>
-      <c r="D57" s="46" t="n">
-        <v>563</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D57" s="45" t="n">
+        <v>554</v>
       </c>
       <c r="E57" s="30" t="n">
         <v>10</v>
@@ -10922,7 +10628,7 @@
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="M57" s="46" t="n">
+      <c r="M57" s="45" t="n">
         <v>64</v>
       </c>
       <c r="N57" s="30" t="n">
@@ -11023,7 +10729,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D62" s="46" t="n">
+      <c r="D62" s="45" t="n">
         <v>176352</v>
       </c>
       <c r="E62" s="30" t="n">
@@ -11057,7 +10763,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D63" s="46" t="n">
+      <c r="D63" s="45" t="n">
         <v>80613</v>
       </c>
       <c r="E63" s="30" t="n">
@@ -11091,7 +10797,7 @@
           <t>제약</t>
         </is>
       </c>
-      <c r="D64" s="46" t="n">
+      <c r="D64" s="45" t="n">
         <v>654</v>
       </c>
       <c r="E64" s="30" t="n">
@@ -11125,7 +10831,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D65" s="46" t="n">
+      <c r="D65" s="45" t="n">
         <v>640</v>
       </c>
       <c r="E65" s="30" t="n">
@@ -11159,7 +10865,7 @@
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D66" s="46" t="n">
+      <c r="D66" s="45" t="n">
         <v>596</v>
       </c>
       <c r="E66" s="30" t="n">
@@ -11193,7 +10899,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D67" s="46" t="n">
+      <c r="D67" s="45" t="n">
         <v>485</v>
       </c>
       <c r="E67" s="30" t="n">
@@ -11227,7 +10933,7 @@
           <t>금속</t>
         </is>
       </c>
-      <c r="D68" s="46" t="n">
+      <c r="D68" s="45" t="n">
         <v>285</v>
       </c>
       <c r="E68" s="30" t="n">
@@ -11261,7 +10967,7 @@
           <t>유통</t>
         </is>
       </c>
-      <c r="D69" s="46" t="n">
+      <c r="D69" s="45" t="n">
         <v>213</v>
       </c>
       <c r="E69" s="30" t="n">
@@ -11295,7 +11001,7 @@
           <t>건설</t>
         </is>
       </c>
-      <c r="D70" s="46" t="n">
+      <c r="D70" s="45" t="n">
         <v>211</v>
       </c>
       <c r="E70" s="30" t="n">
@@ -11329,7 +11035,7 @@
           <t>유통</t>
         </is>
       </c>
-      <c r="D71" s="46" t="n">
+      <c r="D71" s="45" t="n">
         <v>182</v>
       </c>
       <c r="E71" s="30" t="n">
@@ -11446,7 +11152,7 @@
       </c>
       <c r="Q1" s="25" t="inlineStr">
         <is>
-          <t>2026-09-01 ~ 2026-09-24</t>
+          <t>2026-09-01 ~ 2026-09-23</t>
         </is>
       </c>
     </row>
@@ -11588,7 +11294,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J5" s="46" t="n">
+      <c r="J5" s="45" t="n">
         <v>16821.2</v>
       </c>
       <c r="K5" s="66" t="n">
@@ -11653,7 +11359,7 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="J6" s="46" t="n">
+      <c r="J6" s="45" t="n">
         <v>9063.1</v>
       </c>
       <c r="K6" s="66" t="n">
@@ -11718,7 +11424,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J7" s="46" t="n">
+      <c r="J7" s="45" t="n">
         <v>7964.7</v>
       </c>
       <c r="K7" s="66" t="n">
@@ -11779,7 +11485,7 @@
         </is>
       </c>
       <c r="I8" s="35" t="inlineStr"/>
-      <c r="J8" s="46" t="n">
+      <c r="J8" s="45" t="n">
         <v>7025</v>
       </c>
       <c r="K8" s="66" t="n">
@@ -11840,7 +11546,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J9" s="46" t="n">
+      <c r="J9" s="45" t="n">
         <v>2631.2</v>
       </c>
       <c r="K9" s="66" t="n">
@@ -11905,7 +11611,7 @@
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="J10" s="46" t="n">
+      <c r="J10" s="45" t="n">
         <v>2534.2</v>
       </c>
       <c r="K10" s="66" t="n">
@@ -11970,7 +11676,7 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="J11" s="46" t="n">
+      <c r="J11" s="45" t="n">
         <v>2406.1</v>
       </c>
       <c r="K11" s="66" t="n">
@@ -12035,7 +11741,7 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="J12" s="46" t="n">
+      <c r="J12" s="45" t="n">
         <v>2239.1</v>
       </c>
       <c r="K12" s="66" t="n">
@@ -12100,7 +11806,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J13" s="46" t="n">
+      <c r="J13" s="45" t="n">
         <v>2140.1</v>
       </c>
       <c r="K13" s="66" t="n">
@@ -12165,7 +11871,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J14" s="46" t="n">
+      <c r="J14" s="45" t="n">
         <v>1923.3</v>
       </c>
       <c r="K14" s="66" t="n">
@@ -12257,7 +11963,7 @@
       </c>
       <c r="L1" s="25" t="inlineStr">
         <is>
-          <t>2026-09-01 ~ 2026-09-24</t>
+          <t>2026-09-01 ~ 2026-09-23</t>
         </is>
       </c>
     </row>
@@ -13576,7 +13282,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9E000867-A916-4865-8887-6C923CDB5826}</x14:id>
+          <x14:id>{DC07DC6C-31A3-40B8-B518-5041140083C4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13590,7 +13296,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{77DCFCE3-A0D5-471A-9234-988517A198BD}</x14:id>
+          <x14:id>{38AE9222-224D-45F8-A48E-9BE78F9FB682}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13604,7 +13310,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7B77ED0A-F457-42C8-BAB6-48B37902D852}</x14:id>
+          <x14:id>{6BDB3E11-5A87-4205-A792-57BE64617593}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13618,7 +13324,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0DAB3FDC-D89B-43EA-9FA6-9F86D998E6CE}</x14:id>
+          <x14:id>{0469EFAF-31B9-40FD-AD0A-6B1A0D046D6C}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13628,7 +13334,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9E000867-A916-4865-8887-6C923CDB5826}">
+          <x14:cfRule type="dataBar" id="{DC07DC6C-31A3-40B8-B518-5041140083C4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13641,7 +13347,7 @@
           <xm:sqref>B5:B28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{77DCFCE3-A0D5-471A-9234-988517A198BD}">
+          <x14:cfRule type="dataBar" id="{38AE9222-224D-45F8-A48E-9BE78F9FB682}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13654,7 +13360,7 @@
           <xm:sqref>C5:C28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7B77ED0A-F457-42C8-BAB6-48B37902D852}">
+          <x14:cfRule type="dataBar" id="{6BDB3E11-5A87-4205-A792-57BE64617593}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13667,7 +13373,7 @@
           <xm:sqref>D5:D28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0DAB3FDC-D89B-43EA-9FA6-9F86D998E6CE}">
+          <x14:cfRule type="dataBar" id="{0469EFAF-31B9-40FD-AD0A-6B1A0D046D6C}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/public/monthly_review.xlsx
+++ b/public/monthly_review.xlsx
@@ -1270,11 +1270,11 @@
       </c>
       <c r="C17" s="31" t="inlineStr">
         <is>
-          <t>산업재</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="D17" s="34" t="n">
-        <v>-2.61</v>
+        <v>-4.49</v>
       </c>
     </row>
     <row r="18">
@@ -13282,7 +13282,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{DC07DC6C-31A3-40B8-B518-5041140083C4}</x14:id>
+          <x14:id>{93E268D4-C5F1-4C4E-B644-9BF36B5A1229}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13296,7 +13296,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{38AE9222-224D-45F8-A48E-9BE78F9FB682}</x14:id>
+          <x14:id>{BE1E5884-4C31-4BF7-91F9-6BDC80E4E4E6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13310,7 +13310,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6BDB3E11-5A87-4205-A792-57BE64617593}</x14:id>
+          <x14:id>{B551D18A-631D-4A32-8634-797F2CACA18B}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13324,7 +13324,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0469EFAF-31B9-40FD-AD0A-6B1A0D046D6C}</x14:id>
+          <x14:id>{EDF90DEE-0094-4DCD-8507-2EE5F6B352A8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13334,7 +13334,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{DC07DC6C-31A3-40B8-B518-5041140083C4}">
+          <x14:cfRule type="dataBar" id="{93E268D4-C5F1-4C4E-B644-9BF36B5A1229}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13347,7 +13347,7 @@
           <xm:sqref>B5:B28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{38AE9222-224D-45F8-A48E-9BE78F9FB682}">
+          <x14:cfRule type="dataBar" id="{BE1E5884-4C31-4BF7-91F9-6BDC80E4E4E6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13360,7 +13360,7 @@
           <xm:sqref>C5:C28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6BDB3E11-5A87-4205-A792-57BE64617593}">
+          <x14:cfRule type="dataBar" id="{B551D18A-631D-4A32-8634-797F2CACA18B}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13373,7 +13373,7 @@
           <xm:sqref>D5:D28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0469EFAF-31B9-40FD-AD0A-6B1A0D046D6C}">
+          <x14:cfRule type="dataBar" id="{EDF90DEE-0094-4DCD-8507-2EE5F6B352A8}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/public/monthly_review.xlsx
+++ b/public/monthly_review.xlsx
@@ -326,7 +326,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -421,6 +421,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1031,7 +1034,7 @@
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>미국 종가 기준 09/30 → 10/01, %</t>
+          <t>미국 종가 기준 09/30 → 10/02, %</t>
         </is>
       </c>
       <c r="I6" s="18" t="inlineStr"/>
@@ -1101,19 +1104,19 @@
         <v>7156</v>
       </c>
       <c r="E8" s="29" t="n">
-        <v>0.19</v>
+        <v>0.93</v>
       </c>
       <c r="F8" s="29" t="n">
-        <v>0.04</v>
+        <v>0.53</v>
       </c>
       <c r="G8" s="29" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H8" s="29" t="n">
-        <v>0.31</v>
+        <v>1.23</v>
+      </c>
+      <c r="H8" s="28" t="n">
+        <v>-6.3</v>
       </c>
       <c r="I8" s="29" t="n">
-        <v>1.59</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="9">
@@ -1168,11 +1171,11 @@
       </c>
       <c r="C12" s="31" t="inlineStr">
         <is>
-          <t>에너지</t>
+          <t>반도체</t>
         </is>
       </c>
       <c r="D12" s="32" t="n">
-        <v>1.95</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="13">
@@ -1188,11 +1191,11 @@
       </c>
       <c r="C13" s="31" t="inlineStr">
         <is>
-          <t>반도체</t>
+          <t>에너지</t>
         </is>
       </c>
       <c r="D13" s="32" t="n">
-        <v>1.45</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="14">
@@ -1212,7 +1215,7 @@
         </is>
       </c>
       <c r="D14" s="32" t="n">
-        <v>1.05</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="15">
@@ -1232,7 +1235,7 @@
         </is>
       </c>
       <c r="D15" s="33" t="n">
-        <v>-2.01</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="16">
@@ -1252,7 +1255,7 @@
         </is>
       </c>
       <c r="D16" s="33" t="n">
-        <v>-1.32</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="17">
@@ -1268,11 +1271,13 @@
       </c>
       <c r="C17" s="31" t="inlineStr">
         <is>
-          <t>소재</t>
-        </is>
-      </c>
-      <c r="D17" s="33" t="n">
-        <v>-0.33</v>
+          <t>데이터 없음</t>
+        </is>
+      </c>
+      <c r="D17" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1980,7 +1985,7 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="D46" s="34" t="inlineStr">
+      <c r="D46" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2021,7 +2026,7 @@
           <t>제주반도체</t>
         </is>
       </c>
-      <c r="D47" s="34" t="inlineStr">
+      <c r="D47" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2062,7 +2067,7 @@
           <t>에코프로</t>
         </is>
       </c>
-      <c r="D48" s="34" t="inlineStr">
+      <c r="D48" s="35" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
@@ -2103,7 +2108,7 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="D49" s="34" t="inlineStr">
+      <c r="D49" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
@@ -2144,7 +2149,7 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="D50" s="34" t="inlineStr">
+      <c r="D50" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2185,7 +2190,7 @@
           <t>LIG디펜스앤에어로스페이스</t>
         </is>
       </c>
-      <c r="D51" s="34" t="inlineStr">
+      <c r="D51" s="35" t="inlineStr">
         <is>
           <t>금속</t>
         </is>
@@ -2226,7 +2231,7 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="D52" s="34" t="inlineStr">
+      <c r="D52" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2267,7 +2272,7 @@
           <t>한화시스템</t>
         </is>
       </c>
-      <c r="D53" s="34" t="inlineStr">
+      <c r="D53" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2308,7 +2313,7 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="D54" s="34" t="inlineStr">
+      <c r="D54" s="35" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
@@ -2349,7 +2354,7 @@
           <t>한화솔루션</t>
         </is>
       </c>
-      <c r="D55" s="34" t="inlineStr">
+      <c r="D55" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
@@ -2386,7 +2391,7 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="D56" s="34" t="inlineStr">
+      <c r="D56" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2427,7 +2432,7 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="D57" s="34" t="inlineStr">
+      <c r="D57" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2468,7 +2473,7 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="D58" s="34" t="inlineStr">
+      <c r="D58" s="35" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
@@ -2509,7 +2514,7 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="D59" s="34" t="inlineStr">
+      <c r="D59" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
@@ -2550,7 +2555,7 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="D60" s="34" t="inlineStr">
+      <c r="D60" s="35" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
@@ -2591,7 +2596,7 @@
           <t>두산</t>
         </is>
       </c>
-      <c r="D61" s="34" t="inlineStr">
+      <c r="D61" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2632,7 +2637,7 @@
           <t>브릴스</t>
         </is>
       </c>
-      <c r="D62" s="34" t="inlineStr">
+      <c r="D62" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
@@ -2667,7 +2672,7 @@
           <t>현대건설</t>
         </is>
       </c>
-      <c r="D63" s="34" t="inlineStr">
+      <c r="D63" s="35" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
@@ -2708,7 +2713,7 @@
           <t>삼성바이오로직스</t>
         </is>
       </c>
-      <c r="D64" s="34" t="inlineStr">
+      <c r="D64" s="35" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
@@ -2745,7 +2750,7 @@
           <t>HD건설기계</t>
         </is>
       </c>
-      <c r="D65" s="34" t="inlineStr">
+      <c r="D65" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
@@ -2799,7 +2804,7 @@
       <c r="K67" s="3" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="35" t="inlineStr">
+      <c r="A68" s="36" t="inlineStr">
         <is>
           <t>● 동반강세 — 추세 지속형 상방 관찰</t>
         </is>
@@ -2816,12 +2821,12 @@
           <t>한화</t>
         </is>
       </c>
-      <c r="B69" s="34" t="inlineStr">
+      <c r="B69" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="C69" s="36" t="n">
+      <c r="C69" s="37" t="n">
         <v>3</v>
       </c>
       <c r="D69" s="31" t="inlineStr"/>
@@ -2831,12 +2836,12 @@
           <t>일신방직</t>
         </is>
       </c>
-      <c r="H69" s="34" t="inlineStr">
+      <c r="H69" s="35" t="inlineStr">
         <is>
           <t>섬유·의류</t>
         </is>
       </c>
-      <c r="I69" s="37" t="n">
+      <c r="I69" s="38" t="n">
         <v>3</v>
       </c>
       <c r="J69" s="31" t="inlineStr"/>
@@ -2860,12 +2865,12 @@
           <t>흥아해운</t>
         </is>
       </c>
-      <c r="B71" s="34" t="inlineStr">
+      <c r="B71" s="35" t="inlineStr">
         <is>
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="C71" s="36" t="n">
+      <c r="C71" s="37" t="n">
         <v>2</v>
       </c>
       <c r="D71" s="31" t="inlineStr"/>
@@ -2875,12 +2880,12 @@
           <t>F&amp;F</t>
         </is>
       </c>
-      <c r="H71" s="34" t="inlineStr">
+      <c r="H71" s="35" t="inlineStr">
         <is>
           <t>섬유·의류</t>
         </is>
       </c>
-      <c r="I71" s="37" t="n">
+      <c r="I71" s="38" t="n">
         <v>1</v>
       </c>
       <c r="J71" s="31" t="inlineStr"/>
@@ -2904,12 +2909,12 @@
           <t>에코프로</t>
         </is>
       </c>
-      <c r="B73" s="34" t="inlineStr">
+      <c r="B73" s="35" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="C73" s="36" t="n">
+      <c r="C73" s="37" t="n">
         <v>1</v>
       </c>
       <c r="D73" s="31" t="inlineStr"/>
@@ -2928,12 +2933,12 @@
           <t>한화솔루션</t>
         </is>
       </c>
-      <c r="B75" s="34" t="inlineStr">
+      <c r="B75" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="C75" s="36" t="n">
+      <c r="C75" s="37" t="n">
         <v>1</v>
       </c>
       <c r="D75" s="31" t="inlineStr"/>
@@ -2952,12 +2957,12 @@
           <t>S-Oil</t>
         </is>
       </c>
-      <c r="B77" s="34" t="inlineStr">
+      <c r="B77" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="C77" s="36" t="n">
+      <c r="C77" s="37" t="n">
         <v>1</v>
       </c>
       <c r="D77" s="31" t="inlineStr"/>
@@ -2972,12 +2977,12 @@
     </row>
     <row r="79"/>
     <row r="80">
-      <c r="A80" s="38" t="inlineStr">
+      <c r="A80" s="39" t="inlineStr">
         <is>
           <t>● 수급이탈 — 상승 후 약화 관찰</t>
         </is>
       </c>
-      <c r="G80" s="39" t="inlineStr">
+      <c r="G80" s="40" t="inlineStr">
         <is>
           <t>● 동반약세 — 약세 지속형 하방 관찰</t>
         </is>
@@ -2989,12 +2994,12 @@
           <t>삼성E&amp;A</t>
         </is>
       </c>
-      <c r="B81" s="34" t="inlineStr">
+      <c r="B81" s="35" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="C81" s="40" t="n">
+      <c r="C81" s="41" t="n">
         <v>-3</v>
       </c>
       <c r="D81" s="31" t="inlineStr"/>
@@ -3004,12 +3009,12 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="H81" s="41" t="inlineStr">
+      <c r="H81" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="I81" s="42" t="n">
+      <c r="I81" s="43" t="n">
         <v>-4</v>
       </c>
       <c r="J81" s="31" t="inlineStr"/>
@@ -3033,12 +3038,12 @@
           <t>알테오젠</t>
         </is>
       </c>
-      <c r="B83" s="34" t="inlineStr">
+      <c r="B83" s="35" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="C83" s="40" t="n">
+      <c r="C83" s="41" t="n">
         <v>-1</v>
       </c>
       <c r="D83" s="31" t="inlineStr"/>
@@ -3048,12 +3053,12 @@
           <t>현대건설</t>
         </is>
       </c>
-      <c r="H83" s="34" t="inlineStr">
+      <c r="H83" s="35" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
       </c>
-      <c r="I83" s="42" t="n">
+      <c r="I83" s="43" t="n">
         <v>-3</v>
       </c>
       <c r="J83" s="31" t="inlineStr"/>
@@ -3072,32 +3077,32 @@
       </c>
     </row>
     <row r="85" ht="31" customHeight="1" s="15">
-      <c r="A85" s="43" t="inlineStr">
+      <c r="A85" s="44" t="inlineStr">
         <is>
           <t>HD현대마린솔루션</t>
         </is>
       </c>
-      <c r="B85" s="34" t="inlineStr">
+      <c r="B85" s="35" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="C85" s="40" t="n">
+      <c r="C85" s="41" t="n">
         <v>-1</v>
       </c>
       <c r="D85" s="31" t="inlineStr"/>
       <c r="E85" s="31" t="inlineStr"/>
-      <c r="G85" s="43" t="inlineStr">
+      <c r="G85" s="44" t="inlineStr">
         <is>
           <t>삼성바이오로직스</t>
         </is>
       </c>
-      <c r="H85" s="34" t="inlineStr">
+      <c r="H85" s="35" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="I85" s="42" t="n">
+      <c r="I85" s="43" t="n">
         <v>-3</v>
       </c>
       <c r="J85" s="31" t="inlineStr"/>
@@ -3121,12 +3126,12 @@
           <t>SK바이오팜</t>
         </is>
       </c>
-      <c r="B87" s="34" t="inlineStr">
+      <c r="B87" s="35" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="C87" s="40" t="n">
+      <c r="C87" s="41" t="n">
         <v>-1</v>
       </c>
       <c r="D87" s="31" t="inlineStr"/>
@@ -3136,12 +3141,12 @@
           <t>한화오션</t>
         </is>
       </c>
-      <c r="H87" s="41" t="inlineStr">
+      <c r="H87" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="I87" s="42" t="n">
+      <c r="I87" s="43" t="n">
         <v>-3</v>
       </c>
       <c r="J87" s="31" t="inlineStr"/>
@@ -3165,12 +3170,12 @@
           <t>리가켐바이오</t>
         </is>
       </c>
-      <c r="B89" s="34" t="inlineStr">
+      <c r="B89" s="35" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="C89" s="40" t="n">
+      <c r="C89" s="41" t="n">
         <v>-1</v>
       </c>
       <c r="D89" s="31" t="inlineStr"/>
@@ -3180,12 +3185,12 @@
           <t>기아</t>
         </is>
       </c>
-      <c r="H89" s="41" t="inlineStr">
+      <c r="H89" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="I89" s="42" t="n">
+      <c r="I89" s="43" t="n">
         <v>-3</v>
       </c>
       <c r="J89" s="31" t="inlineStr"/>
@@ -3205,7 +3210,7 @@
     </row>
     <row r="91"/>
     <row r="92" ht="31" customHeight="1" s="15">
-      <c r="A92" s="44" t="inlineStr">
+      <c r="A92" s="45" t="inlineStr">
         <is>
           <t>현재 확보된 월간 리뷰 데이터 유니버스(순매수 상위 30 등재 · 공매도/대차 랭킹 · 월간 촉매 · 신호 섹터 시총 상위 10) 기준 — 전 시장 스크리닝 아님 · 관찰 우선순위이며 매매 권유 아님</t>
         </is>
@@ -3395,7 +3400,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D108" s="34" t="inlineStr">
+      <c r="D108" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
@@ -3430,7 +3435,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D109" s="34" t="inlineStr">
+      <c r="D109" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -3465,7 +3470,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D110" s="34" t="inlineStr">
+      <c r="D110" s="35" t="inlineStr">
         <is>
           <t>섬유·의류</t>
         </is>
@@ -3500,7 +3505,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D111" s="34" t="inlineStr">
+      <c r="D111" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
@@ -3728,62 +3733,62 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="45" t="inlineStr">
+      <c r="A5" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B5" s="45" t="inlineStr">
+      <c r="B5" s="46" t="inlineStr">
         <is>
           <t>시장</t>
         </is>
       </c>
-      <c r="C5" s="45" t="inlineStr">
+      <c r="C5" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D5" s="45" t="inlineStr">
+      <c r="D5" s="46" t="inlineStr">
         <is>
           <t>합산</t>
         </is>
       </c>
-      <c r="E5" s="45" t="inlineStr">
+      <c r="E5" s="46" t="inlineStr">
         <is>
           <t>외인</t>
         </is>
       </c>
-      <c r="F5" s="45" t="inlineStr">
+      <c r="F5" s="46" t="inlineStr">
         <is>
           <t>기관</t>
         </is>
       </c>
-      <c r="G5" s="45" t="inlineStr">
+      <c r="G5" s="46" t="inlineStr">
         <is>
           <t>개인</t>
         </is>
       </c>
-      <c r="H5" s="45" t="inlineStr">
+      <c r="H5" s="46" t="inlineStr">
         <is>
           <t>공매도</t>
         </is>
       </c>
-      <c r="I5" s="45" t="inlineStr">
+      <c r="I5" s="46" t="inlineStr">
         <is>
           <t>대차잔고</t>
         </is>
       </c>
-      <c r="J5" s="45" t="inlineStr">
+      <c r="J5" s="46" t="inlineStr">
         <is>
           <t>대차증감</t>
         </is>
       </c>
-      <c r="K5" s="45" t="inlineStr">
+      <c r="K5" s="46" t="inlineStr">
         <is>
           <t>월간등락(%)</t>
         </is>
       </c>
-      <c r="L5" s="45" t="inlineStr">
+      <c r="L5" s="46" t="inlineStr">
         <is>
           <t>신고가대비(%)</t>
         </is>
@@ -3800,36 +3805,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C6" s="34" t="inlineStr">
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D6" s="46" t="n">
+      <c r="D6" s="47" t="n">
         <v>54</v>
       </c>
-      <c r="E6" s="46" t="n">
+      <c r="E6" s="47" t="n">
         <v>577</v>
       </c>
-      <c r="F6" s="47" t="n">
+      <c r="F6" s="48" t="n">
         <v>-523</v>
       </c>
-      <c r="G6" s="47" t="n">
+      <c r="G6" s="48" t="n">
         <v>-84</v>
       </c>
-      <c r="H6" s="48" t="n">
+      <c r="H6" s="49" t="n">
         <v>187.5</v>
       </c>
-      <c r="I6" s="48" t="n">
+      <c r="I6" s="49" t="n">
         <v>4179.2</v>
       </c>
-      <c r="J6" s="49" t="n">
+      <c r="J6" s="50" t="n">
         <v>405.2</v>
       </c>
-      <c r="K6" s="50" t="n">
+      <c r="K6" s="51" t="n">
         <v>2.28</v>
       </c>
-      <c r="L6" s="51" t="n">
+      <c r="L6" s="52" t="n">
         <v>-7.86</v>
       </c>
     </row>
@@ -3844,36 +3849,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C7" s="34" t="inlineStr">
+      <c r="C7" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D7" s="46" t="n">
+      <c r="D7" s="47" t="n">
         <v>382</v>
       </c>
-      <c r="E7" s="46" t="n">
+      <c r="E7" s="47" t="n">
         <v>408</v>
       </c>
-      <c r="F7" s="47" t="n">
+      <c r="F7" s="48" t="n">
         <v>-26</v>
       </c>
-      <c r="G7" s="47" t="n">
+      <c r="G7" s="48" t="n">
         <v>-411</v>
       </c>
-      <c r="H7" s="48" t="n">
+      <c r="H7" s="49" t="n">
         <v>194</v>
       </c>
-      <c r="I7" s="48" t="n">
+      <c r="I7" s="49" t="n">
         <v>10105.3</v>
       </c>
-      <c r="J7" s="49" t="n">
+      <c r="J7" s="50" t="n">
         <v>545.2</v>
       </c>
-      <c r="K7" s="50" t="n">
+      <c r="K7" s="51" t="n">
         <v>11.57</v>
       </c>
-      <c r="L7" s="52" t="n">
+      <c r="L7" s="53" t="n">
         <v>-2.03</v>
       </c>
     </row>
@@ -3888,36 +3893,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C8" s="34" t="inlineStr">
+      <c r="C8" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D8" s="46" t="n">
+      <c r="D8" s="47" t="n">
         <v>194</v>
       </c>
-      <c r="E8" s="46" t="n">
+      <c r="E8" s="47" t="n">
         <v>200</v>
       </c>
-      <c r="F8" s="47" t="n">
+      <c r="F8" s="48" t="n">
         <v>-6</v>
       </c>
-      <c r="G8" s="47" t="n">
+      <c r="G8" s="48" t="n">
         <v>-191</v>
       </c>
-      <c r="H8" s="48" t="n">
+      <c r="H8" s="49" t="n">
         <v>128.2</v>
       </c>
-      <c r="I8" s="48" t="n">
+      <c r="I8" s="49" t="n">
         <v>3509</v>
       </c>
-      <c r="J8" s="53" t="n">
+      <c r="J8" s="54" t="n">
         <v>-352.6</v>
       </c>
-      <c r="K8" s="50" t="n">
+      <c r="K8" s="51" t="n">
         <v>1.98</v>
       </c>
-      <c r="L8" s="51" t="n">
+      <c r="L8" s="52" t="n">
         <v>-7.07</v>
       </c>
     </row>
@@ -3932,36 +3937,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C9" s="34" t="inlineStr">
+      <c r="C9" s="35" t="inlineStr">
         <is>
           <t>의료·정밀기기</t>
         </is>
       </c>
-      <c r="D9" s="46" t="n">
+      <c r="D9" s="47" t="n">
         <v>174</v>
       </c>
-      <c r="E9" s="46" t="n">
+      <c r="E9" s="47" t="n">
         <v>223</v>
       </c>
-      <c r="F9" s="47" t="n">
+      <c r="F9" s="48" t="n">
         <v>-49</v>
       </c>
-      <c r="G9" s="47" t="n">
+      <c r="G9" s="48" t="n">
         <v>-162</v>
       </c>
-      <c r="H9" s="48" t="n">
+      <c r="H9" s="49" t="n">
         <v>12</v>
       </c>
-      <c r="I9" s="48" t="n">
+      <c r="I9" s="49" t="n">
         <v>556.4</v>
       </c>
-      <c r="J9" s="49" t="n">
+      <c r="J9" s="50" t="n">
         <v>68.8</v>
       </c>
-      <c r="K9" s="50" t="n">
+      <c r="K9" s="51" t="n">
         <v>14.52</v>
       </c>
-      <c r="L9" s="52" t="n">
+      <c r="L9" s="53" t="n">
         <v>-2.69</v>
       </c>
     </row>
@@ -3976,36 +3981,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C10" s="34" t="inlineStr">
+      <c r="C10" s="35" t="inlineStr">
         <is>
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="D10" s="47" t="n">
+      <c r="D10" s="48" t="n">
         <v>-129</v>
       </c>
-      <c r="E10" s="47" t="n">
+      <c r="E10" s="48" t="n">
         <v>-131</v>
       </c>
-      <c r="F10" s="46" t="n">
+      <c r="F10" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="46" t="n">
+      <c r="G10" s="47" t="n">
         <v>120</v>
       </c>
-      <c r="H10" s="48" t="n">
+      <c r="H10" s="49" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="I10" s="48" t="n">
+      <c r="I10" s="49" t="n">
         <v>1958.5</v>
       </c>
-      <c r="J10" s="53" t="n">
+      <c r="J10" s="54" t="n">
         <v>-47.9</v>
       </c>
-      <c r="K10" s="54" t="n">
+      <c r="K10" s="55" t="n">
         <v>-4.84</v>
       </c>
-      <c r="L10" s="51" t="n">
+      <c r="L10" s="52" t="n">
         <v>-6.56</v>
       </c>
     </row>
@@ -4020,36 +4025,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C11" s="34" t="inlineStr">
+      <c r="C11" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D11" s="46" t="n">
+      <c r="D11" s="47" t="n">
         <v>111</v>
       </c>
-      <c r="E11" s="46" t="n">
+      <c r="E11" s="47" t="n">
         <v>107</v>
       </c>
-      <c r="F11" s="46" t="n">
+      <c r="F11" s="47" t="n">
         <v>4</v>
       </c>
-      <c r="G11" s="47" t="n">
+      <c r="G11" s="48" t="n">
         <v>-96</v>
       </c>
-      <c r="H11" s="48" t="n">
+      <c r="H11" s="49" t="n">
         <v>5.5</v>
       </c>
-      <c r="I11" s="48" t="n">
+      <c r="I11" s="49" t="n">
         <v>275.5</v>
       </c>
-      <c r="J11" s="49" t="n">
+      <c r="J11" s="50" t="n">
         <v>14.9</v>
       </c>
-      <c r="K11" s="50" t="n">
+      <c r="K11" s="51" t="n">
         <v>19.39</v>
       </c>
-      <c r="L11" s="55" t="n">
+      <c r="L11" s="56" t="n">
         <v>-0.85</v>
       </c>
     </row>
@@ -4064,36 +4069,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C12" s="34" t="inlineStr">
+      <c r="C12" s="35" t="inlineStr">
         <is>
           <t>의료·정밀기기</t>
         </is>
       </c>
-      <c r="D12" s="46" t="n">
+      <c r="D12" s="47" t="n">
         <v>126</v>
       </c>
-      <c r="E12" s="46" t="n">
+      <c r="E12" s="47" t="n">
         <v>65</v>
       </c>
-      <c r="F12" s="46" t="n">
+      <c r="F12" s="47" t="n">
         <v>61</v>
       </c>
-      <c r="G12" s="47" t="n">
+      <c r="G12" s="48" t="n">
         <v>-120</v>
       </c>
-      <c r="H12" s="48" t="n">
+      <c r="H12" s="49" t="n">
         <v>29.3</v>
       </c>
-      <c r="I12" s="48" t="n">
+      <c r="I12" s="49" t="n">
         <v>1905.1</v>
       </c>
-      <c r="J12" s="49" t="n">
+      <c r="J12" s="50" t="n">
         <v>112.8</v>
       </c>
-      <c r="K12" s="50" t="n">
+      <c r="K12" s="51" t="n">
         <v>0.87</v>
       </c>
-      <c r="L12" s="51" t="n">
+      <c r="L12" s="52" t="n">
         <v>-9.640000000000001</v>
       </c>
     </row>
@@ -4108,36 +4113,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C13" s="34" t="inlineStr">
+      <c r="C13" s="35" t="inlineStr">
         <is>
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="D13" s="46" t="n">
+      <c r="D13" s="47" t="n">
         <v>161</v>
       </c>
-      <c r="E13" s="46" t="n">
+      <c r="E13" s="47" t="n">
         <v>54</v>
       </c>
-      <c r="F13" s="46" t="n">
+      <c r="F13" s="47" t="n">
         <v>108</v>
       </c>
-      <c r="G13" s="47" t="n">
+      <c r="G13" s="48" t="n">
         <v>-157</v>
       </c>
-      <c r="H13" s="48" t="n">
+      <c r="H13" s="49" t="n">
         <v>8.6</v>
       </c>
-      <c r="I13" s="48" t="n">
+      <c r="I13" s="49" t="n">
         <v>1252.2</v>
       </c>
-      <c r="J13" s="49" t="n">
+      <c r="J13" s="50" t="n">
         <v>25.7</v>
       </c>
-      <c r="K13" s="50" t="n">
+      <c r="K13" s="51" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="L13" s="51" t="n">
+      <c r="L13" s="52" t="n">
         <v>-5.77</v>
       </c>
     </row>
@@ -4152,36 +4157,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C14" s="34" t="inlineStr">
+      <c r="C14" s="35" t="inlineStr">
         <is>
           <t>금속</t>
         </is>
       </c>
-      <c r="D14" s="46" t="n">
+      <c r="D14" s="47" t="n">
         <v>8</v>
       </c>
-      <c r="E14" s="47" t="n">
+      <c r="E14" s="48" t="n">
         <v>-2</v>
       </c>
-      <c r="F14" s="46" t="n">
+      <c r="F14" s="47" t="n">
         <v>10</v>
       </c>
-      <c r="G14" s="47" t="n">
+      <c r="G14" s="48" t="n">
         <v>-8</v>
       </c>
-      <c r="H14" s="48" t="n">
+      <c r="H14" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="48" t="n">
+      <c r="I14" s="49" t="n">
         <v>23.3</v>
       </c>
-      <c r="J14" s="53" t="n">
+      <c r="J14" s="54" t="n">
         <v>-5.7</v>
       </c>
-      <c r="K14" s="50" t="n">
+      <c r="K14" s="51" t="n">
         <v>20.97</v>
       </c>
-      <c r="L14" s="51" t="n">
+      <c r="L14" s="52" t="n">
         <v>-6.38</v>
       </c>
     </row>
@@ -4196,36 +4201,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C15" s="34" t="inlineStr">
+      <c r="C15" s="35" t="inlineStr">
         <is>
           <t>음식료·담배</t>
         </is>
       </c>
-      <c r="D15" s="47" t="n">
+      <c r="D15" s="48" t="n">
         <v>-168</v>
       </c>
-      <c r="E15" s="47" t="n">
+      <c r="E15" s="48" t="n">
         <v>-202</v>
       </c>
-      <c r="F15" s="46" t="n">
+      <c r="F15" s="47" t="n">
         <v>34</v>
       </c>
-      <c r="G15" s="46" t="n">
+      <c r="G15" s="47" t="n">
         <v>27</v>
       </c>
-      <c r="H15" s="48" t="n">
+      <c r="H15" s="49" t="n">
         <v>29</v>
       </c>
-      <c r="I15" s="48" t="n">
+      <c r="I15" s="49" t="n">
         <v>2561</v>
       </c>
-      <c r="J15" s="53" t="n">
+      <c r="J15" s="54" t="n">
         <v>-156.7</v>
       </c>
-      <c r="K15" s="54" t="n">
+      <c r="K15" s="55" t="n">
         <v>-0.06</v>
       </c>
-      <c r="L15" s="51" t="n">
+      <c r="L15" s="52" t="n">
         <v>-9.380000000000001</v>
       </c>
     </row>
@@ -4240,36 +4245,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C16" s="34" t="inlineStr">
+      <c r="C16" s="35" t="inlineStr">
         <is>
           <t>의료·정밀기기</t>
         </is>
       </c>
-      <c r="D16" s="47" t="n">
+      <c r="D16" s="48" t="n">
         <v>-1</v>
       </c>
-      <c r="E16" s="47" t="n">
+      <c r="E16" s="48" t="n">
         <v>-1</v>
       </c>
-      <c r="F16" s="56" t="n">
+      <c r="F16" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="46" t="n">
+      <c r="G16" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="48" t="n">
+      <c r="H16" s="49" t="n">
         <v>0.6</v>
       </c>
-      <c r="I16" s="48" t="n">
+      <c r="I16" s="49" t="n">
         <v>21.2</v>
       </c>
-      <c r="J16" s="49" t="n">
+      <c r="J16" s="50" t="n">
         <v>3.3</v>
       </c>
-      <c r="K16" s="50" t="n">
+      <c r="K16" s="51" t="n">
         <v>40.46</v>
       </c>
-      <c r="L16" s="51" t="n">
+      <c r="L16" s="52" t="n">
         <v>-9.27</v>
       </c>
     </row>
@@ -4284,36 +4289,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C17" s="34" t="inlineStr">
+      <c r="C17" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D17" s="46" t="n">
+      <c r="D17" s="47" t="n">
         <v>11</v>
       </c>
-      <c r="E17" s="46" t="n">
+      <c r="E17" s="47" t="n">
         <v>72</v>
       </c>
-      <c r="F17" s="47" t="n">
+      <c r="F17" s="48" t="n">
         <v>-60</v>
       </c>
-      <c r="G17" s="47" t="n">
+      <c r="G17" s="48" t="n">
         <v>-10</v>
       </c>
-      <c r="H17" s="48" t="n">
+      <c r="H17" s="49" t="n">
         <v>2.5</v>
       </c>
-      <c r="I17" s="48" t="n">
+      <c r="I17" s="49" t="n">
         <v>323.4</v>
       </c>
-      <c r="J17" s="49" t="n">
+      <c r="J17" s="50" t="n">
         <v>10.5</v>
       </c>
-      <c r="K17" s="54" t="n">
+      <c r="K17" s="55" t="n">
         <v>-1.4</v>
       </c>
-      <c r="L17" s="51" t="n">
+      <c r="L17" s="52" t="n">
         <v>-5.01</v>
       </c>
     </row>
@@ -4328,36 +4333,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C18" s="34" t="inlineStr">
+      <c r="C18" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D18" s="46" t="n">
+      <c r="D18" s="47" t="n">
         <v>89</v>
       </c>
-      <c r="E18" s="46" t="n">
+      <c r="E18" s="47" t="n">
         <v>14</v>
       </c>
-      <c r="F18" s="46" t="n">
+      <c r="F18" s="47" t="n">
         <v>75</v>
       </c>
-      <c r="G18" s="47" t="n">
+      <c r="G18" s="48" t="n">
         <v>-90</v>
       </c>
-      <c r="H18" s="48" t="n">
+      <c r="H18" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="I18" s="48" t="n">
+      <c r="I18" s="49" t="n">
         <v>194.2</v>
       </c>
-      <c r="J18" s="49" t="n">
+      <c r="J18" s="50" t="n">
         <v>23.7</v>
       </c>
-      <c r="K18" s="50" t="n">
+      <c r="K18" s="51" t="n">
         <v>18.41</v>
       </c>
-      <c r="L18" s="55" t="n">
+      <c r="L18" s="56" t="n">
         <v>-0.85</v>
       </c>
     </row>
@@ -4372,36 +4377,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C19" s="34" t="inlineStr">
+      <c r="C19" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D19" s="46" t="n">
+      <c r="D19" s="47" t="n">
         <v>6</v>
       </c>
-      <c r="E19" s="46" t="n">
+      <c r="E19" s="47" t="n">
         <v>12</v>
       </c>
-      <c r="F19" s="47" t="n">
+      <c r="F19" s="48" t="n">
         <v>-6</v>
       </c>
-      <c r="G19" s="47" t="n">
+      <c r="G19" s="48" t="n">
         <v>-10</v>
       </c>
-      <c r="H19" s="48" t="n">
+      <c r="H19" s="49" t="n">
         <v>6.8</v>
       </c>
-      <c r="I19" s="48" t="n">
+      <c r="I19" s="49" t="n">
         <v>157.5</v>
       </c>
-      <c r="J19" s="53" t="n">
+      <c r="J19" s="54" t="n">
         <v>-0.6</v>
       </c>
-      <c r="K19" s="50" t="n">
+      <c r="K19" s="51" t="n">
         <v>1.32</v>
       </c>
-      <c r="L19" s="55" t="n">
+      <c r="L19" s="56" t="n">
         <v>-1.52</v>
       </c>
     </row>
@@ -4416,36 +4421,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C20" s="34" t="inlineStr">
+      <c r="C20" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D20" s="47" t="n">
+      <c r="D20" s="48" t="n">
         <v>-8</v>
       </c>
-      <c r="E20" s="47" t="n">
+      <c r="E20" s="48" t="n">
         <v>-8</v>
       </c>
-      <c r="F20" s="56" t="n">
+      <c r="F20" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="46" t="n">
+      <c r="G20" s="47" t="n">
         <v>9</v>
       </c>
-      <c r="H20" s="48" t="n">
+      <c r="H20" s="49" t="n">
         <v>3.6</v>
       </c>
-      <c r="I20" s="48" t="n">
+      <c r="I20" s="49" t="n">
         <v>42</v>
       </c>
-      <c r="J20" s="49" t="n">
+      <c r="J20" s="50" t="n">
         <v>1.7</v>
       </c>
-      <c r="K20" s="50" t="n">
+      <c r="K20" s="51" t="n">
         <v>15.07</v>
       </c>
-      <c r="L20" s="51" t="n">
+      <c r="L20" s="52" t="n">
         <v>-5.89</v>
       </c>
     </row>
@@ -4460,36 +4465,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C21" s="34" t="inlineStr">
+      <c r="C21" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D21" s="46" t="n">
+      <c r="D21" s="47" t="n">
         <v>36</v>
       </c>
-      <c r="E21" s="46" t="n">
+      <c r="E21" s="47" t="n">
         <v>7</v>
       </c>
-      <c r="F21" s="46" t="n">
+      <c r="F21" s="47" t="n">
         <v>29</v>
       </c>
-      <c r="G21" s="47" t="n">
+      <c r="G21" s="48" t="n">
         <v>-38</v>
       </c>
-      <c r="H21" s="48" t="n">
+      <c r="H21" s="49" t="n">
         <v>2.7</v>
       </c>
-      <c r="I21" s="48" t="n">
+      <c r="I21" s="49" t="n">
         <v>192.2</v>
       </c>
-      <c r="J21" s="49" t="n">
+      <c r="J21" s="50" t="n">
         <v>3.2</v>
       </c>
-      <c r="K21" s="50" t="n">
+      <c r="K21" s="51" t="n">
         <v>7.53</v>
       </c>
-      <c r="L21" s="52" t="n">
+      <c r="L21" s="53" t="n">
         <v>-3.51</v>
       </c>
     </row>
@@ -4504,36 +4509,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C22" s="34" t="inlineStr">
+      <c r="C22" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D22" s="46" t="n">
+      <c r="D22" s="47" t="n">
         <v>116</v>
       </c>
-      <c r="E22" s="46" t="n">
+      <c r="E22" s="47" t="n">
         <v>65</v>
       </c>
-      <c r="F22" s="46" t="n">
+      <c r="F22" s="47" t="n">
         <v>51</v>
       </c>
-      <c r="G22" s="47" t="n">
+      <c r="G22" s="48" t="n">
         <v>-109</v>
       </c>
-      <c r="H22" s="48" t="n">
+      <c r="H22" s="49" t="n">
         <v>5.2</v>
       </c>
-      <c r="I22" s="48" t="n">
+      <c r="I22" s="49" t="n">
         <v>194.2</v>
       </c>
-      <c r="J22" s="49" t="n">
+      <c r="J22" s="50" t="n">
         <v>16.9</v>
       </c>
-      <c r="K22" s="50" t="n">
+      <c r="K22" s="51" t="n">
         <v>14.08</v>
       </c>
-      <c r="L22" s="51" t="n">
+      <c r="L22" s="52" t="n">
         <v>-7.47</v>
       </c>
     </row>
@@ -4548,36 +4553,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C23" s="34" t="inlineStr">
+      <c r="C23" s="35" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="D23" s="46" t="n">
+      <c r="D23" s="47" t="n">
         <v>74</v>
       </c>
-      <c r="E23" s="46" t="n">
+      <c r="E23" s="47" t="n">
         <v>47</v>
       </c>
-      <c r="F23" s="46" t="n">
+      <c r="F23" s="47" t="n">
         <v>26</v>
       </c>
-      <c r="G23" s="47" t="n">
+      <c r="G23" s="48" t="n">
         <v>-74</v>
       </c>
-      <c r="H23" s="48" t="n">
+      <c r="H23" s="49" t="n">
         <v>21.7</v>
       </c>
-      <c r="I23" s="48" t="n">
+      <c r="I23" s="49" t="n">
         <v>827.4</v>
       </c>
-      <c r="J23" s="49" t="n">
+      <c r="J23" s="50" t="n">
         <v>41.6</v>
       </c>
-      <c r="K23" s="50" t="n">
+      <c r="K23" s="51" t="n">
         <v>3.8</v>
       </c>
-      <c r="L23" s="52" t="n">
+      <c r="L23" s="53" t="n">
         <v>-2.17</v>
       </c>
     </row>
@@ -4592,36 +4597,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C24" s="34" t="inlineStr">
+      <c r="C24" s="35" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="D24" s="47" t="n">
+      <c r="D24" s="48" t="n">
         <v>-3</v>
       </c>
-      <c r="E24" s="46" t="n">
+      <c r="E24" s="47" t="n">
         <v>12</v>
       </c>
-      <c r="F24" s="47" t="n">
+      <c r="F24" s="48" t="n">
         <v>-15</v>
       </c>
-      <c r="G24" s="46" t="n">
+      <c r="G24" s="47" t="n">
         <v>2</v>
       </c>
-      <c r="H24" s="48" t="n">
+      <c r="H24" s="49" t="n">
         <v>9.6</v>
       </c>
-      <c r="I24" s="48" t="n">
+      <c r="I24" s="49" t="n">
         <v>632.8</v>
       </c>
-      <c r="J24" s="49" t="n">
+      <c r="J24" s="50" t="n">
         <v>4</v>
       </c>
-      <c r="K24" s="50" t="n">
+      <c r="K24" s="51" t="n">
         <v>2.59</v>
       </c>
-      <c r="L24" s="52" t="n">
+      <c r="L24" s="53" t="n">
         <v>-3.11</v>
       </c>
     </row>
@@ -4636,36 +4641,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C25" s="34" t="inlineStr">
+      <c r="C25" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D25" s="47" t="n">
+      <c r="D25" s="48" t="n">
         <v>-7</v>
       </c>
-      <c r="E25" s="46" t="n">
+      <c r="E25" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="47" t="n">
+      <c r="F25" s="48" t="n">
         <v>-8</v>
       </c>
-      <c r="G25" s="46" t="n">
+      <c r="G25" s="47" t="n">
         <v>7</v>
       </c>
-      <c r="H25" s="48" t="n">
+      <c r="H25" s="49" t="n">
         <v>2.2</v>
       </c>
-      <c r="I25" s="48" t="n">
+      <c r="I25" s="49" t="n">
         <v>54.5</v>
       </c>
-      <c r="J25" s="49" t="n">
+      <c r="J25" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="K25" s="54" t="n">
+      <c r="K25" s="55" t="n">
         <v>-2.85</v>
       </c>
-      <c r="L25" s="51" t="n">
+      <c r="L25" s="52" t="n">
         <v>-7.14</v>
       </c>
     </row>
@@ -4680,36 +4685,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C26" s="34" t="inlineStr">
+      <c r="C26" s="35" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="D26" s="46" t="n">
+      <c r="D26" s="47" t="n">
         <v>19</v>
       </c>
-      <c r="E26" s="47" t="n">
+      <c r="E26" s="48" t="n">
         <v>-9</v>
       </c>
-      <c r="F26" s="46" t="n">
+      <c r="F26" s="47" t="n">
         <v>28</v>
       </c>
-      <c r="G26" s="47" t="n">
+      <c r="G26" s="48" t="n">
         <v>-19</v>
       </c>
-      <c r="H26" s="48" t="n">
+      <c r="H26" s="49" t="n">
         <v>3.4</v>
       </c>
-      <c r="I26" s="48" t="n">
+      <c r="I26" s="49" t="n">
         <v>31.8</v>
       </c>
-      <c r="J26" s="53" t="n">
+      <c r="J26" s="54" t="n">
         <v>-2.1</v>
       </c>
-      <c r="K26" s="50" t="n">
+      <c r="K26" s="51" t="n">
         <v>2.3</v>
       </c>
-      <c r="L26" s="51" t="n">
+      <c r="L26" s="52" t="n">
         <v>-6.37</v>
       </c>
     </row>
@@ -4724,36 +4729,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C27" s="34" t="inlineStr">
+      <c r="C27" s="35" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="D27" s="46" t="n">
+      <c r="D27" s="47" t="n">
         <v>42</v>
       </c>
-      <c r="E27" s="46" t="n">
+      <c r="E27" s="47" t="n">
         <v>36</v>
       </c>
-      <c r="F27" s="46" t="n">
+      <c r="F27" s="47" t="n">
         <v>6</v>
       </c>
-      <c r="G27" s="47" t="n">
+      <c r="G27" s="48" t="n">
         <v>-42</v>
       </c>
-      <c r="H27" s="48" t="n">
+      <c r="H27" s="49" t="n">
         <v>4.5</v>
       </c>
-      <c r="I27" s="48" t="n">
+      <c r="I27" s="49" t="n">
         <v>402</v>
       </c>
-      <c r="J27" s="49" t="n">
+      <c r="J27" s="50" t="n">
         <v>14.3</v>
       </c>
-      <c r="K27" s="50" t="n">
+      <c r="K27" s="51" t="n">
         <v>2.81</v>
       </c>
-      <c r="L27" s="52" t="n">
+      <c r="L27" s="53" t="n">
         <v>-2.34</v>
       </c>
     </row>
@@ -4768,36 +4773,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C28" s="34" t="inlineStr">
+      <c r="C28" s="35" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="D28" s="46" t="n">
+      <c r="D28" s="47" t="n">
         <v>8</v>
       </c>
-      <c r="E28" s="47" t="n">
+      <c r="E28" s="48" t="n">
         <v>-6</v>
       </c>
-      <c r="F28" s="46" t="n">
+      <c r="F28" s="47" t="n">
         <v>15</v>
       </c>
-      <c r="G28" s="47" t="n">
+      <c r="G28" s="48" t="n">
         <v>-9</v>
       </c>
-      <c r="H28" s="48" t="n">
+      <c r="H28" s="49" t="n">
         <v>10.9</v>
       </c>
-      <c r="I28" s="48" t="n">
+      <c r="I28" s="49" t="n">
         <v>328.8</v>
       </c>
-      <c r="J28" s="49" t="n">
+      <c r="J28" s="50" t="n">
         <v>8.4</v>
       </c>
-      <c r="K28" s="50" t="n">
+      <c r="K28" s="51" t="n">
         <v>2.6</v>
       </c>
-      <c r="L28" s="51" t="n">
+      <c r="L28" s="52" t="n">
         <v>-9.33</v>
       </c>
     </row>
@@ -4812,36 +4817,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C29" s="34" t="inlineStr">
+      <c r="C29" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D29" s="46" t="n">
+      <c r="D29" s="47" t="n">
         <v>6</v>
       </c>
-      <c r="E29" s="46" t="n">
+      <c r="E29" s="47" t="n">
         <v>7</v>
       </c>
-      <c r="F29" s="56" t="n">
+      <c r="F29" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="G29" s="47" t="n">
+      <c r="G29" s="48" t="n">
         <v>-7</v>
       </c>
-      <c r="H29" s="48" t="n">
+      <c r="H29" s="49" t="n">
         <v>3.6</v>
       </c>
-      <c r="I29" s="48" t="n">
+      <c r="I29" s="49" t="n">
         <v>322.4</v>
       </c>
-      <c r="J29" s="49" t="n">
+      <c r="J29" s="50" t="n">
         <v>3.1</v>
       </c>
-      <c r="K29" s="50" t="n">
+      <c r="K29" s="51" t="n">
         <v>3.68</v>
       </c>
-      <c r="L29" s="52" t="n">
+      <c r="L29" s="53" t="n">
         <v>-4.92</v>
       </c>
     </row>
@@ -4856,36 +4861,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C30" s="34" t="inlineStr">
+      <c r="C30" s="35" t="inlineStr">
         <is>
           <t>유통</t>
         </is>
       </c>
-      <c r="D30" s="46" t="n">
+      <c r="D30" s="47" t="n">
         <v>11</v>
       </c>
-      <c r="E30" s="47" t="n">
+      <c r="E30" s="48" t="n">
         <v>-3</v>
       </c>
-      <c r="F30" s="46" t="n">
+      <c r="F30" s="47" t="n">
         <v>14</v>
       </c>
-      <c r="G30" s="47" t="n">
+      <c r="G30" s="48" t="n">
         <v>-10</v>
       </c>
-      <c r="H30" s="48" t="n">
+      <c r="H30" s="49" t="n">
         <v>2.3</v>
       </c>
-      <c r="I30" s="48" t="n">
+      <c r="I30" s="49" t="n">
         <v>66.5</v>
       </c>
-      <c r="J30" s="49" t="n">
+      <c r="J30" s="50" t="n">
         <v>0.3</v>
       </c>
-      <c r="K30" s="50" t="n">
+      <c r="K30" s="51" t="n">
         <v>3.07</v>
       </c>
-      <c r="L30" s="52" t="n">
+      <c r="L30" s="53" t="n">
         <v>-4.33</v>
       </c>
     </row>
@@ -4900,36 +4905,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C31" s="34" t="inlineStr">
+      <c r="C31" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D31" s="46" t="n">
+      <c r="D31" s="47" t="n">
         <v>6</v>
       </c>
-      <c r="E31" s="46" t="n">
+      <c r="E31" s="47" t="n">
         <v>11</v>
       </c>
-      <c r="F31" s="47" t="n">
+      <c r="F31" s="48" t="n">
         <v>-4</v>
       </c>
-      <c r="G31" s="47" t="n">
+      <c r="G31" s="48" t="n">
         <v>-6</v>
       </c>
-      <c r="H31" s="48" t="n">
+      <c r="H31" s="49" t="n">
         <v>0.4</v>
       </c>
-      <c r="I31" s="48" t="n">
+      <c r="I31" s="49" t="n">
         <v>177.8</v>
       </c>
-      <c r="J31" s="53" t="n">
+      <c r="J31" s="54" t="n">
         <v>-14.6</v>
       </c>
-      <c r="K31" s="50" t="n">
+      <c r="K31" s="51" t="n">
         <v>0.57</v>
       </c>
-      <c r="L31" s="55" t="n">
+      <c r="L31" s="56" t="n">
         <v>-1.24</v>
       </c>
     </row>
@@ -4944,36 +4949,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C32" s="34" t="inlineStr">
+      <c r="C32" s="35" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="D32" s="46" t="n">
+      <c r="D32" s="47" t="n">
         <v>4</v>
       </c>
-      <c r="E32" s="46" t="n">
+      <c r="E32" s="47" t="n">
         <v>5</v>
       </c>
-      <c r="F32" s="56" t="n">
+      <c r="F32" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="G32" s="47" t="n">
+      <c r="G32" s="48" t="n">
         <v>-4</v>
       </c>
-      <c r="H32" s="48" t="n">
+      <c r="H32" s="49" t="n">
         <v>2.1</v>
       </c>
-      <c r="I32" s="48" t="n">
+      <c r="I32" s="49" t="n">
         <v>38.5</v>
       </c>
-      <c r="J32" s="53" t="n">
+      <c r="J32" s="54" t="n">
         <v>-1.3</v>
       </c>
-      <c r="K32" s="50" t="n">
+      <c r="K32" s="51" t="n">
         <v>7.25</v>
       </c>
-      <c r="L32" s="52" t="n">
+      <c r="L32" s="53" t="n">
         <v>-4.04</v>
       </c>
     </row>
@@ -4988,34 +4993,34 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C33" s="34" t="inlineStr">
+      <c r="C33" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D33" s="46" t="n">
+      <c r="D33" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="E33" s="46" t="n">
+      <c r="E33" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="F33" s="56" t="n">
+      <c r="F33" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="G33" s="47" t="n">
+      <c r="G33" s="48" t="n">
         <v>-3</v>
       </c>
-      <c r="H33" s="48" t="inlineStr"/>
-      <c r="I33" s="48" t="n">
+      <c r="H33" s="49" t="inlineStr"/>
+      <c r="I33" s="49" t="n">
         <v>33.9</v>
       </c>
-      <c r="J33" s="57" t="n">
+      <c r="J33" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="K33" s="54" t="n">
+      <c r="K33" s="55" t="n">
         <v>-0.48</v>
       </c>
-      <c r="L33" s="52" t="n">
+      <c r="L33" s="53" t="n">
         <v>-3.57</v>
       </c>
     </row>
@@ -5030,36 +5035,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C34" s="34" t="inlineStr">
+      <c r="C34" s="35" t="inlineStr">
         <is>
           <t>보험</t>
         </is>
       </c>
-      <c r="D34" s="47" t="n">
+      <c r="D34" s="48" t="n">
         <v>-17</v>
       </c>
-      <c r="E34" s="47" t="n">
+      <c r="E34" s="48" t="n">
         <v>-16</v>
       </c>
-      <c r="F34" s="47" t="n">
+      <c r="F34" s="48" t="n">
         <v>-1</v>
       </c>
-      <c r="G34" s="46" t="n">
+      <c r="G34" s="47" t="n">
         <v>13</v>
       </c>
-      <c r="H34" s="48" t="n">
+      <c r="H34" s="49" t="n">
         <v>1.7</v>
       </c>
-      <c r="I34" s="48" t="n">
+      <c r="I34" s="49" t="n">
         <v>793</v>
       </c>
-      <c r="J34" s="53" t="n">
+      <c r="J34" s="54" t="n">
         <v>-15.8</v>
       </c>
-      <c r="K34" s="54" t="n">
+      <c r="K34" s="55" t="n">
         <v>-1.57</v>
       </c>
-      <c r="L34" s="51" t="n">
+      <c r="L34" s="52" t="n">
         <v>-8.83</v>
       </c>
     </row>
@@ -5074,36 +5079,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C35" s="34" t="inlineStr">
+      <c r="C35" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D35" s="46" t="n">
+      <c r="D35" s="47" t="n">
         <v>9</v>
       </c>
-      <c r="E35" s="46" t="n">
+      <c r="E35" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="F35" s="46" t="n">
+      <c r="F35" s="47" t="n">
         <v>6</v>
       </c>
-      <c r="G35" s="47" t="n">
+      <c r="G35" s="48" t="n">
         <v>-9</v>
       </c>
-      <c r="H35" s="48" t="n">
+      <c r="H35" s="49" t="n">
         <v>1.2</v>
       </c>
-      <c r="I35" s="48" t="n">
+      <c r="I35" s="49" t="n">
         <v>235.9</v>
       </c>
-      <c r="J35" s="49" t="n">
+      <c r="J35" s="50" t="n">
         <v>11.3</v>
       </c>
-      <c r="K35" s="50" t="n">
+      <c r="K35" s="51" t="n">
         <v>3.77</v>
       </c>
-      <c r="L35" s="51" t="n">
+      <c r="L35" s="52" t="n">
         <v>-7.27</v>
       </c>
     </row>
@@ -5181,7 +5186,7 @@
           <t>F1 외국인</t>
         </is>
       </c>
-      <c r="E3" s="58" t="inlineStr">
+      <c r="E3" s="59" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
@@ -5191,111 +5196,111 @@
           <t>F2 기관계</t>
         </is>
       </c>
-      <c r="N3" s="58" t="inlineStr">
+      <c r="N3" s="59" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="59" t="inlineStr">
+      <c r="A4" s="60" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="E4" s="60" t="inlineStr">
+      <c r="E4" s="61" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="J4" s="59" t="inlineStr">
+      <c r="J4" s="60" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="N4" s="60" t="inlineStr">
+      <c r="N4" s="61" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="45" t="inlineStr">
+      <c r="A5" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B5" s="45" t="inlineStr">
+      <c r="B5" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C5" s="45" t="inlineStr">
+      <c r="C5" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D5" s="45" t="inlineStr">
+      <c r="D5" s="46" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E5" s="45" t="inlineStr">
+      <c r="E5" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F5" s="45" t="inlineStr">
+      <c r="F5" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G5" s="45" t="inlineStr">
+      <c r="G5" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H5" s="45" t="inlineStr">
+      <c r="H5" s="46" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="J5" s="45" t="inlineStr">
+      <c r="J5" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="K5" s="45" t="inlineStr">
+      <c r="K5" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="L5" s="45" t="inlineStr">
+      <c r="L5" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="M5" s="45" t="inlineStr">
+      <c r="M5" s="46" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="N5" s="45" t="inlineStr">
+      <c r="N5" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O5" s="45" t="inlineStr">
+      <c r="O5" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P5" s="45" t="inlineStr">
+      <c r="P5" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q5" s="45" t="inlineStr">
+      <c r="Q5" s="46" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -5310,12 +5315,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="C6" s="34" t="inlineStr">
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D6" s="47" t="n">
+      <c r="D6" s="48" t="n">
         <v>3188</v>
       </c>
       <c r="E6" s="30" t="n">
@@ -5326,12 +5331,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="G6" s="34" t="inlineStr">
+      <c r="G6" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H6" s="61" t="n">
+      <c r="H6" s="62" t="n">
         <v>-4440</v>
       </c>
       <c r="J6" s="30" t="n">
@@ -5342,12 +5347,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="L6" s="34" t="inlineStr">
+      <c r="L6" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M6" s="47" t="n">
+      <c r="M6" s="48" t="n">
         <v>1838</v>
       </c>
       <c r="N6" s="30" t="n">
@@ -5358,12 +5363,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="P6" s="34" t="inlineStr">
+      <c r="P6" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q6" s="61" t="n">
+      <c r="Q6" s="62" t="n">
         <v>-852</v>
       </c>
     </row>
@@ -5376,12 +5381,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="C7" s="34" t="inlineStr">
+      <c r="C7" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D7" s="47" t="n">
+      <c r="D7" s="48" t="n">
         <v>1283</v>
       </c>
       <c r="E7" s="30" t="n">
@@ -5392,12 +5397,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="G7" s="34" t="inlineStr">
+      <c r="G7" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H7" s="61" t="n">
+      <c r="H7" s="62" t="n">
         <v>-3146</v>
       </c>
       <c r="J7" s="30" t="n">
@@ -5408,12 +5413,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="L7" s="34" t="inlineStr">
+      <c r="L7" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M7" s="47" t="n">
+      <c r="M7" s="48" t="n">
         <v>1777</v>
       </c>
       <c r="N7" s="30" t="n">
@@ -5424,12 +5429,12 @@
           <t>두산</t>
         </is>
       </c>
-      <c r="P7" s="34" t="inlineStr">
+      <c r="P7" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q7" s="61" t="n">
+      <c r="Q7" s="62" t="n">
         <v>-632</v>
       </c>
     </row>
@@ -5442,12 +5447,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="C8" s="34" t="inlineStr">
+      <c r="C8" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D8" s="47" t="n">
+      <c r="D8" s="48" t="n">
         <v>716</v>
       </c>
       <c r="E8" s="30" t="n">
@@ -5458,12 +5463,12 @@
           <t>리노공업</t>
         </is>
       </c>
-      <c r="G8" s="34" t="inlineStr">
+      <c r="G8" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H8" s="61" t="n">
+      <c r="H8" s="62" t="n">
         <v>-769</v>
       </c>
       <c r="J8" s="30" t="n">
@@ -5474,12 +5479,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="L8" s="34" t="inlineStr">
+      <c r="L8" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M8" s="47" t="n">
+      <c r="M8" s="48" t="n">
         <v>1297</v>
       </c>
       <c r="N8" s="30" t="n">
@@ -5490,12 +5495,12 @@
           <t>브릴스</t>
         </is>
       </c>
-      <c r="P8" s="34" t="inlineStr">
+      <c r="P8" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q8" s="61" t="n">
+      <c r="Q8" s="62" t="n">
         <v>-562</v>
       </c>
     </row>
@@ -5508,12 +5513,12 @@
           <t>제주반도체</t>
         </is>
       </c>
-      <c r="C9" s="34" t="inlineStr">
+      <c r="C9" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D9" s="47" t="n">
+      <c r="D9" s="48" t="n">
         <v>449</v>
       </c>
       <c r="E9" s="30" t="n">
@@ -5524,12 +5529,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="G9" s="34" t="inlineStr">
+      <c r="G9" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H9" s="61" t="n">
+      <c r="H9" s="62" t="n">
         <v>-675</v>
       </c>
       <c r="J9" s="30" t="n">
@@ -5540,12 +5545,12 @@
           <t>리노공업</t>
         </is>
       </c>
-      <c r="L9" s="34" t="inlineStr">
+      <c r="L9" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M9" s="47" t="n">
+      <c r="M9" s="48" t="n">
         <v>942</v>
       </c>
       <c r="N9" s="30" t="n">
@@ -5556,12 +5561,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="P9" s="34" t="inlineStr">
+      <c r="P9" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="Q9" s="61" t="n">
+      <c r="Q9" s="62" t="n">
         <v>-506</v>
       </c>
     </row>
@@ -5574,12 +5579,12 @@
           <t>에코프로</t>
         </is>
       </c>
-      <c r="C10" s="34" t="inlineStr">
+      <c r="C10" s="35" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="D10" s="47" t="n">
+      <c r="D10" s="48" t="n">
         <v>349</v>
       </c>
       <c r="E10" s="30" t="n">
@@ -5590,12 +5595,12 @@
           <t>우리금융지주</t>
         </is>
       </c>
-      <c r="G10" s="34" t="inlineStr">
+      <c r="G10" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="H10" s="61" t="n">
+      <c r="H10" s="62" t="n">
         <v>-648</v>
       </c>
       <c r="J10" s="30" t="n">
@@ -5606,12 +5611,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="L10" s="34" t="inlineStr">
+      <c r="L10" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="M10" s="47" t="n">
+      <c r="M10" s="48" t="n">
         <v>582</v>
       </c>
       <c r="N10" s="30" t="n">
@@ -5622,12 +5627,12 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="P10" s="34" t="inlineStr">
+      <c r="P10" s="35" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="Q10" s="61" t="n">
+      <c r="Q10" s="62" t="n">
         <v>-504</v>
       </c>
     </row>
@@ -5640,12 +5645,12 @@
           <t>심텍</t>
         </is>
       </c>
-      <c r="C11" s="34" t="inlineStr">
+      <c r="C11" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D11" s="47" t="n">
+      <c r="D11" s="48" t="n">
         <v>341</v>
       </c>
       <c r="E11" s="30" t="n">
@@ -5656,12 +5661,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="G11" s="34" t="inlineStr">
+      <c r="G11" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="H11" s="61" t="n">
+      <c r="H11" s="62" t="n">
         <v>-625</v>
       </c>
       <c r="J11" s="30" t="n">
@@ -5672,12 +5677,12 @@
           <t>HPSP</t>
         </is>
       </c>
-      <c r="L11" s="34" t="inlineStr">
+      <c r="L11" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M11" s="47" t="n">
+      <c r="M11" s="48" t="n">
         <v>533</v>
       </c>
       <c r="N11" s="30" t="n">
@@ -5688,12 +5693,12 @@
           <t>HD건설기계</t>
         </is>
       </c>
-      <c r="P11" s="34" t="inlineStr">
+      <c r="P11" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q11" s="61" t="n">
+      <c r="Q11" s="62" t="n">
         <v>-466</v>
       </c>
     </row>
@@ -5706,12 +5711,12 @@
           <t>S-Oil</t>
         </is>
       </c>
-      <c r="C12" s="34" t="inlineStr">
+      <c r="C12" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D12" s="47" t="n">
+      <c r="D12" s="48" t="n">
         <v>270</v>
       </c>
       <c r="E12" s="30" t="n">
@@ -5722,12 +5727,12 @@
           <t>KB금융</t>
         </is>
       </c>
-      <c r="G12" s="34" t="inlineStr">
+      <c r="G12" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="H12" s="61" t="n">
+      <c r="H12" s="62" t="n">
         <v>-442</v>
       </c>
       <c r="J12" s="30" t="n">
@@ -5738,12 +5743,12 @@
           <t>대덕전자</t>
         </is>
       </c>
-      <c r="L12" s="34" t="inlineStr">
+      <c r="L12" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M12" s="47" t="n">
+      <c r="M12" s="48" t="n">
         <v>513</v>
       </c>
       <c r="N12" s="30" t="n">
@@ -5754,12 +5759,12 @@
           <t>현대건설</t>
         </is>
       </c>
-      <c r="P12" s="34" t="inlineStr">
+      <c r="P12" s="35" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
       </c>
-      <c r="Q12" s="61" t="n">
+      <c r="Q12" s="62" t="n">
         <v>-367</v>
       </c>
     </row>
@@ -5772,12 +5777,12 @@
           <t>삼화콘덴서</t>
         </is>
       </c>
-      <c r="C13" s="34" t="inlineStr">
+      <c r="C13" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D13" s="47" t="n">
+      <c r="D13" s="48" t="n">
         <v>262</v>
       </c>
       <c r="E13" s="30" t="n">
@@ -5788,12 +5793,12 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="G13" s="34" t="inlineStr">
+      <c r="G13" s="35" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="H13" s="61" t="n">
+      <c r="H13" s="62" t="n">
         <v>-424</v>
       </c>
       <c r="J13" s="30" t="n">
@@ -5804,12 +5809,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="L13" s="34" t="inlineStr">
+      <c r="L13" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M13" s="47" t="n">
+      <c r="M13" s="48" t="n">
         <v>451</v>
       </c>
       <c r="N13" s="30" t="n">
@@ -5820,12 +5825,12 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="P13" s="41" t="inlineStr">
+      <c r="P13" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q13" s="61" t="n">
+      <c r="Q13" s="62" t="n">
         <v>-343</v>
       </c>
     </row>
@@ -5838,12 +5843,12 @@
           <t>고영</t>
         </is>
       </c>
-      <c r="C14" s="34" t="inlineStr">
+      <c r="C14" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D14" s="47" t="n">
+      <c r="D14" s="48" t="n">
         <v>256</v>
       </c>
       <c r="E14" s="30" t="n">
@@ -5854,12 +5859,12 @@
           <t>원익IPS</t>
         </is>
       </c>
-      <c r="G14" s="34" t="inlineStr">
+      <c r="G14" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H14" s="61" t="n">
+      <c r="H14" s="62" t="n">
         <v>-408</v>
       </c>
       <c r="J14" s="30" t="n">
@@ -5870,12 +5875,12 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="L14" s="34" t="inlineStr">
+      <c r="L14" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M14" s="47" t="n">
+      <c r="M14" s="48" t="n">
         <v>447</v>
       </c>
       <c r="N14" s="30" t="n">
@@ -5886,12 +5891,12 @@
           <t>HD현대중공업</t>
         </is>
       </c>
-      <c r="P14" s="41" t="inlineStr">
+      <c r="P14" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q14" s="61" t="n">
+      <c r="Q14" s="62" t="n">
         <v>-307</v>
       </c>
     </row>
@@ -5904,12 +5909,12 @@
           <t>SFA반도체</t>
         </is>
       </c>
-      <c r="C15" s="34" t="inlineStr">
+      <c r="C15" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D15" s="47" t="n">
+      <c r="D15" s="48" t="n">
         <v>238</v>
       </c>
       <c r="E15" s="30" t="n">
@@ -5920,12 +5925,12 @@
           <t>신한지주</t>
         </is>
       </c>
-      <c r="G15" s="34" t="inlineStr">
+      <c r="G15" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="H15" s="61" t="n">
+      <c r="H15" s="62" t="n">
         <v>-393</v>
       </c>
       <c r="J15" s="30" t="n">
@@ -5936,12 +5941,12 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="L15" s="41" t="inlineStr">
+      <c r="L15" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="M15" s="47" t="n">
+      <c r="M15" s="48" t="n">
         <v>424</v>
       </c>
       <c r="N15" s="30" t="n">
@@ -5952,12 +5957,12 @@
           <t>LS</t>
         </is>
       </c>
-      <c r="P15" s="34" t="inlineStr">
+      <c r="P15" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="Q15" s="61" t="n">
+      <c r="Q15" s="62" t="n">
         <v>-217</v>
       </c>
     </row>
@@ -5968,7 +5973,7 @@
           <t>F3 외인+기관</t>
         </is>
       </c>
-      <c r="E17" s="58" t="inlineStr">
+      <c r="E17" s="59" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
@@ -5978,111 +5983,111 @@
           <t>F4 개인</t>
         </is>
       </c>
-      <c r="N17" s="58" t="inlineStr">
+      <c r="N17" s="59" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="59" t="inlineStr">
+      <c r="A18" s="60" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="E18" s="60" t="inlineStr">
+      <c r="E18" s="61" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="J18" s="59" t="inlineStr">
+      <c r="J18" s="60" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="N18" s="60" t="inlineStr">
+      <c r="N18" s="61" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="45" t="inlineStr">
+      <c r="A19" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B19" s="45" t="inlineStr">
+      <c r="B19" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C19" s="45" t="inlineStr">
+      <c r="C19" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D19" s="45" t="inlineStr">
+      <c r="D19" s="46" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E19" s="45" t="inlineStr">
+      <c r="E19" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F19" s="45" t="inlineStr">
+      <c r="F19" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G19" s="45" t="inlineStr">
+      <c r="G19" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H19" s="45" t="inlineStr">
+      <c r="H19" s="46" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="J19" s="45" t="inlineStr">
+      <c r="J19" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="K19" s="45" t="inlineStr">
+      <c r="K19" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="L19" s="45" t="inlineStr">
+      <c r="L19" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="M19" s="45" t="inlineStr">
+      <c r="M19" s="46" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="N19" s="45" t="inlineStr">
+      <c r="N19" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O19" s="45" t="inlineStr">
+      <c r="O19" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P19" s="45" t="inlineStr">
+      <c r="P19" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q19" s="45" t="inlineStr">
+      <c r="Q19" s="46" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -6097,12 +6102,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="C20" s="34" t="inlineStr">
+      <c r="C20" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D20" s="47" t="n">
+      <c r="D20" s="48" t="n">
         <v>4485</v>
       </c>
       <c r="E20" s="30" t="n">
@@ -6113,12 +6118,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="G20" s="34" t="inlineStr">
+      <c r="G20" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H20" s="61" t="n">
+      <c r="H20" s="62" t="n">
         <v>-2602</v>
       </c>
       <c r="J20" s="30" t="n">
@@ -6129,12 +6134,12 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="L20" s="34" t="inlineStr">
+      <c r="L20" s="35" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="M20" s="47" t="n">
+      <c r="M20" s="48" t="n">
         <v>924</v>
       </c>
       <c r="N20" s="30" t="n">
@@ -6145,12 +6150,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="P20" s="34" t="inlineStr">
+      <c r="P20" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q20" s="61" t="n">
+      <c r="Q20" s="62" t="n">
         <v>-17231</v>
       </c>
     </row>
@@ -6163,12 +6168,12 @@
           <t>제주반도체</t>
         </is>
       </c>
-      <c r="C21" s="34" t="inlineStr">
+      <c r="C21" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D21" s="47" t="n">
+      <c r="D21" s="48" t="n">
         <v>796</v>
       </c>
       <c r="E21" s="30" t="n">
@@ -6179,12 +6184,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="G21" s="34" t="inlineStr">
+      <c r="G21" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H21" s="61" t="n">
+      <c r="H21" s="62" t="n">
         <v>-1369</v>
       </c>
       <c r="J21" s="30" t="n">
@@ -6195,12 +6200,12 @@
           <t>브릴스</t>
         </is>
       </c>
-      <c r="L21" s="34" t="inlineStr">
+      <c r="L21" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M21" s="47" t="n">
+      <c r="M21" s="48" t="n">
         <v>782</v>
       </c>
       <c r="N21" s="30" t="n">
@@ -6211,12 +6216,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="P21" s="34" t="inlineStr">
+      <c r="P21" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q21" s="61" t="n">
+      <c r="Q21" s="62" t="n">
         <v>-9470</v>
       </c>
     </row>
@@ -6229,12 +6234,12 @@
           <t>에코프로</t>
         </is>
       </c>
-      <c r="C22" s="34" t="inlineStr">
+      <c r="C22" s="35" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="D22" s="47" t="n">
+      <c r="D22" s="48" t="n">
         <v>594</v>
       </c>
       <c r="E22" s="30" t="n">
@@ -6245,12 +6250,12 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="G22" s="34" t="inlineStr">
+      <c r="G22" s="35" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="H22" s="61" t="n">
+      <c r="H22" s="62" t="n">
         <v>-928</v>
       </c>
       <c r="J22" s="30" t="n">
@@ -6261,12 +6266,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="L22" s="34" t="inlineStr">
+      <c r="L22" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M22" s="47" t="n">
+      <c r="M22" s="48" t="n">
         <v>773</v>
       </c>
       <c r="N22" s="30" t="n">
@@ -6277,12 +6282,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="P22" s="34" t="inlineStr">
+      <c r="P22" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q22" s="61" t="n">
+      <c r="Q22" s="62" t="n">
         <v>-4521</v>
       </c>
     </row>
@@ -6295,12 +6300,12 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="C23" s="34" t="inlineStr">
+      <c r="C23" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D23" s="47" t="n">
+      <c r="D23" s="48" t="n">
         <v>503</v>
       </c>
       <c r="E23" s="30" t="n">
@@ -6311,12 +6316,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="G23" s="34" t="inlineStr">
+      <c r="G23" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H23" s="61" t="n">
+      <c r="H23" s="62" t="n">
         <v>-789</v>
       </c>
       <c r="J23" s="30" t="n">
@@ -6327,12 +6332,12 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="L23" s="41" t="inlineStr">
+      <c r="L23" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="M23" s="47" t="n">
+      <c r="M23" s="48" t="n">
         <v>729</v>
       </c>
       <c r="N23" s="30" t="n">
@@ -6343,12 +6348,12 @@
           <t>제주반도체</t>
         </is>
       </c>
-      <c r="P23" s="34" t="inlineStr">
+      <c r="P23" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q23" s="61" t="n">
+      <c r="Q23" s="62" t="n">
         <v>-789</v>
       </c>
     </row>
@@ -6361,12 +6366,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="C24" s="34" t="inlineStr">
+      <c r="C24" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D24" s="47" t="n">
+      <c r="D24" s="48" t="n">
         <v>497</v>
       </c>
       <c r="E24" s="30" t="n">
@@ -6377,12 +6382,12 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="G24" s="41" t="inlineStr">
+      <c r="G24" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H24" s="61" t="n">
+      <c r="H24" s="62" t="n">
         <v>-723</v>
       </c>
       <c r="J24" s="30" t="n">
@@ -6393,12 +6398,12 @@
           <t>두산</t>
         </is>
       </c>
-      <c r="L24" s="34" t="inlineStr">
+      <c r="L24" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M24" s="47" t="n">
+      <c r="M24" s="48" t="n">
         <v>716</v>
       </c>
       <c r="N24" s="30" t="n">
@@ -6409,12 +6414,12 @@
           <t>에코프로</t>
         </is>
       </c>
-      <c r="P24" s="34" t="inlineStr">
+      <c r="P24" s="35" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="Q24" s="61" t="n">
+      <c r="Q24" s="62" t="n">
         <v>-591</v>
       </c>
     </row>
@@ -6427,12 +6432,12 @@
           <t>LIG디펜스앤에어로스페이스</t>
         </is>
       </c>
-      <c r="C25" s="34" t="inlineStr">
+      <c r="C25" s="35" t="inlineStr">
         <is>
           <t>금속</t>
         </is>
       </c>
-      <c r="D25" s="47" t="n">
+      <c r="D25" s="48" t="n">
         <v>467</v>
       </c>
       <c r="E25" s="30" t="n">
@@ -6443,12 +6448,12 @@
           <t>두산</t>
         </is>
       </c>
-      <c r="G25" s="34" t="inlineStr">
+      <c r="G25" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H25" s="61" t="n">
+      <c r="H25" s="62" t="n">
         <v>-684</v>
       </c>
       <c r="J25" s="30" t="n">
@@ -6459,12 +6464,12 @@
           <t>현대건설</t>
         </is>
       </c>
-      <c r="L25" s="34" t="inlineStr">
+      <c r="L25" s="35" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
       </c>
-      <c r="M25" s="47" t="n">
+      <c r="M25" s="48" t="n">
         <v>426</v>
       </c>
       <c r="N25" s="30" t="n">
@@ -6475,12 +6480,12 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="P25" s="34" t="inlineStr">
+      <c r="P25" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q25" s="61" t="n">
+      <c r="Q25" s="62" t="n">
         <v>-499</v>
       </c>
     </row>
@@ -6493,12 +6498,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="C26" s="34" t="inlineStr">
+      <c r="C26" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D26" s="47" t="n">
+      <c r="D26" s="48" t="n">
         <v>432</v>
       </c>
       <c r="E26" s="30" t="n">
@@ -6509,12 +6514,12 @@
           <t>브릴스</t>
         </is>
       </c>
-      <c r="G26" s="34" t="inlineStr">
+      <c r="G26" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H26" s="61" t="n">
+      <c r="H26" s="62" t="n">
         <v>-560</v>
       </c>
       <c r="J26" s="30" t="n">
@@ -6525,12 +6530,12 @@
           <t>HD건설기계</t>
         </is>
       </c>
-      <c r="L26" s="34" t="inlineStr">
+      <c r="L26" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M26" s="47" t="n">
+      <c r="M26" s="48" t="n">
         <v>413</v>
       </c>
       <c r="N26" s="30" t="n">
@@ -6541,12 +6546,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="P26" s="34" t="inlineStr">
+      <c r="P26" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q26" s="61" t="n">
+      <c r="Q26" s="62" t="n">
         <v>-486</v>
       </c>
     </row>
@@ -6559,12 +6564,12 @@
           <t>한화시스템</t>
         </is>
       </c>
-      <c r="C27" s="34" t="inlineStr">
+      <c r="C27" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D27" s="47" t="n">
+      <c r="D27" s="48" t="n">
         <v>416</v>
       </c>
       <c r="E27" s="30" t="n">
@@ -6575,12 +6580,12 @@
           <t>현대건설</t>
         </is>
       </c>
-      <c r="G27" s="34" t="inlineStr">
+      <c r="G27" s="35" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
       </c>
-      <c r="H27" s="61" t="n">
+      <c r="H27" s="62" t="n">
         <v>-440</v>
       </c>
       <c r="J27" s="30" t="n">
@@ -6591,12 +6596,12 @@
           <t>삼성바이오로직스</t>
         </is>
       </c>
-      <c r="L27" s="34" t="inlineStr">
+      <c r="L27" s="35" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="M27" s="47" t="n">
+      <c r="M27" s="48" t="n">
         <v>413</v>
       </c>
       <c r="N27" s="30" t="n">
@@ -6607,12 +6612,12 @@
           <t>LIG디펜스앤에어로스페이스</t>
         </is>
       </c>
-      <c r="P27" s="34" t="inlineStr">
+      <c r="P27" s="35" t="inlineStr">
         <is>
           <t>금속</t>
         </is>
       </c>
-      <c r="Q27" s="61" t="n">
+      <c r="Q27" s="62" t="n">
         <v>-468</v>
       </c>
     </row>
@@ -6625,12 +6630,12 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="C28" s="41" t="inlineStr">
+      <c r="C28" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="D28" s="47" t="n">
+      <c r="D28" s="48" t="n">
         <v>385</v>
       </c>
       <c r="E28" s="30" t="n">
@@ -6641,12 +6646,12 @@
           <t>삼성바이오로직스</t>
         </is>
       </c>
-      <c r="G28" s="34" t="inlineStr">
+      <c r="G28" s="35" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="H28" s="61" t="n">
+      <c r="H28" s="62" t="n">
         <v>-423</v>
       </c>
       <c r="J28" s="30" t="n">
@@ -6657,12 +6662,12 @@
           <t>LS</t>
         </is>
       </c>
-      <c r="L28" s="34" t="inlineStr">
+      <c r="L28" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="M28" s="47" t="n">
+      <c r="M28" s="48" t="n">
         <v>307</v>
       </c>
       <c r="N28" s="30" t="n">
@@ -6673,12 +6678,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="P28" s="34" t="inlineStr">
+      <c r="P28" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q28" s="61" t="n">
+      <c r="Q28" s="62" t="n">
         <v>-462</v>
       </c>
     </row>
@@ -6691,12 +6696,12 @@
           <t>한화솔루션</t>
         </is>
       </c>
-      <c r="C29" s="34" t="inlineStr">
+      <c r="C29" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D29" s="47" t="n">
+      <c r="D29" s="48" t="n">
         <v>365</v>
       </c>
       <c r="E29" s="30" t="n">
@@ -6707,12 +6712,12 @@
           <t>HD건설기계</t>
         </is>
       </c>
-      <c r="G29" s="34" t="inlineStr">
+      <c r="G29" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H29" s="61" t="n">
+      <c r="H29" s="62" t="n">
         <v>-423</v>
       </c>
       <c r="J29" s="30" t="n">
@@ -6723,12 +6728,12 @@
           <t>우리금융지주</t>
         </is>
       </c>
-      <c r="L29" s="34" t="inlineStr">
+      <c r="L29" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="M29" s="47" t="n">
+      <c r="M29" s="48" t="n">
         <v>299</v>
       </c>
       <c r="N29" s="30" t="n">
@@ -6739,12 +6744,12 @@
           <t>한화시스템</t>
         </is>
       </c>
-      <c r="P29" s="34" t="inlineStr">
+      <c r="P29" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q29" s="61" t="n">
+      <c r="Q29" s="62" t="n">
         <v>-407</v>
       </c>
     </row>
@@ -6755,7 +6760,7 @@
           <t>F5 금융투자</t>
         </is>
       </c>
-      <c r="E31" s="58" t="inlineStr">
+      <c r="E31" s="59" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
@@ -6765,111 +6770,111 @@
           <t>F6 투신(사모)</t>
         </is>
       </c>
-      <c r="N31" s="58" t="inlineStr">
+      <c r="N31" s="59" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="59" t="inlineStr">
+      <c r="A32" s="60" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="E32" s="60" t="inlineStr">
+      <c r="E32" s="61" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="J32" s="59" t="inlineStr">
+      <c r="J32" s="60" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="N32" s="60" t="inlineStr">
+      <c r="N32" s="61" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="45" t="inlineStr">
+      <c r="A33" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B33" s="45" t="inlineStr">
+      <c r="B33" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C33" s="45" t="inlineStr">
+      <c r="C33" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D33" s="45" t="inlineStr">
+      <c r="D33" s="46" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E33" s="45" t="inlineStr">
+      <c r="E33" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F33" s="45" t="inlineStr">
+      <c r="F33" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G33" s="45" t="inlineStr">
+      <c r="G33" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H33" s="45" t="inlineStr">
+      <c r="H33" s="46" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="J33" s="45" t="inlineStr">
+      <c r="J33" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="K33" s="45" t="inlineStr">
+      <c r="K33" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="L33" s="45" t="inlineStr">
+      <c r="L33" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="M33" s="45" t="inlineStr">
+      <c r="M33" s="46" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="N33" s="45" t="inlineStr">
+      <c r="N33" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O33" s="45" t="inlineStr">
+      <c r="O33" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P33" s="45" t="inlineStr">
+      <c r="P33" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q33" s="45" t="inlineStr">
+      <c r="Q33" s="46" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -6884,12 +6889,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="C34" s="34" t="inlineStr">
+      <c r="C34" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D34" s="47" t="n">
+      <c r="D34" s="48" t="n">
         <v>562</v>
       </c>
       <c r="E34" s="30" t="n">
@@ -6900,12 +6905,12 @@
           <t>현대모비스</t>
         </is>
       </c>
-      <c r="G34" s="41" t="inlineStr">
+      <c r="G34" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H34" s="61" t="n">
+      <c r="H34" s="62" t="n">
         <v>-127</v>
       </c>
       <c r="J34" s="30" t="n">
@@ -6916,12 +6921,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="L34" s="34" t="inlineStr">
+      <c r="L34" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M34" s="47" t="n">
+      <c r="M34" s="48" t="n">
         <v>897</v>
       </c>
       <c r="N34" s="30" t="n">
@@ -6932,12 +6937,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="P34" s="34" t="inlineStr">
+      <c r="P34" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q34" s="61" t="n">
+      <c r="Q34" s="62" t="n">
         <v>-543</v>
       </c>
     </row>
@@ -6950,12 +6955,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="C35" s="34" t="inlineStr">
+      <c r="C35" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D35" s="47" t="n">
+      <c r="D35" s="48" t="n">
         <v>411</v>
       </c>
       <c r="E35" s="30" t="n">
@@ -6966,12 +6971,12 @@
           <t>HD현대중공업</t>
         </is>
       </c>
-      <c r="G35" s="41" t="inlineStr">
+      <c r="G35" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H35" s="61" t="n">
+      <c r="H35" s="62" t="n">
         <v>-108</v>
       </c>
       <c r="J35" s="30" t="n">
@@ -6982,12 +6987,12 @@
           <t>리노공업</t>
         </is>
       </c>
-      <c r="L35" s="34" t="inlineStr">
+      <c r="L35" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M35" s="47" t="n">
+      <c r="M35" s="48" t="n">
         <v>702</v>
       </c>
       <c r="N35" s="30" t="n">
@@ -6998,12 +7003,12 @@
           <t>두산</t>
         </is>
       </c>
-      <c r="P35" s="34" t="inlineStr">
+      <c r="P35" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q35" s="61" t="n">
+      <c r="Q35" s="62" t="n">
         <v>-420</v>
       </c>
     </row>
@@ -7016,12 +7021,12 @@
           <t>주성엔지니어링</t>
         </is>
       </c>
-      <c r="C36" s="34" t="inlineStr">
+      <c r="C36" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D36" s="47" t="n">
+      <c r="D36" s="48" t="n">
         <v>321</v>
       </c>
       <c r="E36" s="30" t="n">
@@ -7032,12 +7037,12 @@
           <t>두산</t>
         </is>
       </c>
-      <c r="G36" s="34" t="inlineStr">
+      <c r="G36" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H36" s="61" t="n">
+      <c r="H36" s="62" t="n">
         <v>-98</v>
       </c>
       <c r="J36" s="30" t="n">
@@ -7048,12 +7053,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="L36" s="34" t="inlineStr">
+      <c r="L36" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M36" s="47" t="n">
+      <c r="M36" s="48" t="n">
         <v>605</v>
       </c>
       <c r="N36" s="30" t="n">
@@ -7064,12 +7069,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="P36" s="34" t="inlineStr">
+      <c r="P36" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="Q36" s="61" t="n">
+      <c r="Q36" s="62" t="n">
         <v>-314</v>
       </c>
     </row>
@@ -7082,12 +7087,12 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="C37" s="34" t="inlineStr">
+      <c r="C37" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D37" s="47" t="n">
+      <c r="D37" s="48" t="n">
         <v>273</v>
       </c>
       <c r="E37" s="30" t="n">
@@ -7098,12 +7103,12 @@
           <t>현대건설</t>
         </is>
       </c>
-      <c r="G37" s="34" t="inlineStr">
+      <c r="G37" s="35" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
       </c>
-      <c r="H37" s="61" t="n">
+      <c r="H37" s="62" t="n">
         <v>-75</v>
       </c>
       <c r="J37" s="30" t="n">
@@ -7114,12 +7119,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="L37" s="34" t="inlineStr">
+      <c r="L37" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M37" s="47" t="n">
+      <c r="M37" s="48" t="n">
         <v>370</v>
       </c>
       <c r="N37" s="30" t="n">
@@ -7130,12 +7135,12 @@
           <t>HD건설기계</t>
         </is>
       </c>
-      <c r="P37" s="34" t="inlineStr">
+      <c r="P37" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q37" s="61" t="n">
+      <c r="Q37" s="62" t="n">
         <v>-206</v>
       </c>
     </row>
@@ -7148,12 +7153,12 @@
           <t>KB금융</t>
         </is>
       </c>
-      <c r="C38" s="34" t="inlineStr">
+      <c r="C38" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D38" s="47" t="n">
+      <c r="D38" s="48" t="n">
         <v>271</v>
       </c>
       <c r="E38" s="30" t="n">
@@ -7164,12 +7169,12 @@
           <t>대한항공</t>
         </is>
       </c>
-      <c r="G38" s="34" t="inlineStr">
+      <c r="G38" s="35" t="inlineStr">
         <is>
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="H38" s="61" t="n">
+      <c r="H38" s="62" t="n">
         <v>-56</v>
       </c>
       <c r="J38" s="30" t="n">
@@ -7180,12 +7185,12 @@
           <t>대덕전자</t>
         </is>
       </c>
-      <c r="L38" s="34" t="inlineStr">
+      <c r="L38" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M38" s="47" t="n">
+      <c r="M38" s="48" t="n">
         <v>307</v>
       </c>
       <c r="N38" s="30" t="n">
@@ -7196,12 +7201,12 @@
           <t>HD현대일렉트릭</t>
         </is>
       </c>
-      <c r="P38" s="34" t="inlineStr">
+      <c r="P38" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q38" s="61" t="n">
+      <c r="Q38" s="62" t="n">
         <v>-190</v>
       </c>
     </row>
@@ -7214,12 +7219,12 @@
           <t>HPSP</t>
         </is>
       </c>
-      <c r="C39" s="34" t="inlineStr">
+      <c r="C39" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D39" s="47" t="n">
+      <c r="D39" s="48" t="n">
         <v>261</v>
       </c>
       <c r="E39" s="30" t="n">
@@ -7230,12 +7235,12 @@
           <t>피에스케이</t>
         </is>
       </c>
-      <c r="G39" s="34" t="inlineStr">
+      <c r="G39" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H39" s="61" t="n">
+      <c r="H39" s="62" t="n">
         <v>-53</v>
       </c>
       <c r="J39" s="30" t="n">
@@ -7246,12 +7251,12 @@
           <t>현대모비스</t>
         </is>
       </c>
-      <c r="L39" s="41" t="inlineStr">
+      <c r="L39" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="M39" s="47" t="n">
+      <c r="M39" s="48" t="n">
         <v>239</v>
       </c>
       <c r="N39" s="30" t="n">
@@ -7262,12 +7267,12 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="P39" s="41" t="inlineStr">
+      <c r="P39" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q39" s="61" t="n">
+      <c r="Q39" s="62" t="n">
         <v>-188</v>
       </c>
     </row>
@@ -7280,12 +7285,12 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="C40" s="34" t="inlineStr">
+      <c r="C40" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D40" s="47" t="n">
+      <c r="D40" s="48" t="n">
         <v>232</v>
       </c>
       <c r="E40" s="30" t="n">
@@ -7296,12 +7301,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="G40" s="34" t="inlineStr">
+      <c r="G40" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="H40" s="61" t="n">
+      <c r="H40" s="62" t="n">
         <v>-52</v>
       </c>
       <c r="J40" s="30" t="n">
@@ -7312,12 +7317,12 @@
           <t>NC</t>
         </is>
       </c>
-      <c r="L40" s="34" t="inlineStr">
+      <c r="L40" s="35" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="M40" s="47" t="n">
+      <c r="M40" s="48" t="n">
         <v>238</v>
       </c>
       <c r="N40" s="30" t="n">
@@ -7328,12 +7333,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="P40" s="34" t="inlineStr">
+      <c r="P40" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q40" s="61" t="n">
+      <c r="Q40" s="62" t="n">
         <v>-179</v>
       </c>
     </row>
@@ -7346,12 +7351,12 @@
           <t>원익IPS</t>
         </is>
       </c>
-      <c r="C41" s="34" t="inlineStr">
+      <c r="C41" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D41" s="47" t="n">
+      <c r="D41" s="48" t="n">
         <v>208</v>
       </c>
       <c r="E41" s="30" t="n">
@@ -7362,12 +7367,12 @@
           <t>HD건설기계</t>
         </is>
       </c>
-      <c r="G41" s="34" t="inlineStr">
+      <c r="G41" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H41" s="61" t="n">
+      <c r="H41" s="62" t="n">
         <v>-46</v>
       </c>
       <c r="J41" s="30" t="n">
@@ -7378,12 +7383,12 @@
           <t>제주반도체</t>
         </is>
       </c>
-      <c r="L41" s="34" t="inlineStr">
+      <c r="L41" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M41" s="47" t="n">
+      <c r="M41" s="48" t="n">
         <v>222</v>
       </c>
       <c r="N41" s="30" t="n">
@@ -7394,12 +7399,12 @@
           <t>LS</t>
         </is>
       </c>
-      <c r="P41" s="34" t="inlineStr">
+      <c r="P41" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="Q41" s="61" t="n">
+      <c r="Q41" s="62" t="n">
         <v>-160</v>
       </c>
     </row>
@@ -7412,12 +7417,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="C42" s="34" t="inlineStr">
+      <c r="C42" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D42" s="47" t="n">
+      <c r="D42" s="48" t="n">
         <v>191</v>
       </c>
       <c r="E42" s="30" t="n">
@@ -7428,12 +7433,12 @@
           <t>효성중공업</t>
         </is>
       </c>
-      <c r="G42" s="34" t="inlineStr">
+      <c r="G42" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H42" s="61" t="n">
+      <c r="H42" s="62" t="n">
         <v>-39</v>
       </c>
       <c r="J42" s="30" t="n">
@@ -7444,12 +7449,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="L42" s="34" t="inlineStr">
+      <c r="L42" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M42" s="47" t="n">
+      <c r="M42" s="48" t="n">
         <v>204</v>
       </c>
       <c r="N42" s="30" t="n">
@@ -7460,12 +7465,12 @@
           <t>효성중공업</t>
         </is>
       </c>
-      <c r="P42" s="34" t="inlineStr">
+      <c r="P42" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q42" s="61" t="n">
+      <c r="Q42" s="62" t="n">
         <v>-154</v>
       </c>
     </row>
@@ -7478,12 +7483,12 @@
           <t>신한지주</t>
         </is>
       </c>
-      <c r="C43" s="34" t="inlineStr">
+      <c r="C43" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D43" s="47" t="n">
+      <c r="D43" s="48" t="n">
         <v>184</v>
       </c>
       <c r="E43" s="30" t="n">
@@ -7494,12 +7499,12 @@
           <t>한화오션</t>
         </is>
       </c>
-      <c r="G43" s="41" t="inlineStr">
+      <c r="G43" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H43" s="61" t="n">
+      <c r="H43" s="62" t="n">
         <v>-36</v>
       </c>
       <c r="J43" s="30" t="n">
@@ -7510,12 +7515,12 @@
           <t>HPSP</t>
         </is>
       </c>
-      <c r="L43" s="34" t="inlineStr">
+      <c r="L43" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M43" s="47" t="n">
+      <c r="M43" s="48" t="n">
         <v>168</v>
       </c>
       <c r="N43" s="30" t="n">
@@ -7526,12 +7531,12 @@
           <t>파마리서치</t>
         </is>
       </c>
-      <c r="P43" s="34" t="inlineStr">
+      <c r="P43" s="35" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="Q43" s="61" t="n">
+      <c r="Q43" s="62" t="n">
         <v>-153</v>
       </c>
     </row>
@@ -7542,7 +7547,7 @@
           <t>F7 연기금</t>
         </is>
       </c>
-      <c r="E45" s="58" t="inlineStr">
+      <c r="E45" s="59" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
@@ -7552,111 +7557,111 @@
           <t>F8 보험</t>
         </is>
       </c>
-      <c r="N45" s="58" t="inlineStr">
+      <c r="N45" s="59" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="59" t="inlineStr">
+      <c r="A46" s="60" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="E46" s="60" t="inlineStr">
+      <c r="E46" s="61" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="J46" s="59" t="inlineStr">
+      <c r="J46" s="60" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="N46" s="60" t="inlineStr">
+      <c r="N46" s="61" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="45" t="inlineStr">
+      <c r="A47" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B47" s="45" t="inlineStr">
+      <c r="B47" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C47" s="45" t="inlineStr">
+      <c r="C47" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D47" s="45" t="inlineStr">
+      <c r="D47" s="46" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E47" s="45" t="inlineStr">
+      <c r="E47" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F47" s="45" t="inlineStr">
+      <c r="F47" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G47" s="45" t="inlineStr">
+      <c r="G47" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H47" s="45" t="inlineStr">
+      <c r="H47" s="46" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="J47" s="45" t="inlineStr">
+      <c r="J47" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="K47" s="45" t="inlineStr">
+      <c r="K47" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="L47" s="45" t="inlineStr">
+      <c r="L47" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="M47" s="45" t="inlineStr">
+      <c r="M47" s="46" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="N47" s="45" t="inlineStr">
+      <c r="N47" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O47" s="45" t="inlineStr">
+      <c r="O47" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P47" s="45" t="inlineStr">
+      <c r="P47" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q47" s="45" t="inlineStr">
+      <c r="Q47" s="46" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -7671,12 +7676,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="C48" s="34" t="inlineStr">
+      <c r="C48" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D48" s="47" t="n">
+      <c r="D48" s="48" t="n">
         <v>604</v>
       </c>
       <c r="E48" s="30" t="n">
@@ -7687,12 +7692,12 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="G48" s="34" t="inlineStr">
+      <c r="G48" s="35" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="H48" s="61" t="n">
+      <c r="H48" s="62" t="n">
         <v>-384</v>
       </c>
       <c r="J48" s="30" t="n">
@@ -7703,12 +7708,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="L48" s="34" t="inlineStr">
+      <c r="L48" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M48" s="47" t="n">
+      <c r="M48" s="48" t="n">
         <v>192</v>
       </c>
       <c r="N48" s="30" t="n">
@@ -7719,12 +7724,12 @@
           <t>HD건설기계</t>
         </is>
       </c>
-      <c r="P48" s="34" t="inlineStr">
+      <c r="P48" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q48" s="61" t="n">
+      <c r="Q48" s="62" t="n">
         <v>-67</v>
       </c>
     </row>
@@ -7737,12 +7742,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="C49" s="34" t="inlineStr">
+      <c r="C49" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D49" s="47" t="n">
+      <c r="D49" s="48" t="n">
         <v>551</v>
       </c>
       <c r="E49" s="30" t="n">
@@ -7753,12 +7758,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="G49" s="34" t="inlineStr">
+      <c r="G49" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H49" s="61" t="n">
+      <c r="H49" s="62" t="n">
         <v>-382</v>
       </c>
       <c r="J49" s="30" t="n">
@@ -7769,12 +7774,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="L49" s="34" t="inlineStr">
+      <c r="L49" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M49" s="47" t="n">
+      <c r="M49" s="48" t="n">
         <v>133</v>
       </c>
       <c r="N49" s="30" t="n">
@@ -7785,12 +7790,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="P49" s="34" t="inlineStr">
+      <c r="P49" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="Q49" s="61" t="n">
+      <c r="Q49" s="62" t="n">
         <v>-48</v>
       </c>
     </row>
@@ -7803,12 +7808,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="C50" s="34" t="inlineStr">
+      <c r="C50" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D50" s="47" t="n">
+      <c r="D50" s="48" t="n">
         <v>382</v>
       </c>
       <c r="E50" s="30" t="n">
@@ -7819,12 +7824,12 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="G50" s="41" t="inlineStr">
+      <c r="G50" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H50" s="61" t="n">
+      <c r="H50" s="62" t="n">
         <v>-296</v>
       </c>
       <c r="J50" s="30" t="n">
@@ -7835,12 +7840,12 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="L50" s="41" t="inlineStr">
+      <c r="L50" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="M50" s="47" t="n">
+      <c r="M50" s="48" t="n">
         <v>56</v>
       </c>
       <c r="N50" s="30" t="n">
@@ -7851,12 +7856,12 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="P50" s="34" t="inlineStr">
+      <c r="P50" s="35" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="Q50" s="61" t="n">
+      <c r="Q50" s="62" t="n">
         <v>-45</v>
       </c>
     </row>
@@ -7869,12 +7874,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="C51" s="34" t="inlineStr">
+      <c r="C51" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D51" s="47" t="n">
+      <c r="D51" s="48" t="n">
         <v>246</v>
       </c>
       <c r="E51" s="30" t="n">
@@ -7885,12 +7890,12 @@
           <t>기아</t>
         </is>
       </c>
-      <c r="G51" s="41" t="inlineStr">
+      <c r="G51" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H51" s="61" t="n">
+      <c r="H51" s="62" t="n">
         <v>-183</v>
       </c>
       <c r="J51" s="30" t="n">
@@ -7901,12 +7906,12 @@
           <t>LIG디펜스앤에어로스페이스</t>
         </is>
       </c>
-      <c r="L51" s="34" t="inlineStr">
+      <c r="L51" s="35" t="inlineStr">
         <is>
           <t>금속</t>
         </is>
       </c>
-      <c r="M51" s="47" t="n">
+      <c r="M51" s="48" t="n">
         <v>45</v>
       </c>
       <c r="N51" s="30" t="n">
@@ -7917,12 +7922,12 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="P51" s="41" t="inlineStr">
+      <c r="P51" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q51" s="61" t="n">
+      <c r="Q51" s="62" t="n">
         <v>-36</v>
       </c>
     </row>
@@ -7935,12 +7940,12 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="C52" s="34" t="inlineStr">
+      <c r="C52" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D52" s="47" t="n">
+      <c r="D52" s="48" t="n">
         <v>233</v>
       </c>
       <c r="E52" s="30" t="n">
@@ -7951,12 +7956,12 @@
           <t>현대건설</t>
         </is>
       </c>
-      <c r="G52" s="34" t="inlineStr">
+      <c r="G52" s="35" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
       </c>
-      <c r="H52" s="61" t="n">
+      <c r="H52" s="62" t="n">
         <v>-151</v>
       </c>
       <c r="J52" s="30" t="n">
@@ -7967,12 +7972,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="L52" s="34" t="inlineStr">
+      <c r="L52" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="M52" s="47" t="n">
+      <c r="M52" s="48" t="n">
         <v>42</v>
       </c>
       <c r="N52" s="30" t="n">
@@ -7983,12 +7988,12 @@
           <t>하나금융지주</t>
         </is>
       </c>
-      <c r="P52" s="34" t="inlineStr">
+      <c r="P52" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="Q52" s="61" t="n">
+      <c r="Q52" s="62" t="n">
         <v>-30</v>
       </c>
     </row>
@@ -8001,12 +8006,12 @@
           <t>한화시스템</t>
         </is>
       </c>
-      <c r="C53" s="34" t="inlineStr">
+      <c r="C53" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D53" s="47" t="n">
+      <c r="D53" s="48" t="n">
         <v>210</v>
       </c>
       <c r="E53" s="30" t="n">
@@ -8017,12 +8022,12 @@
           <t>HD건설기계</t>
         </is>
       </c>
-      <c r="G53" s="34" t="inlineStr">
+      <c r="G53" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H53" s="61" t="n">
+      <c r="H53" s="62" t="n">
         <v>-148</v>
       </c>
       <c r="J53" s="30" t="n">
@@ -8033,12 +8038,12 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="L53" s="34" t="inlineStr">
+      <c r="L53" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M53" s="47" t="n">
+      <c r="M53" s="48" t="n">
         <v>36</v>
       </c>
       <c r="N53" s="30" t="n">
@@ -8049,12 +8054,12 @@
           <t>기아</t>
         </is>
       </c>
-      <c r="P53" s="41" t="inlineStr">
+      <c r="P53" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q53" s="61" t="n">
+      <c r="Q53" s="62" t="n">
         <v>-19</v>
       </c>
     </row>
@@ -8067,12 +8072,12 @@
           <t>우리금융지주</t>
         </is>
       </c>
-      <c r="C54" s="34" t="inlineStr">
+      <c r="C54" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D54" s="47" t="n">
+      <c r="D54" s="48" t="n">
         <v>206</v>
       </c>
       <c r="E54" s="30" t="n">
@@ -8083,12 +8088,12 @@
           <t>심텍</t>
         </is>
       </c>
-      <c r="G54" s="34" t="inlineStr">
+      <c r="G54" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H54" s="61" t="n">
+      <c r="H54" s="62" t="n">
         <v>-114</v>
       </c>
       <c r="J54" s="30" t="n">
@@ -8099,12 +8104,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="L54" s="34" t="inlineStr">
+      <c r="L54" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M54" s="47" t="n">
+      <c r="M54" s="48" t="n">
         <v>35</v>
       </c>
       <c r="N54" s="30" t="n">
@@ -8115,12 +8120,12 @@
           <t>두산</t>
         </is>
       </c>
-      <c r="P54" s="34" t="inlineStr">
+      <c r="P54" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q54" s="61" t="n">
+      <c r="Q54" s="62" t="n">
         <v>-18</v>
       </c>
     </row>
@@ -8133,12 +8138,12 @@
           <t>LIG디펜스앤에어로스페이스</t>
         </is>
       </c>
-      <c r="C55" s="34" t="inlineStr">
+      <c r="C55" s="35" t="inlineStr">
         <is>
           <t>금속</t>
         </is>
       </c>
-      <c r="D55" s="47" t="n">
+      <c r="D55" s="48" t="n">
         <v>181</v>
       </c>
       <c r="E55" s="30" t="n">
@@ -8149,12 +8154,12 @@
           <t>LG이노텍</t>
         </is>
       </c>
-      <c r="G55" s="34" t="inlineStr">
+      <c r="G55" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H55" s="61" t="n">
+      <c r="H55" s="62" t="n">
         <v>-108</v>
       </c>
       <c r="J55" s="30" t="n">
@@ -8165,12 +8170,12 @@
           <t>이수페타시스</t>
         </is>
       </c>
-      <c r="L55" s="34" t="inlineStr">
+      <c r="L55" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M55" s="47" t="n">
+      <c r="M55" s="48" t="n">
         <v>33</v>
       </c>
       <c r="N55" s="30" t="n">
@@ -8181,12 +8186,12 @@
           <t>GS</t>
         </is>
       </c>
-      <c r="P55" s="34" t="inlineStr">
+      <c r="P55" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="Q55" s="61" t="n">
+      <c r="Q55" s="62" t="n">
         <v>-17</v>
       </c>
     </row>
@@ -8199,12 +8204,12 @@
           <t>NC</t>
         </is>
       </c>
-      <c r="C56" s="34" t="inlineStr">
+      <c r="C56" s="35" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="D56" s="47" t="n">
+      <c r="D56" s="48" t="n">
         <v>175</v>
       </c>
       <c r="E56" s="30" t="n">
@@ -8215,12 +8220,12 @@
           <t>피에스케이홀딩스</t>
         </is>
       </c>
-      <c r="G56" s="34" t="inlineStr">
+      <c r="G56" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H56" s="61" t="n">
+      <c r="H56" s="62" t="n">
         <v>-98</v>
       </c>
       <c r="J56" s="30" t="n">
@@ -8231,12 +8236,12 @@
           <t>한화시스템</t>
         </is>
       </c>
-      <c r="L56" s="34" t="inlineStr">
+      <c r="L56" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M56" s="47" t="n">
+      <c r="M56" s="48" t="n">
         <v>32</v>
       </c>
       <c r="N56" s="30" t="n">
@@ -8247,12 +8252,12 @@
           <t>한국콜마</t>
         </is>
       </c>
-      <c r="P56" s="34" t="inlineStr">
+      <c r="P56" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="Q56" s="61" t="n">
+      <c r="Q56" s="62" t="n">
         <v>-15</v>
       </c>
     </row>
@@ -8265,12 +8270,12 @@
           <t>리노공업</t>
         </is>
       </c>
-      <c r="C57" s="34" t="inlineStr">
+      <c r="C57" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D57" s="47" t="n">
+      <c r="D57" s="48" t="n">
         <v>164</v>
       </c>
       <c r="E57" s="30" t="n">
@@ -8281,12 +8286,12 @@
           <t>HD현대중공업</t>
         </is>
       </c>
-      <c r="G57" s="41" t="inlineStr">
+      <c r="G57" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H57" s="61" t="n">
+      <c r="H57" s="62" t="n">
         <v>-97</v>
       </c>
       <c r="J57" s="30" t="n">
@@ -8297,12 +8302,12 @@
           <t>리노공업</t>
         </is>
       </c>
-      <c r="L57" s="34" t="inlineStr">
+      <c r="L57" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M57" s="47" t="n">
+      <c r="M57" s="48" t="n">
         <v>30</v>
       </c>
       <c r="N57" s="30" t="n">
@@ -8313,12 +8318,12 @@
           <t>GS건설</t>
         </is>
       </c>
-      <c r="P57" s="34" t="inlineStr">
+      <c r="P57" s="35" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
       </c>
-      <c r="Q57" s="61" t="n">
+      <c r="Q57" s="62" t="n">
         <v>-13</v>
       </c>
     </row>
@@ -8329,61 +8334,61 @@
           <t>F9 기타법인</t>
         </is>
       </c>
-      <c r="E59" s="58" t="inlineStr">
+      <c r="E59" s="59" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="59" t="inlineStr">
+      <c r="A60" s="60" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="E60" s="60" t="inlineStr">
+      <c r="E60" s="61" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="45" t="inlineStr">
+      <c r="A61" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B61" s="45" t="inlineStr">
+      <c r="B61" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C61" s="45" t="inlineStr">
+      <c r="C61" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D61" s="45" t="inlineStr">
+      <c r="D61" s="46" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E61" s="45" t="inlineStr">
+      <c r="E61" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F61" s="45" t="inlineStr">
+      <c r="F61" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G61" s="45" t="inlineStr">
+      <c r="G61" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H61" s="45" t="inlineStr">
+      <c r="H61" s="46" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -8398,12 +8403,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="C62" s="34" t="inlineStr">
+      <c r="C62" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D62" s="47" t="n">
+      <c r="D62" s="48" t="n">
         <v>19833</v>
       </c>
       <c r="E62" s="30" t="n">
@@ -8414,12 +8419,12 @@
           <t>브릴스</t>
         </is>
       </c>
-      <c r="G62" s="34" t="inlineStr">
+      <c r="G62" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H62" s="61" t="n">
+      <c r="H62" s="62" t="n">
         <v>-222</v>
       </c>
     </row>
@@ -8432,12 +8437,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="C63" s="34" t="inlineStr">
+      <c r="C63" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D63" s="47" t="n">
+      <c r="D63" s="48" t="n">
         <v>10839</v>
       </c>
       <c r="E63" s="30" t="n">
@@ -8448,12 +8453,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="G63" s="34" t="inlineStr">
+      <c r="G63" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="H63" s="61" t="n">
+      <c r="H63" s="62" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -8466,12 +8471,12 @@
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="C64" s="34" t="inlineStr">
+      <c r="C64" s="35" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="D64" s="47" t="n">
+      <c r="D64" s="48" t="n">
         <v>185</v>
       </c>
       <c r="E64" s="30" t="n">
@@ -8482,12 +8487,12 @@
           <t>두산</t>
         </is>
       </c>
-      <c r="G64" s="34" t="inlineStr">
+      <c r="G64" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H64" s="61" t="n">
+      <c r="H64" s="62" t="n">
         <v>-32</v>
       </c>
     </row>
@@ -8500,12 +8505,12 @@
           <t>KT&amp;G</t>
         </is>
       </c>
-      <c r="C65" s="34" t="inlineStr">
+      <c r="C65" s="35" t="inlineStr">
         <is>
           <t>음식료·담배</t>
         </is>
       </c>
-      <c r="D65" s="47" t="n">
+      <c r="D65" s="48" t="n">
         <v>70</v>
       </c>
       <c r="E65" s="30" t="n">
@@ -8516,12 +8521,12 @@
           <t>코스모로보틱스</t>
         </is>
       </c>
-      <c r="G65" s="41" t="inlineStr">
+      <c r="G65" s="42" t="inlineStr">
         <is>
           <t>의료·정밀기기</t>
         </is>
       </c>
-      <c r="H65" s="61" t="n">
+      <c r="H65" s="62" t="n">
         <v>-19</v>
       </c>
     </row>
@@ -8534,12 +8539,12 @@
           <t>서진시스템</t>
         </is>
       </c>
-      <c r="C66" s="34" t="inlineStr">
+      <c r="C66" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D66" s="47" t="n">
+      <c r="D66" s="48" t="n">
         <v>54</v>
       </c>
       <c r="E66" s="30" t="n">
@@ -8550,12 +8555,12 @@
           <t>SK텔레콤</t>
         </is>
       </c>
-      <c r="G66" s="34" t="inlineStr">
+      <c r="G66" s="35" t="inlineStr">
         <is>
           <t>통신</t>
         </is>
       </c>
-      <c r="H66" s="61" t="n">
+      <c r="H66" s="62" t="n">
         <v>-18</v>
       </c>
     </row>
@@ -8568,12 +8573,12 @@
           <t>한화오션</t>
         </is>
       </c>
-      <c r="C67" s="41" t="inlineStr">
+      <c r="C67" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="D67" s="47" t="n">
+      <c r="D67" s="48" t="n">
         <v>40</v>
       </c>
       <c r="E67" s="30" t="n">
@@ -8584,12 +8589,12 @@
           <t>대덕전자</t>
         </is>
       </c>
-      <c r="G67" s="34" t="inlineStr">
+      <c r="G67" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H67" s="61" t="n">
+      <c r="H67" s="62" t="n">
         <v>-18</v>
       </c>
     </row>
@@ -8602,12 +8607,12 @@
           <t>리노공업</t>
         </is>
       </c>
-      <c r="C68" s="34" t="inlineStr">
+      <c r="C68" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D68" s="47" t="n">
+      <c r="D68" s="48" t="n">
         <v>36</v>
       </c>
       <c r="E68" s="30" t="n">
@@ -8618,12 +8623,12 @@
           <t>LG이노텍</t>
         </is>
       </c>
-      <c r="G68" s="34" t="inlineStr">
+      <c r="G68" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H68" s="61" t="n">
+      <c r="H68" s="62" t="n">
         <v>-16</v>
       </c>
     </row>
@@ -8636,12 +8641,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="C69" s="34" t="inlineStr">
+      <c r="C69" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D69" s="47" t="n">
+      <c r="D69" s="48" t="n">
         <v>35</v>
       </c>
       <c r="E69" s="30" t="n">
@@ -8652,12 +8657,12 @@
           <t>오킨스전자</t>
         </is>
       </c>
-      <c r="G69" s="34" t="inlineStr">
+      <c r="G69" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H69" s="61" t="n">
+      <c r="H69" s="62" t="n">
         <v>-14</v>
       </c>
     </row>
@@ -8670,12 +8675,12 @@
           <t>파두</t>
         </is>
       </c>
-      <c r="C70" s="34" t="inlineStr">
+      <c r="C70" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D70" s="47" t="n">
+      <c r="D70" s="48" t="n">
         <v>35</v>
       </c>
       <c r="E70" s="30" t="n">
@@ -8686,12 +8691,12 @@
           <t>디아이</t>
         </is>
       </c>
-      <c r="G70" s="41" t="inlineStr">
+      <c r="G70" s="42" t="inlineStr">
         <is>
           <t>의료·정밀기기</t>
         </is>
       </c>
-      <c r="H70" s="61" t="n">
+      <c r="H70" s="62" t="n">
         <v>-11</v>
       </c>
     </row>
@@ -8704,12 +8709,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="C71" s="34" t="inlineStr">
+      <c r="C71" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D71" s="47" t="n">
+      <c r="D71" s="48" t="n">
         <v>31</v>
       </c>
       <c r="E71" s="30" t="n">
@@ -8720,18 +8725,18 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="G71" s="34" t="inlineStr">
+      <c r="G71" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H71" s="61" t="n">
+      <c r="H71" s="62" t="n">
         <v>-11</v>
       </c>
     </row>
     <row r="72"/>
     <row r="73" ht="31" customHeight="1" s="15">
-      <c r="A73" s="62" t="inlineStr">
+      <c r="A73" s="63" t="inlineStr">
         <is>
           <t>외인·기관 동시 등재 종목=종목명 굵게(동반 매수/매도) · netbuy_rank 일별 아카이브 합산 — 상위 30 리스트 등재일만 반영되는 근사치 · 금융투자=증권, 투신(사모)=투자신탁+사모펀드, 기타법인=일반법인(자사주 매입 등) (확정 병합분) · 외인+기관=합산 카드와 동일</t>
         </is>
@@ -8849,87 +8854,87 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="45" t="inlineStr">
+      <c r="A4" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B4" s="45" t="inlineStr">
+      <c r="B4" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="D4" s="46" t="inlineStr">
         <is>
           <t>금액(억)</t>
         </is>
       </c>
-      <c r="E4" s="45" t="inlineStr">
+      <c r="E4" s="46" t="inlineStr">
         <is>
           <t>시총대비(%)</t>
         </is>
       </c>
-      <c r="G4" s="45" t="inlineStr">
+      <c r="G4" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="H4" s="45" t="inlineStr">
+      <c r="H4" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="I4" s="45" t="inlineStr">
+      <c r="I4" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="J4" s="45" t="inlineStr">
+      <c r="J4" s="46" t="inlineStr">
         <is>
           <t>증감(억)</t>
         </is>
       </c>
-      <c r="K4" s="45" t="inlineStr">
+      <c r="K4" s="46" t="inlineStr">
         <is>
           <t>대차잔고(억)</t>
         </is>
       </c>
-      <c r="L4" s="45" t="inlineStr">
+      <c r="L4" s="46" t="inlineStr">
         <is>
           <t>시총대비(%)</t>
         </is>
       </c>
-      <c r="N4" s="45" t="inlineStr">
+      <c r="N4" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O4" s="45" t="inlineStr">
+      <c r="O4" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P4" s="45" t="inlineStr">
+      <c r="P4" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q4" s="45" t="inlineStr">
+      <c r="Q4" s="46" t="inlineStr">
         <is>
           <t>증감(억)</t>
         </is>
       </c>
-      <c r="R4" s="45" t="inlineStr">
+      <c r="R4" s="46" t="inlineStr">
         <is>
           <t>대차잔고(억)</t>
         </is>
       </c>
-      <c r="S4" s="45" t="inlineStr">
+      <c r="S4" s="46" t="inlineStr">
         <is>
           <t>시총대비(%)</t>
         </is>
@@ -8944,15 +8949,15 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="C5" s="34" t="inlineStr">
+      <c r="C5" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D5" s="63" t="n">
+      <c r="D5" s="64" t="n">
         <v>4082</v>
       </c>
-      <c r="E5" s="64" t="n">
+      <c r="E5" s="65" t="n">
         <v>0.03</v>
       </c>
       <c r="G5" s="30" t="n">
@@ -8963,18 +8968,18 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="I5" s="34" t="inlineStr">
+      <c r="I5" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J5" s="47" t="n">
+      <c r="J5" s="48" t="n">
         <v>10005.6</v>
       </c>
-      <c r="K5" s="65" t="n">
+      <c r="K5" s="66" t="n">
         <v>209723.2</v>
       </c>
-      <c r="L5" s="64" t="n">
+      <c r="L5" s="65" t="n">
         <v>1.3</v>
       </c>
       <c r="N5" s="30" t="n">
@@ -8985,18 +8990,18 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="P5" s="34" t="inlineStr">
+      <c r="P5" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q5" s="61" t="n">
+      <c r="Q5" s="62" t="n">
         <v>-434.6</v>
       </c>
-      <c r="R5" s="65" t="n">
+      <c r="R5" s="66" t="n">
         <v>13173.4</v>
       </c>
-      <c r="S5" s="64" t="n">
+      <c r="S5" s="65" t="n">
         <v>3.16</v>
       </c>
     </row>
@@ -9009,15 +9014,15 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="C6" s="34" t="inlineStr">
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D6" s="63" t="n">
+      <c r="D6" s="64" t="n">
         <v>2200</v>
       </c>
-      <c r="E6" s="64" t="n">
+      <c r="E6" s="65" t="n">
         <v>0.01</v>
       </c>
       <c r="G6" s="30" t="n">
@@ -9028,18 +9033,18 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="I6" s="34" t="inlineStr">
+      <c r="I6" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J6" s="47" t="n">
+      <c r="J6" s="48" t="n">
         <v>7293.8</v>
       </c>
-      <c r="K6" s="65" t="n">
+      <c r="K6" s="66" t="n">
         <v>233010.9</v>
       </c>
-      <c r="L6" s="64" t="n">
+      <c r="L6" s="65" t="n">
         <v>1.74</v>
       </c>
       <c r="N6" s="30" t="n">
@@ -9050,18 +9055,18 @@
           <t>S-Oil</t>
         </is>
       </c>
-      <c r="P6" s="34" t="inlineStr">
+      <c r="P6" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="Q6" s="61" t="n">
+      <c r="Q6" s="62" t="n">
         <v>-352.6</v>
       </c>
-      <c r="R6" s="65" t="n">
+      <c r="R6" s="66" t="n">
         <v>3509</v>
       </c>
-      <c r="S6" s="64" t="n">
+      <c r="S6" s="65" t="n">
         <v>2.09</v>
       </c>
     </row>
@@ -9074,15 +9079,15 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="C7" s="34" t="inlineStr">
+      <c r="C7" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D7" s="63" t="n">
+      <c r="D7" s="64" t="n">
         <v>952</v>
       </c>
-      <c r="E7" s="64" t="n">
+      <c r="E7" s="65" t="n">
         <v>0.18</v>
       </c>
       <c r="G7" s="30" t="n">
@@ -9093,18 +9098,18 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="I7" s="34" t="inlineStr">
+      <c r="I7" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="J7" s="47" t="n">
+      <c r="J7" s="48" t="n">
         <v>2471.1</v>
       </c>
-      <c r="K7" s="65" t="n">
+      <c r="K7" s="66" t="n">
         <v>52054.5</v>
       </c>
-      <c r="L7" s="64" t="n">
+      <c r="L7" s="65" t="n">
         <v>20.34</v>
       </c>
       <c r="N7" s="30" t="n">
@@ -9115,18 +9120,18 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="P7" s="34" t="inlineStr">
+      <c r="P7" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q7" s="61" t="n">
+      <c r="Q7" s="62" t="n">
         <v>-212.7</v>
       </c>
-      <c r="R7" s="65" t="n">
+      <c r="R7" s="66" t="n">
         <v>9472.299999999999</v>
       </c>
-      <c r="S7" s="64" t="n">
+      <c r="S7" s="65" t="n">
         <v>2.75</v>
       </c>
     </row>
@@ -9139,11 +9144,11 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="C8" s="34" t="inlineStr"/>
-      <c r="D8" s="63" t="n">
+      <c r="C8" s="35" t="inlineStr"/>
+      <c r="D8" s="64" t="n">
         <v>756</v>
       </c>
-      <c r="E8" s="64" t="n">
+      <c r="E8" s="65" t="n">
         <v>0.11</v>
       </c>
       <c r="G8" s="30" t="n">
@@ -9154,18 +9159,18 @@
           <t>현대모비스</t>
         </is>
       </c>
-      <c r="I8" s="41" t="inlineStr">
+      <c r="I8" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="J8" s="47" t="n">
+      <c r="J8" s="48" t="n">
         <v>1101.6</v>
       </c>
-      <c r="K8" s="65" t="n">
+      <c r="K8" s="66" t="n">
         <v>6040.8</v>
       </c>
-      <c r="L8" s="64" t="n">
+      <c r="L8" s="65" t="n">
         <v>1.76</v>
       </c>
       <c r="N8" s="30" t="n">
@@ -9176,14 +9181,14 @@
           <t>KT&amp;G</t>
         </is>
       </c>
-      <c r="P8" s="34" t="inlineStr"/>
-      <c r="Q8" s="61" t="n">
+      <c r="P8" s="35" t="inlineStr"/>
+      <c r="Q8" s="62" t="n">
         <v>-156.7</v>
       </c>
-      <c r="R8" s="65" t="n">
+      <c r="R8" s="66" t="n">
         <v>2561</v>
       </c>
-      <c r="S8" s="64" t="n">
+      <c r="S8" s="65" t="n">
         <v>1.41</v>
       </c>
     </row>
@@ -9196,15 +9201,15 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="C9" s="34" t="inlineStr">
+      <c r="C9" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D9" s="63" t="n">
+      <c r="D9" s="64" t="n">
         <v>618</v>
       </c>
-      <c r="E9" s="64" t="n">
+      <c r="E9" s="65" t="n">
         <v>0.04</v>
       </c>
       <c r="G9" s="30" t="n">
@@ -9215,18 +9220,18 @@
           <t>원익IPS</t>
         </is>
       </c>
-      <c r="I9" s="34" t="inlineStr">
+      <c r="I9" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="J9" s="47" t="n">
+      <c r="J9" s="48" t="n">
         <v>1066.7</v>
       </c>
-      <c r="K9" s="65" t="n">
+      <c r="K9" s="66" t="n">
         <v>11525</v>
       </c>
-      <c r="L9" s="64" t="n">
+      <c r="L9" s="65" t="n">
         <v>16.36</v>
       </c>
       <c r="N9" s="30" t="n">
@@ -9237,18 +9242,18 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="P9" s="34" t="inlineStr">
+      <c r="P9" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q9" s="61" t="n">
+      <c r="Q9" s="62" t="n">
         <v>-153.2</v>
       </c>
-      <c r="R9" s="65" t="n">
+      <c r="R9" s="66" t="n">
         <v>32814.7</v>
       </c>
-      <c r="S9" s="64" t="n">
+      <c r="S9" s="65" t="n">
         <v>3.89</v>
       </c>
     </row>
@@ -9261,15 +9266,15 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="C10" s="34" t="inlineStr">
+      <c r="C10" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D10" s="63" t="n">
+      <c r="D10" s="64" t="n">
         <v>488</v>
       </c>
-      <c r="E10" s="64" t="n">
+      <c r="E10" s="65" t="n">
         <v>0.19</v>
       </c>
       <c r="G10" s="30" t="n">
@@ -9280,18 +9285,18 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="I10" s="34" t="inlineStr">
+      <c r="I10" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J10" s="47" t="n">
+      <c r="J10" s="48" t="n">
         <v>953</v>
       </c>
-      <c r="K10" s="65" t="n">
+      <c r="K10" s="66" t="n">
         <v>37435.2</v>
       </c>
-      <c r="L10" s="64" t="n">
+      <c r="L10" s="65" t="n">
         <v>3.21</v>
       </c>
       <c r="N10" s="30" t="n">
@@ -9302,18 +9307,18 @@
           <t>GS건설</t>
         </is>
       </c>
-      <c r="P10" s="34" t="inlineStr">
+      <c r="P10" s="35" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
       </c>
-      <c r="Q10" s="61" t="n">
+      <c r="Q10" s="62" t="n">
         <v>-142.1</v>
       </c>
-      <c r="R10" s="65" t="n">
+      <c r="R10" s="66" t="n">
         <v>2301.4</v>
       </c>
-      <c r="S10" s="64" t="n">
+      <c r="S10" s="65" t="n">
         <v>8.16</v>
       </c>
     </row>
@@ -9326,15 +9331,15 @@
           <t>KB금융</t>
         </is>
       </c>
-      <c r="C11" s="34" t="inlineStr">
+      <c r="C11" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D11" s="63" t="n">
+      <c r="D11" s="64" t="n">
         <v>446</v>
       </c>
-      <c r="E11" s="64" t="n">
+      <c r="E11" s="65" t="n">
         <v>0.08</v>
       </c>
       <c r="G11" s="30" t="n">
@@ -9345,14 +9350,14 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="I11" s="34" t="inlineStr"/>
-      <c r="J11" s="47" t="n">
+      <c r="I11" s="35" t="inlineStr"/>
+      <c r="J11" s="48" t="n">
         <v>869.9</v>
       </c>
-      <c r="K11" s="65" t="n">
+      <c r="K11" s="66" t="n">
         <v>25404.9</v>
       </c>
-      <c r="L11" s="64" t="n">
+      <c r="L11" s="65" t="n">
         <v>1.55</v>
       </c>
       <c r="N11" s="30" t="n">
@@ -9363,18 +9368,18 @@
           <t>POSCO홀딩스</t>
         </is>
       </c>
-      <c r="P11" s="34" t="inlineStr">
+      <c r="P11" s="35" t="inlineStr">
         <is>
           <t>금속</t>
         </is>
       </c>
-      <c r="Q11" s="61" t="n">
+      <c r="Q11" s="62" t="n">
         <v>-129.3</v>
       </c>
-      <c r="R11" s="65" t="n">
+      <c r="R11" s="66" t="n">
         <v>6987.6</v>
       </c>
-      <c r="S11" s="64" t="n">
+      <c r="S11" s="65" t="n">
         <v>2.88</v>
       </c>
     </row>
@@ -9387,15 +9392,15 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="C12" s="34" t="inlineStr">
+      <c r="C12" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D12" s="63" t="n">
+      <c r="D12" s="64" t="n">
         <v>401</v>
       </c>
-      <c r="E12" s="64" t="n">
+      <c r="E12" s="65" t="n">
         <v>0.03</v>
       </c>
       <c r="G12" s="30" t="n">
@@ -9406,18 +9411,18 @@
           <t>제주반도체</t>
         </is>
       </c>
-      <c r="I12" s="34" t="inlineStr">
+      <c r="I12" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J12" s="47" t="n">
+      <c r="J12" s="48" t="n">
         <v>860.9</v>
       </c>
-      <c r="K12" s="65" t="n">
+      <c r="K12" s="66" t="n">
         <v>6783.7</v>
       </c>
-      <c r="L12" s="64" t="n">
+      <c r="L12" s="65" t="n">
         <v>22.33</v>
       </c>
       <c r="N12" s="30" t="n">
@@ -9428,18 +9433,18 @@
           <t>KB금융</t>
         </is>
       </c>
-      <c r="P12" s="34" t="inlineStr">
+      <c r="P12" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="Q12" s="61" t="n">
+      <c r="Q12" s="62" t="n">
         <v>-104.3</v>
       </c>
-      <c r="R12" s="65" t="n">
+      <c r="R12" s="66" t="n">
         <v>6800.1</v>
       </c>
-      <c r="S12" s="64" t="n">
+      <c r="S12" s="65" t="n">
         <v>1.15</v>
       </c>
     </row>
@@ -9452,15 +9457,15 @@
           <t>원익IPS</t>
         </is>
       </c>
-      <c r="C13" s="34" t="inlineStr">
+      <c r="C13" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D13" s="63" t="n">
+      <c r="D13" s="64" t="n">
         <v>384</v>
       </c>
-      <c r="E13" s="64" t="n">
+      <c r="E13" s="65" t="n">
         <v>0.54</v>
       </c>
       <c r="G13" s="30" t="n">
@@ -9471,18 +9476,18 @@
           <t>에코프로</t>
         </is>
       </c>
-      <c r="I13" s="34" t="inlineStr">
+      <c r="I13" s="35" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="J13" s="47" t="n">
+      <c r="J13" s="48" t="n">
         <v>741.7</v>
       </c>
-      <c r="K13" s="65" t="n">
+      <c r="K13" s="66" t="n">
         <v>18198.2</v>
       </c>
-      <c r="L13" s="64" t="n">
+      <c r="L13" s="65" t="n">
         <v>15.75</v>
       </c>
       <c r="N13" s="30" t="n">
@@ -9493,18 +9498,18 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="P13" s="34" t="inlineStr">
+      <c r="P13" s="35" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="Q13" s="61" t="n">
+      <c r="Q13" s="62" t="n">
         <v>-95.3</v>
       </c>
-      <c r="R13" s="65" t="n">
+      <c r="R13" s="66" t="n">
         <v>11020.5</v>
       </c>
-      <c r="S13" s="64" t="n">
+      <c r="S13" s="65" t="n">
         <v>3.79</v>
       </c>
     </row>
@@ -9517,15 +9522,15 @@
           <t>LG이노텍</t>
         </is>
       </c>
-      <c r="C14" s="34" t="inlineStr">
+      <c r="C14" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D14" s="63" t="n">
+      <c r="D14" s="64" t="n">
         <v>336</v>
       </c>
-      <c r="E14" s="64" t="n">
+      <c r="E14" s="65" t="n">
         <v>0.24</v>
       </c>
       <c r="G14" s="30" t="n">
@@ -9536,18 +9541,18 @@
           <t>HPSP</t>
         </is>
       </c>
-      <c r="I14" s="34" t="inlineStr">
+      <c r="I14" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="J14" s="47" t="n">
+      <c r="J14" s="48" t="n">
         <v>662.7</v>
       </c>
-      <c r="K14" s="65" t="n">
+      <c r="K14" s="66" t="n">
         <v>7947.5</v>
       </c>
-      <c r="L14" s="64" t="n">
+      <c r="L14" s="65" t="n">
         <v>14</v>
       </c>
       <c r="N14" s="30" t="n">
@@ -9558,24 +9563,24 @@
           <t>LS</t>
         </is>
       </c>
-      <c r="P14" s="34" t="inlineStr">
+      <c r="P14" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="Q14" s="61" t="n">
+      <c r="Q14" s="62" t="n">
         <v>-91.3</v>
       </c>
-      <c r="R14" s="65" t="n">
+      <c r="R14" s="66" t="n">
         <v>2623.4</v>
       </c>
-      <c r="S14" s="64" t="n">
+      <c r="S14" s="65" t="n">
         <v>2.82</v>
       </c>
     </row>
     <row r="15"/>
     <row r="16" ht="31" customHeight="1" s="15">
-      <c r="A16" s="62" t="inlineStr">
+      <c r="A16" s="63" t="inlineStr">
         <is>
           <t>랭킹 유니버스(순매수 상위 30 등재 종목) 한정 · 대차 증감=전월말 대비 최신 잔고 · 시총대비(%)=공매도 누적 금액÷시가총액, 대차잔고÷시가총액(KIS 마스터 시총(주 1회 갱신))</t>
         </is>
@@ -9668,77 +9673,77 @@
       <c r="O3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="45" t="inlineStr">
+      <c r="A4" s="46" t="inlineStr">
         <is>
           <t>업종</t>
         </is>
       </c>
-      <c r="B4" s="45" t="inlineStr">
+      <c r="B4" s="46" t="inlineStr">
         <is>
           <t>YTD</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="46" t="inlineStr">
         <is>
           <t>6M</t>
         </is>
       </c>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="D4" s="46" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="E4" s="45" t="inlineStr">
+      <c r="E4" s="46" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="F4" s="45" t="inlineStr">
+      <c r="F4" s="46" t="inlineStr">
         <is>
           <t>외인</t>
         </is>
       </c>
-      <c r="G4" s="45" t="inlineStr">
+      <c r="G4" s="46" t="inlineStr">
         <is>
           <t>기관(합)</t>
         </is>
       </c>
-      <c r="H4" s="45" t="inlineStr">
+      <c r="H4" s="46" t="inlineStr">
         <is>
           <t>외인+기관</t>
         </is>
       </c>
-      <c r="I4" s="45" t="inlineStr">
+      <c r="I4" s="46" t="inlineStr">
         <is>
           <t>금융투자</t>
         </is>
       </c>
-      <c r="J4" s="45" t="inlineStr">
+      <c r="J4" s="46" t="inlineStr">
         <is>
           <t>투신(사모)</t>
         </is>
       </c>
-      <c r="K4" s="45" t="inlineStr">
+      <c r="K4" s="46" t="inlineStr">
         <is>
           <t>연기금</t>
         </is>
       </c>
-      <c r="L4" s="45" t="inlineStr">
+      <c r="L4" s="46" t="inlineStr">
         <is>
           <t>보험</t>
         </is>
       </c>
-      <c r="M4" s="45" t="inlineStr">
+      <c r="M4" s="46" t="inlineStr">
         <is>
           <t>개인</t>
         </is>
       </c>
-      <c r="N4" s="45" t="inlineStr">
+      <c r="N4" s="46" t="inlineStr">
         <is>
           <t>기타법인</t>
         </is>
       </c>
-      <c r="O4" s="45" t="inlineStr">
+      <c r="O4" s="46" t="inlineStr">
         <is>
           <t>신호</t>
         </is>
@@ -9750,46 +9755,46 @@
           <t>의료·정밀기기</t>
         </is>
       </c>
-      <c r="B5" s="66" t="n">
+      <c r="B5" s="67" t="n">
         <v>35.11</v>
       </c>
-      <c r="C5" s="66" t="n">
+      <c r="C5" s="67" t="n">
         <v>33.36</v>
       </c>
-      <c r="D5" s="66" t="n">
+      <c r="D5" s="67" t="n">
         <v>2.71</v>
       </c>
-      <c r="E5" s="66" t="n">
+      <c r="E5" s="67" t="n">
         <v>6.29</v>
       </c>
-      <c r="F5" s="67" t="n">
+      <c r="F5" s="68" t="n">
         <v>151</v>
       </c>
-      <c r="G5" s="68" t="n">
+      <c r="G5" s="69" t="n">
         <v>-57</v>
       </c>
-      <c r="H5" s="67" t="n">
+      <c r="H5" s="68" t="n">
         <v>95</v>
       </c>
-      <c r="I5" s="67" t="n">
+      <c r="I5" s="68" t="n">
         <v>7</v>
       </c>
-      <c r="J5" s="68" t="n">
+      <c r="J5" s="69" t="n">
         <v>-37</v>
       </c>
-      <c r="K5" s="68" t="n">
+      <c r="K5" s="69" t="n">
         <v>-29</v>
       </c>
-      <c r="L5" s="67" t="n">
+      <c r="L5" s="68" t="n">
         <v>3</v>
       </c>
-      <c r="M5" s="68" t="n">
+      <c r="M5" s="69" t="n">
         <v>-88</v>
       </c>
-      <c r="N5" s="68" t="n">
+      <c r="N5" s="69" t="n">
         <v>-7</v>
       </c>
-      <c r="O5" s="59" t="inlineStr">
+      <c r="O5" s="60" t="inlineStr">
         <is>
           <t>동반강세</t>
         </is>
@@ -9801,43 +9806,43 @@
           <t>금속</t>
         </is>
       </c>
-      <c r="B6" s="66" t="n">
+      <c r="B6" s="67" t="n">
         <v>3.11</v>
       </c>
-      <c r="C6" s="69" t="n">
+      <c r="C6" s="70" t="n">
         <v>-15.24</v>
       </c>
-      <c r="D6" s="66" t="n">
+      <c r="D6" s="67" t="n">
         <v>1.7</v>
       </c>
-      <c r="E6" s="66" t="n">
+      <c r="E6" s="67" t="n">
         <v>3.33</v>
       </c>
-      <c r="F6" s="68" t="n">
+      <c r="F6" s="69" t="n">
         <v>-498</v>
       </c>
-      <c r="G6" s="67" t="n">
+      <c r="G6" s="68" t="n">
         <v>545</v>
       </c>
-      <c r="H6" s="67" t="n">
+      <c r="H6" s="68" t="n">
         <v>46</v>
       </c>
-      <c r="I6" s="67" t="n">
+      <c r="I6" s="68" t="n">
         <v>119</v>
       </c>
-      <c r="J6" s="67" t="n">
+      <c r="J6" s="68" t="n">
         <v>233</v>
       </c>
-      <c r="K6" s="67" t="n">
+      <c r="K6" s="68" t="n">
         <v>118</v>
       </c>
-      <c r="L6" s="67" t="n">
+      <c r="L6" s="68" t="n">
         <v>74</v>
       </c>
-      <c r="M6" s="68" t="n">
+      <c r="M6" s="69" t="n">
         <v>-75</v>
       </c>
-      <c r="N6" s="67" t="n">
+      <c r="N6" s="68" t="n">
         <v>28</v>
       </c>
       <c r="O6" s="30" t="inlineStr"/>
@@ -9848,43 +9853,43 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="B7" s="66" t="n">
+      <c r="B7" s="67" t="n">
         <v>123.01</v>
       </c>
-      <c r="C7" s="66" t="n">
+      <c r="C7" s="67" t="n">
         <v>69.20999999999999</v>
       </c>
-      <c r="D7" s="69" t="n">
+      <c r="D7" s="70" t="n">
         <v>-9</v>
       </c>
-      <c r="E7" s="66" t="n">
+      <c r="E7" s="67" t="n">
         <v>3.25</v>
       </c>
-      <c r="F7" s="68" t="n">
+      <c r="F7" s="69" t="n">
         <v>-2315</v>
       </c>
-      <c r="G7" s="67" t="n">
+      <c r="G7" s="68" t="n">
         <v>5958</v>
       </c>
-      <c r="H7" s="67" t="n">
+      <c r="H7" s="68" t="n">
         <v>3643</v>
       </c>
-      <c r="I7" s="67" t="n">
+      <c r="I7" s="68" t="n">
         <v>2049</v>
       </c>
-      <c r="J7" s="67" t="n">
+      <c r="J7" s="68" t="n">
         <v>1311</v>
       </c>
-      <c r="K7" s="67" t="n">
+      <c r="K7" s="68" t="n">
         <v>2044</v>
       </c>
-      <c r="L7" s="67" t="n">
+      <c r="L7" s="68" t="n">
         <v>524</v>
       </c>
-      <c r="M7" s="68" t="n">
+      <c r="M7" s="69" t="n">
         <v>-34226</v>
       </c>
-      <c r="N7" s="67" t="n">
+      <c r="N7" s="68" t="n">
         <v>30583</v>
       </c>
       <c r="O7" s="30" t="inlineStr"/>
@@ -9895,43 +9900,43 @@
           <t>제조</t>
         </is>
       </c>
-      <c r="B8" s="66" t="n">
+      <c r="B8" s="67" t="n">
         <v>77.8</v>
       </c>
-      <c r="C8" s="66" t="n">
+      <c r="C8" s="67" t="n">
         <v>41.7</v>
       </c>
-      <c r="D8" s="69" t="n">
+      <c r="D8" s="70" t="n">
         <v>-8.699999999999999</v>
       </c>
-      <c r="E8" s="66" t="n">
+      <c r="E8" s="67" t="n">
         <v>2.93</v>
       </c>
-      <c r="F8" s="68" t="n">
+      <c r="F8" s="69" t="n">
         <v>-3615</v>
       </c>
-      <c r="G8" s="67" t="n">
+      <c r="G8" s="68" t="n">
         <v>6335</v>
       </c>
-      <c r="H8" s="67" t="n">
+      <c r="H8" s="68" t="n">
         <v>2720</v>
       </c>
-      <c r="I8" s="67" t="n">
+      <c r="I8" s="68" t="n">
         <v>3011</v>
       </c>
-      <c r="J8" s="67" t="n">
+      <c r="J8" s="68" t="n">
         <v>1186</v>
       </c>
-      <c r="K8" s="67" t="n">
+      <c r="K8" s="68" t="n">
         <v>1596</v>
       </c>
-      <c r="L8" s="67" t="n">
+      <c r="L8" s="68" t="n">
         <v>483</v>
       </c>
-      <c r="M8" s="68" t="n">
+      <c r="M8" s="69" t="n">
         <v>-33800</v>
       </c>
-      <c r="N8" s="67" t="n">
+      <c r="N8" s="68" t="n">
         <v>31080</v>
       </c>
       <c r="O8" s="30" t="inlineStr"/>
@@ -9942,46 +9947,46 @@
           <t>섬유·의류</t>
         </is>
       </c>
-      <c r="B9" s="69" t="n">
+      <c r="B9" s="70" t="n">
         <v>-3.33</v>
       </c>
-      <c r="C9" s="69" t="n">
+      <c r="C9" s="70" t="n">
         <v>-1.43</v>
       </c>
-      <c r="D9" s="69" t="n">
+      <c r="D9" s="70" t="n">
         <v>-3.05</v>
       </c>
-      <c r="E9" s="66" t="n">
+      <c r="E9" s="67" t="n">
         <v>2.48</v>
       </c>
-      <c r="F9" s="67" t="n">
+      <c r="F9" s="68" t="n">
         <v>7</v>
       </c>
-      <c r="G9" s="68" t="n">
+      <c r="G9" s="69" t="n">
         <v>-1</v>
       </c>
-      <c r="H9" s="67" t="n">
+      <c r="H9" s="68" t="n">
         <v>6</v>
       </c>
-      <c r="I9" s="67" t="n">
+      <c r="I9" s="68" t="n">
         <v>2</v>
       </c>
-      <c r="J9" s="67" t="n">
+      <c r="J9" s="68" t="n">
         <v>11</v>
       </c>
-      <c r="K9" s="68" t="n">
+      <c r="K9" s="69" t="n">
         <v>-13</v>
       </c>
-      <c r="L9" s="68" t="n">
+      <c r="L9" s="69" t="n">
         <v>-2</v>
       </c>
-      <c r="M9" s="68" t="n">
+      <c r="M9" s="69" t="n">
         <v>-31</v>
       </c>
-      <c r="N9" s="67" t="n">
+      <c r="N9" s="68" t="n">
         <v>25</v>
       </c>
-      <c r="O9" s="70" t="inlineStr">
+      <c r="O9" s="71" t="inlineStr">
         <is>
           <t>수급유입</t>
         </is>
@@ -9993,43 +9998,43 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="B10" s="66" t="n">
+      <c r="B10" s="67" t="n">
         <v>15.09</v>
       </c>
-      <c r="C10" s="69" t="n">
+      <c r="C10" s="70" t="n">
         <v>-31.98</v>
       </c>
-      <c r="D10" s="69" t="n">
+      <c r="D10" s="70" t="n">
         <v>-14.87</v>
       </c>
-      <c r="E10" s="66" t="n">
+      <c r="E10" s="67" t="n">
         <v>2.41</v>
       </c>
-      <c r="F10" s="67" t="n">
+      <c r="F10" s="68" t="n">
         <v>26</v>
       </c>
-      <c r="G10" s="67" t="n">
+      <c r="G10" s="68" t="n">
         <v>191</v>
       </c>
-      <c r="H10" s="67" t="n">
+      <c r="H10" s="68" t="n">
         <v>217</v>
       </c>
-      <c r="I10" s="67" t="n">
+      <c r="I10" s="68" t="n">
         <v>63</v>
       </c>
-      <c r="J10" s="68" t="n">
+      <c r="J10" s="69" t="n">
         <v>-7</v>
       </c>
-      <c r="K10" s="67" t="n">
+      <c r="K10" s="68" t="n">
         <v>95</v>
       </c>
-      <c r="L10" s="67" t="n">
+      <c r="L10" s="68" t="n">
         <v>9</v>
       </c>
-      <c r="M10" s="68" t="n">
+      <c r="M10" s="69" t="n">
         <v>-225</v>
       </c>
-      <c r="N10" s="67" t="n">
+      <c r="N10" s="68" t="n">
         <v>7</v>
       </c>
       <c r="O10" s="30" t="inlineStr"/>
@@ -10040,46 +10045,46 @@
           <t>화학</t>
         </is>
       </c>
-      <c r="B11" s="66" t="n">
+      <c r="B11" s="67" t="n">
         <v>20.47</v>
       </c>
-      <c r="C11" s="66" t="n">
+      <c r="C11" s="67" t="n">
         <v>7.05</v>
       </c>
-      <c r="D11" s="66" t="n">
+      <c r="D11" s="67" t="n">
         <v>11.01</v>
       </c>
-      <c r="E11" s="66" t="n">
+      <c r="E11" s="67" t="n">
         <v>2.16</v>
       </c>
-      <c r="F11" s="67" t="n">
+      <c r="F11" s="68" t="n">
         <v>739</v>
       </c>
-      <c r="G11" s="67" t="n">
+      <c r="G11" s="68" t="n">
         <v>129</v>
       </c>
-      <c r="H11" s="67" t="n">
+      <c r="H11" s="68" t="n">
         <v>868</v>
       </c>
-      <c r="I11" s="67" t="n">
+      <c r="I11" s="68" t="n">
         <v>237</v>
       </c>
-      <c r="J11" s="67" t="n">
+      <c r="J11" s="68" t="n">
         <v>80</v>
       </c>
-      <c r="K11" s="68" t="n">
+      <c r="K11" s="69" t="n">
         <v>-149</v>
       </c>
-      <c r="L11" s="68" t="n">
+      <c r="L11" s="69" t="n">
         <v>-59</v>
       </c>
-      <c r="M11" s="68" t="n">
+      <c r="M11" s="69" t="n">
         <v>-924</v>
       </c>
-      <c r="N11" s="67" t="n">
+      <c r="N11" s="68" t="n">
         <v>56</v>
       </c>
-      <c r="O11" s="59" t="inlineStr">
+      <c r="O11" s="60" t="inlineStr">
         <is>
           <t>동반강세</t>
         </is>
@@ -10091,46 +10096,46 @@
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="B12" s="69" t="n">
+      <c r="B12" s="70" t="n">
         <v>-5.42</v>
       </c>
-      <c r="C12" s="69" t="n">
+      <c r="C12" s="70" t="n">
         <v>-22.35</v>
       </c>
-      <c r="D12" s="69" t="n">
+      <c r="D12" s="70" t="n">
         <v>-21.62</v>
       </c>
-      <c r="E12" s="66" t="n">
+      <c r="E12" s="67" t="n">
         <v>1.94</v>
       </c>
-      <c r="F12" s="68" t="n">
+      <c r="F12" s="69" t="n">
         <v>-780</v>
       </c>
-      <c r="G12" s="68" t="n">
+      <c r="G12" s="69" t="n">
         <v>-327</v>
       </c>
-      <c r="H12" s="68" t="n">
+      <c r="H12" s="69" t="n">
         <v>-1106</v>
       </c>
-      <c r="I12" s="67" t="n">
+      <c r="I12" s="68" t="n">
         <v>158</v>
       </c>
-      <c r="J12" s="67" t="n">
+      <c r="J12" s="68" t="n">
         <v>52</v>
       </c>
-      <c r="K12" s="68" t="n">
+      <c r="K12" s="69" t="n">
         <v>-533</v>
       </c>
-      <c r="L12" s="68" t="n">
+      <c r="L12" s="69" t="n">
         <v>-11</v>
       </c>
-      <c r="M12" s="67" t="n">
+      <c r="M12" s="68" t="n">
         <v>1069</v>
       </c>
-      <c r="N12" s="67" t="n">
+      <c r="N12" s="68" t="n">
         <v>38</v>
       </c>
-      <c r="O12" s="60" t="inlineStr">
+      <c r="O12" s="61" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -10142,46 +10147,46 @@
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="B13" s="69" t="n">
+      <c r="B13" s="70" t="n">
         <v>-13.29</v>
       </c>
-      <c r="C13" s="69" t="n">
+      <c r="C13" s="70" t="n">
         <v>-0.96</v>
       </c>
-      <c r="D13" s="69" t="n">
+      <c r="D13" s="70" t="n">
         <v>-5.56</v>
       </c>
-      <c r="E13" s="66" t="n">
+      <c r="E13" s="67" t="n">
         <v>1.5</v>
       </c>
-      <c r="F13" s="68" t="n">
+      <c r="F13" s="69" t="n">
         <v>-481</v>
       </c>
-      <c r="G13" s="68" t="n">
+      <c r="G13" s="69" t="n">
         <v>-220</v>
       </c>
-      <c r="H13" s="68" t="n">
+      <c r="H13" s="69" t="n">
         <v>-702</v>
       </c>
-      <c r="I13" s="67" t="n">
+      <c r="I13" s="68" t="n">
         <v>99</v>
       </c>
-      <c r="J13" s="67" t="n">
+      <c r="J13" s="68" t="n">
         <v>131</v>
       </c>
-      <c r="K13" s="68" t="n">
+      <c r="K13" s="69" t="n">
         <v>-413</v>
       </c>
-      <c r="L13" s="68" t="n">
+      <c r="L13" s="69" t="n">
         <v>-36</v>
       </c>
-      <c r="M13" s="67" t="n">
+      <c r="M13" s="68" t="n">
         <v>710</v>
       </c>
-      <c r="N13" s="68" t="n">
+      <c r="N13" s="69" t="n">
         <v>-8</v>
       </c>
-      <c r="O13" s="60" t="inlineStr">
+      <c r="O13" s="61" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -10193,43 +10198,43 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="B14" s="66" t="n">
+      <c r="B14" s="67" t="n">
         <v>14.8</v>
       </c>
-      <c r="C14" s="69" t="n">
+      <c r="C14" s="70" t="n">
         <v>-9.01</v>
       </c>
-      <c r="D14" s="69" t="n">
+      <c r="D14" s="70" t="n">
         <v>-0.63</v>
       </c>
-      <c r="E14" s="66" t="n">
+      <c r="E14" s="67" t="n">
         <v>1.48</v>
       </c>
-      <c r="F14" s="68" t="n">
+      <c r="F14" s="69" t="n">
         <v>-296</v>
       </c>
-      <c r="G14" s="68" t="n">
+      <c r="G14" s="69" t="n">
         <v>-99</v>
       </c>
-      <c r="H14" s="68" t="n">
+      <c r="H14" s="69" t="n">
         <v>-394</v>
       </c>
-      <c r="I14" s="67" t="n">
+      <c r="I14" s="68" t="n">
         <v>236</v>
       </c>
-      <c r="J14" s="68" t="n">
+      <c r="J14" s="69" t="n">
         <v>-411</v>
       </c>
-      <c r="K14" s="67" t="n">
+      <c r="K14" s="68" t="n">
         <v>119</v>
       </c>
-      <c r="L14" s="68" t="n">
+      <c r="L14" s="69" t="n">
         <v>-42</v>
       </c>
-      <c r="M14" s="67" t="n">
+      <c r="M14" s="68" t="n">
         <v>390</v>
       </c>
-      <c r="N14" s="67" t="n">
+      <c r="N14" s="68" t="n">
         <v>5</v>
       </c>
       <c r="O14" s="30" t="inlineStr"/>
@@ -10240,43 +10245,43 @@
           <t>통신</t>
         </is>
       </c>
-      <c r="B15" s="66" t="n">
+      <c r="B15" s="67" t="n">
         <v>24.89</v>
       </c>
-      <c r="C15" s="69" t="n">
+      <c r="C15" s="70" t="n">
         <v>-0.14</v>
       </c>
-      <c r="D15" s="69" t="n">
+      <c r="D15" s="70" t="n">
         <v>-0.73</v>
       </c>
-      <c r="E15" s="66" t="n">
+      <c r="E15" s="67" t="n">
         <v>1.34</v>
       </c>
-      <c r="F15" s="67" t="n">
+      <c r="F15" s="68" t="n">
         <v>138</v>
       </c>
-      <c r="G15" s="68" t="n">
+      <c r="G15" s="69" t="n">
         <v>-82</v>
       </c>
-      <c r="H15" s="67" t="n">
+      <c r="H15" s="68" t="n">
         <v>55</v>
       </c>
-      <c r="I15" s="68" t="n">
+      <c r="I15" s="69" t="n">
         <v>-8</v>
       </c>
-      <c r="J15" s="68" t="n">
+      <c r="J15" s="69" t="n">
         <v>-5</v>
       </c>
-      <c r="K15" s="68" t="n">
+      <c r="K15" s="69" t="n">
         <v>-61</v>
       </c>
-      <c r="L15" s="68" t="n">
+      <c r="L15" s="69" t="n">
         <v>-7</v>
       </c>
-      <c r="M15" s="68" t="n">
+      <c r="M15" s="69" t="n">
         <v>-40</v>
       </c>
-      <c r="N15" s="68" t="n">
+      <c r="N15" s="69" t="n">
         <v>-15</v>
       </c>
       <c r="O15" s="30" t="inlineStr"/>
@@ -10287,46 +10292,46 @@
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="B16" s="66" t="n">
+      <c r="B16" s="67" t="n">
         <v>11.39</v>
       </c>
-      <c r="C16" s="66" t="n">
+      <c r="C16" s="67" t="n">
         <v>4.26</v>
       </c>
-      <c r="D16" s="66" t="n">
+      <c r="D16" s="67" t="n">
         <v>8.029999999999999</v>
       </c>
-      <c r="E16" s="66" t="n">
+      <c r="E16" s="67" t="n">
         <v>1.21</v>
       </c>
-      <c r="F16" s="67" t="n">
+      <c r="F16" s="68" t="n">
         <v>73</v>
       </c>
-      <c r="G16" s="67" t="n">
+      <c r="G16" s="68" t="n">
         <v>115</v>
       </c>
-      <c r="H16" s="67" t="n">
+      <c r="H16" s="68" t="n">
         <v>188</v>
       </c>
-      <c r="I16" s="68" t="n">
+      <c r="I16" s="69" t="n">
         <v>-4</v>
       </c>
-      <c r="J16" s="67" t="n">
+      <c r="J16" s="68" t="n">
         <v>117</v>
       </c>
-      <c r="K16" s="67" t="n">
+      <c r="K16" s="68" t="n">
         <v>3</v>
       </c>
-      <c r="L16" s="68" t="n">
+      <c r="L16" s="69" t="n">
         <v>-3</v>
       </c>
-      <c r="M16" s="68" t="n">
+      <c r="M16" s="69" t="n">
         <v>-212</v>
       </c>
-      <c r="N16" s="67" t="n">
+      <c r="N16" s="68" t="n">
         <v>24</v>
       </c>
-      <c r="O16" s="59" t="inlineStr">
+      <c r="O16" s="60" t="inlineStr">
         <is>
           <t>동반강세</t>
         </is>
@@ -10338,43 +10343,43 @@
           <t>보험</t>
         </is>
       </c>
-      <c r="B17" s="66" t="n">
+      <c r="B17" s="67" t="n">
         <v>53.83</v>
       </c>
-      <c r="C17" s="66" t="n">
+      <c r="C17" s="67" t="n">
         <v>29.06</v>
       </c>
-      <c r="D17" s="69" t="n">
+      <c r="D17" s="70" t="n">
         <v>-8.49</v>
       </c>
-      <c r="E17" s="66" t="n">
+      <c r="E17" s="67" t="n">
         <v>0.88</v>
       </c>
-      <c r="F17" s="67" t="n">
+      <c r="F17" s="68" t="n">
         <v>61</v>
       </c>
-      <c r="G17" s="68" t="n">
+      <c r="G17" s="69" t="n">
         <v>-60</v>
       </c>
-      <c r="H17" s="71" t="n">
+      <c r="H17" s="72" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="67" t="n">
+      <c r="I17" s="68" t="n">
         <v>138</v>
       </c>
-      <c r="J17" s="68" t="n">
+      <c r="J17" s="69" t="n">
         <v>-21</v>
       </c>
-      <c r="K17" s="68" t="n">
+      <c r="K17" s="69" t="n">
         <v>-170</v>
       </c>
-      <c r="L17" s="68" t="n">
+      <c r="L17" s="69" t="n">
         <v>-7</v>
       </c>
-      <c r="M17" s="68" t="n">
+      <c r="M17" s="69" t="n">
         <v>-20</v>
       </c>
-      <c r="N17" s="67" t="n">
+      <c r="N17" s="68" t="n">
         <v>20</v>
       </c>
       <c r="O17" s="30" t="inlineStr"/>
@@ -10385,43 +10390,43 @@
           <t>유통</t>
         </is>
       </c>
-      <c r="B18" s="66" t="n">
+      <c r="B18" s="67" t="n">
         <v>23.6</v>
       </c>
-      <c r="C18" s="66" t="n">
+      <c r="C18" s="67" t="n">
         <v>7.68</v>
       </c>
-      <c r="D18" s="69" t="n">
+      <c r="D18" s="70" t="n">
         <v>-15</v>
       </c>
-      <c r="E18" s="66" t="n">
+      <c r="E18" s="67" t="n">
         <v>0.79</v>
       </c>
-      <c r="F18" s="68" t="n">
+      <c r="F18" s="69" t="n">
         <v>-18</v>
       </c>
-      <c r="G18" s="68" t="n">
+      <c r="G18" s="69" t="n">
         <v>-94</v>
       </c>
-      <c r="H18" s="68" t="n">
+      <c r="H18" s="69" t="n">
         <v>-112</v>
       </c>
-      <c r="I18" s="67" t="n">
+      <c r="I18" s="68" t="n">
         <v>103</v>
       </c>
-      <c r="J18" s="68" t="n">
+      <c r="J18" s="69" t="n">
         <v>-136</v>
       </c>
-      <c r="K18" s="68" t="n">
+      <c r="K18" s="69" t="n">
         <v>-52</v>
       </c>
-      <c r="L18" s="68" t="n">
+      <c r="L18" s="69" t="n">
         <v>-5</v>
       </c>
-      <c r="M18" s="67" t="n">
+      <c r="M18" s="68" t="n">
         <v>92</v>
       </c>
-      <c r="N18" s="67" t="n">
+      <c r="N18" s="68" t="n">
         <v>19</v>
       </c>
       <c r="O18" s="30" t="inlineStr"/>
@@ -10432,46 +10437,46 @@
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="B19" s="66" t="n">
+      <c r="B19" s="67" t="n">
         <v>5.92</v>
       </c>
-      <c r="C19" s="66" t="n">
+      <c r="C19" s="67" t="n">
         <v>4.56</v>
       </c>
-      <c r="D19" s="66" t="n">
+      <c r="D19" s="67" t="n">
         <v>2.71</v>
       </c>
-      <c r="E19" s="66" t="n">
+      <c r="E19" s="67" t="n">
         <v>0.78</v>
       </c>
-      <c r="F19" s="68" t="n">
+      <c r="F19" s="69" t="n">
         <v>-157</v>
       </c>
-      <c r="G19" s="68" t="n">
+      <c r="G19" s="69" t="n">
         <v>-20</v>
       </c>
-      <c r="H19" s="68" t="n">
+      <c r="H19" s="69" t="n">
         <v>-178</v>
       </c>
-      <c r="I19" s="67" t="n">
+      <c r="I19" s="68" t="n">
         <v>61</v>
       </c>
-      <c r="J19" s="68" t="n">
+      <c r="J19" s="69" t="n">
         <v>-61</v>
       </c>
-      <c r="K19" s="68" t="n">
+      <c r="K19" s="69" t="n">
         <v>-6</v>
       </c>
-      <c r="L19" s="68" t="n">
+      <c r="L19" s="69" t="n">
         <v>-14</v>
       </c>
-      <c r="M19" s="67" t="n">
+      <c r="M19" s="68" t="n">
         <v>146</v>
       </c>
-      <c r="N19" s="67" t="n">
+      <c r="N19" s="68" t="n">
         <v>32</v>
       </c>
-      <c r="O19" s="72" t="inlineStr">
+      <c r="O19" s="73" t="inlineStr">
         <is>
           <t>수급이탈</t>
         </is>
@@ -10483,46 +10488,46 @@
           <t>전기·가스</t>
         </is>
       </c>
-      <c r="B20" s="69" t="n">
+      <c r="B20" s="70" t="n">
         <v>-29.36</v>
       </c>
-      <c r="C20" s="69" t="n">
+      <c r="C20" s="70" t="n">
         <v>-22</v>
       </c>
-      <c r="D20" s="69" t="n">
+      <c r="D20" s="70" t="n">
         <v>-15.23</v>
       </c>
-      <c r="E20" s="66" t="n">
+      <c r="E20" s="67" t="n">
         <v>0.7</v>
       </c>
-      <c r="F20" s="68" t="n">
+      <c r="F20" s="69" t="n">
         <v>-67</v>
       </c>
-      <c r="G20" s="68" t="n">
+      <c r="G20" s="69" t="n">
         <v>-51</v>
       </c>
-      <c r="H20" s="68" t="n">
+      <c r="H20" s="69" t="n">
         <v>-118</v>
       </c>
-      <c r="I20" s="68" t="n">
+      <c r="I20" s="69" t="n">
         <v>-3</v>
       </c>
-      <c r="J20" s="67" t="n">
+      <c r="J20" s="68" t="n">
         <v>4</v>
       </c>
-      <c r="K20" s="68" t="n">
+      <c r="K20" s="69" t="n">
         <v>-51</v>
       </c>
-      <c r="L20" s="68" t="n">
+      <c r="L20" s="69" t="n">
         <v>-1</v>
       </c>
-      <c r="M20" s="67" t="n">
+      <c r="M20" s="68" t="n">
         <v>113</v>
       </c>
-      <c r="N20" s="67" t="n">
+      <c r="N20" s="68" t="n">
         <v>5</v>
       </c>
-      <c r="O20" s="60" t="inlineStr">
+      <c r="O20" s="61" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -10534,46 +10539,46 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="B21" s="66" t="n">
+      <c r="B21" s="67" t="n">
         <v>42.04</v>
       </c>
-      <c r="C21" s="66" t="n">
+      <c r="C21" s="67" t="n">
         <v>21.12</v>
       </c>
-      <c r="D21" s="69" t="n">
+      <c r="D21" s="70" t="n">
         <v>-8.58</v>
       </c>
-      <c r="E21" s="66" t="n">
+      <c r="E21" s="67" t="n">
         <v>0.47</v>
       </c>
-      <c r="F21" s="67" t="n">
+      <c r="F21" s="68" t="n">
         <v>3983</v>
       </c>
-      <c r="G21" s="67" t="n">
+      <c r="G21" s="68" t="n">
         <v>1778</v>
       </c>
-      <c r="H21" s="67" t="n">
+      <c r="H21" s="68" t="n">
         <v>5761</v>
       </c>
-      <c r="I21" s="67" t="n">
+      <c r="I21" s="68" t="n">
         <v>1893</v>
       </c>
-      <c r="J21" s="68" t="n">
+      <c r="J21" s="69" t="n">
         <v>-465</v>
       </c>
-      <c r="K21" s="67" t="n">
+      <c r="K21" s="68" t="n">
         <v>130</v>
       </c>
-      <c r="L21" s="68" t="n">
+      <c r="L21" s="69" t="n">
         <v>-79</v>
       </c>
-      <c r="M21" s="67" t="n">
+      <c r="M21" s="68" t="n">
         <v>895</v>
       </c>
-      <c r="N21" s="68" t="n">
+      <c r="N21" s="69" t="n">
         <v>-6656</v>
       </c>
-      <c r="O21" s="59" t="inlineStr">
+      <c r="O21" s="60" t="inlineStr">
         <is>
           <t>동반강세</t>
         </is>
@@ -10585,43 +10590,43 @@
           <t>종이·목재</t>
         </is>
       </c>
-      <c r="B22" s="69" t="n">
+      <c r="B22" s="70" t="n">
         <v>-22.75</v>
       </c>
-      <c r="C22" s="69" t="n">
+      <c r="C22" s="70" t="n">
         <v>-23.09</v>
       </c>
-      <c r="D22" s="69" t="n">
+      <c r="D22" s="70" t="n">
         <v>-0.16</v>
       </c>
-      <c r="E22" s="66" t="n">
+      <c r="E22" s="67" t="n">
         <v>0.38</v>
       </c>
-      <c r="F22" s="68" t="n">
+      <c r="F22" s="69" t="n">
         <v>-2</v>
       </c>
-      <c r="G22" s="67" t="n">
+      <c r="G22" s="68" t="n">
         <v>2</v>
       </c>
-      <c r="H22" s="68" t="n">
+      <c r="H22" s="69" t="n">
         <v>-1</v>
       </c>
-      <c r="I22" s="67" t="n">
+      <c r="I22" s="68" t="n">
         <v>1</v>
       </c>
-      <c r="J22" s="67" t="n">
+      <c r="J22" s="68" t="n">
         <v>1</v>
       </c>
-      <c r="K22" s="71" t="n">
+      <c r="K22" s="72" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="71" t="n">
+      <c r="L22" s="72" t="n">
         <v>0</v>
       </c>
-      <c r="M22" s="67" t="n">
+      <c r="M22" s="68" t="n">
         <v>1</v>
       </c>
-      <c r="N22" s="71" t="n">
+      <c r="N22" s="72" t="n">
         <v>0</v>
       </c>
       <c r="O22" s="30" t="inlineStr"/>
@@ -10632,46 +10637,46 @@
           <t>제약</t>
         </is>
       </c>
-      <c r="B23" s="69" t="n">
+      <c r="B23" s="70" t="n">
         <v>-15.08</v>
       </c>
-      <c r="C23" s="69" t="n">
+      <c r="C23" s="70" t="n">
         <v>-11.38</v>
       </c>
-      <c r="D23" s="69" t="n">
+      <c r="D23" s="70" t="n">
         <v>-0.23</v>
       </c>
-      <c r="E23" s="66" t="n">
+      <c r="E23" s="67" t="n">
         <v>0.35</v>
       </c>
-      <c r="F23" s="68" t="n">
+      <c r="F23" s="69" t="n">
         <v>-302</v>
       </c>
-      <c r="G23" s="67" t="n">
+      <c r="G23" s="68" t="n">
         <v>145</v>
       </c>
-      <c r="H23" s="68" t="n">
+      <c r="H23" s="69" t="n">
         <v>-157</v>
       </c>
-      <c r="I23" s="67" t="n">
+      <c r="I23" s="68" t="n">
         <v>138</v>
       </c>
-      <c r="J23" s="68" t="n">
+      <c r="J23" s="69" t="n">
         <v>-43</v>
       </c>
-      <c r="K23" s="67" t="n">
+      <c r="K23" s="68" t="n">
         <v>33</v>
       </c>
-      <c r="L23" s="67" t="n">
+      <c r="L23" s="68" t="n">
         <v>18</v>
       </c>
-      <c r="M23" s="68" t="n">
+      <c r="M23" s="69" t="n">
         <v>-44</v>
       </c>
-      <c r="N23" s="67" t="n">
+      <c r="N23" s="68" t="n">
         <v>201</v>
       </c>
-      <c r="O23" s="60" t="inlineStr">
+      <c r="O23" s="61" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -10683,43 +10688,43 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="B24" s="69" t="n">
+      <c r="B24" s="70" t="n">
         <v>-10.34</v>
       </c>
-      <c r="C24" s="69" t="n">
+      <c r="C24" s="70" t="n">
         <v>-12.79</v>
       </c>
-      <c r="D24" s="66" t="n">
+      <c r="D24" s="67" t="n">
         <v>3.41</v>
       </c>
-      <c r="E24" s="66" t="n">
+      <c r="E24" s="67" t="n">
         <v>0.29</v>
       </c>
-      <c r="F24" s="68" t="n">
+      <c r="F24" s="69" t="n">
         <v>-23</v>
       </c>
-      <c r="G24" s="67" t="n">
+      <c r="G24" s="68" t="n">
         <v>32</v>
       </c>
-      <c r="H24" s="67" t="n">
+      <c r="H24" s="68" t="n">
         <v>9</v>
       </c>
-      <c r="I24" s="67" t="n">
+      <c r="I24" s="68" t="n">
         <v>39</v>
       </c>
-      <c r="J24" s="68" t="n">
+      <c r="J24" s="69" t="n">
         <v>-11</v>
       </c>
-      <c r="K24" s="67" t="n">
+      <c r="K24" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="L24" s="68" t="n">
+      <c r="L24" s="69" t="n">
         <v>-4</v>
       </c>
-      <c r="M24" s="68" t="n">
+      <c r="M24" s="69" t="n">
         <v>-8</v>
       </c>
-      <c r="N24" s="68" t="n">
+      <c r="N24" s="69" t="n">
         <v>-1</v>
       </c>
       <c r="O24" s="30" t="inlineStr"/>
@@ -10730,46 +10735,46 @@
           <t>음식료·담배</t>
         </is>
       </c>
-      <c r="B25" s="66" t="n">
+      <c r="B25" s="67" t="n">
         <v>3.36</v>
       </c>
-      <c r="C25" s="69" t="n">
+      <c r="C25" s="70" t="n">
         <v>-0.49</v>
       </c>
-      <c r="D25" s="69" t="n">
+      <c r="D25" s="70" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E25" s="69" t="n">
+      <c r="E25" s="70" t="n">
         <v>-0.06</v>
       </c>
-      <c r="F25" s="68" t="n">
+      <c r="F25" s="69" t="n">
         <v>-317</v>
       </c>
-      <c r="G25" s="67" t="n">
+      <c r="G25" s="68" t="n">
         <v>41</v>
       </c>
-      <c r="H25" s="68" t="n">
+      <c r="H25" s="69" t="n">
         <v>-276</v>
       </c>
-      <c r="I25" s="67" t="n">
+      <c r="I25" s="68" t="n">
         <v>61</v>
       </c>
-      <c r="J25" s="68" t="n">
+      <c r="J25" s="69" t="n">
         <v>-11</v>
       </c>
-      <c r="K25" s="67" t="n">
+      <c r="K25" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="L25" s="68" t="n">
+      <c r="L25" s="69" t="n">
         <v>-22</v>
       </c>
-      <c r="M25" s="67" t="n">
+      <c r="M25" s="68" t="n">
         <v>125</v>
       </c>
-      <c r="N25" s="67" t="n">
+      <c r="N25" s="68" t="n">
         <v>150</v>
       </c>
-      <c r="O25" s="60" t="inlineStr">
+      <c r="O25" s="61" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -10781,43 +10786,43 @@
           <t>비금속</t>
         </is>
       </c>
-      <c r="B26" s="69" t="n">
+      <c r="B26" s="70" t="n">
         <v>-14.58</v>
       </c>
-      <c r="C26" s="69" t="n">
+      <c r="C26" s="70" t="n">
         <v>-14.92</v>
       </c>
-      <c r="D26" s="69" t="n">
+      <c r="D26" s="70" t="n">
         <v>-3.16</v>
       </c>
-      <c r="E26" s="69" t="n">
+      <c r="E26" s="70" t="n">
         <v>-0.18</v>
       </c>
-      <c r="F26" s="68" t="n">
+      <c r="F26" s="69" t="n">
         <v>-3</v>
       </c>
-      <c r="G26" s="71" t="n">
+      <c r="G26" s="72" t="n">
         <v>0</v>
       </c>
-      <c r="H26" s="68" t="n">
+      <c r="H26" s="69" t="n">
         <v>-3</v>
       </c>
-      <c r="I26" s="67" t="n">
+      <c r="I26" s="68" t="n">
         <v>4</v>
       </c>
-      <c r="J26" s="68" t="n">
+      <c r="J26" s="69" t="n">
         <v>-1</v>
       </c>
-      <c r="K26" s="68" t="n">
+      <c r="K26" s="69" t="n">
         <v>-3</v>
       </c>
-      <c r="L26" s="71" t="n">
+      <c r="L26" s="72" t="n">
         <v>0</v>
       </c>
-      <c r="M26" s="67" t="n">
+      <c r="M26" s="68" t="n">
         <v>3</v>
       </c>
-      <c r="N26" s="71" t="n">
+      <c r="N26" s="72" t="n">
         <v>0</v>
       </c>
       <c r="O26" s="30" t="inlineStr"/>
@@ -10828,46 +10833,46 @@
           <t>오락·문화</t>
         </is>
       </c>
-      <c r="B27" s="69" t="n">
+      <c r="B27" s="70" t="n">
         <v>-45.95</v>
       </c>
-      <c r="C27" s="69" t="n">
+      <c r="C27" s="70" t="n">
         <v>-33.87</v>
       </c>
-      <c r="D27" s="69" t="n">
+      <c r="D27" s="70" t="n">
         <v>-19.97</v>
       </c>
-      <c r="E27" s="69" t="n">
+      <c r="E27" s="70" t="n">
         <v>-0.64</v>
       </c>
-      <c r="F27" s="68" t="n">
+      <c r="F27" s="69" t="n">
         <v>-43</v>
       </c>
-      <c r="G27" s="68" t="n">
+      <c r="G27" s="69" t="n">
         <v>-46</v>
       </c>
-      <c r="H27" s="68" t="n">
+      <c r="H27" s="69" t="n">
         <v>-89</v>
       </c>
-      <c r="I27" s="67" t="n">
+      <c r="I27" s="68" t="n">
         <v>29</v>
       </c>
-      <c r="J27" s="68" t="n">
+      <c r="J27" s="69" t="n">
         <v>-10</v>
       </c>
-      <c r="K27" s="68" t="n">
+      <c r="K27" s="69" t="n">
         <v>-60</v>
       </c>
-      <c r="L27" s="68" t="n">
+      <c r="L27" s="69" t="n">
         <v>-5</v>
       </c>
-      <c r="M27" s="67" t="n">
+      <c r="M27" s="68" t="n">
         <v>91</v>
       </c>
-      <c r="N27" s="68" t="n">
+      <c r="N27" s="69" t="n">
         <v>-3</v>
       </c>
-      <c r="O27" s="60" t="inlineStr">
+      <c r="O27" s="61" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -10879,46 +10884,46 @@
           <t>건설</t>
         </is>
       </c>
-      <c r="B28" s="66" t="n">
+      <c r="B28" s="67" t="n">
         <v>64.83</v>
       </c>
-      <c r="C28" s="69" t="n">
+      <c r="C28" s="70" t="n">
         <v>-9.380000000000001</v>
       </c>
-      <c r="D28" s="69" t="n">
+      <c r="D28" s="70" t="n">
         <v>-0.09</v>
       </c>
-      <c r="E28" s="69" t="n">
+      <c r="E28" s="70" t="n">
         <v>-1.38</v>
       </c>
-      <c r="F28" s="68" t="n">
+      <c r="F28" s="69" t="n">
         <v>-31</v>
       </c>
-      <c r="G28" s="68" t="n">
+      <c r="G28" s="69" t="n">
         <v>-676</v>
       </c>
-      <c r="H28" s="68" t="n">
+      <c r="H28" s="69" t="n">
         <v>-707</v>
       </c>
-      <c r="I28" s="68" t="n">
+      <c r="I28" s="69" t="n">
         <v>-90</v>
       </c>
-      <c r="J28" s="68" t="n">
+      <c r="J28" s="69" t="n">
         <v>-310</v>
       </c>
-      <c r="K28" s="68" t="n">
+      <c r="K28" s="69" t="n">
         <v>-270</v>
       </c>
-      <c r="L28" s="68" t="n">
+      <c r="L28" s="69" t="n">
         <v>-7</v>
       </c>
-      <c r="M28" s="67" t="n">
+      <c r="M28" s="68" t="n">
         <v>698</v>
       </c>
-      <c r="N28" s="67" t="n">
+      <c r="N28" s="68" t="n">
         <v>9</v>
       </c>
-      <c r="O28" s="60" t="inlineStr">
+      <c r="O28" s="61" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -10956,7 +10961,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{32FE296A-4C74-4166-A229-BD97F399AEED}</x14:id>
+          <x14:id>{89228D8A-F7E0-4D8F-A12C-4967A4915565}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -10970,7 +10975,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{C15EC00A-50EF-486E-9711-FDEE3CB1FC08}</x14:id>
+          <x14:id>{1298C441-CCD3-4591-AF01-9EEC2CA8F408}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -10984,7 +10989,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{97ACF7F3-6B08-4C07-B0CD-E2160A255365}</x14:id>
+          <x14:id>{57AC8B92-D9A1-45FC-A602-75ED6315C21C}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -10998,7 +11003,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0AB3DABE-75A4-45F3-87F1-41C8CF7889CA}</x14:id>
+          <x14:id>{FB86D7E6-497F-4586-B6A3-F970FB3A1DC7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11008,7 +11013,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{32FE296A-4C74-4166-A229-BD97F399AEED}">
+          <x14:cfRule type="dataBar" id="{89228D8A-F7E0-4D8F-A12C-4967A4915565}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11021,7 +11026,7 @@
           <xm:sqref>B5:B28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{C15EC00A-50EF-486E-9711-FDEE3CB1FC08}">
+          <x14:cfRule type="dataBar" id="{1298C441-CCD3-4591-AF01-9EEC2CA8F408}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11034,7 +11039,7 @@
           <xm:sqref>C5:C28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{97ACF7F3-6B08-4C07-B0CD-E2160A255365}">
+          <x14:cfRule type="dataBar" id="{57AC8B92-D9A1-45FC-A602-75ED6315C21C}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11047,7 +11052,7 @@
           <xm:sqref>D5:D28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0AB3DABE-75A4-45F3-87F1-41C8CF7889CA}">
+          <x14:cfRule type="dataBar" id="{FB86D7E6-497F-4586-B6A3-F970FB3A1DC7}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/public/monthly_review.xlsx
+++ b/public/monthly_review.xlsx
@@ -321,7 +321,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -416,9 +416,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1020,7 +1017,7 @@
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>미국 종가 기준 09/30 → 10/07, %</t>
+          <t>미국 종가 기준 09/30 → 10/08, %</t>
         </is>
       </c>
       <c r="I6" s="18" t="inlineStr"/>
@@ -1090,19 +1087,19 @@
         <v>-16253</v>
       </c>
       <c r="E8" s="28" t="n">
-        <v>1.96</v>
+        <v>1.49</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>0.54</v>
+        <v>0.64</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>2.52</v>
+        <v>1.24</v>
       </c>
       <c r="H8" s="29" t="n">
-        <v>-7.71</v>
-      </c>
-      <c r="I8" s="28" t="n">
-        <v>3.46</v>
+        <v>-5.69</v>
+      </c>
+      <c r="I8" s="29" t="n">
+        <v>-0.04</v>
       </c>
     </row>
     <row r="9">
@@ -1161,7 +1158,7 @@
         </is>
       </c>
       <c r="D12" s="32" t="n">
-        <v>3.02</v>
+        <v>6.08</v>
       </c>
     </row>
     <row r="13">
@@ -1177,11 +1174,11 @@
       </c>
       <c r="C13" s="31" t="inlineStr">
         <is>
-          <t>기술</t>
+          <t>임의소비재</t>
         </is>
       </c>
       <c r="D13" s="32" t="n">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="14">
@@ -1197,11 +1194,11 @@
       </c>
       <c r="C14" s="31" t="inlineStr">
         <is>
-          <t>반도체</t>
+          <t>금융</t>
         </is>
       </c>
       <c r="D14" s="32" t="n">
-        <v>2.63</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="15">
@@ -1221,7 +1218,7 @@
         </is>
       </c>
       <c r="D15" s="33" t="n">
-        <v>-4.72</v>
+        <v>-5.32</v>
       </c>
     </row>
     <row r="16">
@@ -1237,13 +1234,11 @@
       </c>
       <c r="C16" s="31" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
-        </is>
-      </c>
-      <c r="D16" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>반도체</t>
+        </is>
+      </c>
+      <c r="D16" s="33" t="n">
+        <v>-0.28</v>
       </c>
     </row>
     <row r="17">
@@ -1259,13 +1254,11 @@
       </c>
       <c r="C17" s="31" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
-        </is>
-      </c>
-      <c r="D17" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>헬스케어</t>
+        </is>
+      </c>
+      <c r="D17" s="33" t="n">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="18">
@@ -2314,7 +2307,7 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="D53" s="35" t="inlineStr">
+      <c r="D53" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2355,7 +2348,7 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="D54" s="35" t="inlineStr">
+      <c r="D54" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2396,7 +2389,7 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="D55" s="35" t="inlineStr">
+      <c r="D55" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2437,7 +2430,7 @@
           <t>주성엔지니어링</t>
         </is>
       </c>
-      <c r="D56" s="35" t="inlineStr">
+      <c r="D56" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
@@ -2478,7 +2471,7 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="D57" s="35" t="inlineStr">
+      <c r="D57" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
@@ -2519,7 +2512,7 @@
           <t>에코프로</t>
         </is>
       </c>
-      <c r="D58" s="35" t="inlineStr">
+      <c r="D58" s="34" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
@@ -2560,7 +2553,7 @@
           <t>고영</t>
         </is>
       </c>
-      <c r="D59" s="35" t="inlineStr">
+      <c r="D59" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
@@ -2601,7 +2594,7 @@
           <t>제주반도체</t>
         </is>
       </c>
-      <c r="D60" s="35" t="inlineStr">
+      <c r="D60" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2642,7 +2635,7 @@
           <t>한화솔루션</t>
         </is>
       </c>
-      <c r="D61" s="35" t="inlineStr">
+      <c r="D61" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
@@ -2683,7 +2676,7 @@
           <t>이수페타시스</t>
         </is>
       </c>
-      <c r="D62" s="35" t="inlineStr">
+      <c r="D62" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2724,7 +2717,7 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="D63" s="35" t="inlineStr">
+      <c r="D63" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2765,7 +2758,7 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="D64" s="35" t="inlineStr">
+      <c r="D64" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2806,7 +2799,7 @@
           <t>효성중공업</t>
         </is>
       </c>
-      <c r="D65" s="35" t="inlineStr">
+      <c r="D65" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2847,7 +2840,7 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="D66" s="35" t="inlineStr">
+      <c r="D66" s="34" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
@@ -2888,7 +2881,7 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="D67" s="35" t="inlineStr">
+      <c r="D67" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
@@ -2929,7 +2922,7 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="D68" s="35" t="inlineStr">
+      <c r="D68" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
@@ -2970,7 +2963,7 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="D69" s="35" t="inlineStr">
+      <c r="D69" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
@@ -3011,7 +3004,7 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="D70" s="35" t="inlineStr">
+      <c r="D70" s="34" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
@@ -3052,7 +3045,7 @@
           <t>삼성바이오로직스</t>
         </is>
       </c>
-      <c r="D71" s="35" t="inlineStr">
+      <c r="D71" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
@@ -3093,7 +3086,7 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="D72" s="35" t="inlineStr">
+      <c r="D72" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -3147,7 +3140,7 @@
       <c r="K74" s="3" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="36" t="inlineStr">
+      <c r="A75" s="35" t="inlineStr">
         <is>
           <t>● 동반강세 — 추세 지속형 상방 관찰</t>
         </is>
@@ -3164,12 +3157,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="B76" s="35" t="inlineStr">
+      <c r="B76" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="C76" s="37" t="n">
+      <c r="C76" s="36" t="n">
         <v>1</v>
       </c>
       <c r="D76" s="31" t="inlineStr"/>
@@ -3179,12 +3172,12 @@
           <t>에스엠</t>
         </is>
       </c>
-      <c r="H76" s="35" t="inlineStr">
+      <c r="H76" s="34" t="inlineStr">
         <is>
           <t>오락·문화</t>
         </is>
       </c>
-      <c r="I76" s="38" t="n">
+      <c r="I76" s="37" t="n">
         <v>3</v>
       </c>
       <c r="J76" s="31" t="inlineStr"/>
@@ -3208,12 +3201,12 @@
           <t>에이피알</t>
         </is>
       </c>
-      <c r="B78" s="35" t="inlineStr">
+      <c r="B78" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="C78" s="37" t="n">
+      <c r="C78" s="36" t="n">
         <v>1</v>
       </c>
       <c r="D78" s="31" t="inlineStr"/>
@@ -3223,12 +3216,12 @@
           <t>하이브</t>
         </is>
       </c>
-      <c r="H78" s="35" t="inlineStr">
+      <c r="H78" s="34" t="inlineStr">
         <is>
           <t>오락·문화</t>
         </is>
       </c>
-      <c r="I78" s="38" t="n">
+      <c r="I78" s="37" t="n">
         <v>1</v>
       </c>
       <c r="J78" s="31" t="inlineStr"/>
@@ -3252,12 +3245,12 @@
           <t>LG화학</t>
         </is>
       </c>
-      <c r="B80" s="35" t="inlineStr">
+      <c r="B80" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="C80" s="37" t="n">
+      <c r="C80" s="36" t="n">
         <v>1</v>
       </c>
       <c r="D80" s="31" t="inlineStr"/>
@@ -3267,12 +3260,12 @@
           <t>파라다이스</t>
         </is>
       </c>
-      <c r="H80" s="35" t="inlineStr">
+      <c r="H80" s="34" t="inlineStr">
         <is>
           <t>오락·문화</t>
         </is>
       </c>
-      <c r="I80" s="38" t="n">
+      <c r="I80" s="37" t="n">
         <v>1</v>
       </c>
       <c r="J80" s="31" t="inlineStr"/>
@@ -3296,12 +3289,12 @@
           <t>S-Oil</t>
         </is>
       </c>
-      <c r="B82" s="35" t="inlineStr">
+      <c r="B82" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="C82" s="37" t="n">
+      <c r="C82" s="36" t="n">
         <v>1</v>
       </c>
       <c r="D82" s="31" t="inlineStr"/>
@@ -3311,12 +3304,12 @@
           <t>CJ CGV</t>
         </is>
       </c>
-      <c r="H82" s="35" t="inlineStr">
+      <c r="H82" s="34" t="inlineStr">
         <is>
           <t>오락·문화</t>
         </is>
       </c>
-      <c r="I82" s="38" t="n">
+      <c r="I82" s="37" t="n">
         <v>1</v>
       </c>
       <c r="J82" s="31" t="inlineStr"/>
@@ -3340,12 +3333,12 @@
           <t>한화솔루션</t>
         </is>
       </c>
-      <c r="B84" s="35" t="inlineStr">
+      <c r="B84" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="C84" s="37" t="n">
+      <c r="C84" s="36" t="n">
         <v>1</v>
       </c>
       <c r="D84" s="31" t="inlineStr"/>
@@ -3360,12 +3353,12 @@
     </row>
     <row r="86"/>
     <row r="87">
-      <c r="A87" s="39" t="inlineStr">
+      <c r="A87" s="38" t="inlineStr">
         <is>
           <t>● 수급이탈 — 상승 후 약화 관찰</t>
         </is>
       </c>
-      <c r="G87" s="40" t="inlineStr">
+      <c r="G87" s="39" t="inlineStr">
         <is>
           <t>● 동반약세 — 약세 지속형 하방 관찰</t>
         </is>
@@ -3377,17 +3370,17 @@
           <t>해당 섹터·조건 충족 종목 없음</t>
         </is>
       </c>
-      <c r="G88" s="41" t="inlineStr">
+      <c r="G88" s="40" t="inlineStr">
         <is>
           <t>삼성바이오로직스</t>
         </is>
       </c>
-      <c r="H88" s="35" t="inlineStr">
+      <c r="H88" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="I88" s="42" t="n">
+      <c r="I88" s="41" t="n">
         <v>-3</v>
       </c>
       <c r="J88" s="31" t="inlineStr"/>
@@ -3406,12 +3399,12 @@
           <t>카카오</t>
         </is>
       </c>
-      <c r="H90" s="35" t="inlineStr">
+      <c r="H90" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="I90" s="42" t="n">
+      <c r="I90" s="41" t="n">
         <v>-3</v>
       </c>
       <c r="J90" s="31" t="inlineStr"/>
@@ -3430,12 +3423,12 @@
           <t>에이비엘바이오</t>
         </is>
       </c>
-      <c r="H92" s="35" t="inlineStr">
+      <c r="H92" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="I92" s="42" t="n">
+      <c r="I92" s="41" t="n">
         <v>-3</v>
       </c>
       <c r="J92" s="31" t="inlineStr"/>
@@ -3454,12 +3447,12 @@
           <t>한화투자증권</t>
         </is>
       </c>
-      <c r="H94" s="35" t="inlineStr">
+      <c r="H94" s="34" t="inlineStr">
         <is>
           <t>증권</t>
         </is>
       </c>
-      <c r="I94" s="42" t="n">
+      <c r="I94" s="41" t="n">
         <v>-3</v>
       </c>
       <c r="J94" s="31" t="inlineStr"/>
@@ -3478,12 +3471,12 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="H96" s="43" t="inlineStr">
+      <c r="H96" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="I96" s="42" t="n">
+      <c r="I96" s="41" t="n">
         <v>-2</v>
       </c>
       <c r="J96" s="31" t="inlineStr"/>
@@ -3498,7 +3491,7 @@
     </row>
     <row r="98"/>
     <row r="99" ht="31" customHeight="1" s="15">
-      <c r="A99" s="44" t="inlineStr">
+      <c r="A99" s="43" t="inlineStr">
         <is>
           <t>현재 확보된 월간 리뷰 데이터 유니버스(순매수 상위 30 등재 · 공매도/대차 랭킹 · 월간 촉매 · 신호 섹터 시총 상위 10) 기준 — 전 시장 스크리닝 아님 · 관찰 우선순위이며 매매 권유 아님</t>
         </is>
@@ -3709,7 +3702,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D118" s="35" t="inlineStr">
+      <c r="D118" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
@@ -3744,7 +3737,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D119" s="35" t="inlineStr">
+      <c r="D119" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -3779,7 +3772,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D120" s="35" t="inlineStr">
+      <c r="D120" s="34" t="inlineStr">
         <is>
           <t>섬유·의류</t>
         </is>
@@ -3814,7 +3807,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D121" s="35" t="inlineStr">
+      <c r="D121" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
@@ -3849,7 +3842,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D122" s="35" t="inlineStr">
+      <c r="D122" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
@@ -3884,7 +3877,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D123" s="35" t="inlineStr">
+      <c r="D123" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
@@ -3919,7 +3912,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D124" s="35" t="inlineStr">
+      <c r="D124" s="34" t="inlineStr">
         <is>
           <t>운송·창고</t>
         </is>
@@ -3954,7 +3947,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D125" s="35" t="inlineStr">
+      <c r="D125" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
@@ -3989,7 +3982,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D126" s="35" t="inlineStr">
+      <c r="D126" s="34" t="inlineStr">
         <is>
           <t>운송·창고</t>
         </is>
@@ -4025,7 +4018,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D127" s="35" t="inlineStr">
+      <c r="D127" s="34" t="inlineStr">
         <is>
           <t>섬유·의류</t>
         </is>
@@ -4060,7 +4053,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D128" s="35" t="inlineStr">
+      <c r="D128" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
@@ -4095,7 +4088,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D129" s="35" t="inlineStr">
+      <c r="D129" s="34" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
@@ -4335,62 +4328,62 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="45" t="inlineStr">
+      <c r="A5" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B5" s="45" t="inlineStr">
+      <c r="B5" s="44" t="inlineStr">
         <is>
           <t>시장</t>
         </is>
       </c>
-      <c r="C5" s="45" t="inlineStr">
+      <c r="C5" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D5" s="45" t="inlineStr">
+      <c r="D5" s="44" t="inlineStr">
         <is>
           <t>합산</t>
         </is>
       </c>
-      <c r="E5" s="45" t="inlineStr">
+      <c r="E5" s="44" t="inlineStr">
         <is>
           <t>외인</t>
         </is>
       </c>
-      <c r="F5" s="45" t="inlineStr">
+      <c r="F5" s="44" t="inlineStr">
         <is>
           <t>기관</t>
         </is>
       </c>
-      <c r="G5" s="45" t="inlineStr">
+      <c r="G5" s="44" t="inlineStr">
         <is>
           <t>개인</t>
         </is>
       </c>
-      <c r="H5" s="45" t="inlineStr">
+      <c r="H5" s="44" t="inlineStr">
         <is>
           <t>공매도</t>
         </is>
       </c>
-      <c r="I5" s="45" t="inlineStr">
+      <c r="I5" s="44" t="inlineStr">
         <is>
           <t>대차잔고</t>
         </is>
       </c>
-      <c r="J5" s="45" t="inlineStr">
+      <c r="J5" s="44" t="inlineStr">
         <is>
           <t>대차증감</t>
         </is>
       </c>
-      <c r="K5" s="45" t="inlineStr">
+      <c r="K5" s="44" t="inlineStr">
         <is>
           <t>월간등락(%)</t>
         </is>
       </c>
-      <c r="L5" s="45" t="inlineStr">
+      <c r="L5" s="44" t="inlineStr">
         <is>
           <t>신고가대비(%)</t>
         </is>
@@ -4407,36 +4400,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="C6" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D6" s="46" t="n">
+      <c r="D6" s="45" t="n">
         <v>1589</v>
       </c>
-      <c r="E6" s="46" t="n">
+      <c r="E6" s="45" t="n">
         <v>1580</v>
       </c>
-      <c r="F6" s="46" t="n">
+      <c r="F6" s="45" t="n">
         <v>9</v>
       </c>
-      <c r="G6" s="47" t="n">
+      <c r="G6" s="46" t="n">
         <v>-1499</v>
       </c>
-      <c r="H6" s="48" t="n">
+      <c r="H6" s="47" t="n">
         <v>1255.8</v>
       </c>
-      <c r="I6" s="48" t="n">
+      <c r="I6" s="47" t="n">
         <v>19079.1</v>
       </c>
-      <c r="J6" s="49" t="n">
+      <c r="J6" s="48" t="n">
         <v>1944.9</v>
       </c>
-      <c r="K6" s="50" t="n">
+      <c r="K6" s="49" t="n">
         <v>14.19</v>
       </c>
-      <c r="L6" s="51" t="n">
+      <c r="L6" s="50" t="n">
         <v>-6.37</v>
       </c>
     </row>
@@ -4451,36 +4444,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C7" s="35" t="inlineStr">
+      <c r="C7" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D7" s="46" t="n">
+      <c r="D7" s="45" t="n">
         <v>1399</v>
       </c>
-      <c r="E7" s="46" t="n">
+      <c r="E7" s="45" t="n">
         <v>819</v>
       </c>
-      <c r="F7" s="46" t="n">
+      <c r="F7" s="45" t="n">
         <v>580</v>
       </c>
-      <c r="G7" s="47" t="n">
+      <c r="G7" s="46" t="n">
         <v>-1416</v>
       </c>
-      <c r="H7" s="48" t="n">
+      <c r="H7" s="47" t="n">
         <v>512.7</v>
       </c>
-      <c r="I7" s="48" t="n">
+      <c r="I7" s="47" t="n">
         <v>4991.6</v>
       </c>
-      <c r="J7" s="49" t="n">
+      <c r="J7" s="48" t="n">
         <v>1217.6</v>
       </c>
-      <c r="K7" s="50" t="n">
+      <c r="K7" s="49" t="n">
         <v>8.18</v>
       </c>
-      <c r="L7" s="52" t="n">
+      <c r="L7" s="51" t="n">
         <v>-1.98</v>
       </c>
     </row>
@@ -4495,36 +4488,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="C8" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D8" s="46" t="n">
+      <c r="D8" s="45" t="n">
         <v>517</v>
       </c>
-      <c r="E8" s="46" t="n">
+      <c r="E8" s="45" t="n">
         <v>1125</v>
       </c>
-      <c r="F8" s="47" t="n">
+      <c r="F8" s="46" t="n">
         <v>-607</v>
       </c>
-      <c r="G8" s="47" t="n">
+      <c r="G8" s="46" t="n">
         <v>-517</v>
       </c>
-      <c r="H8" s="48" t="n">
+      <c r="H8" s="47" t="n">
         <v>353.5</v>
       </c>
-      <c r="I8" s="48" t="n">
+      <c r="I8" s="47" t="n">
         <v>10727.2</v>
       </c>
-      <c r="J8" s="49" t="n">
+      <c r="J8" s="48" t="n">
         <v>1167.1</v>
       </c>
-      <c r="K8" s="50" t="n">
+      <c r="K8" s="49" t="n">
         <v>14.16</v>
       </c>
-      <c r="L8" s="51" t="n">
+      <c r="L8" s="50" t="n">
         <v>-5.98</v>
       </c>
     </row>
@@ -4539,36 +4532,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C9" s="35" t="inlineStr">
+      <c r="C9" s="34" t="inlineStr">
         <is>
           <t>금속</t>
         </is>
       </c>
-      <c r="D9" s="46" t="n">
+      <c r="D9" s="45" t="n">
         <v>15</v>
       </c>
-      <c r="E9" s="46" t="n">
+      <c r="E9" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="46" t="n">
+      <c r="F9" s="45" t="n">
         <v>15</v>
       </c>
-      <c r="G9" s="47" t="n">
+      <c r="G9" s="46" t="n">
         <v>-15</v>
       </c>
-      <c r="H9" s="48" t="n">
+      <c r="H9" s="47" t="n">
         <v>4.9</v>
       </c>
-      <c r="I9" s="48" t="n">
+      <c r="I9" s="47" t="n">
         <v>30.4</v>
       </c>
-      <c r="J9" s="49" t="n">
+      <c r="J9" s="48" t="n">
         <v>1.4</v>
       </c>
-      <c r="K9" s="50" t="n">
+      <c r="K9" s="49" t="n">
         <v>38.7</v>
       </c>
-      <c r="L9" s="53" t="n">
+      <c r="L9" s="52" t="n">
         <v>-4.14</v>
       </c>
     </row>
@@ -4583,36 +4576,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C10" s="35" t="inlineStr">
+      <c r="C10" s="34" t="inlineStr">
         <is>
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="D10" s="47" t="n">
+      <c r="D10" s="46" t="n">
         <v>-69</v>
       </c>
-      <c r="E10" s="46" t="n">
+      <c r="E10" s="45" t="n">
         <v>228</v>
       </c>
-      <c r="F10" s="47" t="n">
+      <c r="F10" s="46" t="n">
         <v>-297</v>
       </c>
-      <c r="G10" s="46" t="n">
+      <c r="G10" s="45" t="n">
         <v>53</v>
       </c>
-      <c r="H10" s="48" t="n">
+      <c r="H10" s="47" t="n">
         <v>55.2</v>
       </c>
-      <c r="I10" s="48" t="n">
+      <c r="I10" s="47" t="n">
         <v>1952.5</v>
       </c>
-      <c r="J10" s="54" t="n">
+      <c r="J10" s="53" t="n">
         <v>-53.9</v>
       </c>
-      <c r="K10" s="55" t="n">
+      <c r="K10" s="54" t="n">
         <v>-4.21</v>
       </c>
-      <c r="L10" s="51" t="n">
+      <c r="L10" s="50" t="n">
         <v>-6.04</v>
       </c>
     </row>
@@ -4627,36 +4620,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C11" s="35" t="inlineStr">
+      <c r="C11" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D11" s="46" t="n">
+      <c r="D11" s="45" t="n">
         <v>118</v>
       </c>
-      <c r="E11" s="46" t="n">
+      <c r="E11" s="45" t="n">
         <v>119</v>
       </c>
-      <c r="F11" s="47" t="n">
+      <c r="F11" s="46" t="n">
         <v>-1</v>
       </c>
-      <c r="G11" s="47" t="n">
+      <c r="G11" s="46" t="n">
         <v>-119</v>
       </c>
-      <c r="H11" s="48" t="n">
+      <c r="H11" s="47" t="n">
         <v>21.2</v>
       </c>
-      <c r="I11" s="48" t="n">
+      <c r="I11" s="47" t="n">
         <v>185.8</v>
       </c>
-      <c r="J11" s="49" t="n">
+      <c r="J11" s="48" t="n">
         <v>5.7</v>
       </c>
-      <c r="K11" s="50" t="n">
+      <c r="K11" s="49" t="n">
         <v>12.75</v>
       </c>
-      <c r="L11" s="51" t="n">
+      <c r="L11" s="50" t="n">
         <v>-6.21</v>
       </c>
     </row>
@@ -4671,36 +4664,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C12" s="35" t="inlineStr">
+      <c r="C12" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D12" s="46" t="n">
+      <c r="D12" s="45" t="n">
         <v>60</v>
       </c>
-      <c r="E12" s="46" t="n">
+      <c r="E12" s="45" t="n">
         <v>329</v>
       </c>
-      <c r="F12" s="47" t="n">
+      <c r="F12" s="46" t="n">
         <v>-268</v>
       </c>
-      <c r="G12" s="47" t="n">
+      <c r="G12" s="46" t="n">
         <v>-77</v>
       </c>
-      <c r="H12" s="48" t="n">
+      <c r="H12" s="47" t="n">
         <v>78.7</v>
       </c>
-      <c r="I12" s="48" t="n">
+      <c r="I12" s="47" t="n">
         <v>1091.8</v>
       </c>
-      <c r="J12" s="54" t="n">
+      <c r="J12" s="53" t="n">
         <v>-62.3</v>
       </c>
-      <c r="K12" s="50" t="n">
+      <c r="K12" s="49" t="n">
         <v>7.61</v>
       </c>
-      <c r="L12" s="51" t="n">
+      <c r="L12" s="50" t="n">
         <v>-6.55</v>
       </c>
     </row>
@@ -4715,36 +4708,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C13" s="35" t="inlineStr">
+      <c r="C13" s="34" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="D13" s="46" t="n">
+      <c r="D13" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="46" t="n">
+      <c r="E13" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="56" t="n">
+      <c r="F13" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="47" t="n">
+      <c r="G13" s="46" t="n">
         <v>-1</v>
       </c>
-      <c r="H13" s="48" t="n">
+      <c r="H13" s="47" t="n">
         <v>0.8</v>
       </c>
-      <c r="I13" s="48" t="n">
+      <c r="I13" s="47" t="n">
         <v>27.8</v>
       </c>
-      <c r="J13" s="54" t="n">
+      <c r="J13" s="53" t="n">
         <v>-0.8</v>
       </c>
-      <c r="K13" s="50" t="n">
+      <c r="K13" s="49" t="n">
         <v>26.86</v>
       </c>
-      <c r="L13" s="51" t="n">
+      <c r="L13" s="50" t="n">
         <v>-6.94</v>
       </c>
     </row>
@@ -4759,36 +4752,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C14" s="35" t="inlineStr">
+      <c r="C14" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D14" s="46" t="n">
+      <c r="D14" s="45" t="n">
         <v>590</v>
       </c>
-      <c r="E14" s="46" t="n">
+      <c r="E14" s="45" t="n">
         <v>265</v>
       </c>
-      <c r="F14" s="46" t="n">
+      <c r="F14" s="45" t="n">
         <v>325</v>
       </c>
-      <c r="G14" s="47" t="n">
+      <c r="G14" s="46" t="n">
         <v>-594</v>
       </c>
-      <c r="H14" s="48" t="n">
+      <c r="H14" s="47" t="n">
         <v>239.7</v>
       </c>
-      <c r="I14" s="48" t="n">
+      <c r="I14" s="47" t="n">
         <v>4078.4</v>
       </c>
-      <c r="J14" s="49" t="n">
+      <c r="J14" s="48" t="n">
         <v>216.8</v>
       </c>
-      <c r="K14" s="50" t="n">
+      <c r="K14" s="49" t="n">
         <v>3.95</v>
       </c>
-      <c r="L14" s="51" t="n">
+      <c r="L14" s="50" t="n">
         <v>-5.29</v>
       </c>
     </row>
@@ -4803,36 +4796,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C15" s="35" t="inlineStr">
+      <c r="C15" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D15" s="46" t="n">
+      <c r="D15" s="45" t="n">
         <v>66</v>
       </c>
-      <c r="E15" s="47" t="n">
+      <c r="E15" s="46" t="n">
         <v>-282</v>
       </c>
-      <c r="F15" s="46" t="n">
+      <c r="F15" s="45" t="n">
         <v>349</v>
       </c>
-      <c r="G15" s="47" t="n">
+      <c r="G15" s="46" t="n">
         <v>-77</v>
       </c>
-      <c r="H15" s="48" t="n">
+      <c r="H15" s="47" t="n">
         <v>311.1</v>
       </c>
-      <c r="I15" s="48" t="n">
+      <c r="I15" s="47" t="n">
         <v>2746.4</v>
       </c>
-      <c r="J15" s="49" t="n">
+      <c r="J15" s="48" t="n">
         <v>445.6</v>
       </c>
-      <c r="K15" s="50" t="n">
+      <c r="K15" s="49" t="n">
         <v>13.01</v>
       </c>
-      <c r="L15" s="51" t="n">
+      <c r="L15" s="50" t="n">
         <v>-5.26</v>
       </c>
     </row>
@@ -4847,36 +4840,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C16" s="35" t="inlineStr">
+      <c r="C16" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D16" s="46" t="n">
+      <c r="D16" s="45" t="n">
         <v>98</v>
       </c>
-      <c r="E16" s="46" t="n">
+      <c r="E16" s="45" t="n">
         <v>163</v>
       </c>
-      <c r="F16" s="47" t="n">
+      <c r="F16" s="46" t="n">
         <v>-66</v>
       </c>
-      <c r="G16" s="47" t="n">
+      <c r="G16" s="46" t="n">
         <v>-78</v>
       </c>
-      <c r="H16" s="48" t="n">
+      <c r="H16" s="47" t="n">
         <v>100.5</v>
       </c>
-      <c r="I16" s="48" t="n">
+      <c r="I16" s="47" t="n">
         <v>2828.9</v>
       </c>
-      <c r="J16" s="49" t="n">
+      <c r="J16" s="48" t="n">
         <v>357.2</v>
       </c>
-      <c r="K16" s="50" t="n">
+      <c r="K16" s="49" t="n">
         <v>18.14</v>
       </c>
-      <c r="L16" s="53" t="n">
+      <c r="L16" s="52" t="n">
         <v>-4.04</v>
       </c>
     </row>
@@ -4891,36 +4884,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C17" s="35" t="inlineStr">
+      <c r="C17" s="34" t="inlineStr">
         <is>
           <t>의료·정밀기기</t>
         </is>
       </c>
-      <c r="D17" s="46" t="n">
+      <c r="D17" s="45" t="n">
         <v>167</v>
       </c>
-      <c r="E17" s="46" t="n">
+      <c r="E17" s="45" t="n">
         <v>435</v>
       </c>
-      <c r="F17" s="47" t="n">
+      <c r="F17" s="46" t="n">
         <v>-269</v>
       </c>
-      <c r="G17" s="47" t="n">
+      <c r="G17" s="46" t="n">
         <v>-152</v>
       </c>
-      <c r="H17" s="48" t="n">
+      <c r="H17" s="47" t="n">
         <v>34</v>
       </c>
-      <c r="I17" s="48" t="n">
+      <c r="I17" s="47" t="n">
         <v>630.3</v>
       </c>
-      <c r="J17" s="49" t="n">
+      <c r="J17" s="48" t="n">
         <v>142.7</v>
       </c>
-      <c r="K17" s="50" t="n">
+      <c r="K17" s="49" t="n">
         <v>13.58</v>
       </c>
-      <c r="L17" s="51" t="n">
+      <c r="L17" s="50" t="n">
         <v>-5.21</v>
       </c>
     </row>
@@ -4935,36 +4928,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C18" s="35" t="inlineStr">
+      <c r="C18" s="34" t="inlineStr">
         <is>
           <t>의료·정밀기기</t>
         </is>
       </c>
-      <c r="D18" s="46" t="n">
+      <c r="D18" s="45" t="n">
         <v>413</v>
       </c>
-      <c r="E18" s="46" t="n">
+      <c r="E18" s="45" t="n">
         <v>133</v>
       </c>
-      <c r="F18" s="46" t="n">
+      <c r="F18" s="45" t="n">
         <v>279</v>
       </c>
-      <c r="G18" s="47" t="n">
+      <c r="G18" s="46" t="n">
         <v>-409</v>
       </c>
-      <c r="H18" s="48" t="n">
+      <c r="H18" s="47" t="n">
         <v>58.2</v>
       </c>
-      <c r="I18" s="48" t="n">
+      <c r="I18" s="47" t="n">
         <v>955.7</v>
       </c>
-      <c r="J18" s="49" t="n">
+      <c r="J18" s="48" t="n">
         <v>256</v>
       </c>
-      <c r="K18" s="50" t="n">
+      <c r="K18" s="49" t="n">
         <v>39.21</v>
       </c>
-      <c r="L18" s="51" t="n">
+      <c r="L18" s="50" t="n">
         <v>-8.94</v>
       </c>
     </row>
@@ -4979,36 +4972,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C19" s="35" t="inlineStr">
+      <c r="C19" s="34" t="inlineStr">
         <is>
           <t>음식료·담배</t>
         </is>
       </c>
-      <c r="D19" s="47" t="n">
+      <c r="D19" s="46" t="n">
         <v>-85</v>
       </c>
-      <c r="E19" s="47" t="n">
+      <c r="E19" s="46" t="n">
         <v>-60</v>
       </c>
-      <c r="F19" s="47" t="n">
+      <c r="F19" s="46" t="n">
         <v>-25</v>
       </c>
-      <c r="G19" s="47" t="n">
+      <c r="G19" s="46" t="n">
         <v>-130</v>
       </c>
-      <c r="H19" s="48" t="n">
+      <c r="H19" s="47" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="I19" s="48" t="n">
+      <c r="I19" s="47" t="n">
         <v>2581</v>
       </c>
-      <c r="J19" s="54" t="n">
+      <c r="J19" s="53" t="n">
         <v>-136.7</v>
       </c>
-      <c r="K19" s="50" t="n">
+      <c r="K19" s="49" t="n">
         <v>0.79</v>
       </c>
-      <c r="L19" s="51" t="n">
+      <c r="L19" s="50" t="n">
         <v>-8.33</v>
       </c>
     </row>
@@ -5023,36 +5016,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C20" s="35" t="inlineStr">
+      <c r="C20" s="34" t="inlineStr">
         <is>
           <t>의료·정밀기기</t>
         </is>
       </c>
-      <c r="D20" s="46" t="n">
+      <c r="D20" s="45" t="n">
         <v>103</v>
       </c>
-      <c r="E20" s="46" t="n">
+      <c r="E20" s="45" t="n">
         <v>70</v>
       </c>
-      <c r="F20" s="46" t="n">
+      <c r="F20" s="45" t="n">
         <v>34</v>
       </c>
-      <c r="G20" s="47" t="n">
+      <c r="G20" s="46" t="n">
         <v>-115</v>
       </c>
-      <c r="H20" s="48" t="n">
+      <c r="H20" s="47" t="n">
         <v>190.3</v>
       </c>
-      <c r="I20" s="48" t="n">
+      <c r="I20" s="47" t="n">
         <v>2065.1</v>
       </c>
-      <c r="J20" s="49" t="n">
+      <c r="J20" s="48" t="n">
         <v>272.8</v>
       </c>
-      <c r="K20" s="50" t="n">
+      <c r="K20" s="49" t="n">
         <v>7.8</v>
       </c>
-      <c r="L20" s="51" t="n">
+      <c r="L20" s="50" t="n">
         <v>-8.210000000000001</v>
       </c>
     </row>
@@ -5067,36 +5060,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C21" s="35" t="inlineStr">
+      <c r="C21" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D21" s="46" t="n">
+      <c r="D21" s="45" t="n">
         <v>64</v>
       </c>
-      <c r="E21" s="46" t="n">
+      <c r="E21" s="45" t="n">
         <v>21</v>
       </c>
-      <c r="F21" s="46" t="n">
+      <c r="F21" s="45" t="n">
         <v>43</v>
       </c>
-      <c r="G21" s="47" t="n">
+      <c r="G21" s="46" t="n">
         <v>-60</v>
       </c>
-      <c r="H21" s="48" t="n">
+      <c r="H21" s="47" t="n">
         <v>19.9</v>
       </c>
-      <c r="I21" s="48" t="n">
+      <c r="I21" s="47" t="n">
         <v>153.5</v>
       </c>
-      <c r="J21" s="54" t="n">
+      <c r="J21" s="53" t="n">
         <v>-4.6</v>
       </c>
-      <c r="K21" s="50" t="n">
+      <c r="K21" s="49" t="n">
         <v>8.210000000000001</v>
       </c>
-      <c r="L21" s="53" t="n">
+      <c r="L21" s="52" t="n">
         <v>-2.61</v>
       </c>
     </row>
@@ -5111,36 +5104,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C22" s="35" t="inlineStr">
+      <c r="C22" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="D22" s="46" t="n">
+      <c r="D22" s="45" t="n">
         <v>4</v>
       </c>
-      <c r="E22" s="47" t="n">
+      <c r="E22" s="46" t="n">
         <v>-1</v>
       </c>
-      <c r="F22" s="46" t="n">
+      <c r="F22" s="45" t="n">
         <v>6</v>
       </c>
-      <c r="G22" s="47" t="n">
+      <c r="G22" s="46" t="n">
         <v>-3</v>
       </c>
-      <c r="H22" s="48" t="n">
+      <c r="H22" s="47" t="n">
         <v>61.9</v>
       </c>
-      <c r="I22" s="48" t="n">
+      <c r="I22" s="47" t="n">
         <v>890.9</v>
       </c>
-      <c r="J22" s="49" t="n">
+      <c r="J22" s="48" t="n">
         <v>67.59999999999999</v>
       </c>
-      <c r="K22" s="50" t="n">
+      <c r="K22" s="49" t="n">
         <v>1.61</v>
       </c>
-      <c r="L22" s="51" t="n">
+      <c r="L22" s="50" t="n">
         <v>-7.69</v>
       </c>
     </row>
@@ -5155,36 +5148,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C23" s="35" t="inlineStr">
+      <c r="C23" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="D23" s="46" t="n">
+      <c r="D23" s="45" t="n">
         <v>220</v>
       </c>
-      <c r="E23" s="46" t="n">
+      <c r="E23" s="45" t="n">
         <v>161</v>
       </c>
-      <c r="F23" s="46" t="n">
+      <c r="F23" s="45" t="n">
         <v>58</v>
       </c>
-      <c r="G23" s="47" t="n">
+      <c r="G23" s="46" t="n">
         <v>-217</v>
       </c>
-      <c r="H23" s="48" t="n">
+      <c r="H23" s="47" t="n">
         <v>64.59999999999999</v>
       </c>
-      <c r="I23" s="48" t="n">
+      <c r="I23" s="47" t="n">
         <v>913.4</v>
       </c>
-      <c r="J23" s="49" t="n">
+      <c r="J23" s="48" t="n">
         <v>127.6</v>
       </c>
-      <c r="K23" s="50" t="n">
+      <c r="K23" s="49" t="n">
         <v>7.04</v>
       </c>
-      <c r="L23" s="51" t="n">
+      <c r="L23" s="50" t="n">
         <v>-6.59</v>
       </c>
     </row>
@@ -5199,36 +5192,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C24" s="35" t="inlineStr">
+      <c r="C24" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D24" s="46" t="n">
+      <c r="D24" s="45" t="n">
         <v>25</v>
       </c>
-      <c r="E24" s="46" t="n">
+      <c r="E24" s="45" t="n">
         <v>17</v>
       </c>
-      <c r="F24" s="46" t="n">
+      <c r="F24" s="45" t="n">
         <v>8</v>
       </c>
-      <c r="G24" s="47" t="n">
+      <c r="G24" s="46" t="n">
         <v>-24</v>
       </c>
-      <c r="H24" s="48" t="n">
+      <c r="H24" s="47" t="n">
         <v>0.9</v>
       </c>
-      <c r="I24" s="48" t="n">
+      <c r="I24" s="47" t="n">
         <v>31.7</v>
       </c>
-      <c r="J24" s="54" t="n">
+      <c r="J24" s="53" t="n">
         <v>-1.8</v>
       </c>
-      <c r="K24" s="50" t="n">
+      <c r="K24" s="49" t="n">
         <v>25.93</v>
       </c>
-      <c r="L24" s="51" t="n">
+      <c r="L24" s="50" t="n">
         <v>-5.45</v>
       </c>
     </row>
@@ -5243,36 +5236,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C25" s="35" t="inlineStr">
+      <c r="C25" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D25" s="47" t="n">
+      <c r="D25" s="46" t="n">
         <v>-19</v>
       </c>
-      <c r="E25" s="47" t="n">
+      <c r="E25" s="46" t="n">
         <v>-10</v>
       </c>
-      <c r="F25" s="47" t="n">
+      <c r="F25" s="46" t="n">
         <v>-9</v>
       </c>
-      <c r="G25" s="46" t="n">
+      <c r="G25" s="45" t="n">
         <v>17</v>
       </c>
-      <c r="H25" s="48" t="n">
+      <c r="H25" s="47" t="n">
         <v>6.6</v>
       </c>
-      <c r="I25" s="48" t="n">
+      <c r="I25" s="47" t="n">
         <v>49</v>
       </c>
-      <c r="J25" s="49" t="n">
+      <c r="J25" s="48" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="K25" s="50" t="n">
+      <c r="K25" s="49" t="n">
         <v>24.84</v>
       </c>
-      <c r="L25" s="52" t="n">
+      <c r="L25" s="51" t="n">
         <v>-1.92</v>
       </c>
     </row>
@@ -5287,36 +5280,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C26" s="35" t="inlineStr">
+      <c r="C26" s="34" t="inlineStr">
         <is>
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="D26" s="46" t="n">
+      <c r="D26" s="45" t="n">
         <v>134</v>
       </c>
-      <c r="E26" s="46" t="n">
+      <c r="E26" s="45" t="n">
         <v>44</v>
       </c>
-      <c r="F26" s="46" t="n">
+      <c r="F26" s="45" t="n">
         <v>90</v>
       </c>
-      <c r="G26" s="47" t="n">
+      <c r="G26" s="46" t="n">
         <v>-129</v>
       </c>
-      <c r="H26" s="48" t="n">
+      <c r="H26" s="47" t="n">
         <v>33.7</v>
       </c>
-      <c r="I26" s="48" t="n">
+      <c r="I26" s="47" t="n">
         <v>1296.7</v>
       </c>
-      <c r="J26" s="49" t="n">
+      <c r="J26" s="48" t="n">
         <v>70.2</v>
       </c>
-      <c r="K26" s="50" t="n">
+      <c r="K26" s="49" t="n">
         <v>4.87</v>
       </c>
-      <c r="L26" s="51" t="n">
+      <c r="L26" s="50" t="n">
         <v>-9.09</v>
       </c>
     </row>
@@ -5331,36 +5324,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C27" s="35" t="inlineStr">
+      <c r="C27" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D27" s="47" t="n">
+      <c r="D27" s="46" t="n">
         <v>-10</v>
       </c>
-      <c r="E27" s="47" t="n">
+      <c r="E27" s="46" t="n">
         <v>-7</v>
       </c>
-      <c r="F27" s="47" t="n">
+      <c r="F27" s="46" t="n">
         <v>-3</v>
       </c>
-      <c r="G27" s="46" t="n">
+      <c r="G27" s="45" t="n">
         <v>10</v>
       </c>
-      <c r="H27" s="48" t="n">
+      <c r="H27" s="47" t="n">
         <v>5.3</v>
       </c>
-      <c r="I27" s="48" t="n">
+      <c r="I27" s="47" t="n">
         <v>52.3</v>
       </c>
-      <c r="J27" s="54" t="n">
+      <c r="J27" s="53" t="n">
         <v>-1.6</v>
       </c>
-      <c r="K27" s="55" t="n">
+      <c r="K27" s="54" t="n">
         <v>-1.34</v>
       </c>
-      <c r="L27" s="51" t="n">
+      <c r="L27" s="50" t="n">
         <v>-7.37</v>
       </c>
     </row>
@@ -5375,36 +5368,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C28" s="35" t="inlineStr">
+      <c r="C28" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D28" s="46" t="n">
+      <c r="D28" s="45" t="n">
         <v>83</v>
       </c>
-      <c r="E28" s="46" t="n">
+      <c r="E28" s="45" t="n">
         <v>87</v>
       </c>
-      <c r="F28" s="47" t="n">
+      <c r="F28" s="46" t="n">
         <v>-4</v>
       </c>
-      <c r="G28" s="47" t="n">
+      <c r="G28" s="46" t="n">
         <v>-67</v>
       </c>
-      <c r="H28" s="48" t="n">
+      <c r="H28" s="47" t="n">
         <v>22.1</v>
       </c>
-      <c r="I28" s="48" t="n">
+      <c r="I28" s="47" t="n">
         <v>278.2</v>
       </c>
-      <c r="J28" s="49" t="n">
+      <c r="J28" s="48" t="n">
         <v>17.6</v>
       </c>
-      <c r="K28" s="50" t="n">
+      <c r="K28" s="49" t="n">
         <v>13.27</v>
       </c>
-      <c r="L28" s="51" t="n">
+      <c r="L28" s="50" t="n">
         <v>-6.5</v>
       </c>
     </row>
@@ -5419,36 +5412,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C29" s="35" t="inlineStr">
+      <c r="C29" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D29" s="46" t="n">
+      <c r="D29" s="45" t="n">
         <v>35</v>
       </c>
-      <c r="E29" s="47" t="n">
+      <c r="E29" s="46" t="n">
         <v>-32</v>
       </c>
-      <c r="F29" s="46" t="n">
+      <c r="F29" s="45" t="n">
         <v>66</v>
       </c>
-      <c r="G29" s="47" t="n">
+      <c r="G29" s="46" t="n">
         <v>-38</v>
       </c>
-      <c r="H29" s="48" t="n">
+      <c r="H29" s="47" t="n">
         <v>6</v>
       </c>
-      <c r="I29" s="48" t="n">
+      <c r="I29" s="47" t="n">
         <v>169</v>
       </c>
-      <c r="J29" s="54" t="n">
+      <c r="J29" s="53" t="n">
         <v>-20</v>
       </c>
-      <c r="K29" s="50" t="n">
+      <c r="K29" s="49" t="n">
         <v>5.38</v>
       </c>
-      <c r="L29" s="51" t="n">
+      <c r="L29" s="50" t="n">
         <v>-6.96</v>
       </c>
     </row>
@@ -5463,36 +5456,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C30" s="35" t="inlineStr">
+      <c r="C30" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D30" s="46" t="n">
+      <c r="D30" s="45" t="n">
         <v>30</v>
       </c>
-      <c r="E30" s="47" t="n">
+      <c r="E30" s="46" t="n">
         <v>-26</v>
       </c>
-      <c r="F30" s="46" t="n">
+      <c r="F30" s="45" t="n">
         <v>55</v>
       </c>
-      <c r="G30" s="47" t="n">
+      <c r="G30" s="46" t="n">
         <v>-30</v>
       </c>
-      <c r="H30" s="48" t="n">
+      <c r="H30" s="47" t="n">
         <v>28.5</v>
       </c>
-      <c r="I30" s="48" t="n">
+      <c r="I30" s="47" t="n">
         <v>388.3</v>
       </c>
-      <c r="J30" s="49" t="n">
+      <c r="J30" s="48" t="n">
         <v>78.7</v>
       </c>
-      <c r="K30" s="50" t="n">
+      <c r="K30" s="49" t="n">
         <v>5.64</v>
       </c>
-      <c r="L30" s="51" t="n">
+      <c r="L30" s="50" t="n">
         <v>-7.18</v>
       </c>
     </row>
@@ -5507,36 +5500,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C31" s="35" t="inlineStr">
+      <c r="C31" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="D31" s="46" t="n">
+      <c r="D31" s="45" t="n">
         <v>68</v>
       </c>
-      <c r="E31" s="46" t="n">
+      <c r="E31" s="45" t="n">
         <v>24</v>
       </c>
-      <c r="F31" s="46" t="n">
+      <c r="F31" s="45" t="n">
         <v>43</v>
       </c>
-      <c r="G31" s="47" t="n">
+      <c r="G31" s="46" t="n">
         <v>-64</v>
       </c>
-      <c r="H31" s="48" t="n">
+      <c r="H31" s="47" t="n">
         <v>5.5</v>
       </c>
-      <c r="I31" s="48" t="n">
+      <c r="I31" s="47" t="n">
         <v>36.5</v>
       </c>
-      <c r="J31" s="49" t="n">
+      <c r="J31" s="48" t="n">
         <v>2.6</v>
       </c>
-      <c r="K31" s="50" t="n">
+      <c r="K31" s="49" t="n">
         <v>13.56</v>
       </c>
-      <c r="L31" s="53" t="n">
+      <c r="L31" s="52" t="n">
         <v>-3.9</v>
       </c>
     </row>
@@ -5551,36 +5544,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C32" s="35" t="inlineStr">
+      <c r="C32" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D32" s="46" t="n">
+      <c r="D32" s="45" t="n">
         <v>65</v>
       </c>
-      <c r="E32" s="47" t="n">
+      <c r="E32" s="46" t="n">
         <v>-12</v>
       </c>
-      <c r="F32" s="46" t="n">
+      <c r="F32" s="45" t="n">
         <v>77</v>
       </c>
-      <c r="G32" s="47" t="n">
+      <c r="G32" s="46" t="n">
         <v>-61</v>
       </c>
-      <c r="H32" s="48" t="n">
+      <c r="H32" s="47" t="n">
         <v>12.4</v>
       </c>
-      <c r="I32" s="48" t="n">
+      <c r="I32" s="47" t="n">
         <v>587.3</v>
       </c>
-      <c r="J32" s="49" t="n">
+      <c r="J32" s="48" t="n">
         <v>11.9</v>
       </c>
-      <c r="K32" s="50" t="n">
+      <c r="K32" s="49" t="n">
         <v>3.92</v>
       </c>
-      <c r="L32" s="53" t="n">
+      <c r="L32" s="52" t="n">
         <v>-4.48</v>
       </c>
     </row>
@@ -5595,36 +5588,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C33" s="35" t="inlineStr">
+      <c r="C33" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="D33" s="46" t="n">
+      <c r="D33" s="45" t="n">
         <v>21</v>
       </c>
-      <c r="E33" s="46" t="n">
+      <c r="E33" s="45" t="n">
         <v>27</v>
       </c>
-      <c r="F33" s="47" t="n">
+      <c r="F33" s="46" t="n">
         <v>-6</v>
       </c>
-      <c r="G33" s="47" t="n">
+      <c r="G33" s="46" t="n">
         <v>-22</v>
       </c>
-      <c r="H33" s="48" t="n">
+      <c r="H33" s="47" t="n">
         <v>10.4</v>
       </c>
-      <c r="I33" s="48" t="n">
+      <c r="I33" s="47" t="n">
         <v>312.5</v>
       </c>
-      <c r="J33" s="49" t="n">
+      <c r="J33" s="48" t="n">
         <v>72.3</v>
       </c>
-      <c r="K33" s="50" t="n">
+      <c r="K33" s="49" t="n">
         <v>16.94</v>
       </c>
-      <c r="L33" s="52" t="n">
+      <c r="L33" s="51" t="n">
         <v>-0.7</v>
       </c>
     </row>
@@ -5639,36 +5632,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C34" s="35" t="inlineStr">
+      <c r="C34" s="34" t="inlineStr">
         <is>
           <t>보험</t>
         </is>
       </c>
-      <c r="D34" s="47" t="n">
+      <c r="D34" s="46" t="n">
         <v>-20</v>
       </c>
-      <c r="E34" s="47" t="n">
+      <c r="E34" s="46" t="n">
         <v>-28</v>
       </c>
-      <c r="F34" s="46" t="n">
+      <c r="F34" s="45" t="n">
         <v>8</v>
       </c>
-      <c r="G34" s="46" t="n">
+      <c r="G34" s="45" t="n">
         <v>6</v>
       </c>
-      <c r="H34" s="48" t="n">
+      <c r="H34" s="47" t="n">
         <v>10.3</v>
       </c>
-      <c r="I34" s="48" t="n">
+      <c r="I34" s="47" t="n">
         <v>810.5</v>
       </c>
-      <c r="J34" s="49" t="n">
+      <c r="J34" s="48" t="n">
         <v>1.7</v>
       </c>
-      <c r="K34" s="55" t="n">
+      <c r="K34" s="54" t="n">
         <v>-0.75</v>
       </c>
-      <c r="L34" s="51" t="n">
+      <c r="L34" s="50" t="n">
         <v>-7.7</v>
       </c>
     </row>
@@ -5683,36 +5676,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C35" s="35" t="inlineStr">
+      <c r="C35" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D35" s="46" t="n">
+      <c r="D35" s="45" t="n">
         <v>115</v>
       </c>
-      <c r="E35" s="46" t="n">
+      <c r="E35" s="45" t="n">
         <v>33</v>
       </c>
-      <c r="F35" s="46" t="n">
+      <c r="F35" s="45" t="n">
         <v>82</v>
       </c>
-      <c r="G35" s="47" t="n">
+      <c r="G35" s="46" t="n">
         <v>-116</v>
       </c>
-      <c r="H35" s="48" t="n">
+      <c r="H35" s="47" t="n">
         <v>6</v>
       </c>
-      <c r="I35" s="48" t="n">
+      <c r="I35" s="47" t="n">
         <v>201.3</v>
       </c>
-      <c r="J35" s="49" t="n">
+      <c r="J35" s="48" t="n">
         <v>30.8</v>
       </c>
-      <c r="K35" s="50" t="n">
+      <c r="K35" s="49" t="n">
         <v>14.12</v>
       </c>
-      <c r="L35" s="51" t="n">
+      <c r="L35" s="50" t="n">
         <v>-8.949999999999999</v>
       </c>
     </row>
@@ -5790,7 +5783,7 @@
           <t>F1 외국인</t>
         </is>
       </c>
-      <c r="E3" s="57" t="inlineStr">
+      <c r="E3" s="56" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
@@ -5800,111 +5793,111 @@
           <t>F2 기관계</t>
         </is>
       </c>
-      <c r="N3" s="57" t="inlineStr">
+      <c r="N3" s="56" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="58" t="inlineStr">
+      <c r="A4" s="57" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="E4" s="59" t="inlineStr">
+      <c r="E4" s="58" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="J4" s="58" t="inlineStr">
+      <c r="J4" s="57" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="N4" s="59" t="inlineStr">
+      <c r="N4" s="58" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="45" t="inlineStr">
+      <c r="A5" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B5" s="45" t="inlineStr">
+      <c r="B5" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C5" s="45" t="inlineStr">
+      <c r="C5" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D5" s="45" t="inlineStr">
+      <c r="D5" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E5" s="45" t="inlineStr">
+      <c r="E5" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F5" s="45" t="inlineStr">
+      <c r="F5" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G5" s="45" t="inlineStr">
+      <c r="G5" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H5" s="45" t="inlineStr">
+      <c r="H5" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="J5" s="45" t="inlineStr">
+      <c r="J5" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="K5" s="45" t="inlineStr">
+      <c r="K5" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="L5" s="45" t="inlineStr">
+      <c r="L5" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="M5" s="45" t="inlineStr">
+      <c r="M5" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="N5" s="45" t="inlineStr">
+      <c r="N5" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O5" s="45" t="inlineStr">
+      <c r="O5" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P5" s="45" t="inlineStr">
+      <c r="P5" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q5" s="45" t="inlineStr">
+      <c r="Q5" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -5919,12 +5912,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="C6" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D6" s="47" t="n">
+      <c r="D6" s="46" t="n">
         <v>3135</v>
       </c>
       <c r="E6" s="30" t="n">
@@ -5935,12 +5928,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="G6" s="35" t="inlineStr">
+      <c r="G6" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H6" s="60" t="n">
+      <c r="H6" s="59" t="n">
         <v>-40638</v>
       </c>
       <c r="J6" s="30" t="n">
@@ -5951,12 +5944,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="L6" s="35" t="inlineStr">
+      <c r="L6" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="M6" s="47" t="n">
+      <c r="M6" s="46" t="n">
         <v>3029</v>
       </c>
       <c r="N6" s="30" t="n">
@@ -5967,12 +5960,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="P6" s="35" t="inlineStr">
+      <c r="P6" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q6" s="60" t="n">
+      <c r="Q6" s="59" t="n">
         <v>-11560</v>
       </c>
     </row>
@@ -5985,12 +5978,12 @@
           <t>주성엔지니어링</t>
         </is>
       </c>
-      <c r="C7" s="35" t="inlineStr">
+      <c r="C7" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D7" s="47" t="n">
+      <c r="D7" s="46" t="n">
         <v>1738</v>
       </c>
       <c r="E7" s="30" t="n">
@@ -6001,12 +5994,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="G7" s="35" t="inlineStr">
+      <c r="G7" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H7" s="60" t="n">
+      <c r="H7" s="59" t="n">
         <v>-11910</v>
       </c>
       <c r="J7" s="30" t="n">
@@ -6017,12 +6010,12 @@
           <t>리노공업</t>
         </is>
       </c>
-      <c r="L7" s="35" t="inlineStr">
+      <c r="L7" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M7" s="47" t="n">
+      <c r="M7" s="46" t="n">
         <v>1656</v>
       </c>
       <c r="N7" s="30" t="n">
@@ -6033,12 +6026,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="P7" s="35" t="inlineStr">
+      <c r="P7" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q7" s="60" t="n">
+      <c r="Q7" s="59" t="n">
         <v>-2845</v>
       </c>
     </row>
@@ -6051,12 +6044,12 @@
           <t>이수페타시스</t>
         </is>
       </c>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="C8" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D8" s="47" t="n">
+      <c r="D8" s="46" t="n">
         <v>1101</v>
       </c>
       <c r="E8" s="30" t="n">
@@ -6067,12 +6060,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="G8" s="35" t="inlineStr">
+      <c r="G8" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="H8" s="60" t="n">
+      <c r="H8" s="59" t="n">
         <v>-4836</v>
       </c>
       <c r="J8" s="30" t="n">
@@ -6083,12 +6076,12 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="L8" s="35" t="inlineStr">
+      <c r="L8" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M8" s="47" t="n">
+      <c r="M8" s="46" t="n">
         <v>1632</v>
       </c>
       <c r="N8" s="30" t="n">
@@ -6099,12 +6092,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="P8" s="35" t="inlineStr">
+      <c r="P8" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q8" s="60" t="n">
+      <c r="Q8" s="59" t="n">
         <v>-1629</v>
       </c>
     </row>
@@ -6117,12 +6110,12 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="C9" s="35" t="inlineStr">
+      <c r="C9" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D9" s="47" t="n">
+      <c r="D9" s="46" t="n">
         <v>932</v>
       </c>
       <c r="E9" s="30" t="n">
@@ -6133,12 +6126,12 @@
           <t>효성중공업</t>
         </is>
       </c>
-      <c r="G9" s="35" t="inlineStr">
+      <c r="G9" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H9" s="60" t="n">
+      <c r="H9" s="59" t="n">
         <v>-2585</v>
       </c>
       <c r="J9" s="30" t="n">
@@ -6149,12 +6142,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="L9" s="35" t="inlineStr">
+      <c r="L9" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M9" s="47" t="n">
+      <c r="M9" s="46" t="n">
         <v>1294</v>
       </c>
       <c r="N9" s="30" t="n">
@@ -6165,12 +6158,12 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="P9" s="43" t="inlineStr">
+      <c r="P9" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q9" s="60" t="n">
+      <c r="Q9" s="59" t="n">
         <v>-1244</v>
       </c>
     </row>
@@ -6183,12 +6176,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="C10" s="35" t="inlineStr">
+      <c r="C10" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D10" s="47" t="n">
+      <c r="D10" s="46" t="n">
         <v>908</v>
       </c>
       <c r="E10" s="30" t="n">
@@ -6199,12 +6192,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="G10" s="35" t="inlineStr">
+      <c r="G10" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H10" s="60" t="n">
+      <c r="H10" s="59" t="n">
         <v>-2196</v>
       </c>
       <c r="J10" s="30" t="n">
@@ -6215,12 +6208,12 @@
           <t>대덕전자</t>
         </is>
       </c>
-      <c r="L10" s="35" t="inlineStr">
+      <c r="L10" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M10" s="47" t="n">
+      <c r="M10" s="46" t="n">
         <v>812</v>
       </c>
       <c r="N10" s="30" t="n">
@@ -6231,12 +6224,12 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="P10" s="43" t="inlineStr">
+      <c r="P10" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q10" s="60" t="n">
+      <c r="Q10" s="59" t="n">
         <v>-846</v>
       </c>
     </row>
@@ -6249,12 +6242,12 @@
           <t>심텍</t>
         </is>
       </c>
-      <c r="C11" s="35" t="inlineStr">
+      <c r="C11" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D11" s="47" t="n">
+      <c r="D11" s="46" t="n">
         <v>679</v>
       </c>
       <c r="E11" s="30" t="n">
@@ -6265,12 +6258,12 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="G11" s="35" t="inlineStr">
+      <c r="G11" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H11" s="60" t="n">
+      <c r="H11" s="59" t="n">
         <v>-1885</v>
       </c>
       <c r="J11" s="30" t="n">
@@ -6281,12 +6274,12 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="L11" s="35" t="inlineStr">
+      <c r="L11" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M11" s="47" t="n">
+      <c r="M11" s="46" t="n">
         <v>752</v>
       </c>
       <c r="N11" s="30" t="n">
@@ -6297,12 +6290,12 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="P11" s="35" t="inlineStr">
+      <c r="P11" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="Q11" s="60" t="n">
+      <c r="Q11" s="59" t="n">
         <v>-830</v>
       </c>
     </row>
@@ -6315,12 +6308,12 @@
           <t>이오테크닉스</t>
         </is>
       </c>
-      <c r="C12" s="35" t="inlineStr">
+      <c r="C12" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D12" s="47" t="n">
+      <c r="D12" s="46" t="n">
         <v>625</v>
       </c>
       <c r="E12" s="30" t="n">
@@ -6331,12 +6324,12 @@
           <t>리노공업</t>
         </is>
       </c>
-      <c r="G12" s="35" t="inlineStr">
+      <c r="G12" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H12" s="60" t="n">
+      <c r="H12" s="59" t="n">
         <v>-1568</v>
       </c>
       <c r="J12" s="30" t="n">
@@ -6347,12 +6340,12 @@
           <t>한화시스템</t>
         </is>
       </c>
-      <c r="L12" s="35" t="inlineStr">
+      <c r="L12" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M12" s="47" t="n">
+      <c r="M12" s="46" t="n">
         <v>730</v>
       </c>
       <c r="N12" s="30" t="n">
@@ -6363,12 +6356,12 @@
           <t>HD건설기계</t>
         </is>
       </c>
-      <c r="P12" s="35" t="inlineStr">
+      <c r="P12" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q12" s="60" t="n">
+      <c r="Q12" s="59" t="n">
         <v>-776</v>
       </c>
     </row>
@@ -6381,12 +6374,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="C13" s="35" t="inlineStr">
+      <c r="C13" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D13" s="47" t="n">
+      <c r="D13" s="46" t="n">
         <v>600</v>
       </c>
       <c r="E13" s="30" t="n">
@@ -6397,12 +6390,12 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="G13" s="43" t="inlineStr">
+      <c r="G13" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H13" s="60" t="n">
+      <c r="H13" s="59" t="n">
         <v>-1346</v>
       </c>
       <c r="J13" s="30" t="n">
@@ -6413,12 +6406,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="L13" s="35" t="inlineStr">
+      <c r="L13" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="M13" s="47" t="n">
+      <c r="M13" s="46" t="n">
         <v>602</v>
       </c>
       <c r="N13" s="30" t="n">
@@ -6429,12 +6422,12 @@
           <t>LS</t>
         </is>
       </c>
-      <c r="P13" s="35" t="inlineStr">
+      <c r="P13" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="Q13" s="60" t="n">
+      <c r="Q13" s="59" t="n">
         <v>-749</v>
       </c>
     </row>
@@ -6447,12 +6440,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="C14" s="35" t="inlineStr">
+      <c r="C14" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D14" s="47" t="n">
+      <c r="D14" s="46" t="n">
         <v>566</v>
       </c>
       <c r="E14" s="30" t="n">
@@ -6463,12 +6456,12 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="G14" s="35" t="inlineStr">
+      <c r="G14" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="H14" s="60" t="n">
+      <c r="H14" s="59" t="n">
         <v>-1341</v>
       </c>
       <c r="J14" s="30" t="n">
@@ -6479,12 +6472,12 @@
           <t>LG이노텍</t>
         </is>
       </c>
-      <c r="L14" s="35" t="inlineStr">
+      <c r="L14" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M14" s="47" t="n">
+      <c r="M14" s="46" t="n">
         <v>535</v>
       </c>
       <c r="N14" s="30" t="n">
@@ -6495,12 +6488,12 @@
           <t>HD현대중공업</t>
         </is>
       </c>
-      <c r="P14" s="43" t="inlineStr">
+      <c r="P14" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q14" s="60" t="n">
+      <c r="Q14" s="59" t="n">
         <v>-739</v>
       </c>
     </row>
@@ -6513,12 +6506,12 @@
           <t>DB하이텍</t>
         </is>
       </c>
-      <c r="C15" s="35" t="inlineStr">
+      <c r="C15" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D15" s="47" t="n">
+      <c r="D15" s="46" t="n">
         <v>553</v>
       </c>
       <c r="E15" s="30" t="n">
@@ -6529,12 +6522,12 @@
           <t>삼성바이오로직스</t>
         </is>
       </c>
-      <c r="G15" s="35" t="inlineStr">
+      <c r="G15" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="H15" s="60" t="n">
+      <c r="H15" s="59" t="n">
         <v>-1155</v>
       </c>
       <c r="J15" s="30" t="n">
@@ -6545,12 +6538,12 @@
           <t>NC</t>
         </is>
       </c>
-      <c r="L15" s="35" t="inlineStr">
+      <c r="L15" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="M15" s="47" t="n">
+      <c r="M15" s="46" t="n">
         <v>507</v>
       </c>
       <c r="N15" s="30" t="n">
@@ -6561,12 +6554,12 @@
           <t>DB하이텍</t>
         </is>
       </c>
-      <c r="P15" s="35" t="inlineStr">
+      <c r="P15" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q15" s="60" t="n">
+      <c r="Q15" s="59" t="n">
         <v>-682</v>
       </c>
     </row>
@@ -6577,7 +6570,7 @@
           <t>F3 외인+기관</t>
         </is>
       </c>
-      <c r="E17" s="57" t="inlineStr">
+      <c r="E17" s="56" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
@@ -6587,111 +6580,111 @@
           <t>F4 개인</t>
         </is>
       </c>
-      <c r="N17" s="57" t="inlineStr">
+      <c r="N17" s="56" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="58" t="inlineStr">
+      <c r="A18" s="57" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="E18" s="59" t="inlineStr">
+      <c r="E18" s="58" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="J18" s="58" t="inlineStr">
+      <c r="J18" s="57" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="N18" s="59" t="inlineStr">
+      <c r="N18" s="58" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="45" t="inlineStr">
+      <c r="A19" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B19" s="45" t="inlineStr">
+      <c r="B19" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C19" s="45" t="inlineStr">
+      <c r="C19" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D19" s="45" t="inlineStr">
+      <c r="D19" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E19" s="45" t="inlineStr">
+      <c r="E19" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F19" s="45" t="inlineStr">
+      <c r="F19" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G19" s="45" t="inlineStr">
+      <c r="G19" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H19" s="45" t="inlineStr">
+      <c r="H19" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="J19" s="45" t="inlineStr">
+      <c r="J19" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="K19" s="45" t="inlineStr">
+      <c r="K19" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="L19" s="45" t="inlineStr">
+      <c r="L19" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="M19" s="45" t="inlineStr">
+      <c r="M19" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="N19" s="45" t="inlineStr">
+      <c r="N19" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O19" s="45" t="inlineStr">
+      <c r="O19" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P19" s="45" t="inlineStr">
+      <c r="P19" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q19" s="45" t="inlineStr">
+      <c r="Q19" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -6706,12 +6699,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="C20" s="35" t="inlineStr">
+      <c r="C20" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D20" s="47" t="n">
+      <c r="D20" s="46" t="n">
         <v>2790</v>
       </c>
       <c r="E20" s="30" t="n">
@@ -6722,12 +6715,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="G20" s="35" t="inlineStr">
+      <c r="G20" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H20" s="60" t="n">
+      <c r="H20" s="59" t="n">
         <v>-43484</v>
       </c>
       <c r="J20" s="30" t="n">
@@ -6738,12 +6731,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="L20" s="35" t="inlineStr">
+      <c r="L20" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M20" s="47" t="n">
+      <c r="M20" s="46" t="n">
         <v>9614</v>
       </c>
       <c r="N20" s="30" t="n">
@@ -6754,12 +6747,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="P20" s="35" t="inlineStr">
+      <c r="P20" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q20" s="60" t="n">
+      <c r="Q20" s="59" t="n">
         <v>-2942</v>
       </c>
     </row>
@@ -6772,12 +6765,12 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="C21" s="35" t="inlineStr">
+      <c r="C21" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D21" s="47" t="n">
+      <c r="D21" s="46" t="n">
         <v>2564</v>
       </c>
       <c r="E21" s="30" t="n">
@@ -6788,12 +6781,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="G21" s="35" t="inlineStr">
+      <c r="G21" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H21" s="60" t="n">
+      <c r="H21" s="59" t="n">
         <v>-23470</v>
       </c>
       <c r="J21" s="30" t="n">
@@ -6804,12 +6797,12 @@
           <t>효성중공업</t>
         </is>
       </c>
-      <c r="L21" s="35" t="inlineStr">
+      <c r="L21" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M21" s="47" t="n">
+      <c r="M21" s="46" t="n">
         <v>3244</v>
       </c>
       <c r="N21" s="30" t="n">
@@ -6820,12 +6813,12 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="P21" s="35" t="inlineStr">
+      <c r="P21" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q21" s="60" t="n">
+      <c r="Q21" s="59" t="n">
         <v>-2573</v>
       </c>
     </row>
@@ -6838,12 +6831,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="C22" s="35" t="inlineStr">
+      <c r="C22" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D22" s="47" t="n">
+      <c r="D22" s="46" t="n">
         <v>1859</v>
       </c>
       <c r="E22" s="30" t="n">
@@ -6854,12 +6847,12 @@
           <t>효성중공업</t>
         </is>
       </c>
-      <c r="G22" s="35" t="inlineStr">
+      <c r="G22" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H22" s="60" t="n">
+      <c r="H22" s="59" t="n">
         <v>-3243</v>
       </c>
       <c r="J22" s="30" t="n">
@@ -6870,12 +6863,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="L22" s="35" t="inlineStr">
+      <c r="L22" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M22" s="47" t="n">
+      <c r="M22" s="46" t="n">
         <v>2660</v>
       </c>
       <c r="N22" s="30" t="n">
@@ -6886,12 +6879,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="P22" s="35" t="inlineStr">
+      <c r="P22" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q22" s="60" t="n">
+      <c r="Q22" s="59" t="n">
         <v>-1820</v>
       </c>
     </row>
@@ -6904,12 +6897,12 @@
           <t>주성엔지니어링</t>
         </is>
       </c>
-      <c r="C23" s="35" t="inlineStr">
+      <c r="C23" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D23" s="47" t="n">
+      <c r="D23" s="46" t="n">
         <v>1646</v>
       </c>
       <c r="E23" s="30" t="n">
@@ -6920,12 +6913,12 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="G23" s="43" t="inlineStr">
+      <c r="G23" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H23" s="60" t="n">
+      <c r="H23" s="59" t="n">
         <v>-2591</v>
       </c>
       <c r="J23" s="30" t="n">
@@ -6936,12 +6929,12 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="L23" s="43" t="inlineStr">
+      <c r="L23" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="M23" s="47" t="n">
+      <c r="M23" s="46" t="n">
         <v>2569</v>
       </c>
       <c r="N23" s="30" t="n">
@@ -6952,12 +6945,12 @@
           <t>주성엔지니어링</t>
         </is>
       </c>
-      <c r="P23" s="35" t="inlineStr">
+      <c r="P23" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q23" s="60" t="n">
+      <c r="Q23" s="59" t="n">
         <v>-1562</v>
       </c>
     </row>
@@ -6970,12 +6963,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="C24" s="35" t="inlineStr">
+      <c r="C24" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D24" s="47" t="n">
+      <c r="D24" s="46" t="n">
         <v>1202</v>
       </c>
       <c r="E24" s="30" t="n">
@@ -6986,12 +6979,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="G24" s="35" t="inlineStr">
+      <c r="G24" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H24" s="60" t="n">
+      <c r="H24" s="59" t="n">
         <v>-2340</v>
       </c>
       <c r="J24" s="30" t="n">
@@ -7002,12 +6995,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="L24" s="35" t="inlineStr">
+      <c r="L24" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M24" s="47" t="n">
+      <c r="M24" s="46" t="n">
         <v>2328</v>
       </c>
       <c r="N24" s="30" t="n">
@@ -7018,12 +7011,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="P24" s="35" t="inlineStr">
+      <c r="P24" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="Q24" s="60" t="n">
+      <c r="Q24" s="59" t="n">
         <v>-1206</v>
       </c>
     </row>
@@ -7036,12 +7029,12 @@
           <t>에코프로</t>
         </is>
       </c>
-      <c r="C25" s="35" t="inlineStr">
+      <c r="C25" s="34" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="D25" s="47" t="n">
+      <c r="D25" s="46" t="n">
         <v>856</v>
       </c>
       <c r="E25" s="30" t="n">
@@ -7052,12 +7045,12 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="G25" s="35" t="inlineStr">
+      <c r="G25" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="H25" s="60" t="n">
+      <c r="H25" s="59" t="n">
         <v>-2171</v>
       </c>
       <c r="J25" s="30" t="n">
@@ -7068,12 +7061,12 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="L25" s="35" t="inlineStr">
+      <c r="L25" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="M25" s="47" t="n">
+      <c r="M25" s="46" t="n">
         <v>2168</v>
       </c>
       <c r="N25" s="30" t="n">
@@ -7084,12 +7077,12 @@
           <t>에코프로</t>
         </is>
       </c>
-      <c r="P25" s="35" t="inlineStr">
+      <c r="P25" s="34" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="Q25" s="60" t="n">
+      <c r="Q25" s="59" t="n">
         <v>-857</v>
       </c>
     </row>
@@ -7102,12 +7095,12 @@
           <t>고영</t>
         </is>
       </c>
-      <c r="C26" s="35" t="inlineStr">
+      <c r="C26" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D26" s="47" t="n">
+      <c r="D26" s="46" t="n">
         <v>606</v>
       </c>
       <c r="E26" s="30" t="n">
@@ -7118,12 +7111,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="G26" s="35" t="inlineStr">
+      <c r="G26" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="H26" s="60" t="n">
+      <c r="H26" s="59" t="n">
         <v>-1807</v>
       </c>
       <c r="J26" s="30" t="n">
@@ -7134,12 +7127,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="L26" s="35" t="inlineStr">
+      <c r="L26" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="M26" s="47" t="n">
+      <c r="M26" s="46" t="n">
         <v>1914</v>
       </c>
       <c r="N26" s="30" t="n">
@@ -7150,12 +7143,12 @@
           <t>고영</t>
         </is>
       </c>
-      <c r="P26" s="35" t="inlineStr">
+      <c r="P26" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q26" s="60" t="n">
+      <c r="Q26" s="59" t="n">
         <v>-632</v>
       </c>
     </row>
@@ -7168,12 +7161,12 @@
           <t>제주반도체</t>
         </is>
       </c>
-      <c r="C27" s="35" t="inlineStr">
+      <c r="C27" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D27" s="47" t="n">
+      <c r="D27" s="46" t="n">
         <v>600</v>
       </c>
       <c r="E27" s="30" t="n">
@@ -7184,12 +7177,12 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="G27" s="43" t="inlineStr">
+      <c r="G27" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H27" s="60" t="n">
+      <c r="H27" s="59" t="n">
         <v>-1766</v>
       </c>
       <c r="J27" s="30" t="n">
@@ -7200,12 +7193,12 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="L27" s="43" t="inlineStr">
+      <c r="L27" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="M27" s="47" t="n">
+      <c r="M27" s="46" t="n">
         <v>1753</v>
       </c>
       <c r="N27" s="30" t="n">
@@ -7216,12 +7209,12 @@
           <t>제주반도체</t>
         </is>
       </c>
-      <c r="P27" s="35" t="inlineStr">
+      <c r="P27" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q27" s="60" t="n">
+      <c r="Q27" s="59" t="n">
         <v>-604</v>
       </c>
     </row>
@@ -7234,12 +7227,12 @@
           <t>한화솔루션</t>
         </is>
       </c>
-      <c r="C28" s="35" t="inlineStr">
+      <c r="C28" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D28" s="47" t="n">
+      <c r="D28" s="46" t="n">
         <v>574</v>
       </c>
       <c r="E28" s="30" t="n">
@@ -7250,12 +7243,12 @@
           <t>삼성바이오로직스</t>
         </is>
       </c>
-      <c r="G28" s="35" t="inlineStr">
+      <c r="G28" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="H28" s="60" t="n">
+      <c r="H28" s="59" t="n">
         <v>-1292</v>
       </c>
       <c r="J28" s="30" t="n">
@@ -7266,12 +7259,12 @@
           <t>삼성바이오로직스</t>
         </is>
       </c>
-      <c r="L28" s="35" t="inlineStr">
+      <c r="L28" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="M28" s="47" t="n">
+      <c r="M28" s="46" t="n">
         <v>1248</v>
       </c>
       <c r="N28" s="30" t="n">
@@ -7282,12 +7275,12 @@
           <t>한화솔루션</t>
         </is>
       </c>
-      <c r="P28" s="35" t="inlineStr">
+      <c r="P28" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="Q28" s="60" t="n">
+      <c r="Q28" s="59" t="n">
         <v>-591</v>
       </c>
     </row>
@@ -7300,12 +7293,12 @@
           <t>이수페타시스</t>
         </is>
       </c>
-      <c r="C29" s="35" t="inlineStr">
+      <c r="C29" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D29" s="47" t="n">
+      <c r="D29" s="46" t="n">
         <v>490</v>
       </c>
       <c r="E29" s="30" t="n">
@@ -7316,12 +7309,12 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="G29" s="35" t="inlineStr">
+      <c r="G29" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H29" s="60" t="n">
+      <c r="H29" s="59" t="n">
         <v>-1133</v>
       </c>
       <c r="J29" s="30" t="n">
@@ -7332,12 +7325,12 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="L29" s="35" t="inlineStr">
+      <c r="L29" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M29" s="47" t="n">
+      <c r="M29" s="46" t="n">
         <v>1067</v>
       </c>
       <c r="N29" s="30" t="n">
@@ -7348,12 +7341,12 @@
           <t>에이피알</t>
         </is>
       </c>
-      <c r="P29" s="35" t="inlineStr">
+      <c r="P29" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="Q29" s="60" t="n">
+      <c r="Q29" s="59" t="n">
         <v>-485</v>
       </c>
     </row>
@@ -7364,7 +7357,7 @@
           <t>F5 금융투자</t>
         </is>
       </c>
-      <c r="E31" s="57" t="inlineStr">
+      <c r="E31" s="56" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
@@ -7374,111 +7367,111 @@
           <t>F6 투신(사모)</t>
         </is>
       </c>
-      <c r="N31" s="57" t="inlineStr">
+      <c r="N31" s="56" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="58" t="inlineStr">
+      <c r="A32" s="57" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="E32" s="59" t="inlineStr">
+      <c r="E32" s="58" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="J32" s="58" t="inlineStr">
+      <c r="J32" s="57" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="N32" s="59" t="inlineStr">
+      <c r="N32" s="58" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="45" t="inlineStr">
+      <c r="A33" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B33" s="45" t="inlineStr">
+      <c r="B33" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C33" s="45" t="inlineStr">
+      <c r="C33" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D33" s="45" t="inlineStr">
+      <c r="D33" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E33" s="45" t="inlineStr">
+      <c r="E33" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F33" s="45" t="inlineStr">
+      <c r="F33" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G33" s="45" t="inlineStr">
+      <c r="G33" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H33" s="45" t="inlineStr">
+      <c r="H33" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="J33" s="45" t="inlineStr">
+      <c r="J33" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="K33" s="45" t="inlineStr">
+      <c r="K33" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="L33" s="45" t="inlineStr">
+      <c r="L33" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="M33" s="45" t="inlineStr">
+      <c r="M33" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="N33" s="45" t="inlineStr">
+      <c r="N33" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O33" s="45" t="inlineStr">
+      <c r="O33" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P33" s="45" t="inlineStr">
+      <c r="P33" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q33" s="45" t="inlineStr">
+      <c r="Q33" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -7493,12 +7486,12 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="C34" s="35" t="inlineStr">
+      <c r="C34" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D34" s="47" t="n">
+      <c r="D34" s="46" t="n">
         <v>1090</v>
       </c>
       <c r="E34" s="30" t="n">
@@ -7509,12 +7502,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="G34" s="35" t="inlineStr">
+      <c r="G34" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H34" s="60" t="n">
+      <c r="H34" s="59" t="n">
         <v>-10388</v>
       </c>
       <c r="J34" s="30" t="n">
@@ -7525,12 +7518,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="L34" s="35" t="inlineStr">
+      <c r="L34" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="M34" s="47" t="n">
+      <c r="M34" s="46" t="n">
         <v>4098</v>
       </c>
       <c r="N34" s="30" t="n">
@@ -7541,12 +7534,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="P34" s="35" t="inlineStr">
+      <c r="P34" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q34" s="60" t="n">
+      <c r="Q34" s="59" t="n">
         <v>-2236</v>
       </c>
     </row>
@@ -7559,12 +7552,12 @@
           <t>주성엔지니어링</t>
         </is>
       </c>
-      <c r="C35" s="35" t="inlineStr">
+      <c r="C35" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D35" s="47" t="n">
+      <c r="D35" s="46" t="n">
         <v>988</v>
       </c>
       <c r="E35" s="30" t="n">
@@ -7575,12 +7568,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="G35" s="35" t="inlineStr">
+      <c r="G35" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H35" s="60" t="n">
+      <c r="H35" s="59" t="n">
         <v>-5967</v>
       </c>
       <c r="J35" s="30" t="n">
@@ -7591,12 +7584,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="L35" s="35" t="inlineStr">
+      <c r="L35" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M35" s="47" t="n">
+      <c r="M35" s="46" t="n">
         <v>2746</v>
       </c>
       <c r="N35" s="30" t="n">
@@ -7607,12 +7600,12 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="P35" s="35" t="inlineStr">
+      <c r="P35" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q35" s="60" t="n">
+      <c r="Q35" s="59" t="n">
         <v>-982</v>
       </c>
     </row>
@@ -7625,12 +7618,12 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="C36" s="35" t="inlineStr">
+      <c r="C36" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D36" s="47" t="n">
+      <c r="D36" s="46" t="n">
         <v>540</v>
       </c>
       <c r="E36" s="30" t="n">
@@ -7641,12 +7634,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="G36" s="35" t="inlineStr">
+      <c r="G36" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H36" s="60" t="n">
+      <c r="H36" s="59" t="n">
         <v>-1700</v>
       </c>
       <c r="J36" s="30" t="n">
@@ -7657,12 +7650,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="L36" s="35" t="inlineStr">
+      <c r="L36" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M36" s="47" t="n">
+      <c r="M36" s="46" t="n">
         <v>983</v>
       </c>
       <c r="N36" s="30" t="n">
@@ -7673,12 +7666,12 @@
           <t>주성엔지니어링</t>
         </is>
       </c>
-      <c r="P36" s="35" t="inlineStr">
+      <c r="P36" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q36" s="60" t="n">
+      <c r="Q36" s="59" t="n">
         <v>-947</v>
       </c>
     </row>
@@ -7691,12 +7684,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="C37" s="35" t="inlineStr">
+      <c r="C37" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D37" s="47" t="n">
+      <c r="D37" s="46" t="n">
         <v>507</v>
       </c>
       <c r="E37" s="30" t="n">
@@ -7707,12 +7700,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="G37" s="35" t="inlineStr">
+      <c r="G37" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="H37" s="60" t="n">
+      <c r="H37" s="59" t="n">
         <v>-929</v>
       </c>
       <c r="J37" s="30" t="n">
@@ -7723,12 +7716,12 @@
           <t>리노공업</t>
         </is>
       </c>
-      <c r="L37" s="35" t="inlineStr">
+      <c r="L37" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M37" s="47" t="n">
+      <c r="M37" s="46" t="n">
         <v>901</v>
       </c>
       <c r="N37" s="30" t="n">
@@ -7739,12 +7732,12 @@
           <t>이수페타시스</t>
         </is>
       </c>
-      <c r="P37" s="35" t="inlineStr">
+      <c r="P37" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q37" s="60" t="n">
+      <c r="Q37" s="59" t="n">
         <v>-882</v>
       </c>
     </row>
@@ -7757,12 +7750,12 @@
           <t>KB금융</t>
         </is>
       </c>
-      <c r="C38" s="35" t="inlineStr">
+      <c r="C38" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D38" s="47" t="n">
+      <c r="D38" s="46" t="n">
         <v>480</v>
       </c>
       <c r="E38" s="30" t="n">
@@ -7773,12 +7766,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="G38" s="35" t="inlineStr">
+      <c r="G38" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H38" s="60" t="n">
+      <c r="H38" s="59" t="n">
         <v>-437</v>
       </c>
       <c r="J38" s="30" t="n">
@@ -7789,12 +7782,12 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="L38" s="35" t="inlineStr">
+      <c r="L38" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M38" s="47" t="n">
+      <c r="M38" s="46" t="n">
         <v>823</v>
       </c>
       <c r="N38" s="30" t="n">
@@ -7805,12 +7798,12 @@
           <t>원익IPS</t>
         </is>
       </c>
-      <c r="P38" s="35" t="inlineStr">
+      <c r="P38" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q38" s="60" t="n">
+      <c r="Q38" s="59" t="n">
         <v>-707</v>
       </c>
     </row>
@@ -7823,12 +7816,12 @@
           <t>LIG디펜스앤에어로스페이스</t>
         </is>
       </c>
-      <c r="C39" s="35" t="inlineStr">
+      <c r="C39" s="34" t="inlineStr">
         <is>
           <t>금속</t>
         </is>
       </c>
-      <c r="D39" s="47" t="n">
+      <c r="D39" s="46" t="n">
         <v>447</v>
       </c>
       <c r="E39" s="30" t="n">
@@ -7839,12 +7832,12 @@
           <t>대한항공</t>
         </is>
       </c>
-      <c r="G39" s="35" t="inlineStr">
+      <c r="G39" s="34" t="inlineStr">
         <is>
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="H39" s="60" t="n">
+      <c r="H39" s="59" t="n">
         <v>-361</v>
       </c>
       <c r="J39" s="30" t="n">
@@ -7855,12 +7848,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="L39" s="35" t="inlineStr">
+      <c r="L39" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M39" s="47" t="n">
+      <c r="M39" s="46" t="n">
         <v>728</v>
       </c>
       <c r="N39" s="30" t="n">
@@ -7871,12 +7864,12 @@
           <t>이오테크닉스</t>
         </is>
       </c>
-      <c r="P39" s="35" t="inlineStr">
+      <c r="P39" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q39" s="60" t="n">
+      <c r="Q39" s="59" t="n">
         <v>-663</v>
       </c>
     </row>
@@ -7889,12 +7882,12 @@
           <t>원익IPS</t>
         </is>
       </c>
-      <c r="C40" s="35" t="inlineStr">
+      <c r="C40" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D40" s="47" t="n">
+      <c r="D40" s="46" t="n">
         <v>425</v>
       </c>
       <c r="E40" s="30" t="n">
@@ -7905,12 +7898,12 @@
           <t>SK</t>
         </is>
       </c>
-      <c r="G40" s="35" t="inlineStr">
+      <c r="G40" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="H40" s="60" t="n">
+      <c r="H40" s="59" t="n">
         <v>-318</v>
       </c>
       <c r="J40" s="30" t="n">
@@ -7921,12 +7914,12 @@
           <t>대덕전자</t>
         </is>
       </c>
-      <c r="L40" s="35" t="inlineStr">
+      <c r="L40" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M40" s="47" t="n">
+      <c r="M40" s="46" t="n">
         <v>524</v>
       </c>
       <c r="N40" s="30" t="n">
@@ -7937,12 +7930,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="P40" s="35" t="inlineStr">
+      <c r="P40" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q40" s="60" t="n">
+      <c r="Q40" s="59" t="n">
         <v>-574</v>
       </c>
     </row>
@@ -7955,12 +7948,12 @@
           <t>HPSP</t>
         </is>
       </c>
-      <c r="C41" s="35" t="inlineStr">
+      <c r="C41" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D41" s="47" t="n">
+      <c r="D41" s="46" t="n">
         <v>405</v>
       </c>
       <c r="E41" s="30" t="n">
@@ -7971,12 +7964,12 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="G41" s="43" t="inlineStr">
+      <c r="G41" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H41" s="60" t="n">
+      <c r="H41" s="59" t="n">
         <v>-259</v>
       </c>
       <c r="J41" s="30" t="n">
@@ -7987,12 +7980,12 @@
           <t>SK</t>
         </is>
       </c>
-      <c r="L41" s="35" t="inlineStr">
+      <c r="L41" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="M41" s="47" t="n">
+      <c r="M41" s="46" t="n">
         <v>454</v>
       </c>
       <c r="N41" s="30" t="n">
@@ -8003,12 +7996,12 @@
           <t>DB하이텍</t>
         </is>
       </c>
-      <c r="P41" s="35" t="inlineStr">
+      <c r="P41" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q41" s="60" t="n">
+      <c r="Q41" s="59" t="n">
         <v>-567</v>
       </c>
     </row>
@@ -8021,12 +8014,12 @@
           <t>LG화학</t>
         </is>
       </c>
-      <c r="C42" s="35" t="inlineStr">
+      <c r="C42" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D42" s="47" t="n">
+      <c r="D42" s="46" t="n">
         <v>382</v>
       </c>
       <c r="E42" s="30" t="n">
@@ -8037,12 +8030,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="G42" s="35" t="inlineStr">
+      <c r="G42" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="H42" s="60" t="n">
+      <c r="H42" s="59" t="n">
         <v>-255</v>
       </c>
       <c r="J42" s="30" t="n">
@@ -8053,12 +8046,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="L42" s="35" t="inlineStr">
+      <c r="L42" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="M42" s="47" t="n">
+      <c r="M42" s="46" t="n">
         <v>422</v>
       </c>
       <c r="N42" s="30" t="n">
@@ -8069,12 +8062,12 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="P42" s="43" t="inlineStr">
+      <c r="P42" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q42" s="60" t="n">
+      <c r="Q42" s="59" t="n">
         <v>-542</v>
       </c>
     </row>
@@ -8087,12 +8080,12 @@
           <t>이오테크닉스</t>
         </is>
       </c>
-      <c r="C43" s="35" t="inlineStr">
+      <c r="C43" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D43" s="47" t="n">
+      <c r="D43" s="46" t="n">
         <v>245</v>
       </c>
       <c r="E43" s="30" t="n">
@@ -8103,12 +8096,12 @@
           <t>효성중공업</t>
         </is>
       </c>
-      <c r="G43" s="35" t="inlineStr">
+      <c r="G43" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H43" s="60" t="n">
+      <c r="H43" s="59" t="n">
         <v>-220</v>
       </c>
       <c r="J43" s="30" t="n">
@@ -8119,12 +8112,12 @@
           <t>LG이노텍</t>
         </is>
       </c>
-      <c r="L43" s="35" t="inlineStr">
+      <c r="L43" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M43" s="47" t="n">
+      <c r="M43" s="46" t="n">
         <v>360</v>
       </c>
       <c r="N43" s="30" t="n">
@@ -8135,12 +8128,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="P43" s="35" t="inlineStr">
+      <c r="P43" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q43" s="60" t="n">
+      <c r="Q43" s="59" t="n">
         <v>-469</v>
       </c>
     </row>
@@ -8151,7 +8144,7 @@
           <t>F7 연기금</t>
         </is>
       </c>
-      <c r="E45" s="57" t="inlineStr">
+      <c r="E45" s="56" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
@@ -8161,111 +8154,111 @@
           <t>F8 보험</t>
         </is>
       </c>
-      <c r="N45" s="57" t="inlineStr">
+      <c r="N45" s="56" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="58" t="inlineStr">
+      <c r="A46" s="57" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="E46" s="59" t="inlineStr">
+      <c r="E46" s="58" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="J46" s="58" t="inlineStr">
+      <c r="J46" s="57" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="N46" s="59" t="inlineStr">
+      <c r="N46" s="58" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="45" t="inlineStr">
+      <c r="A47" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B47" s="45" t="inlineStr">
+      <c r="B47" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C47" s="45" t="inlineStr">
+      <c r="C47" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D47" s="45" t="inlineStr">
+      <c r="D47" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E47" s="45" t="inlineStr">
+      <c r="E47" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F47" s="45" t="inlineStr">
+      <c r="F47" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G47" s="45" t="inlineStr">
+      <c r="G47" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H47" s="45" t="inlineStr">
+      <c r="H47" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="J47" s="45" t="inlineStr">
+      <c r="J47" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="K47" s="45" t="inlineStr">
+      <c r="K47" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="L47" s="45" t="inlineStr">
+      <c r="L47" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="M47" s="45" t="inlineStr">
+      <c r="M47" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="N47" s="45" t="inlineStr">
+      <c r="N47" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O47" s="45" t="inlineStr">
+      <c r="O47" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P47" s="45" t="inlineStr">
+      <c r="P47" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q47" s="45" t="inlineStr">
+      <c r="Q47" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -8280,12 +8273,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="C48" s="35" t="inlineStr">
+      <c r="C48" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D48" s="47" t="n">
+      <c r="D48" s="46" t="n">
         <v>1194</v>
       </c>
       <c r="E48" s="30" t="n">
@@ -8296,12 +8289,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="G48" s="35" t="inlineStr">
+      <c r="G48" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H48" s="60" t="n">
+      <c r="H48" s="59" t="n">
         <v>-1149</v>
       </c>
       <c r="J48" s="30" t="n">
@@ -8312,12 +8305,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="L48" s="35" t="inlineStr">
+      <c r="L48" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M48" s="47" t="n">
+      <c r="M48" s="46" t="n">
         <v>241</v>
       </c>
       <c r="N48" s="30" t="n">
@@ -8328,12 +8321,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="P48" s="35" t="inlineStr">
+      <c r="P48" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q48" s="60" t="n">
+      <c r="Q48" s="59" t="n">
         <v>-170</v>
       </c>
     </row>
@@ -8346,12 +8339,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="C49" s="35" t="inlineStr">
+      <c r="C49" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D49" s="47" t="n">
+      <c r="D49" s="46" t="n">
         <v>925</v>
       </c>
       <c r="E49" s="30" t="n">
@@ -8362,12 +8355,12 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="G49" s="43" t="inlineStr">
+      <c r="G49" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H49" s="60" t="n">
+      <c r="H49" s="59" t="n">
         <v>-839</v>
       </c>
       <c r="J49" s="30" t="n">
@@ -8378,12 +8371,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="L49" s="35" t="inlineStr">
+      <c r="L49" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M49" s="47" t="n">
+      <c r="M49" s="46" t="n">
         <v>237</v>
       </c>
       <c r="N49" s="30" t="n">
@@ -8394,12 +8387,12 @@
           <t>HD건설기계</t>
         </is>
       </c>
-      <c r="P49" s="35" t="inlineStr">
+      <c r="P49" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q49" s="60" t="n">
+      <c r="Q49" s="59" t="n">
         <v>-101</v>
       </c>
     </row>
@@ -8412,12 +8405,12 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="C50" s="35" t="inlineStr">
+      <c r="C50" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D50" s="47" t="n">
+      <c r="D50" s="46" t="n">
         <v>602</v>
       </c>
       <c r="E50" s="30" t="n">
@@ -8428,12 +8421,12 @@
           <t>기아</t>
         </is>
       </c>
-      <c r="G50" s="43" t="inlineStr">
+      <c r="G50" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H50" s="60" t="n">
+      <c r="H50" s="59" t="n">
         <v>-580</v>
       </c>
       <c r="J50" s="30" t="n">
@@ -8444,12 +8437,12 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="L50" s="35" t="inlineStr">
+      <c r="L50" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M50" s="47" t="n">
+      <c r="M50" s="46" t="n">
         <v>95</v>
       </c>
       <c r="N50" s="30" t="n">
@@ -8460,12 +8453,12 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="P50" s="35" t="inlineStr">
+      <c r="P50" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="Q50" s="60" t="n">
+      <c r="Q50" s="59" t="n">
         <v>-70</v>
       </c>
     </row>
@@ -8478,12 +8471,12 @@
           <t>리노공업</t>
         </is>
       </c>
-      <c r="C51" s="35" t="inlineStr">
+      <c r="C51" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D51" s="47" t="n">
+      <c r="D51" s="46" t="n">
         <v>585</v>
       </c>
       <c r="E51" s="30" t="n">
@@ -8494,12 +8487,12 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="G51" s="35" t="inlineStr">
+      <c r="G51" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="H51" s="60" t="n">
+      <c r="H51" s="59" t="n">
         <v>-557</v>
       </c>
       <c r="J51" s="30" t="n">
@@ -8510,12 +8503,12 @@
           <t>LG이노텍</t>
         </is>
       </c>
-      <c r="L51" s="35" t="inlineStr">
+      <c r="L51" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M51" s="47" t="n">
+      <c r="M51" s="46" t="n">
         <v>82</v>
       </c>
       <c r="N51" s="30" t="n">
@@ -8526,12 +8519,12 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="P51" s="43" t="inlineStr">
+      <c r="P51" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q51" s="60" t="n">
+      <c r="Q51" s="59" t="n">
         <v>-60</v>
       </c>
     </row>
@@ -8544,12 +8537,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="C52" s="35" t="inlineStr">
+      <c r="C52" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D52" s="47" t="n">
+      <c r="D52" s="46" t="n">
         <v>447</v>
       </c>
       <c r="E52" s="30" t="n">
@@ -8560,12 +8553,12 @@
           <t>현대건설</t>
         </is>
       </c>
-      <c r="G52" s="35" t="inlineStr">
+      <c r="G52" s="34" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
       </c>
-      <c r="H52" s="60" t="n">
+      <c r="H52" s="59" t="n">
         <v>-429</v>
       </c>
       <c r="J52" s="30" t="n">
@@ -8576,12 +8569,12 @@
           <t>한화시스템</t>
         </is>
       </c>
-      <c r="L52" s="35" t="inlineStr">
+      <c r="L52" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M52" s="47" t="n">
+      <c r="M52" s="46" t="n">
         <v>79</v>
       </c>
       <c r="N52" s="30" t="n">
@@ -8592,12 +8585,12 @@
           <t>효성중공업</t>
         </is>
       </c>
-      <c r="P52" s="35" t="inlineStr">
+      <c r="P52" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q52" s="60" t="n">
+      <c r="Q52" s="59" t="n">
         <v>-58</v>
       </c>
     </row>
@@ -8610,12 +8603,12 @@
           <t>한화시스템</t>
         </is>
       </c>
-      <c r="C53" s="35" t="inlineStr">
+      <c r="C53" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D53" s="47" t="n">
+      <c r="D53" s="46" t="n">
         <v>432</v>
       </c>
       <c r="E53" s="30" t="n">
@@ -8626,12 +8619,12 @@
           <t>HD한국조선해양</t>
         </is>
       </c>
-      <c r="G53" s="35" t="inlineStr">
+      <c r="G53" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="H53" s="60" t="n">
+      <c r="H53" s="59" t="n">
         <v>-352</v>
       </c>
       <c r="J53" s="30" t="n">
@@ -8642,12 +8635,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="L53" s="35" t="inlineStr">
+      <c r="L53" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M53" s="47" t="n">
+      <c r="M53" s="46" t="n">
         <v>77</v>
       </c>
       <c r="N53" s="30" t="n">
@@ -8658,12 +8651,12 @@
           <t>신한지주</t>
         </is>
       </c>
-      <c r="P53" s="35" t="inlineStr">
+      <c r="P53" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="Q53" s="60" t="n">
+      <c r="Q53" s="59" t="n">
         <v>-55</v>
       </c>
     </row>
@@ -8676,12 +8669,12 @@
           <t>NC</t>
         </is>
       </c>
-      <c r="C54" s="35" t="inlineStr">
+      <c r="C54" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="D54" s="47" t="n">
+      <c r="D54" s="46" t="n">
         <v>385</v>
       </c>
       <c r="E54" s="30" t="n">
@@ -8692,12 +8685,12 @@
           <t>HD현대중공업</t>
         </is>
       </c>
-      <c r="G54" s="43" t="inlineStr">
+      <c r="G54" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H54" s="60" t="n">
+      <c r="H54" s="59" t="n">
         <v>-330</v>
       </c>
       <c r="J54" s="30" t="n">
@@ -8708,12 +8701,12 @@
           <t>리노공업</t>
         </is>
       </c>
-      <c r="L54" s="35" t="inlineStr">
+      <c r="L54" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M54" s="47" t="n">
+      <c r="M54" s="46" t="n">
         <v>73</v>
       </c>
       <c r="N54" s="30" t="n">
@@ -8724,12 +8717,12 @@
           <t>기아</t>
         </is>
       </c>
-      <c r="P54" s="43" t="inlineStr">
+      <c r="P54" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q54" s="60" t="n">
+      <c r="Q54" s="59" t="n">
         <v>-51</v>
       </c>
     </row>
@@ -8742,12 +8735,12 @@
           <t>우리금융지주</t>
         </is>
       </c>
-      <c r="C55" s="35" t="inlineStr">
+      <c r="C55" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D55" s="47" t="n">
+      <c r="D55" s="46" t="n">
         <v>217</v>
       </c>
       <c r="E55" s="30" t="n">
@@ -8758,12 +8751,12 @@
           <t>HD건설기계</t>
         </is>
       </c>
-      <c r="G55" s="35" t="inlineStr">
+      <c r="G55" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H55" s="60" t="n">
+      <c r="H55" s="59" t="n">
         <v>-324</v>
       </c>
       <c r="J55" s="30" t="n">
@@ -8774,12 +8767,12 @@
           <t>포스코퓨처엠</t>
         </is>
       </c>
-      <c r="L55" s="35" t="inlineStr">
+      <c r="L55" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M55" s="47" t="n">
+      <c r="M55" s="46" t="n">
         <v>49</v>
       </c>
       <c r="N55" s="30" t="n">
@@ -8790,12 +8783,12 @@
           <t>LS</t>
         </is>
       </c>
-      <c r="P55" s="35" t="inlineStr">
+      <c r="P55" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="Q55" s="60" t="n">
+      <c r="Q55" s="59" t="n">
         <v>-46</v>
       </c>
     </row>
@@ -8808,12 +8801,12 @@
           <t>LG화학</t>
         </is>
       </c>
-      <c r="C56" s="35" t="inlineStr">
+      <c r="C56" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D56" s="47" t="n">
+      <c r="D56" s="46" t="n">
         <v>198</v>
       </c>
       <c r="E56" s="30" t="n">
@@ -8824,12 +8817,12 @@
           <t>심텍</t>
         </is>
       </c>
-      <c r="G56" s="35" t="inlineStr">
+      <c r="G56" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H56" s="60" t="n">
+      <c r="H56" s="59" t="n">
         <v>-268</v>
       </c>
       <c r="J56" s="30" t="n">
@@ -8840,12 +8833,12 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="L56" s="43" t="inlineStr">
+      <c r="L56" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="M56" s="47" t="n">
+      <c r="M56" s="46" t="n">
         <v>33</v>
       </c>
       <c r="N56" s="30" t="n">
@@ -8856,12 +8849,12 @@
           <t>HD한국조선해양</t>
         </is>
       </c>
-      <c r="P56" s="35" t="inlineStr">
+      <c r="P56" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="Q56" s="60" t="n">
+      <c r="Q56" s="59" t="n">
         <v>-38</v>
       </c>
     </row>
@@ -8874,12 +8867,12 @@
           <t>올릭스</t>
         </is>
       </c>
-      <c r="C57" s="35" t="inlineStr">
+      <c r="C57" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="D57" s="47" t="n">
+      <c r="D57" s="46" t="n">
         <v>170</v>
       </c>
       <c r="E57" s="30" t="n">
@@ -8890,12 +8883,12 @@
           <t>LS ELECTRIC</t>
         </is>
       </c>
-      <c r="G57" s="35" t="inlineStr">
+      <c r="G57" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H57" s="60" t="n">
+      <c r="H57" s="59" t="n">
         <v>-217</v>
       </c>
       <c r="J57" s="30" t="n">
@@ -8906,12 +8899,12 @@
           <t>NC</t>
         </is>
       </c>
-      <c r="L57" s="35" t="inlineStr">
+      <c r="L57" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="M57" s="47" t="n">
+      <c r="M57" s="46" t="n">
         <v>32</v>
       </c>
       <c r="N57" s="30" t="n">
@@ -8922,12 +8915,12 @@
           <t>피에스케이홀딩스</t>
         </is>
       </c>
-      <c r="P57" s="35" t="inlineStr">
+      <c r="P57" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q57" s="60" t="n">
+      <c r="Q57" s="59" t="n">
         <v>-30</v>
       </c>
     </row>
@@ -8938,61 +8931,61 @@
           <t>F9 기타법인</t>
         </is>
       </c>
-      <c r="E59" s="57" t="inlineStr">
+      <c r="E59" s="56" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="58" t="inlineStr">
+      <c r="A60" s="57" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="E60" s="59" t="inlineStr">
+      <c r="E60" s="58" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="45" t="inlineStr">
+      <c r="A61" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B61" s="45" t="inlineStr">
+      <c r="B61" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C61" s="45" t="inlineStr">
+      <c r="C61" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D61" s="45" t="inlineStr">
+      <c r="D61" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E61" s="45" t="inlineStr">
+      <c r="E61" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F61" s="45" t="inlineStr">
+      <c r="F61" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G61" s="45" t="inlineStr">
+      <c r="G61" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H61" s="45" t="inlineStr">
+      <c r="H61" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -9007,12 +9000,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="C62" s="35" t="inlineStr">
+      <c r="C62" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D62" s="47" t="n">
+      <c r="D62" s="46" t="n">
         <v>40824</v>
       </c>
       <c r="E62" s="30" t="n">
@@ -9023,12 +9016,12 @@
           <t>브릴스</t>
         </is>
       </c>
-      <c r="G62" s="35" t="inlineStr">
+      <c r="G62" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H62" s="60" t="n">
+      <c r="H62" s="59" t="n">
         <v>-222</v>
       </c>
     </row>
@@ -9041,12 +9034,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="C63" s="35" t="inlineStr">
+      <c r="C63" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D63" s="47" t="n">
+      <c r="D63" s="46" t="n">
         <v>13856</v>
       </c>
       <c r="E63" s="30" t="n">
@@ -9057,12 +9050,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="G63" s="35" t="inlineStr">
+      <c r="G63" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="H63" s="60" t="n">
+      <c r="H63" s="59" t="n">
         <v>-107</v>
       </c>
     </row>
@@ -9075,12 +9068,12 @@
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="C64" s="35" t="inlineStr">
+      <c r="C64" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="D64" s="47" t="n">
+      <c r="D64" s="46" t="n">
         <v>185</v>
       </c>
       <c r="E64" s="30" t="n">
@@ -9091,12 +9084,12 @@
           <t>LG이노텍</t>
         </is>
       </c>
-      <c r="G64" s="35" t="inlineStr">
+      <c r="G64" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H64" s="60" t="n">
+      <c r="H64" s="59" t="n">
         <v>-86</v>
       </c>
     </row>
@@ -9109,12 +9102,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="C65" s="35" t="inlineStr">
+      <c r="C65" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D65" s="47" t="n">
+      <c r="D65" s="46" t="n">
         <v>152</v>
       </c>
       <c r="E65" s="30" t="n">
@@ -9125,12 +9118,12 @@
           <t>주성엔지니어링</t>
         </is>
       </c>
-      <c r="G65" s="35" t="inlineStr">
+      <c r="G65" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H65" s="60" t="n">
+      <c r="H65" s="59" t="n">
         <v>-84</v>
       </c>
     </row>
@@ -9143,12 +9136,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="C66" s="35" t="inlineStr">
+      <c r="C66" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D66" s="47" t="n">
+      <c r="D66" s="46" t="n">
         <v>83</v>
       </c>
       <c r="E66" s="30" t="n">
@@ -9159,12 +9152,12 @@
           <t>두산</t>
         </is>
       </c>
-      <c r="G66" s="35" t="inlineStr">
+      <c r="G66" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H66" s="60" t="n">
+      <c r="H66" s="59" t="n">
         <v>-44</v>
       </c>
     </row>
@@ -9177,12 +9170,12 @@
           <t>KT&amp;G</t>
         </is>
       </c>
-      <c r="C67" s="35" t="inlineStr">
+      <c r="C67" s="34" t="inlineStr">
         <is>
           <t>음식료·담배</t>
         </is>
       </c>
-      <c r="D67" s="47" t="n">
+      <c r="D67" s="46" t="n">
         <v>74</v>
       </c>
       <c r="E67" s="30" t="n">
@@ -9193,12 +9186,12 @@
           <t>피노</t>
         </is>
       </c>
-      <c r="G67" s="35" t="inlineStr">
+      <c r="G67" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H67" s="60" t="n">
+      <c r="H67" s="59" t="n">
         <v>-43</v>
       </c>
     </row>
@@ -9211,12 +9204,12 @@
           <t>한화오션</t>
         </is>
       </c>
-      <c r="C68" s="43" t="inlineStr">
+      <c r="C68" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="D68" s="47" t="n">
+      <c r="D68" s="46" t="n">
         <v>71</v>
       </c>
       <c r="E68" s="30" t="n">
@@ -9227,12 +9220,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="G68" s="35" t="inlineStr">
+      <c r="G68" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H68" s="60" t="n">
+      <c r="H68" s="59" t="n">
         <v>-39</v>
       </c>
     </row>
@@ -9245,12 +9238,12 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="C69" s="35" t="inlineStr">
+      <c r="C69" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D69" s="47" t="n">
+      <c r="D69" s="46" t="n">
         <v>66</v>
       </c>
       <c r="E69" s="30" t="n">
@@ -9261,12 +9254,12 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="G69" s="35" t="inlineStr">
+      <c r="G69" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H69" s="60" t="n">
+      <c r="H69" s="59" t="n">
         <v>-29</v>
       </c>
     </row>
@@ -9279,12 +9272,12 @@
           <t>리노공업</t>
         </is>
       </c>
-      <c r="C70" s="35" t="inlineStr">
+      <c r="C70" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D70" s="47" t="n">
+      <c r="D70" s="46" t="n">
         <v>58</v>
       </c>
       <c r="E70" s="30" t="n">
@@ -9295,12 +9288,12 @@
           <t>포스코퓨처엠</t>
         </is>
       </c>
-      <c r="G70" s="35" t="inlineStr">
+      <c r="G70" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H70" s="60" t="n">
+      <c r="H70" s="59" t="n">
         <v>-22</v>
       </c>
     </row>
@@ -9313,12 +9306,12 @@
           <t>서진시스템</t>
         </is>
       </c>
-      <c r="C71" s="35" t="inlineStr">
+      <c r="C71" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D71" s="47" t="n">
+      <c r="D71" s="46" t="n">
         <v>54</v>
       </c>
       <c r="E71" s="30" t="n">
@@ -9329,18 +9322,18 @@
           <t>롯데쇼핑</t>
         </is>
       </c>
-      <c r="G71" s="35" t="inlineStr">
+      <c r="G71" s="34" t="inlineStr">
         <is>
           <t>유통</t>
         </is>
       </c>
-      <c r="H71" s="60" t="n">
+      <c r="H71" s="59" t="n">
         <v>-22</v>
       </c>
     </row>
     <row r="72"/>
     <row r="73" ht="31" customHeight="1" s="15">
-      <c r="A73" s="61" t="inlineStr">
+      <c r="A73" s="60" t="inlineStr">
         <is>
           <t>외인·기관 동시 등재 종목=종목명 굵게(동반 매수/매도) · netbuy_rank 일별 아카이브 합산 — 상위 30 리스트 등재일만 반영되는 근사치 · 금융투자=증권, 투신(사모)=투자신탁+사모펀드, 기타법인=일반법인(자사주 매입 등) (확정 병합분) · 외인+기관=합산 카드와 동일</t>
         </is>
@@ -9458,87 +9451,87 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="45" t="inlineStr">
+      <c r="A4" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B4" s="45" t="inlineStr">
+      <c r="B4" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="D4" s="44" t="inlineStr">
         <is>
           <t>금액(억)</t>
         </is>
       </c>
-      <c r="E4" s="45" t="inlineStr">
+      <c r="E4" s="44" t="inlineStr">
         <is>
           <t>시총대비(%)</t>
         </is>
       </c>
-      <c r="G4" s="45" t="inlineStr">
+      <c r="G4" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="H4" s="45" t="inlineStr">
+      <c r="H4" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="I4" s="45" t="inlineStr">
+      <c r="I4" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="J4" s="45" t="inlineStr">
+      <c r="J4" s="44" t="inlineStr">
         <is>
           <t>증감(억)</t>
         </is>
       </c>
-      <c r="K4" s="45" t="inlineStr">
+      <c r="K4" s="44" t="inlineStr">
         <is>
           <t>대차잔고(억)</t>
         </is>
       </c>
-      <c r="L4" s="45" t="inlineStr">
+      <c r="L4" s="44" t="inlineStr">
         <is>
           <t>시총대비(%)</t>
         </is>
       </c>
-      <c r="N4" s="45" t="inlineStr">
+      <c r="N4" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O4" s="45" t="inlineStr">
+      <c r="O4" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P4" s="45" t="inlineStr">
+      <c r="P4" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q4" s="45" t="inlineStr">
+      <c r="Q4" s="44" t="inlineStr">
         <is>
           <t>증감(억)</t>
         </is>
       </c>
-      <c r="R4" s="45" t="inlineStr">
+      <c r="R4" s="44" t="inlineStr">
         <is>
           <t>대차잔고(억)</t>
         </is>
       </c>
-      <c r="S4" s="45" t="inlineStr">
+      <c r="S4" s="44" t="inlineStr">
         <is>
           <t>시총대비(%)</t>
         </is>
@@ -9553,15 +9546,15 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="C5" s="35" t="inlineStr">
+      <c r="C5" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D5" s="62" t="n">
+      <c r="D5" s="61" t="n">
         <v>13947</v>
       </c>
-      <c r="E5" s="63" t="n">
+      <c r="E5" s="62" t="n">
         <v>0.11</v>
       </c>
       <c r="G5" s="30" t="n">
@@ -9572,18 +9565,18 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="I5" s="35" t="inlineStr">
+      <c r="I5" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J5" s="47" t="n">
+      <c r="J5" s="46" t="n">
         <v>18929.1</v>
       </c>
-      <c r="K5" s="64" t="n">
+      <c r="K5" s="63" t="n">
         <v>218646.7</v>
       </c>
-      <c r="L5" s="63" t="n">
+      <c r="L5" s="62" t="n">
         <v>1.39</v>
       </c>
       <c r="N5" s="30" t="n">
@@ -9594,18 +9587,18 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="P5" s="35" t="inlineStr">
+      <c r="P5" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q5" s="60" t="n">
+      <c r="Q5" s="59" t="n">
         <v>-23343.8</v>
       </c>
-      <c r="R5" s="64" t="n">
+      <c r="R5" s="63" t="n">
         <v>202373.3</v>
       </c>
-      <c r="S5" s="63" t="n">
+      <c r="S5" s="62" t="n">
         <v>1.61</v>
       </c>
     </row>
@@ -9618,15 +9611,15 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="C6" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D6" s="62" t="n">
+      <c r="D6" s="61" t="n">
         <v>9931</v>
       </c>
-      <c r="E6" s="63" t="n">
+      <c r="E6" s="62" t="n">
         <v>0.06</v>
       </c>
       <c r="G6" s="30" t="n">
@@ -9637,18 +9630,18 @@
           <t>현대모비스</t>
         </is>
       </c>
-      <c r="I6" s="43" t="inlineStr">
+      <c r="I6" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="J6" s="47" t="n">
+      <c r="J6" s="46" t="n">
         <v>3387.4</v>
       </c>
-      <c r="K6" s="64" t="n">
+      <c r="K6" s="63" t="n">
         <v>8326.6</v>
       </c>
-      <c r="L6" s="63" t="n">
+      <c r="L6" s="62" t="n">
         <v>2.48</v>
       </c>
       <c r="N6" s="30" t="n">
@@ -9659,18 +9652,18 @@
           <t>HD현대중공업</t>
         </is>
       </c>
-      <c r="P6" s="43" t="inlineStr">
+      <c r="P6" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q6" s="60" t="n">
+      <c r="Q6" s="59" t="n">
         <v>-2385.4</v>
       </c>
-      <c r="R6" s="64" t="n">
+      <c r="R6" s="63" t="n">
         <v>25550.3</v>
       </c>
-      <c r="S6" s="63" t="n">
+      <c r="S6" s="62" t="n">
         <v>6.09</v>
       </c>
     </row>
@@ -9683,15 +9676,15 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="C7" s="35" t="inlineStr">
+      <c r="C7" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D7" s="62" t="n">
+      <c r="D7" s="61" t="n">
         <v>2690</v>
       </c>
-      <c r="E7" s="63" t="n">
+      <c r="E7" s="62" t="n">
         <v>0.52</v>
       </c>
       <c r="G7" s="30" t="n">
@@ -9702,18 +9695,18 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="I7" s="35" t="inlineStr">
+      <c r="I7" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J7" s="47" t="n">
+      <c r="J7" s="46" t="n">
         <v>2945.2</v>
       </c>
-      <c r="K7" s="64" t="n">
+      <c r="K7" s="63" t="n">
         <v>35913.1</v>
       </c>
-      <c r="L7" s="63" t="n">
+      <c r="L7" s="62" t="n">
         <v>3.93</v>
       </c>
       <c r="N7" s="30" t="n">
@@ -9724,14 +9717,14 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="P7" s="35" t="inlineStr"/>
-      <c r="Q7" s="60" t="n">
+      <c r="P7" s="34" t="inlineStr"/>
+      <c r="Q7" s="59" t="n">
         <v>-907.3</v>
       </c>
-      <c r="R7" s="64" t="n">
+      <c r="R7" s="63" t="n">
         <v>28562</v>
       </c>
-      <c r="S7" s="63" t="n">
+      <c r="S7" s="62" t="n">
         <v>4.18</v>
       </c>
     </row>
@@ -9744,15 +9737,15 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="C8" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D8" s="62" t="n">
+      <c r="D8" s="61" t="n">
         <v>2272</v>
       </c>
-      <c r="E8" s="63" t="n">
+      <c r="E8" s="62" t="n">
         <v>0.15</v>
       </c>
       <c r="G8" s="30" t="n">
@@ -9763,18 +9756,18 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="I8" s="35" t="inlineStr">
+      <c r="I8" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="J8" s="47" t="n">
+      <c r="J8" s="46" t="n">
         <v>2933.8</v>
       </c>
-      <c r="K8" s="64" t="n">
+      <c r="K8" s="63" t="n">
         <v>52517.2</v>
       </c>
-      <c r="L8" s="63" t="n">
+      <c r="L8" s="62" t="n">
         <v>20.83</v>
       </c>
       <c r="N8" s="30" t="n">
@@ -9785,18 +9778,18 @@
           <t>한국항공우주</t>
         </is>
       </c>
-      <c r="P8" s="43" t="inlineStr">
+      <c r="P8" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q8" s="60" t="n">
+      <c r="Q8" s="59" t="n">
         <v>-800.3</v>
       </c>
-      <c r="R8" s="64" t="n">
+      <c r="R8" s="63" t="n">
         <v>13808</v>
       </c>
-      <c r="S8" s="63" t="n">
+      <c r="S8" s="62" t="n">
         <v>11.63</v>
       </c>
     </row>
@@ -9809,15 +9802,15 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="C9" s="35" t="inlineStr">
+      <c r="C9" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D9" s="62" t="n">
+      <c r="D9" s="61" t="n">
         <v>1855</v>
       </c>
-      <c r="E9" s="63" t="n">
+      <c r="E9" s="62" t="n">
         <v>0.74</v>
       </c>
       <c r="G9" s="30" t="n">
@@ -9828,14 +9821,14 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="I9" s="35" t="inlineStr"/>
-      <c r="J9" s="47" t="n">
+      <c r="I9" s="34" t="inlineStr"/>
+      <c r="J9" s="46" t="n">
         <v>2847.6</v>
       </c>
-      <c r="K9" s="64" t="n">
+      <c r="K9" s="63" t="n">
         <v>27382.6</v>
       </c>
-      <c r="L9" s="63" t="n">
+      <c r="L9" s="62" t="n">
         <v>1.72</v>
       </c>
       <c r="N9" s="30" t="n">
@@ -9846,18 +9839,18 @@
           <t>삼성바이오로직스</t>
         </is>
       </c>
-      <c r="P9" s="35" t="inlineStr">
+      <c r="P9" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="Q9" s="60" t="n">
+      <c r="Q9" s="59" t="n">
         <v>-794.2</v>
       </c>
-      <c r="R9" s="64" t="n">
+      <c r="R9" s="63" t="n">
         <v>8488.700000000001</v>
       </c>
-      <c r="S9" s="63" t="n">
+      <c r="S9" s="62" t="n">
         <v>1.44</v>
       </c>
     </row>
@@ -9870,15 +9863,15 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="C10" s="35" t="inlineStr">
+      <c r="C10" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D10" s="62" t="n">
+      <c r="D10" s="61" t="n">
         <v>1622</v>
       </c>
-      <c r="E10" s="63" t="n">
+      <c r="E10" s="62" t="n">
         <v>0.18</v>
       </c>
       <c r="G10" s="30" t="n">
@@ -9889,18 +9882,18 @@
           <t>삼양식품</t>
         </is>
       </c>
-      <c r="I10" s="35" t="inlineStr">
+      <c r="I10" s="34" t="inlineStr">
         <is>
           <t>음식료·담배</t>
         </is>
       </c>
-      <c r="J10" s="47" t="n">
+      <c r="J10" s="46" t="n">
         <v>2317.4</v>
       </c>
-      <c r="K10" s="64" t="n">
+      <c r="K10" s="63" t="n">
         <v>9495.4</v>
       </c>
-      <c r="L10" s="63" t="n">
+      <c r="L10" s="62" t="n">
         <v>10.36</v>
       </c>
       <c r="N10" s="30" t="n">
@@ -9911,18 +9904,18 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="P10" s="43" t="inlineStr">
+      <c r="P10" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q10" s="60" t="n">
+      <c r="Q10" s="59" t="n">
         <v>-583.6</v>
       </c>
-      <c r="R10" s="64" t="n">
+      <c r="R10" s="63" t="n">
         <v>12458</v>
       </c>
-      <c r="S10" s="63" t="n">
+      <c r="S10" s="62" t="n">
         <v>2.49</v>
       </c>
     </row>
@@ -9935,11 +9928,11 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="C11" s="35" t="inlineStr"/>
-      <c r="D11" s="62" t="n">
+      <c r="C11" s="34" t="inlineStr"/>
+      <c r="D11" s="61" t="n">
         <v>1519</v>
       </c>
-      <c r="E11" s="63" t="n">
+      <c r="E11" s="62" t="n">
         <v>0.22</v>
       </c>
       <c r="G11" s="30" t="n">
@@ -9950,18 +9943,18 @@
           <t>에코프로</t>
         </is>
       </c>
-      <c r="I11" s="35" t="inlineStr">
+      <c r="I11" s="34" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="J11" s="47" t="n">
+      <c r="J11" s="46" t="n">
         <v>2255.8</v>
       </c>
-      <c r="K11" s="64" t="n">
+      <c r="K11" s="63" t="n">
         <v>19712.3</v>
       </c>
-      <c r="L11" s="63" t="n">
+      <c r="L11" s="62" t="n">
         <v>15.8</v>
       </c>
       <c r="N11" s="30" t="n">
@@ -9972,18 +9965,18 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="P11" s="35" t="inlineStr">
+      <c r="P11" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q11" s="60" t="n">
+      <c r="Q11" s="59" t="n">
         <v>-549.4</v>
       </c>
-      <c r="R11" s="64" t="n">
+      <c r="R11" s="63" t="n">
         <v>9135.6</v>
       </c>
-      <c r="S11" s="63" t="n">
+      <c r="S11" s="62" t="n">
         <v>2.7</v>
       </c>
     </row>
@@ -9996,15 +9989,15 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="C12" s="35" t="inlineStr">
+      <c r="C12" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D12" s="62" t="n">
+      <c r="D12" s="61" t="n">
         <v>1390</v>
       </c>
-      <c r="E12" s="63" t="n">
+      <c r="E12" s="62" t="n">
         <v>0.41</v>
       </c>
       <c r="G12" s="30" t="n">
@@ -10015,18 +10008,18 @@
           <t>주성엔지니어링</t>
         </is>
       </c>
-      <c r="I12" s="35" t="inlineStr">
+      <c r="I12" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="J12" s="47" t="n">
+      <c r="J12" s="46" t="n">
         <v>1944.9</v>
       </c>
-      <c r="K12" s="64" t="n">
+      <c r="K12" s="63" t="n">
         <v>19079.1</v>
       </c>
-      <c r="L12" s="63" t="n">
+      <c r="L12" s="62" t="n">
         <v>16.58</v>
       </c>
       <c r="N12" s="30" t="n">
@@ -10037,18 +10030,18 @@
           <t>삼성에스디에스</t>
         </is>
       </c>
-      <c r="P12" s="35" t="inlineStr">
+      <c r="P12" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="Q12" s="60" t="n">
+      <c r="Q12" s="59" t="n">
         <v>-415.5</v>
       </c>
-      <c r="R12" s="64" t="n">
+      <c r="R12" s="63" t="n">
         <v>4930.2</v>
       </c>
-      <c r="S12" s="63" t="n">
+      <c r="S12" s="62" t="n">
         <v>3.08</v>
       </c>
     </row>
@@ -10061,15 +10054,15 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="C13" s="35" t="inlineStr">
+      <c r="C13" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D13" s="62" t="n">
+      <c r="D13" s="61" t="n">
         <v>1354</v>
       </c>
-      <c r="E13" s="63" t="n">
+      <c r="E13" s="62" t="n">
         <v>0.11</v>
       </c>
       <c r="G13" s="30" t="n">
@@ -10080,18 +10073,18 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="I13" s="35" t="inlineStr">
+      <c r="I13" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J13" s="47" t="n">
+      <c r="J13" s="46" t="n">
         <v>1590.6</v>
       </c>
-      <c r="K13" s="64" t="n">
+      <c r="K13" s="63" t="n">
         <v>38072.8</v>
       </c>
-      <c r="L13" s="63" t="n">
+      <c r="L13" s="62" t="n">
         <v>3.18</v>
       </c>
       <c r="N13" s="30" t="n">
@@ -10102,18 +10095,18 @@
           <t>한화오션</t>
         </is>
       </c>
-      <c r="P13" s="43" t="inlineStr">
+      <c r="P13" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q13" s="60" t="n">
+      <c r="Q13" s="59" t="n">
         <v>-396.1</v>
       </c>
-      <c r="R13" s="64" t="n">
+      <c r="R13" s="63" t="n">
         <v>6786.8</v>
       </c>
-      <c r="S13" s="63" t="n">
+      <c r="S13" s="62" t="n">
         <v>2.99</v>
       </c>
     </row>
@@ -10126,15 +10119,15 @@
           <t>주성엔지니어링</t>
         </is>
       </c>
-      <c r="C14" s="35" t="inlineStr">
+      <c r="C14" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D14" s="62" t="n">
+      <c r="D14" s="61" t="n">
         <v>1256</v>
       </c>
-      <c r="E14" s="63" t="n">
+      <c r="E14" s="62" t="n">
         <v>1.09</v>
       </c>
       <c r="G14" s="30" t="n">
@@ -10145,18 +10138,18 @@
           <t>HLB</t>
         </is>
       </c>
-      <c r="I14" s="35" t="inlineStr">
+      <c r="I14" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="J14" s="47" t="n">
+      <c r="J14" s="46" t="n">
         <v>1413.7</v>
       </c>
-      <c r="K14" s="64" t="n">
+      <c r="K14" s="63" t="n">
         <v>7584.7</v>
       </c>
-      <c r="L14" s="63" t="n">
+      <c r="L14" s="62" t="n">
         <v>12.41</v>
       </c>
       <c r="N14" s="30" t="n">
@@ -10167,24 +10160,24 @@
           <t>DB손해보험</t>
         </is>
       </c>
-      <c r="P14" s="35" t="inlineStr">
+      <c r="P14" s="34" t="inlineStr">
         <is>
           <t>보험</t>
         </is>
       </c>
-      <c r="Q14" s="60" t="n">
+      <c r="Q14" s="59" t="n">
         <v>-394.9</v>
       </c>
-      <c r="R14" s="64" t="n">
+      <c r="R14" s="63" t="n">
         <v>2387.2</v>
       </c>
-      <c r="S14" s="63" t="n">
+      <c r="S14" s="62" t="n">
         <v>1.95</v>
       </c>
     </row>
     <row r="15"/>
     <row r="16" ht="31" customHeight="1" s="15">
-      <c r="A16" s="61" t="inlineStr">
+      <c r="A16" s="60" t="inlineStr">
         <is>
           <t>랭킹 유니버스(순매수 상위 30 등재 종목) 한정 · 대차 증감=전월말 대비 최신 잔고 · 시총대비(%)=공매도 누적 금액÷시가총액, 대차잔고÷시가총액(KIS 마스터 시총(주 1회 갱신))</t>
         </is>
@@ -10277,77 +10270,77 @@
       <c r="O3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="45" t="inlineStr">
+      <c r="A4" s="44" t="inlineStr">
         <is>
           <t>업종</t>
         </is>
       </c>
-      <c r="B4" s="45" t="inlineStr">
+      <c r="B4" s="44" t="inlineStr">
         <is>
           <t>YTD</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="44" t="inlineStr">
         <is>
           <t>6M</t>
         </is>
       </c>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="D4" s="44" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="E4" s="45" t="inlineStr">
+      <c r="E4" s="44" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="F4" s="45" t="inlineStr">
+      <c r="F4" s="44" t="inlineStr">
         <is>
           <t>외인</t>
         </is>
       </c>
-      <c r="G4" s="45" t="inlineStr">
+      <c r="G4" s="44" t="inlineStr">
         <is>
           <t>기관(합)</t>
         </is>
       </c>
-      <c r="H4" s="45" t="inlineStr">
+      <c r="H4" s="44" t="inlineStr">
         <is>
           <t>외인+기관</t>
         </is>
       </c>
-      <c r="I4" s="45" t="inlineStr">
+      <c r="I4" s="44" t="inlineStr">
         <is>
           <t>금융투자</t>
         </is>
       </c>
-      <c r="J4" s="45" t="inlineStr">
+      <c r="J4" s="44" t="inlineStr">
         <is>
           <t>투신(사모)</t>
         </is>
       </c>
-      <c r="K4" s="45" t="inlineStr">
+      <c r="K4" s="44" t="inlineStr">
         <is>
           <t>연기금</t>
         </is>
       </c>
-      <c r="L4" s="45" t="inlineStr">
+      <c r="L4" s="44" t="inlineStr">
         <is>
           <t>보험</t>
         </is>
       </c>
-      <c r="M4" s="45" t="inlineStr">
+      <c r="M4" s="44" t="inlineStr">
         <is>
           <t>개인</t>
         </is>
       </c>
-      <c r="N4" s="45" t="inlineStr">
+      <c r="N4" s="44" t="inlineStr">
         <is>
           <t>기타법인</t>
         </is>
       </c>
-      <c r="O4" s="45" t="inlineStr">
+      <c r="O4" s="44" t="inlineStr">
         <is>
           <t>신호</t>
         </is>
@@ -10359,46 +10352,46 @@
           <t>의료·정밀기기</t>
         </is>
       </c>
-      <c r="B5" s="65" t="n">
+      <c r="B5" s="64" t="n">
         <v>51.3</v>
       </c>
-      <c r="C5" s="65" t="n">
+      <c r="C5" s="64" t="n">
         <v>41</v>
       </c>
-      <c r="D5" s="65" t="n">
+      <c r="D5" s="64" t="n">
         <v>37.51</v>
       </c>
-      <c r="E5" s="65" t="n">
+      <c r="E5" s="64" t="n">
         <v>19.03</v>
       </c>
-      <c r="F5" s="66" t="n">
+      <c r="F5" s="65" t="n">
         <v>444</v>
       </c>
-      <c r="G5" s="67" t="n">
+      <c r="G5" s="66" t="n">
         <v>-15</v>
       </c>
-      <c r="H5" s="66" t="n">
+      <c r="H5" s="65" t="n">
         <v>429</v>
       </c>
-      <c r="I5" s="66" t="n">
+      <c r="I5" s="65" t="n">
         <v>11</v>
       </c>
-      <c r="J5" s="66" t="n">
+      <c r="J5" s="65" t="n">
         <v>19</v>
       </c>
-      <c r="K5" s="67" t="n">
+      <c r="K5" s="66" t="n">
         <v>-45</v>
       </c>
-      <c r="L5" s="66" t="n">
+      <c r="L5" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="M5" s="67" t="n">
+      <c r="M5" s="66" t="n">
         <v>-417</v>
       </c>
-      <c r="N5" s="67" t="n">
+      <c r="N5" s="66" t="n">
         <v>-12</v>
       </c>
-      <c r="O5" s="58" t="inlineStr">
+      <c r="O5" s="57" t="inlineStr">
         <is>
           <t>동반강세</t>
         </is>
@@ -10410,43 +10403,43 @@
           <t>섬유·의류</t>
         </is>
       </c>
-      <c r="B6" s="68" t="n">
+      <c r="B6" s="67" t="n">
         <v>-1.49</v>
       </c>
-      <c r="C6" s="68" t="n">
+      <c r="C6" s="67" t="n">
         <v>-1.4</v>
       </c>
-      <c r="D6" s="68" t="n">
+      <c r="D6" s="67" t="n">
         <v>-2.14</v>
       </c>
-      <c r="E6" s="65" t="n">
+      <c r="E6" s="64" t="n">
         <v>4.43</v>
       </c>
-      <c r="F6" s="66" t="n">
+      <c r="F6" s="65" t="n">
         <v>11</v>
       </c>
-      <c r="G6" s="67" t="n">
+      <c r="G6" s="66" t="n">
         <v>-8</v>
       </c>
-      <c r="H6" s="66" t="n">
+      <c r="H6" s="65" t="n">
         <v>3</v>
       </c>
-      <c r="I6" s="66" t="n">
+      <c r="I6" s="65" t="n">
         <v>6</v>
       </c>
-      <c r="J6" s="66" t="n">
+      <c r="J6" s="65" t="n">
         <v>3</v>
       </c>
-      <c r="K6" s="67" t="n">
+      <c r="K6" s="66" t="n">
         <v>-14</v>
       </c>
-      <c r="L6" s="67" t="n">
+      <c r="L6" s="66" t="n">
         <v>-3</v>
       </c>
-      <c r="M6" s="67" t="n">
+      <c r="M6" s="66" t="n">
         <v>-62</v>
       </c>
-      <c r="N6" s="66" t="n">
+      <c r="N6" s="65" t="n">
         <v>59</v>
       </c>
       <c r="O6" s="30" t="inlineStr"/>
@@ -10457,46 +10450,46 @@
           <t>화학</t>
         </is>
       </c>
-      <c r="B7" s="65" t="n">
+      <c r="B7" s="64" t="n">
         <v>22.47</v>
       </c>
-      <c r="C7" s="65" t="n">
+      <c r="C7" s="64" t="n">
         <v>2.05</v>
       </c>
-      <c r="D7" s="65" t="n">
+      <c r="D7" s="64" t="n">
         <v>14.15</v>
       </c>
-      <c r="E7" s="65" t="n">
+      <c r="E7" s="64" t="n">
         <v>3.85</v>
       </c>
-      <c r="F7" s="66" t="n">
+      <c r="F7" s="65" t="n">
         <v>914</v>
       </c>
-      <c r="G7" s="66" t="n">
+      <c r="G7" s="65" t="n">
         <v>2380</v>
       </c>
-      <c r="H7" s="66" t="n">
+      <c r="H7" s="65" t="n">
         <v>3295</v>
       </c>
-      <c r="I7" s="66" t="n">
+      <c r="I7" s="65" t="n">
         <v>647</v>
       </c>
-      <c r="J7" s="66" t="n">
+      <c r="J7" s="65" t="n">
         <v>642</v>
       </c>
-      <c r="K7" s="66" t="n">
+      <c r="K7" s="65" t="n">
         <v>1050</v>
       </c>
-      <c r="L7" s="66" t="n">
+      <c r="L7" s="65" t="n">
         <v>47</v>
       </c>
-      <c r="M7" s="67" t="n">
+      <c r="M7" s="66" t="n">
         <v>-3340</v>
       </c>
-      <c r="N7" s="66" t="n">
+      <c r="N7" s="65" t="n">
         <v>46</v>
       </c>
-      <c r="O7" s="58" t="inlineStr">
+      <c r="O7" s="57" t="inlineStr">
         <is>
           <t>동반강세</t>
         </is>
@@ -10508,46 +10501,46 @@
           <t>오락·문화</t>
         </is>
       </c>
-      <c r="B8" s="68" t="n">
+      <c r="B8" s="67" t="n">
         <v>-44.2</v>
       </c>
-      <c r="C8" s="68" t="n">
+      <c r="C8" s="67" t="n">
         <v>-29.91</v>
       </c>
-      <c r="D8" s="68" t="n">
+      <c r="D8" s="67" t="n">
         <v>-20.22</v>
       </c>
-      <c r="E8" s="65" t="n">
+      <c r="E8" s="64" t="n">
         <v>2.56</v>
       </c>
-      <c r="F8" s="66" t="n">
+      <c r="F8" s="65" t="n">
         <v>45</v>
       </c>
-      <c r="G8" s="66" t="n">
+      <c r="G8" s="65" t="n">
         <v>107</v>
       </c>
-      <c r="H8" s="66" t="n">
+      <c r="H8" s="65" t="n">
         <v>152</v>
       </c>
-      <c r="I8" s="67" t="n">
+      <c r="I8" s="66" t="n">
         <v>-80</v>
       </c>
-      <c r="J8" s="66" t="n">
+      <c r="J8" s="65" t="n">
         <v>112</v>
       </c>
-      <c r="K8" s="66" t="n">
+      <c r="K8" s="65" t="n">
         <v>73</v>
       </c>
-      <c r="L8" s="66" t="n">
+      <c r="L8" s="65" t="n">
         <v>4</v>
       </c>
-      <c r="M8" s="67" t="n">
+      <c r="M8" s="66" t="n">
         <v>-147</v>
       </c>
-      <c r="N8" s="67" t="n">
+      <c r="N8" s="66" t="n">
         <v>-5</v>
       </c>
-      <c r="O8" s="69" t="inlineStr">
+      <c r="O8" s="68" t="inlineStr">
         <is>
           <t>수급유입</t>
         </is>
@@ -10559,43 +10552,43 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="B9" s="68" t="n">
+      <c r="B9" s="67" t="n">
         <v>-10.48</v>
       </c>
-      <c r="C9" s="68" t="n">
+      <c r="C9" s="67" t="n">
         <v>-14.05</v>
       </c>
-      <c r="D9" s="65" t="n">
+      <c r="D9" s="64" t="n">
         <v>1.15</v>
       </c>
-      <c r="E9" s="65" t="n">
+      <c r="E9" s="64" t="n">
         <v>0.14</v>
       </c>
-      <c r="F9" s="67" t="n">
+      <c r="F9" s="66" t="n">
         <v>-24</v>
       </c>
-      <c r="G9" s="66" t="n">
+      <c r="G9" s="65" t="n">
         <v>45</v>
       </c>
-      <c r="H9" s="66" t="n">
+      <c r="H9" s="65" t="n">
         <v>21</v>
       </c>
-      <c r="I9" s="66" t="n">
+      <c r="I9" s="65" t="n">
         <v>70</v>
       </c>
-      <c r="J9" s="67" t="n">
+      <c r="J9" s="66" t="n">
         <v>-33</v>
       </c>
-      <c r="K9" s="66" t="n">
+      <c r="K9" s="65" t="n">
         <v>16</v>
       </c>
-      <c r="L9" s="67" t="n">
+      <c r="L9" s="66" t="n">
         <v>-8</v>
       </c>
-      <c r="M9" s="67" t="n">
+      <c r="M9" s="66" t="n">
         <v>-19</v>
       </c>
-      <c r="N9" s="67" t="n">
+      <c r="N9" s="66" t="n">
         <v>-2</v>
       </c>
       <c r="O9" s="30" t="inlineStr"/>
@@ -10606,43 +10599,43 @@
           <t>음식료·담배</t>
         </is>
       </c>
-      <c r="B10" s="65" t="n">
+      <c r="B10" s="64" t="n">
         <v>2.86</v>
       </c>
-      <c r="C10" s="68" t="n">
+      <c r="C10" s="67" t="n">
         <v>-1</v>
       </c>
-      <c r="D10" s="68" t="n">
+      <c r="D10" s="67" t="n">
         <v>-3.59</v>
       </c>
-      <c r="E10" s="68" t="n">
+      <c r="E10" s="67" t="n">
         <v>-0.54</v>
       </c>
-      <c r="F10" s="67" t="n">
+      <c r="F10" s="66" t="n">
         <v>-73</v>
       </c>
-      <c r="G10" s="67" t="n">
+      <c r="G10" s="66" t="n">
         <v>-15</v>
       </c>
-      <c r="H10" s="67" t="n">
+      <c r="H10" s="66" t="n">
         <v>-89</v>
       </c>
-      <c r="I10" s="67" t="n">
+      <c r="I10" s="66" t="n">
         <v>-5</v>
       </c>
-      <c r="J10" s="67" t="n">
+      <c r="J10" s="66" t="n">
         <v>-129</v>
       </c>
-      <c r="K10" s="66" t="n">
+      <c r="K10" s="65" t="n">
         <v>139</v>
       </c>
-      <c r="L10" s="67" t="n">
+      <c r="L10" s="66" t="n">
         <v>-26</v>
       </c>
-      <c r="M10" s="67" t="n">
+      <c r="M10" s="66" t="n">
         <v>-130</v>
       </c>
-      <c r="N10" s="66" t="n">
+      <c r="N10" s="65" t="n">
         <v>219</v>
       </c>
       <c r="O10" s="30" t="inlineStr"/>
@@ -10653,43 +10646,43 @@
           <t>비금속</t>
         </is>
       </c>
-      <c r="B11" s="68" t="n">
+      <c r="B11" s="67" t="n">
         <v>-15.1</v>
       </c>
-      <c r="C11" s="68" t="n">
+      <c r="C11" s="67" t="n">
         <v>-18.29</v>
       </c>
-      <c r="D11" s="68" t="n">
+      <c r="D11" s="67" t="n">
         <v>-3.05</v>
       </c>
-      <c r="E11" s="68" t="n">
+      <c r="E11" s="67" t="n">
         <v>-0.78</v>
       </c>
-      <c r="F11" s="67" t="n">
+      <c r="F11" s="66" t="n">
         <v>-2</v>
       </c>
-      <c r="G11" s="70" t="n">
+      <c r="G11" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="67" t="n">
+      <c r="H11" s="66" t="n">
         <v>-3</v>
       </c>
-      <c r="I11" s="66" t="n">
+      <c r="I11" s="65" t="n">
         <v>5</v>
       </c>
-      <c r="J11" s="70" t="n">
+      <c r="J11" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="67" t="n">
+      <c r="K11" s="66" t="n">
         <v>-5</v>
       </c>
-      <c r="L11" s="70" t="n">
+      <c r="L11" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="M11" s="66" t="n">
+      <c r="M11" s="65" t="n">
         <v>3</v>
       </c>
-      <c r="N11" s="70" t="n">
+      <c r="N11" s="69" t="n">
         <v>0</v>
       </c>
       <c r="O11" s="30" t="inlineStr"/>
@@ -10700,43 +10693,43 @@
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="B12" s="65" t="n">
+      <c r="B12" s="64" t="n">
         <v>4.23</v>
       </c>
-      <c r="C12" s="68" t="n">
+      <c r="C12" s="67" t="n">
         <v>-7</v>
       </c>
-      <c r="D12" s="65" t="n">
+      <c r="D12" s="64" t="n">
         <v>8.359999999999999</v>
       </c>
-      <c r="E12" s="68" t="n">
+      <c r="E12" s="67" t="n">
         <v>-0.83</v>
       </c>
-      <c r="F12" s="67" t="n">
+      <c r="F12" s="66" t="n">
         <v>-106</v>
       </c>
-      <c r="G12" s="67" t="n">
+      <c r="G12" s="66" t="n">
         <v>-164</v>
       </c>
-      <c r="H12" s="67" t="n">
+      <c r="H12" s="66" t="n">
         <v>-270</v>
       </c>
-      <c r="I12" s="66" t="n">
+      <c r="I12" s="65" t="n">
         <v>96</v>
       </c>
-      <c r="J12" s="67" t="n">
+      <c r="J12" s="66" t="n">
         <v>-67</v>
       </c>
-      <c r="K12" s="67" t="n">
+      <c r="K12" s="66" t="n">
         <v>-176</v>
       </c>
-      <c r="L12" s="67" t="n">
+      <c r="L12" s="66" t="n">
         <v>-16</v>
       </c>
-      <c r="M12" s="66" t="n">
+      <c r="M12" s="65" t="n">
         <v>221</v>
       </c>
-      <c r="N12" s="66" t="n">
+      <c r="N12" s="65" t="n">
         <v>49</v>
       </c>
       <c r="O12" s="30" t="inlineStr"/>
@@ -10747,43 +10740,43 @@
           <t>통신</t>
         </is>
       </c>
-      <c r="B13" s="65" t="n">
+      <c r="B13" s="64" t="n">
         <v>21.84</v>
       </c>
-      <c r="C13" s="68" t="n">
+      <c r="C13" s="67" t="n">
         <v>-9.789999999999999</v>
       </c>
-      <c r="D13" s="68" t="n">
+      <c r="D13" s="67" t="n">
         <v>-2.51</v>
       </c>
-      <c r="E13" s="68" t="n">
+      <c r="E13" s="67" t="n">
         <v>-1.13</v>
       </c>
-      <c r="F13" s="66" t="n">
+      <c r="F13" s="65" t="n">
         <v>225</v>
       </c>
-      <c r="G13" s="67" t="n">
+      <c r="G13" s="66" t="n">
         <v>-227</v>
       </c>
-      <c r="H13" s="67" t="n">
+      <c r="H13" s="66" t="n">
         <v>-2</v>
       </c>
-      <c r="I13" s="67" t="n">
+      <c r="I13" s="66" t="n">
         <v>-160</v>
       </c>
-      <c r="J13" s="66" t="n">
+      <c r="J13" s="65" t="n">
         <v>121</v>
       </c>
-      <c r="K13" s="67" t="n">
+      <c r="K13" s="66" t="n">
         <v>-168</v>
       </c>
-      <c r="L13" s="67" t="n">
+      <c r="L13" s="66" t="n">
         <v>-19</v>
       </c>
-      <c r="M13" s="66" t="n">
+      <c r="M13" s="65" t="n">
         <v>14</v>
       </c>
-      <c r="N13" s="67" t="n">
+      <c r="N13" s="66" t="n">
         <v>-13</v>
       </c>
       <c r="O13" s="30" t="inlineStr"/>
@@ -10794,43 +10787,43 @@
           <t>종이·목재</t>
         </is>
       </c>
-      <c r="B14" s="68" t="n">
+      <c r="B14" s="67" t="n">
         <v>-24.1</v>
       </c>
-      <c r="C14" s="68" t="n">
+      <c r="C14" s="67" t="n">
         <v>-24.32</v>
       </c>
-      <c r="D14" s="68" t="n">
+      <c r="D14" s="67" t="n">
         <v>-2.17</v>
       </c>
-      <c r="E14" s="68" t="n">
+      <c r="E14" s="67" t="n">
         <v>-1.37</v>
       </c>
-      <c r="F14" s="67" t="n">
+      <c r="F14" s="66" t="n">
         <v>-2</v>
       </c>
-      <c r="G14" s="66" t="n">
+      <c r="G14" s="65" t="n">
         <v>4</v>
       </c>
-      <c r="H14" s="66" t="n">
+      <c r="H14" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="66" t="n">
+      <c r="I14" s="65" t="n">
         <v>4</v>
       </c>
-      <c r="J14" s="70" t="n">
+      <c r="J14" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="K14" s="70" t="n">
+      <c r="K14" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="70" t="n">
+      <c r="L14" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="M14" s="66" t="n">
+      <c r="M14" s="65" t="n">
         <v>6</v>
       </c>
-      <c r="N14" s="67" t="n">
+      <c r="N14" s="66" t="n">
         <v>-8</v>
       </c>
       <c r="O14" s="30" t="inlineStr"/>
@@ -10841,46 +10834,46 @@
           <t>전기·가스</t>
         </is>
       </c>
-      <c r="B15" s="68" t="n">
+      <c r="B15" s="67" t="n">
         <v>-31.19</v>
       </c>
-      <c r="C15" s="68" t="n">
+      <c r="C15" s="67" t="n">
         <v>-28.09</v>
       </c>
-      <c r="D15" s="68" t="n">
+      <c r="D15" s="67" t="n">
         <v>-15.01</v>
       </c>
-      <c r="E15" s="68" t="n">
+      <c r="E15" s="67" t="n">
         <v>-1.91</v>
       </c>
-      <c r="F15" s="67" t="n">
+      <c r="F15" s="66" t="n">
         <v>-233</v>
       </c>
-      <c r="G15" s="66" t="n">
+      <c r="G15" s="65" t="n">
         <v>31</v>
       </c>
-      <c r="H15" s="67" t="n">
+      <c r="H15" s="66" t="n">
         <v>-202</v>
       </c>
-      <c r="I15" s="66" t="n">
+      <c r="I15" s="65" t="n">
         <v>68</v>
       </c>
-      <c r="J15" s="66" t="n">
+      <c r="J15" s="65" t="n">
         <v>69</v>
       </c>
-      <c r="K15" s="67" t="n">
+      <c r="K15" s="66" t="n">
         <v>-94</v>
       </c>
-      <c r="L15" s="67" t="n">
+      <c r="L15" s="66" t="n">
         <v>-9</v>
       </c>
-      <c r="M15" s="66" t="n">
+      <c r="M15" s="65" t="n">
         <v>196</v>
       </c>
-      <c r="N15" s="66" t="n">
+      <c r="N15" s="65" t="n">
         <v>5</v>
       </c>
-      <c r="O15" s="59" t="inlineStr">
+      <c r="O15" s="58" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -10892,43 +10885,43 @@
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="B16" s="65" t="n">
+      <c r="B16" s="64" t="n">
         <v>7.47</v>
       </c>
-      <c r="C16" s="68" t="n">
+      <c r="C16" s="67" t="n">
         <v>-2.62</v>
       </c>
-      <c r="D16" s="65" t="n">
+      <c r="D16" s="64" t="n">
         <v>3.53</v>
       </c>
-      <c r="E16" s="68" t="n">
+      <c r="E16" s="67" t="n">
         <v>-2.35</v>
       </c>
-      <c r="F16" s="66" t="n">
+      <c r="F16" s="65" t="n">
         <v>478</v>
       </c>
-      <c r="G16" s="67" t="n">
+      <c r="G16" s="66" t="n">
         <v>-537</v>
       </c>
-      <c r="H16" s="67" t="n">
+      <c r="H16" s="66" t="n">
         <v>-59</v>
       </c>
-      <c r="I16" s="67" t="n">
+      <c r="I16" s="66" t="n">
         <v>-480</v>
       </c>
-      <c r="J16" s="66" t="n">
+      <c r="J16" s="65" t="n">
         <v>54</v>
       </c>
-      <c r="K16" s="67" t="n">
+      <c r="K16" s="66" t="n">
         <v>-76</v>
       </c>
-      <c r="L16" s="67" t="n">
+      <c r="L16" s="66" t="n">
         <v>-35</v>
       </c>
-      <c r="M16" s="66" t="n">
+      <c r="M16" s="65" t="n">
         <v>22</v>
       </c>
-      <c r="N16" s="66" t="n">
+      <c r="N16" s="65" t="n">
         <v>37</v>
       </c>
       <c r="O16" s="30" t="inlineStr"/>
@@ -10939,43 +10932,43 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="B17" s="65" t="n">
+      <c r="B17" s="64" t="n">
         <v>10.19</v>
       </c>
-      <c r="C17" s="68" t="n">
+      <c r="C17" s="67" t="n">
         <v>-19.81</v>
       </c>
-      <c r="D17" s="65" t="n">
+      <c r="D17" s="64" t="n">
         <v>6.7</v>
       </c>
-      <c r="E17" s="68" t="n">
+      <c r="E17" s="67" t="n">
         <v>-2.59</v>
       </c>
-      <c r="F17" s="67" t="n">
+      <c r="F17" s="66" t="n">
         <v>-2414</v>
       </c>
-      <c r="G17" s="67" t="n">
+      <c r="G17" s="66" t="n">
         <v>-667</v>
       </c>
-      <c r="H17" s="67" t="n">
+      <c r="H17" s="66" t="n">
         <v>-3081</v>
       </c>
-      <c r="I17" s="66" t="n">
+      <c r="I17" s="65" t="n">
         <v>1474</v>
       </c>
-      <c r="J17" s="67" t="n">
+      <c r="J17" s="66" t="n">
         <v>-1982</v>
       </c>
-      <c r="K17" s="67" t="n">
+      <c r="K17" s="66" t="n">
         <v>-21</v>
       </c>
-      <c r="L17" s="67" t="n">
+      <c r="L17" s="66" t="n">
         <v>-114</v>
       </c>
-      <c r="M17" s="66" t="n">
+      <c r="M17" s="65" t="n">
         <v>3147</v>
       </c>
-      <c r="N17" s="67" t="n">
+      <c r="N17" s="66" t="n">
         <v>-66</v>
       </c>
       <c r="O17" s="30" t="inlineStr"/>
@@ -10986,43 +10979,43 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="B18" s="65" t="n">
+      <c r="B18" s="64" t="n">
         <v>110.02</v>
       </c>
-      <c r="C18" s="65" t="n">
+      <c r="C18" s="64" t="n">
         <v>35.2</v>
       </c>
-      <c r="D18" s="68" t="n">
+      <c r="D18" s="67" t="n">
         <v>-9.06</v>
       </c>
-      <c r="E18" s="68" t="n">
+      <c r="E18" s="67" t="n">
         <v>-2.76</v>
       </c>
-      <c r="F18" s="67" t="n">
+      <c r="F18" s="66" t="n">
         <v>-53546</v>
       </c>
-      <c r="G18" s="67" t="n">
+      <c r="G18" s="66" t="n">
         <v>-12018</v>
       </c>
-      <c r="H18" s="67" t="n">
+      <c r="H18" s="66" t="n">
         <v>-65563</v>
       </c>
-      <c r="I18" s="67" t="n">
+      <c r="I18" s="66" t="n">
         <v>-17432</v>
       </c>
-      <c r="J18" s="66" t="n">
+      <c r="J18" s="65" t="n">
         <v>2148</v>
       </c>
-      <c r="K18" s="66" t="n">
+      <c r="K18" s="65" t="n">
         <v>2521</v>
       </c>
-      <c r="L18" s="66" t="n">
+      <c r="L18" s="65" t="n">
         <v>734</v>
       </c>
-      <c r="M18" s="66" t="n">
+      <c r="M18" s="65" t="n">
         <v>10820</v>
       </c>
-      <c r="N18" s="66" t="n">
+      <c r="N18" s="65" t="n">
         <v>54744</v>
       </c>
       <c r="O18" s="30" t="inlineStr"/>
@@ -11033,43 +11026,43 @@
           <t>제조</t>
         </is>
       </c>
-      <c r="B19" s="65" t="n">
+      <c r="B19" s="64" t="n">
         <v>67.84</v>
       </c>
-      <c r="C19" s="65" t="n">
+      <c r="C19" s="64" t="n">
         <v>17.63</v>
       </c>
-      <c r="D19" s="68" t="n">
+      <c r="D19" s="67" t="n">
         <v>-8.789999999999999</v>
       </c>
-      <c r="E19" s="68" t="n">
+      <c r="E19" s="67" t="n">
         <v>-2.83</v>
       </c>
-      <c r="F19" s="67" t="n">
+      <c r="F19" s="66" t="n">
         <v>-62481</v>
       </c>
-      <c r="G19" s="67" t="n">
+      <c r="G19" s="66" t="n">
         <v>-15087</v>
       </c>
-      <c r="H19" s="67" t="n">
+      <c r="H19" s="66" t="n">
         <v>-77567</v>
       </c>
-      <c r="I19" s="67" t="n">
+      <c r="I19" s="66" t="n">
         <v>-16292</v>
       </c>
-      <c r="J19" s="66" t="n">
+      <c r="J19" s="65" t="n">
         <v>17</v>
       </c>
-      <c r="K19" s="66" t="n">
+      <c r="K19" s="65" t="n">
         <v>784</v>
       </c>
-      <c r="L19" s="66" t="n">
+      <c r="L19" s="65" t="n">
         <v>452</v>
       </c>
-      <c r="M19" s="66" t="n">
+      <c r="M19" s="65" t="n">
         <v>21838</v>
       </c>
-      <c r="N19" s="66" t="n">
+      <c r="N19" s="65" t="n">
         <v>55730</v>
       </c>
       <c r="O19" s="30" t="inlineStr"/>
@@ -11080,43 +11073,43 @@
           <t>보험</t>
         </is>
       </c>
-      <c r="B20" s="65" t="n">
+      <c r="B20" s="64" t="n">
         <v>48.04</v>
       </c>
-      <c r="C20" s="65" t="n">
+      <c r="C20" s="64" t="n">
         <v>16.5</v>
       </c>
-      <c r="D20" s="68" t="n">
+      <c r="D20" s="67" t="n">
         <v>-10.54</v>
       </c>
-      <c r="E20" s="68" t="n">
+      <c r="E20" s="67" t="n">
         <v>-2.92</v>
       </c>
-      <c r="F20" s="66" t="n">
+      <c r="F20" s="65" t="n">
         <v>519</v>
       </c>
-      <c r="G20" s="67" t="n">
+      <c r="G20" s="66" t="n">
         <v>-547</v>
       </c>
-      <c r="H20" s="67" t="n">
+      <c r="H20" s="66" t="n">
         <v>-28</v>
       </c>
-      <c r="I20" s="67" t="n">
+      <c r="I20" s="66" t="n">
         <v>-336</v>
       </c>
-      <c r="J20" s="66" t="n">
+      <c r="J20" s="65" t="n">
         <v>102</v>
       </c>
-      <c r="K20" s="67" t="n">
+      <c r="K20" s="66" t="n">
         <v>-276</v>
       </c>
-      <c r="L20" s="67" t="n">
+      <c r="L20" s="66" t="n">
         <v>-35</v>
       </c>
-      <c r="M20" s="67" t="n">
+      <c r="M20" s="66" t="n">
         <v>-12</v>
       </c>
-      <c r="N20" s="66" t="n">
+      <c r="N20" s="65" t="n">
         <v>40</v>
       </c>
       <c r="O20" s="30" t="inlineStr"/>
@@ -11127,46 +11120,46 @@
           <t>금속</t>
         </is>
       </c>
-      <c r="B21" s="68" t="n">
+      <c r="B21" s="67" t="n">
         <v>-3.14</v>
       </c>
-      <c r="C21" s="68" t="n">
+      <c r="C21" s="67" t="n">
         <v>-25.55</v>
       </c>
-      <c r="D21" s="65" t="n">
+      <c r="D21" s="64" t="n">
         <v>0.43</v>
       </c>
-      <c r="E21" s="68" t="n">
+      <c r="E21" s="67" t="n">
         <v>-2.93</v>
       </c>
-      <c r="F21" s="67" t="n">
+      <c r="F21" s="66" t="n">
         <v>-2319</v>
       </c>
-      <c r="G21" s="66" t="n">
+      <c r="G21" s="65" t="n">
         <v>393</v>
       </c>
-      <c r="H21" s="67" t="n">
+      <c r="H21" s="66" t="n">
         <v>-1926</v>
       </c>
-      <c r="I21" s="66" t="n">
+      <c r="I21" s="65" t="n">
         <v>319</v>
       </c>
-      <c r="J21" s="66" t="n">
+      <c r="J21" s="65" t="n">
         <v>290</v>
       </c>
-      <c r="K21" s="67" t="n">
+      <c r="K21" s="66" t="n">
         <v>-211</v>
       </c>
-      <c r="L21" s="67" t="n">
+      <c r="L21" s="66" t="n">
         <v>-5</v>
       </c>
-      <c r="M21" s="66" t="n">
+      <c r="M21" s="65" t="n">
         <v>1891</v>
       </c>
-      <c r="N21" s="66" t="n">
+      <c r="N21" s="65" t="n">
         <v>36</v>
       </c>
-      <c r="O21" s="59" t="inlineStr">
+      <c r="O21" s="58" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -11178,46 +11171,46 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="B22" s="65" t="n">
+      <c r="B22" s="64" t="n">
         <v>8.51</v>
       </c>
-      <c r="C22" s="68" t="n">
+      <c r="C22" s="67" t="n">
         <v>-42.32</v>
       </c>
-      <c r="D22" s="68" t="n">
+      <c r="D22" s="67" t="n">
         <v>-21.43</v>
       </c>
-      <c r="E22" s="68" t="n">
+      <c r="E22" s="67" t="n">
         <v>-3.45</v>
       </c>
-      <c r="F22" s="67" t="n">
+      <c r="F22" s="66" t="n">
         <v>-390</v>
       </c>
-      <c r="G22" s="66" t="n">
+      <c r="G22" s="65" t="n">
         <v>115</v>
       </c>
-      <c r="H22" s="67" t="n">
+      <c r="H22" s="66" t="n">
         <v>-275</v>
       </c>
-      <c r="I22" s="66" t="n">
+      <c r="I22" s="65" t="n">
         <v>42</v>
       </c>
-      <c r="J22" s="67" t="n">
+      <c r="J22" s="66" t="n">
         <v>-22</v>
       </c>
-      <c r="K22" s="66" t="n">
+      <c r="K22" s="65" t="n">
         <v>14</v>
       </c>
-      <c r="L22" s="67" t="n">
+      <c r="L22" s="66" t="n">
         <v>-6</v>
       </c>
-      <c r="M22" s="66" t="n">
+      <c r="M22" s="65" t="n">
         <v>249</v>
       </c>
-      <c r="N22" s="66" t="n">
+      <c r="N22" s="65" t="n">
         <v>26</v>
       </c>
-      <c r="O22" s="59" t="inlineStr">
+      <c r="O22" s="58" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -11229,43 +11222,43 @@
           <t>유통</t>
         </is>
       </c>
-      <c r="B23" s="65" t="n">
+      <c r="B23" s="64" t="n">
         <v>17.88</v>
       </c>
-      <c r="C23" s="68" t="n">
+      <c r="C23" s="67" t="n">
         <v>-4.15</v>
       </c>
-      <c r="D23" s="68" t="n">
+      <c r="D23" s="67" t="n">
         <v>-16.18</v>
       </c>
-      <c r="E23" s="68" t="n">
+      <c r="E23" s="67" t="n">
         <v>-3.88</v>
       </c>
-      <c r="F23" s="66" t="n">
+      <c r="F23" s="65" t="n">
         <v>372</v>
       </c>
-      <c r="G23" s="67" t="n">
+      <c r="G23" s="66" t="n">
         <v>-422</v>
       </c>
-      <c r="H23" s="67" t="n">
+      <c r="H23" s="66" t="n">
         <v>-49</v>
       </c>
-      <c r="I23" s="66" t="n">
+      <c r="I23" s="65" t="n">
         <v>48</v>
       </c>
-      <c r="J23" s="67" t="n">
+      <c r="J23" s="66" t="n">
         <v>-305</v>
       </c>
-      <c r="K23" s="67" t="n">
+      <c r="K23" s="66" t="n">
         <v>-122</v>
       </c>
-      <c r="L23" s="67" t="n">
+      <c r="L23" s="66" t="n">
         <v>-30</v>
       </c>
-      <c r="M23" s="66" t="n">
+      <c r="M23" s="65" t="n">
         <v>51</v>
       </c>
-      <c r="N23" s="67" t="n">
+      <c r="N23" s="66" t="n">
         <v>-1</v>
       </c>
       <c r="O23" s="30" t="inlineStr"/>
@@ -11276,46 +11269,46 @@
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="B24" s="68" t="n">
+      <c r="B24" s="67" t="n">
         <v>-18.16</v>
       </c>
-      <c r="C24" s="68" t="n">
+      <c r="C24" s="67" t="n">
         <v>-9.33</v>
       </c>
-      <c r="D24" s="68" t="n">
+      <c r="D24" s="67" t="n">
         <v>-7.38</v>
       </c>
-      <c r="E24" s="68" t="n">
+      <c r="E24" s="67" t="n">
         <v>-4.2</v>
       </c>
-      <c r="F24" s="67" t="n">
+      <c r="F24" s="66" t="n">
         <v>-1750</v>
       </c>
-      <c r="G24" s="67" t="n">
+      <c r="G24" s="66" t="n">
         <v>-946</v>
       </c>
-      <c r="H24" s="67" t="n">
+      <c r="H24" s="66" t="n">
         <v>-2695</v>
       </c>
-      <c r="I24" s="67" t="n">
+      <c r="I24" s="66" t="n">
         <v>-37</v>
       </c>
-      <c r="J24" s="67" t="n">
+      <c r="J24" s="66" t="n">
         <v>-240</v>
       </c>
-      <c r="K24" s="67" t="n">
+      <c r="K24" s="66" t="n">
         <v>-624</v>
       </c>
-      <c r="L24" s="67" t="n">
+      <c r="L24" s="66" t="n">
         <v>-45</v>
       </c>
-      <c r="M24" s="66" t="n">
+      <c r="M24" s="65" t="n">
         <v>2693</v>
       </c>
-      <c r="N24" s="66" t="n">
+      <c r="N24" s="65" t="n">
         <v>3</v>
       </c>
-      <c r="O24" s="59" t="inlineStr">
+      <c r="O24" s="58" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -11327,43 +11320,43 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="B25" s="65" t="n">
+      <c r="B25" s="64" t="n">
         <v>34.72</v>
       </c>
-      <c r="C25" s="65" t="n">
+      <c r="C25" s="64" t="n">
         <v>5.78</v>
       </c>
-      <c r="D25" s="68" t="n">
+      <c r="D25" s="67" t="n">
         <v>-8.85</v>
       </c>
-      <c r="E25" s="68" t="n">
+      <c r="E25" s="67" t="n">
         <v>-4.7</v>
       </c>
-      <c r="F25" s="67" t="n">
+      <c r="F25" s="66" t="n">
         <v>-235</v>
       </c>
-      <c r="G25" s="66" t="n">
+      <c r="G25" s="65" t="n">
         <v>2007</v>
       </c>
-      <c r="H25" s="66" t="n">
+      <c r="H25" s="65" t="n">
         <v>1772</v>
       </c>
-      <c r="I25" s="67" t="n">
+      <c r="I25" s="66" t="n">
         <v>-356</v>
       </c>
-      <c r="J25" s="66" t="n">
+      <c r="J25" s="65" t="n">
         <v>3749</v>
       </c>
-      <c r="K25" s="67" t="n">
+      <c r="K25" s="66" t="n">
         <v>-1789</v>
       </c>
-      <c r="L25" s="67" t="n">
+      <c r="L25" s="66" t="n">
         <v>-342</v>
       </c>
-      <c r="M25" s="66" t="n">
+      <c r="M25" s="65" t="n">
         <v>4733</v>
       </c>
-      <c r="N25" s="67" t="n">
+      <c r="N25" s="66" t="n">
         <v>-6505</v>
       </c>
       <c r="O25" s="30" t="inlineStr"/>
@@ -11374,46 +11367,46 @@
           <t>제약</t>
         </is>
       </c>
-      <c r="B26" s="68" t="n">
+      <c r="B26" s="67" t="n">
         <v>-19.75</v>
       </c>
-      <c r="C26" s="68" t="n">
+      <c r="C26" s="67" t="n">
         <v>-16.91</v>
       </c>
-      <c r="D26" s="68" t="n">
+      <c r="D26" s="67" t="n">
         <v>-3.96</v>
       </c>
-      <c r="E26" s="68" t="n">
+      <c r="E26" s="67" t="n">
         <v>-5.16</v>
       </c>
-      <c r="F26" s="67" t="n">
+      <c r="F26" s="66" t="n">
         <v>-1790</v>
       </c>
-      <c r="G26" s="67" t="n">
+      <c r="G26" s="66" t="n">
         <v>-385</v>
       </c>
-      <c r="H26" s="67" t="n">
+      <c r="H26" s="66" t="n">
         <v>-2175</v>
       </c>
-      <c r="I26" s="67" t="n">
+      <c r="I26" s="66" t="n">
         <v>-321</v>
       </c>
-      <c r="J26" s="67" t="n">
+      <c r="J26" s="66" t="n">
         <v>-110</v>
       </c>
-      <c r="K26" s="66" t="n">
+      <c r="K26" s="65" t="n">
         <v>64</v>
       </c>
-      <c r="L26" s="67" t="n">
+      <c r="L26" s="66" t="n">
         <v>-16</v>
       </c>
-      <c r="M26" s="66" t="n">
+      <c r="M26" s="65" t="n">
         <v>1664</v>
       </c>
-      <c r="N26" s="66" t="n">
+      <c r="N26" s="65" t="n">
         <v>511</v>
       </c>
-      <c r="O26" s="59" t="inlineStr">
+      <c r="O26" s="58" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -11425,43 +11418,43 @@
           <t>건설</t>
         </is>
       </c>
-      <c r="B27" s="65" t="n">
+      <c r="B27" s="64" t="n">
         <v>56.14</v>
       </c>
-      <c r="C27" s="68" t="n">
+      <c r="C27" s="67" t="n">
         <v>-31.48</v>
       </c>
-      <c r="D27" s="65" t="n">
+      <c r="D27" s="64" t="n">
         <v>5.49</v>
       </c>
-      <c r="E27" s="68" t="n">
+      <c r="E27" s="67" t="n">
         <v>-6.58</v>
       </c>
-      <c r="F27" s="66" t="n">
+      <c r="F27" s="65" t="n">
         <v>143</v>
       </c>
-      <c r="G27" s="67" t="n">
+      <c r="G27" s="66" t="n">
         <v>-1193</v>
       </c>
-      <c r="H27" s="67" t="n">
+      <c r="H27" s="66" t="n">
         <v>-1049</v>
       </c>
-      <c r="I27" s="66" t="n">
+      <c r="I27" s="65" t="n">
         <v>222</v>
       </c>
-      <c r="J27" s="67" t="n">
+      <c r="J27" s="66" t="n">
         <v>-600</v>
       </c>
-      <c r="K27" s="67" t="n">
+      <c r="K27" s="66" t="n">
         <v>-744</v>
       </c>
-      <c r="L27" s="67" t="n">
+      <c r="L27" s="66" t="n">
         <v>-69</v>
       </c>
-      <c r="M27" s="66" t="n">
+      <c r="M27" s="65" t="n">
         <v>1049</v>
       </c>
-      <c r="N27" s="66" t="n">
+      <c r="N27" s="65" t="n">
         <v>1</v>
       </c>
       <c r="O27" s="30" t="inlineStr"/>
@@ -11472,46 +11465,46 @@
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="B28" s="68" t="n">
+      <c r="B28" s="67" t="n">
         <v>-13.62</v>
       </c>
-      <c r="C28" s="68" t="n">
+      <c r="C28" s="67" t="n">
         <v>-33.4</v>
       </c>
-      <c r="D28" s="68" t="n">
+      <c r="D28" s="67" t="n">
         <v>-24.03</v>
       </c>
-      <c r="E28" s="68" t="n">
+      <c r="E28" s="67" t="n">
         <v>-6.9</v>
       </c>
-      <c r="F28" s="67" t="n">
+      <c r="F28" s="66" t="n">
         <v>-3703</v>
       </c>
-      <c r="G28" s="67" t="n">
+      <c r="G28" s="66" t="n">
         <v>-4755</v>
       </c>
-      <c r="H28" s="67" t="n">
+      <c r="H28" s="66" t="n">
         <v>-8458</v>
       </c>
-      <c r="I28" s="67" t="n">
+      <c r="I28" s="66" t="n">
         <v>-1001</v>
       </c>
-      <c r="J28" s="67" t="n">
+      <c r="J28" s="66" t="n">
         <v>-864</v>
       </c>
-      <c r="K28" s="67" t="n">
+      <c r="K28" s="66" t="n">
         <v>-2693</v>
       </c>
-      <c r="L28" s="67" t="n">
+      <c r="L28" s="66" t="n">
         <v>-166</v>
       </c>
-      <c r="M28" s="66" t="n">
+      <c r="M28" s="65" t="n">
         <v>8255</v>
       </c>
-      <c r="N28" s="66" t="n">
+      <c r="N28" s="65" t="n">
         <v>203</v>
       </c>
-      <c r="O28" s="59" t="inlineStr">
+      <c r="O28" s="58" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -11549,7 +11542,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5A76A9FF-404F-440A-9221-4EEC5BD88296}</x14:id>
+          <x14:id>{EA4673E6-1827-4B3B-A7F1-F148EE3019D5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11563,7 +11556,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{B01AB276-F786-48C7-BB91-DB763EEB2AAC}</x14:id>
+          <x14:id>{9026F695-2DAE-4239-A756-5B889275958E}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11577,7 +11570,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{B4E6AE40-F547-4607-9171-D607DC472CA5}</x14:id>
+          <x14:id>{31D78FCF-3343-4F3D-9394-2C2E9E2F45D3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11591,7 +11584,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{92B7586D-AC9A-401E-953E-50F486D2AA81}</x14:id>
+          <x14:id>{FCBC355B-8106-4A8A-AECC-DC5C8DA02142}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11601,7 +11594,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5A76A9FF-404F-440A-9221-4EEC5BD88296}">
+          <x14:cfRule type="dataBar" id="{EA4673E6-1827-4B3B-A7F1-F148EE3019D5}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11614,7 +11607,7 @@
           <xm:sqref>B5:B28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{B01AB276-F786-48C7-BB91-DB763EEB2AAC}">
+          <x14:cfRule type="dataBar" id="{9026F695-2DAE-4239-A756-5B889275958E}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11627,7 +11620,7 @@
           <xm:sqref>C5:C28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{B4E6AE40-F547-4607-9171-D607DC472CA5}">
+          <x14:cfRule type="dataBar" id="{31D78FCF-3343-4F3D-9394-2C2E9E2F45D3}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11640,7 +11633,7 @@
           <xm:sqref>D5:D28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{92B7586D-AC9A-401E-953E-50F486D2AA81}">
+          <x14:cfRule type="dataBar" id="{FCBC355B-8106-4A8A-AECC-DC5C8DA02142}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/public/monthly_review.xlsx
+++ b/public/monthly_review.xlsx
@@ -1017,7 +1017,7 @@
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>미국 종가 기준 09/30 → 10/15, %</t>
+          <t>미국 종가 기준 09/30 → 10/16, %</t>
         </is>
       </c>
       <c r="I6" s="18" t="inlineStr"/>
@@ -1087,19 +1087,19 @@
         <v>17552</v>
       </c>
       <c r="E8" s="28" t="n">
-        <v>1.21</v>
+        <v>0.1</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="G8" s="29" t="n">
-        <v>-0.55</v>
+        <v>-2.68</v>
       </c>
       <c r="H8" s="28" t="n">
-        <v>0.73</v>
+        <v>22.34</v>
       </c>
       <c r="I8" s="29" t="n">
-        <v>-8.289999999999999</v>
+        <v>-11.81</v>
       </c>
     </row>
     <row r="9">
@@ -1158,7 +1158,7 @@
         </is>
       </c>
       <c r="D12" s="32" t="n">
-        <v>8.23</v>
+        <v>10.96</v>
       </c>
     </row>
     <row r="13">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="D13" s="32" t="n">
-        <v>5.21</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="14">
@@ -1194,11 +1194,11 @@
       </c>
       <c r="C14" s="31" t="inlineStr">
         <is>
-          <t>임의소비재</t>
+          <t>소재</t>
         </is>
       </c>
       <c r="D14" s="32" t="n">
-        <v>4.2</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="15">
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="D15" s="33" t="n">
-        <v>-8.24</v>
+        <v>-11.36</v>
       </c>
     </row>
     <row r="16">
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="D16" s="33" t="n">
-        <v>-5.01</v>
+        <v>-8.470000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="D17" s="33" t="n">
-        <v>-3.35</v>
+        <v>-6.27</v>
       </c>
     </row>
     <row r="18">
@@ -12533,7 +12533,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6465E6DC-CF2B-4C89-947F-3C7E1FAE49B7}</x14:id>
+          <x14:id>{FECEE320-D8CE-4176-B9EA-F2F666A6397E}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12547,7 +12547,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4F9C1BF1-E0A5-4A2F-8A0E-4A5314356E37}</x14:id>
+          <x14:id>{55ED9D88-4BB3-4B27-8CDC-7EE36578434B}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12561,7 +12561,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{FF5AB180-D82C-4CA9-BA4D-360D9676F114}</x14:id>
+          <x14:id>{66E522BF-8341-4D54-A5B0-2C111935C0D8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12575,7 +12575,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{A01ECB40-8140-4E1E-807F-858515B874C9}</x14:id>
+          <x14:id>{40744A85-887D-41DF-8BE7-FE8C45BE0F7B}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12585,7 +12585,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6465E6DC-CF2B-4C89-947F-3C7E1FAE49B7}">
+          <x14:cfRule type="dataBar" id="{FECEE320-D8CE-4176-B9EA-F2F666A6397E}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12598,7 +12598,7 @@
           <xm:sqref>B5:B28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4F9C1BF1-E0A5-4A2F-8A0E-4A5314356E37}">
+          <x14:cfRule type="dataBar" id="{55ED9D88-4BB3-4B27-8CDC-7EE36578434B}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12611,7 +12611,7 @@
           <xm:sqref>C5:C28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{FF5AB180-D82C-4CA9-BA4D-360D9676F114}">
+          <x14:cfRule type="dataBar" id="{66E522BF-8341-4D54-A5B0-2C111935C0D8}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12624,7 +12624,7 @@
           <xm:sqref>D5:D28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{A01ECB40-8140-4E1E-807F-858515B874C9}">
+          <x14:cfRule type="dataBar" id="{40744A85-887D-41DF-8BE7-FE8C45BE0F7B}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/public/monthly_review.xlsx
+++ b/public/monthly_review.xlsx
@@ -517,10 +517,10 @@
     <xf numFmtId="169" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -931,7 +931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K185"/>
+  <dimension ref="A1:K186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.9" customWidth="1" style="15" min="1" max="1"/>
@@ -960,7 +960,7 @@
       </c>
       <c r="I1" s="25" t="inlineStr">
         <is>
-          <t>2026-10-01 ~ 2026-10-22</t>
+          <t>2026-10-01 ~ 2026-10-23</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
       </c>
       <c r="I2" s="25" t="inlineStr">
         <is>
-          <t>2026-10-22 16:28 KST</t>
+          <t>2026-10-23 16:26 KST</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>10월은 견조한 수출 펀더멘털에도 불구하고 미국발 인플레이션 우려와 외국인의 대규모 매도세가 겹치며 극심한 변동성을 보인 한 달이었습니다.</t>
+          <t>10월은 견조한 수출 펀더멘털에도 불구하고 미국발 인플레이션 우려와 외국인 수급 변동성으로 인해 급락과 반등이 교차하는 변동성 장세를 보였습니다.</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>미국 종가 기준 09/30 → 10/21, %</t>
+          <t>미국 종가 기준 09/30 → 10/22, %</t>
         </is>
       </c>
       <c r="I6" s="18" t="inlineStr"/>
@@ -1081,28 +1081,28 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>63230</v>
+        <v>63678</v>
       </c>
       <c r="C8" s="29" t="n">
-        <v>-178876</v>
+        <v>-188702</v>
       </c>
       <c r="D8" s="28" t="n">
-        <v>8012</v>
+        <v>16699</v>
       </c>
       <c r="E8" s="28" t="n">
-        <v>1.38</v>
+        <v>0.16</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>3.83</v>
+        <v>3.85</v>
       </c>
       <c r="G8" s="29" t="n">
-        <v>-0.59</v>
+        <v>-3.17</v>
       </c>
       <c r="H8" s="28" t="n">
-        <v>2.08</v>
+        <v>16.46</v>
       </c>
       <c r="I8" s="29" t="n">
-        <v>-8.890000000000001</v>
+        <v>-15.02</v>
       </c>
     </row>
     <row r="9">
@@ -1112,13 +1112,13 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>5656</v>
+        <v>6292</v>
       </c>
       <c r="C9" s="29" t="n">
-        <v>-6379</v>
+        <v>-6798</v>
       </c>
       <c r="D9" s="28" t="n">
-        <v>461</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10"/>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="D12" s="32" t="n">
-        <v>10.83</v>
+        <v>9.869999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="D13" s="32" t="n">
-        <v>6.25</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="14">
@@ -1197,11 +1197,11 @@
       </c>
       <c r="C14" s="31" t="inlineStr">
         <is>
-          <t>임의소비재</t>
+          <t>소재</t>
         </is>
       </c>
       <c r="D14" s="32" t="n">
-        <v>6.15</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="15">
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="D15" s="33" t="n">
-        <v>-8.59</v>
+        <v>-14.06</v>
       </c>
     </row>
     <row r="16">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="D16" s="33" t="n">
-        <v>-3.68</v>
+        <v>-6.85</v>
       </c>
     </row>
     <row r="17">
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="D17" s="33" t="n">
-        <v>-3.11</v>
+        <v>-3.83</v>
       </c>
     </row>
     <row r="18">
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="D18" s="32" t="n">
-        <v>6.87</v>
+        <v>6.21</v>
       </c>
     </row>
     <row r="19">
@@ -1297,11 +1297,11 @@
       </c>
       <c r="C19" s="31" t="inlineStr">
         <is>
-          <t>음식료·담배</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="D19" s="32" t="n">
-        <v>4.07</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="20">
@@ -1317,11 +1317,11 @@
       </c>
       <c r="C20" s="31" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>음식료·담배</t>
         </is>
       </c>
       <c r="D20" s="32" t="n">
-        <v>1.21</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="21">
@@ -1337,11 +1337,11 @@
       </c>
       <c r="C21" s="31" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>기계·장비</t>
         </is>
       </c>
       <c r="D21" s="33" t="n">
-        <v>-23.56</v>
+        <v>-23.88</v>
       </c>
     </row>
     <row r="22">
@@ -1357,11 +1357,11 @@
       </c>
       <c r="C22" s="31" t="inlineStr">
         <is>
-          <t>기계·장비</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="D22" s="33" t="n">
-        <v>-21.87</v>
+        <v>-22.59</v>
       </c>
     </row>
     <row r="23">
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="D23" s="33" t="n">
-        <v>-20.97</v>
+        <v>-20.46</v>
       </c>
     </row>
     <row r="24"/>
@@ -2468,75 +2468,111 @@
         </is>
       </c>
     </row>
-    <row r="57"/>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="57" ht="31" customHeight="1" s="15">
+      <c r="A57" s="31" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B57" s="31" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C57" s="17" t="inlineStr">
+        <is>
+          <t>신규 실업수당청구건수</t>
+        </is>
+      </c>
+      <c r="D57" s="31" t="n">
+        <v>194</v>
+      </c>
+      <c r="E57" s="31" t="n">
+        <v>200</v>
+      </c>
+      <c r="F57" s="31" t="n">
+        <v>199</v>
+      </c>
+      <c r="G57" s="31" t="inlineStr">
+        <is>
+          <t>Kpers</t>
+        </is>
+      </c>
+      <c r="H57" s="13" t="inlineStr">
+        <is>
+          <t>예상 하회</t>
+        </is>
+      </c>
+    </row>
+    <row r="58"/>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>04</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>일별 요약</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr"/>
-      <c r="D58" s="3" t="inlineStr"/>
-      <c r="E58" s="3" t="inlineStr"/>
-      <c r="F58" s="3" t="inlineStr"/>
-      <c r="G58" s="3" t="inlineStr"/>
-      <c r="H58" s="3" t="inlineStr"/>
-      <c r="I58" s="3" t="inlineStr"/>
-      <c r="J58" s="3" t="inlineStr"/>
-      <c r="K58" s="3" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr"/>
+      <c r="D59" s="3" t="inlineStr"/>
+      <c r="E59" s="3" t="inlineStr"/>
+      <c r="F59" s="3" t="inlineStr"/>
+      <c r="G59" s="3" t="inlineStr"/>
+      <c r="H59" s="3" t="inlineStr"/>
+      <c r="I59" s="3" t="inlineStr"/>
+      <c r="J59" s="3" t="inlineStr"/>
+      <c r="K59" s="3" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>날짜</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>코스피(%)</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>코스피 ▲/▼</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D60" s="4" t="inlineStr">
         <is>
           <t>코스닥(%)</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
+      <c r="E60" s="4" t="inlineStr">
         <is>
           <t>코스닥 ▲/▼</t>
         </is>
       </c>
-      <c r="F59" s="4" t="inlineStr">
+      <c r="F60" s="4" t="inlineStr">
         <is>
           <t>주도 섹터</t>
         </is>
       </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="G60" s="4" t="inlineStr">
         <is>
           <t>그날 지수·수급 반응 요인</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="31" customHeight="1" s="15">
-      <c r="A60" s="31" t="inlineStr">
+    <row r="61" ht="31" customHeight="1" s="15">
+      <c r="A61" s="31" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B60" s="28" t="n">
+      <c r="B61" s="28" t="n">
         <v>1.95</v>
       </c>
-      <c r="C60" s="31" t="inlineStr">
+      <c r="C61" s="31" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2559,10 +2595,10 @@
           </r>
         </is>
       </c>
-      <c r="D60" s="28" t="n">
+      <c r="D61" s="28" t="n">
         <v>4.48</v>
       </c>
-      <c r="E60" s="17" t="inlineStr">
+      <c r="E61" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2585,27 +2621,27 @@
           </r>
         </is>
       </c>
-      <c r="F60" s="17" t="inlineStr">
+      <c r="F61" s="17" t="inlineStr">
         <is>
           <t>의료·정밀기기, 제약</t>
         </is>
       </c>
-      <c r="G60" s="17" t="inlineStr">
-        <is>
-          <t>수출 급증과 기관 매수로 코스피 7,000선 돌파.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="31" customHeight="1" s="15">
-      <c r="A61" s="31" t="inlineStr">
+      <c r="G61" s="17" t="inlineStr">
+        <is>
+          <t>수출 급증과 기관 매수로 지수 동반 급등.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="31" customHeight="1" s="15">
+      <c r="A62" s="31" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B61" s="28" t="n">
+      <c r="B62" s="28" t="n">
         <v>0.46</v>
       </c>
-      <c r="C61" s="17" t="inlineStr">
+      <c r="C62" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2628,10 +2664,10 @@
           </r>
         </is>
       </c>
-      <c r="D61" s="29" t="n">
+      <c r="D62" s="29" t="n">
         <v>-0.11</v>
       </c>
-      <c r="E61" s="17" t="inlineStr">
+      <c r="E62" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2654,27 +2690,27 @@
           </r>
         </is>
       </c>
-      <c r="F61" s="17" t="inlineStr">
+      <c r="F62" s="17" t="inlineStr">
         <is>
           <t>화학, 금속</t>
         </is>
       </c>
-      <c r="G61" s="17" t="inlineStr">
-        <is>
-          <t>기관 매수세로 코스피 7,000선 안착 시도.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="31" customHeight="1" s="15">
-      <c r="A62" s="31" t="inlineStr">
+      <c r="G62" s="17" t="inlineStr">
+        <is>
+          <t>기관 매수세로 코스피 7,000선 돌파.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="31" customHeight="1" s="15">
+      <c r="A63" s="31" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B62" s="29" t="n">
+      <c r="B63" s="29" t="n">
         <v>-0.89</v>
       </c>
-      <c r="C62" s="31" t="inlineStr">
+      <c r="C63" s="31" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2697,10 +2733,10 @@
           </r>
         </is>
       </c>
-      <c r="D62" s="28" t="n">
+      <c r="D63" s="28" t="n">
         <v>2.98</v>
       </c>
-      <c r="E62" s="17" t="inlineStr">
+      <c r="E63" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2723,27 +2759,27 @@
           </r>
         </is>
       </c>
-      <c r="F62" s="17" t="inlineStr">
+      <c r="F63" s="17" t="inlineStr">
         <is>
           <t>의료·정밀기기, 화학</t>
         </is>
       </c>
-      <c r="G62" s="17" t="inlineStr">
-        <is>
-          <t>외국인 1.8조 매도로 코스피 하락, 코스닥은 상승.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="31" customHeight="1" s="15">
-      <c r="A63" s="31" t="inlineStr">
+      <c r="G63" s="17" t="inlineStr">
+        <is>
+          <t>외국인 1.8조 매도로 코스피 하락.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="31" customHeight="1" s="15">
+      <c r="A64" s="31" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B63" s="29" t="n">
+      <c r="B64" s="29" t="n">
         <v>-1.98</v>
       </c>
-      <c r="C63" s="17" t="inlineStr">
+      <c r="C64" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2766,10 +2802,10 @@
           </r>
         </is>
       </c>
-      <c r="D63" s="29" t="n">
+      <c r="D64" s="29" t="n">
         <v>-2.34</v>
       </c>
-      <c r="E63" s="17" t="inlineStr">
+      <c r="E64" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2792,27 +2828,27 @@
           </r>
         </is>
       </c>
-      <c r="F63" s="17" t="inlineStr">
+      <c r="F64" s="17" t="inlineStr">
         <is>
           <t>의료·정밀기기, 오락·문화</t>
         </is>
       </c>
-      <c r="G63" s="17" t="inlineStr">
-        <is>
-          <t>외국인 2.6조 매도에 양 시장 동반 급락.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="31" customHeight="1" s="15">
-      <c r="A64" s="31" t="inlineStr">
+      <c r="G64" s="17" t="inlineStr">
+        <is>
+          <t>외국인 2.6조 매도로 양 시장 하락.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="31" customHeight="1" s="15">
+      <c r="A65" s="31" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B64" s="29" t="n">
+      <c r="B65" s="29" t="n">
         <v>-2.62</v>
       </c>
-      <c r="C64" s="17" t="inlineStr">
+      <c r="C65" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2835,10 +2871,10 @@
           </r>
         </is>
       </c>
-      <c r="D64" s="29" t="n">
+      <c r="D65" s="29" t="n">
         <v>-0.6899999999999999</v>
       </c>
-      <c r="E64" s="17" t="inlineStr">
+      <c r="E65" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2861,27 +2897,27 @@
           </r>
         </is>
       </c>
-      <c r="F64" s="17" t="inlineStr">
+      <c r="F65" s="17" t="inlineStr">
         <is>
           <t>섬유·의류, 종이·목재</t>
         </is>
       </c>
-      <c r="G64" s="17" t="inlineStr">
-        <is>
-          <t>외국인·기관 동반 매도로 코스피 2.62% 급락.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="31" customHeight="1" s="15">
-      <c r="A65" s="31" t="inlineStr">
+      <c r="G65" s="17" t="inlineStr">
+        <is>
+          <t>외국인·기관 동반 매도로 코스피 급락.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="31" customHeight="1" s="15">
+      <c r="A66" s="31" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B65" s="29" t="n">
+      <c r="B66" s="29" t="n">
         <v>-3.65</v>
       </c>
-      <c r="C65" s="17" t="inlineStr">
+      <c r="C66" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2904,10 +2940,10 @@
           </r>
         </is>
       </c>
-      <c r="D65" s="29" t="n">
+      <c r="D66" s="29" t="n">
         <v>-4.83</v>
       </c>
-      <c r="E65" s="17" t="inlineStr">
+      <c r="E66" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2930,27 +2966,27 @@
           </r>
         </is>
       </c>
-      <c r="F65" s="17" t="inlineStr">
+      <c r="F66" s="17" t="inlineStr">
         <is>
           <t>운송·창고, 음식료·담배</t>
         </is>
       </c>
-      <c r="G65" s="17" t="inlineStr">
-        <is>
-          <t>외국인 2조 매도에 코스피 3.65% 급락.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="31" customHeight="1" s="15">
-      <c r="A66" s="31" t="inlineStr">
+      <c r="G66" s="17" t="inlineStr">
+        <is>
+          <t>외국인 2조 매도로 코스피 3.65% 급락.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="31" customHeight="1" s="15">
+      <c r="A67" s="31" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B66" s="29" t="n">
+      <c r="B67" s="29" t="n">
         <v>-5.46</v>
       </c>
-      <c r="C66" s="31" t="inlineStr">
+      <c r="C67" s="31" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2973,10 +3009,10 @@
           </r>
         </is>
       </c>
-      <c r="D66" s="29" t="n">
+      <c r="D67" s="29" t="n">
         <v>-1.43</v>
       </c>
-      <c r="E66" s="17" t="inlineStr">
+      <c r="E67" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2999,27 +3035,27 @@
           </r>
         </is>
       </c>
-      <c r="F66" s="17" t="inlineStr">
+      <c r="F67" s="17" t="inlineStr">
         <is>
           <t>오락·문화, 의료·정밀기기</t>
         </is>
       </c>
-      <c r="G66" s="17" t="inlineStr">
+      <c r="G67" s="17" t="inlineStr">
         <is>
           <t>외국인 4.5조 매도로 코스피 5.46% 급락.</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="31" customHeight="1" s="15">
-      <c r="A67" s="31" t="inlineStr">
+    <row r="68" ht="31" customHeight="1" s="15">
+      <c r="A68" s="31" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B67" s="29" t="n">
+      <c r="B68" s="29" t="n">
         <v>-0.44</v>
       </c>
-      <c r="C67" s="17" t="inlineStr">
+      <c r="C68" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3042,10 +3078,10 @@
           </r>
         </is>
       </c>
-      <c r="D67" s="29" t="n">
+      <c r="D68" s="29" t="n">
         <v>-1.57</v>
       </c>
-      <c r="E67" s="17" t="inlineStr">
+      <c r="E68" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3068,27 +3104,27 @@
           </r>
         </is>
       </c>
-      <c r="F67" s="17" t="inlineStr">
+      <c r="F68" s="17" t="inlineStr">
         <is>
           <t>운송·창고, 화학</t>
         </is>
       </c>
-      <c r="G67" s="17" t="inlineStr">
-        <is>
-          <t>외국인 매도 지속으로 코스피 6,000선 위협.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="31" customHeight="1" s="15">
-      <c r="A68" s="31" t="inlineStr">
+      <c r="G68" s="17" t="inlineStr">
+        <is>
+          <t>외국인 매도 지속으로 코스피 하락.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="31" customHeight="1" s="15">
+      <c r="A69" s="31" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B68" s="29" t="n">
+      <c r="B69" s="29" t="n">
         <v>-7.57</v>
       </c>
-      <c r="C68" s="17" t="inlineStr">
+      <c r="C69" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3111,10 +3147,10 @@
           </r>
         </is>
       </c>
-      <c r="D68" s="29" t="n">
+      <c r="D69" s="29" t="n">
         <v>-7.65</v>
       </c>
-      <c r="E68" s="17" t="inlineStr">
+      <c r="E69" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3137,27 +3173,27 @@
           </r>
         </is>
       </c>
-      <c r="F68" s="17" t="inlineStr">
+      <c r="F69" s="17" t="inlineStr">
         <is>
           <t>제약, 음식료·담배</t>
         </is>
       </c>
-      <c r="G68" s="17" t="inlineStr">
-        <is>
-          <t>인플레이션 우려로 코스피 7.57% 급락.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="31" customHeight="1" s="15">
-      <c r="A69" s="31" t="inlineStr">
+      <c r="G69" s="17" t="inlineStr">
+        <is>
+          <t>외국인 3.6조 매도로 코스피 7.57% 급락.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="31" customHeight="1" s="15">
+      <c r="A70" s="31" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B69" s="28" t="n">
+      <c r="B70" s="28" t="n">
         <v>2.05</v>
       </c>
-      <c r="C69" s="17" t="inlineStr">
+      <c r="C70" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3180,10 +3216,10 @@
           </r>
         </is>
       </c>
-      <c r="D69" s="28" t="n">
+      <c r="D70" s="28" t="n">
         <v>4.46</v>
       </c>
-      <c r="E69" s="17" t="inlineStr">
+      <c r="E70" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3206,27 +3242,27 @@
           </r>
         </is>
       </c>
-      <c r="F69" s="17" t="inlineStr">
+      <c r="F70" s="17" t="inlineStr">
         <is>
           <t>의료·정밀기기, 제약</t>
         </is>
       </c>
-      <c r="G69" s="17" t="inlineStr">
-        <is>
-          <t>저가 매수세 유입으로 코스피 2.05% 반등.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="31" customHeight="1" s="15">
-      <c r="A70" s="31" t="inlineStr">
+      <c r="G70" s="17" t="inlineStr">
+        <is>
+          <t>저가 매수세 유입으로 지수 반등.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="31" customHeight="1" s="15">
+      <c r="A71" s="31" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B70" s="28" t="n">
+      <c r="B71" s="28" t="n">
         <v>1.76</v>
       </c>
-      <c r="C70" s="17" t="inlineStr">
+      <c r="C71" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3249,10 +3285,10 @@
           </r>
         </is>
       </c>
-      <c r="D70" s="28" t="n">
+      <c r="D71" s="28" t="n">
         <v>1.78</v>
       </c>
-      <c r="E70" s="17" t="inlineStr">
+      <c r="E71" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3275,27 +3311,27 @@
           </r>
         </is>
       </c>
-      <c r="F70" s="17" t="inlineStr">
+      <c r="F71" s="17" t="inlineStr">
         <is>
           <t>제약, 금속</t>
         </is>
       </c>
-      <c r="G70" s="17" t="inlineStr">
-        <is>
-          <t>기관 매수세 유입으로 코스피 1.76% 상승.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="31" customHeight="1" s="15">
-      <c r="A71" s="31" t="inlineStr">
+      <c r="G71" s="17" t="inlineStr">
+        <is>
+          <t>기관 매수세로 지수 상승 전환.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="31" customHeight="1" s="15">
+      <c r="A72" s="31" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B71" s="29" t="n">
+      <c r="B72" s="29" t="n">
         <v>-3.73</v>
       </c>
-      <c r="C71" s="17" t="inlineStr">
+      <c r="C72" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3318,10 +3354,10 @@
           </r>
         </is>
       </c>
-      <c r="D71" s="29" t="n">
+      <c r="D72" s="29" t="n">
         <v>-3.33</v>
       </c>
-      <c r="E71" s="17" t="inlineStr">
+      <c r="E72" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3344,27 +3380,27 @@
           </r>
         </is>
       </c>
-      <c r="F71" s="17" t="inlineStr">
+      <c r="F72" s="17" t="inlineStr">
         <is>
           <t>음식료·담배, 부동산</t>
         </is>
       </c>
-      <c r="G71" s="17" t="inlineStr">
-        <is>
-          <t>외국인·기관 동반 매도로 코스피 3.73% 급락.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="31" customHeight="1" s="15">
-      <c r="A72" s="31" t="inlineStr">
+      <c r="G72" s="17" t="inlineStr">
+        <is>
+          <t>외국인·기관 동반 매도로 지수 급락.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="31" customHeight="1" s="15">
+      <c r="A73" s="31" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B72" s="28" t="n">
+      <c r="B73" s="28" t="n">
         <v>3.29</v>
       </c>
-      <c r="C72" s="17" t="inlineStr">
+      <c r="C73" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3387,10 +3423,10 @@
           </r>
         </is>
       </c>
-      <c r="D72" s="28" t="n">
+      <c r="D73" s="28" t="n">
         <v>1.38</v>
       </c>
-      <c r="E72" s="17" t="inlineStr">
+      <c r="E73" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3413,27 +3449,27 @@
           </r>
         </is>
       </c>
-      <c r="F72" s="17" t="inlineStr">
+      <c r="F73" s="17" t="inlineStr">
         <is>
           <t>의료·정밀기기, 전기·전자</t>
         </is>
       </c>
-      <c r="G72" s="17" t="inlineStr">
-        <is>
-          <t>외국인 매수세로 코스피 3.29% 급등.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="31" customHeight="1" s="15">
-      <c r="A73" s="31" t="inlineStr">
+      <c r="G73" s="17" t="inlineStr">
+        <is>
+          <t>외국인 매수세로 반도체 중심 반등.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="31" customHeight="1" s="15">
+      <c r="A74" s="31" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B73" s="29" t="n">
+      <c r="B74" s="29" t="n">
         <v>-3.52</v>
       </c>
-      <c r="C73" s="31" t="inlineStr">
+      <c r="C74" s="31" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3456,10 +3492,10 @@
           </r>
         </is>
       </c>
-      <c r="D73" s="29" t="n">
+      <c r="D74" s="29" t="n">
         <v>-3.62</v>
       </c>
-      <c r="E73" s="17" t="inlineStr">
+      <c r="E74" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3482,242 +3518,227 @@
           </r>
         </is>
       </c>
-      <c r="F73" s="17" t="inlineStr">
+      <c r="F74" s="17" t="inlineStr">
         <is>
           <t>일반서비스, 비금속</t>
         </is>
       </c>
-      <c r="G73" s="17" t="inlineStr">
-        <is>
-          <t>기관 매도세로 코스피 3.52% 급락.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74"/>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="G74" s="17" t="inlineStr">
+        <is>
+          <t>외국인·기관 매도로 지수 급락.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="31" customHeight="1" s="15">
+      <c r="A75" s="31" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B75" s="28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C75" s="31" t="inlineStr">
+        <is>
+          <t>데이터 없음</t>
+        </is>
+      </c>
+      <c r="D75" s="29" t="n">
+        <v>-1.62</v>
+      </c>
+      <c r="E75" s="31" t="inlineStr">
+        <is>
+          <t>데이터 없음</t>
+        </is>
+      </c>
+      <c r="F75" s="17" t="inlineStr">
+        <is>
+          <t>제약, 의료·정밀기기</t>
+        </is>
+      </c>
+      <c r="G75" s="17" t="inlineStr">
+        <is>
+          <t>기관 매수로 코스피 상승 마감.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76"/>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>05</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>월간 종합 코멘트 — 매크로·수급</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr"/>
-      <c r="D75" s="3" t="inlineStr"/>
-      <c r="E75" s="3" t="inlineStr"/>
-      <c r="F75" s="3" t="inlineStr"/>
-      <c r="G75" s="3" t="inlineStr"/>
-      <c r="H75" s="3" t="inlineStr"/>
-      <c r="I75" s="3" t="inlineStr"/>
-      <c r="J75" s="3" t="inlineStr"/>
-      <c r="K75" s="3" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr"/>
+      <c r="D77" s="3" t="inlineStr"/>
+      <c r="E77" s="3" t="inlineStr"/>
+      <c r="F77" s="3" t="inlineStr"/>
+      <c r="G77" s="3" t="inlineStr"/>
+      <c r="H77" s="3" t="inlineStr"/>
+      <c r="I77" s="3" t="inlineStr"/>
+      <c r="J77" s="3" t="inlineStr"/>
+      <c r="K77" s="3" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B76" s="4" t="inlineStr">
+      <c r="B78" s="4" t="inlineStr">
         <is>
           <t>Comment</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="15" customHeight="1" s="15">
-      <c r="A77" s="17" t="inlineStr">
-        <is>
-          <t>- 미국 소비자물가지수(3.7%)와 생산자물가지수(1.3%)가 예상치를 상회하며 인플레이션 압력이 재확인된 매크로 환경이었습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="15" customHeight="1" s="15">
-      <c r="A78" s="17" t="inlineStr">
-        <is>
-          <t>- 외국인은 전기·전자 섹터에 대규모 순매도를 집중하며 지수 하락을 주도했고, 기관은 일부 섹터에서 방어적 매수를 보였습니다.</t>
         </is>
       </c>
     </row>
     <row r="79" ht="31" customHeight="1" s="15">
       <c r="A79" s="17" t="inlineStr">
         <is>
-          <t>- 시장 전반은 AI 인프라 투자 지속성과 수익성 사이에서 방향성을 탐색 중이며, 대형주 중심의 수급 변화가 지수 등락을 결정짓고 있습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="15" customHeight="1" s="15">
+          <t>- 매크로 환경: 9월 수출이 83.5% 급증하며 펀더멘털은 견조했으나, 미국 CPI(3.7%)와 PPI(1.3%)가 예상치를 상회하며 고금리 장기화 우려가 시장을 압박함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="31" customHeight="1" s="15">
       <c r="A80" s="17" t="inlineStr">
         <is>
-          <t>- 수출 펀더멘털은 견조하나, 고금리 장기화 우려가 기술주 중심의 수급 이탈을 가속화하며 변동성을 키우고 있습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81"/>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+          <t>- 수급 구도: 외국인의 대규모 순매도가 전기·전자 섹터에 집중되며 지수 하락을 주도했고, 기관은 제약 및 오락·문화 섹터에서 순매수를 기록하며 방어함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="31" customHeight="1" s="15">
+      <c r="A81" s="17" t="inlineStr">
+        <is>
+          <t>- 종합 관점: 시장은 AI 인프라 투자 지속성과 수익성 사이에서 방향성을 탐색 중이며, 대형주 중심의 외국인 수급 변화가 지수 등락의 핵심 변수로 작용함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82"/>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>06</t>
         </is>
       </c>
-      <c r="B82" s="3" t="inlineStr">
+      <c r="B83" s="3" t="inlineStr">
         <is>
           <t>투자자 합산 순매수 상위/하위</t>
         </is>
       </c>
-      <c r="C82" s="3" t="inlineStr"/>
-      <c r="D82" s="3" t="inlineStr"/>
-      <c r="E82" s="3" t="inlineStr"/>
-      <c r="F82" s="3" t="inlineStr"/>
-      <c r="G82" s="3" t="inlineStr"/>
-      <c r="H82" s="3" t="inlineStr"/>
-      <c r="I82" s="3" t="inlineStr"/>
-      <c r="J82" s="18" t="inlineStr">
+      <c r="C83" s="3" t="inlineStr"/>
+      <c r="D83" s="3" t="inlineStr"/>
+      <c r="E83" s="3" t="inlineStr"/>
+      <c r="F83" s="3" t="inlineStr"/>
+      <c r="G83" s="3" t="inlineStr"/>
+      <c r="H83" s="3" t="inlineStr"/>
+      <c r="I83" s="3" t="inlineStr"/>
+      <c r="J83" s="18" t="inlineStr">
         <is>
           <t>외인+기관계, 억원</t>
         </is>
       </c>
-      <c r="K82" s="3" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="4" t="inlineStr">
+      <c r="K83" s="3" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B83" s="4" t="inlineStr">
+      <c r="B84" s="4" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="C83" s="4" t="inlineStr">
+      <c r="C84" s="4" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="D83" s="4" t="inlineStr">
+      <c r="D84" s="4" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
+      <c r="E84" s="4" t="inlineStr">
         <is>
           <t>합산</t>
         </is>
       </c>
-      <c r="F83" s="4" t="inlineStr">
+      <c r="F84" s="4" t="inlineStr">
         <is>
           <t>외인</t>
         </is>
       </c>
-      <c r="G83" s="4" t="inlineStr">
+      <c r="G84" s="4" t="inlineStr">
         <is>
           <t>기관</t>
         </is>
       </c>
-      <c r="H83" s="4" t="inlineStr">
+      <c r="H84" s="4" t="inlineStr">
         <is>
           <t>개인</t>
         </is>
       </c>
-      <c r="I83" s="4" t="inlineStr">
+      <c r="I84" s="4" t="inlineStr">
         <is>
           <t>공매도</t>
         </is>
       </c>
-      <c r="J83" s="4" t="inlineStr">
+      <c r="J84" s="4" t="inlineStr">
         <is>
           <t>대차잔고</t>
         </is>
       </c>
-      <c r="K83" s="4" t="inlineStr">
+      <c r="K84" s="4" t="inlineStr">
         <is>
           <t>대차증감</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="31" customHeight="1" s="15">
-      <c r="A84" s="8" t="inlineStr">
+    <row r="85" ht="31" customHeight="1" s="15">
+      <c r="A85" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B84" s="31" t="n">
+      <c r="B85" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="C84" s="17" t="inlineStr">
+      <c r="C85" s="17" t="inlineStr">
         <is>
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="D84" s="34" t="inlineStr">
+      <c r="D85" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="E84" s="28" t="n">
+      <c r="E85" s="28" t="n">
         <v>3473</v>
       </c>
-      <c r="F84" s="29" t="n">
+      <c r="F85" s="29" t="n">
         <v>-1026</v>
       </c>
-      <c r="G84" s="28" t="n">
+      <c r="G85" s="28" t="n">
         <v>4498</v>
       </c>
-      <c r="H84" s="29" t="n">
+      <c r="H85" s="29" t="n">
         <v>-3450</v>
       </c>
-      <c r="I84" s="31" t="n">
+      <c r="I85" s="31" t="n">
         <v>6262.4</v>
       </c>
-      <c r="J84" s="31" t="n">
-        <v>42022.8</v>
-      </c>
-      <c r="K84" s="31" t="n">
-        <v>9054.9</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="8" t="inlineStr">
-        <is>
-          <t>순매수 상위</t>
-        </is>
-      </c>
-      <c r="B85" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="C85" s="31" t="inlineStr">
-        <is>
-          <t>삼성E&amp;A</t>
-        </is>
-      </c>
-      <c r="D85" s="34" t="inlineStr">
-        <is>
-          <t>일반서비스</t>
-        </is>
-      </c>
-      <c r="E85" s="28" t="n">
-        <v>2656</v>
-      </c>
-      <c r="F85" s="28" t="n">
-        <v>1314</v>
-      </c>
-      <c r="G85" s="28" t="n">
-        <v>1342</v>
-      </c>
-      <c r="H85" s="29" t="n">
-        <v>-2649</v>
-      </c>
-      <c r="I85" s="31" t="n">
-        <v>475.9</v>
-      </c>
       <c r="J85" s="31" t="n">
-        <v>3191.1</v>
+        <v>39744.6</v>
       </c>
       <c r="K85" s="31" t="n">
-        <v>-7.8</v>
+        <v>6776.7</v>
       </c>
     </row>
     <row r="86">
@@ -3727,38 +3748,38 @@
         </is>
       </c>
       <c r="B86" s="31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C86" s="31" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="D86" s="34" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>일반서비스</t>
         </is>
       </c>
       <c r="E86" s="28" t="n">
-        <v>2653</v>
+        <v>2656</v>
       </c>
       <c r="F86" s="28" t="n">
-        <v>295</v>
+        <v>1314</v>
       </c>
       <c r="G86" s="28" t="n">
-        <v>2357</v>
+        <v>1342</v>
       </c>
       <c r="H86" s="29" t="n">
-        <v>-3245</v>
+        <v>-2649</v>
       </c>
       <c r="I86" s="31" t="n">
-        <v>816.4</v>
+        <v>475.9</v>
       </c>
       <c r="J86" s="31" t="n">
-        <v>13600.9</v>
+        <v>3704.9</v>
       </c>
       <c r="K86" s="31" t="n">
-        <v>885.7</v>
+        <v>506</v>
       </c>
     </row>
     <row r="87">
@@ -3768,38 +3789,38 @@
         </is>
       </c>
       <c r="B87" s="31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C87" s="31" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="D87" s="34" t="inlineStr">
         <is>
-          <t>화학</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="E87" s="28" t="n">
-        <v>2251</v>
+        <v>2653</v>
       </c>
       <c r="F87" s="28" t="n">
-        <v>13</v>
+        <v>295</v>
       </c>
       <c r="G87" s="28" t="n">
-        <v>2239</v>
+        <v>2357</v>
       </c>
       <c r="H87" s="29" t="n">
-        <v>-1986</v>
+        <v>-3245</v>
       </c>
       <c r="I87" s="31" t="n">
-        <v>1762.9</v>
+        <v>816.4</v>
       </c>
       <c r="J87" s="31" t="n">
-        <v>6885.6</v>
+        <v>13339.6</v>
       </c>
       <c r="K87" s="31" t="n">
-        <v>3111.6</v>
+        <v>624.4</v>
       </c>
     </row>
     <row r="88">
@@ -3809,38 +3830,38 @@
         </is>
       </c>
       <c r="B88" s="31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C88" s="31" t="inlineStr">
         <is>
-          <t>HMM</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="D88" s="34" t="inlineStr">
         <is>
-          <t>운송·창고</t>
+          <t>화학</t>
         </is>
       </c>
       <c r="E88" s="28" t="n">
-        <v>1683</v>
+        <v>2251</v>
       </c>
       <c r="F88" s="28" t="n">
-        <v>1042</v>
+        <v>13</v>
       </c>
       <c r="G88" s="28" t="n">
-        <v>641</v>
+        <v>2239</v>
       </c>
       <c r="H88" s="29" t="n">
-        <v>-1670</v>
+        <v>-1986</v>
       </c>
       <c r="I88" s="31" t="n">
-        <v>144.4</v>
+        <v>1762.9</v>
       </c>
       <c r="J88" s="31" t="n">
-        <v>3589.1</v>
+        <v>6369.2</v>
       </c>
       <c r="K88" s="31" t="n">
-        <v>178.6</v>
+        <v>2595.2</v>
       </c>
     </row>
     <row r="89">
@@ -3850,38 +3871,38 @@
         </is>
       </c>
       <c r="B89" s="31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C89" s="31" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>HMM</t>
         </is>
       </c>
       <c r="D89" s="34" t="inlineStr">
         <is>
-          <t>일반서비스</t>
+          <t>운송·창고</t>
         </is>
       </c>
       <c r="E89" s="28" t="n">
-        <v>1537</v>
+        <v>1683</v>
       </c>
       <c r="F89" s="28" t="n">
-        <v>1125</v>
+        <v>1042</v>
       </c>
       <c r="G89" s="28" t="n">
-        <v>412</v>
+        <v>641</v>
       </c>
       <c r="H89" s="29" t="n">
-        <v>-1522</v>
+        <v>-1670</v>
       </c>
       <c r="I89" s="31" t="n">
-        <v>908.6</v>
+        <v>144.4</v>
       </c>
       <c r="J89" s="31" t="n">
-        <v>9403.5</v>
+        <v>3589.1</v>
       </c>
       <c r="K89" s="31" t="n">
-        <v>-1589.8</v>
+        <v>178.6</v>
       </c>
     </row>
     <row r="90">
@@ -3891,38 +3912,38 @@
         </is>
       </c>
       <c r="B90" s="31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C90" s="31" t="inlineStr">
         <is>
-          <t>하이브</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="D90" s="34" t="inlineStr">
         <is>
-          <t>오락·문화</t>
+          <t>일반서비스</t>
         </is>
       </c>
       <c r="E90" s="28" t="n">
-        <v>1295</v>
+        <v>1537</v>
       </c>
       <c r="F90" s="28" t="n">
-        <v>62</v>
+        <v>1125</v>
       </c>
       <c r="G90" s="28" t="n">
-        <v>1233</v>
+        <v>412</v>
       </c>
       <c r="H90" s="29" t="n">
-        <v>-1342</v>
+        <v>-1522</v>
       </c>
       <c r="I90" s="31" t="n">
-        <v>407.3</v>
+        <v>908.6</v>
       </c>
       <c r="J90" s="31" t="n">
-        <v>4399.6</v>
+        <v>9403.5</v>
       </c>
       <c r="K90" s="31" t="n">
-        <v>640.9</v>
+        <v>-1589.8</v>
       </c>
     </row>
     <row r="91">
@@ -3932,38 +3953,38 @@
         </is>
       </c>
       <c r="B91" s="31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C91" s="31" t="inlineStr">
         <is>
-          <t>LG씨엔에스</t>
+          <t>하이브</t>
         </is>
       </c>
       <c r="D91" s="34" t="inlineStr">
         <is>
-          <t>IT 서비스</t>
+          <t>오락·문화</t>
         </is>
       </c>
       <c r="E91" s="28" t="n">
-        <v>1136</v>
+        <v>1295</v>
       </c>
       <c r="F91" s="28" t="n">
-        <v>559</v>
+        <v>62</v>
       </c>
       <c r="G91" s="28" t="n">
-        <v>577</v>
+        <v>1233</v>
       </c>
       <c r="H91" s="29" t="n">
-        <v>-1108</v>
+        <v>-1342</v>
       </c>
       <c r="I91" s="31" t="n">
-        <v>165.1</v>
+        <v>407.3</v>
       </c>
       <c r="J91" s="31" t="n">
-        <v>2007.4</v>
+        <v>4399.6</v>
       </c>
       <c r="K91" s="31" t="n">
-        <v>-406.2</v>
+        <v>640.9</v>
       </c>
     </row>
     <row r="92">
@@ -3973,38 +3994,38 @@
         </is>
       </c>
       <c r="B92" s="31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C92" s="31" t="inlineStr">
         <is>
-          <t>유한양행</t>
+          <t>LG씨엔에스</t>
         </is>
       </c>
       <c r="D92" s="34" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>IT 서비스</t>
         </is>
       </c>
       <c r="E92" s="28" t="n">
-        <v>688</v>
+        <v>1136</v>
       </c>
       <c r="F92" s="28" t="n">
-        <v>271</v>
+        <v>559</v>
       </c>
       <c r="G92" s="28" t="n">
-        <v>417</v>
+        <v>577</v>
       </c>
       <c r="H92" s="29" t="n">
-        <v>-675</v>
+        <v>-1108</v>
       </c>
       <c r="I92" s="31" t="n">
-        <v>139.8</v>
+        <v>165.1</v>
       </c>
       <c r="J92" s="31" t="n">
-        <v>9538.200000000001</v>
+        <v>2038.6</v>
       </c>
       <c r="K92" s="31" t="n">
-        <v>1057.6</v>
+        <v>-375</v>
       </c>
     </row>
     <row r="93">
@@ -4014,79 +4035,79 @@
         </is>
       </c>
       <c r="B93" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="C93" s="31" t="inlineStr">
+        <is>
+          <t>유한양행</t>
+        </is>
+      </c>
+      <c r="D93" s="34" t="inlineStr">
+        <is>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="E93" s="28" t="n">
+        <v>688</v>
+      </c>
+      <c r="F93" s="28" t="n">
+        <v>271</v>
+      </c>
+      <c r="G93" s="28" t="n">
+        <v>417</v>
+      </c>
+      <c r="H93" s="29" t="n">
+        <v>-675</v>
+      </c>
+      <c r="I93" s="31" t="n">
+        <v>139.8</v>
+      </c>
+      <c r="J93" s="31" t="n">
+        <v>9145.9</v>
+      </c>
+      <c r="K93" s="31" t="n">
+        <v>665.3</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B94" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="C93" s="31" t="inlineStr">
+      <c r="C94" s="31" t="inlineStr">
         <is>
           <t>고영</t>
         </is>
       </c>
-      <c r="D93" s="34" t="inlineStr">
+      <c r="D94" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="E93" s="28" t="n">
+      <c r="E94" s="28" t="n">
         <v>596</v>
       </c>
-      <c r="F93" s="28" t="n">
+      <c r="F94" s="28" t="n">
         <v>551</v>
       </c>
-      <c r="G93" s="28" t="n">
+      <c r="G94" s="28" t="n">
         <v>45</v>
       </c>
-      <c r="H93" s="29" t="n">
+      <c r="H94" s="29" t="n">
         <v>-620</v>
       </c>
-      <c r="I93" s="31" t="n">
+      <c r="I94" s="31" t="n">
         <v>93.3</v>
       </c>
-      <c r="J93" s="31" t="n">
+      <c r="J94" s="31" t="n">
         <v>1436.3</v>
       </c>
-      <c r="K93" s="31" t="n">
+      <c r="K94" s="31" t="n">
         <v>-107.4</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="10" t="inlineStr">
-        <is>
-          <t>순매도 상위</t>
-        </is>
-      </c>
-      <c r="B94" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C94" s="31" t="inlineStr">
-        <is>
-          <t>SK하이닉스</t>
-        </is>
-      </c>
-      <c r="D94" s="34" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="E94" s="29" t="n">
-        <v>-100163</v>
-      </c>
-      <c r="F94" s="29" t="n">
-        <v>-97475</v>
-      </c>
-      <c r="G94" s="29" t="n">
-        <v>-2688</v>
-      </c>
-      <c r="H94" s="28" t="n">
-        <v>9900</v>
-      </c>
-      <c r="I94" s="31" t="n">
-        <v>28973.6</v>
-      </c>
-      <c r="J94" s="31" t="n">
-        <v>154505.1</v>
-      </c>
-      <c r="K94" s="31" t="n">
-        <v>-71212</v>
       </c>
     </row>
     <row r="95">
@@ -4096,11 +4117,11 @@
         </is>
       </c>
       <c r="B95" s="31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C95" s="31" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="D95" s="34" t="inlineStr">
@@ -4109,25 +4130,25 @@
         </is>
       </c>
       <c r="E95" s="29" t="n">
-        <v>-52943</v>
+        <v>-100163</v>
       </c>
       <c r="F95" s="29" t="n">
-        <v>-36199</v>
+        <v>-97475</v>
       </c>
       <c r="G95" s="29" t="n">
-        <v>-16744</v>
+        <v>-2688</v>
       </c>
       <c r="H95" s="28" t="n">
-        <v>38513</v>
+        <v>9900</v>
       </c>
       <c r="I95" s="31" t="n">
-        <v>20083.2</v>
+        <v>28973.6</v>
       </c>
       <c r="J95" s="31" t="n">
-        <v>185130.7</v>
+        <v>144905.4</v>
       </c>
       <c r="K95" s="31" t="n">
-        <v>-14586.9</v>
+        <v>-80811.7</v>
       </c>
     </row>
     <row r="96">
@@ -4137,11 +4158,11 @@
         </is>
       </c>
       <c r="B96" s="31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C96" s="31" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="D96" s="34" t="inlineStr">
@@ -4150,25 +4171,25 @@
         </is>
       </c>
       <c r="E96" s="29" t="n">
-        <v>-5814</v>
+        <v>-52943</v>
       </c>
       <c r="F96" s="29" t="n">
-        <v>-3168</v>
+        <v>-36199</v>
       </c>
       <c r="G96" s="29" t="n">
-        <v>-2646</v>
+        <v>-16744</v>
       </c>
       <c r="H96" s="28" t="n">
-        <v>5683</v>
+        <v>38513</v>
       </c>
       <c r="I96" s="31" t="n">
-        <v>3750.9</v>
+        <v>20083.2</v>
       </c>
       <c r="J96" s="31" t="n">
-        <v>28767.9</v>
+        <v>175096.2</v>
       </c>
       <c r="K96" s="31" t="n">
-        <v>-7714.3</v>
+        <v>-24621.4</v>
       </c>
     </row>
     <row r="97">
@@ -4178,38 +4199,38 @@
         </is>
       </c>
       <c r="B97" s="31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C97" s="31" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="D97" s="34" t="inlineStr">
         <is>
-          <t>기타금융</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="E97" s="29" t="n">
-        <v>-5132</v>
+        <v>-5814</v>
       </c>
       <c r="F97" s="29" t="n">
-        <v>-7020</v>
-      </c>
-      <c r="G97" s="28" t="n">
-        <v>1888</v>
+        <v>-3168</v>
+      </c>
+      <c r="G97" s="29" t="n">
+        <v>-2646</v>
       </c>
       <c r="H97" s="28" t="n">
-        <v>5087</v>
+        <v>5683</v>
       </c>
       <c r="I97" s="31" t="n">
-        <v>5124.2</v>
+        <v>3750.9</v>
       </c>
       <c r="J97" s="31" t="n">
-        <v>21826.9</v>
+        <v>28267.5</v>
       </c>
       <c r="K97" s="31" t="n">
-        <v>-9609.5</v>
+        <v>-8214.700000000001</v>
       </c>
     </row>
     <row r="98">
@@ -4219,38 +4240,38 @@
         </is>
       </c>
       <c r="B98" s="31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C98" s="31" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>SK스퀘어</t>
         </is>
       </c>
       <c r="D98" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>기타금융</t>
         </is>
       </c>
       <c r="E98" s="29" t="n">
-        <v>-4840</v>
+        <v>-5132</v>
       </c>
       <c r="F98" s="29" t="n">
-        <v>-3611</v>
-      </c>
-      <c r="G98" s="29" t="n">
-        <v>-1229</v>
+        <v>-7020</v>
+      </c>
+      <c r="G98" s="28" t="n">
+        <v>1888</v>
       </c>
       <c r="H98" s="28" t="n">
-        <v>4425</v>
+        <v>5087</v>
       </c>
       <c r="I98" s="31" t="n">
-        <v>820.2</v>
+        <v>5124.2</v>
       </c>
       <c r="J98" s="31" t="n">
-        <v>25343.8</v>
+        <v>20822.3</v>
       </c>
       <c r="K98" s="31" t="n">
-        <v>808.8</v>
+        <v>-10614.1</v>
       </c>
     </row>
     <row r="99">
@@ -4260,11 +4281,11 @@
         </is>
       </c>
       <c r="B99" s="31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C99" s="31" t="inlineStr">
         <is>
-          <t>효성중공업</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="D99" s="34" t="inlineStr">
@@ -4273,25 +4294,25 @@
         </is>
       </c>
       <c r="E99" s="29" t="n">
-        <v>-4681</v>
+        <v>-4840</v>
       </c>
       <c r="F99" s="29" t="n">
-        <v>-3795</v>
+        <v>-3611</v>
       </c>
       <c r="G99" s="29" t="n">
-        <v>-885</v>
+        <v>-1229</v>
       </c>
       <c r="H99" s="28" t="n">
-        <v>4665</v>
+        <v>4425</v>
       </c>
       <c r="I99" s="31" t="n">
-        <v>1777.7</v>
+        <v>820.2</v>
       </c>
       <c r="J99" s="31" t="n">
-        <v>3861</v>
+        <v>24488.6</v>
       </c>
       <c r="K99" s="31" t="n">
-        <v>-1554.2</v>
+        <v>-46.4</v>
       </c>
     </row>
     <row r="100">
@@ -4301,38 +4322,38 @@
         </is>
       </c>
       <c r="B100" s="31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C100" s="31" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>효성중공업</t>
         </is>
       </c>
       <c r="D100" s="34" t="inlineStr">
         <is>
-          <t>기계·장비</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="E100" s="29" t="n">
-        <v>-3163</v>
+        <v>-4681</v>
       </c>
       <c r="F100" s="29" t="n">
-        <v>-3072</v>
+        <v>-3795</v>
       </c>
       <c r="G100" s="29" t="n">
-        <v>-91</v>
+        <v>-885</v>
       </c>
       <c r="H100" s="28" t="n">
-        <v>3151</v>
+        <v>4665</v>
       </c>
       <c r="I100" s="31" t="n">
-        <v>4413.7</v>
+        <v>1777.7</v>
       </c>
       <c r="J100" s="31" t="n">
-        <v>16844.8</v>
+        <v>3630.1</v>
       </c>
       <c r="K100" s="31" t="n">
-        <v>-3574.9</v>
+        <v>-1785.1</v>
       </c>
     </row>
     <row r="101">
@@ -4342,599 +4363,633 @@
         </is>
       </c>
       <c r="B101" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="C101" s="31" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="D101" s="34" t="inlineStr">
+        <is>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="E101" s="29" t="n">
+        <v>-3163</v>
+      </c>
+      <c r="F101" s="29" t="n">
+        <v>-3072</v>
+      </c>
+      <c r="G101" s="29" t="n">
+        <v>-91</v>
+      </c>
+      <c r="H101" s="28" t="n">
+        <v>3151</v>
+      </c>
+      <c r="I101" s="31" t="n">
+        <v>4413.7</v>
+      </c>
+      <c r="J101" s="31" t="n">
+        <v>16084</v>
+      </c>
+      <c r="K101" s="31" t="n">
+        <v>-4335.7</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B102" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="C101" s="31" t="inlineStr">
+      <c r="C102" s="31" t="inlineStr">
         <is>
           <t>LG전자</t>
         </is>
       </c>
-      <c r="D101" s="34" t="inlineStr">
+      <c r="D102" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="E101" s="29" t="n">
+      <c r="E102" s="29" t="n">
         <v>-2517</v>
       </c>
-      <c r="F101" s="29" t="n">
+      <c r="F102" s="29" t="n">
         <v>-2354</v>
       </c>
-      <c r="G101" s="29" t="n">
+      <c r="G102" s="29" t="n">
         <v>-163</v>
       </c>
-      <c r="H101" s="28" t="n">
+      <c r="H102" s="28" t="n">
         <v>2440</v>
       </c>
-      <c r="I101" s="31" t="n">
+      <c r="I102" s="31" t="n">
         <v>2503.8</v>
       </c>
-      <c r="J101" s="31" t="n">
-        <v>7545.3</v>
-      </c>
-      <c r="K101" s="31" t="n">
-        <v>-2139.7</v>
-      </c>
-    </row>
-    <row r="102" ht="31" customHeight="1" s="15">
-      <c r="A102" s="10" t="inlineStr">
+      <c r="J102" s="31" t="n">
+        <v>7245.5</v>
+      </c>
+      <c r="K102" s="31" t="n">
+        <v>-2439.5</v>
+      </c>
+    </row>
+    <row r="103" ht="31" customHeight="1" s="15">
+      <c r="A103" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B102" s="31" t="n">
+      <c r="B103" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="C102" s="17" t="inlineStr">
+      <c r="C103" s="17" t="inlineStr">
         <is>
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="D102" s="34" t="inlineStr">
+      <c r="D103" s="34" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="E102" s="29" t="n">
+      <c r="E103" s="29" t="n">
         <v>-1653</v>
       </c>
-      <c r="F102" s="29" t="n">
+      <c r="F103" s="29" t="n">
         <v>-1503</v>
       </c>
-      <c r="G102" s="29" t="n">
+      <c r="G103" s="29" t="n">
         <v>-151</v>
       </c>
-      <c r="H102" s="28" t="n">
+      <c r="H103" s="28" t="n">
         <v>1665</v>
       </c>
-      <c r="I102" s="31" t="n">
+      <c r="I103" s="31" t="n">
         <v>2181.3</v>
       </c>
-      <c r="J102" s="31" t="n">
-        <v>9770.4</v>
-      </c>
-      <c r="K102" s="31" t="n">
-        <v>-3271.2</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="10" t="inlineStr">
+      <c r="J103" s="31" t="n">
+        <v>9947.6</v>
+      </c>
+      <c r="K103" s="31" t="n">
+        <v>-3094</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B103" s="31" t="n">
+      <c r="B104" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="C103" s="31" t="inlineStr">
+      <c r="C104" s="31" t="inlineStr">
         <is>
           <t>LS ELECTRIC</t>
         </is>
       </c>
-      <c r="D103" s="34" t="inlineStr">
+      <c r="D104" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="E103" s="29" t="n">
+      <c r="E104" s="29" t="n">
         <v>-1549</v>
       </c>
-      <c r="F103" s="29" t="n">
+      <c r="F104" s="29" t="n">
         <v>-1140</v>
       </c>
-      <c r="G103" s="29" t="n">
+      <c r="G104" s="29" t="n">
         <v>-409</v>
       </c>
-      <c r="H103" s="28" t="n">
+      <c r="H104" s="28" t="n">
         <v>1505</v>
       </c>
-      <c r="I103" s="31" t="n">
+      <c r="I104" s="31" t="n">
         <v>2040.7</v>
       </c>
-      <c r="J103" s="31" t="n">
-        <v>8093.8</v>
-      </c>
-      <c r="K103" s="31" t="n">
-        <v>-725.7</v>
-      </c>
-    </row>
-    <row r="104"/>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="J104" s="31" t="n">
+        <v>7824.1</v>
+      </c>
+      <c r="K104" s="31" t="n">
+        <v>-995.4</v>
+      </c>
+    </row>
+    <row r="105"/>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>07</t>
         </is>
       </c>
-      <c r="B105" s="3" t="inlineStr">
+      <c r="B106" s="3" t="inlineStr">
         <is>
           <t>섹터 시그널 종목 관찰</t>
         </is>
       </c>
-      <c r="C105" s="3" t="inlineStr"/>
-      <c r="D105" s="3" t="inlineStr"/>
-      <c r="E105" s="3" t="inlineStr"/>
-      <c r="F105" s="3" t="inlineStr"/>
-      <c r="G105" s="18" t="inlineStr">
+      <c r="C106" s="3" t="inlineStr"/>
+      <c r="D106" s="3" t="inlineStr"/>
+      <c r="E106" s="3" t="inlineStr"/>
+      <c r="F106" s="3" t="inlineStr"/>
+      <c r="G106" s="18" t="inlineStr">
         <is>
           <t>섹터 상태 x 수급 x 공매도·대차 x 촉매</t>
         </is>
       </c>
-      <c r="H105" s="3" t="inlineStr"/>
-      <c r="I105" s="3" t="inlineStr"/>
-      <c r="J105" s="3" t="inlineStr"/>
-      <c r="K105" s="3" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="35" t="inlineStr">
+      <c r="H106" s="3" t="inlineStr"/>
+      <c r="I106" s="3" t="inlineStr"/>
+      <c r="J106" s="3" t="inlineStr"/>
+      <c r="K106" s="3" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="35" t="inlineStr">
         <is>
           <t>● 동반강세 — 추세 지속형 상방 관찰</t>
         </is>
       </c>
-      <c r="G106" s="3" t="inlineStr">
+      <c r="G107" s="3" t="inlineStr">
         <is>
           <t>● 수급유입 — 초기 유입형 상방 관찰</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="5" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="B108" s="34" t="inlineStr">
+        <is>
+          <t>일반서비스</t>
+        </is>
+      </c>
+      <c r="C108" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D108" s="31" t="inlineStr"/>
+      <c r="E108" s="31" t="inlineStr"/>
+      <c r="G108" s="5" t="inlineStr">
+        <is>
+          <t>아모레퍼시픽</t>
+        </is>
+      </c>
+      <c r="H108" s="34" t="inlineStr">
+        <is>
+          <t>화학</t>
+        </is>
+      </c>
+      <c r="I108" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="J108" s="31" t="inlineStr"/>
+      <c r="K108" s="31" t="inlineStr"/>
+    </row>
+    <row r="109" ht="44.5" customHeight="1" s="15">
+      <c r="A109" s="17" t="inlineStr">
+        <is>
+          <t>외국인 +1,125억 순매수, 기관 +412억 순매수, 대차잔고 -1,590억 감소 — 일반서비스(동반강세) 섹터 추세 지속형 상방 관찰</t>
+        </is>
+      </c>
+      <c r="G109" s="17" t="inlineStr">
+        <is>
+          <t>외국인 +67억 순매수, 기관 +155억 순매수, 대차잔고 -373억 감소 — 화학(수급유입) 섹터 초기 유입형 상방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
         <is>
           <t>케이씨텍</t>
         </is>
       </c>
-      <c r="B107" s="34" t="inlineStr">
+      <c r="B110" s="34" t="inlineStr">
         <is>
           <t>의료·정밀기기</t>
         </is>
       </c>
-      <c r="C107" s="36" t="n">
+      <c r="C110" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="D107" s="31" t="inlineStr"/>
-      <c r="E107" s="31" t="inlineStr"/>
-      <c r="G107" s="5" t="inlineStr">
-        <is>
-          <t>아모레퍼시픽</t>
-        </is>
-      </c>
-      <c r="H107" s="34" t="inlineStr">
+      <c r="D110" s="31" t="inlineStr"/>
+      <c r="E110" s="31" t="inlineStr"/>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>F&amp;F</t>
+        </is>
+      </c>
+      <c r="H110" s="34" t="inlineStr">
+        <is>
+          <t>섬유·의류</t>
+        </is>
+      </c>
+      <c r="I110" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="J110" s="31" t="inlineStr"/>
+      <c r="K110" s="31" t="inlineStr"/>
+    </row>
+    <row r="111" ht="44.5" customHeight="1" s="15">
+      <c r="A111" s="17" t="inlineStr">
+        <is>
+          <t>외국인 +233억 순매수, 기관 +547억 순매수, 대차잔고 -57억 감소 — 의료·정밀기기(동반강세) 섹터 추세 지속형 상방 관찰</t>
+        </is>
+      </c>
+      <c r="G111" s="17" t="inlineStr">
+        <is>
+          <t>외국인 +136억 순매수, 기관 +47억 순매수, 대차잔고 -19억 감소 — 섬유·의류(수급유입) 섹터 초기 유입형 상방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>CJ제일제당</t>
+        </is>
+      </c>
+      <c r="B112" s="34" t="inlineStr">
+        <is>
+          <t>음식료·담배</t>
+        </is>
+      </c>
+      <c r="C112" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D112" s="31" t="inlineStr"/>
+      <c r="E112" s="31" t="inlineStr"/>
+      <c r="G112" s="5" t="inlineStr">
+        <is>
+          <t>LG생활건강</t>
+        </is>
+      </c>
+      <c r="H112" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="I107" s="37" t="n">
+      <c r="I112" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="J107" s="31" t="inlineStr"/>
-      <c r="K107" s="31" t="inlineStr"/>
-    </row>
-    <row r="108" ht="44.5" customHeight="1" s="15">
-      <c r="A108" s="17" t="inlineStr">
-        <is>
-          <t>외국인 +312억 순매수, 기관 +500억 순매수, 대차잔고 0억 감소 — 의료·정밀기기(동반강세) 섹터 추세 지속형 상방 관찰</t>
-        </is>
-      </c>
-      <c r="G108" s="17" t="inlineStr">
-        <is>
-          <t>외국인 +53억 순매수, 기관 +172억 순매수, 대차잔고 -296억 감소 — 화학(수급유입) 섹터 초기 유입형 상방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="5" t="inlineStr">
-        <is>
-          <t>CJ제일제당</t>
-        </is>
-      </c>
-      <c r="B109" s="34" t="inlineStr">
+      <c r="J112" s="31" t="inlineStr"/>
+      <c r="K112" s="31" t="inlineStr"/>
+    </row>
+    <row r="113" ht="44.5" customHeight="1" s="15">
+      <c r="A113" s="17" t="inlineStr">
+        <is>
+          <t>외국인 +120억 순매수, 기관 +244억 순매수, 대차잔고 -214억 감소 — 음식료·담배(동반강세) 섹터 추세 지속형 상방 관찰</t>
+        </is>
+      </c>
+      <c r="G113" s="17" t="inlineStr">
+        <is>
+          <t>외국인 +145억 순매수, 기관 +37억 순매수, 대차잔고 -76억 감소 — 화학(수급유입) 섹터 초기 유입형 상방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>한전기술</t>
+        </is>
+      </c>
+      <c r="B114" s="34" t="inlineStr">
+        <is>
+          <t>일반서비스</t>
+        </is>
+      </c>
+      <c r="C114" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D114" s="31" t="inlineStr"/>
+      <c r="E114" s="31" t="inlineStr"/>
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t>에스엠국일</t>
+        </is>
+      </c>
+      <c r="H114" s="34" t="inlineStr">
+        <is>
+          <t>종이·목재</t>
+        </is>
+      </c>
+      <c r="I114" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="J114" s="31" t="inlineStr"/>
+      <c r="K114" s="31" t="inlineStr"/>
+    </row>
+    <row r="115" ht="44.5" customHeight="1" s="15">
+      <c r="A115" s="17" t="inlineStr">
+        <is>
+          <t>외국인 +320억 순매수, 기관 +30억 순매수, 대차잔고 -1,082억 감소 — 일반서비스(동반강세) 섹터 추세 지속형 상방 관찰</t>
+        </is>
+      </c>
+      <c r="G115" s="17" t="inlineStr">
+        <is>
+          <t>외국인 +4억 순매수, 기관 +8억 순매수, 대차잔고 0억 감소 — 종이·목재(수급유입) 섹터 초기 유입형 상방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>빙그레</t>
+        </is>
+      </c>
+      <c r="B116" s="34" t="inlineStr">
         <is>
           <t>음식료·담배</t>
         </is>
       </c>
-      <c r="C109" s="36" t="n">
+      <c r="C116" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="D109" s="31" t="inlineStr"/>
-      <c r="E109" s="31" t="inlineStr"/>
-      <c r="G109" s="5" t="inlineStr">
-        <is>
-          <t>LG생활건강</t>
-        </is>
-      </c>
-      <c r="H109" s="34" t="inlineStr">
-        <is>
-          <t>화학</t>
-        </is>
-      </c>
-      <c r="I109" s="37" t="n">
+      <c r="D116" s="31" t="inlineStr"/>
+      <c r="E116" s="31" t="inlineStr"/>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>동화기업</t>
+        </is>
+      </c>
+      <c r="H116" s="34" t="inlineStr">
+        <is>
+          <t>종이·목재</t>
+        </is>
+      </c>
+      <c r="I116" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="J109" s="31" t="inlineStr"/>
-      <c r="K109" s="31" t="inlineStr"/>
-    </row>
-    <row r="110" ht="44.5" customHeight="1" s="15">
-      <c r="A110" s="17" t="inlineStr">
-        <is>
-          <t>외국인 +141억 순매수, 기관 +223억 순매수, 대차잔고 -182억 감소 — 음식료·담배(동반강세) 섹터 추세 지속형 상방 관찰</t>
-        </is>
-      </c>
-      <c r="G110" s="17" t="inlineStr">
-        <is>
-          <t>외국인 +147억 순매수, 기관 +34억 순매수, 대차잔고 -114억 감소 — 화학(수급유입) 섹터 초기 유입형 상방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="5" t="inlineStr">
-        <is>
-          <t>빙그레</t>
-        </is>
-      </c>
-      <c r="B111" s="34" t="inlineStr">
-        <is>
-          <t>음식료·담배</t>
-        </is>
-      </c>
-      <c r="C111" s="36" t="n">
-        <v>3</v>
-      </c>
-      <c r="D111" s="31" t="inlineStr"/>
-      <c r="E111" s="31" t="inlineStr"/>
-      <c r="G111" s="5" t="inlineStr">
-        <is>
-          <t>F&amp;F</t>
-        </is>
-      </c>
-      <c r="H111" s="34" t="inlineStr">
-        <is>
-          <t>섬유·의류</t>
-        </is>
-      </c>
-      <c r="I111" s="37" t="n">
-        <v>3</v>
-      </c>
-      <c r="J111" s="31" t="inlineStr"/>
-      <c r="K111" s="31" t="inlineStr"/>
-    </row>
-    <row r="112" ht="44.5" customHeight="1" s="15">
-      <c r="A112" s="17" t="inlineStr">
-        <is>
-          <t>외국인 +113억 순매수, 기관 +45억 순매수, 대차잔고 -31억 감소 — 음식료·담배(동반강세) 섹터 추세 지속형 상방 관찰</t>
-        </is>
-      </c>
-      <c r="G112" s="17" t="inlineStr">
-        <is>
-          <t>외국인 +135억 순매수, 기관 +42억 순매수, 대차잔고 -10억 감소 — 섬유·의류(수급유입) 섹터 초기 유입형 상방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="5" t="inlineStr">
-        <is>
-          <t>인바디</t>
-        </is>
-      </c>
-      <c r="B113" s="34" t="inlineStr">
-        <is>
-          <t>의료·정밀기기</t>
-        </is>
-      </c>
-      <c r="C113" s="36" t="n">
-        <v>3</v>
-      </c>
-      <c r="D113" s="31" t="inlineStr"/>
-      <c r="E113" s="31" t="inlineStr"/>
-      <c r="G113" s="5" t="inlineStr">
-        <is>
-          <t>SGC에너지</t>
-        </is>
-      </c>
-      <c r="H113" s="34" t="inlineStr">
-        <is>
-          <t>전기·가스</t>
-        </is>
-      </c>
-      <c r="I113" s="37" t="n">
-        <v>3</v>
-      </c>
-      <c r="J113" s="31" t="inlineStr"/>
-      <c r="K113" s="31" t="inlineStr"/>
-    </row>
-    <row r="114" ht="44.5" customHeight="1" s="15">
-      <c r="A114" s="17" t="inlineStr">
-        <is>
-          <t>외국인 +5억 순매수, 기관 +17억 순매수, 대차잔고 -22억 감소 — 의료·정밀기기(동반강세) 섹터 추세 지속형 상방 관찰</t>
-        </is>
-      </c>
-      <c r="G114" s="17" t="inlineStr">
-        <is>
-          <t>외국인 +11억 순매수, 기관 +7억 순매수, 대차잔고 -52억 감소 — 전기·가스(수급유입) 섹터 초기 유입형 상방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="5" t="inlineStr">
-        <is>
-          <t>롯데웰푸드</t>
-        </is>
-      </c>
-      <c r="B115" s="34" t="inlineStr">
-        <is>
-          <t>음식료·담배</t>
-        </is>
-      </c>
-      <c r="C115" s="36" t="n">
-        <v>3</v>
-      </c>
-      <c r="D115" s="31" t="inlineStr"/>
-      <c r="E115" s="31" t="inlineStr"/>
-      <c r="G115" s="5" t="inlineStr">
-        <is>
-          <t>에스엠국일</t>
-        </is>
-      </c>
-      <c r="H115" s="34" t="inlineStr">
-        <is>
-          <t>종이·목재</t>
-        </is>
-      </c>
-      <c r="I115" s="37" t="n">
-        <v>3</v>
-      </c>
-      <c r="J115" s="31" t="inlineStr"/>
-      <c r="K115" s="31" t="inlineStr"/>
-    </row>
-    <row r="116" ht="44.5" customHeight="1" s="15">
-      <c r="A116" s="17" t="inlineStr">
-        <is>
-          <t>외국인 +4억 순매수, 기관 +15억 순매수, 대차잔고 -49억 감소 — 음식료·담배(동반강세) 섹터 추세 지속형 상방 관찰</t>
-        </is>
-      </c>
-      <c r="G116" s="17" t="inlineStr">
-        <is>
-          <t>외국인 +4억 순매수, 기관 +8억 순매수, 대차잔고 -1억 감소 — 종이·목재(수급유입) 섹터 초기 유입형 상방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="117"/>
-    <row r="118">
-      <c r="A118" s="38" t="inlineStr">
+      <c r="J116" s="31" t="inlineStr"/>
+      <c r="K116" s="31" t="inlineStr"/>
+    </row>
+    <row r="117" ht="44.5" customHeight="1" s="15">
+      <c r="A117" s="17" t="inlineStr">
+        <is>
+          <t>외국인 +121억 순매수, 기관 +43억 순매수, 대차잔고 -42억 감소 — 음식료·담배(동반강세) 섹터 추세 지속형 상방 관찰</t>
+        </is>
+      </c>
+      <c r="G117" s="17" t="inlineStr">
+        <is>
+          <t>외국인 +6억 순매수, 기관 +2억 순매수, 대차잔고 -10억 감소 — 종이·목재(수급유입) 섹터 초기 유입형 상방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="118"/>
+    <row r="119">
+      <c r="A119" s="38" t="inlineStr">
         <is>
           <t>● 수급이탈 — 상승 후 약화 관찰</t>
         </is>
       </c>
-      <c r="G118" s="39" t="inlineStr">
+      <c r="G119" s="39" t="inlineStr">
         <is>
           <t>● 동반약세 — 약세 지속형 하방 관찰</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="31" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="31" t="inlineStr">
         <is>
           <t>해당 섹터·조건 충족 종목 없음</t>
         </is>
       </c>
-      <c r="G119" s="5" t="inlineStr">
-        <is>
-          <t>삼성전자우</t>
-        </is>
-      </c>
-      <c r="H119" s="34" t="inlineStr">
+      <c r="G120" s="5" t="inlineStr">
+        <is>
+          <t>포스코퓨처엠</t>
+        </is>
+      </c>
+      <c r="H120" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="I119" s="40" t="n">
+      <c r="I120" s="40" t="n">
         <v>-3</v>
       </c>
-      <c r="J119" s="31" t="inlineStr"/>
-      <c r="K119" s="31" t="inlineStr"/>
-    </row>
-    <row r="120" ht="44.5" customHeight="1" s="15">
-      <c r="G120" s="17" t="inlineStr">
-        <is>
-          <t>외국인 -3,611억 순매도, 기관 -1,229억 순매도, 대차잔고 +809억 증가 — 전기·전자(동반약세) 섹터 약세 지속형 하방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="G121" s="5" t="inlineStr">
-        <is>
-          <t>포스코퓨처엠</t>
-        </is>
-      </c>
-      <c r="H121" s="34" t="inlineStr">
+      <c r="J120" s="31" t="inlineStr"/>
+      <c r="K120" s="31" t="inlineStr"/>
+    </row>
+    <row r="121" ht="44.5" customHeight="1" s="15">
+      <c r="G121" s="17" t="inlineStr">
+        <is>
+          <t>외국인 -641억 순매도, 기관 -67억 순매도, 대차잔고 +864억 증가 — 전기·전자(동반약세) 섹터 약세 지속형 하방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="H122" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="I121" s="40" t="n">
-        <v>-3</v>
-      </c>
-      <c r="J121" s="31" t="inlineStr"/>
-      <c r="K121" s="31" t="inlineStr"/>
-    </row>
-    <row r="122" ht="44.5" customHeight="1" s="15">
-      <c r="G122" s="17" t="inlineStr">
-        <is>
-          <t>외국인 -553억 순매도, 기관 -58억 순매도, 대차잔고 +1,549억 증가 — 전기·전자(동반약세) 섹터 약세 지속형 하방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="G123" s="5" t="inlineStr">
-        <is>
-          <t>SK하이닉스</t>
-        </is>
-      </c>
-      <c r="H123" s="34" t="inlineStr">
+      <c r="I122" s="40" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J122" s="31" t="inlineStr"/>
+      <c r="K122" s="31" t="inlineStr"/>
+    </row>
+    <row r="123" ht="44.5" customHeight="1" s="15">
+      <c r="G123" s="17" t="inlineStr">
+        <is>
+          <t>외국인 -97,475억 순매도, 기관 -2,688억 순매도, 공매도 누적 상위 등재 — 전기·전자(동반약세) 섹터 약세 지속형 하방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="G124" s="5" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="H124" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="I123" s="40" t="n">
+      <c r="I124" s="40" t="n">
         <v>-2</v>
       </c>
-      <c r="J123" s="31" t="inlineStr"/>
-      <c r="K123" s="31" t="inlineStr"/>
-    </row>
-    <row r="124" ht="44.5" customHeight="1" s="15">
-      <c r="G124" s="17" t="inlineStr">
-        <is>
-          <t>외국인 -97,475억 순매도, 기관 -2,688억 순매도, 공매도 누적 상위 등재 — 전기·전자(동반약세) 섹터 약세 지속형 하방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="G125" s="5" t="inlineStr">
-        <is>
-          <t>삼성전자</t>
-        </is>
-      </c>
-      <c r="H125" s="34" t="inlineStr">
+      <c r="J124" s="31" t="inlineStr"/>
+      <c r="K124" s="31" t="inlineStr"/>
+    </row>
+    <row r="125" ht="44.5" customHeight="1" s="15">
+      <c r="G125" s="17" t="inlineStr">
+        <is>
+          <t>외국인 -36,199억 순매도, 기관 -16,744억 순매도, 공매도 누적 상위 등재 — 전기·전자(동반약세) 섹터 약세 지속형 하방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="G126" s="5" t="inlineStr">
+        <is>
+          <t>삼성전기</t>
+        </is>
+      </c>
+      <c r="H126" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="I125" s="40" t="n">
+      <c r="I126" s="40" t="n">
         <v>-2</v>
       </c>
-      <c r="J125" s="31" t="inlineStr"/>
-      <c r="K125" s="31" t="inlineStr"/>
-    </row>
-    <row r="126" ht="44.5" customHeight="1" s="15">
-      <c r="G126" s="17" t="inlineStr">
-        <is>
-          <t>외국인 -36,199억 순매도, 기관 -16,744억 순매도, 공매도 누적 상위 등재 — 전기·전자(동반약세) 섹터 약세 지속형 하방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="G127" s="5" t="inlineStr">
-        <is>
-          <t>삼성전기</t>
-        </is>
-      </c>
-      <c r="H127" s="34" t="inlineStr">
+      <c r="J126" s="31" t="inlineStr"/>
+      <c r="K126" s="31" t="inlineStr"/>
+    </row>
+    <row r="127" ht="44.5" customHeight="1" s="15">
+      <c r="G127" s="17" t="inlineStr">
+        <is>
+          <t>외국인 -3,168억 순매도, 기관 -2,646억 순매도, 공매도 누적 상위 등재 — 전기·전자(동반약세) 섹터 약세 지속형 하방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="G128" s="5" t="inlineStr">
+        <is>
+          <t>LG에너지솔루션</t>
+        </is>
+      </c>
+      <c r="H128" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="I127" s="40" t="n">
+      <c r="I128" s="40" t="n">
         <v>-2</v>
       </c>
-      <c r="J127" s="31" t="inlineStr"/>
-      <c r="K127" s="31" t="inlineStr"/>
-    </row>
-    <row r="128" ht="44.5" customHeight="1" s="15">
-      <c r="G128" s="17" t="inlineStr">
-        <is>
-          <t>외국인 -3,168억 순매도, 기관 -2,646억 순매도, 공매도 누적 상위 등재 — 전기·전자(동반약세) 섹터 약세 지속형 하방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="129"/>
-    <row r="130" ht="31" customHeight="1" s="15">
-      <c r="A130" s="41" t="inlineStr">
+      <c r="J128" s="31" t="inlineStr"/>
+      <c r="K128" s="31" t="inlineStr"/>
+    </row>
+    <row r="129" ht="44.5" customHeight="1" s="15">
+      <c r="G129" s="17" t="inlineStr">
+        <is>
+          <t>외국인 -1,026억 순매도, 대차잔고 +6,777억 증가, 공매도 누적 상위 등재 — 전기·전자(동반약세) 섹터 약세 지속형 하방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="130"/>
+    <row r="131" ht="31" customHeight="1" s="15">
+      <c r="A131" s="41" t="inlineStr">
         <is>
           <t>현재 확보된 월간 리뷰 데이터 유니버스(순매수 상위 30 등재 · 공매도/대차 랭킹 · 월간 촉매 · 신호 섹터 시총 상위 10) 기준 — 전 시장 스크리닝 아님 · 관찰 우선순위이며 매매 권유 아님</t>
         </is>
       </c>
     </row>
-    <row r="131"/>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="132"/>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>08</t>
         </is>
       </c>
-      <c r="B132" s="3" t="inlineStr">
+      <c r="B133" s="3" t="inlineStr">
         <is>
           <t>월간 시장 흐름</t>
         </is>
       </c>
-      <c r="C132" s="3" t="inlineStr"/>
-      <c r="D132" s="3" t="inlineStr"/>
-      <c r="E132" s="3" t="inlineStr"/>
-      <c r="F132" s="3" t="inlineStr"/>
-      <c r="G132" s="3" t="inlineStr"/>
-      <c r="H132" s="3" t="inlineStr"/>
-      <c r="I132" s="3" t="inlineStr"/>
-      <c r="J132" s="3" t="inlineStr"/>
-      <c r="K132" s="3" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="4" t="inlineStr">
+      <c r="C133" s="3" t="inlineStr"/>
+      <c r="D133" s="3" t="inlineStr"/>
+      <c r="E133" s="3" t="inlineStr"/>
+      <c r="F133" s="3" t="inlineStr"/>
+      <c r="G133" s="3" t="inlineStr"/>
+      <c r="H133" s="3" t="inlineStr"/>
+      <c r="I133" s="3" t="inlineStr"/>
+      <c r="J133" s="3" t="inlineStr"/>
+      <c r="K133" s="3" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B133" s="4" t="inlineStr">
+      <c r="B134" s="4" t="inlineStr">
         <is>
           <t>Market Flow</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="15" customHeight="1" s="15">
-      <c r="A134" s="17" t="inlineStr">
-        <is>
-          <t>- 월 초 9월 수출이 전년 대비 83.5% 급증하는 등 견조한 펀더멘털을 확인하며 코스피가 7,000선을 돌파하는 강세를 보였습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="31" customHeight="1" s="15">
+    <row r="135" ht="15" customHeight="1" s="15">
       <c r="A135" s="17" t="inlineStr">
         <is>
-          <t>- 월 중순 미국 소비자물가지수(CPI)와 생산자물가지수(PPI)가 예상치를 상회하며 인플레이션 우려가 재점화되어 기술주 중심의 투매가 발생했습니다.</t>
+          <t>- 월 초 9월 수출이 전년 대비 83.5% 급증하는 등 견조한 펀더멘털이 확인되며 코스피 7,000선 회복을 시도함.</t>
         </is>
       </c>
     </row>
     <row r="136" ht="15" customHeight="1" s="15">
       <c r="A136" s="17" t="inlineStr">
         <is>
-          <t>- 외국인은 코스피 시장에서 대규모 순매도를 지속하며 지수 하락을 주도했고, 특히 전기·전자 섹터에 매도세가 집중되었습니다.</t>
+          <t>- 중순 이후 미국 소비자물가지수(CPI)와 생산자물가지수(PPI)가 예상치를 상회하며 인플레이션 우려가 재점화됨.</t>
         </is>
       </c>
     </row>
     <row r="137" ht="15" customHeight="1" s="15">
       <c r="A137" s="17" t="inlineStr">
         <is>
-          <t>- 월 후반 미국 물가 지표의 서프라이즈가 고금리 장기화 공포를 키우며 시장의 변동성을 극대화했습니다.</t>
+          <t>- 외국인의 대규모 순매도세가 전기·전자 섹터에 집중되며 코스피 지수가 5,500선까지 밀리는 급락장이 연출됨.</t>
         </is>
       </c>
     </row>
     <row r="138" ht="15" customHeight="1" s="15">
       <c r="A138" s="17" t="inlineStr">
         <is>
-          <t>- 반도체 대형주를 중심으로 외국인 수급에 따른 급등락이 반복되며 지수 방향성을 결정짓는 핵심 요인으로 작용했습니다.</t>
+          <t>- 주 후반 저가 매수세와 기관의 수급 유입으로 반등을 시도했으나, AI 수익성 우려와 매크로 불확실성으로 변동성이 지속됨.</t>
         </is>
       </c>
     </row>
     <row r="139" ht="15" customHeight="1" s="15">
       <c r="A139" s="17" t="inlineStr">
         <is>
-          <t>- 제약, 오락·문화 등 일부 섹터는 개별 모멘텀과 수급 유입으로 시장 하락 속에서도 상대적 강세를 유지했습니다.</t>
+          <t>- 외국인은 월중 대규모 매도세를 보였으나, 기관은 제약 및 오락·문화 섹터 중심으로 방어적인 수급을 형성함.</t>
         </is>
       </c>
     </row>
@@ -4963,28 +5018,28 @@
     <row r="142" ht="15" customHeight="1" s="15">
       <c r="A142" s="17" t="inlineStr">
         <is>
-          <t>- 월 초 반도체·바이오 섹터가 수출 데이터 호조에 힘입어 시장 상승을 주도했습니다.</t>
+          <t>- 월 초 반도체 수출 데이터 호조로 전기·전자 및 의료·정밀기기 섹터가 주도주로 부상함.</t>
         </is>
       </c>
     </row>
     <row r="143" ht="15" customHeight="1" s="15">
       <c r="A143" s="17" t="inlineStr">
         <is>
-          <t>- 월 중순 이후 미국 인플레이션 우려로 전기·전자 및 반도체 섹터가 지속적인 약세를 보였습니다.</t>
+          <t>- 중순 이후 미국발 인플레이션 공포로 기술주 투매가 발생하며 전기·전자 섹터가 급락함.</t>
         </is>
       </c>
     </row>
     <row r="144" ht="15" customHeight="1" s="15">
       <c r="A144" s="17" t="inlineStr">
         <is>
-          <t>- 운송·창고 섹터는 중동 지정학적 리스크에 따른 해상 운임 상승 기대감으로 강세를 유지했습니다.</t>
+          <t>- 운송·창고 섹터는 중동 지정학적 리스크에 따른 해상 운임 상승 기대감으로 강세를 유지함.</t>
         </is>
       </c>
     </row>
     <row r="145" ht="15" customHeight="1" s="15">
       <c r="A145" s="17" t="inlineStr">
         <is>
-          <t>- 제약 및 오락·문화 섹터는 신약 모멘텀과 IP 가치 부각으로 수급이 유입되며 방어적인 흐름을 보였습니다.</t>
+          <t>- 제약 섹터는 신약 모멘텀과 기관의 순매수세가 집중되며 시장 하락기에도 상대적 강세를 보임.</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5133,7 @@
         </is>
       </c>
       <c r="F149" s="29" t="n">
-        <v>-2.1</v>
+        <v>-6.18</v>
       </c>
       <c r="G149" s="17" t="inlineStr">
         <is>
@@ -5113,7 +5168,7 @@
         </is>
       </c>
       <c r="F150" s="28" t="n">
-        <v>37.42</v>
+        <v>31.02</v>
       </c>
       <c r="G150" s="17" t="inlineStr">
         <is>
@@ -5148,7 +5203,7 @@
         </is>
       </c>
       <c r="F151" s="29" t="n">
-        <v>-8.02</v>
+        <v>-9.92</v>
       </c>
       <c r="G151" s="17" t="inlineStr">
         <is>
@@ -5183,7 +5238,7 @@
         </is>
       </c>
       <c r="F152" s="29" t="n">
-        <v>-14.26</v>
+        <v>-18.52</v>
       </c>
       <c r="G152" s="17" t="inlineStr">
         <is>
@@ -5218,7 +5273,7 @@
         </is>
       </c>
       <c r="F153" s="28" t="n">
-        <v>76.95999999999999</v>
+        <v>100.61</v>
       </c>
       <c r="G153" s="17" t="inlineStr">
         <is>
@@ -5253,7 +5308,7 @@
         </is>
       </c>
       <c r="F154" s="28" t="n">
-        <v>54.54</v>
+        <v>51.93</v>
       </c>
       <c r="G154" s="17" t="inlineStr">
         <is>
@@ -5288,7 +5343,7 @@
         </is>
       </c>
       <c r="F155" s="28" t="n">
-        <v>34.54</v>
+        <v>36.03</v>
       </c>
       <c r="G155" s="17" t="inlineStr">
         <is>
@@ -5358,7 +5413,7 @@
         </is>
       </c>
       <c r="F157" s="28" t="n">
-        <v>200.88</v>
+        <v>158.26</v>
       </c>
       <c r="G157" s="17" t="inlineStr">
         <is>
@@ -5393,7 +5448,7 @@
         </is>
       </c>
       <c r="F158" s="28" t="n">
-        <v>180.94</v>
+        <v>114.09</v>
       </c>
       <c r="G158" s="17" t="inlineStr">
         <is>
@@ -5428,7 +5483,7 @@
         </is>
       </c>
       <c r="F159" s="28" t="n">
-        <v>43.36</v>
+        <v>48.31</v>
       </c>
       <c r="G159" s="17" t="inlineStr">
         <is>
@@ -5464,7 +5519,7 @@
         </is>
       </c>
       <c r="F160" s="28" t="n">
-        <v>28.51</v>
+        <v>23.83</v>
       </c>
       <c r="G160" s="17" t="inlineStr">
         <is>
@@ -5499,7 +5554,7 @@
         </is>
       </c>
       <c r="F161" s="28" t="n">
-        <v>150.52</v>
+        <v>134.86</v>
       </c>
       <c r="G161" s="17" t="inlineStr">
         <is>
@@ -5535,7 +5590,7 @@
         </is>
       </c>
       <c r="F162" s="28" t="n">
-        <v>21.9</v>
+        <v>25.86</v>
       </c>
       <c r="G162" s="17" t="inlineStr">
         <is>
@@ -5544,15 +5599,15 @@
         </is>
       </c>
     </row>
-    <row r="163" ht="31" customHeight="1" s="15">
+    <row r="163" ht="44.5" customHeight="1" s="15">
       <c r="A163" s="31" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B163" s="31" t="inlineStr">
         <is>
-          <t>유니켐</t>
+          <t>국제약품 (2회)</t>
         </is>
       </c>
       <c r="C163" s="31" t="inlineStr">
@@ -5562,7 +5617,7 @@
       </c>
       <c r="D163" s="34" t="inlineStr">
         <is>
-          <t>운송장비·부품</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="E163" s="14" t="inlineStr">
@@ -5571,129 +5626,130 @@
         </is>
       </c>
       <c r="F163" s="28" t="n">
-        <v>83.27</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="G163" s="17" t="inlineStr">
         <is>
-          <t>미국 유연전자 기업 인수 및 로봇 신사업 진출이라는 대형 재료로 상한가 기록.</t>
+          <t>러시아 페스트 우려 관련 이슈에 따른 테마성 매수세 유입
+(10-07) 러시아 페스트 관련 진단키트 수요 급증 및 경영권 승계 기대감 복합 작용.</t>
         </is>
       </c>
     </row>
     <row r="164" ht="31" customHeight="1" s="15">
       <c r="A164" s="31" t="inlineStr">
         <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B164" s="31" t="inlineStr">
+        <is>
+          <t>유니켐</t>
+        </is>
+      </c>
+      <c r="C164" s="31" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="D164" s="34" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
+        </is>
+      </c>
+      <c r="E164" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="F164" s="28" t="n">
+        <v>75.16</v>
+      </c>
+      <c r="G164" s="17" t="inlineStr">
+        <is>
+          <t>미국 유연전자 기업 인수 및 로봇 신사업 진출이라는 대형 재료로 상한가 기록.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="31" customHeight="1" s="15">
+      <c r="A165" s="31" t="inlineStr">
+        <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B164" s="31" t="inlineStr">
+      <c r="B165" s="31" t="inlineStr">
         <is>
           <t>에스엠벡셀</t>
         </is>
       </c>
-      <c r="C164" s="31" t="inlineStr">
+      <c r="C165" s="31" t="inlineStr">
         <is>
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D164" s="34" t="inlineStr">
+      <c r="D165" s="34" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="E164" s="14" t="inlineStr">
+      <c r="E165" s="14" t="inlineStr">
         <is>
           <t>★★★★★</t>
         </is>
       </c>
-      <c r="F164" s="28" t="n">
-        <v>45.84</v>
-      </c>
-      <c r="G164" s="17" t="inlineStr">
+      <c r="F165" s="28" t="n">
+        <v>38.81</v>
+      </c>
+      <c r="G165" s="17" t="inlineStr">
         <is>
           <t>서울대와 공동으로 저궤도 위성용 리튬이온 배터리 제조 기술 확보</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="58" customHeight="1" s="15">
-      <c r="A165" s="31" t="inlineStr">
+    <row r="166" ht="58" customHeight="1" s="15">
+      <c r="A166" s="31" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B165" s="17" t="inlineStr">
+      <c r="B166" s="17" t="inlineStr">
         <is>
           <t>하이퍼코퍼레이션 (2회)</t>
         </is>
       </c>
-      <c r="C165" s="31" t="inlineStr">
+      <c r="C166" s="31" t="inlineStr">
         <is>
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D165" s="34" t="inlineStr">
+      <c r="D166" s="34" t="inlineStr">
         <is>
           <t>유통</t>
         </is>
       </c>
-      <c r="E165" s="14" t="inlineStr">
+      <c r="E166" s="14" t="inlineStr">
         <is>
           <t>★★★★★</t>
         </is>
       </c>
-      <c r="F165" s="28" t="n">
-        <v>37.01</v>
-      </c>
-      <c r="G165" s="17" t="inlineStr">
+      <c r="F166" s="28" t="n">
+        <v>28.44</v>
+      </c>
+      <c r="G166" s="17" t="inlineStr">
         <is>
           <t>100억 규모 유상증자를 통한 최대주주 변경 소식에 따른 기대감 반영
 (10-14) 110억원 규모 제3자배정 유상증자 및 최대주주 변경이라는 경영권 관련 대형 공시로 상한가 기록.</t>
         </is>
       </c>
     </row>
-    <row r="166" ht="31" customHeight="1" s="15">
-      <c r="A166" s="31" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B166" s="31" t="inlineStr">
-        <is>
-          <t>듀켐바이오</t>
-        </is>
-      </c>
-      <c r="C166" s="31" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D166" s="34" t="inlineStr">
-        <is>
-          <t>제약</t>
-        </is>
-      </c>
-      <c r="E166" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="F166" s="28" t="n">
-        <v>21.61</v>
-      </c>
-      <c r="G166" s="17" t="inlineStr">
-        <is>
-          <t>미국 일라이 릴리의 알츠하이머 치료제 국내 허가 기대감 부각</t>
-        </is>
-      </c>
-    </row>
     <row r="167" ht="31" customHeight="1" s="15">
       <c r="A167" s="31" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B167" s="31" t="inlineStr">
         <is>
-          <t>TS트릴리온</t>
+          <t>듀켐바이오</t>
         </is>
       </c>
       <c r="C167" s="31" t="inlineStr">
@@ -5703,7 +5759,7 @@
       </c>
       <c r="D167" s="34" t="inlineStr">
         <is>
-          <t>화학</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="E167" s="14" t="inlineStr">
@@ -5712,11 +5768,11 @@
         </is>
       </c>
       <c r="F167" s="28" t="n">
-        <v>21.64</v>
+        <v>12.12</v>
       </c>
       <c r="G167" s="17" t="inlineStr">
         <is>
-          <t>대규모 AI 데이터센터 공동개발 사업 참여 소식에 따른 강력한 매수세 유입</t>
+          <t>미국 일라이 릴리의 알츠하이머 치료제 국내 허가 기대감 부각</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5784,7 @@
       </c>
       <c r="B168" s="31" t="inlineStr">
         <is>
-          <t>형지글로벌</t>
+          <t>TS트릴리온</t>
         </is>
       </c>
       <c r="C168" s="31" t="inlineStr">
@@ -5738,20 +5794,20 @@
       </c>
       <c r="D168" s="34" t="inlineStr">
         <is>
-          <t>유통</t>
+          <t>화학</t>
         </is>
       </c>
       <c r="E168" s="14" t="inlineStr">
         <is>
-          <t>▼★★★★★</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="F168" s="28" t="n">
-        <v>17.12</v>
+        <v>12.66</v>
       </c>
       <c r="G168" s="17" t="inlineStr">
         <is>
-          <t>주가 미달에 따른 상장폐지 우려 관련 안내 공시 및 주가 급락 발생</t>
+          <t>대규모 AI 데이터센터 공동개발 사업 참여 소식에 따른 강력한 매수세 유입</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5838,7 @@
         </is>
       </c>
       <c r="F169" s="28" t="n">
-        <v>45.84</v>
+        <v>38.81</v>
       </c>
       <c r="G169" s="17" t="inlineStr">
         <is>
@@ -5793,35 +5849,35 @@
     <row r="170" ht="31" customHeight="1" s="15">
       <c r="A170" s="31" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B170" s="17" t="inlineStr">
-        <is>
-          <t>휴니드테크놀러지스</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B170" s="31" t="inlineStr">
+        <is>
+          <t>파이온엑스</t>
         </is>
       </c>
       <c r="C170" s="31" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="D170" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>유통</t>
         </is>
       </c>
       <c r="E170" s="14" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>▼★★★★★</t>
         </is>
       </c>
       <c r="F170" s="28" t="n">
-        <v>9.720000000000001</v>
+        <v>29.93</v>
       </c>
       <c r="G170" s="17" t="inlineStr">
         <is>
-          <t>미국 항공기 업체와 1,031억 원 규모의 대규모 공급계약을 체결했습니다.</t>
+          <t>파산 신청으로 인해 주권매매거래정지 기간이 변경되는 등 심각한 경영 위기가 확인되었습니다.</t>
         </is>
       </c>
     </row>
@@ -5833,17 +5889,17 @@
       </c>
       <c r="B171" s="31" t="inlineStr">
         <is>
-          <t>형지엘리트</t>
+          <t>플리토</t>
         </is>
       </c>
       <c r="C171" s="31" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="D171" s="34" t="inlineStr">
         <is>
-          <t>섬유·의류</t>
+          <t>IT 서비스</t>
         </is>
       </c>
       <c r="E171" s="14" t="inlineStr">
@@ -5852,23 +5908,23 @@
         </is>
       </c>
       <c r="F171" s="28" t="n">
-        <v>40.88</v>
+        <v>24.97</v>
       </c>
       <c r="G171" s="17" t="inlineStr">
         <is>
-          <t>시가총액 미달 기업 상장폐지 절차 잠정 유예 소식에 투자심리가 급격히 개선되었습니다.</t>
+          <t>3분기 창사 이래 최대 실적 달성이라는 확정적 호재가 주가 급등을 이끌었습니다.</t>
         </is>
       </c>
     </row>
     <row r="172" ht="31" customHeight="1" s="15">
       <c r="A172" s="31" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B172" s="31" t="inlineStr">
         <is>
-          <t>플리토</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="C172" s="31" t="inlineStr">
@@ -5878,7 +5934,7 @@
       </c>
       <c r="D172" s="34" t="inlineStr">
         <is>
-          <t>IT 서비스</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="E172" s="14" t="inlineStr">
@@ -5887,23 +5943,23 @@
         </is>
       </c>
       <c r="F172" s="28" t="n">
-        <v>26.09</v>
+        <v>40.9</v>
       </c>
       <c r="G172" s="17" t="inlineStr">
         <is>
-          <t>3분기 창사 이래 최대 실적 달성이라는 확정적 호재가 주가 급등을 이끌었습니다.</t>
+          <t>중국 UBT와 장기지속형 주사제 플랫폼 평가 계약 체결이라는 구체적 성과 발생.</t>
         </is>
       </c>
     </row>
     <row r="173" ht="31" customHeight="1" s="15">
       <c r="A173" s="31" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B173" s="31" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C173" s="31" t="inlineStr">
@@ -5913,7 +5969,7 @@
       </c>
       <c r="D173" s="34" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="E173" s="14" t="inlineStr">
@@ -5922,58 +5978,58 @@
         </is>
       </c>
       <c r="F173" s="28" t="n">
-        <v>16.08</v>
+        <v>27.95</v>
       </c>
       <c r="G173" s="17" t="inlineStr">
         <is>
-          <t>중국 UBT와 장기지속형 주사제 플랫폼 평가 계약 체결이라는 구체적 성과 발생.</t>
-        </is>
-      </c>
-    </row>
-    <row r="174" ht="31" customHeight="1" s="15">
+          <t>데이터센터용 슈퍼커패시터 1,200억 원 규모 대규모 공급계약 체결.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="15" customHeight="1" s="15">
       <c r="A174" s="31" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B174" s="31" t="inlineStr">
         <is>
-          <t>서한</t>
+          <t>뉴인텍</t>
         </is>
       </c>
       <c r="C174" s="31" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="D174" s="34" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>운송장비·부품</t>
         </is>
       </c>
       <c r="E174" s="14" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>▼★★★★★</t>
         </is>
       </c>
       <c r="F174" s="28" t="n">
-        <v>15.3</v>
+        <v>39.85</v>
       </c>
       <c r="G174" s="17" t="inlineStr">
         <is>
-          <t>강남 대치동 데이터센터 신축공사 수주라는 대규모 계약 체결.</t>
+          <t>주권매매거래정지 공시로 인한 투자자 거래 제한.</t>
         </is>
       </c>
     </row>
     <row r="175" ht="31" customHeight="1" s="15">
       <c r="A175" s="31" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B175" s="31" t="inlineStr">
-        <is>
-          <t>비나텍</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B175" s="17" t="inlineStr">
+        <is>
+          <t>아이패밀리에스씨</t>
         </is>
       </c>
       <c r="C175" s="31" t="inlineStr">
@@ -5983,7 +6039,7 @@
       </c>
       <c r="D175" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>화학</t>
         </is>
       </c>
       <c r="E175" s="14" t="inlineStr">
@@ -5992,33 +6048,33 @@
         </is>
       </c>
       <c r="F175" s="28" t="n">
-        <v>16.36</v>
+        <v>34.07</v>
       </c>
       <c r="G175" s="17" t="inlineStr">
         <is>
-          <t>데이터센터용 슈퍼커패시터 1,200억 원 규모 대규모 공급계약 체결.</t>
+          <t>일본 종합상사 마루베니의 지분 공개매수 추진 소식.</t>
         </is>
       </c>
     </row>
     <row r="176" ht="31" customHeight="1" s="15">
       <c r="A176" s="31" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B176" s="31" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>퓨쳐켐</t>
         </is>
       </c>
       <c r="C176" s="31" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="D176" s="34" t="inlineStr">
         <is>
-          <t>일반서비스</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="E176" s="14" t="inlineStr">
@@ -6027,11 +6083,11 @@
         </is>
       </c>
       <c r="F176" s="28" t="n">
-        <v>15.03</v>
+        <v>29.91</v>
       </c>
       <c r="G176" s="17" t="inlineStr">
         <is>
-          <t>3분기 영업이익 5,006억 원 어닝 서프라이즈 및 대규모 자사주 소각 결정.</t>
+          <t>전립선암 치료제 미국 제2a상 임상시험 Topline data 수령.</t>
         </is>
       </c>
     </row>
@@ -6060,146 +6116,153 @@
     <row r="179" ht="15" customHeight="1" s="15">
       <c r="A179" s="17" t="inlineStr">
         <is>
-          <t>- 미국 물가 지표 안정화에 따른 기술주 반등</t>
+          <t>- 주요 기업들의 실적 서프라이즈 발표</t>
         </is>
       </c>
     </row>
     <row r="180" ht="15" customHeight="1" s="15">
       <c r="A180" s="17" t="inlineStr">
         <is>
-          <t>- 주요 대형주 실적 발표 서프라이즈</t>
+          <t>- 미국 인플레이션 우려 완화 및 금리 경로 안정화</t>
         </is>
       </c>
     </row>
     <row r="181" ht="15" customHeight="1" s="15">
       <c r="A181" s="17" t="inlineStr">
         <is>
-          <t>- 고금리 장기화 우려 지속</t>
+          <t>- 외국인의 반도체 섹터 매도세 지속</t>
         </is>
       </c>
     </row>
     <row r="182" ht="15" customHeight="1" s="15">
       <c r="A182" s="17" t="inlineStr">
         <is>
-          <t>- 외국인 매도세 지속에 따른 수급 공백</t>
+          <t>- 미국 연준의 매파적 통화정책 시그널</t>
         </is>
       </c>
     </row>
     <row r="183" ht="15" customHeight="1" s="15">
       <c r="A183" s="17" t="inlineStr">
         <is>
-          <t>- 외국인의 반도체 대형주 순매수 전환 여부를 확인해야 합니다.</t>
+          <t>- 외국인의 코스피 전기·전자 섹터 순매수 전환 여부를 확인해야 함.</t>
         </is>
       </c>
     </row>
     <row r="184" ht="15" customHeight="1" s="15">
       <c r="A184" s="17" t="inlineStr">
         <is>
-          <t>- 2026-10-29 03:00 미국 중앙은행 기준금리 결정</t>
+          <t>- 10-29 03:00 미국 중앙은행 기준금리 결정</t>
         </is>
       </c>
     </row>
     <row r="185" ht="15" customHeight="1" s="15">
       <c r="A185" s="17" t="inlineStr">
         <is>
-          <t>- 2026-10-27~30 주요 기업 실적 발표(삼성전자, SK하이닉스 등)</t>
+          <t>- 10-30 08:00 한국 광공업생산 발표</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="15" customHeight="1" s="15">
+      <c r="A186" s="17" t="inlineStr">
+        <is>
+          <t>- 10-29~30 삼성SDS, 현대건설 등 주요 기업 실적 발표</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="93">
     <mergeCell ref="G158:K158"/>
-    <mergeCell ref="G59:K59"/>
+    <mergeCell ref="A186:K186"/>
+    <mergeCell ref="G117:K117"/>
     <mergeCell ref="G169:K169"/>
     <mergeCell ref="G151:K151"/>
     <mergeCell ref="G67:K67"/>
-    <mergeCell ref="B133:K133"/>
     <mergeCell ref="G61:K61"/>
-    <mergeCell ref="G126:K126"/>
     <mergeCell ref="G70:K70"/>
-    <mergeCell ref="G116:K116"/>
-    <mergeCell ref="G112:K112"/>
+    <mergeCell ref="G125:K125"/>
     <mergeCell ref="G62:K62"/>
-    <mergeCell ref="G118:K118"/>
+    <mergeCell ref="B134:K134"/>
+    <mergeCell ref="G127:K127"/>
     <mergeCell ref="G167:K167"/>
+    <mergeCell ref="A113:E113"/>
     <mergeCell ref="G65:K65"/>
     <mergeCell ref="G73:K73"/>
     <mergeCell ref="A135:K135"/>
     <mergeCell ref="G153:K153"/>
     <mergeCell ref="I2:K2"/>
+    <mergeCell ref="G129:K129"/>
     <mergeCell ref="G63:K63"/>
+    <mergeCell ref="A115:E115"/>
     <mergeCell ref="G173:K173"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="G60:K60"/>
+    <mergeCell ref="G115:K115"/>
     <mergeCell ref="G155:K155"/>
     <mergeCell ref="A142:K142"/>
     <mergeCell ref="A182:K182"/>
     <mergeCell ref="A119:E119"/>
     <mergeCell ref="G170:K170"/>
     <mergeCell ref="A79:K79"/>
-    <mergeCell ref="B76:K76"/>
     <mergeCell ref="G157:K157"/>
-    <mergeCell ref="G122:K122"/>
     <mergeCell ref="G166:K166"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="G172:K172"/>
-    <mergeCell ref="A118:E118"/>
     <mergeCell ref="A137:K137"/>
     <mergeCell ref="G69:K69"/>
+    <mergeCell ref="A120:E120"/>
     <mergeCell ref="A136:K136"/>
     <mergeCell ref="A145:K145"/>
     <mergeCell ref="G152:K152"/>
     <mergeCell ref="A139:K139"/>
     <mergeCell ref="A179:K179"/>
     <mergeCell ref="A181:K181"/>
-    <mergeCell ref="A106:E106"/>
     <mergeCell ref="G64:K64"/>
     <mergeCell ref="A184:K184"/>
+    <mergeCell ref="A131:K131"/>
     <mergeCell ref="A180:K180"/>
+    <mergeCell ref="G119:K119"/>
     <mergeCell ref="G159:K159"/>
     <mergeCell ref="G164:K164"/>
-    <mergeCell ref="G106:K106"/>
     <mergeCell ref="A143:K143"/>
     <mergeCell ref="G161:K161"/>
     <mergeCell ref="A1:G2"/>
-    <mergeCell ref="G120:K120"/>
-    <mergeCell ref="A110:E110"/>
-    <mergeCell ref="A78:K78"/>
+    <mergeCell ref="G107:K107"/>
     <mergeCell ref="G174:K174"/>
     <mergeCell ref="G156:K156"/>
-    <mergeCell ref="A108:E108"/>
     <mergeCell ref="G66:K66"/>
     <mergeCell ref="A80:K80"/>
+    <mergeCell ref="G74:K74"/>
     <mergeCell ref="G68:K68"/>
-    <mergeCell ref="G108:K108"/>
-    <mergeCell ref="G124:K124"/>
     <mergeCell ref="A185:K185"/>
-    <mergeCell ref="G110:K110"/>
     <mergeCell ref="G168:K168"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A112:E112"/>
+    <mergeCell ref="G109:K109"/>
     <mergeCell ref="G150:K150"/>
-    <mergeCell ref="A114:E114"/>
+    <mergeCell ref="B78:K78"/>
+    <mergeCell ref="G111:K111"/>
     <mergeCell ref="G72:K72"/>
-    <mergeCell ref="A130:K130"/>
-    <mergeCell ref="A77:K77"/>
+    <mergeCell ref="A107:E107"/>
     <mergeCell ref="G71:K71"/>
     <mergeCell ref="A138:K138"/>
     <mergeCell ref="G176:K176"/>
     <mergeCell ref="G160:K160"/>
     <mergeCell ref="G175:K175"/>
     <mergeCell ref="A183:K183"/>
-    <mergeCell ref="G128:K128"/>
     <mergeCell ref="G162:K162"/>
     <mergeCell ref="G171:K171"/>
+    <mergeCell ref="G121:K121"/>
     <mergeCell ref="G148:K148"/>
-    <mergeCell ref="A116:E116"/>
-    <mergeCell ref="G114:K114"/>
+    <mergeCell ref="G123:K123"/>
     <mergeCell ref="G154:K154"/>
     <mergeCell ref="G163:K163"/>
     <mergeCell ref="A144:K144"/>
-    <mergeCell ref="A134:K134"/>
+    <mergeCell ref="A109:E109"/>
+    <mergeCell ref="G113:K113"/>
+    <mergeCell ref="A81:K81"/>
     <mergeCell ref="G165:K165"/>
+    <mergeCell ref="A117:E117"/>
+    <mergeCell ref="A111:E111"/>
+    <mergeCell ref="G75:K75"/>
     <mergeCell ref="G149:K149"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6242,7 +6305,7 @@
       </c>
       <c r="K1" s="25" t="inlineStr">
         <is>
-          <t>2026-10-01 ~ 2026-10-22</t>
+          <t>2026-10-01 ~ 2026-10-23</t>
         </is>
       </c>
     </row>
@@ -6401,28 +6464,28 @@
         </is>
       </c>
       <c r="D7" s="44" t="n">
-        <v>165</v>
+        <v>39</v>
       </c>
       <c r="E7" s="43" t="n">
-        <v>-564</v>
+        <v>-604</v>
       </c>
       <c r="F7" s="44" t="n">
-        <v>729</v>
+        <v>643</v>
       </c>
       <c r="G7" s="43" t="n">
-        <v>-570</v>
+        <v>-540</v>
       </c>
       <c r="H7" s="46" t="n">
-        <v>413.3</v>
+        <v>474.8</v>
       </c>
       <c r="I7" s="46" t="n">
-        <v>2812.4</v>
+        <v>2770.1</v>
       </c>
       <c r="J7" s="50" t="n">
-        <v>94.7</v>
+        <v>52.4</v>
       </c>
       <c r="K7" s="51" t="n">
-        <v>9.699999999999999</v>
+        <v>7.26</v>
       </c>
       <c r="L7" s="52" t="n">
         <v>-1.34</v>
@@ -6445,28 +6508,28 @@
         </is>
       </c>
       <c r="D8" s="44" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E8" s="43" t="n">
-        <v>-15</v>
+        <v>-27</v>
       </c>
       <c r="F8" s="44" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G8" s="43" t="n">
-        <v>-38</v>
+        <v>-29</v>
       </c>
       <c r="H8" s="46" t="n">
-        <v>20.2</v>
+        <v>21.2</v>
       </c>
       <c r="I8" s="46" t="n">
-        <v>60.8</v>
-      </c>
-      <c r="J8" s="53" t="n">
-        <v>-5.4</v>
+        <v>72.8</v>
+      </c>
+      <c r="J8" s="50" t="n">
+        <v>6.6</v>
       </c>
       <c r="K8" s="51" t="n">
-        <v>17.44</v>
+        <v>10.11</v>
       </c>
       <c r="L8" s="49" t="n">
         <v>-7.18</v>
@@ -6489,28 +6552,28 @@
         </is>
       </c>
       <c r="D9" s="44" t="n">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="E9" s="43" t="n">
-        <v>-97</v>
+        <v>-133</v>
       </c>
       <c r="F9" s="44" t="n">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-86</v>
+        <v>-70</v>
       </c>
       <c r="H9" s="46" t="n">
-        <v>130.1</v>
+        <v>136.5</v>
       </c>
       <c r="I9" s="46" t="n">
-        <v>151.5</v>
+        <v>150.4</v>
       </c>
       <c r="J9" s="53" t="n">
-        <v>-6.6</v>
+        <v>-7.7</v>
       </c>
       <c r="K9" s="51" t="n">
-        <v>4.65</v>
+        <v>5.58</v>
       </c>
       <c r="L9" s="49" t="n">
         <v>-9.43</v>
@@ -6533,28 +6596,28 @@
         </is>
       </c>
       <c r="D10" s="44" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E10" s="43" t="n">
-        <v>-139</v>
+        <v>-156</v>
       </c>
       <c r="F10" s="44" t="n">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-69</v>
+        <v>-71</v>
       </c>
       <c r="H10" s="46" t="n">
-        <v>318.6</v>
+        <v>342.8</v>
       </c>
       <c r="I10" s="46" t="n">
-        <v>1378.8</v>
+        <v>1406.5</v>
       </c>
       <c r="J10" s="50" t="n">
-        <v>555.5</v>
+        <v>583.2</v>
       </c>
       <c r="K10" s="51" t="n">
-        <v>6.02</v>
+        <v>6.43</v>
       </c>
       <c r="L10" s="49" t="n">
         <v>-5.17</v>
@@ -6577,28 +6640,28 @@
         </is>
       </c>
       <c r="D11" s="44" t="n">
-        <v>212</v>
+        <v>175</v>
       </c>
       <c r="E11" s="44" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F11" s="44" t="n">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-207</v>
+        <v>-171</v>
       </c>
       <c r="H11" s="46" t="n">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="I11" s="46" t="n">
-        <v>523.9</v>
+        <v>539.4</v>
       </c>
       <c r="J11" s="50" t="n">
-        <v>136.2</v>
+        <v>151.7</v>
       </c>
       <c r="K11" s="51" t="n">
-        <v>16.71</v>
+        <v>4.55</v>
       </c>
       <c r="L11" s="49" t="n">
         <v>-6.52</v>
@@ -6621,28 +6684,28 @@
         </is>
       </c>
       <c r="D12" s="44" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E12" s="43" t="n">
-        <v>-115</v>
+        <v>-239</v>
       </c>
       <c r="F12" s="44" t="n">
-        <v>242</v>
+        <v>367</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-126</v>
+        <v>-127</v>
       </c>
       <c r="H12" s="46" t="n">
-        <v>99.5</v>
+        <v>110.2</v>
       </c>
       <c r="I12" s="46" t="n">
-        <v>2775.9</v>
+        <v>2941.5</v>
       </c>
       <c r="J12" s="50" t="n">
-        <v>1563</v>
+        <v>1728.6</v>
       </c>
       <c r="K12" s="51" t="n">
-        <v>16.93</v>
+        <v>16.08</v>
       </c>
       <c r="L12" s="49" t="n">
         <v>-6.63</v>
@@ -6665,28 +6728,28 @@
         </is>
       </c>
       <c r="D13" s="44" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E13" s="43" t="n">
-        <v>-14</v>
+        <v>-22</v>
       </c>
       <c r="F13" s="44" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G13" s="43" t="n">
-        <v>-102</v>
+        <v>-99</v>
       </c>
       <c r="H13" s="46" t="n">
-        <v>17.3</v>
+        <v>20.4</v>
       </c>
       <c r="I13" s="46" t="n">
-        <v>39</v>
+        <v>39.5</v>
       </c>
       <c r="J13" s="50" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="K13" s="51" t="n">
-        <v>15.29</v>
+        <v>11.38</v>
       </c>
       <c r="L13" s="54" t="n">
         <v>-4.8</v>
@@ -6709,28 +6772,28 @@
         </is>
       </c>
       <c r="D14" s="44" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="E14" s="43" t="n">
-        <v>-76</v>
+        <v>-71</v>
       </c>
       <c r="F14" s="44" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="G14" s="43" t="n">
-        <v>-17</v>
+        <v>-30</v>
       </c>
       <c r="H14" s="46" t="n">
-        <v>77.90000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="I14" s="46" t="n">
-        <v>384.1</v>
+        <v>390.1</v>
       </c>
       <c r="J14" s="50" t="n">
-        <v>74.5</v>
+        <v>80.5</v>
       </c>
       <c r="K14" s="51" t="n">
-        <v>10.95</v>
+        <v>11.27</v>
       </c>
       <c r="L14" s="49" t="n">
         <v>-6.09</v>
@@ -6753,28 +6816,28 @@
         </is>
       </c>
       <c r="D15" s="44" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E15" s="44" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="F15" s="44" t="n">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="G15" s="43" t="n">
-        <v>-137</v>
+        <v>-140</v>
       </c>
       <c r="H15" s="46" t="n">
-        <v>63.3</v>
+        <v>67.3</v>
       </c>
       <c r="I15" s="46" t="n">
-        <v>606</v>
+        <v>605.9</v>
       </c>
       <c r="J15" s="53" t="n">
-        <v>-22.8</v>
-      </c>
-      <c r="K15" s="55" t="n">
-        <v>-1</v>
+        <v>-22.9</v>
+      </c>
+      <c r="K15" s="51" t="n">
+        <v>0.4</v>
       </c>
       <c r="L15" s="49" t="n">
         <v>-6.52</v>
@@ -6800,25 +6863,25 @@
         <v>0</v>
       </c>
       <c r="E16" s="43" t="n">
-        <v>-62</v>
+        <v>-65</v>
       </c>
       <c r="F16" s="44" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="H16" s="46" t="n">
-        <v>29.3</v>
+        <v>30.3</v>
       </c>
       <c r="I16" s="46" t="n">
-        <v>829.1</v>
+        <v>847.7</v>
       </c>
       <c r="J16" s="50" t="n">
-        <v>20.3</v>
+        <v>38.9</v>
       </c>
       <c r="K16" s="55" t="n">
-        <v>-2.26</v>
+        <v>-3.63</v>
       </c>
       <c r="L16" s="49" t="n">
         <v>-8.83</v>
@@ -6844,25 +6907,25 @@
         <v>21</v>
       </c>
       <c r="E17" s="43" t="n">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="F17" s="44" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G17" s="43" t="n">
         <v>-21</v>
       </c>
       <c r="H17" s="46" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I17" s="46" t="n">
-        <v>211.2</v>
+        <v>213.8</v>
       </c>
       <c r="J17" s="50" t="n">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="K17" s="51" t="n">
-        <v>6.5</v>
+        <v>5.62</v>
       </c>
       <c r="L17" s="49" t="n">
         <v>-7.81</v>
@@ -6885,28 +6948,28 @@
         </is>
       </c>
       <c r="D18" s="43" t="n">
-        <v>-10</v>
+        <v>-12</v>
       </c>
       <c r="E18" s="43" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="F18" s="43" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="G18" s="43" t="n">
-        <v>-47</v>
+        <v>-50</v>
       </c>
       <c r="H18" s="46" t="n">
         <v>0.5</v>
       </c>
       <c r="I18" s="46" t="n">
-        <v>31.5</v>
+        <v>31.4</v>
       </c>
       <c r="J18" s="50" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="K18" s="51" t="n">
-        <v>8.609999999999999</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="L18" s="49" t="n">
         <v>-7.05</v>
@@ -6975,7 +7038,7 @@
       </c>
       <c r="O1" s="25" t="inlineStr">
         <is>
-          <t>2026-10-01 ~ 2026-10-22</t>
+          <t>2026-10-01 ~ 2026-10-23</t>
         </is>
       </c>
     </row>
@@ -10631,7 +10694,7 @@
       </c>
       <c r="Q1" s="25" t="inlineStr">
         <is>
-          <t>2026-10-01 ~ 2026-10-22</t>
+          <t>2026-10-01 ~ 2026-10-23</t>
         </is>
       </c>
     </row>
@@ -10755,10 +10818,10 @@
         </is>
       </c>
       <c r="D5" s="62" t="n">
-        <v>30475</v>
+        <v>32412</v>
       </c>
       <c r="E5" s="63" t="n">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="G5" s="30" t="n">
         <v>1</v>
@@ -10774,10 +10837,10 @@
         </is>
       </c>
       <c r="J5" s="43" t="n">
-        <v>9054.9</v>
+        <v>6776.7</v>
       </c>
       <c r="K5" s="64" t="n">
-        <v>42022.8</v>
+        <v>39744.6</v>
       </c>
       <c r="L5" s="63" t="n">
         <v>4.36</v>
@@ -10796,13 +10859,13 @@
         </is>
       </c>
       <c r="Q5" s="59" t="n">
-        <v>-71212</v>
+        <v>-80811.7</v>
       </c>
       <c r="R5" s="64" t="n">
-        <v>154505.1</v>
+        <v>144905.4</v>
       </c>
       <c r="S5" s="63" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="6">
@@ -10820,10 +10883,10 @@
         </is>
       </c>
       <c r="D6" s="62" t="n">
-        <v>20167</v>
+        <v>20542</v>
       </c>
       <c r="E6" s="63" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="G6" s="30" t="n">
         <v>2</v>
@@ -10839,13 +10902,13 @@
         </is>
       </c>
       <c r="J6" s="43" t="n">
-        <v>3111.6</v>
+        <v>2595.2</v>
       </c>
       <c r="K6" s="64" t="n">
-        <v>6885.6</v>
+        <v>6369.2</v>
       </c>
       <c r="L6" s="63" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="N6" s="30" t="n">
         <v>2</v>
@@ -10861,13 +10924,13 @@
         </is>
       </c>
       <c r="Q6" s="59" t="n">
-        <v>-14586.9</v>
+        <v>-24621.4</v>
       </c>
       <c r="R6" s="64" t="n">
-        <v>185130.7</v>
+        <v>175096.2</v>
       </c>
       <c r="S6" s="63" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="7">
@@ -10885,10 +10948,10 @@
         </is>
       </c>
       <c r="D7" s="62" t="n">
-        <v>6946</v>
+        <v>7315</v>
       </c>
       <c r="E7" s="63" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="G7" s="30" t="n">
         <v>3</v>
@@ -10904,13 +10967,13 @@
         </is>
       </c>
       <c r="J7" s="43" t="n">
-        <v>2905.2</v>
+        <v>2096.1</v>
       </c>
       <c r="K7" s="64" t="n">
-        <v>16513.2</v>
+        <v>15704.1</v>
       </c>
       <c r="L7" s="63" t="n">
-        <v>3.7</v>
+        <v>3.81</v>
       </c>
       <c r="N7" s="30" t="n">
         <v>3</v>
@@ -10926,13 +10989,13 @@
         </is>
       </c>
       <c r="Q7" s="59" t="n">
-        <v>-9746.4</v>
+        <v>-11658.6</v>
       </c>
       <c r="R7" s="64" t="n">
-        <v>39837</v>
+        <v>37924.8</v>
       </c>
       <c r="S7" s="63" t="n">
-        <v>20.59</v>
+        <v>20.81</v>
       </c>
     </row>
     <row r="8">
@@ -10950,10 +11013,10 @@
         </is>
       </c>
       <c r="D8" s="62" t="n">
-        <v>5449</v>
+        <v>5789</v>
       </c>
       <c r="E8" s="63" t="n">
-        <v>2.82</v>
+        <v>3.18</v>
       </c>
       <c r="G8" s="30" t="n">
         <v>4</v>
@@ -10969,13 +11032,13 @@
         </is>
       </c>
       <c r="J8" s="43" t="n">
-        <v>1563</v>
+        <v>1728.6</v>
       </c>
       <c r="K8" s="64" t="n">
-        <v>2775.9</v>
+        <v>2941.5</v>
       </c>
       <c r="L8" s="63" t="n">
-        <v>7.52</v>
+        <v>8.01</v>
       </c>
       <c r="N8" s="30" t="n">
         <v>4</v>
@@ -10991,13 +11054,13 @@
         </is>
       </c>
       <c r="Q8" s="59" t="n">
-        <v>-9609.5</v>
+        <v>-10614.1</v>
       </c>
       <c r="R8" s="64" t="n">
-        <v>21826.9</v>
+        <v>20822.3</v>
       </c>
       <c r="S8" s="63" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="9" ht="31" customHeight="1" s="15">
@@ -11015,32 +11078,32 @@
         </is>
       </c>
       <c r="D9" s="62" t="n">
-        <v>5178</v>
+        <v>5571</v>
       </c>
       <c r="E9" s="63" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G9" s="30" t="n">
         <v>5</v>
       </c>
       <c r="H9" s="31" t="inlineStr">
         <is>
-          <t>포스코퓨처엠</t>
+          <t>하이브</t>
         </is>
       </c>
       <c r="I9" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>오락·문화</t>
         </is>
       </c>
       <c r="J9" s="43" t="n">
-        <v>1548.6</v>
+        <v>1267.4</v>
       </c>
       <c r="K9" s="64" t="n">
-        <v>15566.7</v>
+        <v>4810.3</v>
       </c>
       <c r="L9" s="63" t="n">
-        <v>9.68</v>
+        <v>6.3</v>
       </c>
       <c r="N9" s="30" t="n">
         <v>5</v>
@@ -11056,13 +11119,13 @@
         </is>
       </c>
       <c r="Q9" s="59" t="n">
-        <v>-9282.5</v>
+        <v>-10085.5</v>
       </c>
       <c r="R9" s="64" t="n">
-        <v>18653.2</v>
+        <v>17850.2</v>
       </c>
       <c r="S9" s="63" t="n">
-        <v>5.55</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="10">
@@ -11080,17 +11143,17 @@
         </is>
       </c>
       <c r="D10" s="62" t="n">
-        <v>4808</v>
+        <v>5135</v>
       </c>
       <c r="E10" s="63" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="G10" s="30" t="n">
         <v>6</v>
       </c>
       <c r="H10" s="31" t="inlineStr">
         <is>
-          <t>삼성바이오로직스</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="I10" s="34" t="inlineStr">
@@ -11099,13 +11162,13 @@
         </is>
       </c>
       <c r="J10" s="43" t="n">
-        <v>1456.6</v>
+        <v>1158.2</v>
       </c>
       <c r="K10" s="64" t="n">
-        <v>10739.5</v>
+        <v>3528</v>
       </c>
       <c r="L10" s="63" t="n">
-        <v>1.64</v>
+        <v>7.5</v>
       </c>
       <c r="N10" s="30" t="n">
         <v>6</v>
@@ -11121,13 +11184,13 @@
         </is>
       </c>
       <c r="Q10" s="59" t="n">
-        <v>-7714.3</v>
+        <v>-8214.700000000001</v>
       </c>
       <c r="R10" s="64" t="n">
-        <v>28767.9</v>
+        <v>28267.5</v>
       </c>
       <c r="S10" s="63" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="11">
@@ -11145,32 +11208,32 @@
         </is>
       </c>
       <c r="D11" s="62" t="n">
-        <v>4282</v>
+        <v>4770</v>
       </c>
       <c r="E11" s="63" t="n">
-        <v>4.49</v>
+        <v>5.5</v>
       </c>
       <c r="G11" s="30" t="n">
         <v>7</v>
       </c>
       <c r="H11" s="31" t="inlineStr">
         <is>
-          <t>하이브</t>
+          <t>삼성바이오로직스</t>
         </is>
       </c>
       <c r="I11" s="34" t="inlineStr">
         <is>
-          <t>오락·문화</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="J11" s="43" t="n">
-        <v>1404</v>
+        <v>1087.2</v>
       </c>
       <c r="K11" s="64" t="n">
-        <v>4946.9</v>
+        <v>10370.1</v>
       </c>
       <c r="L11" s="63" t="n">
-        <v>6.27</v>
+        <v>1.65</v>
       </c>
       <c r="N11" s="30" t="n">
         <v>7</v>
@@ -11182,13 +11245,13 @@
       </c>
       <c r="P11" s="34" t="inlineStr"/>
       <c r="Q11" s="59" t="n">
-        <v>-4371.8</v>
+        <v>-5037.5</v>
       </c>
       <c r="R11" s="64" t="n">
-        <v>25097.5</v>
+        <v>24431.8</v>
       </c>
       <c r="S11" s="63" t="n">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="12">
@@ -11206,10 +11269,10 @@
         </is>
       </c>
       <c r="D12" s="62" t="n">
-        <v>3820</v>
+        <v>4395</v>
       </c>
       <c r="E12" s="63" t="n">
-        <v>0.86</v>
+        <v>1.07</v>
       </c>
       <c r="G12" s="30" t="n">
         <v>8</v>
@@ -11225,13 +11288,13 @@
         </is>
       </c>
       <c r="J12" s="43" t="n">
-        <v>1318.8</v>
+        <v>1086.7</v>
       </c>
       <c r="K12" s="64" t="n">
-        <v>9378</v>
+        <v>9145.9</v>
       </c>
       <c r="L12" s="63" t="n">
-        <v>14.71</v>
+        <v>14.79</v>
       </c>
       <c r="N12" s="30" t="n">
         <v>8</v>
@@ -11247,13 +11310,13 @@
         </is>
       </c>
       <c r="Q12" s="59" t="n">
-        <v>-3799.2</v>
+        <v>-4335.7</v>
       </c>
       <c r="R12" s="64" t="n">
-        <v>16620.5</v>
+        <v>16084</v>
       </c>
       <c r="S12" s="63" t="n">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="13" ht="31" customHeight="1" s="15">
@@ -11271,39 +11334,39 @@
         </is>
       </c>
       <c r="D13" s="62" t="n">
-        <v>3774</v>
+        <v>4280</v>
       </c>
       <c r="E13" s="63" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="G13" s="30" t="n">
         <v>9</v>
       </c>
       <c r="H13" s="31" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>포스코퓨처엠</t>
         </is>
       </c>
       <c r="I13" s="34" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="J13" s="43" t="n">
-        <v>1258.5</v>
+        <v>864.3</v>
       </c>
       <c r="K13" s="64" t="n">
-        <v>3628.3</v>
+        <v>14882.4</v>
       </c>
       <c r="L13" s="63" t="n">
-        <v>7.28</v>
+        <v>10.03</v>
       </c>
       <c r="N13" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="O13" s="17" t="inlineStr">
-        <is>
-          <t>한화에어로스페이스</t>
+      <c r="O13" s="31" t="inlineStr">
+        <is>
+          <t>한국항공우주</t>
         </is>
       </c>
       <c r="P13" s="60" t="inlineStr">
@@ -11312,16 +11375,16 @@
         </is>
       </c>
       <c r="Q13" s="59" t="n">
-        <v>-3271.2</v>
+        <v>-3360.8</v>
       </c>
       <c r="R13" s="64" t="n">
-        <v>9770.4</v>
+        <v>11247.5</v>
       </c>
       <c r="S13" s="63" t="n">
-        <v>2.33</v>
-      </c>
-    </row>
-    <row r="14" ht="31" customHeight="1" s="15">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" s="30" t="n">
         <v>10</v>
       </c>
@@ -11332,54 +11395,54 @@
       </c>
       <c r="C14" s="34" t="inlineStr"/>
       <c r="D14" s="62" t="n">
-        <v>3403</v>
+        <v>3611</v>
       </c>
       <c r="E14" s="63" t="n">
-        <v>0.54</v>
+        <v>0.59</v>
       </c>
       <c r="G14" s="30" t="n">
         <v>10</v>
       </c>
       <c r="H14" s="31" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="I14" s="34" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="J14" s="43" t="n">
-        <v>885.7</v>
+        <v>787.5</v>
       </c>
       <c r="K14" s="64" t="n">
-        <v>13600.9</v>
+        <v>8555.5</v>
       </c>
       <c r="L14" s="63" t="n">
-        <v>2.97</v>
+        <v>6.13</v>
       </c>
       <c r="N14" s="30" t="n">
         <v>10</v>
       </c>
       <c r="O14" s="31" t="inlineStr">
         <is>
-          <t>한국항공우주</t>
-        </is>
-      </c>
-      <c r="P14" s="60" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
+          <t>LG이노텍</t>
+        </is>
+      </c>
+      <c r="P14" s="34" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="Q14" s="59" t="n">
-        <v>-2993</v>
+        <v>-3098.8</v>
       </c>
       <c r="R14" s="64" t="n">
-        <v>11615.3</v>
+        <v>4513.1</v>
       </c>
       <c r="S14" s="63" t="n">
-        <v>10.9</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="15"/>
@@ -11442,7 +11505,7 @@
       </c>
       <c r="L1" s="25" t="inlineStr">
         <is>
-          <t>2026-10-01 ~ 2026-10-22</t>
+          <t>2026-10-01 ~ 2026-10-23</t>
         </is>
       </c>
     </row>
@@ -11560,43 +11623,43 @@
         </is>
       </c>
       <c r="B5" s="65" t="n">
-        <v>-41.86</v>
+        <v>-42.22</v>
       </c>
       <c r="C5" s="65" t="n">
-        <v>-25.93</v>
+        <v>-25.61</v>
       </c>
       <c r="D5" s="65" t="n">
-        <v>-6.21</v>
+        <v>-10.93</v>
       </c>
       <c r="E5" s="66" t="n">
-        <v>6.87</v>
+        <v>6.21</v>
       </c>
       <c r="F5" s="67" t="n">
-        <v>19</v>
-      </c>
-      <c r="G5" s="67" t="n">
-        <v>1432</v>
-      </c>
-      <c r="H5" s="67" t="n">
-        <v>1451</v>
-      </c>
-      <c r="I5" s="68" t="n">
+        <v>-36</v>
+      </c>
+      <c r="G5" s="68" t="n">
+        <v>1534</v>
+      </c>
+      <c r="H5" s="68" t="n">
+        <v>1498</v>
+      </c>
+      <c r="I5" s="67" t="n">
         <v>-6</v>
       </c>
-      <c r="J5" s="67" t="n">
-        <v>790</v>
-      </c>
-      <c r="K5" s="67" t="n">
-        <v>568</v>
-      </c>
-      <c r="L5" s="67" t="n">
-        <v>76</v>
-      </c>
-      <c r="M5" s="68" t="n">
-        <v>-1486</v>
-      </c>
-      <c r="N5" s="67" t="n">
-        <v>35</v>
+      <c r="J5" s="68" t="n">
+        <v>796</v>
+      </c>
+      <c r="K5" s="68" t="n">
+        <v>653</v>
+      </c>
+      <c r="L5" s="68" t="n">
+        <v>87</v>
+      </c>
+      <c r="M5" s="67" t="n">
+        <v>-1531</v>
+      </c>
+      <c r="N5" s="68" t="n">
+        <v>32</v>
       </c>
       <c r="O5" s="69" t="inlineStr">
         <is>
@@ -11607,192 +11670,196 @@
     <row r="6">
       <c r="A6" s="31" t="inlineStr">
         <is>
-          <t>음식료·담배</t>
-        </is>
-      </c>
-      <c r="B6" s="66" t="n">
-        <v>7.62</v>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="B6" s="65" t="n">
+        <v>-11.38</v>
       </c>
       <c r="C6" s="65" t="n">
-        <v>-3.69</v>
+        <v>-6.86</v>
       </c>
       <c r="D6" s="66" t="n">
-        <v>5.6</v>
+        <v>7.16</v>
       </c>
       <c r="E6" s="66" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="F6" s="68" t="n">
-        <v>-940</v>
-      </c>
-      <c r="G6" s="67" t="n">
-        <v>2579</v>
-      </c>
-      <c r="H6" s="67" t="n">
-        <v>1639</v>
+        <v>4.73</v>
+      </c>
+      <c r="F6" s="67" t="n">
+        <v>-2081</v>
+      </c>
+      <c r="G6" s="68" t="n">
+        <v>6140</v>
+      </c>
+      <c r="H6" s="68" t="n">
+        <v>4059</v>
       </c>
       <c r="I6" s="67" t="n">
-        <v>188</v>
-      </c>
-      <c r="J6" s="67" t="n">
-        <v>1107</v>
-      </c>
-      <c r="K6" s="67" t="n">
-        <v>1116</v>
-      </c>
-      <c r="L6" s="67" t="n">
-        <v>173</v>
-      </c>
-      <c r="M6" s="68" t="n">
-        <v>-2036</v>
-      </c>
-      <c r="N6" s="67" t="n">
-        <v>397</v>
-      </c>
-      <c r="O6" s="57" t="inlineStr">
-        <is>
-          <t>동반강세</t>
-        </is>
-      </c>
+        <v>-441</v>
+      </c>
+      <c r="J6" s="68" t="n">
+        <v>2082</v>
+      </c>
+      <c r="K6" s="68" t="n">
+        <v>4011</v>
+      </c>
+      <c r="L6" s="68" t="n">
+        <v>490</v>
+      </c>
+      <c r="M6" s="67" t="n">
+        <v>-4926</v>
+      </c>
+      <c r="N6" s="68" t="n">
+        <v>868</v>
+      </c>
+      <c r="O6" s="30" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="31" t="inlineStr">
         <is>
-          <t>제약</t>
-        </is>
-      </c>
-      <c r="B7" s="65" t="n">
-        <v>-14.35</v>
+          <t>음식료·담배</t>
+        </is>
+      </c>
+      <c r="B7" s="66" t="n">
+        <v>6.32</v>
       </c>
       <c r="C7" s="65" t="n">
-        <v>-10.97</v>
+        <v>-5.16</v>
       </c>
       <c r="D7" s="66" t="n">
-        <v>4.93</v>
+        <v>2.41</v>
       </c>
       <c r="E7" s="66" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="F7" s="68" t="n">
-        <v>-1917</v>
-      </c>
-      <c r="G7" s="67" t="n">
-        <v>5305</v>
-      </c>
-      <c r="H7" s="67" t="n">
-        <v>3388</v>
+        <v>2.81</v>
+      </c>
+      <c r="F7" s="67" t="n">
+        <v>-1206</v>
+      </c>
+      <c r="G7" s="68" t="n">
+        <v>2741</v>
+      </c>
+      <c r="H7" s="68" t="n">
+        <v>1535</v>
       </c>
       <c r="I7" s="68" t="n">
-        <v>-248</v>
-      </c>
-      <c r="J7" s="67" t="n">
-        <v>1767</v>
-      </c>
-      <c r="K7" s="67" t="n">
-        <v>3371</v>
-      </c>
-      <c r="L7" s="67" t="n">
-        <v>419</v>
-      </c>
-      <c r="M7" s="68" t="n">
-        <v>-4270</v>
-      </c>
-      <c r="N7" s="67" t="n">
-        <v>882</v>
-      </c>
-      <c r="O7" s="30" t="inlineStr"/>
+        <v>151</v>
+      </c>
+      <c r="J7" s="68" t="n">
+        <v>1246</v>
+      </c>
+      <c r="K7" s="68" t="n">
+        <v>1160</v>
+      </c>
+      <c r="L7" s="68" t="n">
+        <v>193</v>
+      </c>
+      <c r="M7" s="67" t="n">
+        <v>-2028</v>
+      </c>
+      <c r="N7" s="68" t="n">
+        <v>493</v>
+      </c>
+      <c r="O7" s="57" t="inlineStr">
+        <is>
+          <t>동반강세</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="31" t="inlineStr">
         <is>
-          <t>일반서비스</t>
+          <t>의료·정밀기기</t>
         </is>
       </c>
       <c r="B8" s="66" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="C8" s="65" t="n">
-        <v>-13.11</v>
+        <v>29.04</v>
+      </c>
+      <c r="C8" s="66" t="n">
+        <v>5.27</v>
       </c>
       <c r="D8" s="66" t="n">
-        <v>11.45</v>
-      </c>
-      <c r="E8" s="65" t="n">
-        <v>-0.61</v>
-      </c>
-      <c r="F8" s="67" t="n">
-        <v>1365</v>
-      </c>
-      <c r="G8" s="67" t="n">
-        <v>1844</v>
-      </c>
-      <c r="H8" s="67" t="n">
-        <v>3210</v>
-      </c>
-      <c r="I8" s="67" t="n">
-        <v>741</v>
-      </c>
-      <c r="J8" s="67" t="n">
-        <v>520</v>
+        <v>16.51</v>
+      </c>
+      <c r="E8" s="66" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="F8" s="68" t="n">
+        <v>465</v>
+      </c>
+      <c r="G8" s="68" t="n">
+        <v>264</v>
+      </c>
+      <c r="H8" s="68" t="n">
+        <v>729</v>
+      </c>
+      <c r="I8" s="68" t="n">
+        <v>119</v>
+      </c>
+      <c r="J8" s="68" t="n">
+        <v>201</v>
       </c>
       <c r="K8" s="67" t="n">
-        <v>553</v>
+        <v>-40</v>
       </c>
       <c r="L8" s="67" t="n">
-        <v>33</v>
-      </c>
-      <c r="M8" s="68" t="n">
-        <v>-3335</v>
+        <v>-15</v>
+      </c>
+      <c r="M8" s="67" t="n">
+        <v>-705</v>
       </c>
       <c r="N8" s="67" t="n">
-        <v>125</v>
-      </c>
-      <c r="O8" s="30" t="inlineStr"/>
+        <v>-23</v>
+      </c>
+      <c r="O8" s="57" t="inlineStr">
+        <is>
+          <t>동반강세</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="31" t="inlineStr">
         <is>
-          <t>의료·정밀기기</t>
+          <t>일반서비스</t>
         </is>
       </c>
       <c r="B9" s="66" t="n">
-        <v>25.95</v>
-      </c>
-      <c r="C9" s="66" t="n">
-        <v>3.03</v>
+        <v>5.38</v>
+      </c>
+      <c r="C9" s="65" t="n">
+        <v>-12.06</v>
       </c>
       <c r="D9" s="66" t="n">
-        <v>16.01</v>
-      </c>
-      <c r="E9" s="65" t="n">
-        <v>-0.92</v>
-      </c>
-      <c r="F9" s="67" t="n">
-        <v>535</v>
-      </c>
-      <c r="G9" s="67" t="n">
-        <v>203</v>
-      </c>
-      <c r="H9" s="67" t="n">
-        <v>738</v>
-      </c>
-      <c r="I9" s="67" t="n">
-        <v>106</v>
-      </c>
-      <c r="J9" s="67" t="n">
-        <v>153</v>
+        <v>6.73</v>
+      </c>
+      <c r="E9" s="66" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="F9" s="68" t="n">
+        <v>2932</v>
+      </c>
+      <c r="G9" s="68" t="n">
+        <v>2020</v>
+      </c>
+      <c r="H9" s="68" t="n">
+        <v>4952</v>
+      </c>
+      <c r="I9" s="68" t="n">
+        <v>953</v>
+      </c>
+      <c r="J9" s="68" t="n">
+        <v>539</v>
       </c>
       <c r="K9" s="68" t="n">
-        <v>-33</v>
+        <v>496</v>
       </c>
       <c r="L9" s="68" t="n">
-        <v>-22</v>
-      </c>
-      <c r="M9" s="68" t="n">
-        <v>-713</v>
+        <v>38</v>
+      </c>
+      <c r="M9" s="67" t="n">
+        <v>-5206</v>
       </c>
       <c r="N9" s="68" t="n">
-        <v>-24</v>
+        <v>254</v>
       </c>
       <c r="O9" s="57" t="inlineStr">
         <is>
@@ -11803,47 +11870,47 @@
     <row r="10">
       <c r="A10" s="31" t="inlineStr">
         <is>
-          <t>비금속</t>
+          <t>부동산</t>
         </is>
       </c>
       <c r="B10" s="65" t="n">
-        <v>-16.06</v>
+        <v>-12.09</v>
       </c>
       <c r="C10" s="65" t="n">
-        <v>-21.63</v>
+        <v>-20.98</v>
       </c>
       <c r="D10" s="66" t="n">
-        <v>2.76</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E10" s="65" t="n">
-        <v>-1.91</v>
+        <v>-1.67</v>
       </c>
       <c r="F10" s="67" t="n">
-        <v>49</v>
-      </c>
-      <c r="G10" s="67" t="n">
-        <v>39</v>
-      </c>
-      <c r="H10" s="67" t="n">
-        <v>88</v>
-      </c>
-      <c r="I10" s="67" t="n">
-        <v>17</v>
-      </c>
-      <c r="J10" s="68" t="n">
-        <v>-3</v>
+        <v>-1</v>
+      </c>
+      <c r="G10" s="68" t="n">
+        <v>55</v>
+      </c>
+      <c r="H10" s="68" t="n">
+        <v>54</v>
+      </c>
+      <c r="I10" s="68" t="n">
+        <v>221</v>
+      </c>
+      <c r="J10" s="67" t="n">
+        <v>-99</v>
       </c>
       <c r="K10" s="67" t="n">
-        <v>26</v>
-      </c>
-      <c r="L10" s="70" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="68" t="n">
-        <v>-88</v>
-      </c>
-      <c r="N10" s="70" t="n">
-        <v>0</v>
+        <v>-36</v>
+      </c>
+      <c r="L10" s="67" t="n">
+        <v>-27</v>
+      </c>
+      <c r="M10" s="67" t="n">
+        <v>-39</v>
+      </c>
+      <c r="N10" s="67" t="n">
+        <v>-15</v>
       </c>
       <c r="O10" s="69" t="inlineStr">
         <is>
@@ -11854,47 +11921,47 @@
     <row r="11">
       <c r="A11" s="31" t="inlineStr">
         <is>
-          <t>부동산</t>
+          <t>비금속</t>
         </is>
       </c>
       <c r="B11" s="65" t="n">
-        <v>-12.45</v>
+        <v>-17.18</v>
       </c>
       <c r="C11" s="65" t="n">
-        <v>-21.17</v>
-      </c>
-      <c r="D11" s="66" t="n">
-        <v>2.56</v>
+        <v>-22.18</v>
+      </c>
+      <c r="D11" s="65" t="n">
+        <v>-2.32</v>
       </c>
       <c r="E11" s="65" t="n">
-        <v>-2.06</v>
-      </c>
-      <c r="F11" s="67" t="n">
-        <v>19</v>
-      </c>
-      <c r="G11" s="67" t="n">
-        <v>43</v>
-      </c>
-      <c r="H11" s="67" t="n">
-        <v>62</v>
-      </c>
-      <c r="I11" s="67" t="n">
-        <v>204</v>
-      </c>
-      <c r="J11" s="68" t="n">
-        <v>-90</v>
+        <v>-3.22</v>
+      </c>
+      <c r="F11" s="68" t="n">
+        <v>42</v>
+      </c>
+      <c r="G11" s="68" t="n">
+        <v>42</v>
+      </c>
+      <c r="H11" s="68" t="n">
+        <v>84</v>
+      </c>
+      <c r="I11" s="68" t="n">
+        <v>18</v>
+      </c>
+      <c r="J11" s="67" t="n">
+        <v>-3</v>
       </c>
       <c r="K11" s="68" t="n">
-        <v>-43</v>
-      </c>
-      <c r="L11" s="68" t="n">
-        <v>-25</v>
-      </c>
-      <c r="M11" s="68" t="n">
-        <v>-44</v>
-      </c>
-      <c r="N11" s="68" t="n">
-        <v>-18</v>
+        <v>26</v>
+      </c>
+      <c r="L11" s="70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="67" t="n">
+        <v>-84</v>
+      </c>
+      <c r="N11" s="70" t="n">
+        <v>0</v>
       </c>
       <c r="O11" s="69" t="inlineStr">
         <is>
@@ -11905,94 +11972,98 @@
     <row r="12">
       <c r="A12" s="31" t="inlineStr">
         <is>
-          <t>운송·창고</t>
-        </is>
-      </c>
-      <c r="B12" s="66" t="n">
-        <v>6.57</v>
+          <t>전기·가스</t>
+        </is>
+      </c>
+      <c r="B12" s="65" t="n">
+        <v>-32.58</v>
       </c>
       <c r="C12" s="65" t="n">
-        <v>-6.67</v>
-      </c>
-      <c r="D12" s="66" t="n">
-        <v>4.54</v>
+        <v>-33.23</v>
+      </c>
+      <c r="D12" s="65" t="n">
+        <v>-15.53</v>
       </c>
       <c r="E12" s="65" t="n">
-        <v>-3.17</v>
+        <v>-3.89</v>
       </c>
       <c r="F12" s="67" t="n">
-        <v>1065</v>
-      </c>
-      <c r="G12" s="67" t="n">
-        <v>798</v>
-      </c>
-      <c r="H12" s="67" t="n">
-        <v>1863</v>
+        <v>-14</v>
+      </c>
+      <c r="G12" s="68" t="n">
+        <v>562</v>
+      </c>
+      <c r="H12" s="68" t="n">
+        <v>549</v>
       </c>
       <c r="I12" s="68" t="n">
-        <v>-139</v>
-      </c>
-      <c r="J12" s="67" t="n">
-        <v>6</v>
+        <v>313</v>
+      </c>
+      <c r="J12" s="68" t="n">
+        <v>248</v>
       </c>
       <c r="K12" s="67" t="n">
-        <v>876</v>
-      </c>
-      <c r="L12" s="67" t="n">
-        <v>60</v>
-      </c>
-      <c r="M12" s="68" t="n">
-        <v>-3074</v>
+        <v>-23</v>
+      </c>
+      <c r="L12" s="68" t="n">
+        <v>29</v>
+      </c>
+      <c r="M12" s="67" t="n">
+        <v>-529</v>
       </c>
       <c r="N12" s="67" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O12" s="30" t="inlineStr"/>
+        <v>-20</v>
+      </c>
+      <c r="O12" s="69" t="inlineStr">
+        <is>
+          <t>수급유입</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="31" t="inlineStr">
         <is>
-          <t>전기·가스</t>
-        </is>
-      </c>
-      <c r="B13" s="65" t="n">
-        <v>-32.12</v>
+          <t>운송·창고</t>
+        </is>
+      </c>
+      <c r="B13" s="66" t="n">
+        <v>5.41</v>
       </c>
       <c r="C13" s="65" t="n">
-        <v>-32.7</v>
+        <v>-6.41</v>
       </c>
       <c r="D13" s="65" t="n">
-        <v>-10.32</v>
+        <v>-0.58</v>
       </c>
       <c r="E13" s="65" t="n">
-        <v>-3.23</v>
+        <v>-4.22</v>
       </c>
       <c r="F13" s="68" t="n">
-        <v>-13</v>
-      </c>
-      <c r="G13" s="67" t="n">
-        <v>455</v>
-      </c>
-      <c r="H13" s="67" t="n">
-        <v>441</v>
+        <v>1052</v>
+      </c>
+      <c r="G13" s="68" t="n">
+        <v>769</v>
+      </c>
+      <c r="H13" s="68" t="n">
+        <v>1821</v>
       </c>
       <c r="I13" s="67" t="n">
-        <v>325</v>
+        <v>-114</v>
       </c>
       <c r="J13" s="67" t="n">
-        <v>228</v>
+        <v>-29</v>
       </c>
       <c r="K13" s="68" t="n">
-        <v>-98</v>
-      </c>
-      <c r="L13" s="67" t="n">
-        <v>4</v>
-      </c>
-      <c r="M13" s="68" t="n">
-        <v>-424</v>
+        <v>853</v>
+      </c>
+      <c r="L13" s="68" t="n">
+        <v>65</v>
+      </c>
+      <c r="M13" s="67" t="n">
+        <v>-3044</v>
       </c>
       <c r="N13" s="68" t="n">
-        <v>-17</v>
+        <v>1223</v>
       </c>
       <c r="O13" s="69" t="inlineStr">
         <is>
@@ -12007,43 +12078,43 @@
         </is>
       </c>
       <c r="B14" s="65" t="n">
-        <v>-9.07</v>
+        <v>-10.67</v>
       </c>
       <c r="C14" s="65" t="n">
-        <v>-13.65</v>
+        <v>-15.08</v>
       </c>
       <c r="D14" s="65" t="n">
-        <v>-5.01</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="E14" s="65" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="F14" s="67" t="n">
-        <v>119</v>
-      </c>
-      <c r="G14" s="67" t="n">
-        <v>82</v>
-      </c>
-      <c r="H14" s="67" t="n">
-        <v>201</v>
-      </c>
-      <c r="I14" s="67" t="n">
-        <v>96</v>
-      </c>
-      <c r="J14" s="68" t="n">
-        <v>-10</v>
+        <v>-5.3</v>
+      </c>
+      <c r="F14" s="68" t="n">
+        <v>115</v>
+      </c>
+      <c r="G14" s="68" t="n">
+        <v>81</v>
+      </c>
+      <c r="H14" s="68" t="n">
+        <v>196</v>
+      </c>
+      <c r="I14" s="68" t="n">
+        <v>95</v>
+      </c>
+      <c r="J14" s="67" t="n">
+        <v>-2</v>
       </c>
       <c r="K14" s="67" t="n">
-        <v>4</v>
-      </c>
-      <c r="L14" s="68" t="n">
-        <v>-5</v>
-      </c>
-      <c r="M14" s="68" t="n">
-        <v>-344</v>
-      </c>
-      <c r="N14" s="67" t="n">
-        <v>143</v>
+        <v>-3</v>
+      </c>
+      <c r="L14" s="67" t="n">
+        <v>-6</v>
+      </c>
+      <c r="M14" s="67" t="n">
+        <v>-375</v>
+      </c>
+      <c r="N14" s="68" t="n">
+        <v>180</v>
       </c>
       <c r="O14" s="69" t="inlineStr">
         <is>
@@ -12058,43 +12129,43 @@
         </is>
       </c>
       <c r="B15" s="65" t="n">
-        <v>-19.54</v>
+        <v>-20.33</v>
       </c>
       <c r="C15" s="65" t="n">
-        <v>-17.35</v>
+        <v>-18.22</v>
       </c>
       <c r="D15" s="65" t="n">
-        <v>-6.62</v>
+        <v>-14.2</v>
       </c>
       <c r="E15" s="65" t="n">
-        <v>-5.82</v>
-      </c>
-      <c r="F15" s="67" t="n">
-        <v>451</v>
-      </c>
-      <c r="G15" s="67" t="n">
-        <v>626</v>
-      </c>
-      <c r="H15" s="67" t="n">
-        <v>1077</v>
-      </c>
-      <c r="I15" s="67" t="n">
-        <v>756</v>
-      </c>
-      <c r="J15" s="67" t="n">
-        <v>147</v>
-      </c>
-      <c r="K15" s="68" t="n">
-        <v>-395</v>
-      </c>
-      <c r="L15" s="67" t="n">
-        <v>128</v>
-      </c>
-      <c r="M15" s="68" t="n">
-        <v>-977</v>
-      </c>
-      <c r="N15" s="68" t="n">
-        <v>-100</v>
+        <v>-6.74</v>
+      </c>
+      <c r="F15" s="68" t="n">
+        <v>262</v>
+      </c>
+      <c r="G15" s="68" t="n">
+        <v>945</v>
+      </c>
+      <c r="H15" s="68" t="n">
+        <v>1207</v>
+      </c>
+      <c r="I15" s="68" t="n">
+        <v>720</v>
+      </c>
+      <c r="J15" s="68" t="n">
+        <v>194</v>
+      </c>
+      <c r="K15" s="67" t="n">
+        <v>-162</v>
+      </c>
+      <c r="L15" s="68" t="n">
+        <v>200</v>
+      </c>
+      <c r="M15" s="67" t="n">
+        <v>-1089</v>
+      </c>
+      <c r="N15" s="67" t="n">
+        <v>-118</v>
       </c>
       <c r="O15" s="30" t="inlineStr"/>
     </row>
@@ -12105,42 +12176,42 @@
         </is>
       </c>
       <c r="B16" s="65" t="n">
-        <v>-29.22</v>
+        <v>-30.03</v>
       </c>
       <c r="C16" s="65" t="n">
-        <v>-34.09</v>
+        <v>-33.76</v>
       </c>
       <c r="D16" s="65" t="n">
-        <v>-5.3</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="E16" s="65" t="n">
-        <v>-8.029999999999999</v>
-      </c>
-      <c r="F16" s="67" t="n">
-        <v>4</v>
-      </c>
-      <c r="G16" s="67" t="n">
+        <v>-9.07</v>
+      </c>
+      <c r="F16" s="68" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" s="68" t="n">
         <v>7</v>
       </c>
-      <c r="H16" s="67" t="n">
-        <v>10</v>
-      </c>
-      <c r="I16" s="67" t="n">
+      <c r="H16" s="68" t="n">
         <v>11</v>
       </c>
-      <c r="J16" s="68" t="n">
+      <c r="I16" s="68" t="n">
+        <v>11</v>
+      </c>
+      <c r="J16" s="67" t="n">
         <v>-1</v>
       </c>
-      <c r="K16" s="68" t="n">
+      <c r="K16" s="67" t="n">
         <v>-3</v>
       </c>
       <c r="L16" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="M16" s="67" t="n">
-        <v>9</v>
-      </c>
-      <c r="N16" s="68" t="n">
+      <c r="M16" s="68" t="n">
+        <v>8</v>
+      </c>
+      <c r="N16" s="67" t="n">
         <v>-19</v>
       </c>
       <c r="O16" s="69" t="inlineStr">
@@ -12152,98 +12223,94 @@
     <row r="17">
       <c r="A17" s="31" t="inlineStr">
         <is>
-          <t>통신</t>
+          <t>보험</t>
         </is>
       </c>
       <c r="B17" s="66" t="n">
-        <v>12.64</v>
-      </c>
-      <c r="C17" s="65" t="n">
-        <v>-21.99</v>
+        <v>38.21</v>
+      </c>
+      <c r="C17" s="66" t="n">
+        <v>4.63</v>
       </c>
       <c r="D17" s="65" t="n">
-        <v>-12.79</v>
+        <v>-13.99</v>
       </c>
       <c r="E17" s="65" t="n">
-        <v>-8.59</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="F17" s="67" t="n">
-        <v>293</v>
-      </c>
-      <c r="G17" s="67" t="n">
-        <v>196</v>
-      </c>
-      <c r="H17" s="67" t="n">
-        <v>489</v>
-      </c>
-      <c r="I17" s="67" t="n">
-        <v>17</v>
-      </c>
-      <c r="J17" s="67" t="n">
-        <v>277</v>
+        <v>-1940</v>
+      </c>
+      <c r="G17" s="68" t="n">
+        <v>2428</v>
+      </c>
+      <c r="H17" s="68" t="n">
+        <v>488</v>
+      </c>
+      <c r="I17" s="68" t="n">
+        <v>485</v>
+      </c>
+      <c r="J17" s="68" t="n">
+        <v>1529</v>
       </c>
       <c r="K17" s="68" t="n">
-        <v>-302</v>
+        <v>480</v>
       </c>
       <c r="L17" s="67" t="n">
-        <v>198</v>
-      </c>
-      <c r="M17" s="68" t="n">
-        <v>-471</v>
+        <v>-50</v>
+      </c>
+      <c r="M17" s="67" t="n">
+        <v>-549</v>
       </c>
       <c r="N17" s="68" t="n">
-        <v>-17</v>
-      </c>
-      <c r="O17" s="69" t="inlineStr">
-        <is>
-          <t>수급유입</t>
-        </is>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="O17" s="30" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="31" t="inlineStr">
         <is>
-          <t>화학</t>
+          <t>통신</t>
         </is>
       </c>
       <c r="B18" s="66" t="n">
-        <v>6.92</v>
+        <v>10.45</v>
       </c>
       <c r="C18" s="65" t="n">
-        <v>-19.74</v>
+        <v>-23.05</v>
       </c>
       <c r="D18" s="65" t="n">
-        <v>-0.18</v>
+        <v>-17.25</v>
       </c>
       <c r="E18" s="65" t="n">
-        <v>-9.33</v>
-      </c>
-      <c r="F18" s="67" t="n">
-        <v>287</v>
-      </c>
-      <c r="G18" s="67" t="n">
-        <v>3443</v>
-      </c>
-      <c r="H18" s="67" t="n">
-        <v>3730</v>
-      </c>
-      <c r="I18" s="67" t="n">
-        <v>1314</v>
-      </c>
-      <c r="J18" s="67" t="n">
-        <v>606</v>
+        <v>-10.37</v>
+      </c>
+      <c r="F18" s="68" t="n">
+        <v>219</v>
+      </c>
+      <c r="G18" s="68" t="n">
+        <v>239</v>
+      </c>
+      <c r="H18" s="68" t="n">
+        <v>458</v>
+      </c>
+      <c r="I18" s="68" t="n">
+        <v>85</v>
+      </c>
+      <c r="J18" s="68" t="n">
+        <v>199</v>
       </c>
       <c r="K18" s="67" t="n">
-        <v>1271</v>
-      </c>
-      <c r="L18" s="67" t="n">
-        <v>272</v>
-      </c>
-      <c r="M18" s="68" t="n">
-        <v>-3473</v>
-      </c>
-      <c r="N18" s="68" t="n">
-        <v>-256</v>
+        <v>-238</v>
+      </c>
+      <c r="L18" s="68" t="n">
+        <v>192</v>
+      </c>
+      <c r="M18" s="67" t="n">
+        <v>-449</v>
+      </c>
+      <c r="N18" s="67" t="n">
+        <v>-10</v>
       </c>
       <c r="O18" s="69" t="inlineStr">
         <is>
@@ -12254,94 +12321,98 @@
     <row r="19">
       <c r="A19" s="31" t="inlineStr">
         <is>
-          <t>보험</t>
+          <t>유통</t>
         </is>
       </c>
       <c r="B19" s="66" t="n">
-        <v>38.08</v>
-      </c>
-      <c r="C19" s="66" t="n">
-        <v>6.25</v>
+        <v>8.789999999999999</v>
+      </c>
+      <c r="C19" s="65" t="n">
+        <v>-16.35</v>
       </c>
       <c r="D19" s="65" t="n">
-        <v>-12.13</v>
+        <v>-18.36</v>
       </c>
       <c r="E19" s="65" t="n">
-        <v>-9.449999999999999</v>
+        <v>-11.28</v>
       </c>
       <c r="F19" s="68" t="n">
-        <v>-1843</v>
-      </c>
-      <c r="G19" s="67" t="n">
-        <v>2294</v>
-      </c>
-      <c r="H19" s="67" t="n">
-        <v>451</v>
-      </c>
-      <c r="I19" s="67" t="n">
-        <v>524</v>
+        <v>733</v>
+      </c>
+      <c r="G19" s="68" t="n">
+        <v>1240</v>
+      </c>
+      <c r="H19" s="68" t="n">
+        <v>1973</v>
+      </c>
+      <c r="I19" s="68" t="n">
+        <v>594</v>
       </c>
       <c r="J19" s="67" t="n">
-        <v>1438</v>
-      </c>
-      <c r="K19" s="67" t="n">
-        <v>400</v>
+        <v>-320</v>
+      </c>
+      <c r="K19" s="68" t="n">
+        <v>820</v>
       </c>
       <c r="L19" s="68" t="n">
-        <v>-55</v>
-      </c>
-      <c r="M19" s="68" t="n">
-        <v>-509</v>
-      </c>
-      <c r="N19" s="67" t="n">
-        <v>57</v>
-      </c>
-      <c r="O19" s="30" t="inlineStr"/>
+        <v>180</v>
+      </c>
+      <c r="M19" s="67" t="n">
+        <v>-2008</v>
+      </c>
+      <c r="N19" s="68" t="n">
+        <v>36</v>
+      </c>
+      <c r="O19" s="69" t="inlineStr">
+        <is>
+          <t>수급유입</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="31" t="inlineStr">
         <is>
-          <t>유통</t>
+          <t>화학</t>
         </is>
       </c>
       <c r="B20" s="66" t="n">
-        <v>10.16</v>
+        <v>3.67</v>
       </c>
       <c r="C20" s="65" t="n">
-        <v>-12.69</v>
+        <v>-22.38</v>
       </c>
       <c r="D20" s="65" t="n">
-        <v>-15.28</v>
+        <v>-9</v>
       </c>
       <c r="E20" s="65" t="n">
-        <v>-10.17</v>
-      </c>
-      <c r="F20" s="67" t="n">
-        <v>957</v>
-      </c>
-      <c r="G20" s="67" t="n">
-        <v>1087</v>
-      </c>
-      <c r="H20" s="67" t="n">
-        <v>2044</v>
-      </c>
-      <c r="I20" s="67" t="n">
-        <v>489</v>
+        <v>-12.09</v>
+      </c>
+      <c r="F20" s="68" t="n">
+        <v>507</v>
+      </c>
+      <c r="G20" s="68" t="n">
+        <v>2914</v>
+      </c>
+      <c r="H20" s="68" t="n">
+        <v>3421</v>
+      </c>
+      <c r="I20" s="68" t="n">
+        <v>1413</v>
       </c>
       <c r="J20" s="68" t="n">
-        <v>-333</v>
-      </c>
-      <c r="K20" s="67" t="n">
-        <v>795</v>
-      </c>
-      <c r="L20" s="67" t="n">
-        <v>171</v>
-      </c>
-      <c r="M20" s="68" t="n">
-        <v>-2080</v>
+        <v>286</v>
+      </c>
+      <c r="K20" s="68" t="n">
+        <v>959</v>
+      </c>
+      <c r="L20" s="68" t="n">
+        <v>282</v>
+      </c>
+      <c r="M20" s="67" t="n">
+        <v>-3124</v>
       </c>
       <c r="N20" s="67" t="n">
-        <v>36</v>
+        <v>-297</v>
       </c>
       <c r="O20" s="69" t="inlineStr">
         <is>
@@ -12356,235 +12427,235 @@
         </is>
       </c>
       <c r="B21" s="65" t="n">
-        <v>-3.46</v>
+        <v>-4.65</v>
       </c>
       <c r="C21" s="65" t="n">
-        <v>-49.76</v>
+        <v>-49.97</v>
       </c>
       <c r="D21" s="65" t="n">
-        <v>-24.76</v>
+        <v>-28.36</v>
       </c>
       <c r="E21" s="65" t="n">
-        <v>-14.09</v>
-      </c>
-      <c r="F21" s="68" t="n">
-        <v>-270</v>
-      </c>
-      <c r="G21" s="67" t="n">
-        <v>285</v>
-      </c>
-      <c r="H21" s="67" t="n">
-        <v>14</v>
-      </c>
-      <c r="I21" s="67" t="n">
-        <v>38</v>
-      </c>
-      <c r="J21" s="67" t="n">
-        <v>233</v>
-      </c>
-      <c r="K21" s="68" t="n">
-        <v>-232</v>
-      </c>
-      <c r="L21" s="67" t="n">
-        <v>32</v>
-      </c>
-      <c r="M21" s="68" t="n">
-        <v>-77</v>
-      </c>
-      <c r="N21" s="67" t="n">
-        <v>63</v>
+        <v>-15.15</v>
+      </c>
+      <c r="F21" s="67" t="n">
+        <v>-354</v>
+      </c>
+      <c r="G21" s="68" t="n">
+        <v>362</v>
+      </c>
+      <c r="H21" s="68" t="n">
+        <v>8</v>
+      </c>
+      <c r="I21" s="68" t="n">
+        <v>82</v>
+      </c>
+      <c r="J21" s="68" t="n">
+        <v>277</v>
+      </c>
+      <c r="K21" s="67" t="n">
+        <v>-276</v>
+      </c>
+      <c r="L21" s="68" t="n">
+        <v>52</v>
+      </c>
+      <c r="M21" s="67" t="n">
+        <v>-70</v>
+      </c>
+      <c r="N21" s="68" t="n">
+        <v>62</v>
       </c>
       <c r="O21" s="30" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="31" t="inlineStr">
         <is>
-          <t>금속</t>
-        </is>
-      </c>
-      <c r="B22" s="65" t="n">
-        <v>-14.43</v>
+          <t>금융</t>
+        </is>
+      </c>
+      <c r="B22" s="66" t="n">
+        <v>18.1</v>
       </c>
       <c r="C22" s="65" t="n">
-        <v>-41.35</v>
+        <v>-14.21</v>
       </c>
       <c r="D22" s="65" t="n">
-        <v>-8.66</v>
+        <v>-20.31</v>
       </c>
       <c r="E22" s="65" t="n">
-        <v>-14.25</v>
-      </c>
-      <c r="F22" s="68" t="n">
-        <v>-2476</v>
-      </c>
-      <c r="G22" s="67" t="n">
-        <v>1149</v>
+        <v>-16.46</v>
+      </c>
+      <c r="F22" s="67" t="n">
+        <v>-11085</v>
+      </c>
+      <c r="G22" s="68" t="n">
+        <v>11566</v>
       </c>
       <c r="H22" s="68" t="n">
-        <v>-1327</v>
-      </c>
-      <c r="I22" s="67" t="n">
-        <v>1389</v>
-      </c>
-      <c r="J22" s="67" t="n">
-        <v>155</v>
-      </c>
-      <c r="K22" s="68" t="n">
-        <v>-448</v>
-      </c>
-      <c r="L22" s="67" t="n">
-        <v>51</v>
-      </c>
-      <c r="M22" s="67" t="n">
-        <v>1343</v>
-      </c>
-      <c r="N22" s="68" t="n">
-        <v>-16</v>
-      </c>
-      <c r="O22" s="58" t="inlineStr">
-        <is>
-          <t>동반약세</t>
-        </is>
-      </c>
+        <v>481</v>
+      </c>
+      <c r="I22" s="68" t="n">
+        <v>7862</v>
+      </c>
+      <c r="J22" s="68" t="n">
+        <v>6623</v>
+      </c>
+      <c r="K22" s="67" t="n">
+        <v>-4423</v>
+      </c>
+      <c r="L22" s="68" t="n">
+        <v>62</v>
+      </c>
+      <c r="M22" s="68" t="n">
+        <v>5597</v>
+      </c>
+      <c r="N22" s="67" t="n">
+        <v>-6078</v>
+      </c>
+      <c r="O22" s="30" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="31" t="inlineStr">
         <is>
-          <t>운송장비·부품</t>
-        </is>
-      </c>
-      <c r="B23" s="65" t="n">
-        <v>-21.66</v>
+          <t>건설</t>
+        </is>
+      </c>
+      <c r="B23" s="66" t="n">
+        <v>39.32</v>
       </c>
       <c r="C23" s="65" t="n">
-        <v>-43.83</v>
+        <v>-43.66</v>
       </c>
       <c r="D23" s="65" t="n">
-        <v>-26.63</v>
+        <v>-14.55</v>
       </c>
       <c r="E23" s="65" t="n">
-        <v>-15.57</v>
+        <v>-16.65</v>
       </c>
       <c r="F23" s="68" t="n">
-        <v>-4039</v>
+        <v>1675</v>
       </c>
       <c r="G23" s="67" t="n">
-        <v>5522</v>
+        <v>-2080</v>
       </c>
       <c r="H23" s="67" t="n">
-        <v>1483</v>
+        <v>-405</v>
       </c>
       <c r="I23" s="67" t="n">
-        <v>7383</v>
+        <v>-88</v>
       </c>
       <c r="J23" s="67" t="n">
-        <v>1085</v>
-      </c>
-      <c r="K23" s="68" t="n">
-        <v>-3095</v>
+        <v>-792</v>
+      </c>
+      <c r="K23" s="67" t="n">
+        <v>-1088</v>
       </c>
       <c r="L23" s="67" t="n">
-        <v>195</v>
-      </c>
-      <c r="M23" s="67" t="n">
-        <v>3141</v>
-      </c>
-      <c r="N23" s="68" t="n">
-        <v>-4623</v>
+        <v>-109</v>
+      </c>
+      <c r="M23" s="68" t="n">
+        <v>408</v>
+      </c>
+      <c r="N23" s="67" t="n">
+        <v>-3</v>
       </c>
       <c r="O23" s="30" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="31" t="inlineStr">
         <is>
-          <t>금융</t>
-        </is>
-      </c>
-      <c r="B24" s="66" t="n">
-        <v>19.1</v>
+          <t>금속</t>
+        </is>
+      </c>
+      <c r="B24" s="65" t="n">
+        <v>-17.19</v>
       </c>
       <c r="C24" s="65" t="n">
-        <v>-12.52</v>
+        <v>-42.04</v>
       </c>
       <c r="D24" s="65" t="n">
-        <v>-17.92</v>
+        <v>-17.51</v>
       </c>
       <c r="E24" s="65" t="n">
-        <v>-15.75</v>
-      </c>
-      <c r="F24" s="68" t="n">
-        <v>-9105</v>
-      </c>
-      <c r="G24" s="67" t="n">
-        <v>9914</v>
+        <v>-17.01</v>
+      </c>
+      <c r="F24" s="67" t="n">
+        <v>-2490</v>
+      </c>
+      <c r="G24" s="68" t="n">
+        <v>939</v>
       </c>
       <c r="H24" s="67" t="n">
-        <v>808</v>
-      </c>
-      <c r="I24" s="67" t="n">
-        <v>7011</v>
-      </c>
-      <c r="J24" s="67" t="n">
-        <v>6008</v>
-      </c>
-      <c r="K24" s="68" t="n">
-        <v>-4476</v>
+        <v>-1551</v>
+      </c>
+      <c r="I24" s="68" t="n">
+        <v>1381</v>
+      </c>
+      <c r="J24" s="68" t="n">
+        <v>73</v>
+      </c>
+      <c r="K24" s="67" t="n">
+        <v>-570</v>
       </c>
       <c r="L24" s="68" t="n">
-        <v>-17</v>
-      </c>
-      <c r="M24" s="67" t="n">
-        <v>5294</v>
-      </c>
-      <c r="N24" s="68" t="n">
-        <v>-6103</v>
-      </c>
-      <c r="O24" s="30" t="inlineStr"/>
+        <v>54</v>
+      </c>
+      <c r="M24" s="68" t="n">
+        <v>1570</v>
+      </c>
+      <c r="N24" s="67" t="n">
+        <v>-19</v>
+      </c>
+      <c r="O24" s="58" t="inlineStr">
+        <is>
+          <t>동반약세</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="31" t="inlineStr">
         <is>
-          <t>건설</t>
-        </is>
-      </c>
-      <c r="B25" s="66" t="n">
-        <v>39.21</v>
+          <t>운송장비·부품</t>
+        </is>
+      </c>
+      <c r="B25" s="65" t="n">
+        <v>-23.4</v>
       </c>
       <c r="C25" s="65" t="n">
-        <v>-42.45</v>
+        <v>-44.82</v>
       </c>
       <c r="D25" s="65" t="n">
-        <v>-5.68</v>
+        <v>-31.7</v>
       </c>
       <c r="E25" s="65" t="n">
-        <v>-16.71</v>
+        <v>-17.44</v>
       </c>
       <c r="F25" s="67" t="n">
-        <v>1613</v>
+        <v>-3631</v>
       </c>
       <c r="G25" s="68" t="n">
-        <v>-2126</v>
+        <v>5139</v>
       </c>
       <c r="H25" s="68" t="n">
-        <v>-513</v>
+        <v>1508</v>
       </c>
       <c r="I25" s="68" t="n">
-        <v>-90</v>
+        <v>7490</v>
       </c>
       <c r="J25" s="68" t="n">
-        <v>-887</v>
-      </c>
-      <c r="K25" s="68" t="n">
-        <v>-1021</v>
+        <v>848</v>
+      </c>
+      <c r="K25" s="67" t="n">
+        <v>-3340</v>
       </c>
       <c r="L25" s="68" t="n">
-        <v>-124</v>
-      </c>
-      <c r="M25" s="67" t="n">
-        <v>511</v>
+        <v>190</v>
+      </c>
+      <c r="M25" s="68" t="n">
+        <v>3108</v>
       </c>
       <c r="N25" s="67" t="n">
-        <v>2</v>
+        <v>-4616</v>
       </c>
       <c r="O25" s="30" t="inlineStr"/>
     </row>
@@ -12595,43 +12666,43 @@
         </is>
       </c>
       <c r="B26" s="66" t="n">
-        <v>36.52</v>
+        <v>37.4</v>
       </c>
       <c r="C26" s="65" t="n">
-        <v>-13.29</v>
+        <v>-13.51</v>
       </c>
       <c r="D26" s="65" t="n">
-        <v>-20.04</v>
+        <v>-23.17</v>
       </c>
       <c r="E26" s="65" t="n">
-        <v>-20.97</v>
-      </c>
-      <c r="F26" s="68" t="n">
-        <v>-170314</v>
+        <v>-20.46</v>
+      </c>
+      <c r="F26" s="67" t="n">
+        <v>-179426</v>
       </c>
       <c r="G26" s="68" t="n">
-        <v>-1214</v>
-      </c>
-      <c r="H26" s="68" t="n">
-        <v>-171528</v>
-      </c>
-      <c r="I26" s="67" t="n">
-        <v>7809</v>
-      </c>
-      <c r="J26" s="68" t="n">
-        <v>-18906</v>
-      </c>
-      <c r="K26" s="67" t="n">
-        <v>3473</v>
-      </c>
-      <c r="L26" s="67" t="n">
-        <v>6913</v>
-      </c>
-      <c r="M26" s="67" t="n">
-        <v>69556</v>
-      </c>
-      <c r="N26" s="67" t="n">
-        <v>101971</v>
+        <v>5056</v>
+      </c>
+      <c r="H26" s="67" t="n">
+        <v>-174370</v>
+      </c>
+      <c r="I26" s="68" t="n">
+        <v>12188</v>
+      </c>
+      <c r="J26" s="67" t="n">
+        <v>-17782</v>
+      </c>
+      <c r="K26" s="68" t="n">
+        <v>3607</v>
+      </c>
+      <c r="L26" s="68" t="n">
+        <v>7533</v>
+      </c>
+      <c r="M26" s="68" t="n">
+        <v>71598</v>
+      </c>
+      <c r="N26" s="68" t="n">
+        <v>102772</v>
       </c>
       <c r="O26" s="58" t="inlineStr">
         <is>
@@ -12642,47 +12713,47 @@
     <row r="27">
       <c r="A27" s="31" t="inlineStr">
         <is>
-          <t>기계·장비</t>
-        </is>
-      </c>
-      <c r="B27" s="65" t="n">
-        <v>-11.62</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="B27" s="66" t="n">
+        <v>67.19</v>
       </c>
       <c r="C27" s="65" t="n">
-        <v>-42.7</v>
+        <v>-4.69</v>
       </c>
       <c r="D27" s="65" t="n">
-        <v>-13.06</v>
+        <v>-24.77</v>
       </c>
       <c r="E27" s="65" t="n">
-        <v>-21.87</v>
-      </c>
-      <c r="F27" s="68" t="n">
-        <v>-4629</v>
-      </c>
-      <c r="G27" s="68" t="n">
-        <v>-652</v>
-      </c>
-      <c r="H27" s="68" t="n">
-        <v>-5281</v>
+        <v>-22.59</v>
+      </c>
+      <c r="F27" s="67" t="n">
+        <v>-166518</v>
+      </c>
+      <c r="G27" s="67" t="n">
+        <v>-12335</v>
+      </c>
+      <c r="H27" s="67" t="n">
+        <v>-178854</v>
       </c>
       <c r="I27" s="67" t="n">
-        <v>2608</v>
-      </c>
-      <c r="J27" s="68" t="n">
-        <v>-2724</v>
+        <v>-735</v>
+      </c>
+      <c r="J27" s="67" t="n">
+        <v>-19606</v>
       </c>
       <c r="K27" s="68" t="n">
-        <v>-408</v>
+        <v>1904</v>
       </c>
       <c r="L27" s="68" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M27" s="67" t="n">
-        <v>5319</v>
+        <v>6474</v>
+      </c>
+      <c r="M27" s="68" t="n">
+        <v>72582</v>
       </c>
       <c r="N27" s="68" t="n">
-        <v>-38</v>
+        <v>106272</v>
       </c>
       <c r="O27" s="58" t="inlineStr">
         <is>
@@ -12693,47 +12764,47 @@
     <row r="28">
       <c r="A28" s="31" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="B28" s="66" t="n">
-        <v>65.09999999999999</v>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="B28" s="65" t="n">
+        <v>-13.89</v>
       </c>
       <c r="C28" s="65" t="n">
-        <v>-4.62</v>
+        <v>-45.92</v>
       </c>
       <c r="D28" s="65" t="n">
-        <v>-22.18</v>
+        <v>-19.41</v>
       </c>
       <c r="E28" s="65" t="n">
-        <v>-23.56</v>
-      </c>
-      <c r="F28" s="68" t="n">
-        <v>-157305</v>
-      </c>
-      <c r="G28" s="68" t="n">
-        <v>-18890</v>
-      </c>
-      <c r="H28" s="68" t="n">
-        <v>-176195</v>
+        <v>-23.88</v>
+      </c>
+      <c r="F28" s="67" t="n">
+        <v>-4630</v>
+      </c>
+      <c r="G28" s="67" t="n">
+        <v>-875</v>
+      </c>
+      <c r="H28" s="67" t="n">
+        <v>-5505</v>
       </c>
       <c r="I28" s="68" t="n">
-        <v>-5056</v>
-      </c>
-      <c r="J28" s="68" t="n">
-        <v>-21041</v>
+        <v>2684</v>
+      </c>
+      <c r="J28" s="67" t="n">
+        <v>-2905</v>
       </c>
       <c r="K28" s="67" t="n">
-        <v>1672</v>
+        <v>-498</v>
       </c>
       <c r="L28" s="67" t="n">
-        <v>5930</v>
-      </c>
-      <c r="M28" s="67" t="n">
-        <v>70671</v>
+        <v>-129</v>
+      </c>
+      <c r="M28" s="68" t="n">
+        <v>5575</v>
       </c>
       <c r="N28" s="67" t="n">
-        <v>105524</v>
+        <v>-70</v>
       </c>
       <c r="O28" s="58" t="inlineStr">
         <is>
@@ -12773,7 +12844,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{10224E41-0DE0-486B-AAE0-3C6B3F4AF9DC}</x14:id>
+          <x14:id>{EE7B8045-EC19-4BB5-A7D8-263B480F321A}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12787,7 +12858,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{495136CE-41FD-4978-8ADA-81B67BF607F2}</x14:id>
+          <x14:id>{D0453A34-5CBF-4CF6-BC3D-690832AF9BA8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12801,7 +12872,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{38ECDB25-9ED3-466F-BC6C-4A19A6D374B7}</x14:id>
+          <x14:id>{2E295493-1FE4-4B04-9291-6DF389B0BD12}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12815,7 +12886,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{44590A73-D80A-4926-A6E9-9CE59655980C}</x14:id>
+          <x14:id>{01F5D576-07EB-4504-9791-8DF2EA397790}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12825,7 +12896,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{10224E41-0DE0-486B-AAE0-3C6B3F4AF9DC}">
+          <x14:cfRule type="dataBar" id="{EE7B8045-EC19-4BB5-A7D8-263B480F321A}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12838,7 +12909,7 @@
           <xm:sqref>B5:B28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{495136CE-41FD-4978-8ADA-81B67BF607F2}">
+          <x14:cfRule type="dataBar" id="{D0453A34-5CBF-4CF6-BC3D-690832AF9BA8}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12851,7 +12922,7 @@
           <xm:sqref>C5:C28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{38ECDB25-9ED3-466F-BC6C-4A19A6D374B7}">
+          <x14:cfRule type="dataBar" id="{2E295493-1FE4-4B04-9291-6DF389B0BD12}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12864,7 +12935,7 @@
           <xm:sqref>D5:D28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{44590A73-D80A-4926-A6E9-9CE59655980C}">
+          <x14:cfRule type="dataBar" id="{01F5D576-07EB-4504-9791-8DF2EA397790}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/public/monthly_review.xlsx
+++ b/public/monthly_review.xlsx
@@ -1020,7 +1020,7 @@
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>미국 종가 기준 09/30 → 10/22, %</t>
+          <t>미국 종가 기준 09/30 → 10/23, %</t>
         </is>
       </c>
       <c r="I6" s="18" t="inlineStr"/>
@@ -1089,20 +1089,20 @@
       <c r="D8" s="28" t="n">
         <v>16699</v>
       </c>
-      <c r="E8" s="28" t="n">
-        <v>0.16</v>
+      <c r="E8" s="29" t="n">
+        <v>-0.36</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>3.85</v>
+        <v>2.57</v>
       </c>
       <c r="G8" s="29" t="n">
-        <v>-3.17</v>
+        <v>-3.37</v>
       </c>
       <c r="H8" s="28" t="n">
-        <v>16.46</v>
+        <v>19.03</v>
       </c>
       <c r="I8" s="29" t="n">
-        <v>-15.02</v>
+        <v>-14.64</v>
       </c>
     </row>
     <row r="9">
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="D12" s="32" t="n">
-        <v>9.869999999999999</v>
+        <v>12.73</v>
       </c>
     </row>
     <row r="13">
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="D13" s="32" t="n">
-        <v>7.65</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="14">
@@ -1201,7 +1201,7 @@
         </is>
       </c>
       <c r="D14" s="32" t="n">
-        <v>6.14</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="15">
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="D15" s="33" t="n">
-        <v>-14.06</v>
+        <v>-13.43</v>
       </c>
     </row>
     <row r="16">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="D16" s="33" t="n">
-        <v>-6.85</v>
+        <v>-6.4</v>
       </c>
     </row>
     <row r="17">
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="D17" s="33" t="n">
-        <v>-3.83</v>
+        <v>-5.16</v>
       </c>
     </row>
     <row r="18">
@@ -12844,7 +12844,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{EE7B8045-EC19-4BB5-A7D8-263B480F321A}</x14:id>
+          <x14:id>{6D10690F-C0E0-401B-89F2-5DF5250FF68A}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12858,7 +12858,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{D0453A34-5CBF-4CF6-BC3D-690832AF9BA8}</x14:id>
+          <x14:id>{DA02D0B1-F057-4961-AC2E-F305DD077A83}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12872,7 +12872,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2E295493-1FE4-4B04-9291-6DF389B0BD12}</x14:id>
+          <x14:id>{7EAF0C9F-D299-420A-A99E-2CA80C11B20C}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12886,7 +12886,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{01F5D576-07EB-4504-9791-8DF2EA397790}</x14:id>
+          <x14:id>{8CBE2EA4-B133-4411-B0D1-241C3F04C332}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12896,7 +12896,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{EE7B8045-EC19-4BB5-A7D8-263B480F321A}">
+          <x14:cfRule type="dataBar" id="{6D10690F-C0E0-401B-89F2-5DF5250FF68A}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12909,7 +12909,7 @@
           <xm:sqref>B5:B28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{D0453A34-5CBF-4CF6-BC3D-690832AF9BA8}">
+          <x14:cfRule type="dataBar" id="{DA02D0B1-F057-4961-AC2E-F305DD077A83}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12922,7 +12922,7 @@
           <xm:sqref>C5:C28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2E295493-1FE4-4B04-9291-6DF389B0BD12}">
+          <x14:cfRule type="dataBar" id="{7EAF0C9F-D299-420A-A99E-2CA80C11B20C}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12935,7 +12935,7 @@
           <xm:sqref>D5:D28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{01F5D576-07EB-4504-9791-8DF2EA397790}">
+          <x14:cfRule type="dataBar" id="{8CBE2EA4-B133-4411-B0D1-241C3F04C332}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/public/monthly_review.xlsx
+++ b/public/monthly_review.xlsx
@@ -321,7 +321,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -416,9 +416,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1014,7 +1011,7 @@
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>미국 종가 기준 09/30 → 10/29, %</t>
+          <t>미국 종가 기준 09/30 → 10/30, %</t>
         </is>
       </c>
       <c r="I6" s="18" t="inlineStr"/>
@@ -1083,20 +1080,20 @@
       <c r="D8" s="28" t="n">
         <v>38129</v>
       </c>
-      <c r="E8" s="28" t="n">
-        <v>0.9</v>
+      <c r="E8" s="29" t="n">
+        <v>-0.93</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>2.82</v>
+        <v>1.7</v>
       </c>
       <c r="G8" s="29" t="n">
-        <v>-2.52</v>
+        <v>-5.3</v>
       </c>
       <c r="H8" s="28" t="n">
-        <v>5.26</v>
+        <v>18.85</v>
       </c>
       <c r="I8" s="29" t="n">
-        <v>-8.789999999999999</v>
+        <v>-15.36</v>
       </c>
     </row>
     <row r="9">
@@ -1155,7 +1152,7 @@
         </is>
       </c>
       <c r="D12" s="32" t="n">
-        <v>11.72</v>
+        <v>13.85</v>
       </c>
     </row>
     <row r="13">
@@ -1175,7 +1172,7 @@
         </is>
       </c>
       <c r="D13" s="32" t="n">
-        <v>9.27</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="14">
@@ -1195,7 +1192,7 @@
         </is>
       </c>
       <c r="D14" s="32" t="n">
-        <v>7.86</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1215,7 +1212,7 @@
         </is>
       </c>
       <c r="D15" s="33" t="n">
-        <v>-7.77</v>
+        <v>-14.21</v>
       </c>
     </row>
     <row r="16">
@@ -1235,7 +1232,7 @@
         </is>
       </c>
       <c r="D16" s="33" t="n">
-        <v>-3.58</v>
+        <v>-8.300000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1251,13 +1248,11 @@
       </c>
       <c r="C17" s="31" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
-        </is>
-      </c>
-      <c r="D17" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>바이오</t>
+        </is>
+      </c>
+      <c r="D17" s="33" t="n">
+        <v>-1.08</v>
       </c>
     </row>
     <row r="18">
@@ -4357,7 +4352,7 @@
           <t>삼성E&amp;A</t>
         </is>
       </c>
-      <c r="D99" s="35" t="inlineStr">
+      <c r="D99" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
@@ -4398,7 +4393,7 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="D100" s="35" t="inlineStr">
+      <c r="D100" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -4439,7 +4434,7 @@
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="D101" s="35" t="inlineStr">
+      <c r="D101" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
@@ -4480,7 +4475,7 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="D102" s="35" t="inlineStr">
+      <c r="D102" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
@@ -4521,7 +4516,7 @@
           <t>LG씨엔에스</t>
         </is>
       </c>
-      <c r="D103" s="35" t="inlineStr">
+      <c r="D103" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
@@ -4562,7 +4557,7 @@
           <t>HMM</t>
         </is>
       </c>
-      <c r="D104" s="35" t="inlineStr">
+      <c r="D104" s="34" t="inlineStr">
         <is>
           <t>운송·창고</t>
         </is>
@@ -4603,7 +4598,7 @@
           <t>알테오젠</t>
         </is>
       </c>
-      <c r="D105" s="35" t="inlineStr">
+      <c r="D105" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
@@ -4644,7 +4639,7 @@
           <t>하이브</t>
         </is>
       </c>
-      <c r="D106" s="35" t="inlineStr">
+      <c r="D106" s="34" t="inlineStr">
         <is>
           <t>오락·문화</t>
         </is>
@@ -4685,7 +4680,7 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="D107" s="35" t="inlineStr">
+      <c r="D107" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -4726,7 +4721,7 @@
           <t>삼성물산</t>
         </is>
       </c>
-      <c r="D108" s="35" t="inlineStr">
+      <c r="D108" s="34" t="inlineStr">
         <is>
           <t>유통</t>
         </is>
@@ -4767,7 +4762,7 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="D109" s="35" t="inlineStr">
+      <c r="D109" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -4808,7 +4803,7 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="D110" s="35" t="inlineStr">
+      <c r="D110" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -4849,7 +4844,7 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="D111" s="35" t="inlineStr">
+      <c r="D111" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -4890,7 +4885,7 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="D112" s="35" t="inlineStr">
+      <c r="D112" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -4931,7 +4926,7 @@
           <t>효성중공업</t>
         </is>
       </c>
-      <c r="D113" s="35" t="inlineStr">
+      <c r="D113" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -4972,7 +4967,7 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="D114" s="35" t="inlineStr">
+      <c r="D114" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
@@ -5013,7 +5008,7 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="D115" s="35" t="inlineStr">
+      <c r="D115" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
@@ -5054,7 +5049,7 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="D116" s="35" t="inlineStr">
+      <c r="D116" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -5095,7 +5090,7 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="D117" s="35" t="inlineStr">
+      <c r="D117" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
@@ -5136,7 +5131,7 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="D118" s="35" t="inlineStr">
+      <c r="D118" s="34" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
@@ -5190,7 +5185,7 @@
       <c r="K120" s="3" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="36" t="inlineStr">
+      <c r="A121" s="35" t="inlineStr">
         <is>
           <t>● 동반강세 — 추세 지속형 상방 관찰</t>
         </is>
@@ -5207,12 +5202,12 @@
           <t>삼성생명</t>
         </is>
       </c>
-      <c r="B122" s="35" t="inlineStr">
+      <c r="B122" s="34" t="inlineStr">
         <is>
           <t>보험</t>
         </is>
       </c>
-      <c r="C122" s="37" t="n">
+      <c r="C122" s="36" t="n">
         <v>1</v>
       </c>
       <c r="D122" s="31" t="inlineStr"/>
@@ -5222,12 +5217,12 @@
           <t>아모레퍼시픽</t>
         </is>
       </c>
-      <c r="H122" s="35" t="inlineStr">
+      <c r="H122" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="I122" s="38" t="n">
+      <c r="I122" s="37" t="n">
         <v>3</v>
       </c>
       <c r="J122" s="31" t="inlineStr"/>
@@ -5251,12 +5246,12 @@
           <t>롯데손해보험</t>
         </is>
       </c>
-      <c r="B124" s="35" t="inlineStr">
+      <c r="B124" s="34" t="inlineStr">
         <is>
           <t>보험</t>
         </is>
       </c>
-      <c r="C124" s="37" t="n">
+      <c r="C124" s="36" t="n">
         <v>1</v>
       </c>
       <c r="D124" s="31" t="inlineStr"/>
@@ -5266,12 +5261,12 @@
           <t>LG생활건강</t>
         </is>
       </c>
-      <c r="H124" s="35" t="inlineStr">
+      <c r="H124" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="I124" s="38" t="n">
+      <c r="I124" s="37" t="n">
         <v>3</v>
       </c>
       <c r="J124" s="31" t="inlineStr"/>
@@ -5295,12 +5290,12 @@
           <t>DB손해보험</t>
         </is>
       </c>
-      <c r="B126" s="35" t="inlineStr">
+      <c r="B126" s="34" t="inlineStr">
         <is>
           <t>보험</t>
         </is>
       </c>
-      <c r="C126" s="37" t="n">
+      <c r="C126" s="36" t="n">
         <v>1</v>
       </c>
       <c r="D126" s="31" t="inlineStr"/>
@@ -5310,12 +5305,12 @@
           <t>한일시멘트</t>
         </is>
       </c>
-      <c r="H126" s="35" t="inlineStr">
+      <c r="H126" s="34" t="inlineStr">
         <is>
           <t>비금속</t>
         </is>
       </c>
-      <c r="I126" s="38" t="n">
+      <c r="I126" s="37" t="n">
         <v>3</v>
       </c>
       <c r="J126" s="31" t="inlineStr"/>
@@ -5339,12 +5334,12 @@
           <t>미래에셋생명</t>
         </is>
       </c>
-      <c r="B128" s="35" t="inlineStr">
+      <c r="B128" s="34" t="inlineStr">
         <is>
           <t>보험</t>
         </is>
       </c>
-      <c r="C128" s="37" t="n">
+      <c r="C128" s="36" t="n">
         <v>1</v>
       </c>
       <c r="D128" s="31" t="inlineStr"/>
@@ -5354,12 +5349,12 @@
           <t>CJ CGV</t>
         </is>
       </c>
-      <c r="H128" s="35" t="inlineStr">
+      <c r="H128" s="34" t="inlineStr">
         <is>
           <t>오락·문화</t>
         </is>
       </c>
-      <c r="I128" s="38" t="n">
+      <c r="I128" s="37" t="n">
         <v>3</v>
       </c>
       <c r="J128" s="31" t="inlineStr"/>
@@ -5383,12 +5378,12 @@
           <t>나이스정보통신</t>
         </is>
       </c>
-      <c r="H130" s="35" t="inlineStr">
+      <c r="H130" s="34" t="inlineStr">
         <is>
           <t>통신</t>
         </is>
       </c>
-      <c r="I130" s="38" t="n">
+      <c r="I130" s="37" t="n">
         <v>3</v>
       </c>
       <c r="J130" s="31" t="inlineStr"/>
@@ -5403,12 +5398,12 @@
     </row>
     <row r="132"/>
     <row r="133">
-      <c r="A133" s="39" t="inlineStr">
+      <c r="A133" s="38" t="inlineStr">
         <is>
           <t>● 수급이탈 — 상승 후 약화 관찰</t>
         </is>
       </c>
-      <c r="G133" s="40" t="inlineStr">
+      <c r="G133" s="39" t="inlineStr">
         <is>
           <t>● 동반약세 — 약세 지속형 하방 관찰</t>
         </is>
@@ -5425,12 +5420,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="H134" s="35" t="inlineStr">
+      <c r="H134" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="I134" s="41" t="n">
+      <c r="I134" s="40" t="n">
         <v>-2</v>
       </c>
       <c r="J134" s="31" t="inlineStr"/>
@@ -5449,12 +5444,12 @@
           <t>주성엔지니어링</t>
         </is>
       </c>
-      <c r="H136" s="35" t="inlineStr">
+      <c r="H136" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="I136" s="41" t="n">
+      <c r="I136" s="40" t="n">
         <v>-2</v>
       </c>
       <c r="J136" s="31" t="inlineStr"/>
@@ -5473,12 +5468,12 @@
           <t>원익IPS</t>
         </is>
       </c>
-      <c r="H138" s="35" t="inlineStr">
+      <c r="H138" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="I138" s="41" t="n">
+      <c r="I138" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="J138" s="31" t="inlineStr"/>
@@ -5497,12 +5492,12 @@
           <t>고려아연</t>
         </is>
       </c>
-      <c r="H140" s="35" t="inlineStr">
+      <c r="H140" s="34" t="inlineStr">
         <is>
           <t>금속</t>
         </is>
       </c>
-      <c r="I140" s="41" t="n">
+      <c r="I140" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="J140" s="31" t="inlineStr"/>
@@ -5521,12 +5516,12 @@
           <t>풍산</t>
         </is>
       </c>
-      <c r="H142" s="35" t="inlineStr">
+      <c r="H142" s="34" t="inlineStr">
         <is>
           <t>금속</t>
         </is>
       </c>
-      <c r="I142" s="41" t="n">
+      <c r="I142" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="J142" s="31" t="inlineStr"/>
@@ -5541,7 +5536,7 @@
     </row>
     <row r="144"/>
     <row r="145" ht="31" customHeight="1" s="15">
-      <c r="A145" s="42" t="inlineStr">
+      <c r="A145" s="41" t="inlineStr">
         <is>
           <t>현재 확보된 월간 리뷰 데이터 유니버스(순매수 상위 30 등재 · 공매도/대차 랭킹 · 월간 촉매 · 신호 섹터 시총 상위 10) 기준 — 전 시장 스크리닝 아님 · 관찰 우선순위이며 매매 권유 아님</t>
         </is>
@@ -5745,7 +5740,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D163" s="35" t="inlineStr">
+      <c r="D163" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
@@ -5780,7 +5775,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D164" s="35" t="inlineStr">
+      <c r="D164" s="34" t="inlineStr">
         <is>
           <t>섬유·의류</t>
         </is>
@@ -5815,7 +5810,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D165" s="35" t="inlineStr">
+      <c r="D165" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -5850,7 +5845,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D166" s="35" t="inlineStr">
+      <c r="D166" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
@@ -5885,7 +5880,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D167" s="35" t="inlineStr">
+      <c r="D167" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
@@ -5920,7 +5915,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D168" s="35" t="inlineStr">
+      <c r="D168" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
@@ -5955,7 +5950,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D169" s="35" t="inlineStr">
+      <c r="D169" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
@@ -5990,7 +5985,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D170" s="35" t="inlineStr">
+      <c r="D170" s="34" t="inlineStr">
         <is>
           <t>운송·창고</t>
         </is>
@@ -6025,7 +6020,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D171" s="35" t="inlineStr">
+      <c r="D171" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -6060,7 +6055,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D172" s="35" t="inlineStr">
+      <c r="D172" s="34" t="inlineStr">
         <is>
           <t>섬유·의류</t>
         </is>
@@ -6095,7 +6090,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D173" s="35" t="inlineStr">
+      <c r="D173" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
@@ -6130,7 +6125,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D174" s="35" t="inlineStr">
+      <c r="D174" s="34" t="inlineStr">
         <is>
           <t>운송·창고</t>
         </is>
@@ -6166,7 +6161,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D175" s="35" t="inlineStr">
+      <c r="D175" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
@@ -6202,7 +6197,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D176" s="35" t="inlineStr">
+      <c r="D176" s="34" t="inlineStr">
         <is>
           <t>비금속</t>
         </is>
@@ -6238,7 +6233,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D177" s="35" t="inlineStr">
+      <c r="D177" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
@@ -6274,7 +6269,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D178" s="35" t="inlineStr">
+      <c r="D178" s="34" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
@@ -6309,7 +6304,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D179" s="35" t="inlineStr">
+      <c r="D179" s="34" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
@@ -6344,7 +6339,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D180" s="35" t="inlineStr">
+      <c r="D180" s="34" t="inlineStr">
         <is>
           <t>유통</t>
         </is>
@@ -6379,7 +6374,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D181" s="35" t="inlineStr">
+      <c r="D181" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
@@ -6414,7 +6409,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D182" s="35" t="inlineStr">
+      <c r="D182" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
@@ -6449,7 +6444,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D183" s="35" t="inlineStr">
+      <c r="D183" s="34" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
@@ -6484,7 +6479,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D184" s="35" t="inlineStr">
+      <c r="D184" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -6519,7 +6514,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D185" s="35" t="inlineStr">
+      <c r="D185" s="34" t="inlineStr">
         <is>
           <t>유통</t>
         </is>
@@ -6554,7 +6549,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D186" s="35" t="inlineStr">
+      <c r="D186" s="34" t="inlineStr">
         <is>
           <t>섬유·의류</t>
         </is>
@@ -6589,7 +6584,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D187" s="35" t="inlineStr">
+      <c r="D187" s="34" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
@@ -6624,7 +6619,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D188" s="35" t="inlineStr">
+      <c r="D188" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
@@ -6660,7 +6655,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D189" s="35" t="inlineStr">
+      <c r="D189" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
@@ -6695,7 +6690,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D190" s="35" t="inlineStr">
+      <c r="D190" s="34" t="inlineStr">
         <is>
           <t>유통</t>
         </is>
@@ -6731,7 +6726,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D191" s="35" t="inlineStr">
+      <c r="D191" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
@@ -6766,7 +6761,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D192" s="35" t="inlineStr">
+      <c r="D192" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
@@ -6801,7 +6796,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D193" s="35" t="inlineStr">
+      <c r="D193" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
@@ -6836,7 +6831,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D194" s="35" t="inlineStr">
+      <c r="D194" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
@@ -6871,7 +6866,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D195" s="35" t="inlineStr">
+      <c r="D195" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
@@ -6906,7 +6901,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D196" s="35" t="inlineStr">
+      <c r="D196" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -6941,7 +6936,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D197" s="35" t="inlineStr">
+      <c r="D197" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
@@ -6976,7 +6971,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D198" s="35" t="inlineStr">
+      <c r="D198" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
@@ -7270,62 +7265,62 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="43" t="inlineStr">
+      <c r="A5" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B5" s="43" t="inlineStr">
+      <c r="B5" s="42" t="inlineStr">
         <is>
           <t>시장</t>
         </is>
       </c>
-      <c r="C5" s="43" t="inlineStr">
+      <c r="C5" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D5" s="43" t="inlineStr">
+      <c r="D5" s="42" t="inlineStr">
         <is>
           <t>합산</t>
         </is>
       </c>
-      <c r="E5" s="43" t="inlineStr">
+      <c r="E5" s="42" t="inlineStr">
         <is>
           <t>외인</t>
         </is>
       </c>
-      <c r="F5" s="43" t="inlineStr">
+      <c r="F5" s="42" t="inlineStr">
         <is>
           <t>기관</t>
         </is>
       </c>
-      <c r="G5" s="43" t="inlineStr">
+      <c r="G5" s="42" t="inlineStr">
         <is>
           <t>개인</t>
         </is>
       </c>
-      <c r="H5" s="43" t="inlineStr">
+      <c r="H5" s="42" t="inlineStr">
         <is>
           <t>공매도</t>
         </is>
       </c>
-      <c r="I5" s="43" t="inlineStr">
+      <c r="I5" s="42" t="inlineStr">
         <is>
           <t>대차잔고</t>
         </is>
       </c>
-      <c r="J5" s="43" t="inlineStr">
+      <c r="J5" s="42" t="inlineStr">
         <is>
           <t>대차증감</t>
         </is>
       </c>
-      <c r="K5" s="43" t="inlineStr">
+      <c r="K5" s="42" t="inlineStr">
         <is>
           <t>월간등락(%)</t>
         </is>
       </c>
-      <c r="L5" s="43" t="inlineStr">
+      <c r="L5" s="42" t="inlineStr">
         <is>
           <t>신고가대비(%)</t>
         </is>
@@ -7342,36 +7337,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="C6" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="D6" s="44" t="n">
+      <c r="D6" s="43" t="n">
         <v>5656</v>
       </c>
-      <c r="E6" s="44" t="n">
+      <c r="E6" s="43" t="n">
         <v>4711</v>
       </c>
-      <c r="F6" s="44" t="n">
+      <c r="F6" s="43" t="n">
         <v>945</v>
       </c>
-      <c r="G6" s="45" t="n">
+      <c r="G6" s="44" t="n">
         <v>-6515</v>
       </c>
-      <c r="H6" s="46" t="n">
+      <c r="H6" s="45" t="n">
         <v>1478.7</v>
       </c>
-      <c r="I6" s="46" t="n">
+      <c r="I6" s="45" t="n">
         <v>4245.9</v>
       </c>
-      <c r="J6" s="47" t="n">
+      <c r="J6" s="46" t="n">
         <v>1211</v>
       </c>
-      <c r="K6" s="48" t="n">
+      <c r="K6" s="47" t="n">
         <v>27.56</v>
       </c>
-      <c r="L6" s="49" t="n">
+      <c r="L6" s="48" t="n">
         <v>-9.789999999999999</v>
       </c>
     </row>
@@ -7386,36 +7381,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C7" s="35" t="inlineStr">
+      <c r="C7" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="D7" s="44" t="n">
+      <c r="D7" s="43" t="n">
         <v>346</v>
       </c>
-      <c r="E7" s="44" t="n">
+      <c r="E7" s="43" t="n">
         <v>136</v>
       </c>
-      <c r="F7" s="44" t="n">
+      <c r="F7" s="43" t="n">
         <v>209</v>
       </c>
-      <c r="G7" s="45" t="n">
+      <c r="G7" s="44" t="n">
         <v>-340</v>
       </c>
-      <c r="H7" s="46" t="n">
+      <c r="H7" s="45" t="n">
         <v>288.9</v>
       </c>
-      <c r="I7" s="46" t="n">
+      <c r="I7" s="45" t="n">
         <v>618.8</v>
       </c>
-      <c r="J7" s="47" t="n">
+      <c r="J7" s="46" t="n">
         <v>231.1</v>
       </c>
-      <c r="K7" s="48" t="n">
+      <c r="K7" s="47" t="n">
         <v>64.84</v>
       </c>
-      <c r="L7" s="50" t="n">
+      <c r="L7" s="49" t="n">
         <v>-0.33</v>
       </c>
     </row>
@@ -7430,36 +7425,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="C8" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="D8" s="45" t="n">
+      <c r="D8" s="44" t="n">
         <v>-10</v>
       </c>
-      <c r="E8" s="45" t="n">
+      <c r="E8" s="44" t="n">
         <v>-26</v>
       </c>
-      <c r="F8" s="44" t="n">
+      <c r="F8" s="43" t="n">
         <v>16</v>
       </c>
-      <c r="G8" s="44" t="n">
+      <c r="G8" s="43" t="n">
         <v>21</v>
       </c>
-      <c r="H8" s="46" t="n">
+      <c r="H8" s="45" t="n">
         <v>34.6</v>
       </c>
-      <c r="I8" s="46" t="n">
+      <c r="I8" s="45" t="n">
         <v>70.5</v>
       </c>
-      <c r="J8" s="47" t="n">
+      <c r="J8" s="46" t="n">
         <v>22.4</v>
       </c>
-      <c r="K8" s="48" t="n">
+      <c r="K8" s="47" t="n">
         <v>45.89</v>
       </c>
-      <c r="L8" s="49" t="n">
+      <c r="L8" s="48" t="n">
         <v>-7.86</v>
       </c>
     </row>
@@ -7474,36 +7469,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C9" s="35" t="inlineStr">
+      <c r="C9" s="34" t="inlineStr">
         <is>
           <t>음식료·담배</t>
         </is>
       </c>
-      <c r="D9" s="45" t="n">
+      <c r="D9" s="44" t="n">
         <v>-242</v>
       </c>
-      <c r="E9" s="45" t="n">
+      <c r="E9" s="44" t="n">
         <v>-887</v>
       </c>
-      <c r="F9" s="44" t="n">
+      <c r="F9" s="43" t="n">
         <v>644</v>
       </c>
-      <c r="G9" s="45" t="n">
+      <c r="G9" s="44" t="n">
         <v>-647</v>
       </c>
-      <c r="H9" s="46" t="n">
+      <c r="H9" s="45" t="n">
         <v>683.2</v>
       </c>
-      <c r="I9" s="46" t="n">
+      <c r="I9" s="45" t="n">
         <v>2602.9</v>
       </c>
-      <c r="J9" s="51" t="n">
+      <c r="J9" s="50" t="n">
         <v>-114.8</v>
       </c>
-      <c r="K9" s="48" t="n">
+      <c r="K9" s="47" t="n">
         <v>10.95</v>
       </c>
-      <c r="L9" s="50" t="n">
+      <c r="L9" s="49" t="n">
         <v>-0.41</v>
       </c>
     </row>
@@ -7518,36 +7513,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C10" s="35" t="inlineStr">
+      <c r="C10" s="34" t="inlineStr">
         <is>
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="D10" s="44" t="n">
+      <c r="D10" s="43" t="n">
         <v>2215</v>
       </c>
-      <c r="E10" s="44" t="n">
+      <c r="E10" s="43" t="n">
         <v>1600</v>
       </c>
-      <c r="F10" s="44" t="n">
+      <c r="F10" s="43" t="n">
         <v>615</v>
       </c>
-      <c r="G10" s="45" t="n">
+      <c r="G10" s="44" t="n">
         <v>-3292</v>
       </c>
-      <c r="H10" s="46" t="n">
+      <c r="H10" s="45" t="n">
         <v>338.2</v>
       </c>
-      <c r="I10" s="46" t="n">
+      <c r="I10" s="45" t="n">
         <v>3203.8</v>
       </c>
-      <c r="J10" s="51" t="n">
+      <c r="J10" s="50" t="n">
         <v>-198.3</v>
       </c>
-      <c r="K10" s="48" t="n">
+      <c r="K10" s="47" t="n">
         <v>11.72</v>
       </c>
-      <c r="L10" s="49" t="n">
+      <c r="L10" s="48" t="n">
         <v>-7.08</v>
       </c>
     </row>
@@ -7562,36 +7557,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C11" s="35" t="inlineStr">
+      <c r="C11" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D11" s="44" t="n">
+      <c r="D11" s="43" t="n">
         <v>352</v>
       </c>
-      <c r="E11" s="45" t="n">
+      <c r="E11" s="44" t="n">
         <v>-255</v>
       </c>
-      <c r="F11" s="44" t="n">
+      <c r="F11" s="43" t="n">
         <v>607</v>
       </c>
-      <c r="G11" s="45" t="n">
+      <c r="G11" s="44" t="n">
         <v>-333</v>
       </c>
-      <c r="H11" s="46" t="n">
+      <c r="H11" s="45" t="n">
         <v>95.09999999999999</v>
       </c>
-      <c r="I11" s="46" t="n">
+      <c r="I11" s="45" t="n">
         <v>225.8</v>
       </c>
-      <c r="J11" s="47" t="n">
+      <c r="J11" s="46" t="n">
         <v>48.5</v>
       </c>
-      <c r="K11" s="48" t="n">
+      <c r="K11" s="47" t="n">
         <v>40.19</v>
       </c>
-      <c r="L11" s="52" t="n">
+      <c r="L11" s="51" t="n">
         <v>-3.73</v>
       </c>
     </row>
@@ -7606,36 +7601,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C12" s="35" t="inlineStr">
+      <c r="C12" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D12" s="45" t="n">
+      <c r="D12" s="44" t="n">
         <v>-2</v>
       </c>
-      <c r="E12" s="45" t="n">
+      <c r="E12" s="44" t="n">
         <v>-2</v>
       </c>
-      <c r="F12" s="53" t="n">
+      <c r="F12" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="53" t="n">
+      <c r="G12" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="46" t="n">
+      <c r="H12" s="45" t="n">
         <v>0.9</v>
       </c>
-      <c r="I12" s="46" t="n">
+      <c r="I12" s="45" t="n">
         <v>9.1</v>
       </c>
-      <c r="J12" s="47" t="n">
+      <c r="J12" s="46" t="n">
         <v>3.5</v>
       </c>
-      <c r="K12" s="48" t="n">
+      <c r="K12" s="47" t="n">
         <v>76.27</v>
       </c>
-      <c r="L12" s="52" t="n">
+      <c r="L12" s="51" t="n">
         <v>-4.08</v>
       </c>
     </row>
@@ -7650,36 +7645,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C13" s="35" t="inlineStr">
+      <c r="C13" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="D13" s="44" t="n">
+      <c r="D13" s="43" t="n">
         <v>88</v>
       </c>
-      <c r="E13" s="45" t="n">
+      <c r="E13" s="44" t="n">
         <v>-125</v>
       </c>
-      <c r="F13" s="44" t="n">
+      <c r="F13" s="43" t="n">
         <v>213</v>
       </c>
-      <c r="G13" s="45" t="n">
+      <c r="G13" s="44" t="n">
         <v>-84</v>
       </c>
-      <c r="H13" s="46" t="n">
+      <c r="H13" s="45" t="n">
         <v>429.2</v>
       </c>
-      <c r="I13" s="46" t="n">
+      <c r="I13" s="45" t="n">
         <v>1272.8</v>
       </c>
-      <c r="J13" s="47" t="n">
+      <c r="J13" s="46" t="n">
         <v>449.5</v>
       </c>
-      <c r="K13" s="48" t="n">
+      <c r="K13" s="47" t="n">
         <v>4.42</v>
       </c>
-      <c r="L13" s="49" t="n">
+      <c r="L13" s="48" t="n">
         <v>-7.5</v>
       </c>
     </row>
@@ -7694,36 +7689,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C14" s="35" t="inlineStr">
+      <c r="C14" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D14" s="45" t="n">
+      <c r="D14" s="44" t="n">
         <v>-69</v>
       </c>
-      <c r="E14" s="45" t="n">
+      <c r="E14" s="44" t="n">
         <v>-50</v>
       </c>
-      <c r="F14" s="45" t="n">
+      <c r="F14" s="44" t="n">
         <v>-19</v>
       </c>
-      <c r="G14" s="44" t="n">
+      <c r="G14" s="43" t="n">
         <v>72</v>
       </c>
-      <c r="H14" s="46" t="n">
+      <c r="H14" s="45" t="n">
         <v>27.2</v>
       </c>
-      <c r="I14" s="46" t="n">
+      <c r="I14" s="45" t="n">
         <v>56.2</v>
       </c>
-      <c r="J14" s="47" t="n">
+      <c r="J14" s="46" t="n">
         <v>15.9</v>
       </c>
-      <c r="K14" s="48" t="n">
+      <c r="K14" s="47" t="n">
         <v>29.52</v>
       </c>
-      <c r="L14" s="52" t="n">
+      <c r="L14" s="51" t="n">
         <v>-2.16</v>
       </c>
     </row>
@@ -7738,36 +7733,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C15" s="35" t="inlineStr">
+      <c r="C15" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="D15" s="44" t="n">
+      <c r="D15" s="43" t="n">
         <v>130</v>
       </c>
-      <c r="E15" s="45" t="n">
+      <c r="E15" s="44" t="n">
         <v>-345</v>
       </c>
-      <c r="F15" s="44" t="n">
+      <c r="F15" s="43" t="n">
         <v>475</v>
       </c>
-      <c r="G15" s="45" t="n">
+      <c r="G15" s="44" t="n">
         <v>-128</v>
       </c>
-      <c r="H15" s="46" t="n">
+      <c r="H15" s="45" t="n">
         <v>161</v>
       </c>
-      <c r="I15" s="46" t="n">
+      <c r="I15" s="45" t="n">
         <v>3140.9</v>
       </c>
-      <c r="J15" s="47" t="n">
+      <c r="J15" s="46" t="n">
         <v>1928</v>
       </c>
-      <c r="K15" s="48" t="n">
+      <c r="K15" s="47" t="n">
         <v>18.14</v>
       </c>
-      <c r="L15" s="49" t="n">
+      <c r="L15" s="48" t="n">
         <v>-5.53</v>
       </c>
     </row>
@@ -7782,36 +7777,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C16" s="35" t="inlineStr">
+      <c r="C16" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="D16" s="44" t="n">
+      <c r="D16" s="43" t="n">
         <v>47</v>
       </c>
-      <c r="E16" s="45" t="n">
+      <c r="E16" s="44" t="n">
         <v>-153</v>
       </c>
-      <c r="F16" s="44" t="n">
+      <c r="F16" s="43" t="n">
         <v>200</v>
       </c>
-      <c r="G16" s="45" t="n">
+      <c r="G16" s="44" t="n">
         <v>-48</v>
       </c>
-      <c r="H16" s="46" t="n">
+      <c r="H16" s="45" t="n">
         <v>16.9</v>
       </c>
-      <c r="I16" s="46" t="n">
+      <c r="I16" s="45" t="n">
         <v>471.2</v>
       </c>
-      <c r="J16" s="47" t="n">
+      <c r="J16" s="46" t="n">
         <v>169.8</v>
       </c>
-      <c r="K16" s="48" t="n">
+      <c r="K16" s="47" t="n">
         <v>37.21</v>
       </c>
-      <c r="L16" s="52" t="n">
+      <c r="L16" s="51" t="n">
         <v>-2.5</v>
       </c>
     </row>
@@ -7826,36 +7821,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C17" s="35" t="inlineStr">
+      <c r="C17" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="D17" s="44" t="n">
+      <c r="D17" s="43" t="n">
         <v>127</v>
       </c>
-      <c r="E17" s="44" t="n">
+      <c r="E17" s="43" t="n">
         <v>78</v>
       </c>
-      <c r="F17" s="44" t="n">
+      <c r="F17" s="43" t="n">
         <v>49</v>
       </c>
-      <c r="G17" s="45" t="n">
+      <c r="G17" s="44" t="n">
         <v>-126</v>
       </c>
-      <c r="H17" s="46" t="n">
+      <c r="H17" s="45" t="n">
         <v>113.9</v>
       </c>
-      <c r="I17" s="46" t="n">
+      <c r="I17" s="45" t="n">
         <v>649.5</v>
       </c>
-      <c r="J17" s="47" t="n">
+      <c r="J17" s="46" t="n">
         <v>20.7</v>
       </c>
-      <c r="K17" s="48" t="n">
+      <c r="K17" s="47" t="n">
         <v>3.98</v>
       </c>
-      <c r="L17" s="52" t="n">
+      <c r="L17" s="51" t="n">
         <v>-2.12</v>
       </c>
     </row>
@@ -7870,36 +7865,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C18" s="35" t="inlineStr">
+      <c r="C18" s="34" t="inlineStr">
         <is>
           <t>섬유·의류</t>
         </is>
       </c>
-      <c r="D18" s="45" t="n">
+      <c r="D18" s="44" t="n">
         <v>-4</v>
       </c>
-      <c r="E18" s="45" t="n">
+      <c r="E18" s="44" t="n">
         <v>-5</v>
       </c>
-      <c r="F18" s="44" t="n">
+      <c r="F18" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="44" t="n">
+      <c r="G18" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="H18" s="46" t="n">
+      <c r="H18" s="45" t="n">
         <v>1.1</v>
       </c>
-      <c r="I18" s="46" t="n">
+      <c r="I18" s="45" t="n">
         <v>7.2</v>
       </c>
-      <c r="J18" s="51" t="n">
+      <c r="J18" s="50" t="n">
         <v>-0.4</v>
       </c>
-      <c r="K18" s="48" t="n">
+      <c r="K18" s="47" t="n">
         <v>7.35</v>
       </c>
-      <c r="L18" s="49" t="n">
+      <c r="L18" s="48" t="n">
         <v>-7.53</v>
       </c>
     </row>
@@ -7914,36 +7909,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C19" s="35" t="inlineStr">
+      <c r="C19" s="34" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
       </c>
-      <c r="D19" s="44" t="n">
+      <c r="D19" s="43" t="n">
         <v>86</v>
       </c>
-      <c r="E19" s="45" t="n">
+      <c r="E19" s="44" t="n">
         <v>-1</v>
       </c>
-      <c r="F19" s="44" t="n">
+      <c r="F19" s="43" t="n">
         <v>87</v>
       </c>
-      <c r="G19" s="45" t="n">
+      <c r="G19" s="44" t="n">
         <v>-130</v>
       </c>
-      <c r="H19" s="46" t="n">
+      <c r="H19" s="45" t="n">
         <v>56.9</v>
       </c>
-      <c r="I19" s="46" t="n">
+      <c r="I19" s="45" t="n">
         <v>499</v>
       </c>
-      <c r="J19" s="47" t="n">
+      <c r="J19" s="46" t="n">
         <v>74.90000000000001</v>
       </c>
-      <c r="K19" s="48" t="n">
+      <c r="K19" s="47" t="n">
         <v>4.32</v>
       </c>
-      <c r="L19" s="52" t="n">
+      <c r="L19" s="51" t="n">
         <v>-4.55</v>
       </c>
     </row>
@@ -7958,36 +7953,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C20" s="35" t="inlineStr">
+      <c r="C20" s="34" t="inlineStr">
         <is>
           <t>유통</t>
         </is>
       </c>
-      <c r="D20" s="44" t="n">
+      <c r="D20" s="43" t="n">
         <v>71</v>
       </c>
-      <c r="E20" s="44" t="n">
+      <c r="E20" s="43" t="n">
         <v>36</v>
       </c>
-      <c r="F20" s="44" t="n">
+      <c r="F20" s="43" t="n">
         <v>35</v>
       </c>
-      <c r="G20" s="45" t="n">
+      <c r="G20" s="44" t="n">
         <v>-66</v>
       </c>
-      <c r="H20" s="46" t="n">
+      <c r="H20" s="45" t="n">
         <v>61.9</v>
       </c>
-      <c r="I20" s="46" t="n">
+      <c r="I20" s="45" t="n">
         <v>715.3</v>
       </c>
-      <c r="J20" s="47" t="n">
+      <c r="J20" s="46" t="n">
         <v>79.5</v>
       </c>
-      <c r="K20" s="48" t="n">
+      <c r="K20" s="47" t="n">
         <v>10.78</v>
       </c>
-      <c r="L20" s="49" t="n">
+      <c r="L20" s="48" t="n">
         <v>-9.359999999999999</v>
       </c>
     </row>
@@ -8002,36 +7997,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C21" s="35" t="inlineStr">
+      <c r="C21" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="D21" s="44" t="n">
+      <c r="D21" s="43" t="n">
         <v>26</v>
       </c>
-      <c r="E21" s="45" t="n">
+      <c r="E21" s="44" t="n">
         <v>-10</v>
       </c>
-      <c r="F21" s="44" t="n">
+      <c r="F21" s="43" t="n">
         <v>36</v>
       </c>
-      <c r="G21" s="45" t="n">
+      <c r="G21" s="44" t="n">
         <v>-25</v>
       </c>
-      <c r="H21" s="46" t="n">
+      <c r="H21" s="45" t="n">
         <v>13.1</v>
       </c>
-      <c r="I21" s="46" t="n">
+      <c r="I21" s="45" t="n">
         <v>215.2</v>
       </c>
-      <c r="J21" s="47" t="n">
+      <c r="J21" s="46" t="n">
         <v>10.8</v>
       </c>
-      <c r="K21" s="48" t="n">
+      <c r="K21" s="47" t="n">
         <v>8.44</v>
       </c>
-      <c r="L21" s="49" t="n">
+      <c r="L21" s="48" t="n">
         <v>-6.44</v>
       </c>
     </row>
@@ -8046,36 +8041,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C22" s="35" t="inlineStr">
+      <c r="C22" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="D22" s="44" t="n">
+      <c r="D22" s="43" t="n">
         <v>114</v>
       </c>
-      <c r="E22" s="44" t="n">
+      <c r="E22" s="43" t="n">
         <v>21</v>
       </c>
-      <c r="F22" s="44" t="n">
+      <c r="F22" s="43" t="n">
         <v>93</v>
       </c>
-      <c r="G22" s="45" t="n">
+      <c r="G22" s="44" t="n">
         <v>-110</v>
       </c>
-      <c r="H22" s="46" t="n">
+      <c r="H22" s="45" t="n">
         <v>7.2</v>
       </c>
-      <c r="I22" s="46" t="n">
+      <c r="I22" s="45" t="n">
         <v>39.4</v>
       </c>
-      <c r="J22" s="47" t="n">
+      <c r="J22" s="46" t="n">
         <v>5.8</v>
       </c>
-      <c r="K22" s="48" t="n">
+      <c r="K22" s="47" t="n">
         <v>25.06</v>
       </c>
-      <c r="L22" s="52" t="n">
+      <c r="L22" s="51" t="n">
         <v>-2.71</v>
       </c>
     </row>
@@ -8153,7 +8148,7 @@
           <t>F1 외국인</t>
         </is>
       </c>
-      <c r="E3" s="54" t="inlineStr">
+      <c r="E3" s="53" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
@@ -8163,111 +8158,111 @@
           <t>F2 기관계</t>
         </is>
       </c>
-      <c r="N3" s="54" t="inlineStr">
+      <c r="N3" s="53" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="55" t="inlineStr">
+      <c r="A4" s="54" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="E4" s="56" t="inlineStr">
+      <c r="E4" s="55" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="J4" s="55" t="inlineStr">
+      <c r="J4" s="54" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="N4" s="56" t="inlineStr">
+      <c r="N4" s="55" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="43" t="inlineStr">
+      <c r="A5" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B5" s="43" t="inlineStr">
+      <c r="B5" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C5" s="43" t="inlineStr">
+      <c r="C5" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D5" s="43" t="inlineStr">
+      <c r="D5" s="42" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E5" s="43" t="inlineStr">
+      <c r="E5" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F5" s="43" t="inlineStr">
+      <c r="F5" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G5" s="43" t="inlineStr">
+      <c r="G5" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H5" s="43" t="inlineStr">
+      <c r="H5" s="42" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="J5" s="43" t="inlineStr">
+      <c r="J5" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="K5" s="43" t="inlineStr">
+      <c r="K5" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="L5" s="43" t="inlineStr">
+      <c r="L5" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="M5" s="43" t="inlineStr">
+      <c r="M5" s="42" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="N5" s="43" t="inlineStr">
+      <c r="N5" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O5" s="43" t="inlineStr">
+      <c r="O5" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P5" s="43" t="inlineStr">
+      <c r="P5" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q5" s="43" t="inlineStr">
+      <c r="Q5" s="42" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -8282,12 +8277,12 @@
           <t>삼성E&amp;A</t>
         </is>
       </c>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="C6" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="D6" s="45" t="n">
+      <c r="D6" s="44" t="n">
         <v>3096</v>
       </c>
       <c r="E6" s="30" t="n">
@@ -8298,12 +8293,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="G6" s="35" t="inlineStr">
+      <c r="G6" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H6" s="57" t="n">
+      <c r="H6" s="56" t="n">
         <v>-97751</v>
       </c>
       <c r="J6" s="30" t="n">
@@ -8314,12 +8309,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="L6" s="35" t="inlineStr">
+      <c r="L6" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="M6" s="45" t="n">
+      <c r="M6" s="44" t="n">
         <v>7111</v>
       </c>
       <c r="N6" s="30" t="n">
@@ -8330,12 +8325,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="P6" s="35" t="inlineStr">
+      <c r="P6" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q6" s="57" t="n">
+      <c r="Q6" s="56" t="n">
         <v>-6142</v>
       </c>
     </row>
@@ -8348,12 +8343,12 @@
           <t>이수페타시스</t>
         </is>
       </c>
-      <c r="C7" s="35" t="inlineStr">
+      <c r="C7" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D7" s="45" t="n">
+      <c r="D7" s="44" t="n">
         <v>1579</v>
       </c>
       <c r="E7" s="30" t="n">
@@ -8364,12 +8359,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="G7" s="35" t="inlineStr">
+      <c r="G7" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H7" s="57" t="n">
+      <c r="H7" s="56" t="n">
         <v>-35922</v>
       </c>
       <c r="J7" s="30" t="n">
@@ -8380,12 +8375,12 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="L7" s="35" t="inlineStr">
+      <c r="L7" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M7" s="45" t="n">
+      <c r="M7" s="44" t="n">
         <v>5633</v>
       </c>
       <c r="N7" s="30" t="n">
@@ -8396,12 +8391,12 @@
           <t>이수페타시스</t>
         </is>
       </c>
-      <c r="P7" s="35" t="inlineStr">
+      <c r="P7" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q7" s="57" t="n">
+      <c r="Q7" s="56" t="n">
         <v>-1763</v>
       </c>
     </row>
@@ -8414,12 +8409,12 @@
           <t>S-Oil</t>
         </is>
       </c>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="C8" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D8" s="45" t="n">
+      <c r="D8" s="44" t="n">
         <v>1337</v>
       </c>
       <c r="E8" s="30" t="n">
@@ -8430,12 +8425,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="G8" s="35" t="inlineStr">
+      <c r="G8" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="H8" s="57" t="n">
+      <c r="H8" s="56" t="n">
         <v>-10110</v>
       </c>
       <c r="J8" s="30" t="n">
@@ -8446,12 +8441,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="L8" s="35" t="inlineStr">
+      <c r="L8" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M8" s="45" t="n">
+      <c r="M8" s="44" t="n">
         <v>4348</v>
       </c>
       <c r="N8" s="30" t="n">
@@ -8462,12 +8457,12 @@
           <t>현대건설</t>
         </is>
       </c>
-      <c r="P8" s="35" t="inlineStr">
+      <c r="P8" s="34" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
       </c>
-      <c r="Q8" s="57" t="n">
+      <c r="Q8" s="56" t="n">
         <v>-1650</v>
       </c>
     </row>
@@ -8480,12 +8475,12 @@
           <t>현대건설</t>
         </is>
       </c>
-      <c r="C9" s="35" t="inlineStr">
+      <c r="C9" s="34" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
       </c>
-      <c r="D9" s="45" t="n">
+      <c r="D9" s="44" t="n">
         <v>1267</v>
       </c>
       <c r="E9" s="30" t="n">
@@ -8496,12 +8491,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="G9" s="35" t="inlineStr">
+      <c r="G9" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H9" s="57" t="n">
+      <c r="H9" s="56" t="n">
         <v>-5245</v>
       </c>
       <c r="J9" s="30" t="n">
@@ -8512,12 +8507,12 @@
           <t>삼성바이오로직스</t>
         </is>
       </c>
-      <c r="L9" s="35" t="inlineStr">
+      <c r="L9" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="M9" s="45" t="n">
+      <c r="M9" s="44" t="n">
         <v>3002</v>
       </c>
       <c r="N9" s="30" t="n">
@@ -8528,12 +8523,12 @@
           <t>HD현대중공업</t>
         </is>
       </c>
-      <c r="P9" s="58" t="inlineStr">
+      <c r="P9" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q9" s="57" t="n">
+      <c r="Q9" s="56" t="n">
         <v>-1485</v>
       </c>
     </row>
@@ -8546,12 +8541,12 @@
           <t>HD현대중공업</t>
         </is>
       </c>
-      <c r="C10" s="58" t="inlineStr">
+      <c r="C10" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="D10" s="45" t="n">
+      <c r="D10" s="44" t="n">
         <v>1243</v>
       </c>
       <c r="E10" s="30" t="n">
@@ -8562,12 +8557,12 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="G10" s="35" t="inlineStr">
+      <c r="G10" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H10" s="57" t="n">
+      <c r="H10" s="56" t="n">
         <v>-4581</v>
       </c>
       <c r="J10" s="30" t="n">
@@ -8578,12 +8573,12 @@
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="L10" s="35" t="inlineStr">
+      <c r="L10" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="M10" s="45" t="n">
+      <c r="M10" s="44" t="n">
         <v>2741</v>
       </c>
       <c r="N10" s="30" t="n">
@@ -8594,12 +8589,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="P10" s="35" t="inlineStr">
+      <c r="P10" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q10" s="57" t="n">
+      <c r="Q10" s="56" t="n">
         <v>-1351</v>
       </c>
     </row>
@@ -8612,12 +8607,12 @@
           <t>알테오젠</t>
         </is>
       </c>
-      <c r="C11" s="35" t="inlineStr">
+      <c r="C11" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="D11" s="45" t="n">
+      <c r="D11" s="44" t="n">
         <v>1158</v>
       </c>
       <c r="E11" s="30" t="n">
@@ -8628,12 +8623,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="G11" s="35" t="inlineStr">
+      <c r="G11" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H11" s="57" t="n">
+      <c r="H11" s="56" t="n">
         <v>-4277</v>
       </c>
       <c r="J11" s="30" t="n">
@@ -8644,12 +8639,12 @@
           <t>삼성생명</t>
         </is>
       </c>
-      <c r="L11" s="35" t="inlineStr">
+      <c r="L11" s="34" t="inlineStr">
         <is>
           <t>보험</t>
         </is>
       </c>
-      <c r="M11" s="45" t="n">
+      <c r="M11" s="44" t="n">
         <v>2446</v>
       </c>
       <c r="N11" s="30" t="n">
@@ -8660,12 +8655,12 @@
           <t>S-Oil</t>
         </is>
       </c>
-      <c r="P11" s="35" t="inlineStr">
+      <c r="P11" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="Q11" s="57" t="n">
+      <c r="Q11" s="56" t="n">
         <v>-1323</v>
       </c>
     </row>
@@ -8678,12 +8673,12 @@
           <t>HMM</t>
         </is>
       </c>
-      <c r="C12" s="35" t="inlineStr">
+      <c r="C12" s="34" t="inlineStr">
         <is>
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="D12" s="45" t="n">
+      <c r="D12" s="44" t="n">
         <v>1103</v>
       </c>
       <c r="E12" s="30" t="n">
@@ -8694,12 +8689,12 @@
           <t>효성중공업</t>
         </is>
       </c>
-      <c r="G12" s="35" t="inlineStr">
+      <c r="G12" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H12" s="57" t="n">
+      <c r="H12" s="56" t="n">
         <v>-3793</v>
       </c>
       <c r="J12" s="30" t="n">
@@ -8710,12 +8705,12 @@
           <t>KB금융</t>
         </is>
       </c>
-      <c r="L12" s="35" t="inlineStr">
+      <c r="L12" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="M12" s="45" t="n">
+      <c r="M12" s="44" t="n">
         <v>2337</v>
       </c>
       <c r="N12" s="30" t="n">
@@ -8726,12 +8721,12 @@
           <t>두산</t>
         </is>
       </c>
-      <c r="P12" s="35" t="inlineStr">
+      <c r="P12" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q12" s="57" t="n">
+      <c r="Q12" s="56" t="n">
         <v>-1290</v>
       </c>
     </row>
@@ -8744,12 +8739,12 @@
           <t>DB하이텍</t>
         </is>
       </c>
-      <c r="C13" s="35" t="inlineStr">
+      <c r="C13" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D13" s="45" t="n">
+      <c r="D13" s="44" t="n">
         <v>938</v>
       </c>
       <c r="E13" s="30" t="n">
@@ -8760,12 +8755,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="G13" s="35" t="inlineStr">
+      <c r="G13" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H13" s="57" t="n">
+      <c r="H13" s="56" t="n">
         <v>-3525</v>
       </c>
       <c r="J13" s="30" t="n">
@@ -8776,12 +8771,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="L13" s="35" t="inlineStr">
+      <c r="L13" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="M13" s="45" t="n">
+      <c r="M13" s="44" t="n">
         <v>2184</v>
       </c>
       <c r="N13" s="30" t="n">
@@ -8792,12 +8787,12 @@
           <t>심텍</t>
         </is>
       </c>
-      <c r="P13" s="35" t="inlineStr">
+      <c r="P13" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q13" s="57" t="n">
+      <c r="Q13" s="56" t="n">
         <v>-1288</v>
       </c>
     </row>
@@ -8810,12 +8805,12 @@
           <t>파마리서치</t>
         </is>
       </c>
-      <c r="C14" s="35" t="inlineStr">
+      <c r="C14" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="D14" s="45" t="n">
+      <c r="D14" s="44" t="n">
         <v>873</v>
       </c>
       <c r="E14" s="30" t="n">
@@ -8826,12 +8821,12 @@
           <t>대덕전자</t>
         </is>
       </c>
-      <c r="G14" s="35" t="inlineStr">
+      <c r="G14" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H14" s="57" t="n">
+      <c r="H14" s="56" t="n">
         <v>-2628</v>
       </c>
       <c r="J14" s="30" t="n">
@@ -8842,12 +8837,12 @@
           <t>현대모비스</t>
         </is>
       </c>
-      <c r="L14" s="58" t="inlineStr">
+      <c r="L14" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="M14" s="45" t="n">
+      <c r="M14" s="44" t="n">
         <v>2148</v>
       </c>
       <c r="N14" s="30" t="n">
@@ -8858,12 +8853,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="P14" s="35" t="inlineStr">
+      <c r="P14" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q14" s="57" t="n">
+      <c r="Q14" s="56" t="n">
         <v>-1142</v>
       </c>
     </row>
@@ -8876,12 +8871,12 @@
           <t>GS</t>
         </is>
       </c>
-      <c r="C15" s="35" t="inlineStr">
+      <c r="C15" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D15" s="45" t="n">
+      <c r="D15" s="44" t="n">
         <v>833</v>
       </c>
       <c r="E15" s="30" t="n">
@@ -8892,12 +8887,12 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="G15" s="35" t="inlineStr">
+      <c r="G15" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H15" s="57" t="n">
+      <c r="H15" s="56" t="n">
         <v>-2517</v>
       </c>
       <c r="J15" s="30" t="n">
@@ -8908,12 +8903,12 @@
           <t>한화시스템</t>
         </is>
       </c>
-      <c r="L15" s="35" t="inlineStr">
+      <c r="L15" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M15" s="45" t="n">
+      <c r="M15" s="44" t="n">
         <v>1794</v>
       </c>
       <c r="N15" s="30" t="n">
@@ -8924,12 +8919,12 @@
           <t>HD건설기계</t>
         </is>
       </c>
-      <c r="P15" s="35" t="inlineStr">
+      <c r="P15" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q15" s="57" t="n">
+      <c r="Q15" s="56" t="n">
         <v>-1140</v>
       </c>
     </row>
@@ -8940,7 +8935,7 @@
           <t>F3 외인+기관</t>
         </is>
       </c>
-      <c r="E17" s="54" t="inlineStr">
+      <c r="E17" s="53" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
@@ -8950,111 +8945,111 @@
           <t>F4 개인</t>
         </is>
       </c>
-      <c r="N17" s="54" t="inlineStr">
+      <c r="N17" s="53" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="55" t="inlineStr">
+      <c r="A18" s="54" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="E18" s="56" t="inlineStr">
+      <c r="E18" s="55" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="J18" s="55" t="inlineStr">
+      <c r="J18" s="54" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="N18" s="56" t="inlineStr">
+      <c r="N18" s="55" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="43" t="inlineStr">
+      <c r="A19" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B19" s="43" t="inlineStr">
+      <c r="B19" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C19" s="43" t="inlineStr">
+      <c r="C19" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D19" s="43" t="inlineStr">
+      <c r="D19" s="42" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E19" s="43" t="inlineStr">
+      <c r="E19" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F19" s="43" t="inlineStr">
+      <c r="F19" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G19" s="43" t="inlineStr">
+      <c r="G19" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H19" s="43" t="inlineStr">
+      <c r="H19" s="42" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="J19" s="43" t="inlineStr">
+      <c r="J19" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="K19" s="43" t="inlineStr">
+      <c r="K19" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="L19" s="43" t="inlineStr">
+      <c r="L19" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="M19" s="43" t="inlineStr">
+      <c r="M19" s="42" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="N19" s="43" t="inlineStr">
+      <c r="N19" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O19" s="43" t="inlineStr">
+      <c r="O19" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P19" s="43" t="inlineStr">
+      <c r="P19" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q19" s="43" t="inlineStr">
+      <c r="Q19" s="42" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -9069,12 +9064,12 @@
           <t>삼성E&amp;A</t>
         </is>
       </c>
-      <c r="C20" s="35" t="inlineStr">
+      <c r="C20" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="D20" s="45" t="n">
+      <c r="D20" s="44" t="n">
         <v>4081</v>
       </c>
       <c r="E20" s="30" t="n">
@@ -9085,12 +9080,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="G20" s="35" t="inlineStr">
+      <c r="G20" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H20" s="57" t="n">
+      <c r="H20" s="56" t="n">
         <v>-97913</v>
       </c>
       <c r="J20" s="30" t="n">
@@ -9101,12 +9096,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="L20" s="35" t="inlineStr">
+      <c r="L20" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M20" s="45" t="n">
+      <c r="M20" s="44" t="n">
         <v>29529</v>
       </c>
       <c r="N20" s="30" t="n">
@@ -9117,12 +9112,12 @@
           <t>삼성E&amp;A</t>
         </is>
       </c>
-      <c r="P20" s="35" t="inlineStr">
+      <c r="P20" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="Q20" s="57" t="n">
+      <c r="Q20" s="56" t="n">
         <v>-4828</v>
       </c>
     </row>
@@ -9135,12 +9130,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="C21" s="35" t="inlineStr">
+      <c r="C21" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D21" s="45" t="n">
+      <c r="D21" s="44" t="n">
         <v>3174</v>
       </c>
       <c r="E21" s="30" t="n">
@@ -9151,12 +9146,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="G21" s="35" t="inlineStr">
+      <c r="G21" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H21" s="57" t="n">
+      <c r="H21" s="56" t="n">
         <v>-42064</v>
       </c>
       <c r="J21" s="30" t="n">
@@ -9167,12 +9162,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="L21" s="35" t="inlineStr">
+      <c r="L21" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M21" s="45" t="n">
+      <c r="M21" s="44" t="n">
         <v>6002</v>
       </c>
       <c r="N21" s="30" t="n">
@@ -9183,12 +9178,12 @@
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="P21" s="35" t="inlineStr">
+      <c r="P21" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="Q21" s="57" t="n">
+      <c r="Q21" s="56" t="n">
         <v>-3479</v>
       </c>
     </row>
@@ -9201,12 +9196,12 @@
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="C22" s="35" t="inlineStr">
+      <c r="C22" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="D22" s="45" t="n">
+      <c r="D22" s="44" t="n">
         <v>2690</v>
       </c>
       <c r="E22" s="30" t="n">
@@ -9217,12 +9212,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="G22" s="35" t="inlineStr">
+      <c r="G22" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H22" s="57" t="n">
+      <c r="H22" s="56" t="n">
         <v>-6596</v>
       </c>
       <c r="J22" s="30" t="n">
@@ -9233,12 +9228,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="L22" s="35" t="inlineStr">
+      <c r="L22" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M22" s="45" t="n">
+      <c r="M22" s="44" t="n">
         <v>4981</v>
       </c>
       <c r="N22" s="30" t="n">
@@ -9249,12 +9244,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="P22" s="35" t="inlineStr">
+      <c r="P22" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q22" s="57" t="n">
+      <c r="Q22" s="56" t="n">
         <v>-3149</v>
       </c>
     </row>
@@ -9267,12 +9262,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="C23" s="35" t="inlineStr">
+      <c r="C23" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D23" s="45" t="n">
+      <c r="D23" s="44" t="n">
         <v>2315</v>
       </c>
       <c r="E23" s="30" t="n">
@@ -9283,12 +9278,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="G23" s="35" t="inlineStr">
+      <c r="G23" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H23" s="57" t="n">
+      <c r="H23" s="56" t="n">
         <v>-5290</v>
       </c>
       <c r="J23" s="30" t="n">
@@ -9299,12 +9294,12 @@
           <t>효성중공업</t>
         </is>
       </c>
-      <c r="L23" s="35" t="inlineStr">
+      <c r="L23" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M23" s="45" t="n">
+      <c r="M23" s="44" t="n">
         <v>4690</v>
       </c>
       <c r="N23" s="30" t="n">
@@ -9315,12 +9310,12 @@
           <t>LG씨엔에스</t>
         </is>
       </c>
-      <c r="P23" s="35" t="inlineStr">
+      <c r="P23" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="Q23" s="57" t="n">
+      <c r="Q23" s="56" t="n">
         <v>-1939</v>
       </c>
     </row>
@@ -9333,12 +9328,12 @@
           <t>LG씨엔에스</t>
         </is>
       </c>
-      <c r="C24" s="35" t="inlineStr">
+      <c r="C24" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="D24" s="45" t="n">
+      <c r="D24" s="44" t="n">
         <v>1964</v>
       </c>
       <c r="E24" s="30" t="n">
@@ -9349,12 +9344,12 @@
           <t>효성중공업</t>
         </is>
       </c>
-      <c r="G24" s="35" t="inlineStr">
+      <c r="G24" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H24" s="57" t="n">
+      <c r="H24" s="56" t="n">
         <v>-4708</v>
       </c>
       <c r="J24" s="30" t="n">
@@ -9365,12 +9360,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="L24" s="35" t="inlineStr">
+      <c r="L24" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M24" s="45" t="n">
+      <c r="M24" s="44" t="n">
         <v>4618</v>
       </c>
       <c r="N24" s="30" t="n">
@@ -9381,12 +9376,12 @@
           <t>HMM</t>
         </is>
       </c>
-      <c r="P24" s="35" t="inlineStr">
+      <c r="P24" s="34" t="inlineStr">
         <is>
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="Q24" s="57" t="n">
+      <c r="Q24" s="56" t="n">
         <v>-1861</v>
       </c>
     </row>
@@ -9399,12 +9394,12 @@
           <t>HMM</t>
         </is>
       </c>
-      <c r="C25" s="35" t="inlineStr">
+      <c r="C25" s="34" t="inlineStr">
         <is>
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="D25" s="45" t="n">
+      <c r="D25" s="44" t="n">
         <v>1875</v>
       </c>
       <c r="E25" s="30" t="n">
@@ -9415,12 +9410,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="G25" s="35" t="inlineStr">
+      <c r="G25" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H25" s="57" t="n">
+      <c r="H25" s="56" t="n">
         <v>-4667</v>
       </c>
       <c r="J25" s="30" t="n">
@@ -9431,12 +9426,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="L25" s="35" t="inlineStr">
+      <c r="L25" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="M25" s="45" t="n">
+      <c r="M25" s="44" t="n">
         <v>2980</v>
       </c>
       <c r="N25" s="30" t="n">
@@ -9447,12 +9442,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="P25" s="35" t="inlineStr">
+      <c r="P25" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="Q25" s="57" t="n">
+      <c r="Q25" s="56" t="n">
         <v>-1816</v>
       </c>
     </row>
@@ -9465,12 +9460,12 @@
           <t>알테오젠</t>
         </is>
       </c>
-      <c r="C26" s="35" t="inlineStr">
+      <c r="C26" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="D26" s="45" t="n">
+      <c r="D26" s="44" t="n">
         <v>1567</v>
       </c>
       <c r="E26" s="30" t="n">
@@ -9481,12 +9476,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="G26" s="35" t="inlineStr">
+      <c r="G26" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="H26" s="57" t="n">
+      <c r="H26" s="56" t="n">
         <v>-2999</v>
       </c>
       <c r="J26" s="30" t="n">
@@ -9497,12 +9492,12 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="L26" s="35" t="inlineStr">
+      <c r="L26" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M26" s="45" t="n">
+      <c r="M26" s="44" t="n">
         <v>2537</v>
       </c>
       <c r="N26" s="30" t="n">
@@ -9513,12 +9508,12 @@
           <t>알테오젠</t>
         </is>
       </c>
-      <c r="P26" s="35" t="inlineStr">
+      <c r="P26" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="Q26" s="57" t="n">
+      <c r="Q26" s="56" t="n">
         <v>-1552</v>
       </c>
     </row>
@@ -9531,12 +9526,12 @@
           <t>하이브</t>
         </is>
       </c>
-      <c r="C27" s="35" t="inlineStr">
+      <c r="C27" s="34" t="inlineStr">
         <is>
           <t>오락·문화</t>
         </is>
       </c>
-      <c r="D27" s="45" t="n">
+      <c r="D27" s="44" t="n">
         <v>1130</v>
       </c>
       <c r="E27" s="30" t="n">
@@ -9547,12 +9542,12 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="G27" s="35" t="inlineStr">
+      <c r="G27" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H27" s="57" t="n">
+      <c r="H27" s="56" t="n">
         <v>-2581</v>
       </c>
       <c r="J27" s="30" t="n">
@@ -9563,12 +9558,12 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="L27" s="35" t="inlineStr">
+      <c r="L27" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="M27" s="45" t="n">
+      <c r="M27" s="44" t="n">
         <v>1739</v>
       </c>
       <c r="N27" s="30" t="n">
@@ -9579,12 +9574,12 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="P27" s="35" t="inlineStr">
+      <c r="P27" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q27" s="57" t="n">
+      <c r="Q27" s="56" t="n">
         <v>-1175</v>
       </c>
     </row>
@@ -9597,12 +9592,12 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="C28" s="35" t="inlineStr">
+      <c r="C28" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D28" s="45" t="n">
+      <c r="D28" s="44" t="n">
         <v>1052</v>
       </c>
       <c r="E28" s="30" t="n">
@@ -9613,12 +9608,12 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="G28" s="35" t="inlineStr">
+      <c r="G28" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="H28" s="57" t="n">
+      <c r="H28" s="56" t="n">
         <v>-1728</v>
       </c>
       <c r="J28" s="30" t="n">
@@ -9629,12 +9624,12 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="L28" s="58" t="inlineStr">
+      <c r="L28" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="M28" s="45" t="n">
+      <c r="M28" s="44" t="n">
         <v>1732</v>
       </c>
       <c r="N28" s="30" t="n">
@@ -9645,12 +9640,12 @@
           <t>하이브</t>
         </is>
       </c>
-      <c r="P28" s="35" t="inlineStr">
+      <c r="P28" s="34" t="inlineStr">
         <is>
           <t>오락·문화</t>
         </is>
       </c>
-      <c r="Q28" s="57" t="n">
+      <c r="Q28" s="56" t="n">
         <v>-1174</v>
       </c>
     </row>
@@ -9663,12 +9658,12 @@
           <t>삼성물산</t>
         </is>
       </c>
-      <c r="C29" s="35" t="inlineStr">
+      <c r="C29" s="34" t="inlineStr">
         <is>
           <t>유통</t>
         </is>
       </c>
-      <c r="D29" s="45" t="n">
+      <c r="D29" s="44" t="n">
         <v>914</v>
       </c>
       <c r="E29" s="30" t="n">
@@ -9679,12 +9674,12 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="G29" s="58" t="inlineStr">
+      <c r="G29" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H29" s="57" t="n">
+      <c r="H29" s="56" t="n">
         <v>-1712</v>
       </c>
       <c r="J29" s="30" t="n">
@@ -9695,12 +9690,12 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="L29" s="35" t="inlineStr">
+      <c r="L29" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M29" s="45" t="n">
+      <c r="M29" s="44" t="n">
         <v>1627</v>
       </c>
       <c r="N29" s="30" t="n">
@@ -9711,12 +9706,12 @@
           <t>삼성물산</t>
         </is>
       </c>
-      <c r="P29" s="35" t="inlineStr">
+      <c r="P29" s="34" t="inlineStr">
         <is>
           <t>유통</t>
         </is>
       </c>
-      <c r="Q29" s="57" t="n">
+      <c r="Q29" s="56" t="n">
         <v>-885</v>
       </c>
     </row>
@@ -9727,7 +9722,7 @@
           <t>F5 금융투자</t>
         </is>
       </c>
-      <c r="E31" s="54" t="inlineStr">
+      <c r="E31" s="53" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
@@ -9737,111 +9732,111 @@
           <t>F6 투신(사모)</t>
         </is>
       </c>
-      <c r="N31" s="54" t="inlineStr">
+      <c r="N31" s="53" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="55" t="inlineStr">
+      <c r="A32" s="54" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="E32" s="56" t="inlineStr">
+      <c r="E32" s="55" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="J32" s="55" t="inlineStr">
+      <c r="J32" s="54" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="N32" s="56" t="inlineStr">
+      <c r="N32" s="55" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="43" t="inlineStr">
+      <c r="A33" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B33" s="43" t="inlineStr">
+      <c r="B33" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C33" s="43" t="inlineStr">
+      <c r="C33" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D33" s="43" t="inlineStr">
+      <c r="D33" s="42" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E33" s="43" t="inlineStr">
+      <c r="E33" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F33" s="43" t="inlineStr">
+      <c r="F33" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G33" s="43" t="inlineStr">
+      <c r="G33" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H33" s="43" t="inlineStr">
+      <c r="H33" s="42" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="J33" s="43" t="inlineStr">
+      <c r="J33" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="K33" s="43" t="inlineStr">
+      <c r="K33" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="L33" s="43" t="inlineStr">
+      <c r="L33" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="M33" s="43" t="inlineStr">
+      <c r="M33" s="42" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="N33" s="43" t="inlineStr">
+      <c r="N33" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O33" s="43" t="inlineStr">
+      <c r="O33" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P33" s="43" t="inlineStr">
+      <c r="P33" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q33" s="43" t="inlineStr">
+      <c r="Q33" s="42" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -9856,12 +9851,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="C34" s="35" t="inlineStr">
+      <c r="C34" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D34" s="45" t="n">
+      <c r="D34" s="44" t="n">
         <v>3296</v>
       </c>
       <c r="E34" s="30" t="n">
@@ -9872,12 +9867,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="G34" s="35" t="inlineStr">
+      <c r="G34" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H34" s="57" t="n">
+      <c r="H34" s="56" t="n">
         <v>-1357</v>
       </c>
       <c r="J34" s="30" t="n">
@@ -9888,12 +9883,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="L34" s="35" t="inlineStr">
+      <c r="L34" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="M34" s="45" t="n">
+      <c r="M34" s="44" t="n">
         <v>5943</v>
       </c>
       <c r="N34" s="30" t="n">
@@ -9904,12 +9899,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="P34" s="35" t="inlineStr">
+      <c r="P34" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q34" s="57" t="n">
+      <c r="Q34" s="56" t="n">
         <v>-18725</v>
       </c>
     </row>
@@ -9922,12 +9917,12 @@
           <t>KB금융</t>
         </is>
       </c>
-      <c r="C35" s="35" t="inlineStr">
+      <c r="C35" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D35" s="45" t="n">
+      <c r="D35" s="44" t="n">
         <v>2704</v>
       </c>
       <c r="E35" s="30" t="n">
@@ -9938,12 +9933,12 @@
           <t>삼성바이오로직스</t>
         </is>
       </c>
-      <c r="G35" s="35" t="inlineStr">
+      <c r="G35" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="H35" s="57" t="n">
+      <c r="H35" s="56" t="n">
         <v>-660</v>
       </c>
       <c r="J35" s="30" t="n">
@@ -9954,12 +9949,12 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="L35" s="35" t="inlineStr">
+      <c r="L35" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M35" s="45" t="n">
+      <c r="M35" s="44" t="n">
         <v>3574</v>
       </c>
       <c r="N35" s="30" t="n">
@@ -9970,12 +9965,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="P35" s="35" t="inlineStr">
+      <c r="P35" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q35" s="57" t="n">
+      <c r="Q35" s="56" t="n">
         <v>-3651</v>
       </c>
     </row>
@@ -9988,12 +9983,12 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="C36" s="35" t="inlineStr">
+      <c r="C36" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D36" s="45" t="n">
+      <c r="D36" s="44" t="n">
         <v>1767</v>
       </c>
       <c r="E36" s="30" t="n">
@@ -10004,12 +9999,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="G36" s="35" t="inlineStr">
+      <c r="G36" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H36" s="57" t="n">
+      <c r="H36" s="56" t="n">
         <v>-409</v>
       </c>
       <c r="J36" s="30" t="n">
@@ -10020,12 +10015,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="L36" s="35" t="inlineStr">
+      <c r="L36" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M36" s="45" t="n">
+      <c r="M36" s="44" t="n">
         <v>1833</v>
       </c>
       <c r="N36" s="30" t="n">
@@ -10036,12 +10031,12 @@
           <t>이수페타시스</t>
         </is>
       </c>
-      <c r="P36" s="35" t="inlineStr">
+      <c r="P36" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q36" s="57" t="n">
+      <c r="Q36" s="56" t="n">
         <v>-1840</v>
       </c>
     </row>
@@ -10054,12 +10049,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="C37" s="35" t="inlineStr">
+      <c r="C37" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D37" s="45" t="n">
+      <c r="D37" s="44" t="n">
         <v>1151</v>
       </c>
       <c r="E37" s="30" t="n">
@@ -10070,12 +10065,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="G37" s="35" t="inlineStr">
+      <c r="G37" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H37" s="57" t="n">
+      <c r="H37" s="56" t="n">
         <v>-392</v>
       </c>
       <c r="J37" s="30" t="n">
@@ -10086,12 +10081,12 @@
           <t>SK</t>
         </is>
       </c>
-      <c r="L37" s="35" t="inlineStr">
+      <c r="L37" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="M37" s="45" t="n">
+      <c r="M37" s="44" t="n">
         <v>1557</v>
       </c>
       <c r="N37" s="30" t="n">
@@ -10102,12 +10097,12 @@
           <t>주성엔지니어링</t>
         </is>
       </c>
-      <c r="P37" s="35" t="inlineStr">
+      <c r="P37" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q37" s="57" t="n">
+      <c r="Q37" s="56" t="n">
         <v>-1705</v>
       </c>
     </row>
@@ -10120,12 +10115,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="C38" s="35" t="inlineStr">
+      <c r="C38" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D38" s="45" t="n">
+      <c r="D38" s="44" t="n">
         <v>1025</v>
       </c>
       <c r="E38" s="30" t="n">
@@ -10136,12 +10131,12 @@
           <t>SK</t>
         </is>
       </c>
-      <c r="G38" s="35" t="inlineStr">
+      <c r="G38" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="H38" s="57" t="n">
+      <c r="H38" s="56" t="n">
         <v>-337</v>
       </c>
       <c r="J38" s="30" t="n">
@@ -10152,12 +10147,12 @@
           <t>현대모비스</t>
         </is>
       </c>
-      <c r="L38" s="58" t="inlineStr">
+      <c r="L38" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="M38" s="45" t="n">
+      <c r="M38" s="44" t="n">
         <v>1135</v>
       </c>
       <c r="N38" s="30" t="n">
@@ -10168,12 +10163,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="P38" s="35" t="inlineStr">
+      <c r="P38" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q38" s="57" t="n">
+      <c r="Q38" s="56" t="n">
         <v>-1327</v>
       </c>
     </row>
@@ -10186,12 +10181,12 @@
           <t>주성엔지니어링</t>
         </is>
       </c>
-      <c r="C39" s="35" t="inlineStr">
+      <c r="C39" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D39" s="45" t="n">
+      <c r="D39" s="44" t="n">
         <v>833</v>
       </c>
       <c r="E39" s="30" t="n">
@@ -10202,12 +10197,12 @@
           <t>대한항공</t>
         </is>
       </c>
-      <c r="G39" s="35" t="inlineStr">
+      <c r="G39" s="34" t="inlineStr">
         <is>
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="H39" s="57" t="n">
+      <c r="H39" s="56" t="n">
         <v>-209</v>
       </c>
       <c r="J39" s="30" t="n">
@@ -10218,12 +10213,12 @@
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="L39" s="35" t="inlineStr">
+      <c r="L39" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="M39" s="45" t="n">
+      <c r="M39" s="44" t="n">
         <v>939</v>
       </c>
       <c r="N39" s="30" t="n">
@@ -10234,12 +10229,12 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="P39" s="35" t="inlineStr">
+      <c r="P39" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q39" s="57" t="n">
+      <c r="Q39" s="56" t="n">
         <v>-1321</v>
       </c>
     </row>
@@ -10252,12 +10247,12 @@
           <t>LG화학</t>
         </is>
       </c>
-      <c r="C40" s="35" t="inlineStr">
+      <c r="C40" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D40" s="45" t="n">
+      <c r="D40" s="44" t="n">
         <v>819</v>
       </c>
       <c r="E40" s="30" t="n">
@@ -10268,12 +10263,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="G40" s="35" t="inlineStr">
+      <c r="G40" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="H40" s="57" t="n">
+      <c r="H40" s="56" t="n">
         <v>-205</v>
       </c>
       <c r="J40" s="30" t="n">
@@ -10284,12 +10279,12 @@
           <t>삼성바이오로직스</t>
         </is>
       </c>
-      <c r="L40" s="35" t="inlineStr">
+      <c r="L40" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="M40" s="45" t="n">
+      <c r="M40" s="44" t="n">
         <v>928</v>
       </c>
       <c r="N40" s="30" t="n">
@@ -10300,12 +10295,12 @@
           <t>원익IPS</t>
         </is>
       </c>
-      <c r="P40" s="35" t="inlineStr">
+      <c r="P40" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q40" s="57" t="n">
+      <c r="Q40" s="56" t="n">
         <v>-1189</v>
       </c>
     </row>
@@ -10318,12 +10313,12 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="C41" s="35" t="inlineStr">
+      <c r="C41" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="D41" s="45" t="n">
+      <c r="D41" s="44" t="n">
         <v>765</v>
       </c>
       <c r="E41" s="30" t="n">
@@ -10334,12 +10329,12 @@
           <t>HD건설기계</t>
         </is>
       </c>
-      <c r="G41" s="35" t="inlineStr">
+      <c r="G41" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H41" s="57" t="n">
+      <c r="H41" s="56" t="n">
         <v>-181</v>
       </c>
       <c r="J41" s="30" t="n">
@@ -10350,12 +10345,12 @@
           <t>한화시스템</t>
         </is>
       </c>
-      <c r="L41" s="35" t="inlineStr">
+      <c r="L41" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M41" s="45" t="n">
+      <c r="M41" s="44" t="n">
         <v>885</v>
       </c>
       <c r="N41" s="30" t="n">
@@ -10366,12 +10361,12 @@
           <t>테스</t>
         </is>
       </c>
-      <c r="P41" s="35" t="inlineStr">
+      <c r="P41" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q41" s="57" t="n">
+      <c r="Q41" s="56" t="n">
         <v>-914</v>
       </c>
     </row>
@@ -10384,12 +10379,12 @@
           <t>HPSP</t>
         </is>
       </c>
-      <c r="C42" s="35" t="inlineStr">
+      <c r="C42" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D42" s="45" t="n">
+      <c r="D42" s="44" t="n">
         <v>719</v>
       </c>
       <c r="E42" s="30" t="n">
@@ -10400,12 +10395,12 @@
           <t>엘앤에프</t>
         </is>
       </c>
-      <c r="G42" s="35" t="inlineStr">
+      <c r="G42" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H42" s="57" t="n">
+      <c r="H42" s="56" t="n">
         <v>-150</v>
       </c>
       <c r="J42" s="30" t="n">
@@ -10416,12 +10411,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="L42" s="35" t="inlineStr">
+      <c r="L42" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="M42" s="45" t="n">
+      <c r="M42" s="44" t="n">
         <v>734</v>
       </c>
       <c r="N42" s="30" t="n">
@@ -10432,12 +10427,12 @@
           <t>심텍</t>
         </is>
       </c>
-      <c r="P42" s="35" t="inlineStr">
+      <c r="P42" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q42" s="57" t="n">
+      <c r="Q42" s="56" t="n">
         <v>-878</v>
       </c>
     </row>
@@ -10450,12 +10445,12 @@
           <t>HD현대중공업</t>
         </is>
       </c>
-      <c r="C43" s="58" t="inlineStr">
+      <c r="C43" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="D43" s="45" t="n">
+      <c r="D43" s="44" t="n">
         <v>692</v>
       </c>
       <c r="E43" s="30" t="n">
@@ -10466,12 +10461,12 @@
           <t>엘앤씨바이오</t>
         </is>
       </c>
-      <c r="G43" s="35" t="inlineStr">
+      <c r="G43" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="H43" s="57" t="n">
+      <c r="H43" s="56" t="n">
         <v>-135</v>
       </c>
       <c r="J43" s="30" t="n">
@@ -10482,12 +10477,12 @@
           <t>대덕전자</t>
         </is>
       </c>
-      <c r="L43" s="35" t="inlineStr">
+      <c r="L43" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M43" s="45" t="n">
+      <c r="M43" s="44" t="n">
         <v>703</v>
       </c>
       <c r="N43" s="30" t="n">
@@ -10498,12 +10493,12 @@
           <t>DB하이텍</t>
         </is>
       </c>
-      <c r="P43" s="35" t="inlineStr">
+      <c r="P43" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q43" s="57" t="n">
+      <c r="Q43" s="56" t="n">
         <v>-862</v>
       </c>
     </row>
@@ -10514,7 +10509,7 @@
           <t>F7 연기금</t>
         </is>
       </c>
-      <c r="E45" s="54" t="inlineStr">
+      <c r="E45" s="53" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
@@ -10524,111 +10519,111 @@
           <t>F8 보험</t>
         </is>
       </c>
-      <c r="N45" s="54" t="inlineStr">
+      <c r="N45" s="53" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="55" t="inlineStr">
+      <c r="A46" s="54" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="E46" s="56" t="inlineStr">
+      <c r="E46" s="55" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="J46" s="55" t="inlineStr">
+      <c r="J46" s="54" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="N46" s="56" t="inlineStr">
+      <c r="N46" s="55" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="43" t="inlineStr">
+      <c r="A47" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B47" s="43" t="inlineStr">
+      <c r="B47" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C47" s="43" t="inlineStr">
+      <c r="C47" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D47" s="43" t="inlineStr">
+      <c r="D47" s="42" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E47" s="43" t="inlineStr">
+      <c r="E47" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F47" s="43" t="inlineStr">
+      <c r="F47" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G47" s="43" t="inlineStr">
+      <c r="G47" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H47" s="43" t="inlineStr">
+      <c r="H47" s="42" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="J47" s="43" t="inlineStr">
+      <c r="J47" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="K47" s="43" t="inlineStr">
+      <c r="K47" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="L47" s="43" t="inlineStr">
+      <c r="L47" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="M47" s="43" t="inlineStr">
+      <c r="M47" s="42" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="N47" s="43" t="inlineStr">
+      <c r="N47" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O47" s="43" t="inlineStr">
+      <c r="O47" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P47" s="43" t="inlineStr">
+      <c r="P47" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q47" s="43" t="inlineStr">
+      <c r="Q47" s="42" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -10643,12 +10638,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="C48" s="35" t="inlineStr">
+      <c r="C48" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D48" s="45" t="n">
+      <c r="D48" s="44" t="n">
         <v>7808</v>
       </c>
       <c r="E48" s="30" t="n">
@@ -10659,12 +10654,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="G48" s="35" t="inlineStr">
+      <c r="G48" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H48" s="57" t="n">
+      <c r="H48" s="56" t="n">
         <v>-3630</v>
       </c>
       <c r="J48" s="30" t="n">
@@ -10675,12 +10670,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="L48" s="35" t="inlineStr">
+      <c r="L48" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M48" s="45" t="n">
+      <c r="M48" s="44" t="n">
         <v>2440</v>
       </c>
       <c r="N48" s="30" t="n">
@@ -10691,12 +10686,12 @@
           <t>HD현대중공업</t>
         </is>
       </c>
-      <c r="P48" s="58" t="inlineStr">
+      <c r="P48" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q48" s="57" t="n">
+      <c r="Q48" s="56" t="n">
         <v>-136</v>
       </c>
     </row>
@@ -10709,12 +10704,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="C49" s="35" t="inlineStr">
+      <c r="C49" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D49" s="45" t="n">
+      <c r="D49" s="44" t="n">
         <v>3894</v>
       </c>
       <c r="E49" s="30" t="n">
@@ -10725,12 +10720,12 @@
           <t>HD현대중공업</t>
         </is>
       </c>
-      <c r="G49" s="58" t="inlineStr">
+      <c r="G49" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H49" s="57" t="n">
+      <c r="H49" s="56" t="n">
         <v>-1405</v>
       </c>
       <c r="J49" s="30" t="n">
@@ -10741,12 +10736,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="L49" s="35" t="inlineStr">
+      <c r="L49" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M49" s="45" t="n">
+      <c r="M49" s="44" t="n">
         <v>1601</v>
       </c>
       <c r="N49" s="30" t="n">
@@ -10757,12 +10752,12 @@
           <t>S-Oil</t>
         </is>
       </c>
-      <c r="P49" s="35" t="inlineStr">
+      <c r="P49" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="Q49" s="57" t="n">
+      <c r="Q49" s="56" t="n">
         <v>-119</v>
       </c>
     </row>
@@ -10775,12 +10770,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="C50" s="35" t="inlineStr">
+      <c r="C50" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D50" s="45" t="n">
+      <c r="D50" s="44" t="n">
         <v>2611</v>
       </c>
       <c r="E50" s="30" t="n">
@@ -10791,12 +10786,12 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="G50" s="35" t="inlineStr">
+      <c r="G50" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="H50" s="57" t="n">
+      <c r="H50" s="56" t="n">
         <v>-1203</v>
       </c>
       <c r="J50" s="30" t="n">
@@ -10807,12 +10802,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="L50" s="35" t="inlineStr">
+      <c r="L50" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M50" s="45" t="n">
+      <c r="M50" s="44" t="n">
         <v>489</v>
       </c>
       <c r="N50" s="30" t="n">
@@ -10823,12 +10818,12 @@
           <t>HD건설기계</t>
         </is>
       </c>
-      <c r="P50" s="35" t="inlineStr">
+      <c r="P50" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q50" s="57" t="n">
+      <c r="Q50" s="56" t="n">
         <v>-113</v>
       </c>
     </row>
@@ -10841,12 +10836,12 @@
           <t>삼성바이오로직스</t>
         </is>
       </c>
-      <c r="C51" s="35" t="inlineStr">
+      <c r="C51" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="D51" s="45" t="n">
+      <c r="D51" s="44" t="n">
         <v>2522</v>
       </c>
       <c r="E51" s="30" t="n">
@@ -10857,12 +10852,12 @@
           <t>S-Oil</t>
         </is>
       </c>
-      <c r="G51" s="35" t="inlineStr">
+      <c r="G51" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="H51" s="57" t="n">
+      <c r="H51" s="56" t="n">
         <v>-1148</v>
       </c>
       <c r="J51" s="30" t="n">
@@ -10873,12 +10868,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="L51" s="35" t="inlineStr">
+      <c r="L51" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M51" s="45" t="n">
+      <c r="M51" s="44" t="n">
         <v>411</v>
       </c>
       <c r="N51" s="30" t="n">
@@ -10889,12 +10884,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="P51" s="35" t="inlineStr">
+      <c r="P51" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q51" s="57" t="n">
+      <c r="Q51" s="56" t="n">
         <v>-97</v>
       </c>
     </row>
@@ -10907,12 +10902,12 @@
           <t>삼성생명</t>
         </is>
       </c>
-      <c r="C52" s="35" t="inlineStr">
+      <c r="C52" s="34" t="inlineStr">
         <is>
           <t>보험</t>
         </is>
       </c>
-      <c r="D52" s="45" t="n">
+      <c r="D52" s="44" t="n">
         <v>1705</v>
       </c>
       <c r="E52" s="30" t="n">
@@ -10923,12 +10918,12 @@
           <t>현대건설</t>
         </is>
       </c>
-      <c r="G52" s="35" t="inlineStr">
+      <c r="G52" s="34" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
       </c>
-      <c r="H52" s="57" t="n">
+      <c r="H52" s="56" t="n">
         <v>-1059</v>
       </c>
       <c r="J52" s="30" t="n">
@@ -10939,12 +10934,12 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="L52" s="35" t="inlineStr">
+      <c r="L52" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M52" s="45" t="n">
+      <c r="M52" s="44" t="n">
         <v>400</v>
       </c>
       <c r="N52" s="30" t="n">
@@ -10955,12 +10950,12 @@
           <t>현대건설</t>
         </is>
       </c>
-      <c r="P52" s="35" t="inlineStr">
+      <c r="P52" s="34" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
       </c>
-      <c r="Q52" s="57" t="n">
+      <c r="Q52" s="56" t="n">
         <v>-74</v>
       </c>
     </row>
@@ -10973,12 +10968,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="C53" s="35" t="inlineStr">
+      <c r="C53" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D53" s="45" t="n">
+      <c r="D53" s="44" t="n">
         <v>1518</v>
       </c>
       <c r="E53" s="30" t="n">
@@ -10989,12 +10984,12 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="G53" s="58" t="inlineStr">
+      <c r="G53" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H53" s="57" t="n">
+      <c r="H53" s="56" t="n">
         <v>-972</v>
       </c>
       <c r="J53" s="30" t="n">
@@ -11005,12 +11000,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="L53" s="35" t="inlineStr">
+      <c r="L53" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M53" s="45" t="n">
+      <c r="M53" s="44" t="n">
         <v>352</v>
       </c>
       <c r="N53" s="30" t="n">
@@ -11021,12 +11016,12 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="P53" s="35" t="inlineStr">
+      <c r="P53" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="Q53" s="57" t="n">
+      <c r="Q53" s="56" t="n">
         <v>-70</v>
       </c>
     </row>
@@ -11039,12 +11034,12 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="C54" s="35" t="inlineStr">
+      <c r="C54" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D54" s="45" t="n">
+      <c r="D54" s="44" t="n">
         <v>1406</v>
       </c>
       <c r="E54" s="30" t="n">
@@ -11055,12 +11050,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="G54" s="35" t="inlineStr">
+      <c r="G54" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H54" s="57" t="n">
+      <c r="H54" s="56" t="n">
         <v>-867</v>
       </c>
       <c r="J54" s="30" t="n">
@@ -11071,12 +11066,12 @@
           <t>삼성바이오로직스</t>
         </is>
       </c>
-      <c r="L54" s="35" t="inlineStr">
+      <c r="L54" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="M54" s="45" t="n">
+      <c r="M54" s="44" t="n">
         <v>210</v>
       </c>
       <c r="N54" s="30" t="n">
@@ -11087,12 +11082,12 @@
           <t>DB손해보험</t>
         </is>
       </c>
-      <c r="P54" s="35" t="inlineStr">
+      <c r="P54" s="34" t="inlineStr">
         <is>
           <t>보험</t>
         </is>
       </c>
-      <c r="Q54" s="57" t="n">
+      <c r="Q54" s="56" t="n">
         <v>-56</v>
       </c>
     </row>
@@ -11105,12 +11100,12 @@
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="C55" s="35" t="inlineStr">
+      <c r="C55" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="D55" s="45" t="n">
+      <c r="D55" s="44" t="n">
         <v>1119</v>
       </c>
       <c r="E55" s="30" t="n">
@@ -11121,12 +11116,12 @@
           <t>두산</t>
         </is>
       </c>
-      <c r="G55" s="35" t="inlineStr">
+      <c r="G55" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H55" s="57" t="n">
+      <c r="H55" s="56" t="n">
         <v>-851</v>
       </c>
       <c r="J55" s="30" t="n">
@@ -11137,12 +11132,12 @@
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="L55" s="35" t="inlineStr">
+      <c r="L55" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="M55" s="45" t="n">
+      <c r="M55" s="44" t="n">
         <v>188</v>
       </c>
       <c r="N55" s="30" t="n">
@@ -11153,12 +11148,12 @@
           <t>효성중공업</t>
         </is>
       </c>
-      <c r="P55" s="35" t="inlineStr">
+      <c r="P55" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q55" s="57" t="n">
+      <c r="Q55" s="56" t="n">
         <v>-52</v>
       </c>
     </row>
@@ -11171,12 +11166,12 @@
           <t>LG씨엔에스</t>
         </is>
       </c>
-      <c r="C56" s="35" t="inlineStr">
+      <c r="C56" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="D56" s="45" t="n">
+      <c r="D56" s="44" t="n">
         <v>1021</v>
       </c>
       <c r="E56" s="30" t="n">
@@ -11187,12 +11182,12 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="G56" s="58" t="inlineStr">
+      <c r="G56" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H56" s="57" t="n">
+      <c r="H56" s="56" t="n">
         <v>-745</v>
       </c>
       <c r="J56" s="30" t="n">
@@ -11203,12 +11198,12 @@
           <t>현대모비스</t>
         </is>
       </c>
-      <c r="L56" s="58" t="inlineStr">
+      <c r="L56" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="M56" s="45" t="n">
+      <c r="M56" s="44" t="n">
         <v>174</v>
       </c>
       <c r="N56" s="30" t="n">
@@ -11219,12 +11214,12 @@
           <t>한화오션</t>
         </is>
       </c>
-      <c r="P56" s="58" t="inlineStr">
+      <c r="P56" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q56" s="57" t="n">
+      <c r="Q56" s="56" t="n">
         <v>-46</v>
       </c>
     </row>
@@ -11237,12 +11232,12 @@
           <t>우리금융지주</t>
         </is>
       </c>
-      <c r="C57" s="35" t="inlineStr">
+      <c r="C57" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D57" s="45" t="n">
+      <c r="D57" s="44" t="n">
         <v>836</v>
       </c>
       <c r="E57" s="30" t="n">
@@ -11253,12 +11248,12 @@
           <t>기아</t>
         </is>
       </c>
-      <c r="G57" s="58" t="inlineStr">
+      <c r="G57" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H57" s="57" t="n">
+      <c r="H57" s="56" t="n">
         <v>-713</v>
       </c>
       <c r="J57" s="30" t="n">
@@ -11269,12 +11264,12 @@
           <t>한화시스템</t>
         </is>
       </c>
-      <c r="L57" s="35" t="inlineStr">
+      <c r="L57" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M57" s="45" t="n">
+      <c r="M57" s="44" t="n">
         <v>167</v>
       </c>
       <c r="N57" s="30" t="n">
@@ -11285,12 +11280,12 @@
           <t>심텍</t>
         </is>
       </c>
-      <c r="P57" s="35" t="inlineStr">
+      <c r="P57" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q57" s="57" t="n">
+      <c r="Q57" s="56" t="n">
         <v>-41</v>
       </c>
     </row>
@@ -11301,61 +11296,61 @@
           <t>F9 기타법인</t>
         </is>
       </c>
-      <c r="E59" s="54" t="inlineStr">
+      <c r="E59" s="53" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="55" t="inlineStr">
+      <c r="A60" s="54" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="E60" s="56" t="inlineStr">
+      <c r="E60" s="55" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="43" t="inlineStr">
+      <c r="A61" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B61" s="43" t="inlineStr">
+      <c r="B61" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C61" s="43" t="inlineStr">
+      <c r="C61" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D61" s="43" t="inlineStr">
+      <c r="D61" s="42" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E61" s="43" t="inlineStr">
+      <c r="E61" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F61" s="43" t="inlineStr">
+      <c r="F61" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G61" s="43" t="inlineStr">
+      <c r="G61" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H61" s="43" t="inlineStr">
+      <c r="H61" s="42" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -11370,12 +11365,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="C62" s="35" t="inlineStr">
+      <c r="C62" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D62" s="45" t="n">
+      <c r="D62" s="44" t="n">
         <v>97536</v>
       </c>
       <c r="E62" s="30" t="n">
@@ -11386,12 +11381,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="G62" s="35" t="inlineStr">
+      <c r="G62" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="H62" s="57" t="n">
+      <c r="H62" s="56" t="n">
         <v>-499</v>
       </c>
     </row>
@@ -11404,12 +11399,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="C63" s="35" t="inlineStr">
+      <c r="C63" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D63" s="45" t="n">
+      <c r="D63" s="44" t="n">
         <v>12535</v>
       </c>
       <c r="E63" s="30" t="n">
@@ -11420,12 +11415,12 @@
           <t>브릴스</t>
         </is>
       </c>
-      <c r="G63" s="35" t="inlineStr">
+      <c r="G63" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H63" s="57" t="n">
+      <c r="H63" s="56" t="n">
         <v>-222</v>
       </c>
     </row>
@@ -11438,12 +11433,12 @@
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="C64" s="35" t="inlineStr">
+      <c r="C64" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="D64" s="45" t="n">
+      <c r="D64" s="44" t="n">
         <v>789</v>
       </c>
       <c r="E64" s="30" t="n">
@@ -11454,12 +11449,12 @@
           <t>S-Oil</t>
         </is>
       </c>
-      <c r="G64" s="35" t="inlineStr">
+      <c r="G64" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="H64" s="57" t="n">
+      <c r="H64" s="56" t="n">
         <v>-120</v>
       </c>
     </row>
@@ -11472,12 +11467,12 @@
           <t>삼성E&amp;A</t>
         </is>
       </c>
-      <c r="C65" s="35" t="inlineStr">
+      <c r="C65" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="D65" s="45" t="n">
+      <c r="D65" s="44" t="n">
         <v>747</v>
       </c>
       <c r="E65" s="30" t="n">
@@ -11488,12 +11483,12 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="G65" s="58" t="inlineStr">
+      <c r="G65" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H65" s="57" t="n">
+      <c r="H65" s="56" t="n">
         <v>-84</v>
       </c>
     </row>
@@ -11506,12 +11501,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="C66" s="35" t="inlineStr">
+      <c r="C66" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D66" s="45" t="n">
+      <c r="D66" s="44" t="n">
         <v>594</v>
       </c>
       <c r="E66" s="30" t="n">
@@ -11522,12 +11517,12 @@
           <t>주성엔지니어링</t>
         </is>
       </c>
-      <c r="G66" s="35" t="inlineStr">
+      <c r="G66" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H66" s="57" t="n">
+      <c r="H66" s="56" t="n">
         <v>-73</v>
       </c>
     </row>
@@ -11540,12 +11535,12 @@
           <t>KT&amp;G</t>
         </is>
       </c>
-      <c r="C67" s="35" t="inlineStr">
+      <c r="C67" s="34" t="inlineStr">
         <is>
           <t>음식료·담배</t>
         </is>
       </c>
-      <c r="D67" s="45" t="n">
+      <c r="D67" s="44" t="n">
         <v>530</v>
       </c>
       <c r="E67" s="30" t="n">
@@ -11556,12 +11551,12 @@
           <t>KB금융</t>
         </is>
       </c>
-      <c r="G67" s="35" t="inlineStr">
+      <c r="G67" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="H67" s="57" t="n">
+      <c r="H67" s="56" t="n">
         <v>-71</v>
       </c>
     </row>
@@ -11574,12 +11569,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="C68" s="35" t="inlineStr">
+      <c r="C68" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D68" s="45" t="n">
+      <c r="D68" s="44" t="n">
         <v>309</v>
       </c>
       <c r="E68" s="30" t="n">
@@ -11590,12 +11585,12 @@
           <t>LG이노텍</t>
         </is>
       </c>
-      <c r="G68" s="35" t="inlineStr">
+      <c r="G68" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H68" s="57" t="n">
+      <c r="H68" s="56" t="n">
         <v>-65</v>
       </c>
     </row>
@@ -11608,12 +11603,12 @@
           <t>한화오션</t>
         </is>
       </c>
-      <c r="C69" s="58" t="inlineStr">
+      <c r="C69" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="D69" s="45" t="n">
+      <c r="D69" s="44" t="n">
         <v>178</v>
       </c>
       <c r="E69" s="30" t="n">
@@ -11624,8 +11619,8 @@
           <t>인텔리빅스</t>
         </is>
       </c>
-      <c r="G69" s="35" t="inlineStr"/>
-      <c r="H69" s="57" t="n">
+      <c r="G69" s="34" t="inlineStr"/>
+      <c r="H69" s="56" t="n">
         <v>-60</v>
       </c>
     </row>
@@ -11638,12 +11633,12 @@
           <t>현대로템</t>
         </is>
       </c>
-      <c r="C70" s="58" t="inlineStr">
+      <c r="C70" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="D70" s="45" t="n">
+      <c r="D70" s="44" t="n">
         <v>145</v>
       </c>
       <c r="E70" s="30" t="n">
@@ -11654,12 +11649,12 @@
           <t>HD현대중공업</t>
         </is>
       </c>
-      <c r="G70" s="58" t="inlineStr">
+      <c r="G70" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H70" s="57" t="n">
+      <c r="H70" s="56" t="n">
         <v>-51</v>
       </c>
     </row>
@@ -11672,12 +11667,12 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="C71" s="35" t="inlineStr">
+      <c r="C71" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D71" s="45" t="n">
+      <c r="D71" s="44" t="n">
         <v>123</v>
       </c>
       <c r="E71" s="30" t="n">
@@ -11688,18 +11683,18 @@
           <t>LIG디펜스앤에어로스페이스</t>
         </is>
       </c>
-      <c r="G71" s="35" t="inlineStr">
+      <c r="G71" s="34" t="inlineStr">
         <is>
           <t>금속</t>
         </is>
       </c>
-      <c r="H71" s="57" t="n">
+      <c r="H71" s="56" t="n">
         <v>-49</v>
       </c>
     </row>
     <row r="72"/>
     <row r="73" ht="31" customHeight="1" s="15">
-      <c r="A73" s="59" t="inlineStr">
+      <c r="A73" s="58" t="inlineStr">
         <is>
           <t>외인·기관 동시 등재 종목=종목명 굵게(동반 매수/매도) · netbuy_rank 일별 아카이브 합산 — 상위 30 리스트 등재일만 반영되는 근사치 · 금융투자=증권, 투신(사모)=투자신탁+사모펀드, 기타법인=일반법인(자사주 매입 등) (확정 병합분) · 외인+기관=합산 카드와 동일</t>
         </is>
@@ -11817,87 +11812,87 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B4" s="43" t="inlineStr">
+      <c r="B4" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C4" s="43" t="inlineStr">
+      <c r="C4" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D4" s="43" t="inlineStr">
+      <c r="D4" s="42" t="inlineStr">
         <is>
           <t>금액(억)</t>
         </is>
       </c>
-      <c r="E4" s="43" t="inlineStr">
+      <c r="E4" s="42" t="inlineStr">
         <is>
           <t>시총대비(%)</t>
         </is>
       </c>
-      <c r="G4" s="43" t="inlineStr">
+      <c r="G4" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="H4" s="43" t="inlineStr">
+      <c r="H4" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="I4" s="43" t="inlineStr">
+      <c r="I4" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="J4" s="43" t="inlineStr">
+      <c r="J4" s="42" t="inlineStr">
         <is>
           <t>증감(억)</t>
         </is>
       </c>
-      <c r="K4" s="43" t="inlineStr">
+      <c r="K4" s="42" t="inlineStr">
         <is>
           <t>대차잔고(억)</t>
         </is>
       </c>
-      <c r="L4" s="43" t="inlineStr">
+      <c r="L4" s="42" t="inlineStr">
         <is>
           <t>시총대비(%)</t>
         </is>
       </c>
-      <c r="N4" s="43" t="inlineStr">
+      <c r="N4" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O4" s="43" t="inlineStr">
+      <c r="O4" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P4" s="43" t="inlineStr">
+      <c r="P4" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q4" s="43" t="inlineStr">
+      <c r="Q4" s="42" t="inlineStr">
         <is>
           <t>증감(억)</t>
         </is>
       </c>
-      <c r="R4" s="43" t="inlineStr">
+      <c r="R4" s="42" t="inlineStr">
         <is>
           <t>대차잔고(억)</t>
         </is>
       </c>
-      <c r="S4" s="43" t="inlineStr">
+      <c r="S4" s="42" t="inlineStr">
         <is>
           <t>시총대비(%)</t>
         </is>
@@ -11912,15 +11907,15 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="C5" s="35" t="inlineStr">
+      <c r="C5" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D5" s="60" t="n">
+      <c r="D5" s="59" t="n">
         <v>40944</v>
       </c>
-      <c r="E5" s="61" t="n">
+      <c r="E5" s="60" t="n">
         <v>0.37</v>
       </c>
       <c r="G5" s="30" t="n">
@@ -11931,18 +11926,18 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="I5" s="35" t="inlineStr">
+      <c r="I5" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J5" s="45" t="n">
+      <c r="J5" s="44" t="n">
         <v>5404.1</v>
       </c>
-      <c r="K5" s="62" t="n">
+      <c r="K5" s="61" t="n">
         <v>38372</v>
       </c>
-      <c r="L5" s="61" t="n">
+      <c r="L5" s="60" t="n">
         <v>4.61</v>
       </c>
       <c r="N5" s="30" t="n">
@@ -11953,18 +11948,18 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="P5" s="35" t="inlineStr">
+      <c r="P5" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q5" s="57" t="n">
+      <c r="Q5" s="56" t="n">
         <v>-55472.7</v>
       </c>
-      <c r="R5" s="62" t="n">
+      <c r="R5" s="61" t="n">
         <v>170244.4</v>
       </c>
-      <c r="S5" s="61" t="n">
+      <c r="S5" s="60" t="n">
         <v>1.53</v>
       </c>
     </row>
@@ -11977,15 +11972,15 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="C6" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D6" s="60" t="n">
+      <c r="D6" s="59" t="n">
         <v>24610</v>
       </c>
-      <c r="E6" s="61" t="n">
+      <c r="E6" s="60" t="n">
         <v>0.18</v>
       </c>
       <c r="G6" s="30" t="n">
@@ -11996,18 +11991,18 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="I6" s="35" t="inlineStr">
+      <c r="I6" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J6" s="45" t="n">
+      <c r="J6" s="44" t="n">
         <v>4743.7</v>
       </c>
-      <c r="K6" s="62" t="n">
+      <c r="K6" s="61" t="n">
         <v>18351.7</v>
       </c>
-      <c r="L6" s="61" t="n">
+      <c r="L6" s="60" t="n">
         <v>4.23</v>
       </c>
       <c r="N6" s="30" t="n">
@@ -12018,18 +12013,18 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="P6" s="35" t="inlineStr">
+      <c r="P6" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q6" s="57" t="n">
+      <c r="Q6" s="56" t="n">
         <v>-19909.9</v>
       </c>
-      <c r="R6" s="62" t="n">
+      <c r="R6" s="61" t="n">
         <v>179807.7</v>
       </c>
-      <c r="S6" s="61" t="n">
+      <c r="S6" s="60" t="n">
         <v>1.33</v>
       </c>
     </row>
@@ -12042,15 +12037,15 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="C7" s="35" t="inlineStr">
+      <c r="C7" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D7" s="60" t="n">
+      <c r="D7" s="59" t="n">
         <v>9780</v>
       </c>
-      <c r="E7" s="61" t="n">
+      <c r="E7" s="60" t="n">
         <v>1.17</v>
       </c>
       <c r="G7" s="30" t="n">
@@ -12061,14 +12056,14 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="I7" s="35" t="inlineStr"/>
-      <c r="J7" s="45" t="n">
+      <c r="I7" s="34" t="inlineStr"/>
+      <c r="J7" s="44" t="n">
         <v>2073.1</v>
       </c>
-      <c r="K7" s="62" t="n">
+      <c r="K7" s="61" t="n">
         <v>26608.1</v>
       </c>
-      <c r="L7" s="61" t="n">
+      <c r="L7" s="60" t="n">
         <v>1.8</v>
       </c>
       <c r="N7" s="30" t="n">
@@ -12079,18 +12074,18 @@
           <t>HD현대중공업</t>
         </is>
       </c>
-      <c r="P7" s="58" t="inlineStr">
+      <c r="P7" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q7" s="57" t="n">
+      <c r="Q7" s="56" t="n">
         <v>-12466.1</v>
       </c>
-      <c r="R7" s="62" t="n">
+      <c r="R7" s="61" t="n">
         <v>15469.6</v>
       </c>
-      <c r="S7" s="61" t="n">
+      <c r="S7" s="60" t="n">
         <v>5.42</v>
       </c>
     </row>
@@ -12103,15 +12098,15 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="C8" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D8" s="60" t="n">
+      <c r="D8" s="59" t="n">
         <v>7970</v>
       </c>
-      <c r="E8" s="61" t="n">
+      <c r="E8" s="60" t="n">
         <v>4.25</v>
       </c>
       <c r="G8" s="30" t="n">
@@ -12122,18 +12117,18 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="I8" s="35" t="inlineStr">
+      <c r="I8" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="J8" s="45" t="n">
+      <c r="J8" s="44" t="n">
         <v>2018.3</v>
       </c>
-      <c r="K8" s="62" t="n">
+      <c r="K8" s="61" t="n">
         <v>5792.3</v>
       </c>
-      <c r="L8" s="61" t="n">
+      <c r="L8" s="60" t="n">
         <v>2.64</v>
       </c>
       <c r="N8" s="30" t="n">
@@ -12144,18 +12139,18 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="P8" s="35" t="inlineStr">
+      <c r="P8" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q8" s="57" t="n">
+      <c r="Q8" s="56" t="n">
         <v>-9612.1</v>
       </c>
-      <c r="R8" s="62" t="n">
+      <c r="R8" s="61" t="n">
         <v>39971.3</v>
       </c>
-      <c r="S8" s="61" t="n">
+      <c r="S8" s="60" t="n">
         <v>21.3</v>
       </c>
     </row>
@@ -12168,15 +12163,15 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="C9" s="35" t="inlineStr">
+      <c r="C9" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D9" s="60" t="n">
+      <c r="D9" s="59" t="n">
         <v>7511</v>
       </c>
-      <c r="E9" s="61" t="n">
+      <c r="E9" s="60" t="n">
         <v>0.6</v>
       </c>
       <c r="G9" s="30" t="n">
@@ -12187,18 +12182,18 @@
           <t>에스원</t>
         </is>
       </c>
-      <c r="I9" s="35" t="inlineStr">
+      <c r="I9" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="J9" s="45" t="n">
+      <c r="J9" s="44" t="n">
         <v>1928</v>
       </c>
-      <c r="K9" s="62" t="n">
+      <c r="K9" s="61" t="n">
         <v>3140.9</v>
       </c>
-      <c r="L9" s="61" t="n">
+      <c r="L9" s="60" t="n">
         <v>8.58</v>
       </c>
       <c r="N9" s="30" t="n">
@@ -12209,18 +12204,18 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="P9" s="35" t="inlineStr">
+      <c r="P9" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q9" s="57" t="n">
+      <c r="Q9" s="56" t="n">
         <v>-6743.2</v>
       </c>
-      <c r="R9" s="62" t="n">
+      <c r="R9" s="61" t="n">
         <v>29739</v>
       </c>
-      <c r="S9" s="61" t="n">
+      <c r="S9" s="60" t="n">
         <v>3.08</v>
       </c>
     </row>
@@ -12233,15 +12228,15 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="C10" s="35" t="inlineStr">
+      <c r="C10" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D10" s="60" t="n">
+      <c r="D10" s="59" t="n">
         <v>6717</v>
       </c>
-      <c r="E10" s="61" t="n">
+      <c r="E10" s="60" t="n">
         <v>1.85</v>
       </c>
       <c r="G10" s="30" t="n">
@@ -12252,18 +12247,18 @@
           <t>피에스케이홀딩스</t>
         </is>
       </c>
-      <c r="I10" s="35" t="inlineStr">
+      <c r="I10" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="J10" s="45" t="n">
+      <c r="J10" s="44" t="n">
         <v>1549.6</v>
       </c>
-      <c r="K10" s="62" t="n">
+      <c r="K10" s="61" t="n">
         <v>4021.3</v>
       </c>
-      <c r="L10" s="61" t="n">
+      <c r="L10" s="60" t="n">
         <v>9.6</v>
       </c>
       <c r="N10" s="30" t="n">
@@ -12274,18 +12269,18 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="P10" s="35" t="inlineStr">
+      <c r="P10" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="Q10" s="57" t="n">
+      <c r="Q10" s="56" t="n">
         <v>-5675.5</v>
       </c>
-      <c r="R10" s="62" t="n">
+      <c r="R10" s="61" t="n">
         <v>25760.9</v>
       </c>
-      <c r="S10" s="61" t="n">
+      <c r="S10" s="60" t="n">
         <v>2.05</v>
       </c>
     </row>
@@ -12298,15 +12293,15 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="C11" s="35" t="inlineStr">
+      <c r="C11" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D11" s="60" t="n">
+      <c r="D11" s="59" t="n">
         <v>6482</v>
       </c>
-      <c r="E11" s="61" t="n">
+      <c r="E11" s="60" t="n">
         <v>1.5</v>
       </c>
       <c r="G11" s="30" t="n">
@@ -12317,18 +12312,18 @@
           <t>하이브</t>
         </is>
       </c>
-      <c r="I11" s="35" t="inlineStr">
+      <c r="I11" s="34" t="inlineStr">
         <is>
           <t>오락·문화</t>
         </is>
       </c>
-      <c r="J11" s="45" t="n">
+      <c r="J11" s="44" t="n">
         <v>1230.9</v>
       </c>
-      <c r="K11" s="62" t="n">
+      <c r="K11" s="61" t="n">
         <v>4773.8</v>
       </c>
-      <c r="L11" s="61" t="n">
+      <c r="L11" s="60" t="n">
         <v>7.01</v>
       </c>
       <c r="N11" s="30" t="n">
@@ -12339,14 +12334,14 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="P11" s="35" t="inlineStr"/>
-      <c r="Q11" s="57" t="n">
+      <c r="P11" s="34" t="inlineStr"/>
+      <c r="Q11" s="56" t="n">
         <v>-5011.3</v>
       </c>
-      <c r="R11" s="62" t="n">
+      <c r="R11" s="61" t="n">
         <v>24458</v>
       </c>
-      <c r="S11" s="61" t="n">
+      <c r="S11" s="60" t="n">
         <v>4.11</v>
       </c>
     </row>
@@ -12359,15 +12354,15 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="C12" s="35" t="inlineStr">
+      <c r="C12" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D12" s="60" t="n">
+      <c r="D12" s="59" t="n">
         <v>6180</v>
       </c>
-      <c r="E12" s="61" t="n">
+      <c r="E12" s="60" t="n">
         <v>0.64</v>
       </c>
       <c r="G12" s="30" t="n">
@@ -12378,18 +12373,18 @@
           <t>삼성E&amp;A</t>
         </is>
       </c>
-      <c r="I12" s="35" t="inlineStr">
+      <c r="I12" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="J12" s="45" t="n">
+      <c r="J12" s="44" t="n">
         <v>1211</v>
       </c>
-      <c r="K12" s="62" t="n">
+      <c r="K12" s="61" t="n">
         <v>4245.9</v>
       </c>
-      <c r="L12" s="61" t="n">
+      <c r="L12" s="60" t="n">
         <v>3.45</v>
       </c>
       <c r="N12" s="30" t="n">
@@ -12400,18 +12395,18 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="P12" s="35" t="inlineStr">
+      <c r="P12" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q12" s="57" t="n">
+      <c r="Q12" s="56" t="n">
         <v>-4803</v>
       </c>
-      <c r="R12" s="62" t="n">
+      <c r="R12" s="61" t="n">
         <v>15616.7</v>
       </c>
-      <c r="S12" s="61" t="n">
+      <c r="S12" s="60" t="n">
         <v>4.3</v>
       </c>
     </row>
@@ -12424,15 +12419,15 @@
           <t>주성엔지니어링</t>
         </is>
       </c>
-      <c r="C13" s="35" t="inlineStr">
+      <c r="C13" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D13" s="60" t="n">
+      <c r="D13" s="59" t="n">
         <v>5752</v>
       </c>
-      <c r="E13" s="61" t="n">
+      <c r="E13" s="60" t="n">
         <v>6.99</v>
       </c>
       <c r="G13" s="30" t="n">
@@ -12443,18 +12438,18 @@
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="I13" s="35" t="inlineStr">
+      <c r="I13" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="J13" s="45" t="n">
+      <c r="J13" s="44" t="n">
         <v>1189</v>
       </c>
-      <c r="K13" s="62" t="n">
+      <c r="K13" s="61" t="n">
         <v>13904.2</v>
       </c>
-      <c r="L13" s="61" t="n">
+      <c r="L13" s="60" t="n">
         <v>3.16</v>
       </c>
       <c r="N13" s="30" t="n">
@@ -12465,18 +12460,18 @@
           <t>한국항공우주</t>
         </is>
       </c>
-      <c r="P13" s="58" t="inlineStr">
+      <c r="P13" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q13" s="57" t="n">
+      <c r="Q13" s="56" t="n">
         <v>-4517.5</v>
       </c>
-      <c r="R13" s="62" t="n">
+      <c r="R13" s="61" t="n">
         <v>10090.8</v>
       </c>
-      <c r="S13" s="61" t="n">
+      <c r="S13" s="60" t="n">
         <v>10.31</v>
       </c>
     </row>
@@ -12489,11 +12484,11 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="C14" s="35" t="inlineStr"/>
-      <c r="D14" s="60" t="n">
+      <c r="C14" s="34" t="inlineStr"/>
+      <c r="D14" s="59" t="n">
         <v>5360</v>
       </c>
-      <c r="E14" s="61" t="n">
+      <c r="E14" s="60" t="n">
         <v>0.9</v>
       </c>
       <c r="G14" s="30" t="n">
@@ -12504,18 +12499,18 @@
           <t>삼성바이오로직스</t>
         </is>
       </c>
-      <c r="I14" s="35" t="inlineStr">
+      <c r="I14" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="J14" s="45" t="n">
+      <c r="J14" s="44" t="n">
         <v>1102.9</v>
       </c>
-      <c r="K14" s="62" t="n">
+      <c r="K14" s="61" t="n">
         <v>10385.8</v>
       </c>
-      <c r="L14" s="61" t="n">
+      <c r="L14" s="60" t="n">
         <v>1.64</v>
       </c>
       <c r="N14" s="30" t="n">
@@ -12526,24 +12521,24 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="P14" s="58" t="inlineStr">
+      <c r="P14" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q14" s="57" t="n">
+      <c r="Q14" s="56" t="n">
         <v>-3966.1</v>
       </c>
-      <c r="R14" s="62" t="n">
+      <c r="R14" s="61" t="n">
         <v>9075.5</v>
       </c>
-      <c r="S14" s="61" t="n">
+      <c r="S14" s="60" t="n">
         <v>2.32</v>
       </c>
     </row>
     <row r="15"/>
     <row r="16" ht="31" customHeight="1" s="15">
-      <c r="A16" s="59" t="inlineStr">
+      <c r="A16" s="58" t="inlineStr">
         <is>
           <t>랭킹 유니버스(순매수 상위 30 등재 종목) 한정 · 대차 증감=전월말 대비 최신 잔고 · 시총대비(%)=공매도 누적 금액÷시가총액, 대차잔고÷시가총액(KIS 마스터 시총(주 1회 갱신))</t>
         </is>
@@ -12636,77 +12631,77 @@
       <c r="O3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="42" t="inlineStr">
         <is>
           <t>업종</t>
         </is>
       </c>
-      <c r="B4" s="43" t="inlineStr">
+      <c r="B4" s="42" t="inlineStr">
         <is>
           <t>YTD</t>
         </is>
       </c>
-      <c r="C4" s="43" t="inlineStr">
+      <c r="C4" s="42" t="inlineStr">
         <is>
           <t>6M</t>
         </is>
       </c>
-      <c r="D4" s="43" t="inlineStr">
+      <c r="D4" s="42" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="E4" s="43" t="inlineStr">
+      <c r="E4" s="42" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="F4" s="43" t="inlineStr">
+      <c r="F4" s="42" t="inlineStr">
         <is>
           <t>외인</t>
         </is>
       </c>
-      <c r="G4" s="43" t="inlineStr">
+      <c r="G4" s="42" t="inlineStr">
         <is>
           <t>기관(합)</t>
         </is>
       </c>
-      <c r="H4" s="43" t="inlineStr">
+      <c r="H4" s="42" t="inlineStr">
         <is>
           <t>외인+기관</t>
         </is>
       </c>
-      <c r="I4" s="43" t="inlineStr">
+      <c r="I4" s="42" t="inlineStr">
         <is>
           <t>금융투자</t>
         </is>
       </c>
-      <c r="J4" s="43" t="inlineStr">
+      <c r="J4" s="42" t="inlineStr">
         <is>
           <t>투신(사모)</t>
         </is>
       </c>
-      <c r="K4" s="43" t="inlineStr">
+      <c r="K4" s="42" t="inlineStr">
         <is>
           <t>연기금</t>
         </is>
       </c>
-      <c r="L4" s="43" t="inlineStr">
+      <c r="L4" s="42" t="inlineStr">
         <is>
           <t>보험</t>
         </is>
       </c>
-      <c r="M4" s="43" t="inlineStr">
+      <c r="M4" s="42" t="inlineStr">
         <is>
           <t>개인</t>
         </is>
       </c>
-      <c r="N4" s="43" t="inlineStr">
+      <c r="N4" s="42" t="inlineStr">
         <is>
           <t>기타법인</t>
         </is>
       </c>
-      <c r="O4" s="43" t="inlineStr">
+      <c r="O4" s="42" t="inlineStr">
         <is>
           <t>신호</t>
         </is>
@@ -12718,43 +12713,43 @@
           <t>제약</t>
         </is>
       </c>
-      <c r="B5" s="63" t="n">
+      <c r="B5" s="62" t="n">
         <v>-11.42</v>
       </c>
-      <c r="C5" s="63" t="n">
+      <c r="C5" s="62" t="n">
         <v>-4.19</v>
       </c>
-      <c r="D5" s="64" t="n">
+      <c r="D5" s="63" t="n">
         <v>0.29</v>
       </c>
-      <c r="E5" s="64" t="n">
+      <c r="E5" s="63" t="n">
         <v>4.67</v>
       </c>
-      <c r="F5" s="65" t="n">
+      <c r="F5" s="64" t="n">
         <v>-2729</v>
       </c>
-      <c r="G5" s="66" t="n">
+      <c r="G5" s="65" t="n">
         <v>7121</v>
       </c>
-      <c r="H5" s="66" t="n">
+      <c r="H5" s="65" t="n">
         <v>4393</v>
       </c>
-      <c r="I5" s="65" t="n">
+      <c r="I5" s="64" t="n">
         <v>-463</v>
       </c>
-      <c r="J5" s="66" t="n">
+      <c r="J5" s="65" t="n">
         <v>2111</v>
       </c>
-      <c r="K5" s="66" t="n">
+      <c r="K5" s="65" t="n">
         <v>4884</v>
       </c>
-      <c r="L5" s="66" t="n">
+      <c r="L5" s="65" t="n">
         <v>602</v>
       </c>
-      <c r="M5" s="65" t="n">
+      <c r="M5" s="64" t="n">
         <v>-5629</v>
       </c>
-      <c r="N5" s="66" t="n">
+      <c r="N5" s="65" t="n">
         <v>1236</v>
       </c>
       <c r="O5" s="30" t="inlineStr"/>
@@ -12765,43 +12760,43 @@
           <t>음식료·담배</t>
         </is>
       </c>
-      <c r="B6" s="64" t="n">
+      <c r="B6" s="63" t="n">
         <v>6.65</v>
       </c>
-      <c r="C6" s="63" t="n">
+      <c r="C6" s="62" t="n">
         <v>-6.53</v>
       </c>
-      <c r="D6" s="63" t="n">
+      <c r="D6" s="62" t="n">
         <v>-1.52</v>
       </c>
-      <c r="E6" s="64" t="n">
+      <c r="E6" s="63" t="n">
         <v>3.13</v>
       </c>
-      <c r="F6" s="65" t="n">
+      <c r="F6" s="64" t="n">
         <v>-1598</v>
       </c>
-      <c r="G6" s="66" t="n">
+      <c r="G6" s="65" t="n">
         <v>2757</v>
       </c>
-      <c r="H6" s="66" t="n">
+      <c r="H6" s="65" t="n">
         <v>1159</v>
       </c>
-      <c r="I6" s="66" t="n">
+      <c r="I6" s="65" t="n">
         <v>404</v>
       </c>
-      <c r="J6" s="66" t="n">
+      <c r="J6" s="65" t="n">
         <v>1058</v>
       </c>
-      <c r="K6" s="66" t="n">
+      <c r="K6" s="65" t="n">
         <v>1089</v>
       </c>
-      <c r="L6" s="66" t="n">
+      <c r="L6" s="65" t="n">
         <v>201</v>
       </c>
-      <c r="M6" s="65" t="n">
+      <c r="M6" s="64" t="n">
         <v>-2040</v>
       </c>
-      <c r="N6" s="66" t="n">
+      <c r="N6" s="65" t="n">
         <v>881</v>
       </c>
       <c r="O6" s="30" t="inlineStr"/>
@@ -12812,46 +12807,46 @@
           <t>오락·문화</t>
         </is>
       </c>
-      <c r="B7" s="63" t="n">
+      <c r="B7" s="62" t="n">
         <v>-46.24</v>
       </c>
-      <c r="C7" s="63" t="n">
+      <c r="C7" s="62" t="n">
         <v>-34</v>
       </c>
-      <c r="D7" s="63" t="n">
+      <c r="D7" s="62" t="n">
         <v>-4.32</v>
       </c>
-      <c r="E7" s="63" t="n">
+      <c r="E7" s="62" t="n">
         <v>-1.17</v>
       </c>
-      <c r="F7" s="65" t="n">
+      <c r="F7" s="64" t="n">
         <v>-50</v>
       </c>
-      <c r="G7" s="66" t="n">
+      <c r="G7" s="65" t="n">
         <v>1551</v>
       </c>
-      <c r="H7" s="66" t="n">
+      <c r="H7" s="65" t="n">
         <v>1501</v>
       </c>
-      <c r="I7" s="66" t="n">
+      <c r="I7" s="65" t="n">
         <v>68</v>
       </c>
-      <c r="J7" s="66" t="n">
+      <c r="J7" s="65" t="n">
         <v>723</v>
       </c>
-      <c r="K7" s="66" t="n">
+      <c r="K7" s="65" t="n">
         <v>666</v>
       </c>
-      <c r="L7" s="66" t="n">
+      <c r="L7" s="65" t="n">
         <v>86</v>
       </c>
-      <c r="M7" s="65" t="n">
+      <c r="M7" s="64" t="n">
         <v>-1517</v>
       </c>
-      <c r="N7" s="66" t="n">
+      <c r="N7" s="65" t="n">
         <v>16</v>
       </c>
-      <c r="O7" s="67" t="inlineStr">
+      <c r="O7" s="66" t="inlineStr">
         <is>
           <t>수급유입</t>
         </is>
@@ -12863,43 +12858,43 @@
           <t>의료·정밀기기</t>
         </is>
       </c>
-      <c r="B8" s="64" t="n">
+      <c r="B8" s="63" t="n">
         <v>24.9</v>
       </c>
-      <c r="C8" s="63" t="n">
+      <c r="C8" s="62" t="n">
         <v>-0.31</v>
       </c>
-      <c r="D8" s="64" t="n">
+      <c r="D8" s="63" t="n">
         <v>43.99</v>
       </c>
-      <c r="E8" s="63" t="n">
+      <c r="E8" s="62" t="n">
         <v>-1.74</v>
       </c>
-      <c r="F8" s="66" t="n">
+      <c r="F8" s="65" t="n">
         <v>237</v>
       </c>
-      <c r="G8" s="66" t="n">
+      <c r="G8" s="65" t="n">
         <v>368</v>
       </c>
-      <c r="H8" s="66" t="n">
+      <c r="H8" s="65" t="n">
         <v>606</v>
       </c>
-      <c r="I8" s="66" t="n">
+      <c r="I8" s="65" t="n">
         <v>153</v>
       </c>
-      <c r="J8" s="66" t="n">
+      <c r="J8" s="65" t="n">
         <v>214</v>
       </c>
-      <c r="K8" s="65" t="n">
+      <c r="K8" s="64" t="n">
         <v>-8</v>
       </c>
-      <c r="L8" s="66" t="n">
+      <c r="L8" s="65" t="n">
         <v>8</v>
       </c>
-      <c r="M8" s="65" t="n">
+      <c r="M8" s="64" t="n">
         <v>-582</v>
       </c>
-      <c r="N8" s="65" t="n">
+      <c r="N8" s="64" t="n">
         <v>-24</v>
       </c>
       <c r="O8" s="30" t="inlineStr"/>
@@ -12910,43 +12905,43 @@
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="B9" s="64" t="n">
+      <c r="B9" s="63" t="n">
         <v>7.98</v>
       </c>
-      <c r="C9" s="63" t="n">
+      <c r="C9" s="62" t="n">
         <v>-2.81</v>
       </c>
-      <c r="D9" s="64" t="n">
+      <c r="D9" s="63" t="n">
         <v>6.42</v>
       </c>
-      <c r="E9" s="63" t="n">
+      <c r="E9" s="62" t="n">
         <v>-1.89</v>
       </c>
-      <c r="F9" s="66" t="n">
+      <c r="F9" s="65" t="n">
         <v>1486</v>
       </c>
-      <c r="G9" s="66" t="n">
+      <c r="G9" s="65" t="n">
         <v>609</v>
       </c>
-      <c r="H9" s="66" t="n">
+      <c r="H9" s="65" t="n">
         <v>2095</v>
       </c>
-      <c r="I9" s="65" t="n">
+      <c r="I9" s="64" t="n">
         <v>-15</v>
       </c>
-      <c r="J9" s="65" t="n">
+      <c r="J9" s="64" t="n">
         <v>-48</v>
       </c>
-      <c r="K9" s="66" t="n">
+      <c r="K9" s="65" t="n">
         <v>634</v>
       </c>
-      <c r="L9" s="66" t="n">
+      <c r="L9" s="65" t="n">
         <v>45</v>
       </c>
-      <c r="M9" s="65" t="n">
+      <c r="M9" s="64" t="n">
         <v>-3372</v>
       </c>
-      <c r="N9" s="66" t="n">
+      <c r="N9" s="65" t="n">
         <v>1277</v>
       </c>
       <c r="O9" s="30" t="inlineStr"/>
@@ -12957,46 +12952,46 @@
           <t>보험</t>
         </is>
       </c>
-      <c r="B10" s="64" t="n">
+      <c r="B10" s="63" t="n">
         <v>49.15</v>
       </c>
-      <c r="C10" s="64" t="n">
+      <c r="C10" s="63" t="n">
         <v>15.19</v>
       </c>
-      <c r="D10" s="64" t="n">
+      <c r="D10" s="63" t="n">
         <v>5.56</v>
       </c>
-      <c r="E10" s="63" t="n">
+      <c r="E10" s="62" t="n">
         <v>-2.19</v>
       </c>
-      <c r="F10" s="65" t="n">
+      <c r="F10" s="64" t="n">
         <v>-3203</v>
       </c>
-      <c r="G10" s="66" t="n">
+      <c r="G10" s="65" t="n">
         <v>4160</v>
       </c>
-      <c r="H10" s="66" t="n">
+      <c r="H10" s="65" t="n">
         <v>956</v>
       </c>
-      <c r="I10" s="66" t="n">
+      <c r="I10" s="65" t="n">
         <v>592</v>
       </c>
-      <c r="J10" s="66" t="n">
+      <c r="J10" s="65" t="n">
         <v>1668</v>
       </c>
-      <c r="K10" s="66" t="n">
+      <c r="K10" s="65" t="n">
         <v>1876</v>
       </c>
-      <c r="L10" s="66" t="n">
+      <c r="L10" s="65" t="n">
         <v>30</v>
       </c>
-      <c r="M10" s="65" t="n">
+      <c r="M10" s="64" t="n">
         <v>-993</v>
       </c>
-      <c r="N10" s="66" t="n">
+      <c r="N10" s="65" t="n">
         <v>37</v>
       </c>
-      <c r="O10" s="55" t="inlineStr">
+      <c r="O10" s="54" t="inlineStr">
         <is>
           <t>동반강세</t>
         </is>
@@ -13008,43 +13003,43 @@
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="B11" s="64" t="n">
+      <c r="B11" s="63" t="n">
         <v>2.27</v>
       </c>
-      <c r="C11" s="63" t="n">
+      <c r="C11" s="62" t="n">
         <v>-18.31</v>
       </c>
-      <c r="D11" s="64" t="n">
+      <c r="D11" s="63" t="n">
         <v>12.4</v>
       </c>
-      <c r="E11" s="63" t="n">
+      <c r="E11" s="62" t="n">
         <v>-2.7</v>
       </c>
-      <c r="F11" s="66" t="n">
+      <c r="F11" s="65" t="n">
         <v>4714</v>
       </c>
-      <c r="G11" s="66" t="n">
+      <c r="G11" s="65" t="n">
         <v>1629</v>
       </c>
-      <c r="H11" s="66" t="n">
+      <c r="H11" s="65" t="n">
         <v>6344</v>
       </c>
-      <c r="I11" s="66" t="n">
+      <c r="I11" s="65" t="n">
         <v>1203</v>
       </c>
-      <c r="J11" s="66" t="n">
+      <c r="J11" s="65" t="n">
         <v>324</v>
       </c>
-      <c r="K11" s="66" t="n">
+      <c r="K11" s="65" t="n">
         <v>108</v>
       </c>
-      <c r="L11" s="66" t="n">
+      <c r="L11" s="65" t="n">
         <v>10</v>
       </c>
-      <c r="M11" s="65" t="n">
+      <c r="M11" s="64" t="n">
         <v>-7416</v>
       </c>
-      <c r="N11" s="66" t="n">
+      <c r="N11" s="65" t="n">
         <v>1073</v>
       </c>
       <c r="O11" s="30" t="inlineStr"/>
@@ -13055,46 +13050,46 @@
           <t>전기·가스</t>
         </is>
       </c>
-      <c r="B12" s="63" t="n">
+      <c r="B12" s="62" t="n">
         <v>-32.83</v>
       </c>
-      <c r="C12" s="63" t="n">
+      <c r="C12" s="62" t="n">
         <v>-30.36</v>
       </c>
-      <c r="D12" s="63" t="n">
+      <c r="D12" s="62" t="n">
         <v>-9.789999999999999</v>
       </c>
-      <c r="E12" s="63" t="n">
+      <c r="E12" s="62" t="n">
         <v>-4.23</v>
       </c>
-      <c r="F12" s="66" t="n">
+      <c r="F12" s="65" t="n">
         <v>27</v>
       </c>
-      <c r="G12" s="66" t="n">
+      <c r="G12" s="65" t="n">
         <v>721</v>
       </c>
-      <c r="H12" s="66" t="n">
+      <c r="H12" s="65" t="n">
         <v>748</v>
       </c>
-      <c r="I12" s="66" t="n">
+      <c r="I12" s="65" t="n">
         <v>432</v>
       </c>
-      <c r="J12" s="66" t="n">
+      <c r="J12" s="65" t="n">
         <v>274</v>
       </c>
-      <c r="K12" s="65" t="n">
+      <c r="K12" s="64" t="n">
         <v>-30</v>
       </c>
-      <c r="L12" s="66" t="n">
+      <c r="L12" s="65" t="n">
         <v>50</v>
       </c>
-      <c r="M12" s="65" t="n">
+      <c r="M12" s="64" t="n">
         <v>-752</v>
       </c>
-      <c r="N12" s="66" t="n">
+      <c r="N12" s="65" t="n">
         <v>4</v>
       </c>
-      <c r="O12" s="67" t="inlineStr">
+      <c r="O12" s="66" t="inlineStr">
         <is>
           <t>수급유입</t>
         </is>
@@ -13106,46 +13101,46 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="B13" s="63" t="n">
+      <c r="B13" s="62" t="n">
         <v>-15.64</v>
       </c>
-      <c r="C13" s="63" t="n">
+      <c r="C13" s="62" t="n">
         <v>-20.75</v>
       </c>
-      <c r="D13" s="63" t="n">
+      <c r="D13" s="62" t="n">
         <v>-2.58</v>
       </c>
-      <c r="E13" s="63" t="n">
+      <c r="E13" s="62" t="n">
         <v>-5.63</v>
       </c>
-      <c r="F13" s="66" t="n">
+      <c r="F13" s="65" t="n">
         <v>55</v>
       </c>
-      <c r="G13" s="66" t="n">
+      <c r="G13" s="65" t="n">
         <v>30</v>
       </c>
-      <c r="H13" s="66" t="n">
+      <c r="H13" s="65" t="n">
         <v>85</v>
       </c>
-      <c r="I13" s="66" t="n">
+      <c r="I13" s="65" t="n">
         <v>294</v>
       </c>
-      <c r="J13" s="65" t="n">
+      <c r="J13" s="64" t="n">
         <v>-185</v>
       </c>
-      <c r="K13" s="65" t="n">
+      <c r="K13" s="64" t="n">
         <v>-46</v>
       </c>
-      <c r="L13" s="65" t="n">
+      <c r="L13" s="64" t="n">
         <v>-30</v>
       </c>
-      <c r="M13" s="65" t="n">
+      <c r="M13" s="64" t="n">
         <v>-77</v>
       </c>
-      <c r="N13" s="65" t="n">
+      <c r="N13" s="64" t="n">
         <v>-8</v>
       </c>
-      <c r="O13" s="67" t="inlineStr">
+      <c r="O13" s="66" t="inlineStr">
         <is>
           <t>수급유입</t>
         </is>
@@ -13157,46 +13152,46 @@
           <t>섬유·의류</t>
         </is>
       </c>
-      <c r="B14" s="63" t="n">
+      <c r="B14" s="62" t="n">
         <v>-11.24</v>
       </c>
-      <c r="C14" s="63" t="n">
+      <c r="C14" s="62" t="n">
         <v>-16.59</v>
       </c>
-      <c r="D14" s="63" t="n">
+      <c r="D14" s="62" t="n">
         <v>-9.18</v>
       </c>
-      <c r="E14" s="63" t="n">
+      <c r="E14" s="62" t="n">
         <v>-5.91</v>
       </c>
-      <c r="F14" s="66" t="n">
+      <c r="F14" s="65" t="n">
         <v>139</v>
       </c>
-      <c r="G14" s="66" t="n">
+      <c r="G14" s="65" t="n">
         <v>24</v>
       </c>
-      <c r="H14" s="66" t="n">
+      <c r="H14" s="65" t="n">
         <v>163</v>
       </c>
-      <c r="I14" s="66" t="n">
+      <c r="I14" s="65" t="n">
         <v>108</v>
       </c>
-      <c r="J14" s="65" t="n">
+      <c r="J14" s="64" t="n">
         <v>-43</v>
       </c>
-      <c r="K14" s="65" t="n">
+      <c r="K14" s="64" t="n">
         <v>-29</v>
       </c>
-      <c r="L14" s="65" t="n">
+      <c r="L14" s="64" t="n">
         <v>-8</v>
       </c>
-      <c r="M14" s="65" t="n">
+      <c r="M14" s="64" t="n">
         <v>-389</v>
       </c>
-      <c r="N14" s="66" t="n">
+      <c r="N14" s="65" t="n">
         <v>225</v>
       </c>
-      <c r="O14" s="67" t="inlineStr">
+      <c r="O14" s="66" t="inlineStr">
         <is>
           <t>수급유입</t>
         </is>
@@ -13208,46 +13203,46 @@
           <t>비금속</t>
         </is>
       </c>
-      <c r="B15" s="63" t="n">
+      <c r="B15" s="62" t="n">
         <v>-19.86</v>
       </c>
-      <c r="C15" s="63" t="n">
+      <c r="C15" s="62" t="n">
         <v>-25.28</v>
       </c>
-      <c r="D15" s="64" t="n">
+      <c r="D15" s="63" t="n">
         <v>0.05</v>
       </c>
-      <c r="E15" s="63" t="n">
+      <c r="E15" s="62" t="n">
         <v>-6.35</v>
       </c>
-      <c r="F15" s="66" t="n">
+      <c r="F15" s="65" t="n">
         <v>41</v>
       </c>
-      <c r="G15" s="66" t="n">
+      <c r="G15" s="65" t="n">
         <v>39</v>
       </c>
-      <c r="H15" s="66" t="n">
+      <c r="H15" s="65" t="n">
         <v>81</v>
       </c>
-      <c r="I15" s="66" t="n">
+      <c r="I15" s="65" t="n">
         <v>21</v>
       </c>
-      <c r="J15" s="65" t="n">
+      <c r="J15" s="64" t="n">
         <v>-9</v>
       </c>
-      <c r="K15" s="66" t="n">
+      <c r="K15" s="65" t="n">
         <v>29</v>
       </c>
-      <c r="L15" s="65" t="n">
+      <c r="L15" s="64" t="n">
         <v>-1</v>
       </c>
-      <c r="M15" s="65" t="n">
+      <c r="M15" s="64" t="n">
         <v>-82</v>
       </c>
-      <c r="N15" s="66" t="n">
+      <c r="N15" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="O15" s="67" t="inlineStr">
+      <c r="O15" s="66" t="inlineStr">
         <is>
           <t>수급유입</t>
         </is>
@@ -13259,43 +13254,43 @@
           <t>유통</t>
         </is>
       </c>
-      <c r="B16" s="64" t="n">
+      <c r="B16" s="63" t="n">
         <v>12.46</v>
       </c>
-      <c r="C16" s="63" t="n">
+      <c r="C16" s="62" t="n">
         <v>-13.59</v>
       </c>
-      <c r="D16" s="63" t="n">
+      <c r="D16" s="62" t="n">
         <v>-2.01</v>
       </c>
-      <c r="E16" s="63" t="n">
+      <c r="E16" s="62" t="n">
         <v>-8.289999999999999</v>
       </c>
-      <c r="F16" s="65" t="n">
+      <c r="F16" s="64" t="n">
         <v>-116</v>
       </c>
-      <c r="G16" s="66" t="n">
+      <c r="G16" s="65" t="n">
         <v>2452</v>
       </c>
-      <c r="H16" s="66" t="n">
+      <c r="H16" s="65" t="n">
         <v>2336</v>
       </c>
-      <c r="I16" s="66" t="n">
+      <c r="I16" s="65" t="n">
         <v>756</v>
       </c>
-      <c r="J16" s="66" t="n">
+      <c r="J16" s="65" t="n">
         <v>13</v>
       </c>
-      <c r="K16" s="66" t="n">
+      <c r="K16" s="65" t="n">
         <v>1478</v>
       </c>
-      <c r="L16" s="66" t="n">
+      <c r="L16" s="65" t="n">
         <v>237</v>
       </c>
-      <c r="M16" s="65" t="n">
+      <c r="M16" s="64" t="n">
         <v>-2377</v>
       </c>
-      <c r="N16" s="66" t="n">
+      <c r="N16" s="65" t="n">
         <v>41</v>
       </c>
       <c r="O16" s="30" t="inlineStr"/>
@@ -13306,43 +13301,43 @@
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="B17" s="63" t="n">
+      <c r="B17" s="62" t="n">
         <v>-22.6</v>
       </c>
-      <c r="C17" s="63" t="n">
+      <c r="C17" s="62" t="n">
         <v>-18.89</v>
       </c>
-      <c r="D17" s="63" t="n">
+      <c r="D17" s="62" t="n">
         <v>-9.09</v>
       </c>
-      <c r="E17" s="63" t="n">
+      <c r="E17" s="62" t="n">
         <v>-9.390000000000001</v>
       </c>
-      <c r="F17" s="66" t="n">
+      <c r="F17" s="65" t="n">
         <v>80</v>
       </c>
-      <c r="G17" s="66" t="n">
+      <c r="G17" s="65" t="n">
         <v>1935</v>
       </c>
-      <c r="H17" s="66" t="n">
+      <c r="H17" s="65" t="n">
         <v>2016</v>
       </c>
-      <c r="I17" s="66" t="n">
+      <c r="I17" s="65" t="n">
         <v>1063</v>
       </c>
-      <c r="J17" s="66" t="n">
+      <c r="J17" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="K17" s="66" t="n">
+      <c r="K17" s="65" t="n">
         <v>622</v>
       </c>
-      <c r="L17" s="66" t="n">
+      <c r="L17" s="65" t="n">
         <v>245</v>
       </c>
-      <c r="M17" s="65" t="n">
+      <c r="M17" s="64" t="n">
         <v>-1931</v>
       </c>
-      <c r="N17" s="65" t="n">
+      <c r="N17" s="64" t="n">
         <v>-85</v>
       </c>
       <c r="O17" s="30" t="inlineStr"/>
@@ -13353,46 +13348,46 @@
           <t>통신</t>
         </is>
       </c>
-      <c r="B18" s="64" t="n">
+      <c r="B18" s="63" t="n">
         <v>10.72</v>
       </c>
-      <c r="C18" s="63" t="n">
+      <c r="C18" s="62" t="n">
         <v>-20.22</v>
       </c>
-      <c r="D18" s="63" t="n">
+      <c r="D18" s="62" t="n">
         <v>-7.33</v>
       </c>
-      <c r="E18" s="63" t="n">
+      <c r="E18" s="62" t="n">
         <v>-10.15</v>
       </c>
-      <c r="F18" s="65" t="n">
+      <c r="F18" s="64" t="n">
         <v>-84</v>
       </c>
-      <c r="G18" s="66" t="n">
+      <c r="G18" s="65" t="n">
         <v>615</v>
       </c>
-      <c r="H18" s="66" t="n">
+      <c r="H18" s="65" t="n">
         <v>530</v>
       </c>
-      <c r="I18" s="66" t="n">
+      <c r="I18" s="65" t="n">
         <v>187</v>
       </c>
-      <c r="J18" s="66" t="n">
+      <c r="J18" s="65" t="n">
         <v>182</v>
       </c>
-      <c r="K18" s="65" t="n">
+      <c r="K18" s="64" t="n">
         <v>-6</v>
       </c>
-      <c r="L18" s="66" t="n">
+      <c r="L18" s="65" t="n">
         <v>272</v>
       </c>
-      <c r="M18" s="65" t="n">
+      <c r="M18" s="64" t="n">
         <v>-512</v>
       </c>
-      <c r="N18" s="65" t="n">
+      <c r="N18" s="64" t="n">
         <v>-19</v>
       </c>
-      <c r="O18" s="67" t="inlineStr">
+      <c r="O18" s="66" t="inlineStr">
         <is>
           <t>수급유입</t>
         </is>
@@ -13404,46 +13399,46 @@
           <t>종이·목재</t>
         </is>
       </c>
-      <c r="B19" s="63" t="n">
+      <c r="B19" s="62" t="n">
         <v>-32.6</v>
       </c>
-      <c r="C19" s="63" t="n">
+      <c r="C19" s="62" t="n">
         <v>-35.25</v>
       </c>
-      <c r="D19" s="63" t="n">
+      <c r="D19" s="62" t="n">
         <v>-8.789999999999999</v>
       </c>
-      <c r="E19" s="63" t="n">
+      <c r="E19" s="62" t="n">
         <v>-12.42</v>
       </c>
-      <c r="F19" s="66" t="n">
+      <c r="F19" s="65" t="n">
         <v>3</v>
       </c>
-      <c r="G19" s="66" t="n">
+      <c r="G19" s="65" t="n">
         <v>8</v>
       </c>
-      <c r="H19" s="66" t="n">
+      <c r="H19" s="65" t="n">
         <v>11</v>
       </c>
-      <c r="I19" s="66" t="n">
+      <c r="I19" s="65" t="n">
         <v>14</v>
       </c>
-      <c r="J19" s="65" t="n">
+      <c r="J19" s="64" t="n">
         <v>-2</v>
       </c>
-      <c r="K19" s="65" t="n">
+      <c r="K19" s="64" t="n">
         <v>-5</v>
       </c>
-      <c r="L19" s="68" t="n">
+      <c r="L19" s="67" t="n">
         <v>0</v>
       </c>
-      <c r="M19" s="66" t="n">
+      <c r="M19" s="65" t="n">
         <v>8</v>
       </c>
-      <c r="N19" s="65" t="n">
+      <c r="N19" s="64" t="n">
         <v>-19</v>
       </c>
-      <c r="O19" s="67" t="inlineStr">
+      <c r="O19" s="66" t="inlineStr">
         <is>
           <t>수급유입</t>
         </is>
@@ -13455,46 +13450,46 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="B20" s="64" t="n">
+      <c r="B20" s="63" t="n">
         <v>23.58</v>
       </c>
-      <c r="C20" s="63" t="n">
+      <c r="C20" s="62" t="n">
         <v>-12.6</v>
       </c>
-      <c r="D20" s="63" t="n">
+      <c r="D20" s="62" t="n">
         <v>-2.38</v>
       </c>
-      <c r="E20" s="63" t="n">
+      <c r="E20" s="62" t="n">
         <v>-12.58</v>
       </c>
-      <c r="F20" s="65" t="n">
+      <c r="F20" s="64" t="n">
         <v>-11131</v>
       </c>
-      <c r="G20" s="66" t="n">
+      <c r="G20" s="65" t="n">
         <v>24597</v>
       </c>
-      <c r="H20" s="66" t="n">
+      <c r="H20" s="65" t="n">
         <v>13466</v>
       </c>
-      <c r="I20" s="66" t="n">
+      <c r="I20" s="65" t="n">
         <v>14367</v>
       </c>
-      <c r="J20" s="66" t="n">
+      <c r="J20" s="65" t="n">
         <v>8277</v>
       </c>
-      <c r="K20" s="65" t="n">
+      <c r="K20" s="64" t="n">
         <v>-380</v>
       </c>
-      <c r="L20" s="66" t="n">
+      <c r="L20" s="65" t="n">
         <v>558</v>
       </c>
-      <c r="M20" s="65" t="n">
+      <c r="M20" s="64" t="n">
         <v>-7400</v>
       </c>
-      <c r="N20" s="65" t="n">
+      <c r="N20" s="64" t="n">
         <v>-6065</v>
       </c>
-      <c r="O20" s="67" t="inlineStr">
+      <c r="O20" s="66" t="inlineStr">
         <is>
           <t>수급유입</t>
         </is>
@@ -13506,43 +13501,43 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="B21" s="63" t="n">
+      <c r="B21" s="62" t="n">
         <v>-1.89</v>
       </c>
-      <c r="C21" s="63" t="n">
+      <c r="C21" s="62" t="n">
         <v>-46.26</v>
       </c>
-      <c r="D21" s="63" t="n">
+      <c r="D21" s="62" t="n">
         <v>-11.2</v>
       </c>
-      <c r="E21" s="63" t="n">
+      <c r="E21" s="62" t="n">
         <v>-12.69</v>
       </c>
-      <c r="F21" s="65" t="n">
+      <c r="F21" s="64" t="n">
         <v>-781</v>
       </c>
-      <c r="G21" s="66" t="n">
+      <c r="G21" s="65" t="n">
         <v>1082</v>
       </c>
-      <c r="H21" s="66" t="n">
+      <c r="H21" s="65" t="n">
         <v>302</v>
       </c>
-      <c r="I21" s="66" t="n">
+      <c r="I21" s="65" t="n">
         <v>207</v>
       </c>
-      <c r="J21" s="66" t="n">
+      <c r="J21" s="65" t="n">
         <v>485</v>
       </c>
-      <c r="K21" s="65" t="n">
+      <c r="K21" s="64" t="n">
         <v>-7</v>
       </c>
-      <c r="L21" s="66" t="n">
+      <c r="L21" s="65" t="n">
         <v>113</v>
       </c>
-      <c r="M21" s="65" t="n">
+      <c r="M21" s="64" t="n">
         <v>-446</v>
       </c>
-      <c r="N21" s="66" t="n">
+      <c r="N21" s="65" t="n">
         <v>144</v>
       </c>
       <c r="O21" s="30" t="inlineStr"/>
@@ -13553,46 +13548,46 @@
           <t>화학</t>
         </is>
       </c>
-      <c r="B22" s="63" t="n">
+      <c r="B22" s="62" t="n">
         <v>-0.9</v>
       </c>
-      <c r="C22" s="63" t="n">
+      <c r="C22" s="62" t="n">
         <v>-28.5</v>
       </c>
-      <c r="D22" s="63" t="n">
+      <c r="D22" s="62" t="n">
         <v>-2.65</v>
       </c>
-      <c r="E22" s="63" t="n">
+      <c r="E22" s="62" t="n">
         <v>-15.97</v>
       </c>
-      <c r="F22" s="66" t="n">
+      <c r="F22" s="65" t="n">
         <v>1251</v>
       </c>
-      <c r="G22" s="66" t="n">
+      <c r="G22" s="65" t="n">
         <v>906</v>
       </c>
-      <c r="H22" s="66" t="n">
+      <c r="H22" s="65" t="n">
         <v>2156</v>
       </c>
-      <c r="I22" s="66" t="n">
+      <c r="I22" s="65" t="n">
         <v>1864</v>
       </c>
-      <c r="J22" s="65" t="n">
+      <c r="J22" s="64" t="n">
         <v>-793</v>
       </c>
-      <c r="K22" s="65" t="n">
+      <c r="K22" s="64" t="n">
         <v>-302</v>
       </c>
-      <c r="L22" s="66" t="n">
+      <c r="L22" s="65" t="n">
         <v>162</v>
       </c>
-      <c r="M22" s="65" t="n">
+      <c r="M22" s="64" t="n">
         <v>-1633</v>
       </c>
-      <c r="N22" s="65" t="n">
+      <c r="N22" s="64" t="n">
         <v>-524</v>
       </c>
-      <c r="O22" s="67" t="inlineStr">
+      <c r="O22" s="66" t="inlineStr">
         <is>
           <t>수급유입</t>
         </is>
@@ -13604,43 +13599,43 @@
           <t>제조</t>
         </is>
       </c>
-      <c r="B23" s="64" t="n">
+      <c r="B23" s="63" t="n">
         <v>42.23</v>
       </c>
-      <c r="C23" s="63" t="n">
+      <c r="C23" s="62" t="n">
         <v>-12.31</v>
       </c>
-      <c r="D23" s="64" t="n">
+      <c r="D23" s="63" t="n">
         <v>3.96</v>
       </c>
-      <c r="E23" s="63" t="n">
+      <c r="E23" s="62" t="n">
         <v>-17.66</v>
       </c>
-      <c r="F23" s="65" t="n">
+      <c r="F23" s="64" t="n">
         <v>-184035</v>
       </c>
-      <c r="G23" s="66" t="n">
+      <c r="G23" s="65" t="n">
         <v>16384</v>
       </c>
-      <c r="H23" s="65" t="n">
+      <c r="H23" s="64" t="n">
         <v>-167652</v>
       </c>
-      <c r="I23" s="66" t="n">
+      <c r="I23" s="65" t="n">
         <v>24041</v>
       </c>
-      <c r="J23" s="65" t="n">
+      <c r="J23" s="64" t="n">
         <v>-21338</v>
       </c>
-      <c r="K23" s="66" t="n">
+      <c r="K23" s="65" t="n">
         <v>6825</v>
       </c>
-      <c r="L23" s="66" t="n">
+      <c r="L23" s="65" t="n">
         <v>7421</v>
       </c>
-      <c r="M23" s="66" t="n">
+      <c r="M23" s="65" t="n">
         <v>58576</v>
       </c>
-      <c r="N23" s="66" t="n">
+      <c r="N23" s="65" t="n">
         <v>109075</v>
       </c>
       <c r="O23" s="30" t="inlineStr"/>
@@ -13651,43 +13646,43 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="B24" s="64" t="n">
+      <c r="B24" s="63" t="n">
         <v>76.94</v>
       </c>
-      <c r="C24" s="63" t="n">
+      <c r="C24" s="62" t="n">
         <v>-1.37</v>
       </c>
-      <c r="D24" s="64" t="n">
+      <c r="D24" s="63" t="n">
         <v>9.19</v>
       </c>
-      <c r="E24" s="63" t="n">
+      <c r="E24" s="62" t="n">
         <v>-18.08</v>
       </c>
-      <c r="F24" s="65" t="n">
+      <c r="F24" s="64" t="n">
         <v>-171834</v>
       </c>
-      <c r="G24" s="66" t="n">
+      <c r="G24" s="65" t="n">
         <v>3611</v>
       </c>
-      <c r="H24" s="65" t="n">
+      <c r="H24" s="64" t="n">
         <v>-168223</v>
       </c>
-      <c r="I24" s="66" t="n">
+      <c r="I24" s="65" t="n">
         <v>8546</v>
       </c>
-      <c r="J24" s="65" t="n">
+      <c r="J24" s="64" t="n">
         <v>-20000</v>
       </c>
-      <c r="K24" s="66" t="n">
+      <c r="K24" s="65" t="n">
         <v>8823</v>
       </c>
-      <c r="L24" s="66" t="n">
+      <c r="L24" s="65" t="n">
         <v>6676</v>
       </c>
-      <c r="M24" s="66" t="n">
+      <c r="M24" s="65" t="n">
         <v>56240</v>
       </c>
-      <c r="N24" s="66" t="n">
+      <c r="N24" s="65" t="n">
         <v>111983</v>
       </c>
       <c r="O24" s="30" t="inlineStr"/>
@@ -13698,46 +13693,46 @@
           <t>금속</t>
         </is>
       </c>
-      <c r="B25" s="63" t="n">
+      <c r="B25" s="62" t="n">
         <v>-19.75</v>
       </c>
-      <c r="C25" s="63" t="n">
+      <c r="C25" s="62" t="n">
         <v>-45.29</v>
       </c>
-      <c r="D25" s="63" t="n">
+      <c r="D25" s="62" t="n">
         <v>-10.78</v>
       </c>
-      <c r="E25" s="63" t="n">
+      <c r="E25" s="62" t="n">
         <v>-19.57</v>
       </c>
-      <c r="F25" s="65" t="n">
+      <c r="F25" s="64" t="n">
         <v>-1113</v>
       </c>
-      <c r="G25" s="65" t="n">
+      <c r="G25" s="64" t="n">
         <v>-148</v>
       </c>
-      <c r="H25" s="65" t="n">
+      <c r="H25" s="64" t="n">
         <v>-1261</v>
       </c>
-      <c r="I25" s="66" t="n">
+      <c r="I25" s="65" t="n">
         <v>1572</v>
       </c>
-      <c r="J25" s="65" t="n">
+      <c r="J25" s="64" t="n">
         <v>-612</v>
       </c>
-      <c r="K25" s="65" t="n">
+      <c r="K25" s="64" t="n">
         <v>-1102</v>
       </c>
-      <c r="L25" s="65" t="n">
+      <c r="L25" s="64" t="n">
         <v>-9</v>
       </c>
-      <c r="M25" s="66" t="n">
+      <c r="M25" s="65" t="n">
         <v>1283</v>
       </c>
-      <c r="N25" s="65" t="n">
+      <c r="N25" s="64" t="n">
         <v>-22</v>
       </c>
-      <c r="O25" s="56" t="inlineStr">
+      <c r="O25" s="55" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -13749,43 +13744,43 @@
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="B26" s="63" t="n">
+      <c r="B26" s="62" t="n">
         <v>-28.77</v>
       </c>
-      <c r="C26" s="63" t="n">
+      <c r="C26" s="62" t="n">
         <v>-48.71</v>
       </c>
-      <c r="D26" s="63" t="n">
+      <c r="D26" s="62" t="n">
         <v>-24.66</v>
       </c>
-      <c r="E26" s="63" t="n">
+      <c r="E26" s="62" t="n">
         <v>-23.23</v>
       </c>
-      <c r="F26" s="65" t="n">
+      <c r="F26" s="64" t="n">
         <v>-3019</v>
       </c>
-      <c r="G26" s="66" t="n">
+      <c r="G26" s="65" t="n">
         <v>3769</v>
       </c>
-      <c r="H26" s="66" t="n">
+      <c r="H26" s="65" t="n">
         <v>751</v>
       </c>
-      <c r="I26" s="66" t="n">
+      <c r="I26" s="65" t="n">
         <v>8641</v>
       </c>
-      <c r="J26" s="66" t="n">
+      <c r="J26" s="65" t="n">
         <v>263</v>
       </c>
-      <c r="K26" s="65" t="n">
+      <c r="K26" s="64" t="n">
         <v>-5083</v>
       </c>
-      <c r="L26" s="66" t="n">
+      <c r="L26" s="65" t="n">
         <v>17</v>
       </c>
-      <c r="M26" s="66" t="n">
+      <c r="M26" s="65" t="n">
         <v>3906</v>
       </c>
-      <c r="N26" s="65" t="n">
+      <c r="N26" s="64" t="n">
         <v>-4656</v>
       </c>
       <c r="O26" s="30" t="inlineStr"/>
@@ -13796,43 +13791,43 @@
           <t>건설</t>
         </is>
       </c>
-      <c r="B27" s="64" t="n">
+      <c r="B27" s="63" t="n">
         <v>24.1</v>
       </c>
-      <c r="C27" s="63" t="n">
+      <c r="C27" s="62" t="n">
         <v>-48.67</v>
       </c>
-      <c r="D27" s="64" t="n">
+      <c r="D27" s="63" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="E27" s="63" t="n">
+      <c r="E27" s="62" t="n">
         <v>-25.75</v>
       </c>
-      <c r="F27" s="66" t="n">
+      <c r="F27" s="65" t="n">
         <v>2637</v>
       </c>
-      <c r="G27" s="65" t="n">
+      <c r="G27" s="64" t="n">
         <v>-3351</v>
       </c>
-      <c r="H27" s="65" t="n">
+      <c r="H27" s="64" t="n">
         <v>-714</v>
       </c>
-      <c r="I27" s="65" t="n">
+      <c r="I27" s="64" t="n">
         <v>-100</v>
       </c>
-      <c r="J27" s="65" t="n">
+      <c r="J27" s="64" t="n">
         <v>-1227</v>
       </c>
-      <c r="K27" s="65" t="n">
+      <c r="K27" s="64" t="n">
         <v>-1813</v>
       </c>
-      <c r="L27" s="65" t="n">
+      <c r="L27" s="64" t="n">
         <v>-202</v>
       </c>
-      <c r="M27" s="66" t="n">
+      <c r="M27" s="65" t="n">
         <v>718</v>
       </c>
-      <c r="N27" s="65" t="n">
+      <c r="N27" s="64" t="n">
         <v>-4</v>
       </c>
       <c r="O27" s="30" t="inlineStr"/>
@@ -13843,46 +13838,46 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="B28" s="63" t="n">
+      <c r="B28" s="62" t="n">
         <v>-19.23</v>
       </c>
-      <c r="C28" s="63" t="n">
+      <c r="C28" s="62" t="n">
         <v>-53.3</v>
       </c>
-      <c r="D28" s="63" t="n">
+      <c r="D28" s="62" t="n">
         <v>-6.82</v>
       </c>
-      <c r="E28" s="63" t="n">
+      <c r="E28" s="62" t="n">
         <v>-28.6</v>
       </c>
-      <c r="F28" s="65" t="n">
+      <c r="F28" s="64" t="n">
         <v>-5412</v>
       </c>
-      <c r="G28" s="65" t="n">
+      <c r="G28" s="64" t="n">
         <v>-2070</v>
       </c>
-      <c r="H28" s="65" t="n">
+      <c r="H28" s="64" t="n">
         <v>-7483</v>
       </c>
-      <c r="I28" s="66" t="n">
+      <c r="I28" s="65" t="n">
         <v>3181</v>
       </c>
-      <c r="J28" s="65" t="n">
+      <c r="J28" s="64" t="n">
         <v>-3523</v>
       </c>
-      <c r="K28" s="65" t="n">
+      <c r="K28" s="64" t="n">
         <v>-1471</v>
       </c>
-      <c r="L28" s="65" t="n">
+      <c r="L28" s="64" t="n">
         <v>-225</v>
       </c>
-      <c r="M28" s="66" t="n">
+      <c r="M28" s="65" t="n">
         <v>7495</v>
       </c>
-      <c r="N28" s="65" t="n">
+      <c r="N28" s="64" t="n">
         <v>-13</v>
       </c>
-      <c r="O28" s="56" t="inlineStr">
+      <c r="O28" s="55" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -13920,7 +13915,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{D6D909B0-690A-4A80-9283-CB93B956E10D}</x14:id>
+          <x14:id>{C717074C-FD58-47DA-BE1C-18BAC43C94EB}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13934,7 +13929,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{F42944E9-9D49-4FB0-A10A-5B747A0BD6B3}</x14:id>
+          <x14:id>{E8C0BAFD-FBB7-4C2B-BDED-6288E082FFBD}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13948,7 +13943,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{A11BC713-7748-423A-99AB-64297B73A9E8}</x14:id>
+          <x14:id>{851B1B28-291A-442C-A0BD-C691D80A68D8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13962,7 +13957,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{A3F07BFB-2CA8-478A-9157-E932C1E23656}</x14:id>
+          <x14:id>{6E75245C-2F58-4AE5-8131-96F7CBE1A286}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13972,7 +13967,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{D6D909B0-690A-4A80-9283-CB93B956E10D}">
+          <x14:cfRule type="dataBar" id="{C717074C-FD58-47DA-BE1C-18BAC43C94EB}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13985,7 +13980,7 @@
           <xm:sqref>B5:B28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{F42944E9-9D49-4FB0-A10A-5B747A0BD6B3}">
+          <x14:cfRule type="dataBar" id="{E8C0BAFD-FBB7-4C2B-BDED-6288E082FFBD}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13998,7 +13993,7 @@
           <xm:sqref>C5:C28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{A11BC713-7748-423A-99AB-64297B73A9E8}">
+          <x14:cfRule type="dataBar" id="{851B1B28-291A-442C-A0BD-C691D80A68D8}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14011,7 +14006,7 @@
           <xm:sqref>D5:D28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{A3F07BFB-2CA8-478A-9157-E932C1E23656}">
+          <x14:cfRule type="dataBar" id="{6E75245C-2F58-4AE5-8131-96F7CBE1A286}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
